--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="99">
   <si>
     <t>Data category</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>The largest collection of surface ocean carbon observations</t>
+  </si>
+  <si>
+    <t>https://socat.info/wp-content/uploads/2017/06/cropped-socat_cat.png</t>
   </si>
   <si>
     <t>Data categories</t>
@@ -927,7 +930,9 @@
       <c r="M6" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="N6" s="5"/>
+      <c r="N6" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5"/>
@@ -2018,9 +2023,10 @@
     <hyperlink r:id="rId13" ref="N5"/>
     <hyperlink r:id="rId14" ref="D6"/>
     <hyperlink r:id="rId15" ref="E6"/>
+    <hyperlink r:id="rId16" ref="N6"/>
   </hyperlinks>
-  <drawing r:id="rId16"/>
-  <legacyDrawing r:id="rId17"/>
+  <drawing r:id="rId17"/>
+  <legacyDrawing r:id="rId18"/>
 </worksheet>
 </file>
 
@@ -2036,7 +2042,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>7</v>
@@ -2053,10 +2059,10 @@
         <v>51</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>56</v>
@@ -2064,16 +2070,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
@@ -2081,18 +2087,18 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>30</v>
@@ -2100,10 +2106,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>20</v>
@@ -2111,25 +2117,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="D8" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9">
       <c r="D9" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
       <c r="D10" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2168,76 +2174,76 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F1" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="K1" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="N1" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="N1" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>84</v>
-      </c>
       <c r="P1" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V1" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="W1" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="W1" s="8" t="s">
-        <v>90</v>
-      </c>
       <c r="X1" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2">
@@ -2258,7 +2264,7 @@
         <v>https://essd.copernicus.org/articles/13/777/2021/essd-13-777-2021-avatar-web.png</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>6</v>
@@ -2268,7 +2274,7 @@
         <v>monthly</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>5</v>
@@ -2278,7 +2284,7 @@
         <v>1.0°</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>8</v>
@@ -2288,7 +2294,7 @@
         <v>1982 - 2022</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O2" s="8" t="s">
         <v>7</v>
@@ -2314,14 +2320,14 @@
         <v>https://doi.org/10.25921/m5wx-ja34</v>
       </c>
       <c r="U2" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="V2" s="12" t="str">
         <f>product_listing!M2</f>
         <v/>
       </c>
       <c r="W2" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="X2" s="5" t="str">
         <f>product_listing!L2</f>
@@ -2635,9 +2641,9 @@
         <f>product_listing!C6</f>
         <v>Bakker et al. (2016)</v>
       </c>
-      <c r="D6" s="8" t="str">
+      <c r="D6" s="10" t="str">
         <f>product_listing!N6</f>
-        <v/>
+        <v>https://socat.info/wp-content/uploads/2017/06/cropped-socat_cat.png</v>
       </c>
       <c r="E6" s="8" t="str">
         <f t="shared" ref="E6:F6" si="15">if(not(isblank($B6)), E5, "")</f>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="108">
   <si>
     <t>Data category</t>
   </si>
@@ -268,13 +268,40 @@
     <t>https://socat.info/wp-content/uploads/2017/06/cropped-socat_cat.png</t>
   </si>
   <si>
+    <t>GLODAPv2</t>
+  </si>
+  <si>
+    <t>Lauvset et al. (2024)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5194/essd-16-2047-2024</t>
+  </si>
+  <si>
+    <t>https://glodap.info/</t>
+  </si>
+  <si>
+    <t>Water column, Open Ocean</t>
+  </si>
+  <si>
+    <t>1960 - 2024</t>
+  </si>
+  <si>
+    <t>Discrete bottle</t>
+  </si>
+  <si>
+    <t>Biogeochemical data collected from discrete bottle samples</t>
+  </si>
+  <si>
+    <t>Adjustments are applied by comparing data in the deep ocean (&gt;2000 m) using a crossover and inversion method as described by Johnson et al. (2001).</t>
+  </si>
+  <si>
+    <t>https://glodap.info/wp-content/uploads/2017/09/cropped-glodap_logo_trans.png</t>
+  </si>
+  <si>
     <t>Data categories</t>
   </si>
   <si>
     <t>Coastal</t>
-  </si>
-  <si>
-    <t>Discrete bottle</t>
   </si>
   <si>
     <t>Time series stations</t>
@@ -935,13 +962,40 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+      <c r="A7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="N7" s="5"/>
+      <c r="H7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5"/>
@@ -2024,9 +2078,12 @@
     <hyperlink r:id="rId14" ref="D6"/>
     <hyperlink r:id="rId15" ref="E6"/>
     <hyperlink r:id="rId16" ref="N6"/>
+    <hyperlink r:id="rId17" ref="D7"/>
+    <hyperlink r:id="rId18" ref="E7"/>
+    <hyperlink r:id="rId19" ref="N7"/>
   </hyperlinks>
-  <drawing r:id="rId17"/>
-  <legacyDrawing r:id="rId18"/>
+  <drawing r:id="rId20"/>
+  <legacyDrawing r:id="rId21"/>
 </worksheet>
 </file>
 
@@ -2042,7 +2099,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>7</v>
@@ -2059,10 +2116,10 @@
         <v>51</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>56</v>
@@ -2070,16 +2127,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>59</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4">
@@ -2087,18 +2144,18 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>30</v>
@@ -2106,10 +2163,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>20</v>
@@ -2117,25 +2174,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
       <c r="D8" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
       <c r="D9" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
       <c r="D10" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2174,76 +2231,76 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="T1" s="8" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="V1" s="9" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="X1" s="9" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2">
@@ -2264,7 +2321,7 @@
         <v>https://essd.copernicus.org/articles/13/777/2021/essd-13-777-2021-avatar-web.png</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>6</v>
@@ -2274,7 +2331,7 @@
         <v>monthly</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>5</v>
@@ -2284,7 +2341,7 @@
         <v>1.0°</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>8</v>
@@ -2294,7 +2351,7 @@
         <v>1982 - 2022</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O2" s="8" t="s">
         <v>7</v>
@@ -2320,14 +2377,14 @@
         <v>https://doi.org/10.25921/m5wx-ja34</v>
       </c>
       <c r="U2" s="8" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="V2" s="12" t="str">
         <f>product_listing!M2</f>
         <v/>
       </c>
       <c r="W2" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="X2" s="5" t="str">
         <f>product_listing!L2</f>
@@ -2726,27 +2783,27 @@
     <row r="7">
       <c r="A7" s="8" t="str">
         <f>product_listing!A7</f>
-        <v/>
+        <v>Observations</v>
       </c>
       <c r="B7" s="8" t="str">
         <f>product_listing!B7</f>
-        <v/>
+        <v>GLODAPv2</v>
       </c>
       <c r="C7" s="8" t="str">
         <f>product_listing!C7</f>
-        <v/>
-      </c>
-      <c r="D7" s="8" t="str">
+        <v>Lauvset et al. (2024)</v>
+      </c>
+      <c r="D7" s="10" t="str">
         <f>product_listing!N7</f>
-        <v/>
+        <v>https://glodap.info/wp-content/uploads/2017/09/cropped-glodap_logo_trans.png</v>
       </c>
       <c r="E7" s="8" t="str">
         <f t="shared" ref="E7:F7" si="19">if(not(isblank($B7)), E6, "")</f>
-        <v/>
+        <v>fa-solid fa-hourglass-start</v>
       </c>
       <c r="F7" s="8" t="str">
         <f t="shared" si="19"/>
-        <v/>
+        <v>Temporal resolution</v>
       </c>
       <c r="G7" s="8" t="str">
         <f>product_listing!G7</f>
@@ -2754,11 +2811,11 @@
       </c>
       <c r="H7" s="8" t="str">
         <f t="shared" ref="H7:I7" si="20">if(not(isblank($B7)), H6, "")</f>
-        <v/>
+        <v>fa-solid fa-ruler-horizontal</v>
       </c>
       <c r="I7" s="8" t="str">
         <f t="shared" si="20"/>
-        <v/>
+        <v>Spatial resolution</v>
       </c>
       <c r="J7" s="8" t="str">
         <f>product_listing!F7</f>
@@ -2766,55 +2823,55 @@
       </c>
       <c r="K7" s="8" t="str">
         <f t="shared" ref="K7:L7" si="21">if(not(isblank($B7)), K6, "")</f>
-        <v/>
+        <v>fa-solid fa-calendar-days</v>
       </c>
       <c r="L7" s="8" t="str">
         <f t="shared" si="21"/>
-        <v/>
+        <v>Period</v>
       </c>
       <c r="M7" s="8" t="str">
         <f>product_listing!I7</f>
-        <v/>
+        <v>1960 - 2024</v>
       </c>
       <c r="N7" s="8" t="str">
         <f t="shared" ref="N7:O7" si="22">if(not(isblank($B7)), N6, "")</f>
-        <v/>
+        <v>fa-solid fa-globe</v>
       </c>
       <c r="O7" s="8" t="str">
         <f t="shared" si="22"/>
-        <v/>
+        <v>Spatial domains</v>
       </c>
       <c r="P7" s="8" t="str">
         <f>product_listing!H7</f>
-        <v/>
+        <v>Water column, Open Ocean</v>
       </c>
       <c r="Q7" s="8" t="str">
         <f>product_listing!K7</f>
-        <v/>
+        <v>Biogeochemical data collected from discrete bottle samples</v>
       </c>
       <c r="R7" s="8" t="str">
         <f>product_listing!C7</f>
-        <v/>
-      </c>
-      <c r="S7" s="8" t="str">
+        <v>Lauvset et al. (2024)</v>
+      </c>
+      <c r="S7" s="10" t="str">
         <f>product_listing!D7</f>
-        <v/>
-      </c>
-      <c r="T7" s="8" t="str">
+        <v>https://doi.org/10.5194/essd-16-2047-2024</v>
+      </c>
+      <c r="T7" s="10" t="str">
         <f>product_listing!E7</f>
-        <v/>
+        <v>https://glodap.info/</v>
       </c>
       <c r="U7" s="8" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>Highlight</v>
       </c>
       <c r="V7" s="12" t="str">
         <f>product_listing!M7</f>
-        <v/>
+        <v>Adjustments are applied by comparing data in the deep ocean (&gt;2000 m) using a crossover and inversion method as described by Johnson et al. (2001).</v>
       </c>
       <c r="W7" s="8" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>Method</v>
       </c>
       <c r="X7" s="5" t="str">
         <f>product_listing!L7</f>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -385,6 +385,9 @@
     <t>card-detail.content</t>
   </si>
   <si>
+    <t>fa-solid fa-globe</t>
+  </si>
+  <si>
     <t>fa-solid fa-hourglass-start</t>
   </si>
   <si>
@@ -392,9 +395,6 @@
   </si>
   <si>
     <t>fa-solid fa-calendar-days</t>
-  </si>
-  <si>
-    <t>fa-solid fa-globe</t>
   </si>
   <si>
     <t>Highlight</t>
@@ -2217,18 +2217,18 @@
     <col customWidth="1" min="1" max="2" width="17.25"/>
     <col customWidth="1" min="3" max="3" width="20.38"/>
     <col customWidth="1" min="4" max="4" width="20.5"/>
-    <col customWidth="1" min="5" max="5" width="19.75"/>
-    <col customWidth="1" min="6" max="6" width="15.5"/>
-    <col customWidth="1" min="7" max="7" width="15.38"/>
-    <col customWidth="1" min="8" max="8" width="19.88"/>
-    <col customWidth="1" min="9" max="9" width="14.88"/>
+    <col customWidth="1" min="5" max="5" width="16.25"/>
+    <col customWidth="1" min="6" max="6" width="14.88"/>
+    <col customWidth="1" min="7" max="7" width="17.13"/>
+    <col customWidth="1" min="8" max="8" width="19.75"/>
+    <col customWidth="1" min="9" max="9" width="15.5"/>
     <col customWidth="1" min="10" max="10" width="15.38"/>
-    <col customWidth="1" min="11" max="11" width="19.25"/>
+    <col customWidth="1" min="11" max="11" width="19.88"/>
     <col customWidth="1" min="12" max="12" width="14.88"/>
     <col customWidth="1" min="13" max="13" width="15.38"/>
-    <col customWidth="1" min="14" max="14" width="16.25"/>
+    <col customWidth="1" min="14" max="14" width="19.25"/>
     <col customWidth="1" min="15" max="15" width="14.88"/>
-    <col customWidth="1" min="16" max="16" width="17.13"/>
+    <col customWidth="1" min="16" max="16" width="15.38"/>
     <col customWidth="1" min="17" max="17" width="11.63"/>
     <col customWidth="1" min="18" max="18" width="20.38"/>
     <col customWidth="1" min="19" max="19" width="15.0"/>
@@ -2332,41 +2332,41 @@
         <v>102</v>
       </c>
       <c r="F2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="9" t="str">
+        <f>product_listing!H2</f>
+        <v>Open Ocean, Surface</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="9" t="str">
+      <c r="J2" s="9" t="str">
         <f>product_listing!G2</f>
         <v>monthly</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="I2" s="9" t="s">
+      <c r="K2" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="L2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="12" t="str">
+      <c r="M2" s="12" t="str">
         <f>product_listing!F2</f>
         <v>1.0°</v>
       </c>
-      <c r="K2" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="N2" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="9" t="str">
+      <c r="P2" s="9" t="str">
         <f>product_listing!I2</f>
         <v>1982 - 2022</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="P2" s="9" t="str">
-        <f>product_listing!H2</f>
-        <v>Open Ocean, Surface</v>
       </c>
       <c r="Q2" s="9" t="str">
         <f>product_listing!K2</f>
@@ -2418,51 +2418,51 @@
       </c>
       <c r="E3" s="9" t="str">
         <f t="shared" ref="E3:F3" si="1">if(not(isblank($B3)), E2, "")</f>
-        <v>fa-solid fa-hourglass-start</v>
+        <v>fa-solid fa-globe</v>
       </c>
       <c r="F3" s="9" t="str">
         <f t="shared" si="1"/>
+        <v>Spatial domains</v>
+      </c>
+      <c r="G3" s="9" t="str">
+        <f>product_listing!H3</f>
+        <v>Open Ocean, Surface</v>
+      </c>
+      <c r="H3" s="9" t="str">
+        <f t="shared" ref="H3:I3" si="2">if(not(isblank($B3)), H2, "")</f>
+        <v>fa-solid fa-hourglass-start</v>
+      </c>
+      <c r="I3" s="9" t="str">
+        <f t="shared" si="2"/>
         <v>Temporal resolution</v>
       </c>
-      <c r="G3" s="9" t="str">
+      <c r="J3" s="9" t="str">
         <f>product_listing!G3</f>
         <v>8-daily</v>
       </c>
-      <c r="H3" s="9" t="str">
-        <f t="shared" ref="H3:I3" si="2">if(not(isblank($B3)), H2, "")</f>
+      <c r="K3" s="9" t="str">
+        <f t="shared" ref="K3:L3" si="3">if(not(isblank($B3)), K2, "")</f>
         <v>fa-solid fa-ruler-horizontal</v>
       </c>
-      <c r="I3" s="9" t="str">
-        <f t="shared" si="2"/>
+      <c r="L3" s="9" t="str">
+        <f t="shared" si="3"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="J3" s="14" t="str">
+      <c r="M3" s="14" t="str">
         <f>product_listing!F3</f>
         <v>0.25°</v>
       </c>
-      <c r="K3" s="9" t="str">
-        <f t="shared" ref="K3:L3" si="3">if(not(isblank($B3)), K2, "")</f>
+      <c r="N3" s="9" t="str">
+        <f t="shared" ref="N3:O3" si="4">if(not(isblank($B3)), N2, "")</f>
         <v>fa-solid fa-calendar-days</v>
       </c>
-      <c r="L3" s="9" t="str">
-        <f t="shared" si="3"/>
+      <c r="O3" s="9" t="str">
+        <f t="shared" si="4"/>
         <v>Period</v>
       </c>
-      <c r="M3" s="9" t="str">
+      <c r="P3" s="9" t="str">
         <f>product_listing!I3</f>
         <v>1982 - 2024</v>
-      </c>
-      <c r="N3" s="9" t="str">
-        <f t="shared" ref="N3:O3" si="4">if(not(isblank($B3)), N2, "")</f>
-        <v>fa-solid fa-globe</v>
-      </c>
-      <c r="O3" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v>Spatial domains</v>
-      </c>
-      <c r="P3" s="9" t="str">
-        <f>product_listing!H3</f>
-        <v>Open Ocean, Surface</v>
       </c>
       <c r="Q3" s="9" t="str">
         <f>product_listing!K3</f>
@@ -2516,51 +2516,51 @@
       </c>
       <c r="E4" s="9" t="str">
         <f t="shared" ref="E4:F4" si="5">if(not(isblank($B4)), E3, "")</f>
-        <v>fa-solid fa-hourglass-start</v>
+        <v>fa-solid fa-globe</v>
       </c>
       <c r="F4" s="9" t="str">
         <f t="shared" si="5"/>
+        <v>Spatial domains</v>
+      </c>
+      <c r="G4" s="9" t="str">
+        <f>product_listing!H4</f>
+        <v>Open Ocean, Surface</v>
+      </c>
+      <c r="H4" s="9" t="str">
+        <f t="shared" ref="H4:I4" si="6">if(not(isblank($B4)), H3, "")</f>
+        <v>fa-solid fa-hourglass-start</v>
+      </c>
+      <c r="I4" s="9" t="str">
+        <f t="shared" si="6"/>
         <v>Temporal resolution</v>
       </c>
-      <c r="G4" s="9" t="str">
+      <c r="J4" s="9" t="str">
         <f>product_listing!G4</f>
         <v>climatology, monthly</v>
       </c>
-      <c r="H4" s="9" t="str">
-        <f t="shared" ref="H4:I4" si="6">if(not(isblank($B4)), H3, "")</f>
+      <c r="K4" s="9" t="str">
+        <f t="shared" ref="K4:L4" si="7">if(not(isblank($B4)), K3, "")</f>
         <v>fa-solid fa-ruler-horizontal</v>
       </c>
-      <c r="I4" s="9" t="str">
-        <f t="shared" si="6"/>
+      <c r="L4" s="9" t="str">
+        <f t="shared" si="7"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="J4" s="12" t="str">
+      <c r="M4" s="12" t="str">
         <f>product_listing!F4</f>
         <v>1.0°</v>
       </c>
-      <c r="K4" s="9" t="str">
-        <f t="shared" ref="K4:L4" si="7">if(not(isblank($B4)), K3, "")</f>
-        <v>fa-solid fa-calendar-days</v>
-      </c>
-      <c r="L4" s="9" t="str">
-        <f t="shared" si="7"/>
-        <v>Period</v>
-      </c>
-      <c r="M4" s="9" t="str">
-        <f>product_listing!I4</f>
-        <v/>
-      </c>
       <c r="N4" s="9" t="str">
         <f t="shared" ref="N4:O4" si="8">if(not(isblank($B4)), N3, "")</f>
-        <v>fa-solid fa-globe</v>
+        <v>fa-solid fa-calendar-days</v>
       </c>
       <c r="O4" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Spatial domains</v>
+        <v>Period</v>
       </c>
       <c r="P4" s="9" t="str">
-        <f>product_listing!H4</f>
-        <v>Open Ocean, Surface</v>
+        <f>product_listing!I4</f>
+        <v/>
       </c>
       <c r="Q4" s="9" t="str">
         <f>product_listing!K4</f>
@@ -2614,51 +2614,51 @@
       </c>
       <c r="E5" s="9" t="str">
         <f t="shared" ref="E5:F5" si="11">if(not(isblank($B5)), E4, "")</f>
-        <v>fa-solid fa-hourglass-start</v>
+        <v>fa-solid fa-globe</v>
       </c>
       <c r="F5" s="9" t="str">
         <f t="shared" si="11"/>
+        <v>Spatial domains</v>
+      </c>
+      <c r="G5" s="9" t="str">
+        <f>product_listing!H5</f>
+        <v>Surface, Open Ocean</v>
+      </c>
+      <c r="H5" s="9" t="str">
+        <f t="shared" ref="H5:I5" si="12">if(not(isblank($B5)), H4, "")</f>
+        <v>fa-solid fa-hourglass-start</v>
+      </c>
+      <c r="I5" s="9" t="str">
+        <f t="shared" si="12"/>
         <v>Temporal resolution</v>
       </c>
-      <c r="G5" s="9" t="str">
+      <c r="J5" s="9" t="str">
         <f>product_listing!G5</f>
         <v>monthly</v>
       </c>
-      <c r="H5" s="9" t="str">
-        <f t="shared" ref="H5:I5" si="12">if(not(isblank($B5)), H4, "")</f>
+      <c r="K5" s="9" t="str">
+        <f t="shared" ref="K5:L5" si="13">if(not(isblank($B5)), K4, "")</f>
         <v>fa-solid fa-ruler-horizontal</v>
       </c>
-      <c r="I5" s="9" t="str">
-        <f t="shared" si="12"/>
+      <c r="L5" s="9" t="str">
+        <f t="shared" si="13"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="J5" s="12" t="str">
+      <c r="M5" s="12" t="str">
         <f>product_listing!F5</f>
         <v>1.0°</v>
       </c>
-      <c r="K5" s="9" t="str">
-        <f t="shared" ref="K5:L5" si="13">if(not(isblank($B5)), K4, "")</f>
+      <c r="N5" s="9" t="str">
+        <f t="shared" ref="N5:O5" si="14">if(not(isblank($B5)), N4, "")</f>
         <v>fa-solid fa-calendar-days</v>
       </c>
-      <c r="L5" s="9" t="str">
-        <f t="shared" si="13"/>
+      <c r="O5" s="9" t="str">
+        <f t="shared" si="14"/>
         <v>Period</v>
       </c>
-      <c r="M5" s="9" t="str">
+      <c r="P5" s="9" t="str">
         <f>product_listing!I5</f>
         <v>1982 - 2024</v>
-      </c>
-      <c r="N5" s="9" t="str">
-        <f t="shared" ref="N5:O5" si="14">if(not(isblank($B5)), N4, "")</f>
-        <v>fa-solid fa-globe</v>
-      </c>
-      <c r="O5" s="9" t="str">
-        <f t="shared" si="14"/>
-        <v>Spatial domains</v>
-      </c>
-      <c r="P5" s="9" t="str">
-        <f>product_listing!H5</f>
-        <v>Surface, Open Ocean</v>
       </c>
       <c r="Q5" s="9" t="str">
         <f>product_listing!K5</f>
@@ -2712,51 +2712,51 @@
       </c>
       <c r="E6" s="9" t="str">
         <f t="shared" ref="E6:F6" si="15">if(not(isblank($B6)), E5, "")</f>
-        <v>fa-solid fa-hourglass-start</v>
+        <v>fa-solid fa-globe</v>
       </c>
       <c r="F6" s="9" t="str">
         <f t="shared" si="15"/>
+        <v>Spatial domains</v>
+      </c>
+      <c r="G6" s="9" t="str">
+        <f>product_listing!H6</f>
+        <v>Surface, Open Ocean, Coastal</v>
+      </c>
+      <c r="H6" s="9" t="str">
+        <f t="shared" ref="H6:I6" si="16">if(not(isblank($B6)), H5, "")</f>
+        <v>fa-solid fa-hourglass-start</v>
+      </c>
+      <c r="I6" s="9" t="str">
+        <f t="shared" si="16"/>
         <v>Temporal resolution</v>
       </c>
-      <c r="G6" s="9" t="str">
+      <c r="J6" s="9" t="str">
         <f>product_listing!G6</f>
         <v>continuous</v>
       </c>
-      <c r="H6" s="9" t="str">
-        <f t="shared" ref="H6:I6" si="16">if(not(isblank($B6)), H5, "")</f>
-        <v>fa-solid fa-ruler-horizontal</v>
-      </c>
-      <c r="I6" s="9" t="str">
-        <f t="shared" si="16"/>
-        <v>Spatial resolution</v>
-      </c>
-      <c r="J6" s="9" t="str">
-        <f>product_listing!F6</f>
-        <v/>
-      </c>
       <c r="K6" s="9" t="str">
         <f t="shared" ref="K6:L6" si="17">if(not(isblank($B6)), K5, "")</f>
-        <v>fa-solid fa-calendar-days</v>
+        <v>fa-solid fa-ruler-horizontal</v>
       </c>
       <c r="L6" s="9" t="str">
         <f t="shared" si="17"/>
+        <v>Spatial resolution</v>
+      </c>
+      <c r="M6" s="9" t="str">
+        <f>product_listing!F6</f>
+        <v/>
+      </c>
+      <c r="N6" s="9" t="str">
+        <f t="shared" ref="N6:O6" si="18">if(not(isblank($B6)), N5, "")</f>
+        <v>fa-solid fa-calendar-days</v>
+      </c>
+      <c r="O6" s="9" t="str">
+        <f t="shared" si="18"/>
         <v>Period</v>
       </c>
-      <c r="M6" s="9" t="str">
+      <c r="P6" s="9" t="str">
         <f>product_listing!I6</f>
         <v>1960 - 2025</v>
-      </c>
-      <c r="N6" s="9" t="str">
-        <f t="shared" ref="N6:O6" si="18">if(not(isblank($B6)), N5, "")</f>
-        <v>fa-solid fa-globe</v>
-      </c>
-      <c r="O6" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v>Spatial domains</v>
-      </c>
-      <c r="P6" s="9" t="str">
-        <f>product_listing!H6</f>
-        <v>Surface, Open Ocean, Coastal</v>
       </c>
       <c r="Q6" s="9" t="str">
         <f>product_listing!K6</f>
@@ -2807,51 +2807,51 @@
       </c>
       <c r="E7" s="9" t="str">
         <f t="shared" ref="E7:F7" si="19">if(not(isblank($B7)), E6, "")</f>
-        <v>fa-solid fa-hourglass-start</v>
+        <v>fa-solid fa-globe</v>
       </c>
       <c r="F7" s="9" t="str">
         <f t="shared" si="19"/>
-        <v>Temporal resolution</v>
+        <v>Spatial domains</v>
       </c>
       <c r="G7" s="9" t="str">
-        <f>product_listing!G7</f>
-        <v/>
+        <f>product_listing!H7</f>
+        <v>Water column, Open Ocean</v>
       </c>
       <c r="H7" s="9" t="str">
         <f t="shared" ref="H7:I7" si="20">if(not(isblank($B7)), H6, "")</f>
-        <v>fa-solid fa-ruler-horizontal</v>
+        <v>fa-solid fa-hourglass-start</v>
       </c>
       <c r="I7" s="9" t="str">
         <f t="shared" si="20"/>
-        <v>Spatial resolution</v>
+        <v>Temporal resolution</v>
       </c>
       <c r="J7" s="9" t="str">
-        <f>product_listing!F7</f>
+        <f>product_listing!G7</f>
         <v/>
       </c>
       <c r="K7" s="9" t="str">
         <f t="shared" ref="K7:L7" si="21">if(not(isblank($B7)), K6, "")</f>
-        <v>fa-solid fa-calendar-days</v>
+        <v>fa-solid fa-ruler-horizontal</v>
       </c>
       <c r="L7" s="9" t="str">
         <f t="shared" si="21"/>
+        <v>Spatial resolution</v>
+      </c>
+      <c r="M7" s="9" t="str">
+        <f>product_listing!F7</f>
+        <v/>
+      </c>
+      <c r="N7" s="9" t="str">
+        <f t="shared" ref="N7:O7" si="22">if(not(isblank($B7)), N6, "")</f>
+        <v>fa-solid fa-calendar-days</v>
+      </c>
+      <c r="O7" s="9" t="str">
+        <f t="shared" si="22"/>
         <v>Period</v>
       </c>
-      <c r="M7" s="9" t="str">
+      <c r="P7" s="9" t="str">
         <f>product_listing!I7</f>
         <v>1960 - 2024</v>
-      </c>
-      <c r="N7" s="9" t="str">
-        <f t="shared" ref="N7:O7" si="22">if(not(isblank($B7)), N6, "")</f>
-        <v>fa-solid fa-globe</v>
-      </c>
-      <c r="O7" s="9" t="str">
-        <f t="shared" si="22"/>
-        <v>Spatial domains</v>
-      </c>
-      <c r="P7" s="9" t="str">
-        <f>product_listing!H7</f>
-        <v>Water column, Open Ocean</v>
       </c>
       <c r="Q7" s="9" t="str">
         <f>product_listing!K7</f>
@@ -2912,7 +2912,7 @@
         <v/>
       </c>
       <c r="G8" s="9" t="str">
-        <f>product_listing!G8</f>
+        <f>product_listing!H8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="str">
@@ -2924,7 +2924,7 @@
         <v/>
       </c>
       <c r="J8" s="9" t="str">
-        <f>product_listing!F8</f>
+        <f>product_listing!G8</f>
         <v/>
       </c>
       <c r="K8" s="9" t="str">
@@ -2936,7 +2936,7 @@
         <v/>
       </c>
       <c r="M8" s="9" t="str">
-        <f>product_listing!I8</f>
+        <f>product_listing!F8</f>
         <v/>
       </c>
       <c r="N8" s="9" t="str">
@@ -2948,7 +2948,7 @@
         <v/>
       </c>
       <c r="P8" s="9" t="str">
-        <f>product_listing!H8</f>
+        <f>product_listing!I8</f>
         <v/>
       </c>
       <c r="Q8" s="9" t="str">
@@ -3010,7 +3010,7 @@
         <v/>
       </c>
       <c r="G9" s="9" t="str">
-        <f>product_listing!G9</f>
+        <f>product_listing!H9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="str">
@@ -3022,7 +3022,7 @@
         <v/>
       </c>
       <c r="J9" s="9" t="str">
-        <f>product_listing!F9</f>
+        <f>product_listing!G9</f>
         <v/>
       </c>
       <c r="K9" s="9" t="str">
@@ -3034,7 +3034,7 @@
         <v/>
       </c>
       <c r="M9" s="9" t="str">
-        <f>product_listing!I9</f>
+        <f>product_listing!F9</f>
         <v/>
       </c>
       <c r="N9" s="9" t="str">
@@ -3046,7 +3046,7 @@
         <v/>
       </c>
       <c r="P9" s="9" t="str">
-        <f>product_listing!H9</f>
+        <f>product_listing!I9</f>
         <v/>
       </c>
       <c r="Q9" s="9" t="str">
@@ -3108,7 +3108,7 @@
         <v/>
       </c>
       <c r="G10" s="9" t="str">
-        <f>product_listing!G10</f>
+        <f>product_listing!H10</f>
         <v/>
       </c>
       <c r="H10" s="9" t="str">
@@ -3120,7 +3120,7 @@
         <v/>
       </c>
       <c r="J10" s="9" t="str">
-        <f>product_listing!F10</f>
+        <f>product_listing!G10</f>
         <v/>
       </c>
       <c r="K10" s="9" t="str">
@@ -3132,7 +3132,7 @@
         <v/>
       </c>
       <c r="M10" s="9" t="str">
-        <f>product_listing!I10</f>
+        <f>product_listing!F10</f>
         <v/>
       </c>
       <c r="N10" s="9" t="str">
@@ -3144,7 +3144,7 @@
         <v/>
       </c>
       <c r="P10" s="9" t="str">
-        <f>product_listing!H10</f>
+        <f>product_listing!I10</f>
         <v/>
       </c>
       <c r="Q10" s="9" t="str">
@@ -3206,7 +3206,7 @@
         <v/>
       </c>
       <c r="G11" s="9" t="str">
-        <f>product_listing!G11</f>
+        <f>product_listing!H11</f>
         <v/>
       </c>
       <c r="H11" s="9" t="str">
@@ -3218,7 +3218,7 @@
         <v/>
       </c>
       <c r="J11" s="9" t="str">
-        <f>product_listing!F11</f>
+        <f>product_listing!G11</f>
         <v/>
       </c>
       <c r="K11" s="9" t="str">
@@ -3230,7 +3230,7 @@
         <v/>
       </c>
       <c r="M11" s="9" t="str">
-        <f>product_listing!I11</f>
+        <f>product_listing!F11</f>
         <v/>
       </c>
       <c r="N11" s="9" t="str">
@@ -3242,7 +3242,7 @@
         <v/>
       </c>
       <c r="P11" s="9" t="str">
-        <f>product_listing!H11</f>
+        <f>product_listing!I11</f>
         <v/>
       </c>
       <c r="Q11" s="9" t="str">
@@ -3304,7 +3304,7 @@
         <v/>
       </c>
       <c r="G12" s="9" t="str">
-        <f>product_listing!G12</f>
+        <f>product_listing!H12</f>
         <v/>
       </c>
       <c r="H12" s="9" t="str">
@@ -3316,7 +3316,7 @@
         <v/>
       </c>
       <c r="J12" s="9" t="str">
-        <f>product_listing!F12</f>
+        <f>product_listing!G12</f>
         <v/>
       </c>
       <c r="K12" s="9" t="str">
@@ -3328,7 +3328,7 @@
         <v/>
       </c>
       <c r="M12" s="9" t="str">
-        <f>product_listing!I12</f>
+        <f>product_listing!F12</f>
         <v/>
       </c>
       <c r="N12" s="9" t="str">
@@ -3340,7 +3340,7 @@
         <v/>
       </c>
       <c r="P12" s="9" t="str">
-        <f>product_listing!H12</f>
+        <f>product_listing!I12</f>
         <v/>
       </c>
       <c r="Q12" s="9" t="str">
@@ -3402,7 +3402,7 @@
         <v/>
       </c>
       <c r="G13" s="9" t="str">
-        <f>product_listing!G13</f>
+        <f>product_listing!H13</f>
         <v/>
       </c>
       <c r="H13" s="9" t="str">
@@ -3414,7 +3414,7 @@
         <v/>
       </c>
       <c r="J13" s="9" t="str">
-        <f>product_listing!F13</f>
+        <f>product_listing!G13</f>
         <v/>
       </c>
       <c r="K13" s="9" t="str">
@@ -3426,7 +3426,7 @@
         <v/>
       </c>
       <c r="M13" s="9" t="str">
-        <f>product_listing!I13</f>
+        <f>product_listing!F13</f>
         <v/>
       </c>
       <c r="N13" s="9" t="str">
@@ -3438,7 +3438,7 @@
         <v/>
       </c>
       <c r="P13" s="9" t="str">
-        <f>product_listing!H13</f>
+        <f>product_listing!I13</f>
         <v/>
       </c>
       <c r="Q13" s="9" t="str">
@@ -3500,7 +3500,7 @@
         <v/>
       </c>
       <c r="G14" s="9" t="str">
-        <f>product_listing!G14</f>
+        <f>product_listing!H14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="str">
@@ -3512,7 +3512,7 @@
         <v/>
       </c>
       <c r="J14" s="9" t="str">
-        <f>product_listing!F14</f>
+        <f>product_listing!G14</f>
         <v/>
       </c>
       <c r="K14" s="9" t="str">
@@ -3524,7 +3524,7 @@
         <v/>
       </c>
       <c r="M14" s="9" t="str">
-        <f>product_listing!I14</f>
+        <f>product_listing!F14</f>
         <v/>
       </c>
       <c r="N14" s="9" t="str">
@@ -3536,7 +3536,7 @@
         <v/>
       </c>
       <c r="P14" s="9" t="str">
-        <f>product_listing!H14</f>
+        <f>product_listing!I14</f>
         <v/>
       </c>
       <c r="Q14" s="9" t="str">
@@ -3598,7 +3598,7 @@
         <v/>
       </c>
       <c r="G15" s="9" t="str">
-        <f>product_listing!G15</f>
+        <f>product_listing!H15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="str">
@@ -3610,7 +3610,7 @@
         <v/>
       </c>
       <c r="J15" s="9" t="str">
-        <f>product_listing!F15</f>
+        <f>product_listing!G15</f>
         <v/>
       </c>
       <c r="K15" s="9" t="str">
@@ -3622,7 +3622,7 @@
         <v/>
       </c>
       <c r="M15" s="9" t="str">
-        <f>product_listing!I15</f>
+        <f>product_listing!F15</f>
         <v/>
       </c>
       <c r="N15" s="9" t="str">
@@ -3634,7 +3634,7 @@
         <v/>
       </c>
       <c r="P15" s="9" t="str">
-        <f>product_listing!H15</f>
+        <f>product_listing!I15</f>
         <v/>
       </c>
       <c r="Q15" s="9" t="str">
@@ -3696,7 +3696,7 @@
         <v/>
       </c>
       <c r="G16" s="9" t="str">
-        <f>product_listing!G16</f>
+        <f>product_listing!H16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="str">
@@ -3708,7 +3708,7 @@
         <v/>
       </c>
       <c r="J16" s="9" t="str">
-        <f>product_listing!F16</f>
+        <f>product_listing!G16</f>
         <v/>
       </c>
       <c r="K16" s="9" t="str">
@@ -3720,7 +3720,7 @@
         <v/>
       </c>
       <c r="M16" s="9" t="str">
-        <f>product_listing!I16</f>
+        <f>product_listing!F16</f>
         <v/>
       </c>
       <c r="N16" s="9" t="str">
@@ -3732,7 +3732,7 @@
         <v/>
       </c>
       <c r="P16" s="9" t="str">
-        <f>product_listing!H16</f>
+        <f>product_listing!I16</f>
         <v/>
       </c>
       <c r="Q16" s="9" t="str">
@@ -3794,7 +3794,7 @@
         <v/>
       </c>
       <c r="G17" s="9" t="str">
-        <f>product_listing!G17</f>
+        <f>product_listing!H17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="str">
@@ -3806,7 +3806,7 @@
         <v/>
       </c>
       <c r="J17" s="9" t="str">
-        <f>product_listing!F17</f>
+        <f>product_listing!G17</f>
         <v/>
       </c>
       <c r="K17" s="9" t="str">
@@ -3818,7 +3818,7 @@
         <v/>
       </c>
       <c r="M17" s="9" t="str">
-        <f>product_listing!I17</f>
+        <f>product_listing!F17</f>
         <v/>
       </c>
       <c r="N17" s="9" t="str">
@@ -3830,7 +3830,7 @@
         <v/>
       </c>
       <c r="P17" s="9" t="str">
-        <f>product_listing!H17</f>
+        <f>product_listing!I17</f>
         <v/>
       </c>
       <c r="Q17" s="9" t="str">
@@ -3892,7 +3892,7 @@
         <v/>
       </c>
       <c r="G18" s="9" t="str">
-        <f>product_listing!G18</f>
+        <f>product_listing!H18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="str">
@@ -3904,7 +3904,7 @@
         <v/>
       </c>
       <c r="J18" s="9" t="str">
-        <f>product_listing!F18</f>
+        <f>product_listing!G18</f>
         <v/>
       </c>
       <c r="K18" s="9" t="str">
@@ -3916,7 +3916,7 @@
         <v/>
       </c>
       <c r="M18" s="9" t="str">
-        <f>product_listing!I18</f>
+        <f>product_listing!F18</f>
         <v/>
       </c>
       <c r="N18" s="9" t="str">
@@ -3928,7 +3928,7 @@
         <v/>
       </c>
       <c r="P18" s="9" t="str">
-        <f>product_listing!H18</f>
+        <f>product_listing!I18</f>
         <v/>
       </c>
       <c r="Q18" s="9" t="str">
@@ -3990,7 +3990,7 @@
         <v/>
       </c>
       <c r="G19" s="9" t="str">
-        <f>product_listing!G19</f>
+        <f>product_listing!H19</f>
         <v/>
       </c>
       <c r="H19" s="9" t="str">
@@ -4002,7 +4002,7 @@
         <v/>
       </c>
       <c r="J19" s="9" t="str">
-        <f>product_listing!F19</f>
+        <f>product_listing!G19</f>
         <v/>
       </c>
       <c r="K19" s="9" t="str">
@@ -4014,7 +4014,7 @@
         <v/>
       </c>
       <c r="M19" s="9" t="str">
-        <f>product_listing!I19</f>
+        <f>product_listing!F19</f>
         <v/>
       </c>
       <c r="N19" s="9" t="str">
@@ -4026,7 +4026,7 @@
         <v/>
       </c>
       <c r="P19" s="9" t="str">
-        <f>product_listing!H19</f>
+        <f>product_listing!I19</f>
         <v/>
       </c>
       <c r="Q19" s="9" t="str">
@@ -4088,7 +4088,7 @@
         <v/>
       </c>
       <c r="G20" s="9" t="str">
-        <f>product_listing!G20</f>
+        <f>product_listing!H20</f>
         <v/>
       </c>
       <c r="H20" s="9" t="str">
@@ -4100,7 +4100,7 @@
         <v/>
       </c>
       <c r="J20" s="9" t="str">
-        <f>product_listing!F20</f>
+        <f>product_listing!G20</f>
         <v/>
       </c>
       <c r="K20" s="9" t="str">
@@ -4112,7 +4112,7 @@
         <v/>
       </c>
       <c r="M20" s="9" t="str">
-        <f>product_listing!I20</f>
+        <f>product_listing!F20</f>
         <v/>
       </c>
       <c r="N20" s="9" t="str">
@@ -4124,7 +4124,7 @@
         <v/>
       </c>
       <c r="P20" s="9" t="str">
-        <f>product_listing!H20</f>
+        <f>product_listing!I20</f>
         <v/>
       </c>
       <c r="Q20" s="9" t="str">
@@ -4186,7 +4186,7 @@
         <v/>
       </c>
       <c r="G21" s="9" t="str">
-        <f>product_listing!G21</f>
+        <f>product_listing!H21</f>
         <v/>
       </c>
       <c r="H21" s="9" t="str">
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="J21" s="9" t="str">
-        <f>product_listing!F21</f>
+        <f>product_listing!G21</f>
         <v/>
       </c>
       <c r="K21" s="9" t="str">
@@ -4210,7 +4210,7 @@
         <v/>
       </c>
       <c r="M21" s="9" t="str">
-        <f>product_listing!I21</f>
+        <f>product_listing!F21</f>
         <v/>
       </c>
       <c r="N21" s="9" t="str">
@@ -4222,7 +4222,7 @@
         <v/>
       </c>
       <c r="P21" s="9" t="str">
-        <f>product_listing!H21</f>
+        <f>product_listing!I21</f>
         <v/>
       </c>
       <c r="Q21" s="9" t="str">
@@ -4284,7 +4284,7 @@
         <v/>
       </c>
       <c r="G22" s="9" t="str">
-        <f>product_listing!G22</f>
+        <f>product_listing!H22</f>
         <v/>
       </c>
       <c r="H22" s="9" t="str">
@@ -4296,7 +4296,7 @@
         <v/>
       </c>
       <c r="J22" s="9" t="str">
-        <f>product_listing!F22</f>
+        <f>product_listing!G22</f>
         <v/>
       </c>
       <c r="K22" s="9" t="str">
@@ -4308,7 +4308,7 @@
         <v/>
       </c>
       <c r="M22" s="9" t="str">
-        <f>product_listing!I22</f>
+        <f>product_listing!F22</f>
         <v/>
       </c>
       <c r="N22" s="9" t="str">
@@ -4320,7 +4320,7 @@
         <v/>
       </c>
       <c r="P22" s="9" t="str">
-        <f>product_listing!H22</f>
+        <f>product_listing!I22</f>
         <v/>
       </c>
       <c r="Q22" s="9" t="str">
@@ -4382,7 +4382,7 @@
         <v/>
       </c>
       <c r="G23" s="9" t="str">
-        <f>product_listing!G23</f>
+        <f>product_listing!H23</f>
         <v/>
       </c>
       <c r="H23" s="9" t="str">
@@ -4394,7 +4394,7 @@
         <v/>
       </c>
       <c r="J23" s="9" t="str">
-        <f>product_listing!F23</f>
+        <f>product_listing!G23</f>
         <v/>
       </c>
       <c r="K23" s="9" t="str">
@@ -4406,7 +4406,7 @@
         <v/>
       </c>
       <c r="M23" s="9" t="str">
-        <f>product_listing!I23</f>
+        <f>product_listing!F23</f>
         <v/>
       </c>
       <c r="N23" s="9" t="str">
@@ -4418,7 +4418,7 @@
         <v/>
       </c>
       <c r="P23" s="9" t="str">
-        <f>product_listing!H23</f>
+        <f>product_listing!I23</f>
         <v/>
       </c>
       <c r="Q23" s="9" t="str">
@@ -4480,7 +4480,7 @@
         <v/>
       </c>
       <c r="G24" s="9" t="str">
-        <f>product_listing!G24</f>
+        <f>product_listing!H24</f>
         <v/>
       </c>
       <c r="H24" s="9" t="str">
@@ -4492,7 +4492,7 @@
         <v/>
       </c>
       <c r="J24" s="9" t="str">
-        <f>product_listing!F24</f>
+        <f>product_listing!G24</f>
         <v/>
       </c>
       <c r="K24" s="9" t="str">
@@ -4504,7 +4504,7 @@
         <v/>
       </c>
       <c r="M24" s="9" t="str">
-        <f>product_listing!I24</f>
+        <f>product_listing!F24</f>
         <v/>
       </c>
       <c r="N24" s="9" t="str">
@@ -4516,7 +4516,7 @@
         <v/>
       </c>
       <c r="P24" s="9" t="str">
-        <f>product_listing!H24</f>
+        <f>product_listing!I24</f>
         <v/>
       </c>
       <c r="Q24" s="9" t="str">
@@ -4578,7 +4578,7 @@
         <v/>
       </c>
       <c r="G25" s="9" t="str">
-        <f>product_listing!G25</f>
+        <f>product_listing!H25</f>
         <v/>
       </c>
       <c r="H25" s="9" t="str">
@@ -4590,7 +4590,7 @@
         <v/>
       </c>
       <c r="J25" s="9" t="str">
-        <f>product_listing!F25</f>
+        <f>product_listing!G25</f>
         <v/>
       </c>
       <c r="K25" s="9" t="str">
@@ -4602,7 +4602,7 @@
         <v/>
       </c>
       <c r="M25" s="9" t="str">
-        <f>product_listing!I25</f>
+        <f>product_listing!F25</f>
         <v/>
       </c>
       <c r="N25" s="9" t="str">
@@ -4614,7 +4614,7 @@
         <v/>
       </c>
       <c r="P25" s="9" t="str">
-        <f>product_listing!H25</f>
+        <f>product_listing!I25</f>
         <v/>
       </c>
       <c r="Q25" s="9" t="str">
@@ -4676,7 +4676,7 @@
         <v/>
       </c>
       <c r="G26" s="9" t="str">
-        <f>product_listing!G26</f>
+        <f>product_listing!H26</f>
         <v/>
       </c>
       <c r="H26" s="9" t="str">
@@ -4688,7 +4688,7 @@
         <v/>
       </c>
       <c r="J26" s="9" t="str">
-        <f>product_listing!F26</f>
+        <f>product_listing!G26</f>
         <v/>
       </c>
       <c r="K26" s="9" t="str">
@@ -4700,7 +4700,7 @@
         <v/>
       </c>
       <c r="M26" s="9" t="str">
-        <f>product_listing!I26</f>
+        <f>product_listing!F26</f>
         <v/>
       </c>
       <c r="N26" s="9" t="str">
@@ -4712,7 +4712,7 @@
         <v/>
       </c>
       <c r="P26" s="9" t="str">
-        <f>product_listing!H26</f>
+        <f>product_listing!I26</f>
         <v/>
       </c>
       <c r="Q26" s="9" t="str">
@@ -4774,7 +4774,7 @@
         <v/>
       </c>
       <c r="G27" s="9" t="str">
-        <f>product_listing!G27</f>
+        <f>product_listing!H27</f>
         <v/>
       </c>
       <c r="H27" s="9" t="str">
@@ -4786,7 +4786,7 @@
         <v/>
       </c>
       <c r="J27" s="9" t="str">
-        <f>product_listing!F27</f>
+        <f>product_listing!G27</f>
         <v/>
       </c>
       <c r="K27" s="9" t="str">
@@ -4798,7 +4798,7 @@
         <v/>
       </c>
       <c r="M27" s="9" t="str">
-        <f>product_listing!I27</f>
+        <f>product_listing!F27</f>
         <v/>
       </c>
       <c r="N27" s="9" t="str">
@@ -4810,7 +4810,7 @@
         <v/>
       </c>
       <c r="P27" s="9" t="str">
-        <f>product_listing!H27</f>
+        <f>product_listing!I27</f>
         <v/>
       </c>
       <c r="Q27" s="9" t="str">
@@ -4872,7 +4872,7 @@
         <v/>
       </c>
       <c r="G28" s="9" t="str">
-        <f>product_listing!G28</f>
+        <f>product_listing!H28</f>
         <v/>
       </c>
       <c r="H28" s="9" t="str">
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="J28" s="9" t="str">
-        <f>product_listing!F28</f>
+        <f>product_listing!G28</f>
         <v/>
       </c>
       <c r="K28" s="9" t="str">
@@ -4896,7 +4896,7 @@
         <v/>
       </c>
       <c r="M28" s="9" t="str">
-        <f>product_listing!I28</f>
+        <f>product_listing!F28</f>
         <v/>
       </c>
       <c r="N28" s="9" t="str">
@@ -4908,7 +4908,7 @@
         <v/>
       </c>
       <c r="P28" s="9" t="str">
-        <f>product_listing!H28</f>
+        <f>product_listing!I28</f>
         <v/>
       </c>
       <c r="Q28" s="9" t="str">
@@ -4970,7 +4970,7 @@
         <v/>
       </c>
       <c r="G29" s="9" t="str">
-        <f>product_listing!G29</f>
+        <f>product_listing!H29</f>
         <v/>
       </c>
       <c r="H29" s="9" t="str">
@@ -4982,7 +4982,7 @@
         <v/>
       </c>
       <c r="J29" s="9" t="str">
-        <f>product_listing!F29</f>
+        <f>product_listing!G29</f>
         <v/>
       </c>
       <c r="K29" s="9" t="str">
@@ -4994,7 +4994,7 @@
         <v/>
       </c>
       <c r="M29" s="9" t="str">
-        <f>product_listing!I29</f>
+        <f>product_listing!F29</f>
         <v/>
       </c>
       <c r="N29" s="9" t="str">
@@ -5006,7 +5006,7 @@
         <v/>
       </c>
       <c r="P29" s="9" t="str">
-        <f>product_listing!H29</f>
+        <f>product_listing!I29</f>
         <v/>
       </c>
       <c r="Q29" s="9" t="str">
@@ -5068,7 +5068,7 @@
         <v/>
       </c>
       <c r="G30" s="9" t="str">
-        <f>product_listing!G30</f>
+        <f>product_listing!H30</f>
         <v/>
       </c>
       <c r="H30" s="9" t="str">
@@ -5080,7 +5080,7 @@
         <v/>
       </c>
       <c r="J30" s="9" t="str">
-        <f>product_listing!F30</f>
+        <f>product_listing!G30</f>
         <v/>
       </c>
       <c r="K30" s="9" t="str">
@@ -5092,7 +5092,7 @@
         <v/>
       </c>
       <c r="M30" s="9" t="str">
-        <f>product_listing!I30</f>
+        <f>product_listing!F30</f>
         <v/>
       </c>
       <c r="N30" s="9" t="str">
@@ -5104,7 +5104,7 @@
         <v/>
       </c>
       <c r="P30" s="9" t="str">
-        <f>product_listing!H30</f>
+        <f>product_listing!I30</f>
         <v/>
       </c>
       <c r="Q30" s="9" t="str">
@@ -5166,7 +5166,7 @@
         <v/>
       </c>
       <c r="G31" s="9" t="str">
-        <f>product_listing!G31</f>
+        <f>product_listing!H31</f>
         <v/>
       </c>
       <c r="H31" s="9" t="str">
@@ -5178,7 +5178,7 @@
         <v/>
       </c>
       <c r="J31" s="9" t="str">
-        <f>product_listing!F31</f>
+        <f>product_listing!G31</f>
         <v/>
       </c>
       <c r="K31" s="9" t="str">
@@ -5190,7 +5190,7 @@
         <v/>
       </c>
       <c r="M31" s="9" t="str">
-        <f>product_listing!I31</f>
+        <f>product_listing!F31</f>
         <v/>
       </c>
       <c r="N31" s="9" t="str">
@@ -5202,7 +5202,7 @@
         <v/>
       </c>
       <c r="P31" s="9" t="str">
-        <f>product_listing!H31</f>
+        <f>product_listing!I31</f>
         <v/>
       </c>
       <c r="Q31" s="9" t="str">
@@ -5264,7 +5264,7 @@
         <v/>
       </c>
       <c r="G32" s="9" t="str">
-        <f>product_listing!G32</f>
+        <f>product_listing!H32</f>
         <v/>
       </c>
       <c r="H32" s="9" t="str">
@@ -5276,7 +5276,7 @@
         <v/>
       </c>
       <c r="J32" s="9" t="str">
-        <f>product_listing!F32</f>
+        <f>product_listing!G32</f>
         <v/>
       </c>
       <c r="K32" s="9" t="str">
@@ -5288,7 +5288,7 @@
         <v/>
       </c>
       <c r="M32" s="9" t="str">
-        <f>product_listing!I32</f>
+        <f>product_listing!F32</f>
         <v/>
       </c>
       <c r="N32" s="9" t="str">
@@ -5300,7 +5300,7 @@
         <v/>
       </c>
       <c r="P32" s="9" t="str">
-        <f>product_listing!H32</f>
+        <f>product_listing!I32</f>
         <v/>
       </c>
       <c r="Q32" s="9" t="str">
@@ -5362,7 +5362,7 @@
         <v/>
       </c>
       <c r="G33" s="9" t="str">
-        <f>product_listing!G33</f>
+        <f>product_listing!H33</f>
         <v/>
       </c>
       <c r="H33" s="9" t="str">
@@ -5374,7 +5374,7 @@
         <v/>
       </c>
       <c r="J33" s="9" t="str">
-        <f>product_listing!F33</f>
+        <f>product_listing!G33</f>
         <v/>
       </c>
       <c r="K33" s="9" t="str">
@@ -5386,7 +5386,7 @@
         <v/>
       </c>
       <c r="M33" s="9" t="str">
-        <f>product_listing!I33</f>
+        <f>product_listing!F33</f>
         <v/>
       </c>
       <c r="N33" s="9" t="str">
@@ -5398,7 +5398,7 @@
         <v/>
       </c>
       <c r="P33" s="9" t="str">
-        <f>product_listing!H33</f>
+        <f>product_listing!I33</f>
         <v/>
       </c>
       <c r="Q33" s="9" t="str">
@@ -5460,7 +5460,7 @@
         <v/>
       </c>
       <c r="G34" s="9" t="str">
-        <f>product_listing!G34</f>
+        <f>product_listing!H34</f>
         <v/>
       </c>
       <c r="H34" s="9" t="str">
@@ -5472,7 +5472,7 @@
         <v/>
       </c>
       <c r="J34" s="9" t="str">
-        <f>product_listing!F34</f>
+        <f>product_listing!G34</f>
         <v/>
       </c>
       <c r="K34" s="9" t="str">
@@ -5484,7 +5484,7 @@
         <v/>
       </c>
       <c r="M34" s="9" t="str">
-        <f>product_listing!I34</f>
+        <f>product_listing!F34</f>
         <v/>
       </c>
       <c r="N34" s="9" t="str">
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="P34" s="9" t="str">
-        <f>product_listing!H34</f>
+        <f>product_listing!I34</f>
         <v/>
       </c>
       <c r="Q34" s="9" t="str">
@@ -5558,7 +5558,7 @@
         <v/>
       </c>
       <c r="G35" s="9" t="str">
-        <f>product_listing!G35</f>
+        <f>product_listing!H35</f>
         <v/>
       </c>
       <c r="H35" s="9" t="str">
@@ -5570,7 +5570,7 @@
         <v/>
       </c>
       <c r="J35" s="9" t="str">
-        <f>product_listing!F35</f>
+        <f>product_listing!G35</f>
         <v/>
       </c>
       <c r="K35" s="9" t="str">
@@ -5582,7 +5582,7 @@
         <v/>
       </c>
       <c r="M35" s="9" t="str">
-        <f>product_listing!I35</f>
+        <f>product_listing!F35</f>
         <v/>
       </c>
       <c r="N35" s="9" t="str">
@@ -5594,7 +5594,7 @@
         <v/>
       </c>
       <c r="P35" s="9" t="str">
-        <f>product_listing!H35</f>
+        <f>product_listing!I35</f>
         <v/>
       </c>
       <c r="Q35" s="9" t="str">
@@ -5656,7 +5656,7 @@
         <v/>
       </c>
       <c r="G36" s="9" t="str">
-        <f>product_listing!G36</f>
+        <f>product_listing!H36</f>
         <v/>
       </c>
       <c r="H36" s="9" t="str">
@@ -5668,7 +5668,7 @@
         <v/>
       </c>
       <c r="J36" s="9" t="str">
-        <f>product_listing!F36</f>
+        <f>product_listing!G36</f>
         <v/>
       </c>
       <c r="K36" s="9" t="str">
@@ -5680,7 +5680,7 @@
         <v/>
       </c>
       <c r="M36" s="9" t="str">
-        <f>product_listing!I36</f>
+        <f>product_listing!F36</f>
         <v/>
       </c>
       <c r="N36" s="9" t="str">
@@ -5692,7 +5692,7 @@
         <v/>
       </c>
       <c r="P36" s="9" t="str">
-        <f>product_listing!H36</f>
+        <f>product_listing!I36</f>
         <v/>
       </c>
       <c r="Q36" s="9" t="str">
@@ -5754,7 +5754,7 @@
         <v/>
       </c>
       <c r="G37" s="9" t="str">
-        <f>product_listing!G37</f>
+        <f>product_listing!H37</f>
         <v/>
       </c>
       <c r="H37" s="9" t="str">
@@ -5766,7 +5766,7 @@
         <v/>
       </c>
       <c r="J37" s="9" t="str">
-        <f>product_listing!F37</f>
+        <f>product_listing!G37</f>
         <v/>
       </c>
       <c r="K37" s="9" t="str">
@@ -5778,7 +5778,7 @@
         <v/>
       </c>
       <c r="M37" s="9" t="str">
-        <f>product_listing!I37</f>
+        <f>product_listing!F37</f>
         <v/>
       </c>
       <c r="N37" s="9" t="str">
@@ -5790,7 +5790,7 @@
         <v/>
       </c>
       <c r="P37" s="9" t="str">
-        <f>product_listing!H37</f>
+        <f>product_listing!I37</f>
         <v/>
       </c>
       <c r="Q37" s="9" t="str">
@@ -5852,7 +5852,7 @@
         <v/>
       </c>
       <c r="G38" s="9" t="str">
-        <f>product_listing!G38</f>
+        <f>product_listing!H38</f>
         <v/>
       </c>
       <c r="H38" s="9" t="str">
@@ -5864,7 +5864,7 @@
         <v/>
       </c>
       <c r="J38" s="9" t="str">
-        <f>product_listing!F38</f>
+        <f>product_listing!G38</f>
         <v/>
       </c>
       <c r="K38" s="9" t="str">
@@ -5876,7 +5876,7 @@
         <v/>
       </c>
       <c r="M38" s="9" t="str">
-        <f>product_listing!I38</f>
+        <f>product_listing!F38</f>
         <v/>
       </c>
       <c r="N38" s="9" t="str">
@@ -5888,7 +5888,7 @@
         <v/>
       </c>
       <c r="P38" s="9" t="str">
-        <f>product_listing!H38</f>
+        <f>product_listing!I38</f>
         <v/>
       </c>
       <c r="Q38" s="9" t="str">
@@ -5950,7 +5950,7 @@
         <v/>
       </c>
       <c r="G39" s="9" t="str">
-        <f>product_listing!G39</f>
+        <f>product_listing!H39</f>
         <v/>
       </c>
       <c r="H39" s="9" t="str">
@@ -5962,7 +5962,7 @@
         <v/>
       </c>
       <c r="J39" s="9" t="str">
-        <f>product_listing!F39</f>
+        <f>product_listing!G39</f>
         <v/>
       </c>
       <c r="K39" s="9" t="str">
@@ -5974,7 +5974,7 @@
         <v/>
       </c>
       <c r="M39" s="9" t="str">
-        <f>product_listing!I39</f>
+        <f>product_listing!F39</f>
         <v/>
       </c>
       <c r="N39" s="9" t="str">
@@ -5986,7 +5986,7 @@
         <v/>
       </c>
       <c r="P39" s="9" t="str">
-        <f>product_listing!H39</f>
+        <f>product_listing!I39</f>
         <v/>
       </c>
       <c r="Q39" s="9" t="str">
@@ -6048,7 +6048,7 @@
         <v/>
       </c>
       <c r="G40" s="9" t="str">
-        <f>product_listing!G40</f>
+        <f>product_listing!H40</f>
         <v/>
       </c>
       <c r="H40" s="9" t="str">
@@ -6060,7 +6060,7 @@
         <v/>
       </c>
       <c r="J40" s="9" t="str">
-        <f>product_listing!F40</f>
+        <f>product_listing!G40</f>
         <v/>
       </c>
       <c r="K40" s="9" t="str">
@@ -6072,7 +6072,7 @@
         <v/>
       </c>
       <c r="M40" s="9" t="str">
-        <f>product_listing!I40</f>
+        <f>product_listing!F40</f>
         <v/>
       </c>
       <c r="N40" s="9" t="str">
@@ -6084,7 +6084,7 @@
         <v/>
       </c>
       <c r="P40" s="9" t="str">
-        <f>product_listing!H40</f>
+        <f>product_listing!I40</f>
         <v/>
       </c>
       <c r="Q40" s="9" t="str">
@@ -6146,7 +6146,7 @@
         <v/>
       </c>
       <c r="G41" s="9" t="str">
-        <f>product_listing!G41</f>
+        <f>product_listing!H41</f>
         <v/>
       </c>
       <c r="H41" s="9" t="str">
@@ -6158,7 +6158,7 @@
         <v/>
       </c>
       <c r="J41" s="9" t="str">
-        <f>product_listing!F41</f>
+        <f>product_listing!G41</f>
         <v/>
       </c>
       <c r="K41" s="9" t="str">
@@ -6170,7 +6170,7 @@
         <v/>
       </c>
       <c r="M41" s="9" t="str">
-        <f>product_listing!I41</f>
+        <f>product_listing!F41</f>
         <v/>
       </c>
       <c r="N41" s="9" t="str">
@@ -6182,7 +6182,7 @@
         <v/>
       </c>
       <c r="P41" s="9" t="str">
-        <f>product_listing!H41</f>
+        <f>product_listing!I41</f>
         <v/>
       </c>
       <c r="Q41" s="9" t="str">
@@ -6244,7 +6244,7 @@
         <v/>
       </c>
       <c r="G42" s="9" t="str">
-        <f>product_listing!G42</f>
+        <f>product_listing!H42</f>
         <v/>
       </c>
       <c r="H42" s="9" t="str">
@@ -6256,7 +6256,7 @@
         <v/>
       </c>
       <c r="J42" s="9" t="str">
-        <f>product_listing!F42</f>
+        <f>product_listing!G42</f>
         <v/>
       </c>
       <c r="K42" s="9" t="str">
@@ -6268,7 +6268,7 @@
         <v/>
       </c>
       <c r="M42" s="9" t="str">
-        <f>product_listing!I42</f>
+        <f>product_listing!F42</f>
         <v/>
       </c>
       <c r="N42" s="9" t="str">
@@ -6280,7 +6280,7 @@
         <v/>
       </c>
       <c r="P42" s="9" t="str">
-        <f>product_listing!H42</f>
+        <f>product_listing!I42</f>
         <v/>
       </c>
       <c r="Q42" s="9" t="str">
@@ -6342,7 +6342,7 @@
         <v/>
       </c>
       <c r="G43" s="9" t="str">
-        <f>product_listing!G43</f>
+        <f>product_listing!H43</f>
         <v/>
       </c>
       <c r="H43" s="9" t="str">
@@ -6354,7 +6354,7 @@
         <v/>
       </c>
       <c r="J43" s="9" t="str">
-        <f>product_listing!F43</f>
+        <f>product_listing!G43</f>
         <v/>
       </c>
       <c r="K43" s="9" t="str">
@@ -6366,7 +6366,7 @@
         <v/>
       </c>
       <c r="M43" s="9" t="str">
-        <f>product_listing!I43</f>
+        <f>product_listing!F43</f>
         <v/>
       </c>
       <c r="N43" s="9" t="str">
@@ -6378,7 +6378,7 @@
         <v/>
       </c>
       <c r="P43" s="9" t="str">
-        <f>product_listing!H43</f>
+        <f>product_listing!I43</f>
         <v/>
       </c>
       <c r="Q43" s="9" t="str">
@@ -6440,7 +6440,7 @@
         <v/>
       </c>
       <c r="G44" s="9" t="str">
-        <f>product_listing!G44</f>
+        <f>product_listing!H44</f>
         <v/>
       </c>
       <c r="H44" s="9" t="str">
@@ -6452,7 +6452,7 @@
         <v/>
       </c>
       <c r="J44" s="9" t="str">
-        <f>product_listing!F44</f>
+        <f>product_listing!G44</f>
         <v/>
       </c>
       <c r="K44" s="9" t="str">
@@ -6464,7 +6464,7 @@
         <v/>
       </c>
       <c r="M44" s="9" t="str">
-        <f>product_listing!I44</f>
+        <f>product_listing!F44</f>
         <v/>
       </c>
       <c r="N44" s="9" t="str">
@@ -6476,7 +6476,7 @@
         <v/>
       </c>
       <c r="P44" s="9" t="str">
-        <f>product_listing!H44</f>
+        <f>product_listing!I44</f>
         <v/>
       </c>
       <c r="Q44" s="9" t="str">
@@ -6538,7 +6538,7 @@
         <v/>
       </c>
       <c r="G45" s="9" t="str">
-        <f>product_listing!G45</f>
+        <f>product_listing!H45</f>
         <v/>
       </c>
       <c r="H45" s="9" t="str">
@@ -6550,7 +6550,7 @@
         <v/>
       </c>
       <c r="J45" s="9" t="str">
-        <f>product_listing!F45</f>
+        <f>product_listing!G45</f>
         <v/>
       </c>
       <c r="K45" s="9" t="str">
@@ -6562,7 +6562,7 @@
         <v/>
       </c>
       <c r="M45" s="9" t="str">
-        <f>product_listing!I45</f>
+        <f>product_listing!F45</f>
         <v/>
       </c>
       <c r="N45" s="9" t="str">
@@ -6574,7 +6574,7 @@
         <v/>
       </c>
       <c r="P45" s="9" t="str">
-        <f>product_listing!H45</f>
+        <f>product_listing!I45</f>
         <v/>
       </c>
       <c r="Q45" s="9" t="str">
@@ -6636,7 +6636,7 @@
         <v/>
       </c>
       <c r="G46" s="9" t="str">
-        <f>product_listing!G46</f>
+        <f>product_listing!H46</f>
         <v/>
       </c>
       <c r="H46" s="9" t="str">
@@ -6648,7 +6648,7 @@
         <v/>
       </c>
       <c r="J46" s="9" t="str">
-        <f>product_listing!F46</f>
+        <f>product_listing!G46</f>
         <v/>
       </c>
       <c r="K46" s="9" t="str">
@@ -6660,7 +6660,7 @@
         <v/>
       </c>
       <c r="M46" s="9" t="str">
-        <f>product_listing!I46</f>
+        <f>product_listing!F46</f>
         <v/>
       </c>
       <c r="N46" s="9" t="str">
@@ -6672,7 +6672,7 @@
         <v/>
       </c>
       <c r="P46" s="9" t="str">
-        <f>product_listing!H46</f>
+        <f>product_listing!I46</f>
         <v/>
       </c>
       <c r="Q46" s="9" t="str">
@@ -6734,7 +6734,7 @@
         <v/>
       </c>
       <c r="G47" s="9" t="str">
-        <f>product_listing!G47</f>
+        <f>product_listing!H47</f>
         <v/>
       </c>
       <c r="H47" s="9" t="str">
@@ -6746,7 +6746,7 @@
         <v/>
       </c>
       <c r="J47" s="9" t="str">
-        <f>product_listing!F47</f>
+        <f>product_listing!G47</f>
         <v/>
       </c>
       <c r="K47" s="9" t="str">
@@ -6758,7 +6758,7 @@
         <v/>
       </c>
       <c r="M47" s="9" t="str">
-        <f>product_listing!I47</f>
+        <f>product_listing!F47</f>
         <v/>
       </c>
       <c r="N47" s="9" t="str">
@@ -6770,7 +6770,7 @@
         <v/>
       </c>
       <c r="P47" s="9" t="str">
-        <f>product_listing!H47</f>
+        <f>product_listing!I47</f>
         <v/>
       </c>
       <c r="Q47" s="9" t="str">
@@ -6832,7 +6832,7 @@
         <v/>
       </c>
       <c r="G48" s="9" t="str">
-        <f>product_listing!G48</f>
+        <f>product_listing!H48</f>
         <v/>
       </c>
       <c r="H48" s="9" t="str">
@@ -6844,7 +6844,7 @@
         <v/>
       </c>
       <c r="J48" s="9" t="str">
-        <f>product_listing!F48</f>
+        <f>product_listing!G48</f>
         <v/>
       </c>
       <c r="K48" s="9" t="str">
@@ -6856,7 +6856,7 @@
         <v/>
       </c>
       <c r="M48" s="9" t="str">
-        <f>product_listing!I48</f>
+        <f>product_listing!F48</f>
         <v/>
       </c>
       <c r="N48" s="9" t="str">
@@ -6868,7 +6868,7 @@
         <v/>
       </c>
       <c r="P48" s="9" t="str">
-        <f>product_listing!H48</f>
+        <f>product_listing!I48</f>
         <v/>
       </c>
       <c r="Q48" s="9" t="str">
@@ -6930,7 +6930,7 @@
         <v/>
       </c>
       <c r="G49" s="9" t="str">
-        <f>product_listing!G49</f>
+        <f>product_listing!H49</f>
         <v/>
       </c>
       <c r="H49" s="9" t="str">
@@ -6942,7 +6942,7 @@
         <v/>
       </c>
       <c r="J49" s="9" t="str">
-        <f>product_listing!F49</f>
+        <f>product_listing!G49</f>
         <v/>
       </c>
       <c r="K49" s="9" t="str">
@@ -6954,7 +6954,7 @@
         <v/>
       </c>
       <c r="M49" s="9" t="str">
-        <f>product_listing!I49</f>
+        <f>product_listing!F49</f>
         <v/>
       </c>
       <c r="N49" s="9" t="str">
@@ -6966,7 +6966,7 @@
         <v/>
       </c>
       <c r="P49" s="9" t="str">
-        <f>product_listing!H49</f>
+        <f>product_listing!I49</f>
         <v/>
       </c>
       <c r="Q49" s="9" t="str">
@@ -7028,7 +7028,7 @@
         <v/>
       </c>
       <c r="G50" s="9" t="str">
-        <f>product_listing!G50</f>
+        <f>product_listing!H50</f>
         <v/>
       </c>
       <c r="H50" s="9" t="str">
@@ -7040,7 +7040,7 @@
         <v/>
       </c>
       <c r="J50" s="9" t="str">
-        <f>product_listing!F50</f>
+        <f>product_listing!G50</f>
         <v/>
       </c>
       <c r="K50" s="9" t="str">
@@ -7052,7 +7052,7 @@
         <v/>
       </c>
       <c r="M50" s="9" t="str">
-        <f>product_listing!I50</f>
+        <f>product_listing!F50</f>
         <v/>
       </c>
       <c r="N50" s="9" t="str">
@@ -7064,7 +7064,7 @@
         <v/>
       </c>
       <c r="P50" s="9" t="str">
-        <f>product_listing!H50</f>
+        <f>product_listing!I50</f>
         <v/>
       </c>
       <c r="Q50" s="9" t="str">
@@ -7126,7 +7126,7 @@
         <v/>
       </c>
       <c r="G51" s="9" t="str">
-        <f>product_listing!G51</f>
+        <f>product_listing!H51</f>
         <v/>
       </c>
       <c r="H51" s="9" t="str">
@@ -7138,7 +7138,7 @@
         <v/>
       </c>
       <c r="J51" s="9" t="str">
-        <f>product_listing!F51</f>
+        <f>product_listing!G51</f>
         <v/>
       </c>
       <c r="K51" s="9" t="str">
@@ -7150,7 +7150,7 @@
         <v/>
       </c>
       <c r="M51" s="9" t="str">
-        <f>product_listing!I51</f>
+        <f>product_listing!F51</f>
         <v/>
       </c>
       <c r="N51" s="9" t="str">
@@ -7162,7 +7162,7 @@
         <v/>
       </c>
       <c r="P51" s="9" t="str">
-        <f>product_listing!H51</f>
+        <f>product_listing!I51</f>
         <v/>
       </c>
       <c r="Q51" s="9" t="str">
@@ -7224,7 +7224,7 @@
         <v/>
       </c>
       <c r="G52" s="9" t="str">
-        <f>product_listing!G52</f>
+        <f>product_listing!H52</f>
         <v/>
       </c>
       <c r="H52" s="9" t="str">
@@ -7236,7 +7236,7 @@
         <v/>
       </c>
       <c r="J52" s="9" t="str">
-        <f>product_listing!F52</f>
+        <f>product_listing!G52</f>
         <v/>
       </c>
       <c r="K52" s="9" t="str">
@@ -7248,7 +7248,7 @@
         <v/>
       </c>
       <c r="M52" s="9" t="str">
-        <f>product_listing!I52</f>
+        <f>product_listing!F52</f>
         <v/>
       </c>
       <c r="N52" s="9" t="str">
@@ -7260,7 +7260,7 @@
         <v/>
       </c>
       <c r="P52" s="9" t="str">
-        <f>product_listing!H52</f>
+        <f>product_listing!I52</f>
         <v/>
       </c>
       <c r="Q52" s="9" t="str">
@@ -7322,7 +7322,7 @@
         <v/>
       </c>
       <c r="G53" s="9" t="str">
-        <f>product_listing!G53</f>
+        <f>product_listing!H53</f>
         <v/>
       </c>
       <c r="H53" s="9" t="str">
@@ -7334,7 +7334,7 @@
         <v/>
       </c>
       <c r="J53" s="9" t="str">
-        <f>product_listing!F53</f>
+        <f>product_listing!G53</f>
         <v/>
       </c>
       <c r="K53" s="9" t="str">
@@ -7346,7 +7346,7 @@
         <v/>
       </c>
       <c r="M53" s="9" t="str">
-        <f>product_listing!I53</f>
+        <f>product_listing!F53</f>
         <v/>
       </c>
       <c r="N53" s="9" t="str">
@@ -7358,7 +7358,7 @@
         <v/>
       </c>
       <c r="P53" s="9" t="str">
-        <f>product_listing!H53</f>
+        <f>product_listing!I53</f>
         <v/>
       </c>
       <c r="Q53" s="9" t="str">
@@ -7420,7 +7420,7 @@
         <v/>
       </c>
       <c r="G54" s="9" t="str">
-        <f>product_listing!G54</f>
+        <f>product_listing!H54</f>
         <v/>
       </c>
       <c r="H54" s="9" t="str">
@@ -7432,7 +7432,7 @@
         <v/>
       </c>
       <c r="J54" s="9" t="str">
-        <f>product_listing!F54</f>
+        <f>product_listing!G54</f>
         <v/>
       </c>
       <c r="K54" s="9" t="str">
@@ -7444,7 +7444,7 @@
         <v/>
       </c>
       <c r="M54" s="9" t="str">
-        <f>product_listing!I54</f>
+        <f>product_listing!F54</f>
         <v/>
       </c>
       <c r="N54" s="9" t="str">
@@ -7456,7 +7456,7 @@
         <v/>
       </c>
       <c r="P54" s="9" t="str">
-        <f>product_listing!H54</f>
+        <f>product_listing!I54</f>
         <v/>
       </c>
       <c r="Q54" s="9" t="str">
@@ -7518,7 +7518,7 @@
         <v/>
       </c>
       <c r="G55" s="9" t="str">
-        <f>product_listing!G55</f>
+        <f>product_listing!H55</f>
         <v/>
       </c>
       <c r="H55" s="9" t="str">
@@ -7530,7 +7530,7 @@
         <v/>
       </c>
       <c r="J55" s="9" t="str">
-        <f>product_listing!F55</f>
+        <f>product_listing!G55</f>
         <v/>
       </c>
       <c r="K55" s="9" t="str">
@@ -7542,7 +7542,7 @@
         <v/>
       </c>
       <c r="M55" s="9" t="str">
-        <f>product_listing!I55</f>
+        <f>product_listing!F55</f>
         <v/>
       </c>
       <c r="N55" s="9" t="str">
@@ -7554,7 +7554,7 @@
         <v/>
       </c>
       <c r="P55" s="9" t="str">
-        <f>product_listing!H55</f>
+        <f>product_listing!I55</f>
         <v/>
       </c>
       <c r="Q55" s="9" t="str">
@@ -7616,7 +7616,7 @@
         <v/>
       </c>
       <c r="G56" s="9" t="str">
-        <f>product_listing!G56</f>
+        <f>product_listing!H56</f>
         <v/>
       </c>
       <c r="H56" s="9" t="str">
@@ -7628,7 +7628,7 @@
         <v/>
       </c>
       <c r="J56" s="9" t="str">
-        <f>product_listing!F56</f>
+        <f>product_listing!G56</f>
         <v/>
       </c>
       <c r="K56" s="9" t="str">
@@ -7640,7 +7640,7 @@
         <v/>
       </c>
       <c r="M56" s="9" t="str">
-        <f>product_listing!I56</f>
+        <f>product_listing!F56</f>
         <v/>
       </c>
       <c r="N56" s="9" t="str">
@@ -7652,7 +7652,7 @@
         <v/>
       </c>
       <c r="P56" s="9" t="str">
-        <f>product_listing!H56</f>
+        <f>product_listing!I56</f>
         <v/>
       </c>
       <c r="Q56" s="9" t="str">
@@ -7714,7 +7714,7 @@
         <v/>
       </c>
       <c r="G57" s="9" t="str">
-        <f>product_listing!G57</f>
+        <f>product_listing!H57</f>
         <v/>
       </c>
       <c r="H57" s="9" t="str">
@@ -7726,7 +7726,7 @@
         <v/>
       </c>
       <c r="J57" s="9" t="str">
-        <f>product_listing!F57</f>
+        <f>product_listing!G57</f>
         <v/>
       </c>
       <c r="K57" s="9" t="str">
@@ -7738,7 +7738,7 @@
         <v/>
       </c>
       <c r="M57" s="9" t="str">
-        <f>product_listing!I57</f>
+        <f>product_listing!F57</f>
         <v/>
       </c>
       <c r="N57" s="9" t="str">
@@ -7750,7 +7750,7 @@
         <v/>
       </c>
       <c r="P57" s="9" t="str">
-        <f>product_listing!H57</f>
+        <f>product_listing!I57</f>
         <v/>
       </c>
       <c r="Q57" s="9" t="str">
@@ -7812,7 +7812,7 @@
         <v/>
       </c>
       <c r="G58" s="9" t="str">
-        <f>product_listing!G58</f>
+        <f>product_listing!H58</f>
         <v/>
       </c>
       <c r="H58" s="9" t="str">
@@ -7824,7 +7824,7 @@
         <v/>
       </c>
       <c r="J58" s="9" t="str">
-        <f>product_listing!F58</f>
+        <f>product_listing!G58</f>
         <v/>
       </c>
       <c r="K58" s="9" t="str">
@@ -7836,7 +7836,7 @@
         <v/>
       </c>
       <c r="M58" s="9" t="str">
-        <f>product_listing!I58</f>
+        <f>product_listing!F58</f>
         <v/>
       </c>
       <c r="N58" s="9" t="str">
@@ -7848,7 +7848,7 @@
         <v/>
       </c>
       <c r="P58" s="9" t="str">
-        <f>product_listing!H58</f>
+        <f>product_listing!I58</f>
         <v/>
       </c>
       <c r="Q58" s="9" t="str">
@@ -7910,7 +7910,7 @@
         <v/>
       </c>
       <c r="G59" s="9" t="str">
-        <f>product_listing!G59</f>
+        <f>product_listing!H59</f>
         <v/>
       </c>
       <c r="H59" s="9" t="str">
@@ -7922,7 +7922,7 @@
         <v/>
       </c>
       <c r="J59" s="9" t="str">
-        <f>product_listing!F59</f>
+        <f>product_listing!G59</f>
         <v/>
       </c>
       <c r="K59" s="9" t="str">
@@ -7934,7 +7934,7 @@
         <v/>
       </c>
       <c r="M59" s="9" t="str">
-        <f>product_listing!I59</f>
+        <f>product_listing!F59</f>
         <v/>
       </c>
       <c r="N59" s="9" t="str">
@@ -7946,7 +7946,7 @@
         <v/>
       </c>
       <c r="P59" s="9" t="str">
-        <f>product_listing!H59</f>
+        <f>product_listing!I59</f>
         <v/>
       </c>
       <c r="Q59" s="9" t="str">
@@ -8008,7 +8008,7 @@
         <v/>
       </c>
       <c r="G60" s="9" t="str">
-        <f>product_listing!G60</f>
+        <f>product_listing!H60</f>
         <v/>
       </c>
       <c r="H60" s="9" t="str">
@@ -8020,7 +8020,7 @@
         <v/>
       </c>
       <c r="J60" s="9" t="str">
-        <f>product_listing!F60</f>
+        <f>product_listing!G60</f>
         <v/>
       </c>
       <c r="K60" s="9" t="str">
@@ -8032,7 +8032,7 @@
         <v/>
       </c>
       <c r="M60" s="9" t="str">
-        <f>product_listing!I60</f>
+        <f>product_listing!F60</f>
         <v/>
       </c>
       <c r="N60" s="9" t="str">
@@ -8044,7 +8044,7 @@
         <v/>
       </c>
       <c r="P60" s="9" t="str">
-        <f>product_listing!H60</f>
+        <f>product_listing!I60</f>
         <v/>
       </c>
       <c r="Q60" s="9" t="str">
@@ -8106,7 +8106,7 @@
         <v/>
       </c>
       <c r="G61" s="9" t="str">
-        <f>product_listing!G61</f>
+        <f>product_listing!H61</f>
         <v/>
       </c>
       <c r="H61" s="9" t="str">
@@ -8118,7 +8118,7 @@
         <v/>
       </c>
       <c r="J61" s="9" t="str">
-        <f>product_listing!F61</f>
+        <f>product_listing!G61</f>
         <v/>
       </c>
       <c r="K61" s="9" t="str">
@@ -8130,7 +8130,7 @@
         <v/>
       </c>
       <c r="M61" s="9" t="str">
-        <f>product_listing!I61</f>
+        <f>product_listing!F61</f>
         <v/>
       </c>
       <c r="N61" s="9" t="str">
@@ -8142,7 +8142,7 @@
         <v/>
       </c>
       <c r="P61" s="9" t="str">
-        <f>product_listing!H61</f>
+        <f>product_listing!I61</f>
         <v/>
       </c>
       <c r="Q61" s="9" t="str">
@@ -8204,7 +8204,7 @@
         <v/>
       </c>
       <c r="G62" s="9" t="str">
-        <f>product_listing!G62</f>
+        <f>product_listing!H62</f>
         <v/>
       </c>
       <c r="H62" s="9" t="str">
@@ -8216,7 +8216,7 @@
         <v/>
       </c>
       <c r="J62" s="9" t="str">
-        <f>product_listing!F62</f>
+        <f>product_listing!G62</f>
         <v/>
       </c>
       <c r="K62" s="9" t="str">
@@ -8228,7 +8228,7 @@
         <v/>
       </c>
       <c r="M62" s="9" t="str">
-        <f>product_listing!I62</f>
+        <f>product_listing!F62</f>
         <v/>
       </c>
       <c r="N62" s="9" t="str">
@@ -8240,7 +8240,7 @@
         <v/>
       </c>
       <c r="P62" s="9" t="str">
-        <f>product_listing!H62</f>
+        <f>product_listing!I62</f>
         <v/>
       </c>
       <c r="Q62" s="9" t="str">
@@ -8302,7 +8302,7 @@
         <v/>
       </c>
       <c r="G63" s="9" t="str">
-        <f>product_listing!G63</f>
+        <f>product_listing!H63</f>
         <v/>
       </c>
       <c r="H63" s="9" t="str">
@@ -8314,7 +8314,7 @@
         <v/>
       </c>
       <c r="J63" s="9" t="str">
-        <f>product_listing!F63</f>
+        <f>product_listing!G63</f>
         <v/>
       </c>
       <c r="K63" s="9" t="str">
@@ -8326,7 +8326,7 @@
         <v/>
       </c>
       <c r="M63" s="9" t="str">
-        <f>product_listing!I63</f>
+        <f>product_listing!F63</f>
         <v/>
       </c>
       <c r="N63" s="9" t="str">
@@ -8338,7 +8338,7 @@
         <v/>
       </c>
       <c r="P63" s="9" t="str">
-        <f>product_listing!H63</f>
+        <f>product_listing!I63</f>
         <v/>
       </c>
       <c r="Q63" s="9" t="str">
@@ -8400,7 +8400,7 @@
         <v/>
       </c>
       <c r="G64" s="9" t="str">
-        <f>product_listing!G64</f>
+        <f>product_listing!H64</f>
         <v/>
       </c>
       <c r="H64" s="9" t="str">
@@ -8412,7 +8412,7 @@
         <v/>
       </c>
       <c r="J64" s="9" t="str">
-        <f>product_listing!F64</f>
+        <f>product_listing!G64</f>
         <v/>
       </c>
       <c r="K64" s="9" t="str">
@@ -8424,7 +8424,7 @@
         <v/>
       </c>
       <c r="M64" s="9" t="str">
-        <f>product_listing!I64</f>
+        <f>product_listing!F64</f>
         <v/>
       </c>
       <c r="N64" s="9" t="str">
@@ -8436,7 +8436,7 @@
         <v/>
       </c>
       <c r="P64" s="9" t="str">
-        <f>product_listing!H64</f>
+        <f>product_listing!I64</f>
         <v/>
       </c>
       <c r="Q64" s="9" t="str">
@@ -8498,7 +8498,7 @@
         <v/>
       </c>
       <c r="G65" s="9" t="str">
-        <f>product_listing!G65</f>
+        <f>product_listing!H65</f>
         <v/>
       </c>
       <c r="H65" s="9" t="str">
@@ -8510,7 +8510,7 @@
         <v/>
       </c>
       <c r="J65" s="9" t="str">
-        <f>product_listing!F65</f>
+        <f>product_listing!G65</f>
         <v/>
       </c>
       <c r="K65" s="9" t="str">
@@ -8522,7 +8522,7 @@
         <v/>
       </c>
       <c r="M65" s="9" t="str">
-        <f>product_listing!I65</f>
+        <f>product_listing!F65</f>
         <v/>
       </c>
       <c r="N65" s="9" t="str">
@@ -8534,7 +8534,7 @@
         <v/>
       </c>
       <c r="P65" s="9" t="str">
-        <f>product_listing!H65</f>
+        <f>product_listing!I65</f>
         <v/>
       </c>
       <c r="Q65" s="9" t="str">
@@ -8596,7 +8596,7 @@
         <v/>
       </c>
       <c r="G66" s="9" t="str">
-        <f>product_listing!G66</f>
+        <f>product_listing!H66</f>
         <v/>
       </c>
       <c r="H66" s="9" t="str">
@@ -8608,7 +8608,7 @@
         <v/>
       </c>
       <c r="J66" s="9" t="str">
-        <f>product_listing!F66</f>
+        <f>product_listing!G66</f>
         <v/>
       </c>
       <c r="K66" s="9" t="str">
@@ -8620,7 +8620,7 @@
         <v/>
       </c>
       <c r="M66" s="9" t="str">
-        <f>product_listing!I66</f>
+        <f>product_listing!F66</f>
         <v/>
       </c>
       <c r="N66" s="9" t="str">
@@ -8632,7 +8632,7 @@
         <v/>
       </c>
       <c r="P66" s="9" t="str">
-        <f>product_listing!H66</f>
+        <f>product_listing!I66</f>
         <v/>
       </c>
       <c r="Q66" s="9" t="str">
@@ -8694,7 +8694,7 @@
         <v/>
       </c>
       <c r="G67" s="9" t="str">
-        <f>product_listing!G67</f>
+        <f>product_listing!H67</f>
         <v/>
       </c>
       <c r="H67" s="9" t="str">
@@ -8706,7 +8706,7 @@
         <v/>
       </c>
       <c r="J67" s="9" t="str">
-        <f>product_listing!F67</f>
+        <f>product_listing!G67</f>
         <v/>
       </c>
       <c r="K67" s="9" t="str">
@@ -8718,7 +8718,7 @@
         <v/>
       </c>
       <c r="M67" s="9" t="str">
-        <f>product_listing!I67</f>
+        <f>product_listing!F67</f>
         <v/>
       </c>
       <c r="N67" s="9" t="str">
@@ -8730,7 +8730,7 @@
         <v/>
       </c>
       <c r="P67" s="9" t="str">
-        <f>product_listing!H67</f>
+        <f>product_listing!I67</f>
         <v/>
       </c>
       <c r="Q67" s="9" t="str">
@@ -8792,7 +8792,7 @@
         <v/>
       </c>
       <c r="G68" s="9" t="str">
-        <f>product_listing!G68</f>
+        <f>product_listing!H68</f>
         <v/>
       </c>
       <c r="H68" s="9" t="str">
@@ -8804,7 +8804,7 @@
         <v/>
       </c>
       <c r="J68" s="9" t="str">
-        <f>product_listing!F68</f>
+        <f>product_listing!G68</f>
         <v/>
       </c>
       <c r="K68" s="9" t="str">
@@ -8816,7 +8816,7 @@
         <v/>
       </c>
       <c r="M68" s="9" t="str">
-        <f>product_listing!I68</f>
+        <f>product_listing!F68</f>
         <v/>
       </c>
       <c r="N68" s="9" t="str">
@@ -8828,7 +8828,7 @@
         <v/>
       </c>
       <c r="P68" s="9" t="str">
-        <f>product_listing!H68</f>
+        <f>product_listing!I68</f>
         <v/>
       </c>
       <c r="Q68" s="9" t="str">
@@ -8890,7 +8890,7 @@
         <v/>
       </c>
       <c r="G69" s="9" t="str">
-        <f>product_listing!G69</f>
+        <f>product_listing!H69</f>
         <v/>
       </c>
       <c r="H69" s="9" t="str">
@@ -8902,7 +8902,7 @@
         <v/>
       </c>
       <c r="J69" s="9" t="str">
-        <f>product_listing!F69</f>
+        <f>product_listing!G69</f>
         <v/>
       </c>
       <c r="K69" s="9" t="str">
@@ -8914,7 +8914,7 @@
         <v/>
       </c>
       <c r="M69" s="9" t="str">
-        <f>product_listing!I69</f>
+        <f>product_listing!F69</f>
         <v/>
       </c>
       <c r="N69" s="9" t="str">
@@ -8926,7 +8926,7 @@
         <v/>
       </c>
       <c r="P69" s="9" t="str">
-        <f>product_listing!H69</f>
+        <f>product_listing!I69</f>
         <v/>
       </c>
       <c r="Q69" s="9" t="str">
@@ -8988,7 +8988,7 @@
         <v/>
       </c>
       <c r="G70" s="9" t="str">
-        <f>product_listing!G70</f>
+        <f>product_listing!H70</f>
         <v/>
       </c>
       <c r="H70" s="9" t="str">
@@ -9000,7 +9000,7 @@
         <v/>
       </c>
       <c r="J70" s="9" t="str">
-        <f>product_listing!F70</f>
+        <f>product_listing!G70</f>
         <v/>
       </c>
       <c r="K70" s="9" t="str">
@@ -9012,7 +9012,7 @@
         <v/>
       </c>
       <c r="M70" s="9" t="str">
-        <f>product_listing!I70</f>
+        <f>product_listing!F70</f>
         <v/>
       </c>
       <c r="N70" s="9" t="str">
@@ -9024,7 +9024,7 @@
         <v/>
       </c>
       <c r="P70" s="9" t="str">
-        <f>product_listing!H70</f>
+        <f>product_listing!I70</f>
         <v/>
       </c>
       <c r="Q70" s="9" t="str">
@@ -9086,7 +9086,7 @@
         <v/>
       </c>
       <c r="G71" s="9" t="str">
-        <f>product_listing!G71</f>
+        <f>product_listing!H71</f>
         <v/>
       </c>
       <c r="H71" s="9" t="str">
@@ -9098,7 +9098,7 @@
         <v/>
       </c>
       <c r="J71" s="9" t="str">
-        <f>product_listing!F71</f>
+        <f>product_listing!G71</f>
         <v/>
       </c>
       <c r="K71" s="9" t="str">
@@ -9110,7 +9110,7 @@
         <v/>
       </c>
       <c r="M71" s="9" t="str">
-        <f>product_listing!I71</f>
+        <f>product_listing!F71</f>
         <v/>
       </c>
       <c r="N71" s="9" t="str">
@@ -9122,7 +9122,7 @@
         <v/>
       </c>
       <c r="P71" s="9" t="str">
-        <f>product_listing!H71</f>
+        <f>product_listing!I71</f>
         <v/>
       </c>
       <c r="Q71" s="9" t="str">
@@ -9184,7 +9184,7 @@
         <v/>
       </c>
       <c r="G72" s="9" t="str">
-        <f>product_listing!G72</f>
+        <f>product_listing!H72</f>
         <v/>
       </c>
       <c r="H72" s="9" t="str">
@@ -9196,7 +9196,7 @@
         <v/>
       </c>
       <c r="J72" s="9" t="str">
-        <f>product_listing!F72</f>
+        <f>product_listing!G72</f>
         <v/>
       </c>
       <c r="K72" s="9" t="str">
@@ -9208,7 +9208,7 @@
         <v/>
       </c>
       <c r="M72" s="9" t="str">
-        <f>product_listing!I72</f>
+        <f>product_listing!F72</f>
         <v/>
       </c>
       <c r="N72" s="9" t="str">
@@ -9220,7 +9220,7 @@
         <v/>
       </c>
       <c r="P72" s="9" t="str">
-        <f>product_listing!H72</f>
+        <f>product_listing!I72</f>
         <v/>
       </c>
       <c r="Q72" s="9" t="str">
@@ -9282,7 +9282,7 @@
         <v/>
       </c>
       <c r="G73" s="9" t="str">
-        <f>product_listing!G73</f>
+        <f>product_listing!H73</f>
         <v/>
       </c>
       <c r="H73" s="9" t="str">
@@ -9294,7 +9294,7 @@
         <v/>
       </c>
       <c r="J73" s="9" t="str">
-        <f>product_listing!F73</f>
+        <f>product_listing!G73</f>
         <v/>
       </c>
       <c r="K73" s="9" t="str">
@@ -9306,7 +9306,7 @@
         <v/>
       </c>
       <c r="M73" s="9" t="str">
-        <f>product_listing!I73</f>
+        <f>product_listing!F73</f>
         <v/>
       </c>
       <c r="N73" s="9" t="str">
@@ -9318,7 +9318,7 @@
         <v/>
       </c>
       <c r="P73" s="9" t="str">
-        <f>product_listing!H73</f>
+        <f>product_listing!I73</f>
         <v/>
       </c>
       <c r="Q73" s="9" t="str">
@@ -9380,7 +9380,7 @@
         <v/>
       </c>
       <c r="G74" s="9" t="str">
-        <f>product_listing!G74</f>
+        <f>product_listing!H74</f>
         <v/>
       </c>
       <c r="H74" s="9" t="str">
@@ -9392,7 +9392,7 @@
         <v/>
       </c>
       <c r="J74" s="9" t="str">
-        <f>product_listing!F74</f>
+        <f>product_listing!G74</f>
         <v/>
       </c>
       <c r="K74" s="9" t="str">
@@ -9404,7 +9404,7 @@
         <v/>
       </c>
       <c r="M74" s="9" t="str">
-        <f>product_listing!I74</f>
+        <f>product_listing!F74</f>
         <v/>
       </c>
       <c r="N74" s="9" t="str">
@@ -9416,7 +9416,7 @@
         <v/>
       </c>
       <c r="P74" s="9" t="str">
-        <f>product_listing!H74</f>
+        <f>product_listing!I74</f>
         <v/>
       </c>
       <c r="Q74" s="9" t="str">
@@ -9478,7 +9478,7 @@
         <v/>
       </c>
       <c r="G75" s="9" t="str">
-        <f>product_listing!G75</f>
+        <f>product_listing!H75</f>
         <v/>
       </c>
       <c r="H75" s="9" t="str">
@@ -9490,7 +9490,7 @@
         <v/>
       </c>
       <c r="J75" s="9" t="str">
-        <f>product_listing!F75</f>
+        <f>product_listing!G75</f>
         <v/>
       </c>
       <c r="K75" s="9" t="str">
@@ -9502,7 +9502,7 @@
         <v/>
       </c>
       <c r="M75" s="9" t="str">
-        <f>product_listing!I75</f>
+        <f>product_listing!F75</f>
         <v/>
       </c>
       <c r="N75" s="9" t="str">
@@ -9514,7 +9514,7 @@
         <v/>
       </c>
       <c r="P75" s="9" t="str">
-        <f>product_listing!H75</f>
+        <f>product_listing!I75</f>
         <v/>
       </c>
       <c r="Q75" s="9" t="str">
@@ -9576,7 +9576,7 @@
         <v/>
       </c>
       <c r="G76" s="9" t="str">
-        <f>product_listing!G76</f>
+        <f>product_listing!H76</f>
         <v/>
       </c>
       <c r="H76" s="9" t="str">
@@ -9588,7 +9588,7 @@
         <v/>
       </c>
       <c r="J76" s="9" t="str">
-        <f>product_listing!F76</f>
+        <f>product_listing!G76</f>
         <v/>
       </c>
       <c r="K76" s="9" t="str">
@@ -9600,7 +9600,7 @@
         <v/>
       </c>
       <c r="M76" s="9" t="str">
-        <f>product_listing!I76</f>
+        <f>product_listing!F76</f>
         <v/>
       </c>
       <c r="N76" s="9" t="str">
@@ -9612,7 +9612,7 @@
         <v/>
       </c>
       <c r="P76" s="9" t="str">
-        <f>product_listing!H76</f>
+        <f>product_listing!I76</f>
         <v/>
       </c>
       <c r="Q76" s="9" t="str">
@@ -9674,7 +9674,7 @@
         <v/>
       </c>
       <c r="G77" s="9" t="str">
-        <f>product_listing!G77</f>
+        <f>product_listing!H77</f>
         <v/>
       </c>
       <c r="H77" s="9" t="str">
@@ -9686,7 +9686,7 @@
         <v/>
       </c>
       <c r="J77" s="9" t="str">
-        <f>product_listing!F77</f>
+        <f>product_listing!G77</f>
         <v/>
       </c>
       <c r="K77" s="9" t="str">
@@ -9698,7 +9698,7 @@
         <v/>
       </c>
       <c r="M77" s="9" t="str">
-        <f>product_listing!I77</f>
+        <f>product_listing!F77</f>
         <v/>
       </c>
       <c r="N77" s="9" t="str">
@@ -9710,7 +9710,7 @@
         <v/>
       </c>
       <c r="P77" s="9" t="str">
-        <f>product_listing!H77</f>
+        <f>product_listing!I77</f>
         <v/>
       </c>
       <c r="Q77" s="9" t="str">
@@ -9772,7 +9772,7 @@
         <v/>
       </c>
       <c r="G78" s="9" t="str">
-        <f>product_listing!G78</f>
+        <f>product_listing!H78</f>
         <v/>
       </c>
       <c r="H78" s="9" t="str">
@@ -9784,7 +9784,7 @@
         <v/>
       </c>
       <c r="J78" s="9" t="str">
-        <f>product_listing!F78</f>
+        <f>product_listing!G78</f>
         <v/>
       </c>
       <c r="K78" s="9" t="str">
@@ -9796,7 +9796,7 @@
         <v/>
       </c>
       <c r="M78" s="9" t="str">
-        <f>product_listing!I78</f>
+        <f>product_listing!F78</f>
         <v/>
       </c>
       <c r="N78" s="9" t="str">
@@ -9808,7 +9808,7 @@
         <v/>
       </c>
       <c r="P78" s="9" t="str">
-        <f>product_listing!H78</f>
+        <f>product_listing!I78</f>
         <v/>
       </c>
       <c r="Q78" s="9" t="str">
@@ -9870,7 +9870,7 @@
         <v/>
       </c>
       <c r="G79" s="9" t="str">
-        <f>product_listing!G79</f>
+        <f>product_listing!H79</f>
         <v/>
       </c>
       <c r="H79" s="9" t="str">
@@ -9882,7 +9882,7 @@
         <v/>
       </c>
       <c r="J79" s="9" t="str">
-        <f>product_listing!F79</f>
+        <f>product_listing!G79</f>
         <v/>
       </c>
       <c r="K79" s="9" t="str">
@@ -9894,7 +9894,7 @@
         <v/>
       </c>
       <c r="M79" s="9" t="str">
-        <f>product_listing!I79</f>
+        <f>product_listing!F79</f>
         <v/>
       </c>
       <c r="N79" s="9" t="str">
@@ -9906,7 +9906,7 @@
         <v/>
       </c>
       <c r="P79" s="9" t="str">
-        <f>product_listing!H79</f>
+        <f>product_listing!I79</f>
         <v/>
       </c>
       <c r="Q79" s="9" t="str">
@@ -9968,7 +9968,7 @@
         <v/>
       </c>
       <c r="G80" s="9" t="str">
-        <f>product_listing!G80</f>
+        <f>product_listing!H80</f>
         <v/>
       </c>
       <c r="H80" s="9" t="str">
@@ -9980,7 +9980,7 @@
         <v/>
       </c>
       <c r="J80" s="9" t="str">
-        <f>product_listing!F80</f>
+        <f>product_listing!G80</f>
         <v/>
       </c>
       <c r="K80" s="9" t="str">
@@ -9992,7 +9992,7 @@
         <v/>
       </c>
       <c r="M80" s="9" t="str">
-        <f>product_listing!I80</f>
+        <f>product_listing!F80</f>
         <v/>
       </c>
       <c r="N80" s="9" t="str">
@@ -10004,7 +10004,7 @@
         <v/>
       </c>
       <c r="P80" s="9" t="str">
-        <f>product_listing!H80</f>
+        <f>product_listing!I80</f>
         <v/>
       </c>
       <c r="Q80" s="9" t="str">
@@ -10066,7 +10066,7 @@
         <v/>
       </c>
       <c r="G81" s="9" t="str">
-        <f>product_listing!G81</f>
+        <f>product_listing!H81</f>
         <v/>
       </c>
       <c r="H81" s="9" t="str">
@@ -10078,7 +10078,7 @@
         <v/>
       </c>
       <c r="J81" s="9" t="str">
-        <f>product_listing!F81</f>
+        <f>product_listing!G81</f>
         <v/>
       </c>
       <c r="K81" s="9" t="str">
@@ -10090,7 +10090,7 @@
         <v/>
       </c>
       <c r="M81" s="9" t="str">
-        <f>product_listing!I81</f>
+        <f>product_listing!F81</f>
         <v/>
       </c>
       <c r="N81" s="9" t="str">
@@ -10102,7 +10102,7 @@
         <v/>
       </c>
       <c r="P81" s="9" t="str">
-        <f>product_listing!H81</f>
+        <f>product_listing!I81</f>
         <v/>
       </c>
       <c r="Q81" s="9" t="str">
@@ -10164,7 +10164,7 @@
         <v/>
       </c>
       <c r="G82" s="9" t="str">
-        <f>product_listing!G82</f>
+        <f>product_listing!H82</f>
         <v/>
       </c>
       <c r="H82" s="9" t="str">
@@ -10176,7 +10176,7 @@
         <v/>
       </c>
       <c r="J82" s="9" t="str">
-        <f>product_listing!F82</f>
+        <f>product_listing!G82</f>
         <v/>
       </c>
       <c r="K82" s="9" t="str">
@@ -10188,7 +10188,7 @@
         <v/>
       </c>
       <c r="M82" s="9" t="str">
-        <f>product_listing!I82</f>
+        <f>product_listing!F82</f>
         <v/>
       </c>
       <c r="N82" s="9" t="str">
@@ -10200,7 +10200,7 @@
         <v/>
       </c>
       <c r="P82" s="9" t="str">
-        <f>product_listing!H82</f>
+        <f>product_listing!I82</f>
         <v/>
       </c>
       <c r="Q82" s="9" t="str">
@@ -10262,7 +10262,7 @@
         <v/>
       </c>
       <c r="G83" s="9" t="str">
-        <f>product_listing!G83</f>
+        <f>product_listing!H83</f>
         <v/>
       </c>
       <c r="H83" s="9" t="str">
@@ -10274,7 +10274,7 @@
         <v/>
       </c>
       <c r="J83" s="9" t="str">
-        <f>product_listing!F83</f>
+        <f>product_listing!G83</f>
         <v/>
       </c>
       <c r="K83" s="9" t="str">
@@ -10286,7 +10286,7 @@
         <v/>
       </c>
       <c r="M83" s="9" t="str">
-        <f>product_listing!I83</f>
+        <f>product_listing!F83</f>
         <v/>
       </c>
       <c r="N83" s="9" t="str">
@@ -10298,7 +10298,7 @@
         <v/>
       </c>
       <c r="P83" s="9" t="str">
-        <f>product_listing!H83</f>
+        <f>product_listing!I83</f>
         <v/>
       </c>
       <c r="Q83" s="9" t="str">
@@ -10360,7 +10360,7 @@
         <v/>
       </c>
       <c r="G84" s="9" t="str">
-        <f>product_listing!G84</f>
+        <f>product_listing!H84</f>
         <v/>
       </c>
       <c r="H84" s="9" t="str">
@@ -10372,7 +10372,7 @@
         <v/>
       </c>
       <c r="J84" s="9" t="str">
-        <f>product_listing!F84</f>
+        <f>product_listing!G84</f>
         <v/>
       </c>
       <c r="K84" s="9" t="str">
@@ -10384,7 +10384,7 @@
         <v/>
       </c>
       <c r="M84" s="9" t="str">
-        <f>product_listing!I84</f>
+        <f>product_listing!F84</f>
         <v/>
       </c>
       <c r="N84" s="9" t="str">
@@ -10396,7 +10396,7 @@
         <v/>
       </c>
       <c r="P84" s="9" t="str">
-        <f>product_listing!H84</f>
+        <f>product_listing!I84</f>
         <v/>
       </c>
       <c r="Q84" s="9" t="str">
@@ -10458,7 +10458,7 @@
         <v/>
       </c>
       <c r="G85" s="9" t="str">
-        <f>product_listing!G85</f>
+        <f>product_listing!H85</f>
         <v/>
       </c>
       <c r="H85" s="9" t="str">
@@ -10470,7 +10470,7 @@
         <v/>
       </c>
       <c r="J85" s="9" t="str">
-        <f>product_listing!F85</f>
+        <f>product_listing!G85</f>
         <v/>
       </c>
       <c r="K85" s="9" t="str">
@@ -10482,7 +10482,7 @@
         <v/>
       </c>
       <c r="M85" s="9" t="str">
-        <f>product_listing!I85</f>
+        <f>product_listing!F85</f>
         <v/>
       </c>
       <c r="N85" s="9" t="str">
@@ -10494,7 +10494,7 @@
         <v/>
       </c>
       <c r="P85" s="9" t="str">
-        <f>product_listing!H85</f>
+        <f>product_listing!I85</f>
         <v/>
       </c>
       <c r="Q85" s="9" t="str">
@@ -10556,7 +10556,7 @@
         <v/>
       </c>
       <c r="G86" s="9" t="str">
-        <f>product_listing!G86</f>
+        <f>product_listing!H86</f>
         <v/>
       </c>
       <c r="H86" s="9" t="str">
@@ -10568,7 +10568,7 @@
         <v/>
       </c>
       <c r="J86" s="9" t="str">
-        <f>product_listing!F86</f>
+        <f>product_listing!G86</f>
         <v/>
       </c>
       <c r="K86" s="9" t="str">
@@ -10580,7 +10580,7 @@
         <v/>
       </c>
       <c r="M86" s="9" t="str">
-        <f>product_listing!I86</f>
+        <f>product_listing!F86</f>
         <v/>
       </c>
       <c r="N86" s="9" t="str">
@@ -10592,7 +10592,7 @@
         <v/>
       </c>
       <c r="P86" s="9" t="str">
-        <f>product_listing!H86</f>
+        <f>product_listing!I86</f>
         <v/>
       </c>
       <c r="Q86" s="9" t="str">
@@ -10654,7 +10654,7 @@
         <v/>
       </c>
       <c r="G87" s="9" t="str">
-        <f>product_listing!G87</f>
+        <f>product_listing!H87</f>
         <v/>
       </c>
       <c r="H87" s="9" t="str">
@@ -10666,7 +10666,7 @@
         <v/>
       </c>
       <c r="J87" s="9" t="str">
-        <f>product_listing!F87</f>
+        <f>product_listing!G87</f>
         <v/>
       </c>
       <c r="K87" s="9" t="str">
@@ -10678,7 +10678,7 @@
         <v/>
       </c>
       <c r="M87" s="9" t="str">
-        <f>product_listing!I87</f>
+        <f>product_listing!F87</f>
         <v/>
       </c>
       <c r="N87" s="9" t="str">
@@ -10690,7 +10690,7 @@
         <v/>
       </c>
       <c r="P87" s="9" t="str">
-        <f>product_listing!H87</f>
+        <f>product_listing!I87</f>
         <v/>
       </c>
       <c r="Q87" s="9" t="str">
@@ -10752,7 +10752,7 @@
         <v/>
       </c>
       <c r="G88" s="9" t="str">
-        <f>product_listing!G88</f>
+        <f>product_listing!H88</f>
         <v/>
       </c>
       <c r="H88" s="9" t="str">
@@ -10764,7 +10764,7 @@
         <v/>
       </c>
       <c r="J88" s="9" t="str">
-        <f>product_listing!F88</f>
+        <f>product_listing!G88</f>
         <v/>
       </c>
       <c r="K88" s="9" t="str">
@@ -10776,7 +10776,7 @@
         <v/>
       </c>
       <c r="M88" s="9" t="str">
-        <f>product_listing!I88</f>
+        <f>product_listing!F88</f>
         <v/>
       </c>
       <c r="N88" s="9" t="str">
@@ -10788,7 +10788,7 @@
         <v/>
       </c>
       <c r="P88" s="9" t="str">
-        <f>product_listing!H88</f>
+        <f>product_listing!I88</f>
         <v/>
       </c>
       <c r="Q88" s="9" t="str">
@@ -10850,7 +10850,7 @@
         <v/>
       </c>
       <c r="G89" s="9" t="str">
-        <f>product_listing!G89</f>
+        <f>product_listing!H89</f>
         <v/>
       </c>
       <c r="H89" s="9" t="str">
@@ -10862,7 +10862,7 @@
         <v/>
       </c>
       <c r="J89" s="9" t="str">
-        <f>product_listing!F89</f>
+        <f>product_listing!G89</f>
         <v/>
       </c>
       <c r="K89" s="9" t="str">
@@ -10874,7 +10874,7 @@
         <v/>
       </c>
       <c r="M89" s="9" t="str">
-        <f>product_listing!I89</f>
+        <f>product_listing!F89</f>
         <v/>
       </c>
       <c r="N89" s="9" t="str">
@@ -10886,7 +10886,7 @@
         <v/>
       </c>
       <c r="P89" s="9" t="str">
-        <f>product_listing!H89</f>
+        <f>product_listing!I89</f>
         <v/>
       </c>
       <c r="Q89" s="9" t="str">
@@ -10948,7 +10948,7 @@
         <v/>
       </c>
       <c r="G90" s="9" t="str">
-        <f>product_listing!G90</f>
+        <f>product_listing!H90</f>
         <v/>
       </c>
       <c r="H90" s="9" t="str">
@@ -10960,7 +10960,7 @@
         <v/>
       </c>
       <c r="J90" s="9" t="str">
-        <f>product_listing!F90</f>
+        <f>product_listing!G90</f>
         <v/>
       </c>
       <c r="K90" s="9" t="str">
@@ -10972,7 +10972,7 @@
         <v/>
       </c>
       <c r="M90" s="9" t="str">
-        <f>product_listing!I90</f>
+        <f>product_listing!F90</f>
         <v/>
       </c>
       <c r="N90" s="9" t="str">
@@ -10984,7 +10984,7 @@
         <v/>
       </c>
       <c r="P90" s="9" t="str">
-        <f>product_listing!H90</f>
+        <f>product_listing!I90</f>
         <v/>
       </c>
       <c r="Q90" s="9" t="str">
@@ -11046,7 +11046,7 @@
         <v/>
       </c>
       <c r="G91" s="9" t="str">
-        <f>product_listing!G91</f>
+        <f>product_listing!H91</f>
         <v/>
       </c>
       <c r="H91" s="9" t="str">
@@ -11058,7 +11058,7 @@
         <v/>
       </c>
       <c r="J91" s="9" t="str">
-        <f>product_listing!F91</f>
+        <f>product_listing!G91</f>
         <v/>
       </c>
       <c r="K91" s="9" t="str">
@@ -11070,7 +11070,7 @@
         <v/>
       </c>
       <c r="M91" s="9" t="str">
-        <f>product_listing!I91</f>
+        <f>product_listing!F91</f>
         <v/>
       </c>
       <c r="N91" s="9" t="str">
@@ -11082,7 +11082,7 @@
         <v/>
       </c>
       <c r="P91" s="9" t="str">
-        <f>product_listing!H91</f>
+        <f>product_listing!I91</f>
         <v/>
       </c>
       <c r="Q91" s="9" t="str">
@@ -11144,7 +11144,7 @@
         <v/>
       </c>
       <c r="G92" s="9" t="str">
-        <f>product_listing!G92</f>
+        <f>product_listing!H92</f>
         <v/>
       </c>
       <c r="H92" s="9" t="str">
@@ -11156,7 +11156,7 @@
         <v/>
       </c>
       <c r="J92" s="9" t="str">
-        <f>product_listing!F92</f>
+        <f>product_listing!G92</f>
         <v/>
       </c>
       <c r="K92" s="9" t="str">
@@ -11168,7 +11168,7 @@
         <v/>
       </c>
       <c r="M92" s="9" t="str">
-        <f>product_listing!I92</f>
+        <f>product_listing!F92</f>
         <v/>
       </c>
       <c r="N92" s="9" t="str">
@@ -11180,7 +11180,7 @@
         <v/>
       </c>
       <c r="P92" s="9" t="str">
-        <f>product_listing!H92</f>
+        <f>product_listing!I92</f>
         <v/>
       </c>
       <c r="Q92" s="9" t="str">
@@ -11242,7 +11242,7 @@
         <v/>
       </c>
       <c r="G93" s="9" t="str">
-        <f>product_listing!G93</f>
+        <f>product_listing!H93</f>
         <v/>
       </c>
       <c r="H93" s="9" t="str">
@@ -11254,7 +11254,7 @@
         <v/>
       </c>
       <c r="J93" s="9" t="str">
-        <f>product_listing!F93</f>
+        <f>product_listing!G93</f>
         <v/>
       </c>
       <c r="K93" s="9" t="str">
@@ -11266,7 +11266,7 @@
         <v/>
       </c>
       <c r="M93" s="9" t="str">
-        <f>product_listing!I93</f>
+        <f>product_listing!F93</f>
         <v/>
       </c>
       <c r="N93" s="9" t="str">
@@ -11278,7 +11278,7 @@
         <v/>
       </c>
       <c r="P93" s="9" t="str">
-        <f>product_listing!H93</f>
+        <f>product_listing!I93</f>
         <v/>
       </c>
       <c r="Q93" s="9" t="str">
@@ -11340,7 +11340,7 @@
         <v/>
       </c>
       <c r="G94" s="9" t="str">
-        <f>product_listing!G94</f>
+        <f>product_listing!H94</f>
         <v/>
       </c>
       <c r="H94" s="9" t="str">
@@ -11352,7 +11352,7 @@
         <v/>
       </c>
       <c r="J94" s="9" t="str">
-        <f>product_listing!F94</f>
+        <f>product_listing!G94</f>
         <v/>
       </c>
       <c r="K94" s="9" t="str">
@@ -11364,7 +11364,7 @@
         <v/>
       </c>
       <c r="M94" s="9" t="str">
-        <f>product_listing!I94</f>
+        <f>product_listing!F94</f>
         <v/>
       </c>
       <c r="N94" s="9" t="str">
@@ -11376,7 +11376,7 @@
         <v/>
       </c>
       <c r="P94" s="9" t="str">
-        <f>product_listing!H94</f>
+        <f>product_listing!I94</f>
         <v/>
       </c>
       <c r="Q94" s="9" t="str">
@@ -11438,7 +11438,7 @@
         <v/>
       </c>
       <c r="G95" s="9" t="str">
-        <f>product_listing!G95</f>
+        <f>product_listing!H95</f>
         <v/>
       </c>
       <c r="H95" s="9" t="str">
@@ -11450,7 +11450,7 @@
         <v/>
       </c>
       <c r="J95" s="9" t="str">
-        <f>product_listing!F95</f>
+        <f>product_listing!G95</f>
         <v/>
       </c>
       <c r="K95" s="9" t="str">
@@ -11462,7 +11462,7 @@
         <v/>
       </c>
       <c r="M95" s="9" t="str">
-        <f>product_listing!I95</f>
+        <f>product_listing!F95</f>
         <v/>
       </c>
       <c r="N95" s="9" t="str">
@@ -11474,7 +11474,7 @@
         <v/>
       </c>
       <c r="P95" s="9" t="str">
-        <f>product_listing!H95</f>
+        <f>product_listing!I95</f>
         <v/>
       </c>
       <c r="Q95" s="9" t="str">
@@ -11536,7 +11536,7 @@
         <v/>
       </c>
       <c r="G96" s="9" t="str">
-        <f>product_listing!G96</f>
+        <f>product_listing!H96</f>
         <v/>
       </c>
       <c r="H96" s="9" t="str">
@@ -11548,7 +11548,7 @@
         <v/>
       </c>
       <c r="J96" s="9" t="str">
-        <f>product_listing!F96</f>
+        <f>product_listing!G96</f>
         <v/>
       </c>
       <c r="K96" s="9" t="str">
@@ -11560,7 +11560,7 @@
         <v/>
       </c>
       <c r="M96" s="9" t="str">
-        <f>product_listing!I96</f>
+        <f>product_listing!F96</f>
         <v/>
       </c>
       <c r="N96" s="9" t="str">
@@ -11572,7 +11572,7 @@
         <v/>
       </c>
       <c r="P96" s="9" t="str">
-        <f>product_listing!H96</f>
+        <f>product_listing!I96</f>
         <v/>
       </c>
       <c r="Q96" s="9" t="str">
@@ -11634,7 +11634,7 @@
         <v/>
       </c>
       <c r="G97" s="9" t="str">
-        <f>product_listing!G97</f>
+        <f>product_listing!H97</f>
         <v/>
       </c>
       <c r="H97" s="9" t="str">
@@ -11646,7 +11646,7 @@
         <v/>
       </c>
       <c r="J97" s="9" t="str">
-        <f>product_listing!F97</f>
+        <f>product_listing!G97</f>
         <v/>
       </c>
       <c r="K97" s="9" t="str">
@@ -11658,7 +11658,7 @@
         <v/>
       </c>
       <c r="M97" s="9" t="str">
-        <f>product_listing!I97</f>
+        <f>product_listing!F97</f>
         <v/>
       </c>
       <c r="N97" s="9" t="str">
@@ -11670,7 +11670,7 @@
         <v/>
       </c>
       <c r="P97" s="9" t="str">
-        <f>product_listing!H97</f>
+        <f>product_listing!I97</f>
         <v/>
       </c>
       <c r="Q97" s="9" t="str">
@@ -11732,7 +11732,7 @@
         <v/>
       </c>
       <c r="G98" s="9" t="str">
-        <f>product_listing!G98</f>
+        <f>product_listing!H98</f>
         <v/>
       </c>
       <c r="H98" s="9" t="str">
@@ -11744,7 +11744,7 @@
         <v/>
       </c>
       <c r="J98" s="9" t="str">
-        <f>product_listing!F98</f>
+        <f>product_listing!G98</f>
         <v/>
       </c>
       <c r="K98" s="9" t="str">
@@ -11756,7 +11756,7 @@
         <v/>
       </c>
       <c r="M98" s="9" t="str">
-        <f>product_listing!I98</f>
+        <f>product_listing!F98</f>
         <v/>
       </c>
       <c r="N98" s="9" t="str">
@@ -11768,7 +11768,7 @@
         <v/>
       </c>
       <c r="P98" s="9" t="str">
-        <f>product_listing!H98</f>
+        <f>product_listing!I98</f>
         <v/>
       </c>
       <c r="Q98" s="9" t="str">
@@ -11830,7 +11830,7 @@
         <v/>
       </c>
       <c r="G99" s="9" t="str">
-        <f>product_listing!G99</f>
+        <f>product_listing!H99</f>
         <v/>
       </c>
       <c r="H99" s="9" t="str">
@@ -11842,7 +11842,7 @@
         <v/>
       </c>
       <c r="J99" s="9" t="str">
-        <f>product_listing!F99</f>
+        <f>product_listing!G99</f>
         <v/>
       </c>
       <c r="K99" s="9" t="str">
@@ -11854,7 +11854,7 @@
         <v/>
       </c>
       <c r="M99" s="9" t="str">
-        <f>product_listing!I99</f>
+        <f>product_listing!F99</f>
         <v/>
       </c>
       <c r="N99" s="9" t="str">
@@ -11866,7 +11866,7 @@
         <v/>
       </c>
       <c r="P99" s="9" t="str">
-        <f>product_listing!H99</f>
+        <f>product_listing!I99</f>
         <v/>
       </c>
       <c r="Q99" s="9" t="str">
@@ -11928,7 +11928,7 @@
         <v/>
       </c>
       <c r="G100" s="9" t="str">
-        <f>product_listing!G100</f>
+        <f>product_listing!H100</f>
         <v/>
       </c>
       <c r="H100" s="9" t="str">
@@ -11940,7 +11940,7 @@
         <v/>
       </c>
       <c r="J100" s="9" t="str">
-        <f>product_listing!F100</f>
+        <f>product_listing!G100</f>
         <v/>
       </c>
       <c r="K100" s="9" t="str">
@@ -11952,7 +11952,7 @@
         <v/>
       </c>
       <c r="M100" s="9" t="str">
-        <f>product_listing!I100</f>
+        <f>product_listing!F100</f>
         <v/>
       </c>
       <c r="N100" s="9" t="str">
@@ -11964,7 +11964,7 @@
         <v/>
       </c>
       <c r="P100" s="9" t="str">
-        <f>product_listing!H100</f>
+        <f>product_listing!I100</f>
         <v/>
       </c>
       <c r="Q100" s="9" t="str">
@@ -12026,7 +12026,7 @@
         <v/>
       </c>
       <c r="G101" s="9" t="str">
-        <f>product_listing!G101</f>
+        <f>product_listing!H101</f>
         <v/>
       </c>
       <c r="H101" s="9" t="str">
@@ -12038,7 +12038,7 @@
         <v/>
       </c>
       <c r="J101" s="9" t="str">
-        <f>product_listing!F101</f>
+        <f>product_listing!G101</f>
         <v/>
       </c>
       <c r="K101" s="9" t="str">
@@ -12050,7 +12050,7 @@
         <v/>
       </c>
       <c r="M101" s="9" t="str">
-        <f>product_listing!I101</f>
+        <f>product_listing!F101</f>
         <v/>
       </c>
       <c r="N101" s="9" t="str">
@@ -12062,7 +12062,7 @@
         <v/>
       </c>
       <c r="P101" s="9" t="str">
-        <f>product_listing!H101</f>
+        <f>product_listing!I101</f>
         <v/>
       </c>
       <c r="Q101" s="9" t="str">
@@ -12124,7 +12124,7 @@
         <v/>
       </c>
       <c r="G102" s="9" t="str">
-        <f>product_listing!G102</f>
+        <f>product_listing!H102</f>
         <v/>
       </c>
       <c r="H102" s="9" t="str">
@@ -12136,7 +12136,7 @@
         <v/>
       </c>
       <c r="J102" s="9" t="str">
-        <f>product_listing!F102</f>
+        <f>product_listing!G102</f>
         <v/>
       </c>
       <c r="K102" s="9" t="str">
@@ -12148,7 +12148,7 @@
         <v/>
       </c>
       <c r="M102" s="9" t="str">
-        <f>product_listing!I102</f>
+        <f>product_listing!F102</f>
         <v/>
       </c>
       <c r="N102" s="9" t="str">
@@ -12160,7 +12160,7 @@
         <v/>
       </c>
       <c r="P102" s="9" t="str">
-        <f>product_listing!H102</f>
+        <f>product_listing!I102</f>
         <v/>
       </c>
       <c r="Q102" s="9" t="str">
@@ -12222,7 +12222,7 @@
         <v/>
       </c>
       <c r="G103" s="9" t="str">
-        <f>product_listing!G103</f>
+        <f>product_listing!H103</f>
         <v/>
       </c>
       <c r="H103" s="9" t="str">
@@ -12234,7 +12234,7 @@
         <v/>
       </c>
       <c r="J103" s="9" t="str">
-        <f>product_listing!F103</f>
+        <f>product_listing!G103</f>
         <v/>
       </c>
       <c r="K103" s="9" t="str">
@@ -12246,7 +12246,7 @@
         <v/>
       </c>
       <c r="M103" s="9" t="str">
-        <f>product_listing!I103</f>
+        <f>product_listing!F103</f>
         <v/>
       </c>
       <c r="N103" s="9" t="str">
@@ -12258,7 +12258,7 @@
         <v/>
       </c>
       <c r="P103" s="9" t="str">
-        <f>product_listing!H103</f>
+        <f>product_listing!I103</f>
         <v/>
       </c>
       <c r="Q103" s="9" t="str">
@@ -12320,7 +12320,7 @@
         <v/>
       </c>
       <c r="G104" s="9" t="str">
-        <f>product_listing!G104</f>
+        <f>product_listing!H104</f>
         <v/>
       </c>
       <c r="H104" s="9" t="str">
@@ -12332,7 +12332,7 @@
         <v/>
       </c>
       <c r="J104" s="9" t="str">
-        <f>product_listing!F104</f>
+        <f>product_listing!G104</f>
         <v/>
       </c>
       <c r="K104" s="9" t="str">
@@ -12344,7 +12344,7 @@
         <v/>
       </c>
       <c r="M104" s="9" t="str">
-        <f>product_listing!I104</f>
+        <f>product_listing!F104</f>
         <v/>
       </c>
       <c r="N104" s="9" t="str">
@@ -12356,7 +12356,7 @@
         <v/>
       </c>
       <c r="P104" s="9" t="str">
-        <f>product_listing!H104</f>
+        <f>product_listing!I104</f>
         <v/>
       </c>
       <c r="Q104" s="9" t="str">
@@ -12418,7 +12418,7 @@
         <v/>
       </c>
       <c r="G105" s="9" t="str">
-        <f>product_listing!G105</f>
+        <f>product_listing!H105</f>
         <v/>
       </c>
       <c r="H105" s="9" t="str">
@@ -12430,7 +12430,7 @@
         <v/>
       </c>
       <c r="J105" s="9" t="str">
-        <f>product_listing!F105</f>
+        <f>product_listing!G105</f>
         <v/>
       </c>
       <c r="K105" s="9" t="str">
@@ -12442,7 +12442,7 @@
         <v/>
       </c>
       <c r="M105" s="9" t="str">
-        <f>product_listing!I105</f>
+        <f>product_listing!F105</f>
         <v/>
       </c>
       <c r="N105" s="9" t="str">
@@ -12454,7 +12454,7 @@
         <v/>
       </c>
       <c r="P105" s="9" t="str">
-        <f>product_listing!H105</f>
+        <f>product_listing!I105</f>
         <v/>
       </c>
       <c r="Q105" s="9" t="str">
@@ -12516,7 +12516,7 @@
         <v/>
       </c>
       <c r="G106" s="9" t="str">
-        <f>product_listing!G106</f>
+        <f>product_listing!H106</f>
         <v/>
       </c>
       <c r="H106" s="9" t="str">
@@ -12528,7 +12528,7 @@
         <v/>
       </c>
       <c r="J106" s="9" t="str">
-        <f>product_listing!F106</f>
+        <f>product_listing!G106</f>
         <v/>
       </c>
       <c r="K106" s="9" t="str">
@@ -12540,7 +12540,7 @@
         <v/>
       </c>
       <c r="M106" s="9" t="str">
-        <f>product_listing!I106</f>
+        <f>product_listing!F106</f>
         <v/>
       </c>
       <c r="N106" s="9" t="str">
@@ -12552,7 +12552,7 @@
         <v/>
       </c>
       <c r="P106" s="9" t="str">
-        <f>product_listing!H106</f>
+        <f>product_listing!I106</f>
         <v/>
       </c>
       <c r="Q106" s="9" t="str">
@@ -12614,7 +12614,7 @@
         <v/>
       </c>
       <c r="G107" s="9" t="str">
-        <f>product_listing!G107</f>
+        <f>product_listing!H107</f>
         <v/>
       </c>
       <c r="H107" s="9" t="str">
@@ -12626,7 +12626,7 @@
         <v/>
       </c>
       <c r="J107" s="9" t="str">
-        <f>product_listing!F107</f>
+        <f>product_listing!G107</f>
         <v/>
       </c>
       <c r="K107" s="9" t="str">
@@ -12638,7 +12638,7 @@
         <v/>
       </c>
       <c r="M107" s="9" t="str">
-        <f>product_listing!I107</f>
+        <f>product_listing!F107</f>
         <v/>
       </c>
       <c r="N107" s="9" t="str">
@@ -12650,7 +12650,7 @@
         <v/>
       </c>
       <c r="P107" s="9" t="str">
-        <f>product_listing!H107</f>
+        <f>product_listing!I107</f>
         <v/>
       </c>
       <c r="Q107" s="9" t="str">
@@ -12712,7 +12712,7 @@
         <v/>
       </c>
       <c r="G108" s="9" t="str">
-        <f>product_listing!G108</f>
+        <f>product_listing!H108</f>
         <v/>
       </c>
       <c r="H108" s="9" t="str">
@@ -12724,7 +12724,7 @@
         <v/>
       </c>
       <c r="J108" s="9" t="str">
-        <f>product_listing!F108</f>
+        <f>product_listing!G108</f>
         <v/>
       </c>
       <c r="K108" s="9" t="str">
@@ -12736,7 +12736,7 @@
         <v/>
       </c>
       <c r="M108" s="9" t="str">
-        <f>product_listing!I108</f>
+        <f>product_listing!F108</f>
         <v/>
       </c>
       <c r="N108" s="9" t="str">
@@ -12748,7 +12748,7 @@
         <v/>
       </c>
       <c r="P108" s="9" t="str">
-        <f>product_listing!H108</f>
+        <f>product_listing!I108</f>
         <v/>
       </c>
       <c r="Q108" s="9" t="str">
@@ -12810,7 +12810,7 @@
         <v/>
       </c>
       <c r="G109" s="9" t="str">
-        <f>product_listing!G109</f>
+        <f>product_listing!H109</f>
         <v/>
       </c>
       <c r="H109" s="9" t="str">
@@ -12822,7 +12822,7 @@
         <v/>
       </c>
       <c r="J109" s="9" t="str">
-        <f>product_listing!F109</f>
+        <f>product_listing!G109</f>
         <v/>
       </c>
       <c r="K109" s="9" t="str">
@@ -12834,7 +12834,7 @@
         <v/>
       </c>
       <c r="M109" s="9" t="str">
-        <f>product_listing!I109</f>
+        <f>product_listing!F109</f>
         <v/>
       </c>
       <c r="N109" s="9" t="str">
@@ -12846,7 +12846,7 @@
         <v/>
       </c>
       <c r="P109" s="9" t="str">
-        <f>product_listing!H109</f>
+        <f>product_listing!I109</f>
         <v/>
       </c>
       <c r="Q109" s="9" t="str">
@@ -12908,7 +12908,7 @@
         <v/>
       </c>
       <c r="G110" s="9" t="str">
-        <f>product_listing!G110</f>
+        <f>product_listing!H110</f>
         <v/>
       </c>
       <c r="H110" s="9" t="str">
@@ -12920,7 +12920,7 @@
         <v/>
       </c>
       <c r="J110" s="9" t="str">
-        <f>product_listing!F110</f>
+        <f>product_listing!G110</f>
         <v/>
       </c>
       <c r="K110" s="9" t="str">
@@ -12932,7 +12932,7 @@
         <v/>
       </c>
       <c r="M110" s="9" t="str">
-        <f>product_listing!I110</f>
+        <f>product_listing!F110</f>
         <v/>
       </c>
       <c r="N110" s="9" t="str">
@@ -12944,7 +12944,7 @@
         <v/>
       </c>
       <c r="P110" s="9" t="str">
-        <f>product_listing!H110</f>
+        <f>product_listing!I110</f>
         <v/>
       </c>
       <c r="Q110" s="9" t="str">
@@ -13006,7 +13006,7 @@
         <v/>
       </c>
       <c r="G111" s="9" t="str">
-        <f>product_listing!G111</f>
+        <f>product_listing!H111</f>
         <v/>
       </c>
       <c r="H111" s="9" t="str">
@@ -13018,7 +13018,7 @@
         <v/>
       </c>
       <c r="J111" s="9" t="str">
-        <f>product_listing!F111</f>
+        <f>product_listing!G111</f>
         <v/>
       </c>
       <c r="K111" s="9" t="str">
@@ -13030,7 +13030,7 @@
         <v/>
       </c>
       <c r="M111" s="9" t="str">
-        <f>product_listing!I111</f>
+        <f>product_listing!F111</f>
         <v/>
       </c>
       <c r="N111" s="9" t="str">
@@ -13042,7 +13042,7 @@
         <v/>
       </c>
       <c r="P111" s="9" t="str">
-        <f>product_listing!H111</f>
+        <f>product_listing!I111</f>
         <v/>
       </c>
       <c r="Q111" s="9" t="str">
@@ -13104,7 +13104,7 @@
         <v/>
       </c>
       <c r="G112" s="9" t="str">
-        <f>product_listing!G112</f>
+        <f>product_listing!H112</f>
         <v/>
       </c>
       <c r="H112" s="9" t="str">
@@ -13116,7 +13116,7 @@
         <v/>
       </c>
       <c r="J112" s="9" t="str">
-        <f>product_listing!F112</f>
+        <f>product_listing!G112</f>
         <v/>
       </c>
       <c r="K112" s="9" t="str">
@@ -13128,7 +13128,7 @@
         <v/>
       </c>
       <c r="M112" s="9" t="str">
-        <f>product_listing!I112</f>
+        <f>product_listing!F112</f>
         <v/>
       </c>
       <c r="N112" s="9" t="str">
@@ -13140,7 +13140,7 @@
         <v/>
       </c>
       <c r="P112" s="9" t="str">
-        <f>product_listing!H112</f>
+        <f>product_listing!I112</f>
         <v/>
       </c>
       <c r="Q112" s="9" t="str">
@@ -13202,7 +13202,7 @@
         <v/>
       </c>
       <c r="G113" s="9" t="str">
-        <f>product_listing!G113</f>
+        <f>product_listing!H113</f>
         <v/>
       </c>
       <c r="H113" s="9" t="str">
@@ -13214,7 +13214,7 @@
         <v/>
       </c>
       <c r="J113" s="9" t="str">
-        <f>product_listing!F113</f>
+        <f>product_listing!G113</f>
         <v/>
       </c>
       <c r="K113" s="9" t="str">
@@ -13226,7 +13226,7 @@
         <v/>
       </c>
       <c r="M113" s="9" t="str">
-        <f>product_listing!I113</f>
+        <f>product_listing!F113</f>
         <v/>
       </c>
       <c r="N113" s="9" t="str">
@@ -13238,7 +13238,7 @@
         <v/>
       </c>
       <c r="P113" s="9" t="str">
-        <f>product_listing!H113</f>
+        <f>product_listing!I113</f>
         <v/>
       </c>
       <c r="Q113" s="9" t="str">
@@ -13300,7 +13300,7 @@
         <v/>
       </c>
       <c r="G114" s="9" t="str">
-        <f>product_listing!G114</f>
+        <f>product_listing!H114</f>
         <v/>
       </c>
       <c r="H114" s="9" t="str">
@@ -13312,7 +13312,7 @@
         <v/>
       </c>
       <c r="J114" s="9" t="str">
-        <f>product_listing!F114</f>
+        <f>product_listing!G114</f>
         <v/>
       </c>
       <c r="K114" s="9" t="str">
@@ -13324,7 +13324,7 @@
         <v/>
       </c>
       <c r="M114" s="9" t="str">
-        <f>product_listing!I114</f>
+        <f>product_listing!F114</f>
         <v/>
       </c>
       <c r="N114" s="9" t="str">
@@ -13336,7 +13336,7 @@
         <v/>
       </c>
       <c r="P114" s="9" t="str">
-        <f>product_listing!H114</f>
+        <f>product_listing!I114</f>
         <v/>
       </c>
       <c r="Q114" s="9" t="str">
@@ -13398,7 +13398,7 @@
         <v/>
       </c>
       <c r="G115" s="9" t="str">
-        <f>product_listing!G115</f>
+        <f>product_listing!H115</f>
         <v/>
       </c>
       <c r="H115" s="9" t="str">
@@ -13410,7 +13410,7 @@
         <v/>
       </c>
       <c r="J115" s="9" t="str">
-        <f>product_listing!F115</f>
+        <f>product_listing!G115</f>
         <v/>
       </c>
       <c r="K115" s="9" t="str">
@@ -13422,7 +13422,7 @@
         <v/>
       </c>
       <c r="M115" s="9" t="str">
-        <f>product_listing!I115</f>
+        <f>product_listing!F115</f>
         <v/>
       </c>
       <c r="N115" s="9" t="str">
@@ -13434,7 +13434,7 @@
         <v/>
       </c>
       <c r="P115" s="9" t="str">
-        <f>product_listing!H115</f>
+        <f>product_listing!I115</f>
         <v/>
       </c>
       <c r="Q115" s="9" t="str">
@@ -13496,7 +13496,7 @@
         <v/>
       </c>
       <c r="G116" s="9" t="str">
-        <f>product_listing!G116</f>
+        <f>product_listing!H116</f>
         <v/>
       </c>
       <c r="H116" s="9" t="str">
@@ -13508,7 +13508,7 @@
         <v/>
       </c>
       <c r="J116" s="9" t="str">
-        <f>product_listing!F116</f>
+        <f>product_listing!G116</f>
         <v/>
       </c>
       <c r="K116" s="9" t="str">
@@ -13520,7 +13520,7 @@
         <v/>
       </c>
       <c r="M116" s="9" t="str">
-        <f>product_listing!I116</f>
+        <f>product_listing!F116</f>
         <v/>
       </c>
       <c r="N116" s="9" t="str">
@@ -13532,7 +13532,7 @@
         <v/>
       </c>
       <c r="P116" s="9" t="str">
-        <f>product_listing!H116</f>
+        <f>product_listing!I116</f>
         <v/>
       </c>
       <c r="Q116" s="9" t="str">
@@ -13594,7 +13594,7 @@
         <v/>
       </c>
       <c r="G117" s="9" t="str">
-        <f>product_listing!G117</f>
+        <f>product_listing!H117</f>
         <v/>
       </c>
       <c r="H117" s="9" t="str">
@@ -13606,7 +13606,7 @@
         <v/>
       </c>
       <c r="J117" s="9" t="str">
-        <f>product_listing!F117</f>
+        <f>product_listing!G117</f>
         <v/>
       </c>
       <c r="K117" s="9" t="str">
@@ -13618,7 +13618,7 @@
         <v/>
       </c>
       <c r="M117" s="9" t="str">
-        <f>product_listing!I117</f>
+        <f>product_listing!F117</f>
         <v/>
       </c>
       <c r="N117" s="9" t="str">
@@ -13630,7 +13630,7 @@
         <v/>
       </c>
       <c r="P117" s="9" t="str">
-        <f>product_listing!H117</f>
+        <f>product_listing!I117</f>
         <v/>
       </c>
       <c r="Q117" s="9" t="str">
@@ -13692,7 +13692,7 @@
         <v/>
       </c>
       <c r="G118" s="9" t="str">
-        <f>product_listing!G118</f>
+        <f>product_listing!H118</f>
         <v/>
       </c>
       <c r="H118" s="9" t="str">
@@ -13704,7 +13704,7 @@
         <v/>
       </c>
       <c r="J118" s="9" t="str">
-        <f>product_listing!F118</f>
+        <f>product_listing!G118</f>
         <v/>
       </c>
       <c r="K118" s="9" t="str">
@@ -13716,7 +13716,7 @@
         <v/>
       </c>
       <c r="M118" s="9" t="str">
-        <f>product_listing!I118</f>
+        <f>product_listing!F118</f>
         <v/>
       </c>
       <c r="N118" s="9" t="str">
@@ -13728,7 +13728,7 @@
         <v/>
       </c>
       <c r="P118" s="9" t="str">
-        <f>product_listing!H118</f>
+        <f>product_listing!I118</f>
         <v/>
       </c>
       <c r="Q118" s="9" t="str">
@@ -13790,7 +13790,7 @@
         <v/>
       </c>
       <c r="G119" s="9" t="str">
-        <f>product_listing!G119</f>
+        <f>product_listing!H119</f>
         <v/>
       </c>
       <c r="H119" s="9" t="str">
@@ -13802,7 +13802,7 @@
         <v/>
       </c>
       <c r="J119" s="9" t="str">
-        <f>product_listing!F119</f>
+        <f>product_listing!G119</f>
         <v/>
       </c>
       <c r="K119" s="9" t="str">
@@ -13814,7 +13814,7 @@
         <v/>
       </c>
       <c r="M119" s="9" t="str">
-        <f>product_listing!I119</f>
+        <f>product_listing!F119</f>
         <v/>
       </c>
       <c r="N119" s="9" t="str">
@@ -13826,7 +13826,7 @@
         <v/>
       </c>
       <c r="P119" s="9" t="str">
-        <f>product_listing!H119</f>
+        <f>product_listing!I119</f>
         <v/>
       </c>
       <c r="Q119" s="9" t="str">
@@ -13888,7 +13888,7 @@
         <v/>
       </c>
       <c r="G120" s="9" t="str">
-        <f>product_listing!G120</f>
+        <f>product_listing!H120</f>
         <v/>
       </c>
       <c r="H120" s="9" t="str">
@@ -13900,7 +13900,7 @@
         <v/>
       </c>
       <c r="J120" s="9" t="str">
-        <f>product_listing!F120</f>
+        <f>product_listing!G120</f>
         <v/>
       </c>
       <c r="K120" s="9" t="str">
@@ -13912,7 +13912,7 @@
         <v/>
       </c>
       <c r="M120" s="9" t="str">
-        <f>product_listing!I120</f>
+        <f>product_listing!F120</f>
         <v/>
       </c>
       <c r="N120" s="9" t="str">
@@ -13924,7 +13924,7 @@
         <v/>
       </c>
       <c r="P120" s="9" t="str">
-        <f>product_listing!H120</f>
+        <f>product_listing!I120</f>
         <v/>
       </c>
       <c r="Q120" s="9" t="str">
@@ -13986,7 +13986,7 @@
         <v/>
       </c>
       <c r="G121" s="9" t="str">
-        <f>product_listing!G121</f>
+        <f>product_listing!H121</f>
         <v/>
       </c>
       <c r="H121" s="9" t="str">
@@ -13998,7 +13998,7 @@
         <v/>
       </c>
       <c r="J121" s="9" t="str">
-        <f>product_listing!F121</f>
+        <f>product_listing!G121</f>
         <v/>
       </c>
       <c r="K121" s="9" t="str">
@@ -14010,7 +14010,7 @@
         <v/>
       </c>
       <c r="M121" s="9" t="str">
-        <f>product_listing!I121</f>
+        <f>product_listing!F121</f>
         <v/>
       </c>
       <c r="N121" s="9" t="str">
@@ -14022,7 +14022,7 @@
         <v/>
       </c>
       <c r="P121" s="9" t="str">
-        <f>product_listing!H121</f>
+        <f>product_listing!I121</f>
         <v/>
       </c>
       <c r="Q121" s="9" t="str">
@@ -14084,7 +14084,7 @@
         <v/>
       </c>
       <c r="G122" s="9" t="str">
-        <f>product_listing!G122</f>
+        <f>product_listing!H122</f>
         <v/>
       </c>
       <c r="H122" s="9" t="str">
@@ -14096,7 +14096,7 @@
         <v/>
       </c>
       <c r="J122" s="9" t="str">
-        <f>product_listing!F122</f>
+        <f>product_listing!G122</f>
         <v/>
       </c>
       <c r="K122" s="9" t="str">
@@ -14108,7 +14108,7 @@
         <v/>
       </c>
       <c r="M122" s="9" t="str">
-        <f>product_listing!I122</f>
+        <f>product_listing!F122</f>
         <v/>
       </c>
       <c r="N122" s="9" t="str">
@@ -14120,7 +14120,7 @@
         <v/>
       </c>
       <c r="P122" s="9" t="str">
-        <f>product_listing!H122</f>
+        <f>product_listing!I122</f>
         <v/>
       </c>
       <c r="Q122" s="9" t="str">
@@ -14182,7 +14182,7 @@
         <v/>
       </c>
       <c r="G123" s="9" t="str">
-        <f>product_listing!G123</f>
+        <f>product_listing!H123</f>
         <v/>
       </c>
       <c r="H123" s="9" t="str">
@@ -14194,7 +14194,7 @@
         <v/>
       </c>
       <c r="J123" s="9" t="str">
-        <f>product_listing!F123</f>
+        <f>product_listing!G123</f>
         <v/>
       </c>
       <c r="K123" s="9" t="str">
@@ -14206,7 +14206,7 @@
         <v/>
       </c>
       <c r="M123" s="9" t="str">
-        <f>product_listing!I123</f>
+        <f>product_listing!F123</f>
         <v/>
       </c>
       <c r="N123" s="9" t="str">
@@ -14218,7 +14218,7 @@
         <v/>
       </c>
       <c r="P123" s="9" t="str">
-        <f>product_listing!H123</f>
+        <f>product_listing!I123</f>
         <v/>
       </c>
       <c r="Q123" s="9" t="str">
@@ -14280,7 +14280,7 @@
         <v/>
       </c>
       <c r="G124" s="9" t="str">
-        <f>product_listing!G124</f>
+        <f>product_listing!H124</f>
         <v/>
       </c>
       <c r="H124" s="9" t="str">
@@ -14292,7 +14292,7 @@
         <v/>
       </c>
       <c r="J124" s="9" t="str">
-        <f>product_listing!F124</f>
+        <f>product_listing!G124</f>
         <v/>
       </c>
       <c r="K124" s="9" t="str">
@@ -14304,7 +14304,7 @@
         <v/>
       </c>
       <c r="M124" s="9" t="str">
-        <f>product_listing!I124</f>
+        <f>product_listing!F124</f>
         <v/>
       </c>
       <c r="N124" s="9" t="str">
@@ -14316,7 +14316,7 @@
         <v/>
       </c>
       <c r="P124" s="9" t="str">
-        <f>product_listing!H124</f>
+        <f>product_listing!I124</f>
         <v/>
       </c>
       <c r="Q124" s="9" t="str">

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -2770,7 +2770,10 @@
         <f>product_listing!D6</f>
         <v>https://doi.org/10.5194/essd-8-383-2016</v>
       </c>
-      <c r="T6" s="9"/>
+      <c r="T6" s="11" t="str">
+        <f>product_listing!E6</f>
+        <v>https://socat.info/</v>
+      </c>
       <c r="U6" s="9" t="str">
         <f t="shared" si="9"/>
         <v>Highlight</v>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="100">
   <si>
     <t>Data category</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>The largest collection of surface ocean carbon observations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Surface Ocean CO2 Atlas features surface fCO2 measurements from both the open ocean and the coastal ocean, predominantly sourced from research vessels, ships of opportunity, and autonomous platforms including fixed moorings and uncrewed surface vehicles (USVs) (Bakker et al., 2016). It represents the most extensive collection of observational ocean CO2 data for the global surface ocean. Since 2013, SOCAT has been updated annually. Dataset flags indicate the estimated uncertainty and completeness of metadata in SOCAT synthesis products. The SOCAT gridded product contains fCO2 values with an estimated uncertainty of less than 5 µatm. </t>
   </si>
   <si>
     <t>GLODAPv2</t>
@@ -935,38 +938,41 @@
       <c r="L6" s="8" t="s">
         <v>56</v>
       </c>
+      <c r="M6" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8">
@@ -2187,7 +2193,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>8</v>
@@ -2204,10 +2210,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>52</v>
@@ -2215,16 +2221,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4">
@@ -2232,18 +2238,18 @@
         <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>29</v>
@@ -2251,10 +2257,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>20</v>
@@ -2262,25 +2268,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
       <c r="D8" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
       <c r="D9" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
       <c r="D10" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2319,70 +2325,70 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F1" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="I1" s="11" t="s">
+      <c r="J1" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="K1" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="K1" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="L1" s="11" t="s">
+      <c r="M1" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="N1" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="O1" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="N1" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>87</v>
-      </c>
       <c r="P1" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="U1" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="V1" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
@@ -2403,7 +2409,7 @@
         <v>https://essd.copernicus.org/articles/13/777/2021/essd-13-777-2021-avatar-web.png</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>8</v>
@@ -2413,7 +2419,7 @@
         <v>Open Ocean, Surface</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>7</v>
@@ -2423,7 +2429,7 @@
         <v>monthly</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L2" s="11" t="s">
         <v>6</v>
@@ -2433,7 +2439,7 @@
         <v>1.0°</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>9</v>
@@ -2822,8 +2828,8 @@
         <v>Description</v>
       </c>
       <c r="V6" s="15" t="str">
-        <f>product_listing!L6</f>
-        <v>The largest collection of surface ocean carbon observations</v>
+        <f>product_listing!M6</f>
+        <v>The Surface Ocean CO2 Atlas features surface fCO2 measurements from both the open ocean and the coastal ocean, predominantly sourced from research vessels, ships of opportunity, and autonomous platforms including fixed moorings and uncrewed surface vehicles (USVs) (Bakker et al., 2016). It represents the most extensive collection of observational ocean CO2 data for the global surface ocean. Since 2013, SOCAT has been updated annually. Dataset flags indicate the estimated uncertainty and completeness of metadata in SOCAT synthesis products. The SOCAT gridded product contains fCO2 values with an estimated uncertainty of less than 5 µatm. </v>
       </c>
     </row>
     <row r="7">
@@ -7661,10 +7667,7 @@
         <f>product_listing!J60</f>
         <v/>
       </c>
-      <c r="Q60" s="11" t="str">
-        <f>product_listing!L60</f>
-        <v/>
-      </c>
+      <c r="Q60" s="11"/>
       <c r="R60" s="11" t="str">
         <f>product_listing!C60</f>
         <v/>
@@ -7751,10 +7754,7 @@
         <f>product_listing!J61</f>
         <v/>
       </c>
-      <c r="Q61" s="11" t="str">
-        <f t="shared" ref="Q61:Q124" si="242">#REF!</f>
-        <v>#REF!</v>
-      </c>
+      <c r="Q61" s="11"/>
       <c r="R61" s="11" t="str">
         <f>product_listing!C61</f>
         <v/>
@@ -7841,10 +7841,7 @@
         <f>product_listing!J62</f>
         <v/>
       </c>
-      <c r="Q62" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q62" s="11"/>
       <c r="R62" s="11" t="str">
         <f>product_listing!C62</f>
         <v/>
@@ -7884,11 +7881,11 @@
         <v/>
       </c>
       <c r="E63" s="11" t="str">
-        <f t="shared" ref="E63:F63" si="243">if(not(isblank($B63)), E62, "")</f>
+        <f t="shared" ref="E63:F63" si="242">if(not(isblank($B63)), E62, "")</f>
         <v/>
       </c>
       <c r="F63" s="11" t="str">
-        <f t="shared" si="243"/>
+        <f t="shared" si="242"/>
         <v/>
       </c>
       <c r="G63" s="11" t="str">
@@ -7896,11 +7893,11 @@
         <v/>
       </c>
       <c r="H63" s="11" t="str">
-        <f t="shared" ref="H63:I63" si="244">if(not(isblank($B63)), H62, "")</f>
+        <f t="shared" ref="H63:I63" si="243">if(not(isblank($B63)), H62, "")</f>
         <v/>
       </c>
       <c r="I63" s="11" t="str">
-        <f t="shared" si="244"/>
+        <f t="shared" si="243"/>
         <v/>
       </c>
       <c r="J63" s="11" t="str">
@@ -7908,11 +7905,11 @@
         <v/>
       </c>
       <c r="K63" s="11" t="str">
-        <f t="shared" ref="K63:L63" si="245">if(not(isblank($B63)), K62, "")</f>
+        <f t="shared" ref="K63:L63" si="244">if(not(isblank($B63)), K62, "")</f>
         <v/>
       </c>
       <c r="L63" s="11" t="str">
-        <f t="shared" si="245"/>
+        <f t="shared" si="244"/>
         <v/>
       </c>
       <c r="M63" s="11" t="str">
@@ -7920,21 +7917,18 @@
         <v/>
       </c>
       <c r="N63" s="11" t="str">
-        <f t="shared" ref="N63:O63" si="246">if(not(isblank($B63)), N62, "")</f>
+        <f t="shared" ref="N63:O63" si="245">if(not(isblank($B63)), N62, "")</f>
         <v/>
       </c>
       <c r="O63" s="11" t="str">
-        <f t="shared" si="246"/>
+        <f t="shared" si="245"/>
         <v/>
       </c>
       <c r="P63" s="11" t="str">
         <f>product_listing!J63</f>
         <v/>
       </c>
-      <c r="Q63" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q63" s="11"/>
       <c r="R63" s="11" t="str">
         <f>product_listing!C63</f>
         <v/>
@@ -7974,11 +7968,11 @@
         <v/>
       </c>
       <c r="E64" s="11" t="str">
-        <f t="shared" ref="E64:F64" si="247">if(not(isblank($B64)), E63, "")</f>
+        <f t="shared" ref="E64:F64" si="246">if(not(isblank($B64)), E63, "")</f>
         <v/>
       </c>
       <c r="F64" s="11" t="str">
-        <f t="shared" si="247"/>
+        <f t="shared" si="246"/>
         <v/>
       </c>
       <c r="G64" s="11" t="str">
@@ -7986,11 +7980,11 @@
         <v/>
       </c>
       <c r="H64" s="11" t="str">
-        <f t="shared" ref="H64:I64" si="248">if(not(isblank($B64)), H63, "")</f>
+        <f t="shared" ref="H64:I64" si="247">if(not(isblank($B64)), H63, "")</f>
         <v/>
       </c>
       <c r="I64" s="11" t="str">
-        <f t="shared" si="248"/>
+        <f t="shared" si="247"/>
         <v/>
       </c>
       <c r="J64" s="11" t="str">
@@ -7998,11 +7992,11 @@
         <v/>
       </c>
       <c r="K64" s="11" t="str">
-        <f t="shared" ref="K64:L64" si="249">if(not(isblank($B64)), K63, "")</f>
+        <f t="shared" ref="K64:L64" si="248">if(not(isblank($B64)), K63, "")</f>
         <v/>
       </c>
       <c r="L64" s="11" t="str">
-        <f t="shared" si="249"/>
+        <f t="shared" si="248"/>
         <v/>
       </c>
       <c r="M64" s="11" t="str">
@@ -8010,21 +8004,18 @@
         <v/>
       </c>
       <c r="N64" s="11" t="str">
-        <f t="shared" ref="N64:O64" si="250">if(not(isblank($B64)), N63, "")</f>
+        <f t="shared" ref="N64:O64" si="249">if(not(isblank($B64)), N63, "")</f>
         <v/>
       </c>
       <c r="O64" s="11" t="str">
-        <f t="shared" si="250"/>
+        <f t="shared" si="249"/>
         <v/>
       </c>
       <c r="P64" s="11" t="str">
         <f>product_listing!J64</f>
         <v/>
       </c>
-      <c r="Q64" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q64" s="11"/>
       <c r="R64" s="11" t="str">
         <f>product_listing!C64</f>
         <v/>
@@ -8064,11 +8055,11 @@
         <v/>
       </c>
       <c r="E65" s="11" t="str">
-        <f t="shared" ref="E65:F65" si="251">if(not(isblank($B65)), E64, "")</f>
+        <f t="shared" ref="E65:F65" si="250">if(not(isblank($B65)), E64, "")</f>
         <v/>
       </c>
       <c r="F65" s="11" t="str">
-        <f t="shared" si="251"/>
+        <f t="shared" si="250"/>
         <v/>
       </c>
       <c r="G65" s="11" t="str">
@@ -8076,11 +8067,11 @@
         <v/>
       </c>
       <c r="H65" s="11" t="str">
-        <f t="shared" ref="H65:I65" si="252">if(not(isblank($B65)), H64, "")</f>
+        <f t="shared" ref="H65:I65" si="251">if(not(isblank($B65)), H64, "")</f>
         <v/>
       </c>
       <c r="I65" s="11" t="str">
-        <f t="shared" si="252"/>
+        <f t="shared" si="251"/>
         <v/>
       </c>
       <c r="J65" s="11" t="str">
@@ -8088,11 +8079,11 @@
         <v/>
       </c>
       <c r="K65" s="11" t="str">
-        <f t="shared" ref="K65:L65" si="253">if(not(isblank($B65)), K64, "")</f>
+        <f t="shared" ref="K65:L65" si="252">if(not(isblank($B65)), K64, "")</f>
         <v/>
       </c>
       <c r="L65" s="11" t="str">
-        <f t="shared" si="253"/>
+        <f t="shared" si="252"/>
         <v/>
       </c>
       <c r="M65" s="11" t="str">
@@ -8100,21 +8091,18 @@
         <v/>
       </c>
       <c r="N65" s="11" t="str">
-        <f t="shared" ref="N65:O65" si="254">if(not(isblank($B65)), N64, "")</f>
+        <f t="shared" ref="N65:O65" si="253">if(not(isblank($B65)), N64, "")</f>
         <v/>
       </c>
       <c r="O65" s="11" t="str">
-        <f t="shared" si="254"/>
+        <f t="shared" si="253"/>
         <v/>
       </c>
       <c r="P65" s="11" t="str">
         <f>product_listing!J65</f>
         <v/>
       </c>
-      <c r="Q65" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q65" s="11"/>
       <c r="R65" s="11" t="str">
         <f>product_listing!C65</f>
         <v/>
@@ -8154,11 +8142,11 @@
         <v/>
       </c>
       <c r="E66" s="11" t="str">
-        <f t="shared" ref="E66:F66" si="255">if(not(isblank($B66)), E65, "")</f>
+        <f t="shared" ref="E66:F66" si="254">if(not(isblank($B66)), E65, "")</f>
         <v/>
       </c>
       <c r="F66" s="11" t="str">
-        <f t="shared" si="255"/>
+        <f t="shared" si="254"/>
         <v/>
       </c>
       <c r="G66" s="11" t="str">
@@ -8166,11 +8154,11 @@
         <v/>
       </c>
       <c r="H66" s="11" t="str">
-        <f t="shared" ref="H66:I66" si="256">if(not(isblank($B66)), H65, "")</f>
+        <f t="shared" ref="H66:I66" si="255">if(not(isblank($B66)), H65, "")</f>
         <v/>
       </c>
       <c r="I66" s="11" t="str">
-        <f t="shared" si="256"/>
+        <f t="shared" si="255"/>
         <v/>
       </c>
       <c r="J66" s="11" t="str">
@@ -8178,11 +8166,11 @@
         <v/>
       </c>
       <c r="K66" s="11" t="str">
-        <f t="shared" ref="K66:L66" si="257">if(not(isblank($B66)), K65, "")</f>
+        <f t="shared" ref="K66:L66" si="256">if(not(isblank($B66)), K65, "")</f>
         <v/>
       </c>
       <c r="L66" s="11" t="str">
-        <f t="shared" si="257"/>
+        <f t="shared" si="256"/>
         <v/>
       </c>
       <c r="M66" s="11" t="str">
@@ -8190,21 +8178,18 @@
         <v/>
       </c>
       <c r="N66" s="11" t="str">
-        <f t="shared" ref="N66:O66" si="258">if(not(isblank($B66)), N65, "")</f>
+        <f t="shared" ref="N66:O66" si="257">if(not(isblank($B66)), N65, "")</f>
         <v/>
       </c>
       <c r="O66" s="11" t="str">
-        <f t="shared" si="258"/>
+        <f t="shared" si="257"/>
         <v/>
       </c>
       <c r="P66" s="11" t="str">
         <f>product_listing!J66</f>
         <v/>
       </c>
-      <c r="Q66" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q66" s="11"/>
       <c r="R66" s="11" t="str">
         <f>product_listing!C66</f>
         <v/>
@@ -8244,11 +8229,11 @@
         <v/>
       </c>
       <c r="E67" s="11" t="str">
-        <f t="shared" ref="E67:F67" si="259">if(not(isblank($B67)), E66, "")</f>
+        <f t="shared" ref="E67:F67" si="258">if(not(isblank($B67)), E66, "")</f>
         <v/>
       </c>
       <c r="F67" s="11" t="str">
-        <f t="shared" si="259"/>
+        <f t="shared" si="258"/>
         <v/>
       </c>
       <c r="G67" s="11" t="str">
@@ -8256,11 +8241,11 @@
         <v/>
       </c>
       <c r="H67" s="11" t="str">
-        <f t="shared" ref="H67:I67" si="260">if(not(isblank($B67)), H66, "")</f>
+        <f t="shared" ref="H67:I67" si="259">if(not(isblank($B67)), H66, "")</f>
         <v/>
       </c>
       <c r="I67" s="11" t="str">
-        <f t="shared" si="260"/>
+        <f t="shared" si="259"/>
         <v/>
       </c>
       <c r="J67" s="11" t="str">
@@ -8268,11 +8253,11 @@
         <v/>
       </c>
       <c r="K67" s="11" t="str">
-        <f t="shared" ref="K67:L67" si="261">if(not(isblank($B67)), K66, "")</f>
+        <f t="shared" ref="K67:L67" si="260">if(not(isblank($B67)), K66, "")</f>
         <v/>
       </c>
       <c r="L67" s="11" t="str">
-        <f t="shared" si="261"/>
+        <f t="shared" si="260"/>
         <v/>
       </c>
       <c r="M67" s="11" t="str">
@@ -8280,21 +8265,18 @@
         <v/>
       </c>
       <c r="N67" s="11" t="str">
-        <f t="shared" ref="N67:O67" si="262">if(not(isblank($B67)), N66, "")</f>
+        <f t="shared" ref="N67:O67" si="261">if(not(isblank($B67)), N66, "")</f>
         <v/>
       </c>
       <c r="O67" s="11" t="str">
-        <f t="shared" si="262"/>
+        <f t="shared" si="261"/>
         <v/>
       </c>
       <c r="P67" s="11" t="str">
         <f>product_listing!J67</f>
         <v/>
       </c>
-      <c r="Q67" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q67" s="11"/>
       <c r="R67" s="11" t="str">
         <f>product_listing!C67</f>
         <v/>
@@ -8334,11 +8316,11 @@
         <v/>
       </c>
       <c r="E68" s="11" t="str">
-        <f t="shared" ref="E68:F68" si="263">if(not(isblank($B68)), E67, "")</f>
+        <f t="shared" ref="E68:F68" si="262">if(not(isblank($B68)), E67, "")</f>
         <v/>
       </c>
       <c r="F68" s="11" t="str">
-        <f t="shared" si="263"/>
+        <f t="shared" si="262"/>
         <v/>
       </c>
       <c r="G68" s="11" t="str">
@@ -8346,11 +8328,11 @@
         <v/>
       </c>
       <c r="H68" s="11" t="str">
-        <f t="shared" ref="H68:I68" si="264">if(not(isblank($B68)), H67, "")</f>
+        <f t="shared" ref="H68:I68" si="263">if(not(isblank($B68)), H67, "")</f>
         <v/>
       </c>
       <c r="I68" s="11" t="str">
-        <f t="shared" si="264"/>
+        <f t="shared" si="263"/>
         <v/>
       </c>
       <c r="J68" s="11" t="str">
@@ -8358,11 +8340,11 @@
         <v/>
       </c>
       <c r="K68" s="11" t="str">
-        <f t="shared" ref="K68:L68" si="265">if(not(isblank($B68)), K67, "")</f>
+        <f t="shared" ref="K68:L68" si="264">if(not(isblank($B68)), K67, "")</f>
         <v/>
       </c>
       <c r="L68" s="11" t="str">
-        <f t="shared" si="265"/>
+        <f t="shared" si="264"/>
         <v/>
       </c>
       <c r="M68" s="11" t="str">
@@ -8370,21 +8352,18 @@
         <v/>
       </c>
       <c r="N68" s="11" t="str">
-        <f t="shared" ref="N68:O68" si="266">if(not(isblank($B68)), N67, "")</f>
+        <f t="shared" ref="N68:O68" si="265">if(not(isblank($B68)), N67, "")</f>
         <v/>
       </c>
       <c r="O68" s="11" t="str">
-        <f t="shared" si="266"/>
+        <f t="shared" si="265"/>
         <v/>
       </c>
       <c r="P68" s="11" t="str">
         <f>product_listing!J68</f>
         <v/>
       </c>
-      <c r="Q68" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q68" s="11"/>
       <c r="R68" s="11" t="str">
         <f>product_listing!C68</f>
         <v/>
@@ -8424,11 +8403,11 @@
         <v/>
       </c>
       <c r="E69" s="11" t="str">
-        <f t="shared" ref="E69:F69" si="267">if(not(isblank($B69)), E68, "")</f>
+        <f t="shared" ref="E69:F69" si="266">if(not(isblank($B69)), E68, "")</f>
         <v/>
       </c>
       <c r="F69" s="11" t="str">
-        <f t="shared" si="267"/>
+        <f t="shared" si="266"/>
         <v/>
       </c>
       <c r="G69" s="11" t="str">
@@ -8436,11 +8415,11 @@
         <v/>
       </c>
       <c r="H69" s="11" t="str">
-        <f t="shared" ref="H69:I69" si="268">if(not(isblank($B69)), H68, "")</f>
+        <f t="shared" ref="H69:I69" si="267">if(not(isblank($B69)), H68, "")</f>
         <v/>
       </c>
       <c r="I69" s="11" t="str">
-        <f t="shared" si="268"/>
+        <f t="shared" si="267"/>
         <v/>
       </c>
       <c r="J69" s="11" t="str">
@@ -8448,11 +8427,11 @@
         <v/>
       </c>
       <c r="K69" s="11" t="str">
-        <f t="shared" ref="K69:L69" si="269">if(not(isblank($B69)), K68, "")</f>
+        <f t="shared" ref="K69:L69" si="268">if(not(isblank($B69)), K68, "")</f>
         <v/>
       </c>
       <c r="L69" s="11" t="str">
-        <f t="shared" si="269"/>
+        <f t="shared" si="268"/>
         <v/>
       </c>
       <c r="M69" s="11" t="str">
@@ -8460,21 +8439,18 @@
         <v/>
       </c>
       <c r="N69" s="11" t="str">
-        <f t="shared" ref="N69:O69" si="270">if(not(isblank($B69)), N68, "")</f>
+        <f t="shared" ref="N69:O69" si="269">if(not(isblank($B69)), N68, "")</f>
         <v/>
       </c>
       <c r="O69" s="11" t="str">
-        <f t="shared" si="270"/>
+        <f t="shared" si="269"/>
         <v/>
       </c>
       <c r="P69" s="11" t="str">
         <f>product_listing!J69</f>
         <v/>
       </c>
-      <c r="Q69" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q69" s="11"/>
       <c r="R69" s="11" t="str">
         <f>product_listing!C69</f>
         <v/>
@@ -8514,11 +8490,11 @@
         <v/>
       </c>
       <c r="E70" s="11" t="str">
-        <f t="shared" ref="E70:F70" si="271">if(not(isblank($B70)), E69, "")</f>
+        <f t="shared" ref="E70:F70" si="270">if(not(isblank($B70)), E69, "")</f>
         <v/>
       </c>
       <c r="F70" s="11" t="str">
-        <f t="shared" si="271"/>
+        <f t="shared" si="270"/>
         <v/>
       </c>
       <c r="G70" s="11" t="str">
@@ -8526,11 +8502,11 @@
         <v/>
       </c>
       <c r="H70" s="11" t="str">
-        <f t="shared" ref="H70:I70" si="272">if(not(isblank($B70)), H69, "")</f>
+        <f t="shared" ref="H70:I70" si="271">if(not(isblank($B70)), H69, "")</f>
         <v/>
       </c>
       <c r="I70" s="11" t="str">
-        <f t="shared" si="272"/>
+        <f t="shared" si="271"/>
         <v/>
       </c>
       <c r="J70" s="11" t="str">
@@ -8538,11 +8514,11 @@
         <v/>
       </c>
       <c r="K70" s="11" t="str">
-        <f t="shared" ref="K70:L70" si="273">if(not(isblank($B70)), K69, "")</f>
+        <f t="shared" ref="K70:L70" si="272">if(not(isblank($B70)), K69, "")</f>
         <v/>
       </c>
       <c r="L70" s="11" t="str">
-        <f t="shared" si="273"/>
+        <f t="shared" si="272"/>
         <v/>
       </c>
       <c r="M70" s="11" t="str">
@@ -8550,21 +8526,18 @@
         <v/>
       </c>
       <c r="N70" s="11" t="str">
-        <f t="shared" ref="N70:O70" si="274">if(not(isblank($B70)), N69, "")</f>
+        <f t="shared" ref="N70:O70" si="273">if(not(isblank($B70)), N69, "")</f>
         <v/>
       </c>
       <c r="O70" s="11" t="str">
-        <f t="shared" si="274"/>
+        <f t="shared" si="273"/>
         <v/>
       </c>
       <c r="P70" s="11" t="str">
         <f>product_listing!J70</f>
         <v/>
       </c>
-      <c r="Q70" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q70" s="11"/>
       <c r="R70" s="11" t="str">
         <f>product_listing!C70</f>
         <v/>
@@ -8604,11 +8577,11 @@
         <v/>
       </c>
       <c r="E71" s="11" t="str">
-        <f t="shared" ref="E71:F71" si="275">if(not(isblank($B71)), E70, "")</f>
+        <f t="shared" ref="E71:F71" si="274">if(not(isblank($B71)), E70, "")</f>
         <v/>
       </c>
       <c r="F71" s="11" t="str">
-        <f t="shared" si="275"/>
+        <f t="shared" si="274"/>
         <v/>
       </c>
       <c r="G71" s="11" t="str">
@@ -8616,11 +8589,11 @@
         <v/>
       </c>
       <c r="H71" s="11" t="str">
-        <f t="shared" ref="H71:I71" si="276">if(not(isblank($B71)), H70, "")</f>
+        <f t="shared" ref="H71:I71" si="275">if(not(isblank($B71)), H70, "")</f>
         <v/>
       </c>
       <c r="I71" s="11" t="str">
-        <f t="shared" si="276"/>
+        <f t="shared" si="275"/>
         <v/>
       </c>
       <c r="J71" s="11" t="str">
@@ -8628,11 +8601,11 @@
         <v/>
       </c>
       <c r="K71" s="11" t="str">
-        <f t="shared" ref="K71:L71" si="277">if(not(isblank($B71)), K70, "")</f>
+        <f t="shared" ref="K71:L71" si="276">if(not(isblank($B71)), K70, "")</f>
         <v/>
       </c>
       <c r="L71" s="11" t="str">
-        <f t="shared" si="277"/>
+        <f t="shared" si="276"/>
         <v/>
       </c>
       <c r="M71" s="11" t="str">
@@ -8640,21 +8613,18 @@
         <v/>
       </c>
       <c r="N71" s="11" t="str">
-        <f t="shared" ref="N71:O71" si="278">if(not(isblank($B71)), N70, "")</f>
+        <f t="shared" ref="N71:O71" si="277">if(not(isblank($B71)), N70, "")</f>
         <v/>
       </c>
       <c r="O71" s="11" t="str">
-        <f t="shared" si="278"/>
+        <f t="shared" si="277"/>
         <v/>
       </c>
       <c r="P71" s="11" t="str">
         <f>product_listing!J71</f>
         <v/>
       </c>
-      <c r="Q71" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q71" s="11"/>
       <c r="R71" s="11" t="str">
         <f>product_listing!C71</f>
         <v/>
@@ -8694,11 +8664,11 @@
         <v/>
       </c>
       <c r="E72" s="11" t="str">
-        <f t="shared" ref="E72:F72" si="279">if(not(isblank($B72)), E71, "")</f>
+        <f t="shared" ref="E72:F72" si="278">if(not(isblank($B72)), E71, "")</f>
         <v/>
       </c>
       <c r="F72" s="11" t="str">
-        <f t="shared" si="279"/>
+        <f t="shared" si="278"/>
         <v/>
       </c>
       <c r="G72" s="11" t="str">
@@ -8706,11 +8676,11 @@
         <v/>
       </c>
       <c r="H72" s="11" t="str">
-        <f t="shared" ref="H72:I72" si="280">if(not(isblank($B72)), H71, "")</f>
+        <f t="shared" ref="H72:I72" si="279">if(not(isblank($B72)), H71, "")</f>
         <v/>
       </c>
       <c r="I72" s="11" t="str">
-        <f t="shared" si="280"/>
+        <f t="shared" si="279"/>
         <v/>
       </c>
       <c r="J72" s="11" t="str">
@@ -8718,11 +8688,11 @@
         <v/>
       </c>
       <c r="K72" s="11" t="str">
-        <f t="shared" ref="K72:L72" si="281">if(not(isblank($B72)), K71, "")</f>
+        <f t="shared" ref="K72:L72" si="280">if(not(isblank($B72)), K71, "")</f>
         <v/>
       </c>
       <c r="L72" s="11" t="str">
-        <f t="shared" si="281"/>
+        <f t="shared" si="280"/>
         <v/>
       </c>
       <c r="M72" s="11" t="str">
@@ -8730,21 +8700,18 @@
         <v/>
       </c>
       <c r="N72" s="11" t="str">
-        <f t="shared" ref="N72:O72" si="282">if(not(isblank($B72)), N71, "")</f>
+        <f t="shared" ref="N72:O72" si="281">if(not(isblank($B72)), N71, "")</f>
         <v/>
       </c>
       <c r="O72" s="11" t="str">
-        <f t="shared" si="282"/>
+        <f t="shared" si="281"/>
         <v/>
       </c>
       <c r="P72" s="11" t="str">
         <f>product_listing!J72</f>
         <v/>
       </c>
-      <c r="Q72" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q72" s="11"/>
       <c r="R72" s="11" t="str">
         <f>product_listing!C72</f>
         <v/>
@@ -8784,11 +8751,11 @@
         <v/>
       </c>
       <c r="E73" s="11" t="str">
-        <f t="shared" ref="E73:F73" si="283">if(not(isblank($B73)), E72, "")</f>
+        <f t="shared" ref="E73:F73" si="282">if(not(isblank($B73)), E72, "")</f>
         <v/>
       </c>
       <c r="F73" s="11" t="str">
-        <f t="shared" si="283"/>
+        <f t="shared" si="282"/>
         <v/>
       </c>
       <c r="G73" s="11" t="str">
@@ -8796,11 +8763,11 @@
         <v/>
       </c>
       <c r="H73" s="11" t="str">
-        <f t="shared" ref="H73:I73" si="284">if(not(isblank($B73)), H72, "")</f>
+        <f t="shared" ref="H73:I73" si="283">if(not(isblank($B73)), H72, "")</f>
         <v/>
       </c>
       <c r="I73" s="11" t="str">
-        <f t="shared" si="284"/>
+        <f t="shared" si="283"/>
         <v/>
       </c>
       <c r="J73" s="11" t="str">
@@ -8808,11 +8775,11 @@
         <v/>
       </c>
       <c r="K73" s="11" t="str">
-        <f t="shared" ref="K73:L73" si="285">if(not(isblank($B73)), K72, "")</f>
+        <f t="shared" ref="K73:L73" si="284">if(not(isblank($B73)), K72, "")</f>
         <v/>
       </c>
       <c r="L73" s="11" t="str">
-        <f t="shared" si="285"/>
+        <f t="shared" si="284"/>
         <v/>
       </c>
       <c r="M73" s="11" t="str">
@@ -8820,21 +8787,18 @@
         <v/>
       </c>
       <c r="N73" s="11" t="str">
-        <f t="shared" ref="N73:O73" si="286">if(not(isblank($B73)), N72, "")</f>
+        <f t="shared" ref="N73:O73" si="285">if(not(isblank($B73)), N72, "")</f>
         <v/>
       </c>
       <c r="O73" s="11" t="str">
-        <f t="shared" si="286"/>
+        <f t="shared" si="285"/>
         <v/>
       </c>
       <c r="P73" s="11" t="str">
         <f>product_listing!J73</f>
         <v/>
       </c>
-      <c r="Q73" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q73" s="11"/>
       <c r="R73" s="11" t="str">
         <f>product_listing!C73</f>
         <v/>
@@ -8874,11 +8838,11 @@
         <v/>
       </c>
       <c r="E74" s="11" t="str">
-        <f t="shared" ref="E74:F74" si="287">if(not(isblank($B74)), E73, "")</f>
+        <f t="shared" ref="E74:F74" si="286">if(not(isblank($B74)), E73, "")</f>
         <v/>
       </c>
       <c r="F74" s="11" t="str">
-        <f t="shared" si="287"/>
+        <f t="shared" si="286"/>
         <v/>
       </c>
       <c r="G74" s="11" t="str">
@@ -8886,11 +8850,11 @@
         <v/>
       </c>
       <c r="H74" s="11" t="str">
-        <f t="shared" ref="H74:I74" si="288">if(not(isblank($B74)), H73, "")</f>
+        <f t="shared" ref="H74:I74" si="287">if(not(isblank($B74)), H73, "")</f>
         <v/>
       </c>
       <c r="I74" s="11" t="str">
-        <f t="shared" si="288"/>
+        <f t="shared" si="287"/>
         <v/>
       </c>
       <c r="J74" s="11" t="str">
@@ -8898,11 +8862,11 @@
         <v/>
       </c>
       <c r="K74" s="11" t="str">
-        <f t="shared" ref="K74:L74" si="289">if(not(isblank($B74)), K73, "")</f>
+        <f t="shared" ref="K74:L74" si="288">if(not(isblank($B74)), K73, "")</f>
         <v/>
       </c>
       <c r="L74" s="11" t="str">
-        <f t="shared" si="289"/>
+        <f t="shared" si="288"/>
         <v/>
       </c>
       <c r="M74" s="11" t="str">
@@ -8910,21 +8874,18 @@
         <v/>
       </c>
       <c r="N74" s="11" t="str">
-        <f t="shared" ref="N74:O74" si="290">if(not(isblank($B74)), N73, "")</f>
+        <f t="shared" ref="N74:O74" si="289">if(not(isblank($B74)), N73, "")</f>
         <v/>
       </c>
       <c r="O74" s="11" t="str">
-        <f t="shared" si="290"/>
+        <f t="shared" si="289"/>
         <v/>
       </c>
       <c r="P74" s="11" t="str">
         <f>product_listing!J74</f>
         <v/>
       </c>
-      <c r="Q74" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q74" s="11"/>
       <c r="R74" s="11" t="str">
         <f>product_listing!C74</f>
         <v/>
@@ -8964,11 +8925,11 @@
         <v/>
       </c>
       <c r="E75" s="11" t="str">
-        <f t="shared" ref="E75:F75" si="291">if(not(isblank($B75)), E74, "")</f>
+        <f t="shared" ref="E75:F75" si="290">if(not(isblank($B75)), E74, "")</f>
         <v/>
       </c>
       <c r="F75" s="11" t="str">
-        <f t="shared" si="291"/>
+        <f t="shared" si="290"/>
         <v/>
       </c>
       <c r="G75" s="11" t="str">
@@ -8976,11 +8937,11 @@
         <v/>
       </c>
       <c r="H75" s="11" t="str">
-        <f t="shared" ref="H75:I75" si="292">if(not(isblank($B75)), H74, "")</f>
+        <f t="shared" ref="H75:I75" si="291">if(not(isblank($B75)), H74, "")</f>
         <v/>
       </c>
       <c r="I75" s="11" t="str">
-        <f t="shared" si="292"/>
+        <f t="shared" si="291"/>
         <v/>
       </c>
       <c r="J75" s="11" t="str">
@@ -8988,11 +8949,11 @@
         <v/>
       </c>
       <c r="K75" s="11" t="str">
-        <f t="shared" ref="K75:L75" si="293">if(not(isblank($B75)), K74, "")</f>
+        <f t="shared" ref="K75:L75" si="292">if(not(isblank($B75)), K74, "")</f>
         <v/>
       </c>
       <c r="L75" s="11" t="str">
-        <f t="shared" si="293"/>
+        <f t="shared" si="292"/>
         <v/>
       </c>
       <c r="M75" s="11" t="str">
@@ -9000,21 +8961,18 @@
         <v/>
       </c>
       <c r="N75" s="11" t="str">
-        <f t="shared" ref="N75:O75" si="294">if(not(isblank($B75)), N74, "")</f>
+        <f t="shared" ref="N75:O75" si="293">if(not(isblank($B75)), N74, "")</f>
         <v/>
       </c>
       <c r="O75" s="11" t="str">
-        <f t="shared" si="294"/>
+        <f t="shared" si="293"/>
         <v/>
       </c>
       <c r="P75" s="11" t="str">
         <f>product_listing!J75</f>
         <v/>
       </c>
-      <c r="Q75" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q75" s="11"/>
       <c r="R75" s="11" t="str">
         <f>product_listing!C75</f>
         <v/>
@@ -9054,11 +9012,11 @@
         <v/>
       </c>
       <c r="E76" s="11" t="str">
-        <f t="shared" ref="E76:F76" si="295">if(not(isblank($B76)), E75, "")</f>
+        <f t="shared" ref="E76:F76" si="294">if(not(isblank($B76)), E75, "")</f>
         <v/>
       </c>
       <c r="F76" s="11" t="str">
-        <f t="shared" si="295"/>
+        <f t="shared" si="294"/>
         <v/>
       </c>
       <c r="G76" s="11" t="str">
@@ -9066,11 +9024,11 @@
         <v/>
       </c>
       <c r="H76" s="11" t="str">
-        <f t="shared" ref="H76:I76" si="296">if(not(isblank($B76)), H75, "")</f>
+        <f t="shared" ref="H76:I76" si="295">if(not(isblank($B76)), H75, "")</f>
         <v/>
       </c>
       <c r="I76" s="11" t="str">
-        <f t="shared" si="296"/>
+        <f t="shared" si="295"/>
         <v/>
       </c>
       <c r="J76" s="11" t="str">
@@ -9078,11 +9036,11 @@
         <v/>
       </c>
       <c r="K76" s="11" t="str">
-        <f t="shared" ref="K76:L76" si="297">if(not(isblank($B76)), K75, "")</f>
+        <f t="shared" ref="K76:L76" si="296">if(not(isblank($B76)), K75, "")</f>
         <v/>
       </c>
       <c r="L76" s="11" t="str">
-        <f t="shared" si="297"/>
+        <f t="shared" si="296"/>
         <v/>
       </c>
       <c r="M76" s="11" t="str">
@@ -9090,21 +9048,18 @@
         <v/>
       </c>
       <c r="N76" s="11" t="str">
-        <f t="shared" ref="N76:O76" si="298">if(not(isblank($B76)), N75, "")</f>
+        <f t="shared" ref="N76:O76" si="297">if(not(isblank($B76)), N75, "")</f>
         <v/>
       </c>
       <c r="O76" s="11" t="str">
-        <f t="shared" si="298"/>
+        <f t="shared" si="297"/>
         <v/>
       </c>
       <c r="P76" s="11" t="str">
         <f>product_listing!J76</f>
         <v/>
       </c>
-      <c r="Q76" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q76" s="11"/>
       <c r="R76" s="11" t="str">
         <f>product_listing!C76</f>
         <v/>
@@ -9144,11 +9099,11 @@
         <v/>
       </c>
       <c r="E77" s="11" t="str">
-        <f t="shared" ref="E77:F77" si="299">if(not(isblank($B77)), E76, "")</f>
+        <f t="shared" ref="E77:F77" si="298">if(not(isblank($B77)), E76, "")</f>
         <v/>
       </c>
       <c r="F77" s="11" t="str">
-        <f t="shared" si="299"/>
+        <f t="shared" si="298"/>
         <v/>
       </c>
       <c r="G77" s="11" t="str">
@@ -9156,11 +9111,11 @@
         <v/>
       </c>
       <c r="H77" s="11" t="str">
-        <f t="shared" ref="H77:I77" si="300">if(not(isblank($B77)), H76, "")</f>
+        <f t="shared" ref="H77:I77" si="299">if(not(isblank($B77)), H76, "")</f>
         <v/>
       </c>
       <c r="I77" s="11" t="str">
-        <f t="shared" si="300"/>
+        <f t="shared" si="299"/>
         <v/>
       </c>
       <c r="J77" s="11" t="str">
@@ -9168,11 +9123,11 @@
         <v/>
       </c>
       <c r="K77" s="11" t="str">
-        <f t="shared" ref="K77:L77" si="301">if(not(isblank($B77)), K76, "")</f>
+        <f t="shared" ref="K77:L77" si="300">if(not(isblank($B77)), K76, "")</f>
         <v/>
       </c>
       <c r="L77" s="11" t="str">
-        <f t="shared" si="301"/>
+        <f t="shared" si="300"/>
         <v/>
       </c>
       <c r="M77" s="11" t="str">
@@ -9180,21 +9135,18 @@
         <v/>
       </c>
       <c r="N77" s="11" t="str">
-        <f t="shared" ref="N77:O77" si="302">if(not(isblank($B77)), N76, "")</f>
+        <f t="shared" ref="N77:O77" si="301">if(not(isblank($B77)), N76, "")</f>
         <v/>
       </c>
       <c r="O77" s="11" t="str">
-        <f t="shared" si="302"/>
+        <f t="shared" si="301"/>
         <v/>
       </c>
       <c r="P77" s="11" t="str">
         <f>product_listing!J77</f>
         <v/>
       </c>
-      <c r="Q77" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q77" s="11"/>
       <c r="R77" s="11" t="str">
         <f>product_listing!C77</f>
         <v/>
@@ -9234,11 +9186,11 @@
         <v/>
       </c>
       <c r="E78" s="11" t="str">
-        <f t="shared" ref="E78:F78" si="303">if(not(isblank($B78)), E77, "")</f>
+        <f t="shared" ref="E78:F78" si="302">if(not(isblank($B78)), E77, "")</f>
         <v/>
       </c>
       <c r="F78" s="11" t="str">
-        <f t="shared" si="303"/>
+        <f t="shared" si="302"/>
         <v/>
       </c>
       <c r="G78" s="11" t="str">
@@ -9246,11 +9198,11 @@
         <v/>
       </c>
       <c r="H78" s="11" t="str">
-        <f t="shared" ref="H78:I78" si="304">if(not(isblank($B78)), H77, "")</f>
+        <f t="shared" ref="H78:I78" si="303">if(not(isblank($B78)), H77, "")</f>
         <v/>
       </c>
       <c r="I78" s="11" t="str">
-        <f t="shared" si="304"/>
+        <f t="shared" si="303"/>
         <v/>
       </c>
       <c r="J78" s="11" t="str">
@@ -9258,11 +9210,11 @@
         <v/>
       </c>
       <c r="K78" s="11" t="str">
-        <f t="shared" ref="K78:L78" si="305">if(not(isblank($B78)), K77, "")</f>
+        <f t="shared" ref="K78:L78" si="304">if(not(isblank($B78)), K77, "")</f>
         <v/>
       </c>
       <c r="L78" s="11" t="str">
-        <f t="shared" si="305"/>
+        <f t="shared" si="304"/>
         <v/>
       </c>
       <c r="M78" s="11" t="str">
@@ -9270,21 +9222,18 @@
         <v/>
       </c>
       <c r="N78" s="11" t="str">
-        <f t="shared" ref="N78:O78" si="306">if(not(isblank($B78)), N77, "")</f>
+        <f t="shared" ref="N78:O78" si="305">if(not(isblank($B78)), N77, "")</f>
         <v/>
       </c>
       <c r="O78" s="11" t="str">
-        <f t="shared" si="306"/>
+        <f t="shared" si="305"/>
         <v/>
       </c>
       <c r="P78" s="11" t="str">
         <f>product_listing!J78</f>
         <v/>
       </c>
-      <c r="Q78" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q78" s="11"/>
       <c r="R78" s="11" t="str">
         <f>product_listing!C78</f>
         <v/>
@@ -9324,11 +9273,11 @@
         <v/>
       </c>
       <c r="E79" s="11" t="str">
-        <f t="shared" ref="E79:F79" si="307">if(not(isblank($B79)), E78, "")</f>
+        <f t="shared" ref="E79:F79" si="306">if(not(isblank($B79)), E78, "")</f>
         <v/>
       </c>
       <c r="F79" s="11" t="str">
-        <f t="shared" si="307"/>
+        <f t="shared" si="306"/>
         <v/>
       </c>
       <c r="G79" s="11" t="str">
@@ -9336,11 +9285,11 @@
         <v/>
       </c>
       <c r="H79" s="11" t="str">
-        <f t="shared" ref="H79:I79" si="308">if(not(isblank($B79)), H78, "")</f>
+        <f t="shared" ref="H79:I79" si="307">if(not(isblank($B79)), H78, "")</f>
         <v/>
       </c>
       <c r="I79" s="11" t="str">
-        <f t="shared" si="308"/>
+        <f t="shared" si="307"/>
         <v/>
       </c>
       <c r="J79" s="11" t="str">
@@ -9348,11 +9297,11 @@
         <v/>
       </c>
       <c r="K79" s="11" t="str">
-        <f t="shared" ref="K79:L79" si="309">if(not(isblank($B79)), K78, "")</f>
+        <f t="shared" ref="K79:L79" si="308">if(not(isblank($B79)), K78, "")</f>
         <v/>
       </c>
       <c r="L79" s="11" t="str">
-        <f t="shared" si="309"/>
+        <f t="shared" si="308"/>
         <v/>
       </c>
       <c r="M79" s="11" t="str">
@@ -9360,21 +9309,18 @@
         <v/>
       </c>
       <c r="N79" s="11" t="str">
-        <f t="shared" ref="N79:O79" si="310">if(not(isblank($B79)), N78, "")</f>
+        <f t="shared" ref="N79:O79" si="309">if(not(isblank($B79)), N78, "")</f>
         <v/>
       </c>
       <c r="O79" s="11" t="str">
-        <f t="shared" si="310"/>
+        <f t="shared" si="309"/>
         <v/>
       </c>
       <c r="P79" s="11" t="str">
         <f>product_listing!J79</f>
         <v/>
       </c>
-      <c r="Q79" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q79" s="11"/>
       <c r="R79" s="11" t="str">
         <f>product_listing!C79</f>
         <v/>
@@ -9414,11 +9360,11 @@
         <v/>
       </c>
       <c r="E80" s="11" t="str">
-        <f t="shared" ref="E80:F80" si="311">if(not(isblank($B80)), E79, "")</f>
+        <f t="shared" ref="E80:F80" si="310">if(not(isblank($B80)), E79, "")</f>
         <v/>
       </c>
       <c r="F80" s="11" t="str">
-        <f t="shared" si="311"/>
+        <f t="shared" si="310"/>
         <v/>
       </c>
       <c r="G80" s="11" t="str">
@@ -9426,11 +9372,11 @@
         <v/>
       </c>
       <c r="H80" s="11" t="str">
-        <f t="shared" ref="H80:I80" si="312">if(not(isblank($B80)), H79, "")</f>
+        <f t="shared" ref="H80:I80" si="311">if(not(isblank($B80)), H79, "")</f>
         <v/>
       </c>
       <c r="I80" s="11" t="str">
-        <f t="shared" si="312"/>
+        <f t="shared" si="311"/>
         <v/>
       </c>
       <c r="J80" s="11" t="str">
@@ -9438,11 +9384,11 @@
         <v/>
       </c>
       <c r="K80" s="11" t="str">
-        <f t="shared" ref="K80:L80" si="313">if(not(isblank($B80)), K79, "")</f>
+        <f t="shared" ref="K80:L80" si="312">if(not(isblank($B80)), K79, "")</f>
         <v/>
       </c>
       <c r="L80" s="11" t="str">
-        <f t="shared" si="313"/>
+        <f t="shared" si="312"/>
         <v/>
       </c>
       <c r="M80" s="11" t="str">
@@ -9450,21 +9396,18 @@
         <v/>
       </c>
       <c r="N80" s="11" t="str">
-        <f t="shared" ref="N80:O80" si="314">if(not(isblank($B80)), N79, "")</f>
+        <f t="shared" ref="N80:O80" si="313">if(not(isblank($B80)), N79, "")</f>
         <v/>
       </c>
       <c r="O80" s="11" t="str">
-        <f t="shared" si="314"/>
+        <f t="shared" si="313"/>
         <v/>
       </c>
       <c r="P80" s="11" t="str">
         <f>product_listing!J80</f>
         <v/>
       </c>
-      <c r="Q80" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q80" s="11"/>
       <c r="R80" s="11" t="str">
         <f>product_listing!C80</f>
         <v/>
@@ -9504,11 +9447,11 @@
         <v/>
       </c>
       <c r="E81" s="11" t="str">
-        <f t="shared" ref="E81:F81" si="315">if(not(isblank($B81)), E80, "")</f>
+        <f t="shared" ref="E81:F81" si="314">if(not(isblank($B81)), E80, "")</f>
         <v/>
       </c>
       <c r="F81" s="11" t="str">
-        <f t="shared" si="315"/>
+        <f t="shared" si="314"/>
         <v/>
       </c>
       <c r="G81" s="11" t="str">
@@ -9516,11 +9459,11 @@
         <v/>
       </c>
       <c r="H81" s="11" t="str">
-        <f t="shared" ref="H81:I81" si="316">if(not(isblank($B81)), H80, "")</f>
+        <f t="shared" ref="H81:I81" si="315">if(not(isblank($B81)), H80, "")</f>
         <v/>
       </c>
       <c r="I81" s="11" t="str">
-        <f t="shared" si="316"/>
+        <f t="shared" si="315"/>
         <v/>
       </c>
       <c r="J81" s="11" t="str">
@@ -9528,11 +9471,11 @@
         <v/>
       </c>
       <c r="K81" s="11" t="str">
-        <f t="shared" ref="K81:L81" si="317">if(not(isblank($B81)), K80, "")</f>
+        <f t="shared" ref="K81:L81" si="316">if(not(isblank($B81)), K80, "")</f>
         <v/>
       </c>
       <c r="L81" s="11" t="str">
-        <f t="shared" si="317"/>
+        <f t="shared" si="316"/>
         <v/>
       </c>
       <c r="M81" s="11" t="str">
@@ -9540,21 +9483,18 @@
         <v/>
       </c>
       <c r="N81" s="11" t="str">
-        <f t="shared" ref="N81:O81" si="318">if(not(isblank($B81)), N80, "")</f>
+        <f t="shared" ref="N81:O81" si="317">if(not(isblank($B81)), N80, "")</f>
         <v/>
       </c>
       <c r="O81" s="11" t="str">
-        <f t="shared" si="318"/>
+        <f t="shared" si="317"/>
         <v/>
       </c>
       <c r="P81" s="11" t="str">
         <f>product_listing!J81</f>
         <v/>
       </c>
-      <c r="Q81" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q81" s="11"/>
       <c r="R81" s="11" t="str">
         <f>product_listing!C81</f>
         <v/>
@@ -9594,11 +9534,11 @@
         <v/>
       </c>
       <c r="E82" s="11" t="str">
-        <f t="shared" ref="E82:F82" si="319">if(not(isblank($B82)), E81, "")</f>
+        <f t="shared" ref="E82:F82" si="318">if(not(isblank($B82)), E81, "")</f>
         <v/>
       </c>
       <c r="F82" s="11" t="str">
-        <f t="shared" si="319"/>
+        <f t="shared" si="318"/>
         <v/>
       </c>
       <c r="G82" s="11" t="str">
@@ -9606,11 +9546,11 @@
         <v/>
       </c>
       <c r="H82" s="11" t="str">
-        <f t="shared" ref="H82:I82" si="320">if(not(isblank($B82)), H81, "")</f>
+        <f t="shared" ref="H82:I82" si="319">if(not(isblank($B82)), H81, "")</f>
         <v/>
       </c>
       <c r="I82" s="11" t="str">
-        <f t="shared" si="320"/>
+        <f t="shared" si="319"/>
         <v/>
       </c>
       <c r="J82" s="11" t="str">
@@ -9618,11 +9558,11 @@
         <v/>
       </c>
       <c r="K82" s="11" t="str">
-        <f t="shared" ref="K82:L82" si="321">if(not(isblank($B82)), K81, "")</f>
+        <f t="shared" ref="K82:L82" si="320">if(not(isblank($B82)), K81, "")</f>
         <v/>
       </c>
       <c r="L82" s="11" t="str">
-        <f t="shared" si="321"/>
+        <f t="shared" si="320"/>
         <v/>
       </c>
       <c r="M82" s="11" t="str">
@@ -9630,21 +9570,18 @@
         <v/>
       </c>
       <c r="N82" s="11" t="str">
-        <f t="shared" ref="N82:O82" si="322">if(not(isblank($B82)), N81, "")</f>
+        <f t="shared" ref="N82:O82" si="321">if(not(isblank($B82)), N81, "")</f>
         <v/>
       </c>
       <c r="O82" s="11" t="str">
-        <f t="shared" si="322"/>
+        <f t="shared" si="321"/>
         <v/>
       </c>
       <c r="P82" s="11" t="str">
         <f>product_listing!J82</f>
         <v/>
       </c>
-      <c r="Q82" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q82" s="11"/>
       <c r="R82" s="11" t="str">
         <f>product_listing!C82</f>
         <v/>
@@ -9684,11 +9621,11 @@
         <v/>
       </c>
       <c r="E83" s="11" t="str">
-        <f t="shared" ref="E83:F83" si="323">if(not(isblank($B83)), E82, "")</f>
+        <f t="shared" ref="E83:F83" si="322">if(not(isblank($B83)), E82, "")</f>
         <v/>
       </c>
       <c r="F83" s="11" t="str">
-        <f t="shared" si="323"/>
+        <f t="shared" si="322"/>
         <v/>
       </c>
       <c r="G83" s="11" t="str">
@@ -9696,11 +9633,11 @@
         <v/>
       </c>
       <c r="H83" s="11" t="str">
-        <f t="shared" ref="H83:I83" si="324">if(not(isblank($B83)), H82, "")</f>
+        <f t="shared" ref="H83:I83" si="323">if(not(isblank($B83)), H82, "")</f>
         <v/>
       </c>
       <c r="I83" s="11" t="str">
-        <f t="shared" si="324"/>
+        <f t="shared" si="323"/>
         <v/>
       </c>
       <c r="J83" s="11" t="str">
@@ -9708,11 +9645,11 @@
         <v/>
       </c>
       <c r="K83" s="11" t="str">
-        <f t="shared" ref="K83:L83" si="325">if(not(isblank($B83)), K82, "")</f>
+        <f t="shared" ref="K83:L83" si="324">if(not(isblank($B83)), K82, "")</f>
         <v/>
       </c>
       <c r="L83" s="11" t="str">
-        <f t="shared" si="325"/>
+        <f t="shared" si="324"/>
         <v/>
       </c>
       <c r="M83" s="11" t="str">
@@ -9720,21 +9657,18 @@
         <v/>
       </c>
       <c r="N83" s="11" t="str">
-        <f t="shared" ref="N83:O83" si="326">if(not(isblank($B83)), N82, "")</f>
+        <f t="shared" ref="N83:O83" si="325">if(not(isblank($B83)), N82, "")</f>
         <v/>
       </c>
       <c r="O83" s="11" t="str">
-        <f t="shared" si="326"/>
+        <f t="shared" si="325"/>
         <v/>
       </c>
       <c r="P83" s="11" t="str">
         <f>product_listing!J83</f>
         <v/>
       </c>
-      <c r="Q83" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q83" s="11"/>
       <c r="R83" s="11" t="str">
         <f>product_listing!C83</f>
         <v/>
@@ -9774,11 +9708,11 @@
         <v/>
       </c>
       <c r="E84" s="11" t="str">
-        <f t="shared" ref="E84:F84" si="327">if(not(isblank($B84)), E83, "")</f>
+        <f t="shared" ref="E84:F84" si="326">if(not(isblank($B84)), E83, "")</f>
         <v/>
       </c>
       <c r="F84" s="11" t="str">
-        <f t="shared" si="327"/>
+        <f t="shared" si="326"/>
         <v/>
       </c>
       <c r="G84" s="11" t="str">
@@ -9786,11 +9720,11 @@
         <v/>
       </c>
       <c r="H84" s="11" t="str">
-        <f t="shared" ref="H84:I84" si="328">if(not(isblank($B84)), H83, "")</f>
+        <f t="shared" ref="H84:I84" si="327">if(not(isblank($B84)), H83, "")</f>
         <v/>
       </c>
       <c r="I84" s="11" t="str">
-        <f t="shared" si="328"/>
+        <f t="shared" si="327"/>
         <v/>
       </c>
       <c r="J84" s="11" t="str">
@@ -9798,11 +9732,11 @@
         <v/>
       </c>
       <c r="K84" s="11" t="str">
-        <f t="shared" ref="K84:L84" si="329">if(not(isblank($B84)), K83, "")</f>
+        <f t="shared" ref="K84:L84" si="328">if(not(isblank($B84)), K83, "")</f>
         <v/>
       </c>
       <c r="L84" s="11" t="str">
-        <f t="shared" si="329"/>
+        <f t="shared" si="328"/>
         <v/>
       </c>
       <c r="M84" s="11" t="str">
@@ -9810,21 +9744,18 @@
         <v/>
       </c>
       <c r="N84" s="11" t="str">
-        <f t="shared" ref="N84:O84" si="330">if(not(isblank($B84)), N83, "")</f>
+        <f t="shared" ref="N84:O84" si="329">if(not(isblank($B84)), N83, "")</f>
         <v/>
       </c>
       <c r="O84" s="11" t="str">
-        <f t="shared" si="330"/>
+        <f t="shared" si="329"/>
         <v/>
       </c>
       <c r="P84" s="11" t="str">
         <f>product_listing!J84</f>
         <v/>
       </c>
-      <c r="Q84" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q84" s="11"/>
       <c r="R84" s="11" t="str">
         <f>product_listing!C84</f>
         <v/>
@@ -9864,11 +9795,11 @@
         <v/>
       </c>
       <c r="E85" s="11" t="str">
-        <f t="shared" ref="E85:F85" si="331">if(not(isblank($B85)), E84, "")</f>
+        <f t="shared" ref="E85:F85" si="330">if(not(isblank($B85)), E84, "")</f>
         <v/>
       </c>
       <c r="F85" s="11" t="str">
-        <f t="shared" si="331"/>
+        <f t="shared" si="330"/>
         <v/>
       </c>
       <c r="G85" s="11" t="str">
@@ -9876,11 +9807,11 @@
         <v/>
       </c>
       <c r="H85" s="11" t="str">
-        <f t="shared" ref="H85:I85" si="332">if(not(isblank($B85)), H84, "")</f>
+        <f t="shared" ref="H85:I85" si="331">if(not(isblank($B85)), H84, "")</f>
         <v/>
       </c>
       <c r="I85" s="11" t="str">
-        <f t="shared" si="332"/>
+        <f t="shared" si="331"/>
         <v/>
       </c>
       <c r="J85" s="11" t="str">
@@ -9888,11 +9819,11 @@
         <v/>
       </c>
       <c r="K85" s="11" t="str">
-        <f t="shared" ref="K85:L85" si="333">if(not(isblank($B85)), K84, "")</f>
+        <f t="shared" ref="K85:L85" si="332">if(not(isblank($B85)), K84, "")</f>
         <v/>
       </c>
       <c r="L85" s="11" t="str">
-        <f t="shared" si="333"/>
+        <f t="shared" si="332"/>
         <v/>
       </c>
       <c r="M85" s="11" t="str">
@@ -9900,21 +9831,18 @@
         <v/>
       </c>
       <c r="N85" s="11" t="str">
-        <f t="shared" ref="N85:O85" si="334">if(not(isblank($B85)), N84, "")</f>
+        <f t="shared" ref="N85:O85" si="333">if(not(isblank($B85)), N84, "")</f>
         <v/>
       </c>
       <c r="O85" s="11" t="str">
-        <f t="shared" si="334"/>
+        <f t="shared" si="333"/>
         <v/>
       </c>
       <c r="P85" s="11" t="str">
         <f>product_listing!J85</f>
         <v/>
       </c>
-      <c r="Q85" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q85" s="11"/>
       <c r="R85" s="11" t="str">
         <f>product_listing!C85</f>
         <v/>
@@ -9954,11 +9882,11 @@
         <v/>
       </c>
       <c r="E86" s="11" t="str">
-        <f t="shared" ref="E86:F86" si="335">if(not(isblank($B86)), E85, "")</f>
+        <f t="shared" ref="E86:F86" si="334">if(not(isblank($B86)), E85, "")</f>
         <v/>
       </c>
       <c r="F86" s="11" t="str">
-        <f t="shared" si="335"/>
+        <f t="shared" si="334"/>
         <v/>
       </c>
       <c r="G86" s="11" t="str">
@@ -9966,11 +9894,11 @@
         <v/>
       </c>
       <c r="H86" s="11" t="str">
-        <f t="shared" ref="H86:I86" si="336">if(not(isblank($B86)), H85, "")</f>
+        <f t="shared" ref="H86:I86" si="335">if(not(isblank($B86)), H85, "")</f>
         <v/>
       </c>
       <c r="I86" s="11" t="str">
-        <f t="shared" si="336"/>
+        <f t="shared" si="335"/>
         <v/>
       </c>
       <c r="J86" s="11" t="str">
@@ -9978,11 +9906,11 @@
         <v/>
       </c>
       <c r="K86" s="11" t="str">
-        <f t="shared" ref="K86:L86" si="337">if(not(isblank($B86)), K85, "")</f>
+        <f t="shared" ref="K86:L86" si="336">if(not(isblank($B86)), K85, "")</f>
         <v/>
       </c>
       <c r="L86" s="11" t="str">
-        <f t="shared" si="337"/>
+        <f t="shared" si="336"/>
         <v/>
       </c>
       <c r="M86" s="11" t="str">
@@ -9990,21 +9918,18 @@
         <v/>
       </c>
       <c r="N86" s="11" t="str">
-        <f t="shared" ref="N86:O86" si="338">if(not(isblank($B86)), N85, "")</f>
+        <f t="shared" ref="N86:O86" si="337">if(not(isblank($B86)), N85, "")</f>
         <v/>
       </c>
       <c r="O86" s="11" t="str">
-        <f t="shared" si="338"/>
+        <f t="shared" si="337"/>
         <v/>
       </c>
       <c r="P86" s="11" t="str">
         <f>product_listing!J86</f>
         <v/>
       </c>
-      <c r="Q86" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q86" s="11"/>
       <c r="R86" s="11" t="str">
         <f>product_listing!C86</f>
         <v/>
@@ -10044,11 +9969,11 @@
         <v/>
       </c>
       <c r="E87" s="11" t="str">
-        <f t="shared" ref="E87:F87" si="339">if(not(isblank($B87)), E86, "")</f>
+        <f t="shared" ref="E87:F87" si="338">if(not(isblank($B87)), E86, "")</f>
         <v/>
       </c>
       <c r="F87" s="11" t="str">
-        <f t="shared" si="339"/>
+        <f t="shared" si="338"/>
         <v/>
       </c>
       <c r="G87" s="11" t="str">
@@ -10056,11 +9981,11 @@
         <v/>
       </c>
       <c r="H87" s="11" t="str">
-        <f t="shared" ref="H87:I87" si="340">if(not(isblank($B87)), H86, "")</f>
+        <f t="shared" ref="H87:I87" si="339">if(not(isblank($B87)), H86, "")</f>
         <v/>
       </c>
       <c r="I87" s="11" t="str">
-        <f t="shared" si="340"/>
+        <f t="shared" si="339"/>
         <v/>
       </c>
       <c r="J87" s="11" t="str">
@@ -10068,11 +9993,11 @@
         <v/>
       </c>
       <c r="K87" s="11" t="str">
-        <f t="shared" ref="K87:L87" si="341">if(not(isblank($B87)), K86, "")</f>
+        <f t="shared" ref="K87:L87" si="340">if(not(isblank($B87)), K86, "")</f>
         <v/>
       </c>
       <c r="L87" s="11" t="str">
-        <f t="shared" si="341"/>
+        <f t="shared" si="340"/>
         <v/>
       </c>
       <c r="M87" s="11" t="str">
@@ -10080,21 +10005,18 @@
         <v/>
       </c>
       <c r="N87" s="11" t="str">
-        <f t="shared" ref="N87:O87" si="342">if(not(isblank($B87)), N86, "")</f>
+        <f t="shared" ref="N87:O87" si="341">if(not(isblank($B87)), N86, "")</f>
         <v/>
       </c>
       <c r="O87" s="11" t="str">
-        <f t="shared" si="342"/>
+        <f t="shared" si="341"/>
         <v/>
       </c>
       <c r="P87" s="11" t="str">
         <f>product_listing!J87</f>
         <v/>
       </c>
-      <c r="Q87" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q87" s="11"/>
       <c r="R87" s="11" t="str">
         <f>product_listing!C87</f>
         <v/>
@@ -10134,11 +10056,11 @@
         <v/>
       </c>
       <c r="E88" s="11" t="str">
-        <f t="shared" ref="E88:F88" si="343">if(not(isblank($B88)), E87, "")</f>
+        <f t="shared" ref="E88:F88" si="342">if(not(isblank($B88)), E87, "")</f>
         <v/>
       </c>
       <c r="F88" s="11" t="str">
-        <f t="shared" si="343"/>
+        <f t="shared" si="342"/>
         <v/>
       </c>
       <c r="G88" s="11" t="str">
@@ -10146,11 +10068,11 @@
         <v/>
       </c>
       <c r="H88" s="11" t="str">
-        <f t="shared" ref="H88:I88" si="344">if(not(isblank($B88)), H87, "")</f>
+        <f t="shared" ref="H88:I88" si="343">if(not(isblank($B88)), H87, "")</f>
         <v/>
       </c>
       <c r="I88" s="11" t="str">
-        <f t="shared" si="344"/>
+        <f t="shared" si="343"/>
         <v/>
       </c>
       <c r="J88" s="11" t="str">
@@ -10158,11 +10080,11 @@
         <v/>
       </c>
       <c r="K88" s="11" t="str">
-        <f t="shared" ref="K88:L88" si="345">if(not(isblank($B88)), K87, "")</f>
+        <f t="shared" ref="K88:L88" si="344">if(not(isblank($B88)), K87, "")</f>
         <v/>
       </c>
       <c r="L88" s="11" t="str">
-        <f t="shared" si="345"/>
+        <f t="shared" si="344"/>
         <v/>
       </c>
       <c r="M88" s="11" t="str">
@@ -10170,21 +10092,18 @@
         <v/>
       </c>
       <c r="N88" s="11" t="str">
-        <f t="shared" ref="N88:O88" si="346">if(not(isblank($B88)), N87, "")</f>
+        <f t="shared" ref="N88:O88" si="345">if(not(isblank($B88)), N87, "")</f>
         <v/>
       </c>
       <c r="O88" s="11" t="str">
-        <f t="shared" si="346"/>
+        <f t="shared" si="345"/>
         <v/>
       </c>
       <c r="P88" s="11" t="str">
         <f>product_listing!J88</f>
         <v/>
       </c>
-      <c r="Q88" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q88" s="11"/>
       <c r="R88" s="11" t="str">
         <f>product_listing!C88</f>
         <v/>
@@ -10224,11 +10143,11 @@
         <v/>
       </c>
       <c r="E89" s="11" t="str">
-        <f t="shared" ref="E89:F89" si="347">if(not(isblank($B89)), E88, "")</f>
+        <f t="shared" ref="E89:F89" si="346">if(not(isblank($B89)), E88, "")</f>
         <v/>
       </c>
       <c r="F89" s="11" t="str">
-        <f t="shared" si="347"/>
+        <f t="shared" si="346"/>
         <v/>
       </c>
       <c r="G89" s="11" t="str">
@@ -10236,11 +10155,11 @@
         <v/>
       </c>
       <c r="H89" s="11" t="str">
-        <f t="shared" ref="H89:I89" si="348">if(not(isblank($B89)), H88, "")</f>
+        <f t="shared" ref="H89:I89" si="347">if(not(isblank($B89)), H88, "")</f>
         <v/>
       </c>
       <c r="I89" s="11" t="str">
-        <f t="shared" si="348"/>
+        <f t="shared" si="347"/>
         <v/>
       </c>
       <c r="J89" s="11" t="str">
@@ -10248,11 +10167,11 @@
         <v/>
       </c>
       <c r="K89" s="11" t="str">
-        <f t="shared" ref="K89:L89" si="349">if(not(isblank($B89)), K88, "")</f>
+        <f t="shared" ref="K89:L89" si="348">if(not(isblank($B89)), K88, "")</f>
         <v/>
       </c>
       <c r="L89" s="11" t="str">
-        <f t="shared" si="349"/>
+        <f t="shared" si="348"/>
         <v/>
       </c>
       <c r="M89" s="11" t="str">
@@ -10260,21 +10179,18 @@
         <v/>
       </c>
       <c r="N89" s="11" t="str">
-        <f t="shared" ref="N89:O89" si="350">if(not(isblank($B89)), N88, "")</f>
+        <f t="shared" ref="N89:O89" si="349">if(not(isblank($B89)), N88, "")</f>
         <v/>
       </c>
       <c r="O89" s="11" t="str">
-        <f t="shared" si="350"/>
+        <f t="shared" si="349"/>
         <v/>
       </c>
       <c r="P89" s="11" t="str">
         <f>product_listing!J89</f>
         <v/>
       </c>
-      <c r="Q89" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q89" s="11"/>
       <c r="R89" s="11" t="str">
         <f>product_listing!C89</f>
         <v/>
@@ -10314,11 +10230,11 @@
         <v/>
       </c>
       <c r="E90" s="11" t="str">
-        <f t="shared" ref="E90:F90" si="351">if(not(isblank($B90)), E89, "")</f>
+        <f t="shared" ref="E90:F90" si="350">if(not(isblank($B90)), E89, "")</f>
         <v/>
       </c>
       <c r="F90" s="11" t="str">
-        <f t="shared" si="351"/>
+        <f t="shared" si="350"/>
         <v/>
       </c>
       <c r="G90" s="11" t="str">
@@ -10326,11 +10242,11 @@
         <v/>
       </c>
       <c r="H90" s="11" t="str">
-        <f t="shared" ref="H90:I90" si="352">if(not(isblank($B90)), H89, "")</f>
+        <f t="shared" ref="H90:I90" si="351">if(not(isblank($B90)), H89, "")</f>
         <v/>
       </c>
       <c r="I90" s="11" t="str">
-        <f t="shared" si="352"/>
+        <f t="shared" si="351"/>
         <v/>
       </c>
       <c r="J90" s="11" t="str">
@@ -10338,11 +10254,11 @@
         <v/>
       </c>
       <c r="K90" s="11" t="str">
-        <f t="shared" ref="K90:L90" si="353">if(not(isblank($B90)), K89, "")</f>
+        <f t="shared" ref="K90:L90" si="352">if(not(isblank($B90)), K89, "")</f>
         <v/>
       </c>
       <c r="L90" s="11" t="str">
-        <f t="shared" si="353"/>
+        <f t="shared" si="352"/>
         <v/>
       </c>
       <c r="M90" s="11" t="str">
@@ -10350,21 +10266,18 @@
         <v/>
       </c>
       <c r="N90" s="11" t="str">
-        <f t="shared" ref="N90:O90" si="354">if(not(isblank($B90)), N89, "")</f>
+        <f t="shared" ref="N90:O90" si="353">if(not(isblank($B90)), N89, "")</f>
         <v/>
       </c>
       <c r="O90" s="11" t="str">
-        <f t="shared" si="354"/>
+        <f t="shared" si="353"/>
         <v/>
       </c>
       <c r="P90" s="11" t="str">
         <f>product_listing!J90</f>
         <v/>
       </c>
-      <c r="Q90" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q90" s="11"/>
       <c r="R90" s="11" t="str">
         <f>product_listing!C90</f>
         <v/>
@@ -10404,11 +10317,11 @@
         <v/>
       </c>
       <c r="E91" s="11" t="str">
-        <f t="shared" ref="E91:F91" si="355">if(not(isblank($B91)), E90, "")</f>
+        <f t="shared" ref="E91:F91" si="354">if(not(isblank($B91)), E90, "")</f>
         <v/>
       </c>
       <c r="F91" s="11" t="str">
-        <f t="shared" si="355"/>
+        <f t="shared" si="354"/>
         <v/>
       </c>
       <c r="G91" s="11" t="str">
@@ -10416,11 +10329,11 @@
         <v/>
       </c>
       <c r="H91" s="11" t="str">
-        <f t="shared" ref="H91:I91" si="356">if(not(isblank($B91)), H90, "")</f>
+        <f t="shared" ref="H91:I91" si="355">if(not(isblank($B91)), H90, "")</f>
         <v/>
       </c>
       <c r="I91" s="11" t="str">
-        <f t="shared" si="356"/>
+        <f t="shared" si="355"/>
         <v/>
       </c>
       <c r="J91" s="11" t="str">
@@ -10428,11 +10341,11 @@
         <v/>
       </c>
       <c r="K91" s="11" t="str">
-        <f t="shared" ref="K91:L91" si="357">if(not(isblank($B91)), K90, "")</f>
+        <f t="shared" ref="K91:L91" si="356">if(not(isblank($B91)), K90, "")</f>
         <v/>
       </c>
       <c r="L91" s="11" t="str">
-        <f t="shared" si="357"/>
+        <f t="shared" si="356"/>
         <v/>
       </c>
       <c r="M91" s="11" t="str">
@@ -10440,21 +10353,18 @@
         <v/>
       </c>
       <c r="N91" s="11" t="str">
-        <f t="shared" ref="N91:O91" si="358">if(not(isblank($B91)), N90, "")</f>
+        <f t="shared" ref="N91:O91" si="357">if(not(isblank($B91)), N90, "")</f>
         <v/>
       </c>
       <c r="O91" s="11" t="str">
-        <f t="shared" si="358"/>
+        <f t="shared" si="357"/>
         <v/>
       </c>
       <c r="P91" s="11" t="str">
         <f>product_listing!J91</f>
         <v/>
       </c>
-      <c r="Q91" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q91" s="11"/>
       <c r="R91" s="11" t="str">
         <f>product_listing!C91</f>
         <v/>
@@ -10494,11 +10404,11 @@
         <v/>
       </c>
       <c r="E92" s="11" t="str">
-        <f t="shared" ref="E92:F92" si="359">if(not(isblank($B92)), E91, "")</f>
+        <f t="shared" ref="E92:F92" si="358">if(not(isblank($B92)), E91, "")</f>
         <v/>
       </c>
       <c r="F92" s="11" t="str">
-        <f t="shared" si="359"/>
+        <f t="shared" si="358"/>
         <v/>
       </c>
       <c r="G92" s="11" t="str">
@@ -10506,11 +10416,11 @@
         <v/>
       </c>
       <c r="H92" s="11" t="str">
-        <f t="shared" ref="H92:I92" si="360">if(not(isblank($B92)), H91, "")</f>
+        <f t="shared" ref="H92:I92" si="359">if(not(isblank($B92)), H91, "")</f>
         <v/>
       </c>
       <c r="I92" s="11" t="str">
-        <f t="shared" si="360"/>
+        <f t="shared" si="359"/>
         <v/>
       </c>
       <c r="J92" s="11" t="str">
@@ -10518,11 +10428,11 @@
         <v/>
       </c>
       <c r="K92" s="11" t="str">
-        <f t="shared" ref="K92:L92" si="361">if(not(isblank($B92)), K91, "")</f>
+        <f t="shared" ref="K92:L92" si="360">if(not(isblank($B92)), K91, "")</f>
         <v/>
       </c>
       <c r="L92" s="11" t="str">
-        <f t="shared" si="361"/>
+        <f t="shared" si="360"/>
         <v/>
       </c>
       <c r="M92" s="11" t="str">
@@ -10530,21 +10440,18 @@
         <v/>
       </c>
       <c r="N92" s="11" t="str">
-        <f t="shared" ref="N92:O92" si="362">if(not(isblank($B92)), N91, "")</f>
+        <f t="shared" ref="N92:O92" si="361">if(not(isblank($B92)), N91, "")</f>
         <v/>
       </c>
       <c r="O92" s="11" t="str">
-        <f t="shared" si="362"/>
+        <f t="shared" si="361"/>
         <v/>
       </c>
       <c r="P92" s="11" t="str">
         <f>product_listing!J92</f>
         <v/>
       </c>
-      <c r="Q92" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q92" s="11"/>
       <c r="R92" s="11" t="str">
         <f>product_listing!C92</f>
         <v/>
@@ -10584,11 +10491,11 @@
         <v/>
       </c>
       <c r="E93" s="11" t="str">
-        <f t="shared" ref="E93:F93" si="363">if(not(isblank($B93)), E92, "")</f>
+        <f t="shared" ref="E93:F93" si="362">if(not(isblank($B93)), E92, "")</f>
         <v/>
       </c>
       <c r="F93" s="11" t="str">
-        <f t="shared" si="363"/>
+        <f t="shared" si="362"/>
         <v/>
       </c>
       <c r="G93" s="11" t="str">
@@ -10596,11 +10503,11 @@
         <v/>
       </c>
       <c r="H93" s="11" t="str">
-        <f t="shared" ref="H93:I93" si="364">if(not(isblank($B93)), H92, "")</f>
+        <f t="shared" ref="H93:I93" si="363">if(not(isblank($B93)), H92, "")</f>
         <v/>
       </c>
       <c r="I93" s="11" t="str">
-        <f t="shared" si="364"/>
+        <f t="shared" si="363"/>
         <v/>
       </c>
       <c r="J93" s="11" t="str">
@@ -10608,11 +10515,11 @@
         <v/>
       </c>
       <c r="K93" s="11" t="str">
-        <f t="shared" ref="K93:L93" si="365">if(not(isblank($B93)), K92, "")</f>
+        <f t="shared" ref="K93:L93" si="364">if(not(isblank($B93)), K92, "")</f>
         <v/>
       </c>
       <c r="L93" s="11" t="str">
-        <f t="shared" si="365"/>
+        <f t="shared" si="364"/>
         <v/>
       </c>
       <c r="M93" s="11" t="str">
@@ -10620,21 +10527,18 @@
         <v/>
       </c>
       <c r="N93" s="11" t="str">
-        <f t="shared" ref="N93:O93" si="366">if(not(isblank($B93)), N92, "")</f>
+        <f t="shared" ref="N93:O93" si="365">if(not(isblank($B93)), N92, "")</f>
         <v/>
       </c>
       <c r="O93" s="11" t="str">
-        <f t="shared" si="366"/>
+        <f t="shared" si="365"/>
         <v/>
       </c>
       <c r="P93" s="11" t="str">
         <f>product_listing!J93</f>
         <v/>
       </c>
-      <c r="Q93" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q93" s="11"/>
       <c r="R93" s="11" t="str">
         <f>product_listing!C93</f>
         <v/>
@@ -10674,11 +10578,11 @@
         <v/>
       </c>
       <c r="E94" s="11" t="str">
-        <f t="shared" ref="E94:F94" si="367">if(not(isblank($B94)), E93, "")</f>
+        <f t="shared" ref="E94:F94" si="366">if(not(isblank($B94)), E93, "")</f>
         <v/>
       </c>
       <c r="F94" s="11" t="str">
-        <f t="shared" si="367"/>
+        <f t="shared" si="366"/>
         <v/>
       </c>
       <c r="G94" s="11" t="str">
@@ -10686,11 +10590,11 @@
         <v/>
       </c>
       <c r="H94" s="11" t="str">
-        <f t="shared" ref="H94:I94" si="368">if(not(isblank($B94)), H93, "")</f>
+        <f t="shared" ref="H94:I94" si="367">if(not(isblank($B94)), H93, "")</f>
         <v/>
       </c>
       <c r="I94" s="11" t="str">
-        <f t="shared" si="368"/>
+        <f t="shared" si="367"/>
         <v/>
       </c>
       <c r="J94" s="11" t="str">
@@ -10698,11 +10602,11 @@
         <v/>
       </c>
       <c r="K94" s="11" t="str">
-        <f t="shared" ref="K94:L94" si="369">if(not(isblank($B94)), K93, "")</f>
+        <f t="shared" ref="K94:L94" si="368">if(not(isblank($B94)), K93, "")</f>
         <v/>
       </c>
       <c r="L94" s="11" t="str">
-        <f t="shared" si="369"/>
+        <f t="shared" si="368"/>
         <v/>
       </c>
       <c r="M94" s="11" t="str">
@@ -10710,21 +10614,18 @@
         <v/>
       </c>
       <c r="N94" s="11" t="str">
-        <f t="shared" ref="N94:O94" si="370">if(not(isblank($B94)), N93, "")</f>
+        <f t="shared" ref="N94:O94" si="369">if(not(isblank($B94)), N93, "")</f>
         <v/>
       </c>
       <c r="O94" s="11" t="str">
-        <f t="shared" si="370"/>
+        <f t="shared" si="369"/>
         <v/>
       </c>
       <c r="P94" s="11" t="str">
         <f>product_listing!J94</f>
         <v/>
       </c>
-      <c r="Q94" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q94" s="11"/>
       <c r="R94" s="11" t="str">
         <f>product_listing!C94</f>
         <v/>
@@ -10764,11 +10665,11 @@
         <v/>
       </c>
       <c r="E95" s="11" t="str">
-        <f t="shared" ref="E95:F95" si="371">if(not(isblank($B95)), E94, "")</f>
+        <f t="shared" ref="E95:F95" si="370">if(not(isblank($B95)), E94, "")</f>
         <v/>
       </c>
       <c r="F95" s="11" t="str">
-        <f t="shared" si="371"/>
+        <f t="shared" si="370"/>
         <v/>
       </c>
       <c r="G95" s="11" t="str">
@@ -10776,11 +10677,11 @@
         <v/>
       </c>
       <c r="H95" s="11" t="str">
-        <f t="shared" ref="H95:I95" si="372">if(not(isblank($B95)), H94, "")</f>
+        <f t="shared" ref="H95:I95" si="371">if(not(isblank($B95)), H94, "")</f>
         <v/>
       </c>
       <c r="I95" s="11" t="str">
-        <f t="shared" si="372"/>
+        <f t="shared" si="371"/>
         <v/>
       </c>
       <c r="J95" s="11" t="str">
@@ -10788,11 +10689,11 @@
         <v/>
       </c>
       <c r="K95" s="11" t="str">
-        <f t="shared" ref="K95:L95" si="373">if(not(isblank($B95)), K94, "")</f>
+        <f t="shared" ref="K95:L95" si="372">if(not(isblank($B95)), K94, "")</f>
         <v/>
       </c>
       <c r="L95" s="11" t="str">
-        <f t="shared" si="373"/>
+        <f t="shared" si="372"/>
         <v/>
       </c>
       <c r="M95" s="11" t="str">
@@ -10800,21 +10701,18 @@
         <v/>
       </c>
       <c r="N95" s="11" t="str">
-        <f t="shared" ref="N95:O95" si="374">if(not(isblank($B95)), N94, "")</f>
+        <f t="shared" ref="N95:O95" si="373">if(not(isblank($B95)), N94, "")</f>
         <v/>
       </c>
       <c r="O95" s="11" t="str">
-        <f t="shared" si="374"/>
+        <f t="shared" si="373"/>
         <v/>
       </c>
       <c r="P95" s="11" t="str">
         <f>product_listing!J95</f>
         <v/>
       </c>
-      <c r="Q95" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q95" s="11"/>
       <c r="R95" s="11" t="str">
         <f>product_listing!C95</f>
         <v/>
@@ -10854,11 +10752,11 @@
         <v/>
       </c>
       <c r="E96" s="11" t="str">
-        <f t="shared" ref="E96:F96" si="375">if(not(isblank($B96)), E95, "")</f>
+        <f t="shared" ref="E96:F96" si="374">if(not(isblank($B96)), E95, "")</f>
         <v/>
       </c>
       <c r="F96" s="11" t="str">
-        <f t="shared" si="375"/>
+        <f t="shared" si="374"/>
         <v/>
       </c>
       <c r="G96" s="11" t="str">
@@ -10866,11 +10764,11 @@
         <v/>
       </c>
       <c r="H96" s="11" t="str">
-        <f t="shared" ref="H96:I96" si="376">if(not(isblank($B96)), H95, "")</f>
+        <f t="shared" ref="H96:I96" si="375">if(not(isblank($B96)), H95, "")</f>
         <v/>
       </c>
       <c r="I96" s="11" t="str">
-        <f t="shared" si="376"/>
+        <f t="shared" si="375"/>
         <v/>
       </c>
       <c r="J96" s="11" t="str">
@@ -10878,11 +10776,11 @@
         <v/>
       </c>
       <c r="K96" s="11" t="str">
-        <f t="shared" ref="K96:L96" si="377">if(not(isblank($B96)), K95, "")</f>
+        <f t="shared" ref="K96:L96" si="376">if(not(isblank($B96)), K95, "")</f>
         <v/>
       </c>
       <c r="L96" s="11" t="str">
-        <f t="shared" si="377"/>
+        <f t="shared" si="376"/>
         <v/>
       </c>
       <c r="M96" s="11" t="str">
@@ -10890,21 +10788,18 @@
         <v/>
       </c>
       <c r="N96" s="11" t="str">
-        <f t="shared" ref="N96:O96" si="378">if(not(isblank($B96)), N95, "")</f>
+        <f t="shared" ref="N96:O96" si="377">if(not(isblank($B96)), N95, "")</f>
         <v/>
       </c>
       <c r="O96" s="11" t="str">
-        <f t="shared" si="378"/>
+        <f t="shared" si="377"/>
         <v/>
       </c>
       <c r="P96" s="11" t="str">
         <f>product_listing!J96</f>
         <v/>
       </c>
-      <c r="Q96" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q96" s="11"/>
       <c r="R96" s="11" t="str">
         <f>product_listing!C96</f>
         <v/>
@@ -10944,11 +10839,11 @@
         <v/>
       </c>
       <c r="E97" s="11" t="str">
-        <f t="shared" ref="E97:F97" si="379">if(not(isblank($B97)), E96, "")</f>
+        <f t="shared" ref="E97:F97" si="378">if(not(isblank($B97)), E96, "")</f>
         <v/>
       </c>
       <c r="F97" s="11" t="str">
-        <f t="shared" si="379"/>
+        <f t="shared" si="378"/>
         <v/>
       </c>
       <c r="G97" s="11" t="str">
@@ -10956,11 +10851,11 @@
         <v/>
       </c>
       <c r="H97" s="11" t="str">
-        <f t="shared" ref="H97:I97" si="380">if(not(isblank($B97)), H96, "")</f>
+        <f t="shared" ref="H97:I97" si="379">if(not(isblank($B97)), H96, "")</f>
         <v/>
       </c>
       <c r="I97" s="11" t="str">
-        <f t="shared" si="380"/>
+        <f t="shared" si="379"/>
         <v/>
       </c>
       <c r="J97" s="11" t="str">
@@ -10968,11 +10863,11 @@
         <v/>
       </c>
       <c r="K97" s="11" t="str">
-        <f t="shared" ref="K97:L97" si="381">if(not(isblank($B97)), K96, "")</f>
+        <f t="shared" ref="K97:L97" si="380">if(not(isblank($B97)), K96, "")</f>
         <v/>
       </c>
       <c r="L97" s="11" t="str">
-        <f t="shared" si="381"/>
+        <f t="shared" si="380"/>
         <v/>
       </c>
       <c r="M97" s="11" t="str">
@@ -10980,21 +10875,18 @@
         <v/>
       </c>
       <c r="N97" s="11" t="str">
-        <f t="shared" ref="N97:O97" si="382">if(not(isblank($B97)), N96, "")</f>
+        <f t="shared" ref="N97:O97" si="381">if(not(isblank($B97)), N96, "")</f>
         <v/>
       </c>
       <c r="O97" s="11" t="str">
-        <f t="shared" si="382"/>
+        <f t="shared" si="381"/>
         <v/>
       </c>
       <c r="P97" s="11" t="str">
         <f>product_listing!J97</f>
         <v/>
       </c>
-      <c r="Q97" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q97" s="11"/>
       <c r="R97" s="11" t="str">
         <f>product_listing!C97</f>
         <v/>
@@ -11034,11 +10926,11 @@
         <v/>
       </c>
       <c r="E98" s="11" t="str">
-        <f t="shared" ref="E98:F98" si="383">if(not(isblank($B98)), E97, "")</f>
+        <f t="shared" ref="E98:F98" si="382">if(not(isblank($B98)), E97, "")</f>
         <v/>
       </c>
       <c r="F98" s="11" t="str">
-        <f t="shared" si="383"/>
+        <f t="shared" si="382"/>
         <v/>
       </c>
       <c r="G98" s="11" t="str">
@@ -11046,11 +10938,11 @@
         <v/>
       </c>
       <c r="H98" s="11" t="str">
-        <f t="shared" ref="H98:I98" si="384">if(not(isblank($B98)), H97, "")</f>
+        <f t="shared" ref="H98:I98" si="383">if(not(isblank($B98)), H97, "")</f>
         <v/>
       </c>
       <c r="I98" s="11" t="str">
-        <f t="shared" si="384"/>
+        <f t="shared" si="383"/>
         <v/>
       </c>
       <c r="J98" s="11" t="str">
@@ -11058,11 +10950,11 @@
         <v/>
       </c>
       <c r="K98" s="11" t="str">
-        <f t="shared" ref="K98:L98" si="385">if(not(isblank($B98)), K97, "")</f>
+        <f t="shared" ref="K98:L98" si="384">if(not(isblank($B98)), K97, "")</f>
         <v/>
       </c>
       <c r="L98" s="11" t="str">
-        <f t="shared" si="385"/>
+        <f t="shared" si="384"/>
         <v/>
       </c>
       <c r="M98" s="11" t="str">
@@ -11070,21 +10962,18 @@
         <v/>
       </c>
       <c r="N98" s="11" t="str">
-        <f t="shared" ref="N98:O98" si="386">if(not(isblank($B98)), N97, "")</f>
+        <f t="shared" ref="N98:O98" si="385">if(not(isblank($B98)), N97, "")</f>
         <v/>
       </c>
       <c r="O98" s="11" t="str">
-        <f t="shared" si="386"/>
+        <f t="shared" si="385"/>
         <v/>
       </c>
       <c r="P98" s="11" t="str">
         <f>product_listing!J98</f>
         <v/>
       </c>
-      <c r="Q98" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q98" s="11"/>
       <c r="R98" s="11" t="str">
         <f>product_listing!C98</f>
         <v/>
@@ -11124,11 +11013,11 @@
         <v/>
       </c>
       <c r="E99" s="11" t="str">
-        <f t="shared" ref="E99:F99" si="387">if(not(isblank($B99)), E98, "")</f>
+        <f t="shared" ref="E99:F99" si="386">if(not(isblank($B99)), E98, "")</f>
         <v/>
       </c>
       <c r="F99" s="11" t="str">
-        <f t="shared" si="387"/>
+        <f t="shared" si="386"/>
         <v/>
       </c>
       <c r="G99" s="11" t="str">
@@ -11136,11 +11025,11 @@
         <v/>
       </c>
       <c r="H99" s="11" t="str">
-        <f t="shared" ref="H99:I99" si="388">if(not(isblank($B99)), H98, "")</f>
+        <f t="shared" ref="H99:I99" si="387">if(not(isblank($B99)), H98, "")</f>
         <v/>
       </c>
       <c r="I99" s="11" t="str">
-        <f t="shared" si="388"/>
+        <f t="shared" si="387"/>
         <v/>
       </c>
       <c r="J99" s="11" t="str">
@@ -11148,11 +11037,11 @@
         <v/>
       </c>
       <c r="K99" s="11" t="str">
-        <f t="shared" ref="K99:L99" si="389">if(not(isblank($B99)), K98, "")</f>
+        <f t="shared" ref="K99:L99" si="388">if(not(isblank($B99)), K98, "")</f>
         <v/>
       </c>
       <c r="L99" s="11" t="str">
-        <f t="shared" si="389"/>
+        <f t="shared" si="388"/>
         <v/>
       </c>
       <c r="M99" s="11" t="str">
@@ -11160,21 +11049,18 @@
         <v/>
       </c>
       <c r="N99" s="11" t="str">
-        <f t="shared" ref="N99:O99" si="390">if(not(isblank($B99)), N98, "")</f>
+        <f t="shared" ref="N99:O99" si="389">if(not(isblank($B99)), N98, "")</f>
         <v/>
       </c>
       <c r="O99" s="11" t="str">
-        <f t="shared" si="390"/>
+        <f t="shared" si="389"/>
         <v/>
       </c>
       <c r="P99" s="11" t="str">
         <f>product_listing!J99</f>
         <v/>
       </c>
-      <c r="Q99" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q99" s="11"/>
       <c r="R99" s="11" t="str">
         <f>product_listing!C99</f>
         <v/>
@@ -11214,11 +11100,11 @@
         <v/>
       </c>
       <c r="E100" s="11" t="str">
-        <f t="shared" ref="E100:F100" si="391">if(not(isblank($B100)), E99, "")</f>
+        <f t="shared" ref="E100:F100" si="390">if(not(isblank($B100)), E99, "")</f>
         <v/>
       </c>
       <c r="F100" s="11" t="str">
-        <f t="shared" si="391"/>
+        <f t="shared" si="390"/>
         <v/>
       </c>
       <c r="G100" s="11" t="str">
@@ -11226,11 +11112,11 @@
         <v/>
       </c>
       <c r="H100" s="11" t="str">
-        <f t="shared" ref="H100:I100" si="392">if(not(isblank($B100)), H99, "")</f>
+        <f t="shared" ref="H100:I100" si="391">if(not(isblank($B100)), H99, "")</f>
         <v/>
       </c>
       <c r="I100" s="11" t="str">
-        <f t="shared" si="392"/>
+        <f t="shared" si="391"/>
         <v/>
       </c>
       <c r="J100" s="11" t="str">
@@ -11238,11 +11124,11 @@
         <v/>
       </c>
       <c r="K100" s="11" t="str">
-        <f t="shared" ref="K100:L100" si="393">if(not(isblank($B100)), K99, "")</f>
+        <f t="shared" ref="K100:L100" si="392">if(not(isblank($B100)), K99, "")</f>
         <v/>
       </c>
       <c r="L100" s="11" t="str">
-        <f t="shared" si="393"/>
+        <f t="shared" si="392"/>
         <v/>
       </c>
       <c r="M100" s="11" t="str">
@@ -11250,21 +11136,18 @@
         <v/>
       </c>
       <c r="N100" s="11" t="str">
-        <f t="shared" ref="N100:O100" si="394">if(not(isblank($B100)), N99, "")</f>
+        <f t="shared" ref="N100:O100" si="393">if(not(isblank($B100)), N99, "")</f>
         <v/>
       </c>
       <c r="O100" s="11" t="str">
-        <f t="shared" si="394"/>
+        <f t="shared" si="393"/>
         <v/>
       </c>
       <c r="P100" s="11" t="str">
         <f>product_listing!J100</f>
         <v/>
       </c>
-      <c r="Q100" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q100" s="11"/>
       <c r="R100" s="11" t="str">
         <f>product_listing!C100</f>
         <v/>
@@ -11304,11 +11187,11 @@
         <v/>
       </c>
       <c r="E101" s="11" t="str">
-        <f t="shared" ref="E101:F101" si="395">if(not(isblank($B101)), E100, "")</f>
+        <f t="shared" ref="E101:F101" si="394">if(not(isblank($B101)), E100, "")</f>
         <v/>
       </c>
       <c r="F101" s="11" t="str">
-        <f t="shared" si="395"/>
+        <f t="shared" si="394"/>
         <v/>
       </c>
       <c r="G101" s="11" t="str">
@@ -11316,11 +11199,11 @@
         <v/>
       </c>
       <c r="H101" s="11" t="str">
-        <f t="shared" ref="H101:I101" si="396">if(not(isblank($B101)), H100, "")</f>
+        <f t="shared" ref="H101:I101" si="395">if(not(isblank($B101)), H100, "")</f>
         <v/>
       </c>
       <c r="I101" s="11" t="str">
-        <f t="shared" si="396"/>
+        <f t="shared" si="395"/>
         <v/>
       </c>
       <c r="J101" s="11" t="str">
@@ -11328,11 +11211,11 @@
         <v/>
       </c>
       <c r="K101" s="11" t="str">
-        <f t="shared" ref="K101:L101" si="397">if(not(isblank($B101)), K100, "")</f>
+        <f t="shared" ref="K101:L101" si="396">if(not(isblank($B101)), K100, "")</f>
         <v/>
       </c>
       <c r="L101" s="11" t="str">
-        <f t="shared" si="397"/>
+        <f t="shared" si="396"/>
         <v/>
       </c>
       <c r="M101" s="11" t="str">
@@ -11340,21 +11223,18 @@
         <v/>
       </c>
       <c r="N101" s="11" t="str">
-        <f t="shared" ref="N101:O101" si="398">if(not(isblank($B101)), N100, "")</f>
+        <f t="shared" ref="N101:O101" si="397">if(not(isblank($B101)), N100, "")</f>
         <v/>
       </c>
       <c r="O101" s="11" t="str">
-        <f t="shared" si="398"/>
+        <f t="shared" si="397"/>
         <v/>
       </c>
       <c r="P101" s="11" t="str">
         <f>product_listing!J101</f>
         <v/>
       </c>
-      <c r="Q101" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q101" s="11"/>
       <c r="R101" s="11" t="str">
         <f>product_listing!C101</f>
         <v/>
@@ -11394,11 +11274,11 @@
         <v/>
       </c>
       <c r="E102" s="11" t="str">
-        <f t="shared" ref="E102:F102" si="399">if(not(isblank($B102)), E101, "")</f>
+        <f t="shared" ref="E102:F102" si="398">if(not(isblank($B102)), E101, "")</f>
         <v/>
       </c>
       <c r="F102" s="11" t="str">
-        <f t="shared" si="399"/>
+        <f t="shared" si="398"/>
         <v/>
       </c>
       <c r="G102" s="11" t="str">
@@ -11406,11 +11286,11 @@
         <v/>
       </c>
       <c r="H102" s="11" t="str">
-        <f t="shared" ref="H102:I102" si="400">if(not(isblank($B102)), H101, "")</f>
+        <f t="shared" ref="H102:I102" si="399">if(not(isblank($B102)), H101, "")</f>
         <v/>
       </c>
       <c r="I102" s="11" t="str">
-        <f t="shared" si="400"/>
+        <f t="shared" si="399"/>
         <v/>
       </c>
       <c r="J102" s="11" t="str">
@@ -11418,11 +11298,11 @@
         <v/>
       </c>
       <c r="K102" s="11" t="str">
-        <f t="shared" ref="K102:L102" si="401">if(not(isblank($B102)), K101, "")</f>
+        <f t="shared" ref="K102:L102" si="400">if(not(isblank($B102)), K101, "")</f>
         <v/>
       </c>
       <c r="L102" s="11" t="str">
-        <f t="shared" si="401"/>
+        <f t="shared" si="400"/>
         <v/>
       </c>
       <c r="M102" s="11" t="str">
@@ -11430,21 +11310,18 @@
         <v/>
       </c>
       <c r="N102" s="11" t="str">
-        <f t="shared" ref="N102:O102" si="402">if(not(isblank($B102)), N101, "")</f>
+        <f t="shared" ref="N102:O102" si="401">if(not(isblank($B102)), N101, "")</f>
         <v/>
       </c>
       <c r="O102" s="11" t="str">
-        <f t="shared" si="402"/>
+        <f t="shared" si="401"/>
         <v/>
       </c>
       <c r="P102" s="11" t="str">
         <f>product_listing!J102</f>
         <v/>
       </c>
-      <c r="Q102" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q102" s="11"/>
       <c r="R102" s="11" t="str">
         <f>product_listing!C102</f>
         <v/>
@@ -11484,11 +11361,11 @@
         <v/>
       </c>
       <c r="E103" s="11" t="str">
-        <f t="shared" ref="E103:F103" si="403">if(not(isblank($B103)), E102, "")</f>
+        <f t="shared" ref="E103:F103" si="402">if(not(isblank($B103)), E102, "")</f>
         <v/>
       </c>
       <c r="F103" s="11" t="str">
-        <f t="shared" si="403"/>
+        <f t="shared" si="402"/>
         <v/>
       </c>
       <c r="G103" s="11" t="str">
@@ -11496,11 +11373,11 @@
         <v/>
       </c>
       <c r="H103" s="11" t="str">
-        <f t="shared" ref="H103:I103" si="404">if(not(isblank($B103)), H102, "")</f>
+        <f t="shared" ref="H103:I103" si="403">if(not(isblank($B103)), H102, "")</f>
         <v/>
       </c>
       <c r="I103" s="11" t="str">
-        <f t="shared" si="404"/>
+        <f t="shared" si="403"/>
         <v/>
       </c>
       <c r="J103" s="11" t="str">
@@ -11508,11 +11385,11 @@
         <v/>
       </c>
       <c r="K103" s="11" t="str">
-        <f t="shared" ref="K103:L103" si="405">if(not(isblank($B103)), K102, "")</f>
+        <f t="shared" ref="K103:L103" si="404">if(not(isblank($B103)), K102, "")</f>
         <v/>
       </c>
       <c r="L103" s="11" t="str">
-        <f t="shared" si="405"/>
+        <f t="shared" si="404"/>
         <v/>
       </c>
       <c r="M103" s="11" t="str">
@@ -11520,21 +11397,18 @@
         <v/>
       </c>
       <c r="N103" s="11" t="str">
-        <f t="shared" ref="N103:O103" si="406">if(not(isblank($B103)), N102, "")</f>
+        <f t="shared" ref="N103:O103" si="405">if(not(isblank($B103)), N102, "")</f>
         <v/>
       </c>
       <c r="O103" s="11" t="str">
-        <f t="shared" si="406"/>
+        <f t="shared" si="405"/>
         <v/>
       </c>
       <c r="P103" s="11" t="str">
         <f>product_listing!J103</f>
         <v/>
       </c>
-      <c r="Q103" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q103" s="11"/>
       <c r="R103" s="11" t="str">
         <f>product_listing!C103</f>
         <v/>
@@ -11574,11 +11448,11 @@
         <v/>
       </c>
       <c r="E104" s="11" t="str">
-        <f t="shared" ref="E104:F104" si="407">if(not(isblank($B104)), E103, "")</f>
+        <f t="shared" ref="E104:F104" si="406">if(not(isblank($B104)), E103, "")</f>
         <v/>
       </c>
       <c r="F104" s="11" t="str">
-        <f t="shared" si="407"/>
+        <f t="shared" si="406"/>
         <v/>
       </c>
       <c r="G104" s="11" t="str">
@@ -11586,11 +11460,11 @@
         <v/>
       </c>
       <c r="H104" s="11" t="str">
-        <f t="shared" ref="H104:I104" si="408">if(not(isblank($B104)), H103, "")</f>
+        <f t="shared" ref="H104:I104" si="407">if(not(isblank($B104)), H103, "")</f>
         <v/>
       </c>
       <c r="I104" s="11" t="str">
-        <f t="shared" si="408"/>
+        <f t="shared" si="407"/>
         <v/>
       </c>
       <c r="J104" s="11" t="str">
@@ -11598,11 +11472,11 @@
         <v/>
       </c>
       <c r="K104" s="11" t="str">
-        <f t="shared" ref="K104:L104" si="409">if(not(isblank($B104)), K103, "")</f>
+        <f t="shared" ref="K104:L104" si="408">if(not(isblank($B104)), K103, "")</f>
         <v/>
       </c>
       <c r="L104" s="11" t="str">
-        <f t="shared" si="409"/>
+        <f t="shared" si="408"/>
         <v/>
       </c>
       <c r="M104" s="11" t="str">
@@ -11610,21 +11484,18 @@
         <v/>
       </c>
       <c r="N104" s="11" t="str">
-        <f t="shared" ref="N104:O104" si="410">if(not(isblank($B104)), N103, "")</f>
+        <f t="shared" ref="N104:O104" si="409">if(not(isblank($B104)), N103, "")</f>
         <v/>
       </c>
       <c r="O104" s="11" t="str">
-        <f t="shared" si="410"/>
+        <f t="shared" si="409"/>
         <v/>
       </c>
       <c r="P104" s="11" t="str">
         <f>product_listing!J104</f>
         <v/>
       </c>
-      <c r="Q104" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q104" s="11"/>
       <c r="R104" s="11" t="str">
         <f>product_listing!C104</f>
         <v/>
@@ -11664,11 +11535,11 @@
         <v/>
       </c>
       <c r="E105" s="11" t="str">
-        <f t="shared" ref="E105:F105" si="411">if(not(isblank($B105)), E104, "")</f>
+        <f t="shared" ref="E105:F105" si="410">if(not(isblank($B105)), E104, "")</f>
         <v/>
       </c>
       <c r="F105" s="11" t="str">
-        <f t="shared" si="411"/>
+        <f t="shared" si="410"/>
         <v/>
       </c>
       <c r="G105" s="11" t="str">
@@ -11676,11 +11547,11 @@
         <v/>
       </c>
       <c r="H105" s="11" t="str">
-        <f t="shared" ref="H105:I105" si="412">if(not(isblank($B105)), H104, "")</f>
+        <f t="shared" ref="H105:I105" si="411">if(not(isblank($B105)), H104, "")</f>
         <v/>
       </c>
       <c r="I105" s="11" t="str">
-        <f t="shared" si="412"/>
+        <f t="shared" si="411"/>
         <v/>
       </c>
       <c r="J105" s="11" t="str">
@@ -11688,11 +11559,11 @@
         <v/>
       </c>
       <c r="K105" s="11" t="str">
-        <f t="shared" ref="K105:L105" si="413">if(not(isblank($B105)), K104, "")</f>
+        <f t="shared" ref="K105:L105" si="412">if(not(isblank($B105)), K104, "")</f>
         <v/>
       </c>
       <c r="L105" s="11" t="str">
-        <f t="shared" si="413"/>
+        <f t="shared" si="412"/>
         <v/>
       </c>
       <c r="M105" s="11" t="str">
@@ -11700,21 +11571,18 @@
         <v/>
       </c>
       <c r="N105" s="11" t="str">
-        <f t="shared" ref="N105:O105" si="414">if(not(isblank($B105)), N104, "")</f>
+        <f t="shared" ref="N105:O105" si="413">if(not(isblank($B105)), N104, "")</f>
         <v/>
       </c>
       <c r="O105" s="11" t="str">
-        <f t="shared" si="414"/>
+        <f t="shared" si="413"/>
         <v/>
       </c>
       <c r="P105" s="11" t="str">
         <f>product_listing!J105</f>
         <v/>
       </c>
-      <c r="Q105" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q105" s="11"/>
       <c r="R105" s="11" t="str">
         <f>product_listing!C105</f>
         <v/>
@@ -11754,11 +11622,11 @@
         <v/>
       </c>
       <c r="E106" s="11" t="str">
-        <f t="shared" ref="E106:F106" si="415">if(not(isblank($B106)), E105, "")</f>
+        <f t="shared" ref="E106:F106" si="414">if(not(isblank($B106)), E105, "")</f>
         <v/>
       </c>
       <c r="F106" s="11" t="str">
-        <f t="shared" si="415"/>
+        <f t="shared" si="414"/>
         <v/>
       </c>
       <c r="G106" s="11" t="str">
@@ -11766,11 +11634,11 @@
         <v/>
       </c>
       <c r="H106" s="11" t="str">
-        <f t="shared" ref="H106:I106" si="416">if(not(isblank($B106)), H105, "")</f>
+        <f t="shared" ref="H106:I106" si="415">if(not(isblank($B106)), H105, "")</f>
         <v/>
       </c>
       <c r="I106" s="11" t="str">
-        <f t="shared" si="416"/>
+        <f t="shared" si="415"/>
         <v/>
       </c>
       <c r="J106" s="11" t="str">
@@ -11778,11 +11646,11 @@
         <v/>
       </c>
       <c r="K106" s="11" t="str">
-        <f t="shared" ref="K106:L106" si="417">if(not(isblank($B106)), K105, "")</f>
+        <f t="shared" ref="K106:L106" si="416">if(not(isblank($B106)), K105, "")</f>
         <v/>
       </c>
       <c r="L106" s="11" t="str">
-        <f t="shared" si="417"/>
+        <f t="shared" si="416"/>
         <v/>
       </c>
       <c r="M106" s="11" t="str">
@@ -11790,21 +11658,18 @@
         <v/>
       </c>
       <c r="N106" s="11" t="str">
-        <f t="shared" ref="N106:O106" si="418">if(not(isblank($B106)), N105, "")</f>
+        <f t="shared" ref="N106:O106" si="417">if(not(isblank($B106)), N105, "")</f>
         <v/>
       </c>
       <c r="O106" s="11" t="str">
-        <f t="shared" si="418"/>
+        <f t="shared" si="417"/>
         <v/>
       </c>
       <c r="P106" s="11" t="str">
         <f>product_listing!J106</f>
         <v/>
       </c>
-      <c r="Q106" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q106" s="11"/>
       <c r="R106" s="11" t="str">
         <f>product_listing!C106</f>
         <v/>
@@ -11844,11 +11709,11 @@
         <v/>
       </c>
       <c r="E107" s="11" t="str">
-        <f t="shared" ref="E107:F107" si="419">if(not(isblank($B107)), E106, "")</f>
+        <f t="shared" ref="E107:F107" si="418">if(not(isblank($B107)), E106, "")</f>
         <v/>
       </c>
       <c r="F107" s="11" t="str">
-        <f t="shared" si="419"/>
+        <f t="shared" si="418"/>
         <v/>
       </c>
       <c r="G107" s="11" t="str">
@@ -11856,11 +11721,11 @@
         <v/>
       </c>
       <c r="H107" s="11" t="str">
-        <f t="shared" ref="H107:I107" si="420">if(not(isblank($B107)), H106, "")</f>
+        <f t="shared" ref="H107:I107" si="419">if(not(isblank($B107)), H106, "")</f>
         <v/>
       </c>
       <c r="I107" s="11" t="str">
-        <f t="shared" si="420"/>
+        <f t="shared" si="419"/>
         <v/>
       </c>
       <c r="J107" s="11" t="str">
@@ -11868,11 +11733,11 @@
         <v/>
       </c>
       <c r="K107" s="11" t="str">
-        <f t="shared" ref="K107:L107" si="421">if(not(isblank($B107)), K106, "")</f>
+        <f t="shared" ref="K107:L107" si="420">if(not(isblank($B107)), K106, "")</f>
         <v/>
       </c>
       <c r="L107" s="11" t="str">
-        <f t="shared" si="421"/>
+        <f t="shared" si="420"/>
         <v/>
       </c>
       <c r="M107" s="11" t="str">
@@ -11880,21 +11745,18 @@
         <v/>
       </c>
       <c r="N107" s="11" t="str">
-        <f t="shared" ref="N107:O107" si="422">if(not(isblank($B107)), N106, "")</f>
+        <f t="shared" ref="N107:O107" si="421">if(not(isblank($B107)), N106, "")</f>
         <v/>
       </c>
       <c r="O107" s="11" t="str">
-        <f t="shared" si="422"/>
+        <f t="shared" si="421"/>
         <v/>
       </c>
       <c r="P107" s="11" t="str">
         <f>product_listing!J107</f>
         <v/>
       </c>
-      <c r="Q107" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q107" s="11"/>
       <c r="R107" s="11" t="str">
         <f>product_listing!C107</f>
         <v/>
@@ -11934,11 +11796,11 @@
         <v/>
       </c>
       <c r="E108" s="11" t="str">
-        <f t="shared" ref="E108:F108" si="423">if(not(isblank($B108)), E107, "")</f>
+        <f t="shared" ref="E108:F108" si="422">if(not(isblank($B108)), E107, "")</f>
         <v/>
       </c>
       <c r="F108" s="11" t="str">
-        <f t="shared" si="423"/>
+        <f t="shared" si="422"/>
         <v/>
       </c>
       <c r="G108" s="11" t="str">
@@ -11946,11 +11808,11 @@
         <v/>
       </c>
       <c r="H108" s="11" t="str">
-        <f t="shared" ref="H108:I108" si="424">if(not(isblank($B108)), H107, "")</f>
+        <f t="shared" ref="H108:I108" si="423">if(not(isblank($B108)), H107, "")</f>
         <v/>
       </c>
       <c r="I108" s="11" t="str">
-        <f t="shared" si="424"/>
+        <f t="shared" si="423"/>
         <v/>
       </c>
       <c r="J108" s="11" t="str">
@@ -11958,11 +11820,11 @@
         <v/>
       </c>
       <c r="K108" s="11" t="str">
-        <f t="shared" ref="K108:L108" si="425">if(not(isblank($B108)), K107, "")</f>
+        <f t="shared" ref="K108:L108" si="424">if(not(isblank($B108)), K107, "")</f>
         <v/>
       </c>
       <c r="L108" s="11" t="str">
-        <f t="shared" si="425"/>
+        <f t="shared" si="424"/>
         <v/>
       </c>
       <c r="M108" s="11" t="str">
@@ -11970,21 +11832,18 @@
         <v/>
       </c>
       <c r="N108" s="11" t="str">
-        <f t="shared" ref="N108:O108" si="426">if(not(isblank($B108)), N107, "")</f>
+        <f t="shared" ref="N108:O108" si="425">if(not(isblank($B108)), N107, "")</f>
         <v/>
       </c>
       <c r="O108" s="11" t="str">
-        <f t="shared" si="426"/>
+        <f t="shared" si="425"/>
         <v/>
       </c>
       <c r="P108" s="11" t="str">
         <f>product_listing!J108</f>
         <v/>
       </c>
-      <c r="Q108" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q108" s="11"/>
       <c r="R108" s="11" t="str">
         <f>product_listing!C108</f>
         <v/>
@@ -12024,11 +11883,11 @@
         <v/>
       </c>
       <c r="E109" s="11" t="str">
-        <f t="shared" ref="E109:F109" si="427">if(not(isblank($B109)), E108, "")</f>
+        <f t="shared" ref="E109:F109" si="426">if(not(isblank($B109)), E108, "")</f>
         <v/>
       </c>
       <c r="F109" s="11" t="str">
-        <f t="shared" si="427"/>
+        <f t="shared" si="426"/>
         <v/>
       </c>
       <c r="G109" s="11" t="str">
@@ -12036,11 +11895,11 @@
         <v/>
       </c>
       <c r="H109" s="11" t="str">
-        <f t="shared" ref="H109:I109" si="428">if(not(isblank($B109)), H108, "")</f>
+        <f t="shared" ref="H109:I109" si="427">if(not(isblank($B109)), H108, "")</f>
         <v/>
       </c>
       <c r="I109" s="11" t="str">
-        <f t="shared" si="428"/>
+        <f t="shared" si="427"/>
         <v/>
       </c>
       <c r="J109" s="11" t="str">
@@ -12048,11 +11907,11 @@
         <v/>
       </c>
       <c r="K109" s="11" t="str">
-        <f t="shared" ref="K109:L109" si="429">if(not(isblank($B109)), K108, "")</f>
+        <f t="shared" ref="K109:L109" si="428">if(not(isblank($B109)), K108, "")</f>
         <v/>
       </c>
       <c r="L109" s="11" t="str">
-        <f t="shared" si="429"/>
+        <f t="shared" si="428"/>
         <v/>
       </c>
       <c r="M109" s="11" t="str">
@@ -12060,21 +11919,18 @@
         <v/>
       </c>
       <c r="N109" s="11" t="str">
-        <f t="shared" ref="N109:O109" si="430">if(not(isblank($B109)), N108, "")</f>
+        <f t="shared" ref="N109:O109" si="429">if(not(isblank($B109)), N108, "")</f>
         <v/>
       </c>
       <c r="O109" s="11" t="str">
-        <f t="shared" si="430"/>
+        <f t="shared" si="429"/>
         <v/>
       </c>
       <c r="P109" s="11" t="str">
         <f>product_listing!J109</f>
         <v/>
       </c>
-      <c r="Q109" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q109" s="11"/>
       <c r="R109" s="11" t="str">
         <f>product_listing!C109</f>
         <v/>
@@ -12114,11 +11970,11 @@
         <v/>
       </c>
       <c r="E110" s="11" t="str">
-        <f t="shared" ref="E110:F110" si="431">if(not(isblank($B110)), E109, "")</f>
+        <f t="shared" ref="E110:F110" si="430">if(not(isblank($B110)), E109, "")</f>
         <v/>
       </c>
       <c r="F110" s="11" t="str">
-        <f t="shared" si="431"/>
+        <f t="shared" si="430"/>
         <v/>
       </c>
       <c r="G110" s="11" t="str">
@@ -12126,11 +11982,11 @@
         <v/>
       </c>
       <c r="H110" s="11" t="str">
-        <f t="shared" ref="H110:I110" si="432">if(not(isblank($B110)), H109, "")</f>
+        <f t="shared" ref="H110:I110" si="431">if(not(isblank($B110)), H109, "")</f>
         <v/>
       </c>
       <c r="I110" s="11" t="str">
-        <f t="shared" si="432"/>
+        <f t="shared" si="431"/>
         <v/>
       </c>
       <c r="J110" s="11" t="str">
@@ -12138,11 +11994,11 @@
         <v/>
       </c>
       <c r="K110" s="11" t="str">
-        <f t="shared" ref="K110:L110" si="433">if(not(isblank($B110)), K109, "")</f>
+        <f t="shared" ref="K110:L110" si="432">if(not(isblank($B110)), K109, "")</f>
         <v/>
       </c>
       <c r="L110" s="11" t="str">
-        <f t="shared" si="433"/>
+        <f t="shared" si="432"/>
         <v/>
       </c>
       <c r="M110" s="11" t="str">
@@ -12150,21 +12006,18 @@
         <v/>
       </c>
       <c r="N110" s="11" t="str">
-        <f t="shared" ref="N110:O110" si="434">if(not(isblank($B110)), N109, "")</f>
+        <f t="shared" ref="N110:O110" si="433">if(not(isblank($B110)), N109, "")</f>
         <v/>
       </c>
       <c r="O110" s="11" t="str">
-        <f t="shared" si="434"/>
+        <f t="shared" si="433"/>
         <v/>
       </c>
       <c r="P110" s="11" t="str">
         <f>product_listing!J110</f>
         <v/>
       </c>
-      <c r="Q110" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q110" s="11"/>
       <c r="R110" s="11" t="str">
         <f>product_listing!C110</f>
         <v/>
@@ -12204,11 +12057,11 @@
         <v/>
       </c>
       <c r="E111" s="11" t="str">
-        <f t="shared" ref="E111:F111" si="435">if(not(isblank($B111)), E110, "")</f>
+        <f t="shared" ref="E111:F111" si="434">if(not(isblank($B111)), E110, "")</f>
         <v/>
       </c>
       <c r="F111" s="11" t="str">
-        <f t="shared" si="435"/>
+        <f t="shared" si="434"/>
         <v/>
       </c>
       <c r="G111" s="11" t="str">
@@ -12216,11 +12069,11 @@
         <v/>
       </c>
       <c r="H111" s="11" t="str">
-        <f t="shared" ref="H111:I111" si="436">if(not(isblank($B111)), H110, "")</f>
+        <f t="shared" ref="H111:I111" si="435">if(not(isblank($B111)), H110, "")</f>
         <v/>
       </c>
       <c r="I111" s="11" t="str">
-        <f t="shared" si="436"/>
+        <f t="shared" si="435"/>
         <v/>
       </c>
       <c r="J111" s="11" t="str">
@@ -12228,11 +12081,11 @@
         <v/>
       </c>
       <c r="K111" s="11" t="str">
-        <f t="shared" ref="K111:L111" si="437">if(not(isblank($B111)), K110, "")</f>
+        <f t="shared" ref="K111:L111" si="436">if(not(isblank($B111)), K110, "")</f>
         <v/>
       </c>
       <c r="L111" s="11" t="str">
-        <f t="shared" si="437"/>
+        <f t="shared" si="436"/>
         <v/>
       </c>
       <c r="M111" s="11" t="str">
@@ -12240,21 +12093,18 @@
         <v/>
       </c>
       <c r="N111" s="11" t="str">
-        <f t="shared" ref="N111:O111" si="438">if(not(isblank($B111)), N110, "")</f>
+        <f t="shared" ref="N111:O111" si="437">if(not(isblank($B111)), N110, "")</f>
         <v/>
       </c>
       <c r="O111" s="11" t="str">
-        <f t="shared" si="438"/>
+        <f t="shared" si="437"/>
         <v/>
       </c>
       <c r="P111" s="11" t="str">
         <f>product_listing!J111</f>
         <v/>
       </c>
-      <c r="Q111" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q111" s="11"/>
       <c r="R111" s="11" t="str">
         <f>product_listing!C111</f>
         <v/>
@@ -12294,11 +12144,11 @@
         <v/>
       </c>
       <c r="E112" s="11" t="str">
-        <f t="shared" ref="E112:F112" si="439">if(not(isblank($B112)), E111, "")</f>
+        <f t="shared" ref="E112:F112" si="438">if(not(isblank($B112)), E111, "")</f>
         <v/>
       </c>
       <c r="F112" s="11" t="str">
-        <f t="shared" si="439"/>
+        <f t="shared" si="438"/>
         <v/>
       </c>
       <c r="G112" s="11" t="str">
@@ -12306,11 +12156,11 @@
         <v/>
       </c>
       <c r="H112" s="11" t="str">
-        <f t="shared" ref="H112:I112" si="440">if(not(isblank($B112)), H111, "")</f>
+        <f t="shared" ref="H112:I112" si="439">if(not(isblank($B112)), H111, "")</f>
         <v/>
       </c>
       <c r="I112" s="11" t="str">
-        <f t="shared" si="440"/>
+        <f t="shared" si="439"/>
         <v/>
       </c>
       <c r="J112" s="11" t="str">
@@ -12318,11 +12168,11 @@
         <v/>
       </c>
       <c r="K112" s="11" t="str">
-        <f t="shared" ref="K112:L112" si="441">if(not(isblank($B112)), K111, "")</f>
+        <f t="shared" ref="K112:L112" si="440">if(not(isblank($B112)), K111, "")</f>
         <v/>
       </c>
       <c r="L112" s="11" t="str">
-        <f t="shared" si="441"/>
+        <f t="shared" si="440"/>
         <v/>
       </c>
       <c r="M112" s="11" t="str">
@@ -12330,21 +12180,18 @@
         <v/>
       </c>
       <c r="N112" s="11" t="str">
-        <f t="shared" ref="N112:O112" si="442">if(not(isblank($B112)), N111, "")</f>
+        <f t="shared" ref="N112:O112" si="441">if(not(isblank($B112)), N111, "")</f>
         <v/>
       </c>
       <c r="O112" s="11" t="str">
-        <f t="shared" si="442"/>
+        <f t="shared" si="441"/>
         <v/>
       </c>
       <c r="P112" s="11" t="str">
         <f>product_listing!J112</f>
         <v/>
       </c>
-      <c r="Q112" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q112" s="11"/>
       <c r="R112" s="11" t="str">
         <f>product_listing!C112</f>
         <v/>
@@ -12384,11 +12231,11 @@
         <v/>
       </c>
       <c r="E113" s="11" t="str">
-        <f t="shared" ref="E113:F113" si="443">if(not(isblank($B113)), E112, "")</f>
+        <f t="shared" ref="E113:F113" si="442">if(not(isblank($B113)), E112, "")</f>
         <v/>
       </c>
       <c r="F113" s="11" t="str">
-        <f t="shared" si="443"/>
+        <f t="shared" si="442"/>
         <v/>
       </c>
       <c r="G113" s="11" t="str">
@@ -12396,11 +12243,11 @@
         <v/>
       </c>
       <c r="H113" s="11" t="str">
-        <f t="shared" ref="H113:I113" si="444">if(not(isblank($B113)), H112, "")</f>
+        <f t="shared" ref="H113:I113" si="443">if(not(isblank($B113)), H112, "")</f>
         <v/>
       </c>
       <c r="I113" s="11" t="str">
-        <f t="shared" si="444"/>
+        <f t="shared" si="443"/>
         <v/>
       </c>
       <c r="J113" s="11" t="str">
@@ -12408,11 +12255,11 @@
         <v/>
       </c>
       <c r="K113" s="11" t="str">
-        <f t="shared" ref="K113:L113" si="445">if(not(isblank($B113)), K112, "")</f>
+        <f t="shared" ref="K113:L113" si="444">if(not(isblank($B113)), K112, "")</f>
         <v/>
       </c>
       <c r="L113" s="11" t="str">
-        <f t="shared" si="445"/>
+        <f t="shared" si="444"/>
         <v/>
       </c>
       <c r="M113" s="11" t="str">
@@ -12420,21 +12267,18 @@
         <v/>
       </c>
       <c r="N113" s="11" t="str">
-        <f t="shared" ref="N113:O113" si="446">if(not(isblank($B113)), N112, "")</f>
+        <f t="shared" ref="N113:O113" si="445">if(not(isblank($B113)), N112, "")</f>
         <v/>
       </c>
       <c r="O113" s="11" t="str">
-        <f t="shared" si="446"/>
+        <f t="shared" si="445"/>
         <v/>
       </c>
       <c r="P113" s="11" t="str">
         <f>product_listing!J113</f>
         <v/>
       </c>
-      <c r="Q113" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q113" s="11"/>
       <c r="R113" s="11" t="str">
         <f>product_listing!C113</f>
         <v/>
@@ -12474,11 +12318,11 @@
         <v/>
       </c>
       <c r="E114" s="11" t="str">
-        <f t="shared" ref="E114:F114" si="447">if(not(isblank($B114)), E113, "")</f>
+        <f t="shared" ref="E114:F114" si="446">if(not(isblank($B114)), E113, "")</f>
         <v/>
       </c>
       <c r="F114" s="11" t="str">
-        <f t="shared" si="447"/>
+        <f t="shared" si="446"/>
         <v/>
       </c>
       <c r="G114" s="11" t="str">
@@ -12486,11 +12330,11 @@
         <v/>
       </c>
       <c r="H114" s="11" t="str">
-        <f t="shared" ref="H114:I114" si="448">if(not(isblank($B114)), H113, "")</f>
+        <f t="shared" ref="H114:I114" si="447">if(not(isblank($B114)), H113, "")</f>
         <v/>
       </c>
       <c r="I114" s="11" t="str">
-        <f t="shared" si="448"/>
+        <f t="shared" si="447"/>
         <v/>
       </c>
       <c r="J114" s="11" t="str">
@@ -12498,11 +12342,11 @@
         <v/>
       </c>
       <c r="K114" s="11" t="str">
-        <f t="shared" ref="K114:L114" si="449">if(not(isblank($B114)), K113, "")</f>
+        <f t="shared" ref="K114:L114" si="448">if(not(isblank($B114)), K113, "")</f>
         <v/>
       </c>
       <c r="L114" s="11" t="str">
-        <f t="shared" si="449"/>
+        <f t="shared" si="448"/>
         <v/>
       </c>
       <c r="M114" s="11" t="str">
@@ -12510,21 +12354,18 @@
         <v/>
       </c>
       <c r="N114" s="11" t="str">
-        <f t="shared" ref="N114:O114" si="450">if(not(isblank($B114)), N113, "")</f>
+        <f t="shared" ref="N114:O114" si="449">if(not(isblank($B114)), N113, "")</f>
         <v/>
       </c>
       <c r="O114" s="11" t="str">
-        <f t="shared" si="450"/>
+        <f t="shared" si="449"/>
         <v/>
       </c>
       <c r="P114" s="11" t="str">
         <f>product_listing!J114</f>
         <v/>
       </c>
-      <c r="Q114" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q114" s="11"/>
       <c r="R114" s="11" t="str">
         <f>product_listing!C114</f>
         <v/>
@@ -12564,11 +12405,11 @@
         <v/>
       </c>
       <c r="E115" s="11" t="str">
-        <f t="shared" ref="E115:F115" si="451">if(not(isblank($B115)), E114, "")</f>
+        <f t="shared" ref="E115:F115" si="450">if(not(isblank($B115)), E114, "")</f>
         <v/>
       </c>
       <c r="F115" s="11" t="str">
-        <f t="shared" si="451"/>
+        <f t="shared" si="450"/>
         <v/>
       </c>
       <c r="G115" s="11" t="str">
@@ -12576,11 +12417,11 @@
         <v/>
       </c>
       <c r="H115" s="11" t="str">
-        <f t="shared" ref="H115:I115" si="452">if(not(isblank($B115)), H114, "")</f>
+        <f t="shared" ref="H115:I115" si="451">if(not(isblank($B115)), H114, "")</f>
         <v/>
       </c>
       <c r="I115" s="11" t="str">
-        <f t="shared" si="452"/>
+        <f t="shared" si="451"/>
         <v/>
       </c>
       <c r="J115" s="11" t="str">
@@ -12588,11 +12429,11 @@
         <v/>
       </c>
       <c r="K115" s="11" t="str">
-        <f t="shared" ref="K115:L115" si="453">if(not(isblank($B115)), K114, "")</f>
+        <f t="shared" ref="K115:L115" si="452">if(not(isblank($B115)), K114, "")</f>
         <v/>
       </c>
       <c r="L115" s="11" t="str">
-        <f t="shared" si="453"/>
+        <f t="shared" si="452"/>
         <v/>
       </c>
       <c r="M115" s="11" t="str">
@@ -12600,21 +12441,18 @@
         <v/>
       </c>
       <c r="N115" s="11" t="str">
-        <f t="shared" ref="N115:O115" si="454">if(not(isblank($B115)), N114, "")</f>
+        <f t="shared" ref="N115:O115" si="453">if(not(isblank($B115)), N114, "")</f>
         <v/>
       </c>
       <c r="O115" s="11" t="str">
-        <f t="shared" si="454"/>
+        <f t="shared" si="453"/>
         <v/>
       </c>
       <c r="P115" s="11" t="str">
         <f>product_listing!J115</f>
         <v/>
       </c>
-      <c r="Q115" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q115" s="11"/>
       <c r="R115" s="11" t="str">
         <f>product_listing!C115</f>
         <v/>
@@ -12654,11 +12492,11 @@
         <v/>
       </c>
       <c r="E116" s="11" t="str">
-        <f t="shared" ref="E116:F116" si="455">if(not(isblank($B116)), E115, "")</f>
+        <f t="shared" ref="E116:F116" si="454">if(not(isblank($B116)), E115, "")</f>
         <v/>
       </c>
       <c r="F116" s="11" t="str">
-        <f t="shared" si="455"/>
+        <f t="shared" si="454"/>
         <v/>
       </c>
       <c r="G116" s="11" t="str">
@@ -12666,11 +12504,11 @@
         <v/>
       </c>
       <c r="H116" s="11" t="str">
-        <f t="shared" ref="H116:I116" si="456">if(not(isblank($B116)), H115, "")</f>
+        <f t="shared" ref="H116:I116" si="455">if(not(isblank($B116)), H115, "")</f>
         <v/>
       </c>
       <c r="I116" s="11" t="str">
-        <f t="shared" si="456"/>
+        <f t="shared" si="455"/>
         <v/>
       </c>
       <c r="J116" s="11" t="str">
@@ -12678,11 +12516,11 @@
         <v/>
       </c>
       <c r="K116" s="11" t="str">
-        <f t="shared" ref="K116:L116" si="457">if(not(isblank($B116)), K115, "")</f>
+        <f t="shared" ref="K116:L116" si="456">if(not(isblank($B116)), K115, "")</f>
         <v/>
       </c>
       <c r="L116" s="11" t="str">
-        <f t="shared" si="457"/>
+        <f t="shared" si="456"/>
         <v/>
       </c>
       <c r="M116" s="11" t="str">
@@ -12690,21 +12528,18 @@
         <v/>
       </c>
       <c r="N116" s="11" t="str">
-        <f t="shared" ref="N116:O116" si="458">if(not(isblank($B116)), N115, "")</f>
+        <f t="shared" ref="N116:O116" si="457">if(not(isblank($B116)), N115, "")</f>
         <v/>
       </c>
       <c r="O116" s="11" t="str">
-        <f t="shared" si="458"/>
+        <f t="shared" si="457"/>
         <v/>
       </c>
       <c r="P116" s="11" t="str">
         <f>product_listing!J116</f>
         <v/>
       </c>
-      <c r="Q116" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q116" s="11"/>
       <c r="R116" s="11" t="str">
         <f>product_listing!C116</f>
         <v/>
@@ -12744,11 +12579,11 @@
         <v/>
       </c>
       <c r="E117" s="11" t="str">
-        <f t="shared" ref="E117:F117" si="459">if(not(isblank($B117)), E116, "")</f>
+        <f t="shared" ref="E117:F117" si="458">if(not(isblank($B117)), E116, "")</f>
         <v/>
       </c>
       <c r="F117" s="11" t="str">
-        <f t="shared" si="459"/>
+        <f t="shared" si="458"/>
         <v/>
       </c>
       <c r="G117" s="11" t="str">
@@ -12756,11 +12591,11 @@
         <v/>
       </c>
       <c r="H117" s="11" t="str">
-        <f t="shared" ref="H117:I117" si="460">if(not(isblank($B117)), H116, "")</f>
+        <f t="shared" ref="H117:I117" si="459">if(not(isblank($B117)), H116, "")</f>
         <v/>
       </c>
       <c r="I117" s="11" t="str">
-        <f t="shared" si="460"/>
+        <f t="shared" si="459"/>
         <v/>
       </c>
       <c r="J117" s="11" t="str">
@@ -12768,11 +12603,11 @@
         <v/>
       </c>
       <c r="K117" s="11" t="str">
-        <f t="shared" ref="K117:L117" si="461">if(not(isblank($B117)), K116, "")</f>
+        <f t="shared" ref="K117:L117" si="460">if(not(isblank($B117)), K116, "")</f>
         <v/>
       </c>
       <c r="L117" s="11" t="str">
-        <f t="shared" si="461"/>
+        <f t="shared" si="460"/>
         <v/>
       </c>
       <c r="M117" s="11" t="str">
@@ -12780,21 +12615,18 @@
         <v/>
       </c>
       <c r="N117" s="11" t="str">
-        <f t="shared" ref="N117:O117" si="462">if(not(isblank($B117)), N116, "")</f>
+        <f t="shared" ref="N117:O117" si="461">if(not(isblank($B117)), N116, "")</f>
         <v/>
       </c>
       <c r="O117" s="11" t="str">
-        <f t="shared" si="462"/>
+        <f t="shared" si="461"/>
         <v/>
       </c>
       <c r="P117" s="11" t="str">
         <f>product_listing!J117</f>
         <v/>
       </c>
-      <c r="Q117" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q117" s="11"/>
       <c r="R117" s="11" t="str">
         <f>product_listing!C117</f>
         <v/>
@@ -12834,11 +12666,11 @@
         <v/>
       </c>
       <c r="E118" s="11" t="str">
-        <f t="shared" ref="E118:F118" si="463">if(not(isblank($B118)), E117, "")</f>
+        <f t="shared" ref="E118:F118" si="462">if(not(isblank($B118)), E117, "")</f>
         <v/>
       </c>
       <c r="F118" s="11" t="str">
-        <f t="shared" si="463"/>
+        <f t="shared" si="462"/>
         <v/>
       </c>
       <c r="G118" s="11" t="str">
@@ -12846,11 +12678,11 @@
         <v/>
       </c>
       <c r="H118" s="11" t="str">
-        <f t="shared" ref="H118:I118" si="464">if(not(isblank($B118)), H117, "")</f>
+        <f t="shared" ref="H118:I118" si="463">if(not(isblank($B118)), H117, "")</f>
         <v/>
       </c>
       <c r="I118" s="11" t="str">
-        <f t="shared" si="464"/>
+        <f t="shared" si="463"/>
         <v/>
       </c>
       <c r="J118" s="11" t="str">
@@ -12858,11 +12690,11 @@
         <v/>
       </c>
       <c r="K118" s="11" t="str">
-        <f t="shared" ref="K118:L118" si="465">if(not(isblank($B118)), K117, "")</f>
+        <f t="shared" ref="K118:L118" si="464">if(not(isblank($B118)), K117, "")</f>
         <v/>
       </c>
       <c r="L118" s="11" t="str">
-        <f t="shared" si="465"/>
+        <f t="shared" si="464"/>
         <v/>
       </c>
       <c r="M118" s="11" t="str">
@@ -12870,21 +12702,18 @@
         <v/>
       </c>
       <c r="N118" s="11" t="str">
-        <f t="shared" ref="N118:O118" si="466">if(not(isblank($B118)), N117, "")</f>
+        <f t="shared" ref="N118:O118" si="465">if(not(isblank($B118)), N117, "")</f>
         <v/>
       </c>
       <c r="O118" s="11" t="str">
-        <f t="shared" si="466"/>
+        <f t="shared" si="465"/>
         <v/>
       </c>
       <c r="P118" s="11" t="str">
         <f>product_listing!J118</f>
         <v/>
       </c>
-      <c r="Q118" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q118" s="11"/>
       <c r="R118" s="11" t="str">
         <f>product_listing!C118</f>
         <v/>
@@ -12924,11 +12753,11 @@
         <v/>
       </c>
       <c r="E119" s="11" t="str">
-        <f t="shared" ref="E119:F119" si="467">if(not(isblank($B119)), E118, "")</f>
+        <f t="shared" ref="E119:F119" si="466">if(not(isblank($B119)), E118, "")</f>
         <v/>
       </c>
       <c r="F119" s="11" t="str">
-        <f t="shared" si="467"/>
+        <f t="shared" si="466"/>
         <v/>
       </c>
       <c r="G119" s="11" t="str">
@@ -12936,11 +12765,11 @@
         <v/>
       </c>
       <c r="H119" s="11" t="str">
-        <f t="shared" ref="H119:I119" si="468">if(not(isblank($B119)), H118, "")</f>
+        <f t="shared" ref="H119:I119" si="467">if(not(isblank($B119)), H118, "")</f>
         <v/>
       </c>
       <c r="I119" s="11" t="str">
-        <f t="shared" si="468"/>
+        <f t="shared" si="467"/>
         <v/>
       </c>
       <c r="J119" s="11" t="str">
@@ -12948,11 +12777,11 @@
         <v/>
       </c>
       <c r="K119" s="11" t="str">
-        <f t="shared" ref="K119:L119" si="469">if(not(isblank($B119)), K118, "")</f>
+        <f t="shared" ref="K119:L119" si="468">if(not(isblank($B119)), K118, "")</f>
         <v/>
       </c>
       <c r="L119" s="11" t="str">
-        <f t="shared" si="469"/>
+        <f t="shared" si="468"/>
         <v/>
       </c>
       <c r="M119" s="11" t="str">
@@ -12960,21 +12789,18 @@
         <v/>
       </c>
       <c r="N119" s="11" t="str">
-        <f t="shared" ref="N119:O119" si="470">if(not(isblank($B119)), N118, "")</f>
+        <f t="shared" ref="N119:O119" si="469">if(not(isblank($B119)), N118, "")</f>
         <v/>
       </c>
       <c r="O119" s="11" t="str">
-        <f t="shared" si="470"/>
+        <f t="shared" si="469"/>
         <v/>
       </c>
       <c r="P119" s="11" t="str">
         <f>product_listing!J119</f>
         <v/>
       </c>
-      <c r="Q119" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q119" s="11"/>
       <c r="R119" s="11" t="str">
         <f>product_listing!C119</f>
         <v/>
@@ -13014,11 +12840,11 @@
         <v/>
       </c>
       <c r="E120" s="11" t="str">
-        <f t="shared" ref="E120:F120" si="471">if(not(isblank($B120)), E119, "")</f>
+        <f t="shared" ref="E120:F120" si="470">if(not(isblank($B120)), E119, "")</f>
         <v/>
       </c>
       <c r="F120" s="11" t="str">
-        <f t="shared" si="471"/>
+        <f t="shared" si="470"/>
         <v/>
       </c>
       <c r="G120" s="11" t="str">
@@ -13026,11 +12852,11 @@
         <v/>
       </c>
       <c r="H120" s="11" t="str">
-        <f t="shared" ref="H120:I120" si="472">if(not(isblank($B120)), H119, "")</f>
+        <f t="shared" ref="H120:I120" si="471">if(not(isblank($B120)), H119, "")</f>
         <v/>
       </c>
       <c r="I120" s="11" t="str">
-        <f t="shared" si="472"/>
+        <f t="shared" si="471"/>
         <v/>
       </c>
       <c r="J120" s="11" t="str">
@@ -13038,11 +12864,11 @@
         <v/>
       </c>
       <c r="K120" s="11" t="str">
-        <f t="shared" ref="K120:L120" si="473">if(not(isblank($B120)), K119, "")</f>
+        <f t="shared" ref="K120:L120" si="472">if(not(isblank($B120)), K119, "")</f>
         <v/>
       </c>
       <c r="L120" s="11" t="str">
-        <f t="shared" si="473"/>
+        <f t="shared" si="472"/>
         <v/>
       </c>
       <c r="M120" s="11" t="str">
@@ -13050,21 +12876,18 @@
         <v/>
       </c>
       <c r="N120" s="11" t="str">
-        <f t="shared" ref="N120:O120" si="474">if(not(isblank($B120)), N119, "")</f>
+        <f t="shared" ref="N120:O120" si="473">if(not(isblank($B120)), N119, "")</f>
         <v/>
       </c>
       <c r="O120" s="11" t="str">
-        <f t="shared" si="474"/>
+        <f t="shared" si="473"/>
         <v/>
       </c>
       <c r="P120" s="11" t="str">
         <f>product_listing!J120</f>
         <v/>
       </c>
-      <c r="Q120" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q120" s="11"/>
       <c r="R120" s="11" t="str">
         <f>product_listing!C120</f>
         <v/>
@@ -13104,11 +12927,11 @@
         <v/>
       </c>
       <c r="E121" s="11" t="str">
-        <f t="shared" ref="E121:F121" si="475">if(not(isblank($B121)), E120, "")</f>
+        <f t="shared" ref="E121:F121" si="474">if(not(isblank($B121)), E120, "")</f>
         <v/>
       </c>
       <c r="F121" s="11" t="str">
-        <f t="shared" si="475"/>
+        <f t="shared" si="474"/>
         <v/>
       </c>
       <c r="G121" s="11" t="str">
@@ -13116,11 +12939,11 @@
         <v/>
       </c>
       <c r="H121" s="11" t="str">
-        <f t="shared" ref="H121:I121" si="476">if(not(isblank($B121)), H120, "")</f>
+        <f t="shared" ref="H121:I121" si="475">if(not(isblank($B121)), H120, "")</f>
         <v/>
       </c>
       <c r="I121" s="11" t="str">
-        <f t="shared" si="476"/>
+        <f t="shared" si="475"/>
         <v/>
       </c>
       <c r="J121" s="11" t="str">
@@ -13128,11 +12951,11 @@
         <v/>
       </c>
       <c r="K121" s="11" t="str">
-        <f t="shared" ref="K121:L121" si="477">if(not(isblank($B121)), K120, "")</f>
+        <f t="shared" ref="K121:L121" si="476">if(not(isblank($B121)), K120, "")</f>
         <v/>
       </c>
       <c r="L121" s="11" t="str">
-        <f t="shared" si="477"/>
+        <f t="shared" si="476"/>
         <v/>
       </c>
       <c r="M121" s="11" t="str">
@@ -13140,21 +12963,18 @@
         <v/>
       </c>
       <c r="N121" s="11" t="str">
-        <f t="shared" ref="N121:O121" si="478">if(not(isblank($B121)), N120, "")</f>
+        <f t="shared" ref="N121:O121" si="477">if(not(isblank($B121)), N120, "")</f>
         <v/>
       </c>
       <c r="O121" s="11" t="str">
-        <f t="shared" si="478"/>
+        <f t="shared" si="477"/>
         <v/>
       </c>
       <c r="P121" s="11" t="str">
         <f>product_listing!J121</f>
         <v/>
       </c>
-      <c r="Q121" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q121" s="11"/>
       <c r="R121" s="11" t="str">
         <f>product_listing!C121</f>
         <v/>
@@ -13194,11 +13014,11 @@
         <v/>
       </c>
       <c r="E122" s="11" t="str">
-        <f t="shared" ref="E122:F122" si="479">if(not(isblank($B122)), E121, "")</f>
+        <f t="shared" ref="E122:F122" si="478">if(not(isblank($B122)), E121, "")</f>
         <v/>
       </c>
       <c r="F122" s="11" t="str">
-        <f t="shared" si="479"/>
+        <f t="shared" si="478"/>
         <v/>
       </c>
       <c r="G122" s="11" t="str">
@@ -13206,11 +13026,11 @@
         <v/>
       </c>
       <c r="H122" s="11" t="str">
-        <f t="shared" ref="H122:I122" si="480">if(not(isblank($B122)), H121, "")</f>
+        <f t="shared" ref="H122:I122" si="479">if(not(isblank($B122)), H121, "")</f>
         <v/>
       </c>
       <c r="I122" s="11" t="str">
-        <f t="shared" si="480"/>
+        <f t="shared" si="479"/>
         <v/>
       </c>
       <c r="J122" s="11" t="str">
@@ -13218,11 +13038,11 @@
         <v/>
       </c>
       <c r="K122" s="11" t="str">
-        <f t="shared" ref="K122:L122" si="481">if(not(isblank($B122)), K121, "")</f>
+        <f t="shared" ref="K122:L122" si="480">if(not(isblank($B122)), K121, "")</f>
         <v/>
       </c>
       <c r="L122" s="11" t="str">
-        <f t="shared" si="481"/>
+        <f t="shared" si="480"/>
         <v/>
       </c>
       <c r="M122" s="11" t="str">
@@ -13230,21 +13050,18 @@
         <v/>
       </c>
       <c r="N122" s="11" t="str">
-        <f t="shared" ref="N122:O122" si="482">if(not(isblank($B122)), N121, "")</f>
+        <f t="shared" ref="N122:O122" si="481">if(not(isblank($B122)), N121, "")</f>
         <v/>
       </c>
       <c r="O122" s="11" t="str">
-        <f t="shared" si="482"/>
+        <f t="shared" si="481"/>
         <v/>
       </c>
       <c r="P122" s="11" t="str">
         <f>product_listing!J122</f>
         <v/>
       </c>
-      <c r="Q122" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q122" s="11"/>
       <c r="R122" s="11" t="str">
         <f>product_listing!C122</f>
         <v/>
@@ -13284,11 +13101,11 @@
         <v/>
       </c>
       <c r="E123" s="11" t="str">
-        <f t="shared" ref="E123:F123" si="483">if(not(isblank($B123)), E122, "")</f>
+        <f t="shared" ref="E123:F123" si="482">if(not(isblank($B123)), E122, "")</f>
         <v/>
       </c>
       <c r="F123" s="11" t="str">
-        <f t="shared" si="483"/>
+        <f t="shared" si="482"/>
         <v/>
       </c>
       <c r="G123" s="11" t="str">
@@ -13296,11 +13113,11 @@
         <v/>
       </c>
       <c r="H123" s="11" t="str">
-        <f t="shared" ref="H123:I123" si="484">if(not(isblank($B123)), H122, "")</f>
+        <f t="shared" ref="H123:I123" si="483">if(not(isblank($B123)), H122, "")</f>
         <v/>
       </c>
       <c r="I123" s="11" t="str">
-        <f t="shared" si="484"/>
+        <f t="shared" si="483"/>
         <v/>
       </c>
       <c r="J123" s="11" t="str">
@@ -13308,11 +13125,11 @@
         <v/>
       </c>
       <c r="K123" s="11" t="str">
-        <f t="shared" ref="K123:L123" si="485">if(not(isblank($B123)), K122, "")</f>
+        <f t="shared" ref="K123:L123" si="484">if(not(isblank($B123)), K122, "")</f>
         <v/>
       </c>
       <c r="L123" s="11" t="str">
-        <f t="shared" si="485"/>
+        <f t="shared" si="484"/>
         <v/>
       </c>
       <c r="M123" s="11" t="str">
@@ -13320,21 +13137,18 @@
         <v/>
       </c>
       <c r="N123" s="11" t="str">
-        <f t="shared" ref="N123:O123" si="486">if(not(isblank($B123)), N122, "")</f>
+        <f t="shared" ref="N123:O123" si="485">if(not(isblank($B123)), N122, "")</f>
         <v/>
       </c>
       <c r="O123" s="11" t="str">
-        <f t="shared" si="486"/>
+        <f t="shared" si="485"/>
         <v/>
       </c>
       <c r="P123" s="11" t="str">
         <f>product_listing!J123</f>
         <v/>
       </c>
-      <c r="Q123" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q123" s="11"/>
       <c r="R123" s="11" t="str">
         <f>product_listing!C123</f>
         <v/>
@@ -13374,11 +13188,11 @@
         <v/>
       </c>
       <c r="E124" s="11" t="str">
-        <f t="shared" ref="E124:F124" si="487">if(not(isblank($B124)), E123, "")</f>
+        <f t="shared" ref="E124:F124" si="486">if(not(isblank($B124)), E123, "")</f>
         <v/>
       </c>
       <c r="F124" s="11" t="str">
-        <f t="shared" si="487"/>
+        <f t="shared" si="486"/>
         <v/>
       </c>
       <c r="G124" s="11" t="str">
@@ -13386,11 +13200,11 @@
         <v/>
       </c>
       <c r="H124" s="11" t="str">
-        <f t="shared" ref="H124:I124" si="488">if(not(isblank($B124)), H123, "")</f>
+        <f t="shared" ref="H124:I124" si="487">if(not(isblank($B124)), H123, "")</f>
         <v/>
       </c>
       <c r="I124" s="11" t="str">
-        <f t="shared" si="488"/>
+        <f t="shared" si="487"/>
         <v/>
       </c>
       <c r="J124" s="11" t="str">
@@ -13398,11 +13212,11 @@
         <v/>
       </c>
       <c r="K124" s="11" t="str">
-        <f t="shared" ref="K124:L124" si="489">if(not(isblank($B124)), K123, "")</f>
+        <f t="shared" ref="K124:L124" si="488">if(not(isblank($B124)), K123, "")</f>
         <v/>
       </c>
       <c r="L124" s="11" t="str">
-        <f t="shared" si="489"/>
+        <f t="shared" si="488"/>
         <v/>
       </c>
       <c r="M124" s="11" t="str">
@@ -13410,21 +13224,18 @@
         <v/>
       </c>
       <c r="N124" s="11" t="str">
-        <f t="shared" ref="N124:O124" si="490">if(not(isblank($B124)), N123, "")</f>
+        <f t="shared" ref="N124:O124" si="489">if(not(isblank($B124)), N123, "")</f>
         <v/>
       </c>
       <c r="O124" s="11" t="str">
-        <f t="shared" si="490"/>
+        <f t="shared" si="489"/>
         <v/>
       </c>
       <c r="P124" s="11" t="str">
         <f>product_listing!J124</f>
         <v/>
       </c>
-      <c r="Q124" s="11" t="str">
-        <f t="shared" si="242"/>
-        <v>#REF!</v>
-      </c>
+      <c r="Q124" s="11"/>
       <c r="R124" s="11" t="str">
         <f>product_listing!C124</f>
         <v/>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="101">
   <si>
     <t>Data category</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>Adjustments are applied by comparing data in the deep ocean (&gt;2000 m) using a crossover and inversion method as described by Johnson et al. (2001).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Global Ocean Data Analysis Project Version 2 (GLODAPv2) aggregates biogeochemical data collected from discrete bottle samples, offering extensive global coverage from the surface to depths (Key et al., 2015; Olsen et al., 2016; Lauvset et al., 2024). While GLODAP is primarily a product for basin-scale hydrographic data, it also includes coastal datasets and observations from a few time-series. The GLODAPv2 data product provides rigorously quality-controlled measurements for 14 essential oceanographic variables: temperature, salinity, dissolved oxygen (DO), nitrate, silicate, phosphate, DIC, TA, pH, chlorofluorocarbons (CFC-11, CFC-12, CFC-113), carbon tetrachloride (CCl4), and sulfur hexafluoride (SF6). These variables, excluding temperature, undergo both primary and secondary quality control procedures to detect outliers and adjust for significant measurement biases. GLODAPv2 was first published in 2016 and was updated annually through a living data process in Earth System Science Data from 2019 through “v2023,” which was published in 2024. For these updates, new data (including historical data not previously included in the data product) are quality controlled and adjusted to the 2016 version (Olsen et al., 2019; Olsen et al., 2020; Lauvset et al., 2021; Lauvset et al., 2022; Lauvset et al., 2024). Since the global repeat hydrography programs operate with decadal repetitions, the aim is to produce a completely new version of GLODAP, where all cruise datasets will be reevaluated, every decade. Release of the GLODAPv3 data product is planned for 2026, and is expected to evolve the secondary data quality control practices relative to those used in GLODAPv2. For more information on the secondary quality control process, refer to Tanhua et al. (2010) and Lauvset and Tanhua (2015). GLODAPv2 offers two kind of products: the collection of quality controlled data from discrete bottle samples taken at sampling location (Key et al., 2015; Olsen et al., 2016; Olsen et al., 2019; Olsen et al., 2020; Lauvset et al., 2021; Lauvset et al., 2022; Lauvset et al., 2024), and a gridded product, interpolated to a 1° × 1°  grid and the 33 standard depth levels of World Ocean Atlas (WOA) (Lauvset et al., 2016). </t>
   </si>
   <si>
     <t>Data categories</t>
@@ -974,6 +977,9 @@
       <c r="L7" s="8" t="s">
         <v>66</v>
       </c>
+      <c r="M7" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5"/>
@@ -2193,7 +2199,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>8</v>
@@ -2210,7 +2216,7 @@
         <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>65</v>
@@ -2221,16 +2227,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
@@ -2238,18 +2244,18 @@
         <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>29</v>
@@ -2257,10 +2263,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>20</v>
@@ -2268,25 +2274,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="D8" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
       <c r="D9" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
       <c r="D10" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2325,70 +2331,70 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F1" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="I1" s="11" t="s">
+      <c r="J1" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="K1" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="K1" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="L1" s="11" t="s">
+      <c r="M1" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="N1" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="O1" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="N1" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>88</v>
-      </c>
       <c r="P1" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="U1" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="V1" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
@@ -2409,7 +2415,7 @@
         <v>https://essd.copernicus.org/articles/13/777/2021/essd-13-777-2021-avatar-web.png</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>8</v>
@@ -2419,7 +2425,7 @@
         <v>Open Ocean, Surface</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>7</v>
@@ -2429,7 +2435,7 @@
         <v>monthly</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L2" s="11" t="s">
         <v>6</v>
@@ -2439,7 +2445,7 @@
         <v>1.0°</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>9</v>
@@ -2468,7 +2474,7 @@
         <v>12</v>
       </c>
       <c r="V2" s="15" t="str">
-        <f>product_listing!L2</f>
+        <f>product_listing!M2</f>
         <v/>
       </c>
     </row>
@@ -2558,7 +2564,7 @@
         <v>Description</v>
       </c>
       <c r="V3" s="15" t="str">
-        <f>product_listing!L3</f>
+        <f>product_listing!M3</f>
         <v/>
       </c>
     </row>
@@ -2648,8 +2654,8 @@
         <v>Description</v>
       </c>
       <c r="V4" s="15" t="str">
-        <f>product_listing!L4</f>
-        <v>else</v>
+        <f>product_listing!M4</f>
+        <v>something</v>
       </c>
     </row>
     <row r="5">
@@ -2738,8 +2744,8 @@
         <v>Description</v>
       </c>
       <c r="V5" s="15" t="str">
-        <f>product_listing!L5</f>
-        <v/>
+        <f>product_listing!M5</f>
+        <v>Self Organising Map – Feed-Forward Neural Network</v>
       </c>
     </row>
     <row r="6">
@@ -2918,8 +2924,8 @@
         <v>Description</v>
       </c>
       <c r="V7" s="15" t="str">
-        <f>product_listing!L7</f>
-        <v>Adjustments are applied by comparing data in the deep ocean (&gt;2000 m) using a crossover and inversion method as described by Johnson et al. (2001).</v>
+        <f>product_listing!M7</f>
+        <v>The Global Ocean Data Analysis Project Version 2 (GLODAPv2) aggregates biogeochemical data collected from discrete bottle samples, offering extensive global coverage from the surface to depths (Key et al., 2015; Olsen et al., 2016; Lauvset et al., 2024). While GLODAP is primarily a product for basin-scale hydrographic data, it also includes coastal datasets and observations from a few time-series. The GLODAPv2 data product provides rigorously quality-controlled measurements for 14 essential oceanographic variables: temperature, salinity, dissolved oxygen (DO), nitrate, silicate, phosphate, DIC, TA, pH, chlorofluorocarbons (CFC-11, CFC-12, CFC-113), carbon tetrachloride (CCl4), and sulfur hexafluoride (SF6). These variables, excluding temperature, undergo both primary and secondary quality control procedures to detect outliers and adjust for significant measurement biases. GLODAPv2 was first published in 2016 and was updated annually through a living data process in Earth System Science Data from 2019 through “v2023,” which was published in 2024. For these updates, new data (including historical data not previously included in the data product) are quality controlled and adjusted to the 2016 version (Olsen et al., 2019; Olsen et al., 2020; Lauvset et al., 2021; Lauvset et al., 2022; Lauvset et al., 2024). Since the global repeat hydrography programs operate with decadal repetitions, the aim is to produce a completely new version of GLODAP, where all cruise datasets will be reevaluated, every decade. Release of the GLODAPv3 data product is planned for 2026, and is expected to evolve the secondary data quality control practices relative to those used in GLODAPv2. For more information on the secondary quality control process, refer to Tanhua et al. (2010) and Lauvset and Tanhua (2015). GLODAPv2 offers two kind of products: the collection of quality controlled data from discrete bottle samples taken at sampling location (Key et al., 2015; Olsen et al., 2016; Olsen et al., 2019; Olsen et al., 2020; Lauvset et al., 2021; Lauvset et al., 2022; Lauvset et al., 2024), and a gridded product, interpolated to a 1° × 1°  grid and the 33 standard depth levels of World Ocean Atlas (WOA) (Lauvset et al., 2016). </v>
       </c>
     </row>
     <row r="8">

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -3470,8 +3470,8 @@
     </row>
     <row r="14">
       <c r="A14" s="11" t="str">
-        <f>product_listing!A14</f>
-        <v/>
+        <f t="array" ref="A14">INDIRECT(CONCAT("product_listing!","A5"))</f>
+        <v>Surface data-derived</v>
       </c>
       <c r="B14" s="11" t="str">
         <f>product_listing!B14</f>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -2399,7 +2399,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="str">
-        <f>product_listing!A2</f>
+        <f t="shared" ref="A2:A7" si="5">INDIRECT(CONCAT("product_listing!A",row()))</f>
         <v>Observations</v>
       </c>
       <c r="B2" s="11" t="str">
@@ -2489,7 +2489,7 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="str">
-        <f>product_listing!A3</f>
+        <f t="shared" si="5"/>
         <v>Observations</v>
       </c>
       <c r="B3" s="11" t="str">
@@ -2505,11 +2505,11 @@
         <v>https://glodap.info/wp-content/uploads/2017/09/cropped-glodap_logo_trans.png</v>
       </c>
       <c r="E3" s="11" t="str">
-        <f t="shared" ref="E3:F3" si="5">if(not(isblank($B3)), E2, "")</f>
+        <f t="shared" ref="E3:F3" si="6">if(not(isblank($B3)), E2, "")</f>
         <v>fa-solid fa-globe</v>
       </c>
       <c r="F3" s="11" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Spatial domains</v>
       </c>
       <c r="G3" s="11" t="str">
@@ -2517,11 +2517,11 @@
         <v>Water column, Open Ocean</v>
       </c>
       <c r="H3" s="11" t="str">
-        <f t="shared" ref="H3:I3" si="6">if(not(isblank($B3)), H2, "")</f>
+        <f t="shared" ref="H3:I3" si="7">if(not(isblank($B3)), H2, "")</f>
         <v>fa-solid fa-hourglass-start</v>
       </c>
       <c r="I3" s="11" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Temporal resolution</v>
       </c>
       <c r="J3" s="11" t="str">
@@ -2529,11 +2529,11 @@
         <v/>
       </c>
       <c r="K3" s="11" t="str">
-        <f t="shared" ref="K3:L3" si="7">if(not(isblank($B3)), K2, "")</f>
+        <f t="shared" ref="K3:L3" si="8">if(not(isblank($B3)), K2, "")</f>
         <v>fa-solid fa-ruler-horizontal</v>
       </c>
       <c r="L3" s="11" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Spatial resolution</v>
       </c>
       <c r="M3" s="11" t="str">
@@ -2541,11 +2541,11 @@
         <v/>
       </c>
       <c r="N3" s="11" t="str">
-        <f t="shared" ref="N3:O3" si="8">if(not(isblank($B3)), N2, "")</f>
+        <f t="shared" ref="N3:O3" si="9">if(not(isblank($B3)), N2, "")</f>
         <v>fa-solid fa-calendar-days</v>
       </c>
       <c r="O3" s="11" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Period</v>
       </c>
       <c r="P3" s="11" t="str">
@@ -2579,7 +2579,7 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="str">
-        <f>product_listing!A4</f>
+        <f t="shared" si="5"/>
         <v>Surface data-derived</v>
       </c>
       <c r="B4" s="11" t="str">
@@ -2660,7 +2660,7 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="str">
-        <f>product_listing!A5</f>
+        <f t="shared" si="5"/>
         <v>Surface data-derived</v>
       </c>
       <c r="B5" s="11" t="str">
@@ -2676,11 +2676,11 @@
         <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/7decc330-7468-429c-bae9-ac51b085be30/gbc21584-fig-0007-m.jpg</v>
       </c>
       <c r="E5" s="11" t="str">
-        <f t="shared" ref="E5:F5" si="9">if(not(isblank($B5)), E4, "")</f>
+        <f t="shared" ref="E5:F5" si="10">if(not(isblank($B5)), E4, "")</f>
         <v>fa-solid fa-globe</v>
       </c>
       <c r="F5" s="11" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Spatial domains</v>
       </c>
       <c r="G5" s="11" t="str">
@@ -2688,11 +2688,11 @@
         <v>Open Ocean, Surface</v>
       </c>
       <c r="H5" s="11" t="str">
-        <f t="shared" ref="H5:I5" si="10">if(not(isblank($B5)), H4, "")</f>
+        <f t="shared" ref="H5:I5" si="11">if(not(isblank($B5)), H4, "")</f>
         <v>fa-solid fa-hourglass-start</v>
       </c>
       <c r="I5" s="11" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Temporal resolution</v>
       </c>
       <c r="J5" s="11" t="str">
@@ -2700,11 +2700,11 @@
         <v>8-daily</v>
       </c>
       <c r="K5" s="11" t="str">
-        <f t="shared" ref="K5:L5" si="11">if(not(isblank($B5)), K4, "")</f>
+        <f t="shared" ref="K5:L5" si="12">if(not(isblank($B5)), K4, "")</f>
         <v>fa-solid fa-ruler-horizontal</v>
       </c>
       <c r="L5" s="11" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Spatial resolution</v>
       </c>
       <c r="M5" s="16" t="str">
@@ -2712,11 +2712,11 @@
         <v>0.25°</v>
       </c>
       <c r="N5" s="11" t="str">
-        <f t="shared" ref="N5:O5" si="12">if(not(isblank($B5)), N4, "")</f>
+        <f t="shared" ref="N5:O5" si="13">if(not(isblank($B5)), N4, "")</f>
         <v>fa-solid fa-calendar-days</v>
       </c>
       <c r="O5" s="11" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>Period</v>
       </c>
       <c r="P5" s="11" t="str">
@@ -2740,7 +2740,7 @@
         <v>https://zenodo.org/records/11206366</v>
       </c>
       <c r="U5" s="11" t="str">
-        <f t="shared" ref="U5:U7" si="17">if(not(isblank($B5)), U4, "")</f>
+        <f t="shared" ref="U5:U7" si="18">if(not(isblank($B5)), U4, "")</f>
         <v>Description</v>
       </c>
       <c r="V5" s="14" t="str">
@@ -2750,7 +2750,7 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="str">
-        <f>product_listing!A6</f>
+        <f t="shared" si="5"/>
         <v>Surface data-derived</v>
       </c>
       <c r="B6" s="11" t="str">
@@ -2766,11 +2766,11 @@
         <v>https://essd.copernicus.org/articles/16/2123/2024/essd-16-2123-2024-avatar-web.png</v>
       </c>
       <c r="E6" s="11" t="str">
-        <f t="shared" ref="E6:F6" si="13">if(not(isblank($B6)), E5, "")</f>
+        <f t="shared" ref="E6:F6" si="14">if(not(isblank($B6)), E5, "")</f>
         <v>fa-solid fa-globe</v>
       </c>
       <c r="F6" s="11" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Spatial domains</v>
       </c>
       <c r="G6" s="11" t="str">
@@ -2778,11 +2778,11 @@
         <v>Open Ocean, Surface</v>
       </c>
       <c r="H6" s="11" t="str">
-        <f t="shared" ref="H6:I6" si="14">if(not(isblank($B6)), H5, "")</f>
+        <f t="shared" ref="H6:I6" si="15">if(not(isblank($B6)), H5, "")</f>
         <v>fa-solid fa-hourglass-start</v>
       </c>
       <c r="I6" s="11" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Temporal resolution</v>
       </c>
       <c r="J6" s="11" t="str">
@@ -2790,11 +2790,11 @@
         <v>climatology, monthly</v>
       </c>
       <c r="K6" s="11" t="str">
-        <f t="shared" ref="K6:L6" si="15">if(not(isblank($B6)), K5, "")</f>
+        <f t="shared" ref="K6:L6" si="16">if(not(isblank($B6)), K5, "")</f>
         <v>fa-solid fa-ruler-horizontal</v>
       </c>
       <c r="L6" s="11" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Spatial resolution</v>
       </c>
       <c r="M6" s="15" t="str">
@@ -2802,11 +2802,11 @@
         <v>1.0°</v>
       </c>
       <c r="N6" s="11" t="str">
-        <f t="shared" ref="N6:O6" si="16">if(not(isblank($B6)), N5, "")</f>
+        <f t="shared" ref="N6:O6" si="17">if(not(isblank($B6)), N5, "")</f>
         <v>fa-solid fa-calendar-days</v>
       </c>
       <c r="O6" s="11" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>Period</v>
       </c>
       <c r="P6" s="11" t="str">
@@ -2830,7 +2830,7 @@
         <v>https://doi.org/10.25921/295g-sn13</v>
       </c>
       <c r="U6" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>Description</v>
       </c>
       <c r="V6" s="14" t="str">
@@ -2840,7 +2840,7 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="str">
-        <f>product_listing!A7</f>
+        <f t="shared" si="5"/>
         <v>Surface data-derived</v>
       </c>
       <c r="B7" s="11" t="str">
@@ -2856,11 +2856,11 @@
         <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/547d18a7-69b5-4e93-96b2-5e8371310b43/gbc20188-fig-0001-m.jpg</v>
       </c>
       <c r="E7" s="11" t="str">
-        <f t="shared" ref="E7:F7" si="18">if(not(isblank($B7)), E6, "")</f>
+        <f t="shared" ref="E7:F7" si="19">if(not(isblank($B7)), E6, "")</f>
         <v>fa-solid fa-globe</v>
       </c>
       <c r="F7" s="11" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>Spatial domains</v>
       </c>
       <c r="G7" s="11" t="str">
@@ -2868,11 +2868,11 @@
         <v>Surface, Open Ocean</v>
       </c>
       <c r="H7" s="11" t="str">
-        <f t="shared" ref="H7:I7" si="19">if(not(isblank($B7)), H6, "")</f>
+        <f t="shared" ref="H7:I7" si="20">if(not(isblank($B7)), H6, "")</f>
         <v>fa-solid fa-hourglass-start</v>
       </c>
       <c r="I7" s="11" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>Temporal resolution</v>
       </c>
       <c r="J7" s="11" t="str">
@@ -2880,11 +2880,11 @@
         <v>monthly</v>
       </c>
       <c r="K7" s="11" t="str">
-        <f t="shared" ref="K7:L7" si="20">if(not(isblank($B7)), K6, "")</f>
+        <f t="shared" ref="K7:L7" si="21">if(not(isblank($B7)), K6, "")</f>
         <v>fa-solid fa-ruler-horizontal</v>
       </c>
       <c r="L7" s="11" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>Spatial resolution</v>
       </c>
       <c r="M7" s="15" t="str">
@@ -2892,11 +2892,11 @@
         <v>1.0°</v>
       </c>
       <c r="N7" s="11" t="str">
-        <f t="shared" ref="N7:O7" si="21">if(not(isblank($B7)), N6, "")</f>
+        <f t="shared" ref="N7:O7" si="22">if(not(isblank($B7)), N6, "")</f>
         <v>fa-solid fa-calendar-days</v>
       </c>
       <c r="O7" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>Period</v>
       </c>
       <c r="P7" s="11" t="str">
@@ -2920,7 +2920,7 @@
         <v>https://doi.org/10.7289/v5z899n6</v>
       </c>
       <c r="U7" s="11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>Description</v>
       </c>
       <c r="V7" s="14" t="str">
@@ -2946,11 +2946,11 @@
         <v/>
       </c>
       <c r="E8" s="11" t="str">
-        <f t="shared" ref="E8:F8" si="22">if(not(isblank($B8)), E3, "")</f>
+        <f t="shared" ref="E8:F8" si="23">if(not(isblank($B8)), E3, "")</f>
         <v/>
       </c>
       <c r="F8" s="11" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="G8" s="11" t="str">
@@ -2958,11 +2958,11 @@
         <v/>
       </c>
       <c r="H8" s="11" t="str">
-        <f t="shared" ref="H8:I8" si="23">if(not(isblank($B8)), H3, "")</f>
+        <f t="shared" ref="H8:I8" si="24">if(not(isblank($B8)), H3, "")</f>
         <v/>
       </c>
       <c r="I8" s="11" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="J8" s="11" t="str">
@@ -2970,11 +2970,11 @@
         <v/>
       </c>
       <c r="K8" s="11" t="str">
-        <f t="shared" ref="K8:L8" si="24">if(not(isblank($B8)), K3, "")</f>
+        <f t="shared" ref="K8:L8" si="25">if(not(isblank($B8)), K3, "")</f>
         <v/>
       </c>
       <c r="L8" s="11" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M8" s="11" t="str">
@@ -2982,11 +2982,11 @@
         <v/>
       </c>
       <c r="N8" s="11" t="str">
-        <f t="shared" ref="N8:O8" si="25">if(not(isblank($B8)), N3, "")</f>
+        <f t="shared" ref="N8:O8" si="26">if(not(isblank($B8)), N3, "")</f>
         <v/>
       </c>
       <c r="O8" s="11" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P8" s="11" t="str">
@@ -3036,11 +3036,11 @@
         <v/>
       </c>
       <c r="E9" s="11" t="str">
-        <f t="shared" ref="E9:F9" si="26">if(not(isblank($B9)), E8, "")</f>
+        <f t="shared" ref="E9:F9" si="27">if(not(isblank($B9)), E8, "")</f>
         <v/>
       </c>
       <c r="F9" s="11" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="G9" s="11" t="str">
@@ -3048,11 +3048,11 @@
         <v/>
       </c>
       <c r="H9" s="11" t="str">
-        <f t="shared" ref="H9:I9" si="27">if(not(isblank($B9)), H8, "")</f>
+        <f t="shared" ref="H9:I9" si="28">if(not(isblank($B9)), H8, "")</f>
         <v/>
       </c>
       <c r="I9" s="11" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="J9" s="11" t="str">
@@ -3060,11 +3060,11 @@
         <v/>
       </c>
       <c r="K9" s="11" t="str">
-        <f t="shared" ref="K9:L9" si="28">if(not(isblank($B9)), K8, "")</f>
+        <f t="shared" ref="K9:L9" si="29">if(not(isblank($B9)), K8, "")</f>
         <v/>
       </c>
       <c r="L9" s="11" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="M9" s="11" t="str">
@@ -3072,11 +3072,11 @@
         <v/>
       </c>
       <c r="N9" s="11" t="str">
-        <f t="shared" ref="N9:O9" si="29">if(not(isblank($B9)), N8, "")</f>
+        <f t="shared" ref="N9:O9" si="30">if(not(isblank($B9)), N8, "")</f>
         <v/>
       </c>
       <c r="O9" s="11" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="P9" s="11" t="str">
@@ -3100,7 +3100,7 @@
         <v/>
       </c>
       <c r="U9" s="11" t="str">
-        <f t="shared" ref="U9:U124" si="34">if(not(isblank($B9)), U8, "")</f>
+        <f t="shared" ref="U9:U124" si="35">if(not(isblank($B9)), U8, "")</f>
         <v/>
       </c>
       <c r="V9" s="14" t="str">
@@ -3126,11 +3126,11 @@
         <v/>
       </c>
       <c r="E10" s="11" t="str">
-        <f t="shared" ref="E10:F10" si="30">if(not(isblank($B10)), E9, "")</f>
+        <f t="shared" ref="E10:F10" si="31">if(not(isblank($B10)), E9, "")</f>
         <v/>
       </c>
       <c r="F10" s="11" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="G10" s="11" t="str">
@@ -3138,11 +3138,11 @@
         <v/>
       </c>
       <c r="H10" s="11" t="str">
-        <f t="shared" ref="H10:I10" si="31">if(not(isblank($B10)), H9, "")</f>
+        <f t="shared" ref="H10:I10" si="32">if(not(isblank($B10)), H9, "")</f>
         <v/>
       </c>
       <c r="I10" s="11" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="J10" s="11" t="str">
@@ -3150,11 +3150,11 @@
         <v/>
       </c>
       <c r="K10" s="11" t="str">
-        <f t="shared" ref="K10:L10" si="32">if(not(isblank($B10)), K9, "")</f>
+        <f t="shared" ref="K10:L10" si="33">if(not(isblank($B10)), K9, "")</f>
         <v/>
       </c>
       <c r="L10" s="11" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M10" s="11" t="str">
@@ -3162,11 +3162,11 @@
         <v/>
       </c>
       <c r="N10" s="11" t="str">
-        <f t="shared" ref="N10:O10" si="33">if(not(isblank($B10)), N9, "")</f>
+        <f t="shared" ref="N10:O10" si="34">if(not(isblank($B10)), N9, "")</f>
         <v/>
       </c>
       <c r="O10" s="11" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="P10" s="11" t="str">
@@ -3190,7 +3190,7 @@
         <v/>
       </c>
       <c r="U10" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V10" s="14" t="str">
@@ -3216,11 +3216,11 @@
         <v/>
       </c>
       <c r="E11" s="11" t="str">
-        <f t="shared" ref="E11:F11" si="35">if(not(isblank($B11)), E10, "")</f>
+        <f t="shared" ref="E11:F11" si="36">if(not(isblank($B11)), E10, "")</f>
         <v/>
       </c>
       <c r="F11" s="11" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="G11" s="11" t="str">
@@ -3228,11 +3228,11 @@
         <v/>
       </c>
       <c r="H11" s="11" t="str">
-        <f t="shared" ref="H11:I11" si="36">if(not(isblank($B11)), H10, "")</f>
+        <f t="shared" ref="H11:I11" si="37">if(not(isblank($B11)), H10, "")</f>
         <v/>
       </c>
       <c r="I11" s="11" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="J11" s="11" t="str">
@@ -3240,11 +3240,11 @@
         <v/>
       </c>
       <c r="K11" s="11" t="str">
-        <f t="shared" ref="K11:L11" si="37">if(not(isblank($B11)), K10, "")</f>
+        <f t="shared" ref="K11:L11" si="38">if(not(isblank($B11)), K10, "")</f>
         <v/>
       </c>
       <c r="L11" s="11" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="M11" s="11" t="str">
@@ -3252,11 +3252,11 @@
         <v/>
       </c>
       <c r="N11" s="11" t="str">
-        <f t="shared" ref="N11:O11" si="38">if(not(isblank($B11)), N10, "")</f>
+        <f t="shared" ref="N11:O11" si="39">if(not(isblank($B11)), N10, "")</f>
         <v/>
       </c>
       <c r="O11" s="11" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P11" s="11" t="str">
@@ -3280,7 +3280,7 @@
         <v/>
       </c>
       <c r="U11" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V11" s="14" t="str">
@@ -3306,11 +3306,11 @@
         <v/>
       </c>
       <c r="E12" s="11" t="str">
-        <f t="shared" ref="E12:F12" si="39">if(not(isblank($B12)), E11, "")</f>
+        <f t="shared" ref="E12:F12" si="40">if(not(isblank($B12)), E11, "")</f>
         <v/>
       </c>
       <c r="F12" s="11" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="G12" s="11" t="str">
@@ -3318,11 +3318,11 @@
         <v/>
       </c>
       <c r="H12" s="11" t="str">
-        <f t="shared" ref="H12:I12" si="40">if(not(isblank($B12)), H11, "")</f>
+        <f t="shared" ref="H12:I12" si="41">if(not(isblank($B12)), H11, "")</f>
         <v/>
       </c>
       <c r="I12" s="11" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="J12" s="11" t="str">
@@ -3330,11 +3330,11 @@
         <v/>
       </c>
       <c r="K12" s="11" t="str">
-        <f t="shared" ref="K12:L12" si="41">if(not(isblank($B12)), K11, "")</f>
+        <f t="shared" ref="K12:L12" si="42">if(not(isblank($B12)), K11, "")</f>
         <v/>
       </c>
       <c r="L12" s="11" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="M12" s="11" t="str">
@@ -3342,11 +3342,11 @@
         <v/>
       </c>
       <c r="N12" s="11" t="str">
-        <f t="shared" ref="N12:O12" si="42">if(not(isblank($B12)), N11, "")</f>
+        <f t="shared" ref="N12:O12" si="43">if(not(isblank($B12)), N11, "")</f>
         <v/>
       </c>
       <c r="O12" s="11" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="P12" s="11" t="str">
@@ -3370,7 +3370,7 @@
         <v/>
       </c>
       <c r="U12" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V12" s="14" t="str">
@@ -3396,11 +3396,11 @@
         <v/>
       </c>
       <c r="E13" s="11" t="str">
-        <f t="shared" ref="E13:F13" si="43">if(not(isblank($B13)), E12, "")</f>
+        <f t="shared" ref="E13:F13" si="44">if(not(isblank($B13)), E12, "")</f>
         <v/>
       </c>
       <c r="F13" s="11" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="G13" s="11" t="str">
@@ -3408,11 +3408,11 @@
         <v/>
       </c>
       <c r="H13" s="11" t="str">
-        <f t="shared" ref="H13:I13" si="44">if(not(isblank($B13)), H12, "")</f>
+        <f t="shared" ref="H13:I13" si="45">if(not(isblank($B13)), H12, "")</f>
         <v/>
       </c>
       <c r="I13" s="11" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="J13" s="11" t="str">
@@ -3420,11 +3420,11 @@
         <v/>
       </c>
       <c r="K13" s="11" t="str">
-        <f t="shared" ref="K13:L13" si="45">if(not(isblank($B13)), K12, "")</f>
+        <f t="shared" ref="K13:L13" si="46">if(not(isblank($B13)), K12, "")</f>
         <v/>
       </c>
       <c r="L13" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="M13" s="11" t="str">
@@ -3432,11 +3432,11 @@
         <v/>
       </c>
       <c r="N13" s="11" t="str">
-        <f t="shared" ref="N13:O13" si="46">if(not(isblank($B13)), N12, "")</f>
+        <f t="shared" ref="N13:O13" si="47">if(not(isblank($B13)), N12, "")</f>
         <v/>
       </c>
       <c r="O13" s="11" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="P13" s="11" t="str">
@@ -3460,7 +3460,7 @@
         <v/>
       </c>
       <c r="U13" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V13" s="14" t="str">
@@ -3470,8 +3470,8 @@
     </row>
     <row r="14">
       <c r="A14" s="11" t="str">
-        <f t="array" ref="A14">INDIRECT(CONCAT("product_listing!","A5"))</f>
-        <v>Surface data-derived</v>
+        <f t="array" ref="A14">INDIRECT(CONCAT("product_listing!A",row()))</f>
+        <v/>
       </c>
       <c r="B14" s="11" t="str">
         <f>product_listing!B14</f>
@@ -3486,11 +3486,11 @@
         <v/>
       </c>
       <c r="E14" s="11" t="str">
-        <f t="shared" ref="E14:F14" si="47">if(not(isblank($B14)), E13, "")</f>
+        <f t="shared" ref="E14:F14" si="48">if(not(isblank($B14)), E13, "")</f>
         <v/>
       </c>
       <c r="F14" s="11" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="G14" s="11" t="str">
@@ -3498,11 +3498,11 @@
         <v/>
       </c>
       <c r="H14" s="11" t="str">
-        <f t="shared" ref="H14:I14" si="48">if(not(isblank($B14)), H13, "")</f>
+        <f t="shared" ref="H14:I14" si="49">if(not(isblank($B14)), H13, "")</f>
         <v/>
       </c>
       <c r="I14" s="11" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="J14" s="11" t="str">
@@ -3510,11 +3510,11 @@
         <v/>
       </c>
       <c r="K14" s="11" t="str">
-        <f t="shared" ref="K14:L14" si="49">if(not(isblank($B14)), K13, "")</f>
+        <f t="shared" ref="K14:L14" si="50">if(not(isblank($B14)), K13, "")</f>
         <v/>
       </c>
       <c r="L14" s="11" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="M14" s="11" t="str">
@@ -3522,11 +3522,11 @@
         <v/>
       </c>
       <c r="N14" s="11" t="str">
-        <f t="shared" ref="N14:O14" si="50">if(not(isblank($B14)), N13, "")</f>
+        <f t="shared" ref="N14:O14" si="51">if(not(isblank($B14)), N13, "")</f>
         <v/>
       </c>
       <c r="O14" s="11" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="P14" s="11" t="str">
@@ -3550,7 +3550,7 @@
         <v/>
       </c>
       <c r="U14" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V14" s="14" t="str">
@@ -3576,11 +3576,11 @@
         <v/>
       </c>
       <c r="E15" s="11" t="str">
-        <f t="shared" ref="E15:F15" si="51">if(not(isblank($B15)), E14, "")</f>
+        <f t="shared" ref="E15:F15" si="52">if(not(isblank($B15)), E14, "")</f>
         <v/>
       </c>
       <c r="F15" s="11" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="G15" s="11" t="str">
@@ -3588,11 +3588,11 @@
         <v/>
       </c>
       <c r="H15" s="11" t="str">
-        <f t="shared" ref="H15:I15" si="52">if(not(isblank($B15)), H14, "")</f>
+        <f t="shared" ref="H15:I15" si="53">if(not(isblank($B15)), H14, "")</f>
         <v/>
       </c>
       <c r="I15" s="11" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="J15" s="11" t="str">
@@ -3600,11 +3600,11 @@
         <v/>
       </c>
       <c r="K15" s="11" t="str">
-        <f t="shared" ref="K15:L15" si="53">if(not(isblank($B15)), K14, "")</f>
+        <f t="shared" ref="K15:L15" si="54">if(not(isblank($B15)), K14, "")</f>
         <v/>
       </c>
       <c r="L15" s="11" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="M15" s="11" t="str">
@@ -3612,11 +3612,11 @@
         <v/>
       </c>
       <c r="N15" s="11" t="str">
-        <f t="shared" ref="N15:O15" si="54">if(not(isblank($B15)), N14, "")</f>
+        <f t="shared" ref="N15:O15" si="55">if(not(isblank($B15)), N14, "")</f>
         <v/>
       </c>
       <c r="O15" s="11" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="P15" s="11" t="str">
@@ -3640,7 +3640,7 @@
         <v/>
       </c>
       <c r="U15" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V15" s="14" t="str">
@@ -3666,11 +3666,11 @@
         <v/>
       </c>
       <c r="E16" s="11" t="str">
-        <f t="shared" ref="E16:F16" si="55">if(not(isblank($B16)), E15, "")</f>
+        <f t="shared" ref="E16:F16" si="56">if(not(isblank($B16)), E15, "")</f>
         <v/>
       </c>
       <c r="F16" s="11" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="G16" s="11" t="str">
@@ -3678,11 +3678,11 @@
         <v/>
       </c>
       <c r="H16" s="11" t="str">
-        <f t="shared" ref="H16:I16" si="56">if(not(isblank($B16)), H15, "")</f>
+        <f t="shared" ref="H16:I16" si="57">if(not(isblank($B16)), H15, "")</f>
         <v/>
       </c>
       <c r="I16" s="11" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v/>
       </c>
       <c r="J16" s="11" t="str">
@@ -3690,11 +3690,11 @@
         <v/>
       </c>
       <c r="K16" s="11" t="str">
-        <f t="shared" ref="K16:L16" si="57">if(not(isblank($B16)), K15, "")</f>
+        <f t="shared" ref="K16:L16" si="58">if(not(isblank($B16)), K15, "")</f>
         <v/>
       </c>
       <c r="L16" s="11" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="M16" s="11" t="str">
@@ -3702,11 +3702,11 @@
         <v/>
       </c>
       <c r="N16" s="11" t="str">
-        <f t="shared" ref="N16:O16" si="58">if(not(isblank($B16)), N15, "")</f>
+        <f t="shared" ref="N16:O16" si="59">if(not(isblank($B16)), N15, "")</f>
         <v/>
       </c>
       <c r="O16" s="11" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="P16" s="11" t="str">
@@ -3730,7 +3730,7 @@
         <v/>
       </c>
       <c r="U16" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V16" s="14" t="str">
@@ -3756,11 +3756,11 @@
         <v/>
       </c>
       <c r="E17" s="11" t="str">
-        <f t="shared" ref="E17:F17" si="59">if(not(isblank($B17)), E16, "")</f>
+        <f t="shared" ref="E17:F17" si="60">if(not(isblank($B17)), E16, "")</f>
         <v/>
       </c>
       <c r="F17" s="11" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v/>
       </c>
       <c r="G17" s="11" t="str">
@@ -3768,11 +3768,11 @@
         <v/>
       </c>
       <c r="H17" s="11" t="str">
-        <f t="shared" ref="H17:I17" si="60">if(not(isblank($B17)), H16, "")</f>
+        <f t="shared" ref="H17:I17" si="61">if(not(isblank($B17)), H16, "")</f>
         <v/>
       </c>
       <c r="I17" s="11" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="J17" s="11" t="str">
@@ -3780,11 +3780,11 @@
         <v/>
       </c>
       <c r="K17" s="11" t="str">
-        <f t="shared" ref="K17:L17" si="61">if(not(isblank($B17)), K16, "")</f>
+        <f t="shared" ref="K17:L17" si="62">if(not(isblank($B17)), K16, "")</f>
         <v/>
       </c>
       <c r="L17" s="11" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v/>
       </c>
       <c r="M17" s="11" t="str">
@@ -3792,11 +3792,11 @@
         <v/>
       </c>
       <c r="N17" s="11" t="str">
-        <f t="shared" ref="N17:O17" si="62">if(not(isblank($B17)), N16, "")</f>
+        <f t="shared" ref="N17:O17" si="63">if(not(isblank($B17)), N16, "")</f>
         <v/>
       </c>
       <c r="O17" s="11" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="P17" s="11" t="str">
@@ -3820,7 +3820,7 @@
         <v/>
       </c>
       <c r="U17" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V17" s="14" t="str">
@@ -3846,11 +3846,11 @@
         <v/>
       </c>
       <c r="E18" s="11" t="str">
-        <f t="shared" ref="E18:F18" si="63">if(not(isblank($B18)), E17, "")</f>
+        <f t="shared" ref="E18:F18" si="64">if(not(isblank($B18)), E17, "")</f>
         <v/>
       </c>
       <c r="F18" s="11" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G18" s="11" t="str">
@@ -3858,11 +3858,11 @@
         <v/>
       </c>
       <c r="H18" s="11" t="str">
-        <f t="shared" ref="H18:I18" si="64">if(not(isblank($B18)), H17, "")</f>
+        <f t="shared" ref="H18:I18" si="65">if(not(isblank($B18)), H17, "")</f>
         <v/>
       </c>
       <c r="I18" s="11" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="J18" s="11" t="str">
@@ -3870,11 +3870,11 @@
         <v/>
       </c>
       <c r="K18" s="11" t="str">
-        <f t="shared" ref="K18:L18" si="65">if(not(isblank($B18)), K17, "")</f>
+        <f t="shared" ref="K18:L18" si="66">if(not(isblank($B18)), K17, "")</f>
         <v/>
       </c>
       <c r="L18" s="11" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="M18" s="11" t="str">
@@ -3882,11 +3882,11 @@
         <v/>
       </c>
       <c r="N18" s="11" t="str">
-        <f t="shared" ref="N18:O18" si="66">if(not(isblank($B18)), N17, "")</f>
+        <f t="shared" ref="N18:O18" si="67">if(not(isblank($B18)), N17, "")</f>
         <v/>
       </c>
       <c r="O18" s="11" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="P18" s="11" t="str">
@@ -3910,7 +3910,7 @@
         <v/>
       </c>
       <c r="U18" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V18" s="14" t="str">
@@ -3936,11 +3936,11 @@
         <v/>
       </c>
       <c r="E19" s="11" t="str">
-        <f t="shared" ref="E19:F19" si="67">if(not(isblank($B19)), E18, "")</f>
+        <f t="shared" ref="E19:F19" si="68">if(not(isblank($B19)), E18, "")</f>
         <v/>
       </c>
       <c r="F19" s="11" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v/>
       </c>
       <c r="G19" s="11" t="str">
@@ -3948,11 +3948,11 @@
         <v/>
       </c>
       <c r="H19" s="11" t="str">
-        <f t="shared" ref="H19:I19" si="68">if(not(isblank($B19)), H18, "")</f>
+        <f t="shared" ref="H19:I19" si="69">if(not(isblank($B19)), H18, "")</f>
         <v/>
       </c>
       <c r="I19" s="11" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v/>
       </c>
       <c r="J19" s="11" t="str">
@@ -3960,11 +3960,11 @@
         <v/>
       </c>
       <c r="K19" s="11" t="str">
-        <f t="shared" ref="K19:L19" si="69">if(not(isblank($B19)), K18, "")</f>
+        <f t="shared" ref="K19:L19" si="70">if(not(isblank($B19)), K18, "")</f>
         <v/>
       </c>
       <c r="L19" s="11" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v/>
       </c>
       <c r="M19" s="11" t="str">
@@ -3972,11 +3972,11 @@
         <v/>
       </c>
       <c r="N19" s="11" t="str">
-        <f t="shared" ref="N19:O19" si="70">if(not(isblank($B19)), N18, "")</f>
+        <f t="shared" ref="N19:O19" si="71">if(not(isblank($B19)), N18, "")</f>
         <v/>
       </c>
       <c r="O19" s="11" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v/>
       </c>
       <c r="P19" s="11" t="str">
@@ -4000,7 +4000,7 @@
         <v/>
       </c>
       <c r="U19" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V19" s="14" t="str">
@@ -4026,11 +4026,11 @@
         <v/>
       </c>
       <c r="E20" s="11" t="str">
-        <f t="shared" ref="E20:F20" si="71">if(not(isblank($B20)), E19, "")</f>
+        <f t="shared" ref="E20:F20" si="72">if(not(isblank($B20)), E19, "")</f>
         <v/>
       </c>
       <c r="F20" s="11" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v/>
       </c>
       <c r="G20" s="11" t="str">
@@ -4038,11 +4038,11 @@
         <v/>
       </c>
       <c r="H20" s="11" t="str">
-        <f t="shared" ref="H20:I20" si="72">if(not(isblank($B20)), H19, "")</f>
+        <f t="shared" ref="H20:I20" si="73">if(not(isblank($B20)), H19, "")</f>
         <v/>
       </c>
       <c r="I20" s="11" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v/>
       </c>
       <c r="J20" s="11" t="str">
@@ -4050,11 +4050,11 @@
         <v/>
       </c>
       <c r="K20" s="11" t="str">
-        <f t="shared" ref="K20:L20" si="73">if(not(isblank($B20)), K19, "")</f>
+        <f t="shared" ref="K20:L20" si="74">if(not(isblank($B20)), K19, "")</f>
         <v/>
       </c>
       <c r="L20" s="11" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="M20" s="11" t="str">
@@ -4062,11 +4062,11 @@
         <v/>
       </c>
       <c r="N20" s="11" t="str">
-        <f t="shared" ref="N20:O20" si="74">if(not(isblank($B20)), N19, "")</f>
+        <f t="shared" ref="N20:O20" si="75">if(not(isblank($B20)), N19, "")</f>
         <v/>
       </c>
       <c r="O20" s="11" t="str">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v/>
       </c>
       <c r="P20" s="11" t="str">
@@ -4090,7 +4090,7 @@
         <v/>
       </c>
       <c r="U20" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V20" s="14" t="str">
@@ -4116,11 +4116,11 @@
         <v/>
       </c>
       <c r="E21" s="11" t="str">
-        <f t="shared" ref="E21:F21" si="75">if(not(isblank($B21)), E20, "")</f>
+        <f t="shared" ref="E21:F21" si="76">if(not(isblank($B21)), E20, "")</f>
         <v/>
       </c>
       <c r="F21" s="11" t="str">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v/>
       </c>
       <c r="G21" s="11" t="str">
@@ -4128,11 +4128,11 @@
         <v/>
       </c>
       <c r="H21" s="11" t="str">
-        <f t="shared" ref="H21:I21" si="76">if(not(isblank($B21)), H20, "")</f>
+        <f t="shared" ref="H21:I21" si="77">if(not(isblank($B21)), H20, "")</f>
         <v/>
       </c>
       <c r="I21" s="11" t="str">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v/>
       </c>
       <c r="J21" s="11" t="str">
@@ -4140,11 +4140,11 @@
         <v/>
       </c>
       <c r="K21" s="11" t="str">
-        <f t="shared" ref="K21:L21" si="77">if(not(isblank($B21)), K20, "")</f>
+        <f t="shared" ref="K21:L21" si="78">if(not(isblank($B21)), K20, "")</f>
         <v/>
       </c>
       <c r="L21" s="11" t="str">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v/>
       </c>
       <c r="M21" s="11" t="str">
@@ -4152,11 +4152,11 @@
         <v/>
       </c>
       <c r="N21" s="11" t="str">
-        <f t="shared" ref="N21:O21" si="78">if(not(isblank($B21)), N20, "")</f>
+        <f t="shared" ref="N21:O21" si="79">if(not(isblank($B21)), N20, "")</f>
         <v/>
       </c>
       <c r="O21" s="11" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v/>
       </c>
       <c r="P21" s="11" t="str">
@@ -4180,7 +4180,7 @@
         <v/>
       </c>
       <c r="U21" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V21" s="14" t="str">
@@ -4206,11 +4206,11 @@
         <v/>
       </c>
       <c r="E22" s="11" t="str">
-        <f t="shared" ref="E22:F22" si="79">if(not(isblank($B22)), E21, "")</f>
+        <f t="shared" ref="E22:F22" si="80">if(not(isblank($B22)), E21, "")</f>
         <v/>
       </c>
       <c r="F22" s="11" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v/>
       </c>
       <c r="G22" s="11" t="str">
@@ -4218,11 +4218,11 @@
         <v/>
       </c>
       <c r="H22" s="11" t="str">
-        <f t="shared" ref="H22:I22" si="80">if(not(isblank($B22)), H21, "")</f>
+        <f t="shared" ref="H22:I22" si="81">if(not(isblank($B22)), H21, "")</f>
         <v/>
       </c>
       <c r="I22" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v/>
       </c>
       <c r="J22" s="11" t="str">
@@ -4230,11 +4230,11 @@
         <v/>
       </c>
       <c r="K22" s="11" t="str">
-        <f t="shared" ref="K22:L22" si="81">if(not(isblank($B22)), K21, "")</f>
+        <f t="shared" ref="K22:L22" si="82">if(not(isblank($B22)), K21, "")</f>
         <v/>
       </c>
       <c r="L22" s="11" t="str">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v/>
       </c>
       <c r="M22" s="11" t="str">
@@ -4242,11 +4242,11 @@
         <v/>
       </c>
       <c r="N22" s="11" t="str">
-        <f t="shared" ref="N22:O22" si="82">if(not(isblank($B22)), N21, "")</f>
+        <f t="shared" ref="N22:O22" si="83">if(not(isblank($B22)), N21, "")</f>
         <v/>
       </c>
       <c r="O22" s="11" t="str">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v/>
       </c>
       <c r="P22" s="11" t="str">
@@ -4270,7 +4270,7 @@
         <v/>
       </c>
       <c r="U22" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V22" s="14" t="str">
@@ -4296,11 +4296,11 @@
         <v/>
       </c>
       <c r="E23" s="11" t="str">
-        <f t="shared" ref="E23:F23" si="83">if(not(isblank($B23)), E22, "")</f>
+        <f t="shared" ref="E23:F23" si="84">if(not(isblank($B23)), E22, "")</f>
         <v/>
       </c>
       <c r="F23" s="11" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v/>
       </c>
       <c r="G23" s="11" t="str">
@@ -4308,11 +4308,11 @@
         <v/>
       </c>
       <c r="H23" s="11" t="str">
-        <f t="shared" ref="H23:I23" si="84">if(not(isblank($B23)), H22, "")</f>
+        <f t="shared" ref="H23:I23" si="85">if(not(isblank($B23)), H22, "")</f>
         <v/>
       </c>
       <c r="I23" s="11" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v/>
       </c>
       <c r="J23" s="11" t="str">
@@ -4320,11 +4320,11 @@
         <v/>
       </c>
       <c r="K23" s="11" t="str">
-        <f t="shared" ref="K23:L23" si="85">if(not(isblank($B23)), K22, "")</f>
+        <f t="shared" ref="K23:L23" si="86">if(not(isblank($B23)), K22, "")</f>
         <v/>
       </c>
       <c r="L23" s="11" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="M23" s="11" t="str">
@@ -4332,11 +4332,11 @@
         <v/>
       </c>
       <c r="N23" s="11" t="str">
-        <f t="shared" ref="N23:O23" si="86">if(not(isblank($B23)), N22, "")</f>
+        <f t="shared" ref="N23:O23" si="87">if(not(isblank($B23)), N22, "")</f>
         <v/>
       </c>
       <c r="O23" s="11" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v/>
       </c>
       <c r="P23" s="11" t="str">
@@ -4360,7 +4360,7 @@
         <v/>
       </c>
       <c r="U23" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V23" s="14" t="str">
@@ -4386,11 +4386,11 @@
         <v/>
       </c>
       <c r="E24" s="11" t="str">
-        <f t="shared" ref="E24:F24" si="87">if(not(isblank($B24)), E23, "")</f>
+        <f t="shared" ref="E24:F24" si="88">if(not(isblank($B24)), E23, "")</f>
         <v/>
       </c>
       <c r="F24" s="11" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="G24" s="11" t="str">
@@ -4398,11 +4398,11 @@
         <v/>
       </c>
       <c r="H24" s="11" t="str">
-        <f t="shared" ref="H24:I24" si="88">if(not(isblank($B24)), H23, "")</f>
+        <f t="shared" ref="H24:I24" si="89">if(not(isblank($B24)), H23, "")</f>
         <v/>
       </c>
       <c r="I24" s="11" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="J24" s="11" t="str">
@@ -4410,11 +4410,11 @@
         <v/>
       </c>
       <c r="K24" s="11" t="str">
-        <f t="shared" ref="K24:L24" si="89">if(not(isblank($B24)), K23, "")</f>
+        <f t="shared" ref="K24:L24" si="90">if(not(isblank($B24)), K23, "")</f>
         <v/>
       </c>
       <c r="L24" s="11" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="M24" s="11" t="str">
@@ -4422,11 +4422,11 @@
         <v/>
       </c>
       <c r="N24" s="11" t="str">
-        <f t="shared" ref="N24:O24" si="90">if(not(isblank($B24)), N23, "")</f>
+        <f t="shared" ref="N24:O24" si="91">if(not(isblank($B24)), N23, "")</f>
         <v/>
       </c>
       <c r="O24" s="11" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v/>
       </c>
       <c r="P24" s="11" t="str">
@@ -4450,7 +4450,7 @@
         <v/>
       </c>
       <c r="U24" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V24" s="14" t="str">
@@ -4476,11 +4476,11 @@
         <v/>
       </c>
       <c r="E25" s="11" t="str">
-        <f t="shared" ref="E25:F25" si="91">if(not(isblank($B25)), E24, "")</f>
+        <f t="shared" ref="E25:F25" si="92">if(not(isblank($B25)), E24, "")</f>
         <v/>
       </c>
       <c r="F25" s="11" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v/>
       </c>
       <c r="G25" s="11" t="str">
@@ -4488,11 +4488,11 @@
         <v/>
       </c>
       <c r="H25" s="11" t="str">
-        <f t="shared" ref="H25:I25" si="92">if(not(isblank($B25)), H24, "")</f>
+        <f t="shared" ref="H25:I25" si="93">if(not(isblank($B25)), H24, "")</f>
         <v/>
       </c>
       <c r="I25" s="11" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v/>
       </c>
       <c r="J25" s="11" t="str">
@@ -4500,11 +4500,11 @@
         <v/>
       </c>
       <c r="K25" s="11" t="str">
-        <f t="shared" ref="K25:L25" si="93">if(not(isblank($B25)), K24, "")</f>
+        <f t="shared" ref="K25:L25" si="94">if(not(isblank($B25)), K24, "")</f>
         <v/>
       </c>
       <c r="L25" s="11" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v/>
       </c>
       <c r="M25" s="11" t="str">
@@ -4512,11 +4512,11 @@
         <v/>
       </c>
       <c r="N25" s="11" t="str">
-        <f t="shared" ref="N25:O25" si="94">if(not(isblank($B25)), N24, "")</f>
+        <f t="shared" ref="N25:O25" si="95">if(not(isblank($B25)), N24, "")</f>
         <v/>
       </c>
       <c r="O25" s="11" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="P25" s="11" t="str">
@@ -4540,7 +4540,7 @@
         <v/>
       </c>
       <c r="U25" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V25" s="14" t="str">
@@ -4566,11 +4566,11 @@
         <v/>
       </c>
       <c r="E26" s="11" t="str">
-        <f t="shared" ref="E26:F26" si="95">if(not(isblank($B26)), E25, "")</f>
+        <f t="shared" ref="E26:F26" si="96">if(not(isblank($B26)), E25, "")</f>
         <v/>
       </c>
       <c r="F26" s="11" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="G26" s="11" t="str">
@@ -4578,11 +4578,11 @@
         <v/>
       </c>
       <c r="H26" s="11" t="str">
-        <f t="shared" ref="H26:I26" si="96">if(not(isblank($B26)), H25, "")</f>
+        <f t="shared" ref="H26:I26" si="97">if(not(isblank($B26)), H25, "")</f>
         <v/>
       </c>
       <c r="I26" s="11" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v/>
       </c>
       <c r="J26" s="11" t="str">
@@ -4590,11 +4590,11 @@
         <v/>
       </c>
       <c r="K26" s="11" t="str">
-        <f t="shared" ref="K26:L26" si="97">if(not(isblank($B26)), K25, "")</f>
+        <f t="shared" ref="K26:L26" si="98">if(not(isblank($B26)), K25, "")</f>
         <v/>
       </c>
       <c r="L26" s="11" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v/>
       </c>
       <c r="M26" s="11" t="str">
@@ -4602,11 +4602,11 @@
         <v/>
       </c>
       <c r="N26" s="11" t="str">
-        <f t="shared" ref="N26:O26" si="98">if(not(isblank($B26)), N25, "")</f>
+        <f t="shared" ref="N26:O26" si="99">if(not(isblank($B26)), N25, "")</f>
         <v/>
       </c>
       <c r="O26" s="11" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v/>
       </c>
       <c r="P26" s="11" t="str">
@@ -4630,7 +4630,7 @@
         <v/>
       </c>
       <c r="U26" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V26" s="14" t="str">
@@ -4656,11 +4656,11 @@
         <v/>
       </c>
       <c r="E27" s="11" t="str">
-        <f t="shared" ref="E27:F27" si="99">if(not(isblank($B27)), E26, "")</f>
+        <f t="shared" ref="E27:F27" si="100">if(not(isblank($B27)), E26, "")</f>
         <v/>
       </c>
       <c r="F27" s="11" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v/>
       </c>
       <c r="G27" s="11" t="str">
@@ -4668,11 +4668,11 @@
         <v/>
       </c>
       <c r="H27" s="11" t="str">
-        <f t="shared" ref="H27:I27" si="100">if(not(isblank($B27)), H26, "")</f>
+        <f t="shared" ref="H27:I27" si="101">if(not(isblank($B27)), H26, "")</f>
         <v/>
       </c>
       <c r="I27" s="11" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v/>
       </c>
       <c r="J27" s="11" t="str">
@@ -4680,11 +4680,11 @@
         <v/>
       </c>
       <c r="K27" s="11" t="str">
-        <f t="shared" ref="K27:L27" si="101">if(not(isblank($B27)), K26, "")</f>
+        <f t="shared" ref="K27:L27" si="102">if(not(isblank($B27)), K26, "")</f>
         <v/>
       </c>
       <c r="L27" s="11" t="str">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v/>
       </c>
       <c r="M27" s="11" t="str">
@@ -4692,11 +4692,11 @@
         <v/>
       </c>
       <c r="N27" s="11" t="str">
-        <f t="shared" ref="N27:O27" si="102">if(not(isblank($B27)), N26, "")</f>
+        <f t="shared" ref="N27:O27" si="103">if(not(isblank($B27)), N26, "")</f>
         <v/>
       </c>
       <c r="O27" s="11" t="str">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v/>
       </c>
       <c r="P27" s="11" t="str">
@@ -4720,7 +4720,7 @@
         <v/>
       </c>
       <c r="U27" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V27" s="14" t="str">
@@ -4746,11 +4746,11 @@
         <v/>
       </c>
       <c r="E28" s="11" t="str">
-        <f t="shared" ref="E28:F28" si="103">if(not(isblank($B28)), E27, "")</f>
+        <f t="shared" ref="E28:F28" si="104">if(not(isblank($B28)), E27, "")</f>
         <v/>
       </c>
       <c r="F28" s="11" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="G28" s="11" t="str">
@@ -4758,11 +4758,11 @@
         <v/>
       </c>
       <c r="H28" s="11" t="str">
-        <f t="shared" ref="H28:I28" si="104">if(not(isblank($B28)), H27, "")</f>
+        <f t="shared" ref="H28:I28" si="105">if(not(isblank($B28)), H27, "")</f>
         <v/>
       </c>
       <c r="I28" s="11" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v/>
       </c>
       <c r="J28" s="11" t="str">
@@ -4770,11 +4770,11 @@
         <v/>
       </c>
       <c r="K28" s="11" t="str">
-        <f t="shared" ref="K28:L28" si="105">if(not(isblank($B28)), K27, "")</f>
+        <f t="shared" ref="K28:L28" si="106">if(not(isblank($B28)), K27, "")</f>
         <v/>
       </c>
       <c r="L28" s="11" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v/>
       </c>
       <c r="M28" s="11" t="str">
@@ -4782,11 +4782,11 @@
         <v/>
       </c>
       <c r="N28" s="11" t="str">
-        <f t="shared" ref="N28:O28" si="106">if(not(isblank($B28)), N27, "")</f>
+        <f t="shared" ref="N28:O28" si="107">if(not(isblank($B28)), N27, "")</f>
         <v/>
       </c>
       <c r="O28" s="11" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v/>
       </c>
       <c r="P28" s="11" t="str">
@@ -4810,7 +4810,7 @@
         <v/>
       </c>
       <c r="U28" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V28" s="14" t="str">
@@ -4836,11 +4836,11 @@
         <v/>
       </c>
       <c r="E29" s="11" t="str">
-        <f t="shared" ref="E29:F29" si="107">if(not(isblank($B29)), E28, "")</f>
+        <f t="shared" ref="E29:F29" si="108">if(not(isblank($B29)), E28, "")</f>
         <v/>
       </c>
       <c r="F29" s="11" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v/>
       </c>
       <c r="G29" s="11" t="str">
@@ -4848,11 +4848,11 @@
         <v/>
       </c>
       <c r="H29" s="11" t="str">
-        <f t="shared" ref="H29:I29" si="108">if(not(isblank($B29)), H28, "")</f>
+        <f t="shared" ref="H29:I29" si="109">if(not(isblank($B29)), H28, "")</f>
         <v/>
       </c>
       <c r="I29" s="11" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v/>
       </c>
       <c r="J29" s="11" t="str">
@@ -4860,11 +4860,11 @@
         <v/>
       </c>
       <c r="K29" s="11" t="str">
-        <f t="shared" ref="K29:L29" si="109">if(not(isblank($B29)), K28, "")</f>
+        <f t="shared" ref="K29:L29" si="110">if(not(isblank($B29)), K28, "")</f>
         <v/>
       </c>
       <c r="L29" s="11" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="110"/>
         <v/>
       </c>
       <c r="M29" s="11" t="str">
@@ -4872,11 +4872,11 @@
         <v/>
       </c>
       <c r="N29" s="11" t="str">
-        <f t="shared" ref="N29:O29" si="110">if(not(isblank($B29)), N28, "")</f>
+        <f t="shared" ref="N29:O29" si="111">if(not(isblank($B29)), N28, "")</f>
         <v/>
       </c>
       <c r="O29" s="11" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v/>
       </c>
       <c r="P29" s="11" t="str">
@@ -4900,7 +4900,7 @@
         <v/>
       </c>
       <c r="U29" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V29" s="14" t="str">
@@ -4926,11 +4926,11 @@
         <v/>
       </c>
       <c r="E30" s="11" t="str">
-        <f t="shared" ref="E30:F30" si="111">if(not(isblank($B30)), E29, "")</f>
+        <f t="shared" ref="E30:F30" si="112">if(not(isblank($B30)), E29, "")</f>
         <v/>
       </c>
       <c r="F30" s="11" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v/>
       </c>
       <c r="G30" s="11" t="str">
@@ -4938,11 +4938,11 @@
         <v/>
       </c>
       <c r="H30" s="11" t="str">
-        <f t="shared" ref="H30:I30" si="112">if(not(isblank($B30)), H29, "")</f>
+        <f t="shared" ref="H30:I30" si="113">if(not(isblank($B30)), H29, "")</f>
         <v/>
       </c>
       <c r="I30" s="11" t="str">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v/>
       </c>
       <c r="J30" s="11" t="str">
@@ -4950,11 +4950,11 @@
         <v/>
       </c>
       <c r="K30" s="11" t="str">
-        <f t="shared" ref="K30:L30" si="113">if(not(isblank($B30)), K29, "")</f>
+        <f t="shared" ref="K30:L30" si="114">if(not(isblank($B30)), K29, "")</f>
         <v/>
       </c>
       <c r="L30" s="11" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v/>
       </c>
       <c r="M30" s="11" t="str">
@@ -4962,11 +4962,11 @@
         <v/>
       </c>
       <c r="N30" s="11" t="str">
-        <f t="shared" ref="N30:O30" si="114">if(not(isblank($B30)), N29, "")</f>
+        <f t="shared" ref="N30:O30" si="115">if(not(isblank($B30)), N29, "")</f>
         <v/>
       </c>
       <c r="O30" s="11" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v/>
       </c>
       <c r="P30" s="11" t="str">
@@ -4990,7 +4990,7 @@
         <v/>
       </c>
       <c r="U30" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V30" s="14" t="str">
@@ -5016,11 +5016,11 @@
         <v/>
       </c>
       <c r="E31" s="11" t="str">
-        <f t="shared" ref="E31:F31" si="115">if(not(isblank($B31)), E30, "")</f>
+        <f t="shared" ref="E31:F31" si="116">if(not(isblank($B31)), E30, "")</f>
         <v/>
       </c>
       <c r="F31" s="11" t="str">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v/>
       </c>
       <c r="G31" s="11" t="str">
@@ -5028,11 +5028,11 @@
         <v/>
       </c>
       <c r="H31" s="11" t="str">
-        <f t="shared" ref="H31:I31" si="116">if(not(isblank($B31)), H30, "")</f>
+        <f t="shared" ref="H31:I31" si="117">if(not(isblank($B31)), H30, "")</f>
         <v/>
       </c>
       <c r="I31" s="11" t="str">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v/>
       </c>
       <c r="J31" s="11" t="str">
@@ -5040,11 +5040,11 @@
         <v/>
       </c>
       <c r="K31" s="11" t="str">
-        <f t="shared" ref="K31:L31" si="117">if(not(isblank($B31)), K30, "")</f>
+        <f t="shared" ref="K31:L31" si="118">if(not(isblank($B31)), K30, "")</f>
         <v/>
       </c>
       <c r="L31" s="11" t="str">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v/>
       </c>
       <c r="M31" s="11" t="str">
@@ -5052,11 +5052,11 @@
         <v/>
       </c>
       <c r="N31" s="11" t="str">
-        <f t="shared" ref="N31:O31" si="118">if(not(isblank($B31)), N30, "")</f>
+        <f t="shared" ref="N31:O31" si="119">if(not(isblank($B31)), N30, "")</f>
         <v/>
       </c>
       <c r="O31" s="11" t="str">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v/>
       </c>
       <c r="P31" s="11" t="str">
@@ -5080,7 +5080,7 @@
         <v/>
       </c>
       <c r="U31" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V31" s="14" t="str">
@@ -5106,11 +5106,11 @@
         <v/>
       </c>
       <c r="E32" s="11" t="str">
-        <f t="shared" ref="E32:F32" si="119">if(not(isblank($B32)), E31, "")</f>
+        <f t="shared" ref="E32:F32" si="120">if(not(isblank($B32)), E31, "")</f>
         <v/>
       </c>
       <c r="F32" s="11" t="str">
-        <f t="shared" si="119"/>
+        <f t="shared" si="120"/>
         <v/>
       </c>
       <c r="G32" s="11" t="str">
@@ -5118,11 +5118,11 @@
         <v/>
       </c>
       <c r="H32" s="11" t="str">
-        <f t="shared" ref="H32:I32" si="120">if(not(isblank($B32)), H31, "")</f>
+        <f t="shared" ref="H32:I32" si="121">if(not(isblank($B32)), H31, "")</f>
         <v/>
       </c>
       <c r="I32" s="11" t="str">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v/>
       </c>
       <c r="J32" s="11" t="str">
@@ -5130,11 +5130,11 @@
         <v/>
       </c>
       <c r="K32" s="11" t="str">
-        <f t="shared" ref="K32:L32" si="121">if(not(isblank($B32)), K31, "")</f>
+        <f t="shared" ref="K32:L32" si="122">if(not(isblank($B32)), K31, "")</f>
         <v/>
       </c>
       <c r="L32" s="11" t="str">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v/>
       </c>
       <c r="M32" s="11" t="str">
@@ -5142,11 +5142,11 @@
         <v/>
       </c>
       <c r="N32" s="11" t="str">
-        <f t="shared" ref="N32:O32" si="122">if(not(isblank($B32)), N31, "")</f>
+        <f t="shared" ref="N32:O32" si="123">if(not(isblank($B32)), N31, "")</f>
         <v/>
       </c>
       <c r="O32" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v/>
       </c>
       <c r="P32" s="11" t="str">
@@ -5170,7 +5170,7 @@
         <v/>
       </c>
       <c r="U32" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V32" s="14" t="str">
@@ -5196,11 +5196,11 @@
         <v/>
       </c>
       <c r="E33" s="11" t="str">
-        <f t="shared" ref="E33:F33" si="123">if(not(isblank($B33)), E32, "")</f>
+        <f t="shared" ref="E33:F33" si="124">if(not(isblank($B33)), E32, "")</f>
         <v/>
       </c>
       <c r="F33" s="11" t="str">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v/>
       </c>
       <c r="G33" s="11" t="str">
@@ -5208,11 +5208,11 @@
         <v/>
       </c>
       <c r="H33" s="11" t="str">
-        <f t="shared" ref="H33:I33" si="124">if(not(isblank($B33)), H32, "")</f>
+        <f t="shared" ref="H33:I33" si="125">if(not(isblank($B33)), H32, "")</f>
         <v/>
       </c>
       <c r="I33" s="11" t="str">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v/>
       </c>
       <c r="J33" s="11" t="str">
@@ -5220,11 +5220,11 @@
         <v/>
       </c>
       <c r="K33" s="11" t="str">
-        <f t="shared" ref="K33:L33" si="125">if(not(isblank($B33)), K32, "")</f>
+        <f t="shared" ref="K33:L33" si="126">if(not(isblank($B33)), K32, "")</f>
         <v/>
       </c>
       <c r="L33" s="11" t="str">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v/>
       </c>
       <c r="M33" s="11" t="str">
@@ -5232,11 +5232,11 @@
         <v/>
       </c>
       <c r="N33" s="11" t="str">
-        <f t="shared" ref="N33:O33" si="126">if(not(isblank($B33)), N32, "")</f>
+        <f t="shared" ref="N33:O33" si="127">if(not(isblank($B33)), N32, "")</f>
         <v/>
       </c>
       <c r="O33" s="11" t="str">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v/>
       </c>
       <c r="P33" s="11" t="str">
@@ -5260,7 +5260,7 @@
         <v/>
       </c>
       <c r="U33" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V33" s="14" t="str">
@@ -5286,11 +5286,11 @@
         <v/>
       </c>
       <c r="E34" s="11" t="str">
-        <f t="shared" ref="E34:F34" si="127">if(not(isblank($B34)), E33, "")</f>
+        <f t="shared" ref="E34:F34" si="128">if(not(isblank($B34)), E33, "")</f>
         <v/>
       </c>
       <c r="F34" s="11" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v/>
       </c>
       <c r="G34" s="11" t="str">
@@ -5298,11 +5298,11 @@
         <v/>
       </c>
       <c r="H34" s="11" t="str">
-        <f t="shared" ref="H34:I34" si="128">if(not(isblank($B34)), H33, "")</f>
+        <f t="shared" ref="H34:I34" si="129">if(not(isblank($B34)), H33, "")</f>
         <v/>
       </c>
       <c r="I34" s="11" t="str">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v/>
       </c>
       <c r="J34" s="11" t="str">
@@ -5310,11 +5310,11 @@
         <v/>
       </c>
       <c r="K34" s="11" t="str">
-        <f t="shared" ref="K34:L34" si="129">if(not(isblank($B34)), K33, "")</f>
+        <f t="shared" ref="K34:L34" si="130">if(not(isblank($B34)), K33, "")</f>
         <v/>
       </c>
       <c r="L34" s="11" t="str">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v/>
       </c>
       <c r="M34" s="11" t="str">
@@ -5322,11 +5322,11 @@
         <v/>
       </c>
       <c r="N34" s="11" t="str">
-        <f t="shared" ref="N34:O34" si="130">if(not(isblank($B34)), N33, "")</f>
+        <f t="shared" ref="N34:O34" si="131">if(not(isblank($B34)), N33, "")</f>
         <v/>
       </c>
       <c r="O34" s="11" t="str">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v/>
       </c>
       <c r="P34" s="11" t="str">
@@ -5350,7 +5350,7 @@
         <v/>
       </c>
       <c r="U34" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V34" s="14" t="str">
@@ -5376,11 +5376,11 @@
         <v/>
       </c>
       <c r="E35" s="11" t="str">
-        <f t="shared" ref="E35:F35" si="131">if(not(isblank($B35)), E34, "")</f>
+        <f t="shared" ref="E35:F35" si="132">if(not(isblank($B35)), E34, "")</f>
         <v/>
       </c>
       <c r="F35" s="11" t="str">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v/>
       </c>
       <c r="G35" s="11" t="str">
@@ -5388,11 +5388,11 @@
         <v/>
       </c>
       <c r="H35" s="11" t="str">
-        <f t="shared" ref="H35:I35" si="132">if(not(isblank($B35)), H34, "")</f>
+        <f t="shared" ref="H35:I35" si="133">if(not(isblank($B35)), H34, "")</f>
         <v/>
       </c>
       <c r="I35" s="11" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v/>
       </c>
       <c r="J35" s="11" t="str">
@@ -5400,11 +5400,11 @@
         <v/>
       </c>
       <c r="K35" s="11" t="str">
-        <f t="shared" ref="K35:L35" si="133">if(not(isblank($B35)), K34, "")</f>
+        <f t="shared" ref="K35:L35" si="134">if(not(isblank($B35)), K34, "")</f>
         <v/>
       </c>
       <c r="L35" s="11" t="str">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v/>
       </c>
       <c r="M35" s="11" t="str">
@@ -5412,11 +5412,11 @@
         <v/>
       </c>
       <c r="N35" s="11" t="str">
-        <f t="shared" ref="N35:O35" si="134">if(not(isblank($B35)), N34, "")</f>
+        <f t="shared" ref="N35:O35" si="135">if(not(isblank($B35)), N34, "")</f>
         <v/>
       </c>
       <c r="O35" s="11" t="str">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v/>
       </c>
       <c r="P35" s="11" t="str">
@@ -5440,7 +5440,7 @@
         <v/>
       </c>
       <c r="U35" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V35" s="14" t="str">
@@ -5466,11 +5466,11 @@
         <v/>
       </c>
       <c r="E36" s="11" t="str">
-        <f t="shared" ref="E36:F36" si="135">if(not(isblank($B36)), E35, "")</f>
+        <f t="shared" ref="E36:F36" si="136">if(not(isblank($B36)), E35, "")</f>
         <v/>
       </c>
       <c r="F36" s="11" t="str">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v/>
       </c>
       <c r="G36" s="11" t="str">
@@ -5478,11 +5478,11 @@
         <v/>
       </c>
       <c r="H36" s="11" t="str">
-        <f t="shared" ref="H36:I36" si="136">if(not(isblank($B36)), H35, "")</f>
+        <f t="shared" ref="H36:I36" si="137">if(not(isblank($B36)), H35, "")</f>
         <v/>
       </c>
       <c r="I36" s="11" t="str">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v/>
       </c>
       <c r="J36" s="11" t="str">
@@ -5490,11 +5490,11 @@
         <v/>
       </c>
       <c r="K36" s="11" t="str">
-        <f t="shared" ref="K36:L36" si="137">if(not(isblank($B36)), K35, "")</f>
+        <f t="shared" ref="K36:L36" si="138">if(not(isblank($B36)), K35, "")</f>
         <v/>
       </c>
       <c r="L36" s="11" t="str">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v/>
       </c>
       <c r="M36" s="11" t="str">
@@ -5502,11 +5502,11 @@
         <v/>
       </c>
       <c r="N36" s="11" t="str">
-        <f t="shared" ref="N36:O36" si="138">if(not(isblank($B36)), N35, "")</f>
+        <f t="shared" ref="N36:O36" si="139">if(not(isblank($B36)), N35, "")</f>
         <v/>
       </c>
       <c r="O36" s="11" t="str">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v/>
       </c>
       <c r="P36" s="11" t="str">
@@ -5530,7 +5530,7 @@
         <v/>
       </c>
       <c r="U36" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V36" s="14" t="str">
@@ -5556,11 +5556,11 @@
         <v/>
       </c>
       <c r="E37" s="11" t="str">
-        <f t="shared" ref="E37:F37" si="139">if(not(isblank($B37)), E36, "")</f>
+        <f t="shared" ref="E37:F37" si="140">if(not(isblank($B37)), E36, "")</f>
         <v/>
       </c>
       <c r="F37" s="11" t="str">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v/>
       </c>
       <c r="G37" s="11" t="str">
@@ -5568,11 +5568,11 @@
         <v/>
       </c>
       <c r="H37" s="11" t="str">
-        <f t="shared" ref="H37:I37" si="140">if(not(isblank($B37)), H36, "")</f>
+        <f t="shared" ref="H37:I37" si="141">if(not(isblank($B37)), H36, "")</f>
         <v/>
       </c>
       <c r="I37" s="11" t="str">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v/>
       </c>
       <c r="J37" s="11" t="str">
@@ -5580,11 +5580,11 @@
         <v/>
       </c>
       <c r="K37" s="11" t="str">
-        <f t="shared" ref="K37:L37" si="141">if(not(isblank($B37)), K36, "")</f>
+        <f t="shared" ref="K37:L37" si="142">if(not(isblank($B37)), K36, "")</f>
         <v/>
       </c>
       <c r="L37" s="11" t="str">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v/>
       </c>
       <c r="M37" s="11" t="str">
@@ -5592,11 +5592,11 @@
         <v/>
       </c>
       <c r="N37" s="11" t="str">
-        <f t="shared" ref="N37:O37" si="142">if(not(isblank($B37)), N36, "")</f>
+        <f t="shared" ref="N37:O37" si="143">if(not(isblank($B37)), N36, "")</f>
         <v/>
       </c>
       <c r="O37" s="11" t="str">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v/>
       </c>
       <c r="P37" s="11" t="str">
@@ -5620,7 +5620,7 @@
         <v/>
       </c>
       <c r="U37" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V37" s="14" t="str">
@@ -5646,11 +5646,11 @@
         <v/>
       </c>
       <c r="E38" s="11" t="str">
-        <f t="shared" ref="E38:F38" si="143">if(not(isblank($B38)), E37, "")</f>
+        <f t="shared" ref="E38:F38" si="144">if(not(isblank($B38)), E37, "")</f>
         <v/>
       </c>
       <c r="F38" s="11" t="str">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v/>
       </c>
       <c r="G38" s="11" t="str">
@@ -5658,11 +5658,11 @@
         <v/>
       </c>
       <c r="H38" s="11" t="str">
-        <f t="shared" ref="H38:I38" si="144">if(not(isblank($B38)), H37, "")</f>
+        <f t="shared" ref="H38:I38" si="145">if(not(isblank($B38)), H37, "")</f>
         <v/>
       </c>
       <c r="I38" s="11" t="str">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v/>
       </c>
       <c r="J38" s="11" t="str">
@@ -5670,11 +5670,11 @@
         <v/>
       </c>
       <c r="K38" s="11" t="str">
-        <f t="shared" ref="K38:L38" si="145">if(not(isblank($B38)), K37, "")</f>
+        <f t="shared" ref="K38:L38" si="146">if(not(isblank($B38)), K37, "")</f>
         <v/>
       </c>
       <c r="L38" s="11" t="str">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v/>
       </c>
       <c r="M38" s="11" t="str">
@@ -5682,11 +5682,11 @@
         <v/>
       </c>
       <c r="N38" s="11" t="str">
-        <f t="shared" ref="N38:O38" si="146">if(not(isblank($B38)), N37, "")</f>
+        <f t="shared" ref="N38:O38" si="147">if(not(isblank($B38)), N37, "")</f>
         <v/>
       </c>
       <c r="O38" s="11" t="str">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v/>
       </c>
       <c r="P38" s="11" t="str">
@@ -5710,7 +5710,7 @@
         <v/>
       </c>
       <c r="U38" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V38" s="14" t="str">
@@ -5736,11 +5736,11 @@
         <v/>
       </c>
       <c r="E39" s="11" t="str">
-        <f t="shared" ref="E39:F39" si="147">if(not(isblank($B39)), E38, "")</f>
+        <f t="shared" ref="E39:F39" si="148">if(not(isblank($B39)), E38, "")</f>
         <v/>
       </c>
       <c r="F39" s="11" t="str">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v/>
       </c>
       <c r="G39" s="11" t="str">
@@ -5748,11 +5748,11 @@
         <v/>
       </c>
       <c r="H39" s="11" t="str">
-        <f t="shared" ref="H39:I39" si="148">if(not(isblank($B39)), H38, "")</f>
+        <f t="shared" ref="H39:I39" si="149">if(not(isblank($B39)), H38, "")</f>
         <v/>
       </c>
       <c r="I39" s="11" t="str">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v/>
       </c>
       <c r="J39" s="11" t="str">
@@ -5760,11 +5760,11 @@
         <v/>
       </c>
       <c r="K39" s="11" t="str">
-        <f t="shared" ref="K39:L39" si="149">if(not(isblank($B39)), K38, "")</f>
+        <f t="shared" ref="K39:L39" si="150">if(not(isblank($B39)), K38, "")</f>
         <v/>
       </c>
       <c r="L39" s="11" t="str">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v/>
       </c>
       <c r="M39" s="11" t="str">
@@ -5772,11 +5772,11 @@
         <v/>
       </c>
       <c r="N39" s="11" t="str">
-        <f t="shared" ref="N39:O39" si="150">if(not(isblank($B39)), N38, "")</f>
+        <f t="shared" ref="N39:O39" si="151">if(not(isblank($B39)), N38, "")</f>
         <v/>
       </c>
       <c r="O39" s="11" t="str">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v/>
       </c>
       <c r="P39" s="11" t="str">
@@ -5800,7 +5800,7 @@
         <v/>
       </c>
       <c r="U39" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V39" s="14" t="str">
@@ -5826,11 +5826,11 @@
         <v/>
       </c>
       <c r="E40" s="11" t="str">
-        <f t="shared" ref="E40:F40" si="151">if(not(isblank($B40)), E39, "")</f>
+        <f t="shared" ref="E40:F40" si="152">if(not(isblank($B40)), E39, "")</f>
         <v/>
       </c>
       <c r="F40" s="11" t="str">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v/>
       </c>
       <c r="G40" s="11" t="str">
@@ -5838,11 +5838,11 @@
         <v/>
       </c>
       <c r="H40" s="11" t="str">
-        <f t="shared" ref="H40:I40" si="152">if(not(isblank($B40)), H39, "")</f>
+        <f t="shared" ref="H40:I40" si="153">if(not(isblank($B40)), H39, "")</f>
         <v/>
       </c>
       <c r="I40" s="11" t="str">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v/>
       </c>
       <c r="J40" s="11" t="str">
@@ -5850,11 +5850,11 @@
         <v/>
       </c>
       <c r="K40" s="11" t="str">
-        <f t="shared" ref="K40:L40" si="153">if(not(isblank($B40)), K39, "")</f>
+        <f t="shared" ref="K40:L40" si="154">if(not(isblank($B40)), K39, "")</f>
         <v/>
       </c>
       <c r="L40" s="11" t="str">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v/>
       </c>
       <c r="M40" s="11" t="str">
@@ -5862,11 +5862,11 @@
         <v/>
       </c>
       <c r="N40" s="11" t="str">
-        <f t="shared" ref="N40:O40" si="154">if(not(isblank($B40)), N39, "")</f>
+        <f t="shared" ref="N40:O40" si="155">if(not(isblank($B40)), N39, "")</f>
         <v/>
       </c>
       <c r="O40" s="11" t="str">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v/>
       </c>
       <c r="P40" s="11" t="str">
@@ -5890,7 +5890,7 @@
         <v/>
       </c>
       <c r="U40" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V40" s="14" t="str">
@@ -5916,11 +5916,11 @@
         <v/>
       </c>
       <c r="E41" s="11" t="str">
-        <f t="shared" ref="E41:F41" si="155">if(not(isblank($B41)), E40, "")</f>
+        <f t="shared" ref="E41:F41" si="156">if(not(isblank($B41)), E40, "")</f>
         <v/>
       </c>
       <c r="F41" s="11" t="str">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v/>
       </c>
       <c r="G41" s="11" t="str">
@@ -5928,11 +5928,11 @@
         <v/>
       </c>
       <c r="H41" s="11" t="str">
-        <f t="shared" ref="H41:I41" si="156">if(not(isblank($B41)), H40, "")</f>
+        <f t="shared" ref="H41:I41" si="157">if(not(isblank($B41)), H40, "")</f>
         <v/>
       </c>
       <c r="I41" s="11" t="str">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v/>
       </c>
       <c r="J41" s="11" t="str">
@@ -5940,11 +5940,11 @@
         <v/>
       </c>
       <c r="K41" s="11" t="str">
-        <f t="shared" ref="K41:L41" si="157">if(not(isblank($B41)), K40, "")</f>
+        <f t="shared" ref="K41:L41" si="158">if(not(isblank($B41)), K40, "")</f>
         <v/>
       </c>
       <c r="L41" s="11" t="str">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v/>
       </c>
       <c r="M41" s="11" t="str">
@@ -5952,11 +5952,11 @@
         <v/>
       </c>
       <c r="N41" s="11" t="str">
-        <f t="shared" ref="N41:O41" si="158">if(not(isblank($B41)), N40, "")</f>
+        <f t="shared" ref="N41:O41" si="159">if(not(isblank($B41)), N40, "")</f>
         <v/>
       </c>
       <c r="O41" s="11" t="str">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v/>
       </c>
       <c r="P41" s="11" t="str">
@@ -5980,7 +5980,7 @@
         <v/>
       </c>
       <c r="U41" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V41" s="14" t="str">
@@ -6006,11 +6006,11 @@
         <v/>
       </c>
       <c r="E42" s="11" t="str">
-        <f t="shared" ref="E42:F42" si="159">if(not(isblank($B42)), E41, "")</f>
+        <f t="shared" ref="E42:F42" si="160">if(not(isblank($B42)), E41, "")</f>
         <v/>
       </c>
       <c r="F42" s="11" t="str">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v/>
       </c>
       <c r="G42" s="11" t="str">
@@ -6018,11 +6018,11 @@
         <v/>
       </c>
       <c r="H42" s="11" t="str">
-        <f t="shared" ref="H42:I42" si="160">if(not(isblank($B42)), H41, "")</f>
+        <f t="shared" ref="H42:I42" si="161">if(not(isblank($B42)), H41, "")</f>
         <v/>
       </c>
       <c r="I42" s="11" t="str">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v/>
       </c>
       <c r="J42" s="11" t="str">
@@ -6030,11 +6030,11 @@
         <v/>
       </c>
       <c r="K42" s="11" t="str">
-        <f t="shared" ref="K42:L42" si="161">if(not(isblank($B42)), K41, "")</f>
+        <f t="shared" ref="K42:L42" si="162">if(not(isblank($B42)), K41, "")</f>
         <v/>
       </c>
       <c r="L42" s="11" t="str">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v/>
       </c>
       <c r="M42" s="11" t="str">
@@ -6042,11 +6042,11 @@
         <v/>
       </c>
       <c r="N42" s="11" t="str">
-        <f t="shared" ref="N42:O42" si="162">if(not(isblank($B42)), N41, "")</f>
+        <f t="shared" ref="N42:O42" si="163">if(not(isblank($B42)), N41, "")</f>
         <v/>
       </c>
       <c r="O42" s="11" t="str">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v/>
       </c>
       <c r="P42" s="11" t="str">
@@ -6070,7 +6070,7 @@
         <v/>
       </c>
       <c r="U42" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V42" s="14" t="str">
@@ -6096,11 +6096,11 @@
         <v/>
       </c>
       <c r="E43" s="11" t="str">
-        <f t="shared" ref="E43:F43" si="163">if(not(isblank($B43)), E42, "")</f>
+        <f t="shared" ref="E43:F43" si="164">if(not(isblank($B43)), E42, "")</f>
         <v/>
       </c>
       <c r="F43" s="11" t="str">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v/>
       </c>
       <c r="G43" s="11" t="str">
@@ -6108,11 +6108,11 @@
         <v/>
       </c>
       <c r="H43" s="11" t="str">
-        <f t="shared" ref="H43:I43" si="164">if(not(isblank($B43)), H42, "")</f>
+        <f t="shared" ref="H43:I43" si="165">if(not(isblank($B43)), H42, "")</f>
         <v/>
       </c>
       <c r="I43" s="11" t="str">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v/>
       </c>
       <c r="J43" s="11" t="str">
@@ -6120,11 +6120,11 @@
         <v/>
       </c>
       <c r="K43" s="11" t="str">
-        <f t="shared" ref="K43:L43" si="165">if(not(isblank($B43)), K42, "")</f>
+        <f t="shared" ref="K43:L43" si="166">if(not(isblank($B43)), K42, "")</f>
         <v/>
       </c>
       <c r="L43" s="11" t="str">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v/>
       </c>
       <c r="M43" s="11" t="str">
@@ -6132,11 +6132,11 @@
         <v/>
       </c>
       <c r="N43" s="11" t="str">
-        <f t="shared" ref="N43:O43" si="166">if(not(isblank($B43)), N42, "")</f>
+        <f t="shared" ref="N43:O43" si="167">if(not(isblank($B43)), N42, "")</f>
         <v/>
       </c>
       <c r="O43" s="11" t="str">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v/>
       </c>
       <c r="P43" s="11" t="str">
@@ -6160,7 +6160,7 @@
         <v/>
       </c>
       <c r="U43" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V43" s="14" t="str">
@@ -6186,11 +6186,11 @@
         <v/>
       </c>
       <c r="E44" s="11" t="str">
-        <f t="shared" ref="E44:F44" si="167">if(not(isblank($B44)), E43, "")</f>
+        <f t="shared" ref="E44:F44" si="168">if(not(isblank($B44)), E43, "")</f>
         <v/>
       </c>
       <c r="F44" s="11" t="str">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v/>
       </c>
       <c r="G44" s="11" t="str">
@@ -6198,11 +6198,11 @@
         <v/>
       </c>
       <c r="H44" s="11" t="str">
-        <f t="shared" ref="H44:I44" si="168">if(not(isblank($B44)), H43, "")</f>
+        <f t="shared" ref="H44:I44" si="169">if(not(isblank($B44)), H43, "")</f>
         <v/>
       </c>
       <c r="I44" s="11" t="str">
-        <f t="shared" si="168"/>
+        <f t="shared" si="169"/>
         <v/>
       </c>
       <c r="J44" s="11" t="str">
@@ -6210,11 +6210,11 @@
         <v/>
       </c>
       <c r="K44" s="11" t="str">
-        <f t="shared" ref="K44:L44" si="169">if(not(isblank($B44)), K43, "")</f>
+        <f t="shared" ref="K44:L44" si="170">if(not(isblank($B44)), K43, "")</f>
         <v/>
       </c>
       <c r="L44" s="11" t="str">
-        <f t="shared" si="169"/>
+        <f t="shared" si="170"/>
         <v/>
       </c>
       <c r="M44" s="11" t="str">
@@ -6222,11 +6222,11 @@
         <v/>
       </c>
       <c r="N44" s="11" t="str">
-        <f t="shared" ref="N44:O44" si="170">if(not(isblank($B44)), N43, "")</f>
+        <f t="shared" ref="N44:O44" si="171">if(not(isblank($B44)), N43, "")</f>
         <v/>
       </c>
       <c r="O44" s="11" t="str">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v/>
       </c>
       <c r="P44" s="11" t="str">
@@ -6250,7 +6250,7 @@
         <v/>
       </c>
       <c r="U44" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V44" s="14" t="str">
@@ -6276,11 +6276,11 @@
         <v/>
       </c>
       <c r="E45" s="11" t="str">
-        <f t="shared" ref="E45:F45" si="171">if(not(isblank($B45)), E44, "")</f>
+        <f t="shared" ref="E45:F45" si="172">if(not(isblank($B45)), E44, "")</f>
         <v/>
       </c>
       <c r="F45" s="11" t="str">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v/>
       </c>
       <c r="G45" s="11" t="str">
@@ -6288,11 +6288,11 @@
         <v/>
       </c>
       <c r="H45" s="11" t="str">
-        <f t="shared" ref="H45:I45" si="172">if(not(isblank($B45)), H44, "")</f>
+        <f t="shared" ref="H45:I45" si="173">if(not(isblank($B45)), H44, "")</f>
         <v/>
       </c>
       <c r="I45" s="11" t="str">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v/>
       </c>
       <c r="J45" s="11" t="str">
@@ -6300,11 +6300,11 @@
         <v/>
       </c>
       <c r="K45" s="11" t="str">
-        <f t="shared" ref="K45:L45" si="173">if(not(isblank($B45)), K44, "")</f>
+        <f t="shared" ref="K45:L45" si="174">if(not(isblank($B45)), K44, "")</f>
         <v/>
       </c>
       <c r="L45" s="11" t="str">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v/>
       </c>
       <c r="M45" s="11" t="str">
@@ -6312,11 +6312,11 @@
         <v/>
       </c>
       <c r="N45" s="11" t="str">
-        <f t="shared" ref="N45:O45" si="174">if(not(isblank($B45)), N44, "")</f>
+        <f t="shared" ref="N45:O45" si="175">if(not(isblank($B45)), N44, "")</f>
         <v/>
       </c>
       <c r="O45" s="11" t="str">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v/>
       </c>
       <c r="P45" s="11" t="str">
@@ -6340,7 +6340,7 @@
         <v/>
       </c>
       <c r="U45" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V45" s="14" t="str">
@@ -6366,11 +6366,11 @@
         <v/>
       </c>
       <c r="E46" s="11" t="str">
-        <f t="shared" ref="E46:F46" si="175">if(not(isblank($B46)), E45, "")</f>
+        <f t="shared" ref="E46:F46" si="176">if(not(isblank($B46)), E45, "")</f>
         <v/>
       </c>
       <c r="F46" s="11" t="str">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v/>
       </c>
       <c r="G46" s="11" t="str">
@@ -6378,11 +6378,11 @@
         <v/>
       </c>
       <c r="H46" s="11" t="str">
-        <f t="shared" ref="H46:I46" si="176">if(not(isblank($B46)), H45, "")</f>
+        <f t="shared" ref="H46:I46" si="177">if(not(isblank($B46)), H45, "")</f>
         <v/>
       </c>
       <c r="I46" s="11" t="str">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v/>
       </c>
       <c r="J46" s="11" t="str">
@@ -6390,11 +6390,11 @@
         <v/>
       </c>
       <c r="K46" s="11" t="str">
-        <f t="shared" ref="K46:L46" si="177">if(not(isblank($B46)), K45, "")</f>
+        <f t="shared" ref="K46:L46" si="178">if(not(isblank($B46)), K45, "")</f>
         <v/>
       </c>
       <c r="L46" s="11" t="str">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v/>
       </c>
       <c r="M46" s="11" t="str">
@@ -6402,11 +6402,11 @@
         <v/>
       </c>
       <c r="N46" s="11" t="str">
-        <f t="shared" ref="N46:O46" si="178">if(not(isblank($B46)), N45, "")</f>
+        <f t="shared" ref="N46:O46" si="179">if(not(isblank($B46)), N45, "")</f>
         <v/>
       </c>
       <c r="O46" s="11" t="str">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v/>
       </c>
       <c r="P46" s="11" t="str">
@@ -6430,7 +6430,7 @@
         <v/>
       </c>
       <c r="U46" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V46" s="14" t="str">
@@ -6456,11 +6456,11 @@
         <v/>
       </c>
       <c r="E47" s="11" t="str">
-        <f t="shared" ref="E47:F47" si="179">if(not(isblank($B47)), E46, "")</f>
+        <f t="shared" ref="E47:F47" si="180">if(not(isblank($B47)), E46, "")</f>
         <v/>
       </c>
       <c r="F47" s="11" t="str">
-        <f t="shared" si="179"/>
+        <f t="shared" si="180"/>
         <v/>
       </c>
       <c r="G47" s="11" t="str">
@@ -6468,11 +6468,11 @@
         <v/>
       </c>
       <c r="H47" s="11" t="str">
-        <f t="shared" ref="H47:I47" si="180">if(not(isblank($B47)), H46, "")</f>
+        <f t="shared" ref="H47:I47" si="181">if(not(isblank($B47)), H46, "")</f>
         <v/>
       </c>
       <c r="I47" s="11" t="str">
-        <f t="shared" si="180"/>
+        <f t="shared" si="181"/>
         <v/>
       </c>
       <c r="J47" s="11" t="str">
@@ -6480,11 +6480,11 @@
         <v/>
       </c>
       <c r="K47" s="11" t="str">
-        <f t="shared" ref="K47:L47" si="181">if(not(isblank($B47)), K46, "")</f>
+        <f t="shared" ref="K47:L47" si="182">if(not(isblank($B47)), K46, "")</f>
         <v/>
       </c>
       <c r="L47" s="11" t="str">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v/>
       </c>
       <c r="M47" s="11" t="str">
@@ -6492,11 +6492,11 @@
         <v/>
       </c>
       <c r="N47" s="11" t="str">
-        <f t="shared" ref="N47:O47" si="182">if(not(isblank($B47)), N46, "")</f>
+        <f t="shared" ref="N47:O47" si="183">if(not(isblank($B47)), N46, "")</f>
         <v/>
       </c>
       <c r="O47" s="11" t="str">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v/>
       </c>
       <c r="P47" s="11" t="str">
@@ -6520,7 +6520,7 @@
         <v/>
       </c>
       <c r="U47" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V47" s="14" t="str">
@@ -6546,11 +6546,11 @@
         <v/>
       </c>
       <c r="E48" s="11" t="str">
-        <f t="shared" ref="E48:F48" si="183">if(not(isblank($B48)), E47, "")</f>
+        <f t="shared" ref="E48:F48" si="184">if(not(isblank($B48)), E47, "")</f>
         <v/>
       </c>
       <c r="F48" s="11" t="str">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v/>
       </c>
       <c r="G48" s="11" t="str">
@@ -6558,11 +6558,11 @@
         <v/>
       </c>
       <c r="H48" s="11" t="str">
-        <f t="shared" ref="H48:I48" si="184">if(not(isblank($B48)), H47, "")</f>
+        <f t="shared" ref="H48:I48" si="185">if(not(isblank($B48)), H47, "")</f>
         <v/>
       </c>
       <c r="I48" s="11" t="str">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v/>
       </c>
       <c r="J48" s="11" t="str">
@@ -6570,11 +6570,11 @@
         <v/>
       </c>
       <c r="K48" s="11" t="str">
-        <f t="shared" ref="K48:L48" si="185">if(not(isblank($B48)), K47, "")</f>
+        <f t="shared" ref="K48:L48" si="186">if(not(isblank($B48)), K47, "")</f>
         <v/>
       </c>
       <c r="L48" s="11" t="str">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v/>
       </c>
       <c r="M48" s="11" t="str">
@@ -6582,11 +6582,11 @@
         <v/>
       </c>
       <c r="N48" s="11" t="str">
-        <f t="shared" ref="N48:O48" si="186">if(not(isblank($B48)), N47, "")</f>
+        <f t="shared" ref="N48:O48" si="187">if(not(isblank($B48)), N47, "")</f>
         <v/>
       </c>
       <c r="O48" s="11" t="str">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v/>
       </c>
       <c r="P48" s="11" t="str">
@@ -6610,7 +6610,7 @@
         <v/>
       </c>
       <c r="U48" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V48" s="14" t="str">
@@ -6636,11 +6636,11 @@
         <v/>
       </c>
       <c r="E49" s="11" t="str">
-        <f t="shared" ref="E49:F49" si="187">if(not(isblank($B49)), E48, "")</f>
+        <f t="shared" ref="E49:F49" si="188">if(not(isblank($B49)), E48, "")</f>
         <v/>
       </c>
       <c r="F49" s="11" t="str">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v/>
       </c>
       <c r="G49" s="11" t="str">
@@ -6648,11 +6648,11 @@
         <v/>
       </c>
       <c r="H49" s="11" t="str">
-        <f t="shared" ref="H49:I49" si="188">if(not(isblank($B49)), H48, "")</f>
+        <f t="shared" ref="H49:I49" si="189">if(not(isblank($B49)), H48, "")</f>
         <v/>
       </c>
       <c r="I49" s="11" t="str">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v/>
       </c>
       <c r="J49" s="11" t="str">
@@ -6660,11 +6660,11 @@
         <v/>
       </c>
       <c r="K49" s="11" t="str">
-        <f t="shared" ref="K49:L49" si="189">if(not(isblank($B49)), K48, "")</f>
+        <f t="shared" ref="K49:L49" si="190">if(not(isblank($B49)), K48, "")</f>
         <v/>
       </c>
       <c r="L49" s="11" t="str">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v/>
       </c>
       <c r="M49" s="11" t="str">
@@ -6672,11 +6672,11 @@
         <v/>
       </c>
       <c r="N49" s="11" t="str">
-        <f t="shared" ref="N49:O49" si="190">if(not(isblank($B49)), N48, "")</f>
+        <f t="shared" ref="N49:O49" si="191">if(not(isblank($B49)), N48, "")</f>
         <v/>
       </c>
       <c r="O49" s="11" t="str">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v/>
       </c>
       <c r="P49" s="11" t="str">
@@ -6700,7 +6700,7 @@
         <v/>
       </c>
       <c r="U49" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V49" s="14" t="str">
@@ -6726,11 +6726,11 @@
         <v/>
       </c>
       <c r="E50" s="11" t="str">
-        <f t="shared" ref="E50:F50" si="191">if(not(isblank($B50)), E49, "")</f>
+        <f t="shared" ref="E50:F50" si="192">if(not(isblank($B50)), E49, "")</f>
         <v/>
       </c>
       <c r="F50" s="11" t="str">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v/>
       </c>
       <c r="G50" s="11" t="str">
@@ -6738,11 +6738,11 @@
         <v/>
       </c>
       <c r="H50" s="11" t="str">
-        <f t="shared" ref="H50:I50" si="192">if(not(isblank($B50)), H49, "")</f>
+        <f t="shared" ref="H50:I50" si="193">if(not(isblank($B50)), H49, "")</f>
         <v/>
       </c>
       <c r="I50" s="11" t="str">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v/>
       </c>
       <c r="J50" s="11" t="str">
@@ -6750,11 +6750,11 @@
         <v/>
       </c>
       <c r="K50" s="11" t="str">
-        <f t="shared" ref="K50:L50" si="193">if(not(isblank($B50)), K49, "")</f>
+        <f t="shared" ref="K50:L50" si="194">if(not(isblank($B50)), K49, "")</f>
         <v/>
       </c>
       <c r="L50" s="11" t="str">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v/>
       </c>
       <c r="M50" s="11" t="str">
@@ -6762,11 +6762,11 @@
         <v/>
       </c>
       <c r="N50" s="11" t="str">
-        <f t="shared" ref="N50:O50" si="194">if(not(isblank($B50)), N49, "")</f>
+        <f t="shared" ref="N50:O50" si="195">if(not(isblank($B50)), N49, "")</f>
         <v/>
       </c>
       <c r="O50" s="11" t="str">
-        <f t="shared" si="194"/>
+        <f t="shared" si="195"/>
         <v/>
       </c>
       <c r="P50" s="11" t="str">
@@ -6790,7 +6790,7 @@
         <v/>
       </c>
       <c r="U50" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V50" s="14" t="str">
@@ -6816,11 +6816,11 @@
         <v/>
       </c>
       <c r="E51" s="11" t="str">
-        <f t="shared" ref="E51:F51" si="195">if(not(isblank($B51)), E50, "")</f>
+        <f t="shared" ref="E51:F51" si="196">if(not(isblank($B51)), E50, "")</f>
         <v/>
       </c>
       <c r="F51" s="11" t="str">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v/>
       </c>
       <c r="G51" s="11" t="str">
@@ -6828,11 +6828,11 @@
         <v/>
       </c>
       <c r="H51" s="11" t="str">
-        <f t="shared" ref="H51:I51" si="196">if(not(isblank($B51)), H50, "")</f>
+        <f t="shared" ref="H51:I51" si="197">if(not(isblank($B51)), H50, "")</f>
         <v/>
       </c>
       <c r="I51" s="11" t="str">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v/>
       </c>
       <c r="J51" s="11" t="str">
@@ -6840,11 +6840,11 @@
         <v/>
       </c>
       <c r="K51" s="11" t="str">
-        <f t="shared" ref="K51:L51" si="197">if(not(isblank($B51)), K50, "")</f>
+        <f t="shared" ref="K51:L51" si="198">if(not(isblank($B51)), K50, "")</f>
         <v/>
       </c>
       <c r="L51" s="11" t="str">
-        <f t="shared" si="197"/>
+        <f t="shared" si="198"/>
         <v/>
       </c>
       <c r="M51" s="11" t="str">
@@ -6852,11 +6852,11 @@
         <v/>
       </c>
       <c r="N51" s="11" t="str">
-        <f t="shared" ref="N51:O51" si="198">if(not(isblank($B51)), N50, "")</f>
+        <f t="shared" ref="N51:O51" si="199">if(not(isblank($B51)), N50, "")</f>
         <v/>
       </c>
       <c r="O51" s="11" t="str">
-        <f t="shared" si="198"/>
+        <f t="shared" si="199"/>
         <v/>
       </c>
       <c r="P51" s="11" t="str">
@@ -6880,7 +6880,7 @@
         <v/>
       </c>
       <c r="U51" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V51" s="14" t="str">
@@ -6906,11 +6906,11 @@
         <v/>
       </c>
       <c r="E52" s="11" t="str">
-        <f t="shared" ref="E52:F52" si="199">if(not(isblank($B52)), E51, "")</f>
+        <f t="shared" ref="E52:F52" si="200">if(not(isblank($B52)), E51, "")</f>
         <v/>
       </c>
       <c r="F52" s="11" t="str">
-        <f t="shared" si="199"/>
+        <f t="shared" si="200"/>
         <v/>
       </c>
       <c r="G52" s="11" t="str">
@@ -6918,11 +6918,11 @@
         <v/>
       </c>
       <c r="H52" s="11" t="str">
-        <f t="shared" ref="H52:I52" si="200">if(not(isblank($B52)), H51, "")</f>
+        <f t="shared" ref="H52:I52" si="201">if(not(isblank($B52)), H51, "")</f>
         <v/>
       </c>
       <c r="I52" s="11" t="str">
-        <f t="shared" si="200"/>
+        <f t="shared" si="201"/>
         <v/>
       </c>
       <c r="J52" s="11" t="str">
@@ -6930,11 +6930,11 @@
         <v/>
       </c>
       <c r="K52" s="11" t="str">
-        <f t="shared" ref="K52:L52" si="201">if(not(isblank($B52)), K51, "")</f>
+        <f t="shared" ref="K52:L52" si="202">if(not(isblank($B52)), K51, "")</f>
         <v/>
       </c>
       <c r="L52" s="11" t="str">
-        <f t="shared" si="201"/>
+        <f t="shared" si="202"/>
         <v/>
       </c>
       <c r="M52" s="11" t="str">
@@ -6942,11 +6942,11 @@
         <v/>
       </c>
       <c r="N52" s="11" t="str">
-        <f t="shared" ref="N52:O52" si="202">if(not(isblank($B52)), N51, "")</f>
+        <f t="shared" ref="N52:O52" si="203">if(not(isblank($B52)), N51, "")</f>
         <v/>
       </c>
       <c r="O52" s="11" t="str">
-        <f t="shared" si="202"/>
+        <f t="shared" si="203"/>
         <v/>
       </c>
       <c r="P52" s="11" t="str">
@@ -6970,7 +6970,7 @@
         <v/>
       </c>
       <c r="U52" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V52" s="14" t="str">
@@ -6996,11 +6996,11 @@
         <v/>
       </c>
       <c r="E53" s="11" t="str">
-        <f t="shared" ref="E53:F53" si="203">if(not(isblank($B53)), E52, "")</f>
+        <f t="shared" ref="E53:F53" si="204">if(not(isblank($B53)), E52, "")</f>
         <v/>
       </c>
       <c r="F53" s="11" t="str">
-        <f t="shared" si="203"/>
+        <f t="shared" si="204"/>
         <v/>
       </c>
       <c r="G53" s="11" t="str">
@@ -7008,11 +7008,11 @@
         <v/>
       </c>
       <c r="H53" s="11" t="str">
-        <f t="shared" ref="H53:I53" si="204">if(not(isblank($B53)), H52, "")</f>
+        <f t="shared" ref="H53:I53" si="205">if(not(isblank($B53)), H52, "")</f>
         <v/>
       </c>
       <c r="I53" s="11" t="str">
-        <f t="shared" si="204"/>
+        <f t="shared" si="205"/>
         <v/>
       </c>
       <c r="J53" s="11" t="str">
@@ -7020,11 +7020,11 @@
         <v/>
       </c>
       <c r="K53" s="11" t="str">
-        <f t="shared" ref="K53:L53" si="205">if(not(isblank($B53)), K52, "")</f>
+        <f t="shared" ref="K53:L53" si="206">if(not(isblank($B53)), K52, "")</f>
         <v/>
       </c>
       <c r="L53" s="11" t="str">
-        <f t="shared" si="205"/>
+        <f t="shared" si="206"/>
         <v/>
       </c>
       <c r="M53" s="11" t="str">
@@ -7032,11 +7032,11 @@
         <v/>
       </c>
       <c r="N53" s="11" t="str">
-        <f t="shared" ref="N53:O53" si="206">if(not(isblank($B53)), N52, "")</f>
+        <f t="shared" ref="N53:O53" si="207">if(not(isblank($B53)), N52, "")</f>
         <v/>
       </c>
       <c r="O53" s="11" t="str">
-        <f t="shared" si="206"/>
+        <f t="shared" si="207"/>
         <v/>
       </c>
       <c r="P53" s="11" t="str">
@@ -7060,7 +7060,7 @@
         <v/>
       </c>
       <c r="U53" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V53" s="14" t="str">
@@ -7086,11 +7086,11 @@
         <v/>
       </c>
       <c r="E54" s="11" t="str">
-        <f t="shared" ref="E54:F54" si="207">if(not(isblank($B54)), E53, "")</f>
+        <f t="shared" ref="E54:F54" si="208">if(not(isblank($B54)), E53, "")</f>
         <v/>
       </c>
       <c r="F54" s="11" t="str">
-        <f t="shared" si="207"/>
+        <f t="shared" si="208"/>
         <v/>
       </c>
       <c r="G54" s="11" t="str">
@@ -7098,11 +7098,11 @@
         <v/>
       </c>
       <c r="H54" s="11" t="str">
-        <f t="shared" ref="H54:I54" si="208">if(not(isblank($B54)), H53, "")</f>
+        <f t="shared" ref="H54:I54" si="209">if(not(isblank($B54)), H53, "")</f>
         <v/>
       </c>
       <c r="I54" s="11" t="str">
-        <f t="shared" si="208"/>
+        <f t="shared" si="209"/>
         <v/>
       </c>
       <c r="J54" s="11" t="str">
@@ -7110,11 +7110,11 @@
         <v/>
       </c>
       <c r="K54" s="11" t="str">
-        <f t="shared" ref="K54:L54" si="209">if(not(isblank($B54)), K53, "")</f>
+        <f t="shared" ref="K54:L54" si="210">if(not(isblank($B54)), K53, "")</f>
         <v/>
       </c>
       <c r="L54" s="11" t="str">
-        <f t="shared" si="209"/>
+        <f t="shared" si="210"/>
         <v/>
       </c>
       <c r="M54" s="11" t="str">
@@ -7122,11 +7122,11 @@
         <v/>
       </c>
       <c r="N54" s="11" t="str">
-        <f t="shared" ref="N54:O54" si="210">if(not(isblank($B54)), N53, "")</f>
+        <f t="shared" ref="N54:O54" si="211">if(not(isblank($B54)), N53, "")</f>
         <v/>
       </c>
       <c r="O54" s="11" t="str">
-        <f t="shared" si="210"/>
+        <f t="shared" si="211"/>
         <v/>
       </c>
       <c r="P54" s="11" t="str">
@@ -7150,7 +7150,7 @@
         <v/>
       </c>
       <c r="U54" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V54" s="14" t="str">
@@ -7176,11 +7176,11 @@
         <v/>
       </c>
       <c r="E55" s="11" t="str">
-        <f t="shared" ref="E55:F55" si="211">if(not(isblank($B55)), E54, "")</f>
+        <f t="shared" ref="E55:F55" si="212">if(not(isblank($B55)), E54, "")</f>
         <v/>
       </c>
       <c r="F55" s="11" t="str">
-        <f t="shared" si="211"/>
+        <f t="shared" si="212"/>
         <v/>
       </c>
       <c r="G55" s="11" t="str">
@@ -7188,11 +7188,11 @@
         <v/>
       </c>
       <c r="H55" s="11" t="str">
-        <f t="shared" ref="H55:I55" si="212">if(not(isblank($B55)), H54, "")</f>
+        <f t="shared" ref="H55:I55" si="213">if(not(isblank($B55)), H54, "")</f>
         <v/>
       </c>
       <c r="I55" s="11" t="str">
-        <f t="shared" si="212"/>
+        <f t="shared" si="213"/>
         <v/>
       </c>
       <c r="J55" s="11" t="str">
@@ -7200,11 +7200,11 @@
         <v/>
       </c>
       <c r="K55" s="11" t="str">
-        <f t="shared" ref="K55:L55" si="213">if(not(isblank($B55)), K54, "")</f>
+        <f t="shared" ref="K55:L55" si="214">if(not(isblank($B55)), K54, "")</f>
         <v/>
       </c>
       <c r="L55" s="11" t="str">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v/>
       </c>
       <c r="M55" s="11" t="str">
@@ -7212,11 +7212,11 @@
         <v/>
       </c>
       <c r="N55" s="11" t="str">
-        <f t="shared" ref="N55:O55" si="214">if(not(isblank($B55)), N54, "")</f>
+        <f t="shared" ref="N55:O55" si="215">if(not(isblank($B55)), N54, "")</f>
         <v/>
       </c>
       <c r="O55" s="11" t="str">
-        <f t="shared" si="214"/>
+        <f t="shared" si="215"/>
         <v/>
       </c>
       <c r="P55" s="11" t="str">
@@ -7240,7 +7240,7 @@
         <v/>
       </c>
       <c r="U55" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V55" s="14" t="str">
@@ -7266,11 +7266,11 @@
         <v/>
       </c>
       <c r="E56" s="11" t="str">
-        <f t="shared" ref="E56:F56" si="215">if(not(isblank($B56)), E55, "")</f>
+        <f t="shared" ref="E56:F56" si="216">if(not(isblank($B56)), E55, "")</f>
         <v/>
       </c>
       <c r="F56" s="11" t="str">
-        <f t="shared" si="215"/>
+        <f t="shared" si="216"/>
         <v/>
       </c>
       <c r="G56" s="11" t="str">
@@ -7278,11 +7278,11 @@
         <v/>
       </c>
       <c r="H56" s="11" t="str">
-        <f t="shared" ref="H56:I56" si="216">if(not(isblank($B56)), H55, "")</f>
+        <f t="shared" ref="H56:I56" si="217">if(not(isblank($B56)), H55, "")</f>
         <v/>
       </c>
       <c r="I56" s="11" t="str">
-        <f t="shared" si="216"/>
+        <f t="shared" si="217"/>
         <v/>
       </c>
       <c r="J56" s="11" t="str">
@@ -7290,11 +7290,11 @@
         <v/>
       </c>
       <c r="K56" s="11" t="str">
-        <f t="shared" ref="K56:L56" si="217">if(not(isblank($B56)), K55, "")</f>
+        <f t="shared" ref="K56:L56" si="218">if(not(isblank($B56)), K55, "")</f>
         <v/>
       </c>
       <c r="L56" s="11" t="str">
-        <f t="shared" si="217"/>
+        <f t="shared" si="218"/>
         <v/>
       </c>
       <c r="M56" s="11" t="str">
@@ -7302,11 +7302,11 @@
         <v/>
       </c>
       <c r="N56" s="11" t="str">
-        <f t="shared" ref="N56:O56" si="218">if(not(isblank($B56)), N55, "")</f>
+        <f t="shared" ref="N56:O56" si="219">if(not(isblank($B56)), N55, "")</f>
         <v/>
       </c>
       <c r="O56" s="11" t="str">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v/>
       </c>
       <c r="P56" s="11" t="str">
@@ -7330,7 +7330,7 @@
         <v/>
       </c>
       <c r="U56" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V56" s="14" t="str">
@@ -7356,11 +7356,11 @@
         <v/>
       </c>
       <c r="E57" s="11" t="str">
-        <f t="shared" ref="E57:F57" si="219">if(not(isblank($B57)), E56, "")</f>
+        <f t="shared" ref="E57:F57" si="220">if(not(isblank($B57)), E56, "")</f>
         <v/>
       </c>
       <c r="F57" s="11" t="str">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v/>
       </c>
       <c r="G57" s="11" t="str">
@@ -7368,11 +7368,11 @@
         <v/>
       </c>
       <c r="H57" s="11" t="str">
-        <f t="shared" ref="H57:I57" si="220">if(not(isblank($B57)), H56, "")</f>
+        <f t="shared" ref="H57:I57" si="221">if(not(isblank($B57)), H56, "")</f>
         <v/>
       </c>
       <c r="I57" s="11" t="str">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v/>
       </c>
       <c r="J57" s="11" t="str">
@@ -7380,11 +7380,11 @@
         <v/>
       </c>
       <c r="K57" s="11" t="str">
-        <f t="shared" ref="K57:L57" si="221">if(not(isblank($B57)), K56, "")</f>
+        <f t="shared" ref="K57:L57" si="222">if(not(isblank($B57)), K56, "")</f>
         <v/>
       </c>
       <c r="L57" s="11" t="str">
-        <f t="shared" si="221"/>
+        <f t="shared" si="222"/>
         <v/>
       </c>
       <c r="M57" s="11" t="str">
@@ -7392,11 +7392,11 @@
         <v/>
       </c>
       <c r="N57" s="11" t="str">
-        <f t="shared" ref="N57:O57" si="222">if(not(isblank($B57)), N56, "")</f>
+        <f t="shared" ref="N57:O57" si="223">if(not(isblank($B57)), N56, "")</f>
         <v/>
       </c>
       <c r="O57" s="11" t="str">
-        <f t="shared" si="222"/>
+        <f t="shared" si="223"/>
         <v/>
       </c>
       <c r="P57" s="11" t="str">
@@ -7420,7 +7420,7 @@
         <v/>
       </c>
       <c r="U57" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V57" s="14" t="str">
@@ -7446,11 +7446,11 @@
         <v/>
       </c>
       <c r="E58" s="11" t="str">
-        <f t="shared" ref="E58:F58" si="223">if(not(isblank($B58)), E57, "")</f>
+        <f t="shared" ref="E58:F58" si="224">if(not(isblank($B58)), E57, "")</f>
         <v/>
       </c>
       <c r="F58" s="11" t="str">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v/>
       </c>
       <c r="G58" s="11" t="str">
@@ -7458,11 +7458,11 @@
         <v/>
       </c>
       <c r="H58" s="11" t="str">
-        <f t="shared" ref="H58:I58" si="224">if(not(isblank($B58)), H57, "")</f>
+        <f t="shared" ref="H58:I58" si="225">if(not(isblank($B58)), H57, "")</f>
         <v/>
       </c>
       <c r="I58" s="11" t="str">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v/>
       </c>
       <c r="J58" s="11" t="str">
@@ -7470,11 +7470,11 @@
         <v/>
       </c>
       <c r="K58" s="11" t="str">
-        <f t="shared" ref="K58:L58" si="225">if(not(isblank($B58)), K57, "")</f>
+        <f t="shared" ref="K58:L58" si="226">if(not(isblank($B58)), K57, "")</f>
         <v/>
       </c>
       <c r="L58" s="11" t="str">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v/>
       </c>
       <c r="M58" s="11" t="str">
@@ -7482,11 +7482,11 @@
         <v/>
       </c>
       <c r="N58" s="11" t="str">
-        <f t="shared" ref="N58:O58" si="226">if(not(isblank($B58)), N57, "")</f>
+        <f t="shared" ref="N58:O58" si="227">if(not(isblank($B58)), N57, "")</f>
         <v/>
       </c>
       <c r="O58" s="11" t="str">
-        <f t="shared" si="226"/>
+        <f t="shared" si="227"/>
         <v/>
       </c>
       <c r="P58" s="11" t="str">
@@ -7510,7 +7510,7 @@
         <v/>
       </c>
       <c r="U58" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V58" s="14" t="str">
@@ -7536,11 +7536,11 @@
         <v/>
       </c>
       <c r="E59" s="11" t="str">
-        <f t="shared" ref="E59:F59" si="227">if(not(isblank($B59)), E58, "")</f>
+        <f t="shared" ref="E59:F59" si="228">if(not(isblank($B59)), E58, "")</f>
         <v/>
       </c>
       <c r="F59" s="11" t="str">
-        <f t="shared" si="227"/>
+        <f t="shared" si="228"/>
         <v/>
       </c>
       <c r="G59" s="11" t="str">
@@ -7548,11 +7548,11 @@
         <v/>
       </c>
       <c r="H59" s="11" t="str">
-        <f t="shared" ref="H59:I59" si="228">if(not(isblank($B59)), H58, "")</f>
+        <f t="shared" ref="H59:I59" si="229">if(not(isblank($B59)), H58, "")</f>
         <v/>
       </c>
       <c r="I59" s="11" t="str">
-        <f t="shared" si="228"/>
+        <f t="shared" si="229"/>
         <v/>
       </c>
       <c r="J59" s="11" t="str">
@@ -7560,11 +7560,11 @@
         <v/>
       </c>
       <c r="K59" s="11" t="str">
-        <f t="shared" ref="K59:L59" si="229">if(not(isblank($B59)), K58, "")</f>
+        <f t="shared" ref="K59:L59" si="230">if(not(isblank($B59)), K58, "")</f>
         <v/>
       </c>
       <c r="L59" s="11" t="str">
-        <f t="shared" si="229"/>
+        <f t="shared" si="230"/>
         <v/>
       </c>
       <c r="M59" s="11" t="str">
@@ -7572,11 +7572,11 @@
         <v/>
       </c>
       <c r="N59" s="11" t="str">
-        <f t="shared" ref="N59:O59" si="230">if(not(isblank($B59)), N58, "")</f>
+        <f t="shared" ref="N59:O59" si="231">if(not(isblank($B59)), N58, "")</f>
         <v/>
       </c>
       <c r="O59" s="11" t="str">
-        <f t="shared" si="230"/>
+        <f t="shared" si="231"/>
         <v/>
       </c>
       <c r="P59" s="11" t="str">
@@ -7600,7 +7600,7 @@
         <v/>
       </c>
       <c r="U59" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V59" s="14" t="str">
@@ -7626,11 +7626,11 @@
         <v/>
       </c>
       <c r="E60" s="11" t="str">
-        <f t="shared" ref="E60:F60" si="231">if(not(isblank($B60)), E59, "")</f>
+        <f t="shared" ref="E60:F60" si="232">if(not(isblank($B60)), E59, "")</f>
         <v/>
       </c>
       <c r="F60" s="11" t="str">
-        <f t="shared" si="231"/>
+        <f t="shared" si="232"/>
         <v/>
       </c>
       <c r="G60" s="11" t="str">
@@ -7638,11 +7638,11 @@
         <v/>
       </c>
       <c r="H60" s="11" t="str">
-        <f t="shared" ref="H60:I60" si="232">if(not(isblank($B60)), H59, "")</f>
+        <f t="shared" ref="H60:I60" si="233">if(not(isblank($B60)), H59, "")</f>
         <v/>
       </c>
       <c r="I60" s="11" t="str">
-        <f t="shared" si="232"/>
+        <f t="shared" si="233"/>
         <v/>
       </c>
       <c r="J60" s="11" t="str">
@@ -7650,11 +7650,11 @@
         <v/>
       </c>
       <c r="K60" s="11" t="str">
-        <f t="shared" ref="K60:L60" si="233">if(not(isblank($B60)), K59, "")</f>
+        <f t="shared" ref="K60:L60" si="234">if(not(isblank($B60)), K59, "")</f>
         <v/>
       </c>
       <c r="L60" s="11" t="str">
-        <f t="shared" si="233"/>
+        <f t="shared" si="234"/>
         <v/>
       </c>
       <c r="M60" s="11" t="str">
@@ -7662,11 +7662,11 @@
         <v/>
       </c>
       <c r="N60" s="11" t="str">
-        <f t="shared" ref="N60:O60" si="234">if(not(isblank($B60)), N59, "")</f>
+        <f t="shared" ref="N60:O60" si="235">if(not(isblank($B60)), N59, "")</f>
         <v/>
       </c>
       <c r="O60" s="11" t="str">
-        <f t="shared" si="234"/>
+        <f t="shared" si="235"/>
         <v/>
       </c>
       <c r="P60" s="11" t="str">
@@ -7687,7 +7687,7 @@
         <v/>
       </c>
       <c r="U60" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V60" s="14" t="str">
@@ -7713,11 +7713,11 @@
         <v/>
       </c>
       <c r="E61" s="11" t="str">
-        <f t="shared" ref="E61:F61" si="235">if(not(isblank($B61)), E60, "")</f>
+        <f t="shared" ref="E61:F61" si="236">if(not(isblank($B61)), E60, "")</f>
         <v/>
       </c>
       <c r="F61" s="11" t="str">
-        <f t="shared" si="235"/>
+        <f t="shared" si="236"/>
         <v/>
       </c>
       <c r="G61" s="11" t="str">
@@ -7725,11 +7725,11 @@
         <v/>
       </c>
       <c r="H61" s="11" t="str">
-        <f t="shared" ref="H61:I61" si="236">if(not(isblank($B61)), H60, "")</f>
+        <f t="shared" ref="H61:I61" si="237">if(not(isblank($B61)), H60, "")</f>
         <v/>
       </c>
       <c r="I61" s="11" t="str">
-        <f t="shared" si="236"/>
+        <f t="shared" si="237"/>
         <v/>
       </c>
       <c r="J61" s="11" t="str">
@@ -7737,11 +7737,11 @@
         <v/>
       </c>
       <c r="K61" s="11" t="str">
-        <f t="shared" ref="K61:L61" si="237">if(not(isblank($B61)), K60, "")</f>
+        <f t="shared" ref="K61:L61" si="238">if(not(isblank($B61)), K60, "")</f>
         <v/>
       </c>
       <c r="L61" s="11" t="str">
-        <f t="shared" si="237"/>
+        <f t="shared" si="238"/>
         <v/>
       </c>
       <c r="M61" s="11" t="str">
@@ -7749,11 +7749,11 @@
         <v/>
       </c>
       <c r="N61" s="11" t="str">
-        <f t="shared" ref="N61:O61" si="238">if(not(isblank($B61)), N60, "")</f>
+        <f t="shared" ref="N61:O61" si="239">if(not(isblank($B61)), N60, "")</f>
         <v/>
       </c>
       <c r="O61" s="11" t="str">
-        <f t="shared" si="238"/>
+        <f t="shared" si="239"/>
         <v/>
       </c>
       <c r="P61" s="11" t="str">
@@ -7774,7 +7774,7 @@
         <v/>
       </c>
       <c r="U61" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V61" s="14" t="str">
@@ -7800,11 +7800,11 @@
         <v/>
       </c>
       <c r="E62" s="11" t="str">
-        <f t="shared" ref="E62:F62" si="239">if(not(isblank($B62)), E61, "")</f>
+        <f t="shared" ref="E62:F62" si="240">if(not(isblank($B62)), E61, "")</f>
         <v/>
       </c>
       <c r="F62" s="11" t="str">
-        <f t="shared" si="239"/>
+        <f t="shared" si="240"/>
         <v/>
       </c>
       <c r="G62" s="11" t="str">
@@ -7812,11 +7812,11 @@
         <v/>
       </c>
       <c r="H62" s="11" t="str">
-        <f t="shared" ref="H62:I62" si="240">if(not(isblank($B62)), H61, "")</f>
+        <f t="shared" ref="H62:I62" si="241">if(not(isblank($B62)), H61, "")</f>
         <v/>
       </c>
       <c r="I62" s="11" t="str">
-        <f t="shared" si="240"/>
+        <f t="shared" si="241"/>
         <v/>
       </c>
       <c r="J62" s="11" t="str">
@@ -7824,11 +7824,11 @@
         <v/>
       </c>
       <c r="K62" s="11" t="str">
-        <f t="shared" ref="K62:L62" si="241">if(not(isblank($B62)), K61, "")</f>
+        <f t="shared" ref="K62:L62" si="242">if(not(isblank($B62)), K61, "")</f>
         <v/>
       </c>
       <c r="L62" s="11" t="str">
-        <f t="shared" si="241"/>
+        <f t="shared" si="242"/>
         <v/>
       </c>
       <c r="M62" s="11" t="str">
@@ -7836,11 +7836,11 @@
         <v/>
       </c>
       <c r="N62" s="11" t="str">
-        <f t="shared" ref="N62:O62" si="242">if(not(isblank($B62)), N61, "")</f>
+        <f t="shared" ref="N62:O62" si="243">if(not(isblank($B62)), N61, "")</f>
         <v/>
       </c>
       <c r="O62" s="11" t="str">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v/>
       </c>
       <c r="P62" s="11" t="str">
@@ -7861,7 +7861,7 @@
         <v/>
       </c>
       <c r="U62" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V62" s="14" t="str">
@@ -7887,11 +7887,11 @@
         <v/>
       </c>
       <c r="E63" s="11" t="str">
-        <f t="shared" ref="E63:F63" si="243">if(not(isblank($B63)), E62, "")</f>
+        <f t="shared" ref="E63:F63" si="244">if(not(isblank($B63)), E62, "")</f>
         <v/>
       </c>
       <c r="F63" s="11" t="str">
-        <f t="shared" si="243"/>
+        <f t="shared" si="244"/>
         <v/>
       </c>
       <c r="G63" s="11" t="str">
@@ -7899,11 +7899,11 @@
         <v/>
       </c>
       <c r="H63" s="11" t="str">
-        <f t="shared" ref="H63:I63" si="244">if(not(isblank($B63)), H62, "")</f>
+        <f t="shared" ref="H63:I63" si="245">if(not(isblank($B63)), H62, "")</f>
         <v/>
       </c>
       <c r="I63" s="11" t="str">
-        <f t="shared" si="244"/>
+        <f t="shared" si="245"/>
         <v/>
       </c>
       <c r="J63" s="11" t="str">
@@ -7911,11 +7911,11 @@
         <v/>
       </c>
       <c r="K63" s="11" t="str">
-        <f t="shared" ref="K63:L63" si="245">if(not(isblank($B63)), K62, "")</f>
+        <f t="shared" ref="K63:L63" si="246">if(not(isblank($B63)), K62, "")</f>
         <v/>
       </c>
       <c r="L63" s="11" t="str">
-        <f t="shared" si="245"/>
+        <f t="shared" si="246"/>
         <v/>
       </c>
       <c r="M63" s="11" t="str">
@@ -7923,11 +7923,11 @@
         <v/>
       </c>
       <c r="N63" s="11" t="str">
-        <f t="shared" ref="N63:O63" si="246">if(not(isblank($B63)), N62, "")</f>
+        <f t="shared" ref="N63:O63" si="247">if(not(isblank($B63)), N62, "")</f>
         <v/>
       </c>
       <c r="O63" s="11" t="str">
-        <f t="shared" si="246"/>
+        <f t="shared" si="247"/>
         <v/>
       </c>
       <c r="P63" s="11" t="str">
@@ -7948,7 +7948,7 @@
         <v/>
       </c>
       <c r="U63" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V63" s="14" t="str">
@@ -7974,11 +7974,11 @@
         <v/>
       </c>
       <c r="E64" s="11" t="str">
-        <f t="shared" ref="E64:F64" si="247">if(not(isblank($B64)), E63, "")</f>
+        <f t="shared" ref="E64:F64" si="248">if(not(isblank($B64)), E63, "")</f>
         <v/>
       </c>
       <c r="F64" s="11" t="str">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v/>
       </c>
       <c r="G64" s="11" t="str">
@@ -7986,11 +7986,11 @@
         <v/>
       </c>
       <c r="H64" s="11" t="str">
-        <f t="shared" ref="H64:I64" si="248">if(not(isblank($B64)), H63, "")</f>
+        <f t="shared" ref="H64:I64" si="249">if(not(isblank($B64)), H63, "")</f>
         <v/>
       </c>
       <c r="I64" s="11" t="str">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v/>
       </c>
       <c r="J64" s="11" t="str">
@@ -7998,11 +7998,11 @@
         <v/>
       </c>
       <c r="K64" s="11" t="str">
-        <f t="shared" ref="K64:L64" si="249">if(not(isblank($B64)), K63, "")</f>
+        <f t="shared" ref="K64:L64" si="250">if(not(isblank($B64)), K63, "")</f>
         <v/>
       </c>
       <c r="L64" s="11" t="str">
-        <f t="shared" si="249"/>
+        <f t="shared" si="250"/>
         <v/>
       </c>
       <c r="M64" s="11" t="str">
@@ -8010,11 +8010,11 @@
         <v/>
       </c>
       <c r="N64" s="11" t="str">
-        <f t="shared" ref="N64:O64" si="250">if(not(isblank($B64)), N63, "")</f>
+        <f t="shared" ref="N64:O64" si="251">if(not(isblank($B64)), N63, "")</f>
         <v/>
       </c>
       <c r="O64" s="11" t="str">
-        <f t="shared" si="250"/>
+        <f t="shared" si="251"/>
         <v/>
       </c>
       <c r="P64" s="11" t="str">
@@ -8035,7 +8035,7 @@
         <v/>
       </c>
       <c r="U64" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V64" s="14" t="str">
@@ -8061,11 +8061,11 @@
         <v/>
       </c>
       <c r="E65" s="11" t="str">
-        <f t="shared" ref="E65:F65" si="251">if(not(isblank($B65)), E64, "")</f>
+        <f t="shared" ref="E65:F65" si="252">if(not(isblank($B65)), E64, "")</f>
         <v/>
       </c>
       <c r="F65" s="11" t="str">
-        <f t="shared" si="251"/>
+        <f t="shared" si="252"/>
         <v/>
       </c>
       <c r="G65" s="11" t="str">
@@ -8073,11 +8073,11 @@
         <v/>
       </c>
       <c r="H65" s="11" t="str">
-        <f t="shared" ref="H65:I65" si="252">if(not(isblank($B65)), H64, "")</f>
+        <f t="shared" ref="H65:I65" si="253">if(not(isblank($B65)), H64, "")</f>
         <v/>
       </c>
       <c r="I65" s="11" t="str">
-        <f t="shared" si="252"/>
+        <f t="shared" si="253"/>
         <v/>
       </c>
       <c r="J65" s="11" t="str">
@@ -8085,11 +8085,11 @@
         <v/>
       </c>
       <c r="K65" s="11" t="str">
-        <f t="shared" ref="K65:L65" si="253">if(not(isblank($B65)), K64, "")</f>
+        <f t="shared" ref="K65:L65" si="254">if(not(isblank($B65)), K64, "")</f>
         <v/>
       </c>
       <c r="L65" s="11" t="str">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v/>
       </c>
       <c r="M65" s="11" t="str">
@@ -8097,11 +8097,11 @@
         <v/>
       </c>
       <c r="N65" s="11" t="str">
-        <f t="shared" ref="N65:O65" si="254">if(not(isblank($B65)), N64, "")</f>
+        <f t="shared" ref="N65:O65" si="255">if(not(isblank($B65)), N64, "")</f>
         <v/>
       </c>
       <c r="O65" s="11" t="str">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v/>
       </c>
       <c r="P65" s="11" t="str">
@@ -8122,7 +8122,7 @@
         <v/>
       </c>
       <c r="U65" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V65" s="14" t="str">
@@ -8148,11 +8148,11 @@
         <v/>
       </c>
       <c r="E66" s="11" t="str">
-        <f t="shared" ref="E66:F66" si="255">if(not(isblank($B66)), E65, "")</f>
+        <f t="shared" ref="E66:F66" si="256">if(not(isblank($B66)), E65, "")</f>
         <v/>
       </c>
       <c r="F66" s="11" t="str">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v/>
       </c>
       <c r="G66" s="11" t="str">
@@ -8160,11 +8160,11 @@
         <v/>
       </c>
       <c r="H66" s="11" t="str">
-        <f t="shared" ref="H66:I66" si="256">if(not(isblank($B66)), H65, "")</f>
+        <f t="shared" ref="H66:I66" si="257">if(not(isblank($B66)), H65, "")</f>
         <v/>
       </c>
       <c r="I66" s="11" t="str">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v/>
       </c>
       <c r="J66" s="11" t="str">
@@ -8172,11 +8172,11 @@
         <v/>
       </c>
       <c r="K66" s="11" t="str">
-        <f t="shared" ref="K66:L66" si="257">if(not(isblank($B66)), K65, "")</f>
+        <f t="shared" ref="K66:L66" si="258">if(not(isblank($B66)), K65, "")</f>
         <v/>
       </c>
       <c r="L66" s="11" t="str">
-        <f t="shared" si="257"/>
+        <f t="shared" si="258"/>
         <v/>
       </c>
       <c r="M66" s="11" t="str">
@@ -8184,11 +8184,11 @@
         <v/>
       </c>
       <c r="N66" s="11" t="str">
-        <f t="shared" ref="N66:O66" si="258">if(not(isblank($B66)), N65, "")</f>
+        <f t="shared" ref="N66:O66" si="259">if(not(isblank($B66)), N65, "")</f>
         <v/>
       </c>
       <c r="O66" s="11" t="str">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v/>
       </c>
       <c r="P66" s="11" t="str">
@@ -8209,7 +8209,7 @@
         <v/>
       </c>
       <c r="U66" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V66" s="14" t="str">
@@ -8235,11 +8235,11 @@
         <v/>
       </c>
       <c r="E67" s="11" t="str">
-        <f t="shared" ref="E67:F67" si="259">if(not(isblank($B67)), E66, "")</f>
+        <f t="shared" ref="E67:F67" si="260">if(not(isblank($B67)), E66, "")</f>
         <v/>
       </c>
       <c r="F67" s="11" t="str">
-        <f t="shared" si="259"/>
+        <f t="shared" si="260"/>
         <v/>
       </c>
       <c r="G67" s="11" t="str">
@@ -8247,11 +8247,11 @@
         <v/>
       </c>
       <c r="H67" s="11" t="str">
-        <f t="shared" ref="H67:I67" si="260">if(not(isblank($B67)), H66, "")</f>
+        <f t="shared" ref="H67:I67" si="261">if(not(isblank($B67)), H66, "")</f>
         <v/>
       </c>
       <c r="I67" s="11" t="str">
-        <f t="shared" si="260"/>
+        <f t="shared" si="261"/>
         <v/>
       </c>
       <c r="J67" s="11" t="str">
@@ -8259,11 +8259,11 @@
         <v/>
       </c>
       <c r="K67" s="11" t="str">
-        <f t="shared" ref="K67:L67" si="261">if(not(isblank($B67)), K66, "")</f>
+        <f t="shared" ref="K67:L67" si="262">if(not(isblank($B67)), K66, "")</f>
         <v/>
       </c>
       <c r="L67" s="11" t="str">
-        <f t="shared" si="261"/>
+        <f t="shared" si="262"/>
         <v/>
       </c>
       <c r="M67" s="11" t="str">
@@ -8271,11 +8271,11 @@
         <v/>
       </c>
       <c r="N67" s="11" t="str">
-        <f t="shared" ref="N67:O67" si="262">if(not(isblank($B67)), N66, "")</f>
+        <f t="shared" ref="N67:O67" si="263">if(not(isblank($B67)), N66, "")</f>
         <v/>
       </c>
       <c r="O67" s="11" t="str">
-        <f t="shared" si="262"/>
+        <f t="shared" si="263"/>
         <v/>
       </c>
       <c r="P67" s="11" t="str">
@@ -8296,7 +8296,7 @@
         <v/>
       </c>
       <c r="U67" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V67" s="14" t="str">
@@ -8322,11 +8322,11 @@
         <v/>
       </c>
       <c r="E68" s="11" t="str">
-        <f t="shared" ref="E68:F68" si="263">if(not(isblank($B68)), E67, "")</f>
+        <f t="shared" ref="E68:F68" si="264">if(not(isblank($B68)), E67, "")</f>
         <v/>
       </c>
       <c r="F68" s="11" t="str">
-        <f t="shared" si="263"/>
+        <f t="shared" si="264"/>
         <v/>
       </c>
       <c r="G68" s="11" t="str">
@@ -8334,11 +8334,11 @@
         <v/>
       </c>
       <c r="H68" s="11" t="str">
-        <f t="shared" ref="H68:I68" si="264">if(not(isblank($B68)), H67, "")</f>
+        <f t="shared" ref="H68:I68" si="265">if(not(isblank($B68)), H67, "")</f>
         <v/>
       </c>
       <c r="I68" s="11" t="str">
-        <f t="shared" si="264"/>
+        <f t="shared" si="265"/>
         <v/>
       </c>
       <c r="J68" s="11" t="str">
@@ -8346,11 +8346,11 @@
         <v/>
       </c>
       <c r="K68" s="11" t="str">
-        <f t="shared" ref="K68:L68" si="265">if(not(isblank($B68)), K67, "")</f>
+        <f t="shared" ref="K68:L68" si="266">if(not(isblank($B68)), K67, "")</f>
         <v/>
       </c>
       <c r="L68" s="11" t="str">
-        <f t="shared" si="265"/>
+        <f t="shared" si="266"/>
         <v/>
       </c>
       <c r="M68" s="11" t="str">
@@ -8358,11 +8358,11 @@
         <v/>
       </c>
       <c r="N68" s="11" t="str">
-        <f t="shared" ref="N68:O68" si="266">if(not(isblank($B68)), N67, "")</f>
+        <f t="shared" ref="N68:O68" si="267">if(not(isblank($B68)), N67, "")</f>
         <v/>
       </c>
       <c r="O68" s="11" t="str">
-        <f t="shared" si="266"/>
+        <f t="shared" si="267"/>
         <v/>
       </c>
       <c r="P68" s="11" t="str">
@@ -8383,7 +8383,7 @@
         <v/>
       </c>
       <c r="U68" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V68" s="14" t="str">
@@ -8409,11 +8409,11 @@
         <v/>
       </c>
       <c r="E69" s="11" t="str">
-        <f t="shared" ref="E69:F69" si="267">if(not(isblank($B69)), E68, "")</f>
+        <f t="shared" ref="E69:F69" si="268">if(not(isblank($B69)), E68, "")</f>
         <v/>
       </c>
       <c r="F69" s="11" t="str">
-        <f t="shared" si="267"/>
+        <f t="shared" si="268"/>
         <v/>
       </c>
       <c r="G69" s="11" t="str">
@@ -8421,11 +8421,11 @@
         <v/>
       </c>
       <c r="H69" s="11" t="str">
-        <f t="shared" ref="H69:I69" si="268">if(not(isblank($B69)), H68, "")</f>
+        <f t="shared" ref="H69:I69" si="269">if(not(isblank($B69)), H68, "")</f>
         <v/>
       </c>
       <c r="I69" s="11" t="str">
-        <f t="shared" si="268"/>
+        <f t="shared" si="269"/>
         <v/>
       </c>
       <c r="J69" s="11" t="str">
@@ -8433,11 +8433,11 @@
         <v/>
       </c>
       <c r="K69" s="11" t="str">
-        <f t="shared" ref="K69:L69" si="269">if(not(isblank($B69)), K68, "")</f>
+        <f t="shared" ref="K69:L69" si="270">if(not(isblank($B69)), K68, "")</f>
         <v/>
       </c>
       <c r="L69" s="11" t="str">
-        <f t="shared" si="269"/>
+        <f t="shared" si="270"/>
         <v/>
       </c>
       <c r="M69" s="11" t="str">
@@ -8445,11 +8445,11 @@
         <v/>
       </c>
       <c r="N69" s="11" t="str">
-        <f t="shared" ref="N69:O69" si="270">if(not(isblank($B69)), N68, "")</f>
+        <f t="shared" ref="N69:O69" si="271">if(not(isblank($B69)), N68, "")</f>
         <v/>
       </c>
       <c r="O69" s="11" t="str">
-        <f t="shared" si="270"/>
+        <f t="shared" si="271"/>
         <v/>
       </c>
       <c r="P69" s="11" t="str">
@@ -8470,7 +8470,7 @@
         <v/>
       </c>
       <c r="U69" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V69" s="14" t="str">
@@ -8496,11 +8496,11 @@
         <v/>
       </c>
       <c r="E70" s="11" t="str">
-        <f t="shared" ref="E70:F70" si="271">if(not(isblank($B70)), E69, "")</f>
+        <f t="shared" ref="E70:F70" si="272">if(not(isblank($B70)), E69, "")</f>
         <v/>
       </c>
       <c r="F70" s="11" t="str">
-        <f t="shared" si="271"/>
+        <f t="shared" si="272"/>
         <v/>
       </c>
       <c r="G70" s="11" t="str">
@@ -8508,11 +8508,11 @@
         <v/>
       </c>
       <c r="H70" s="11" t="str">
-        <f t="shared" ref="H70:I70" si="272">if(not(isblank($B70)), H69, "")</f>
+        <f t="shared" ref="H70:I70" si="273">if(not(isblank($B70)), H69, "")</f>
         <v/>
       </c>
       <c r="I70" s="11" t="str">
-        <f t="shared" si="272"/>
+        <f t="shared" si="273"/>
         <v/>
       </c>
       <c r="J70" s="11" t="str">
@@ -8520,11 +8520,11 @@
         <v/>
       </c>
       <c r="K70" s="11" t="str">
-        <f t="shared" ref="K70:L70" si="273">if(not(isblank($B70)), K69, "")</f>
+        <f t="shared" ref="K70:L70" si="274">if(not(isblank($B70)), K69, "")</f>
         <v/>
       </c>
       <c r="L70" s="11" t="str">
-        <f t="shared" si="273"/>
+        <f t="shared" si="274"/>
         <v/>
       </c>
       <c r="M70" s="11" t="str">
@@ -8532,11 +8532,11 @@
         <v/>
       </c>
       <c r="N70" s="11" t="str">
-        <f t="shared" ref="N70:O70" si="274">if(not(isblank($B70)), N69, "")</f>
+        <f t="shared" ref="N70:O70" si="275">if(not(isblank($B70)), N69, "")</f>
         <v/>
       </c>
       <c r="O70" s="11" t="str">
-        <f t="shared" si="274"/>
+        <f t="shared" si="275"/>
         <v/>
       </c>
       <c r="P70" s="11" t="str">
@@ -8557,7 +8557,7 @@
         <v/>
       </c>
       <c r="U70" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V70" s="14" t="str">
@@ -8583,11 +8583,11 @@
         <v/>
       </c>
       <c r="E71" s="11" t="str">
-        <f t="shared" ref="E71:F71" si="275">if(not(isblank($B71)), E70, "")</f>
+        <f t="shared" ref="E71:F71" si="276">if(not(isblank($B71)), E70, "")</f>
         <v/>
       </c>
       <c r="F71" s="11" t="str">
-        <f t="shared" si="275"/>
+        <f t="shared" si="276"/>
         <v/>
       </c>
       <c r="G71" s="11" t="str">
@@ -8595,11 +8595,11 @@
         <v/>
       </c>
       <c r="H71" s="11" t="str">
-        <f t="shared" ref="H71:I71" si="276">if(not(isblank($B71)), H70, "")</f>
+        <f t="shared" ref="H71:I71" si="277">if(not(isblank($B71)), H70, "")</f>
         <v/>
       </c>
       <c r="I71" s="11" t="str">
-        <f t="shared" si="276"/>
+        <f t="shared" si="277"/>
         <v/>
       </c>
       <c r="J71" s="11" t="str">
@@ -8607,11 +8607,11 @@
         <v/>
       </c>
       <c r="K71" s="11" t="str">
-        <f t="shared" ref="K71:L71" si="277">if(not(isblank($B71)), K70, "")</f>
+        <f t="shared" ref="K71:L71" si="278">if(not(isblank($B71)), K70, "")</f>
         <v/>
       </c>
       <c r="L71" s="11" t="str">
-        <f t="shared" si="277"/>
+        <f t="shared" si="278"/>
         <v/>
       </c>
       <c r="M71" s="11" t="str">
@@ -8619,11 +8619,11 @@
         <v/>
       </c>
       <c r="N71" s="11" t="str">
-        <f t="shared" ref="N71:O71" si="278">if(not(isblank($B71)), N70, "")</f>
+        <f t="shared" ref="N71:O71" si="279">if(not(isblank($B71)), N70, "")</f>
         <v/>
       </c>
       <c r="O71" s="11" t="str">
-        <f t="shared" si="278"/>
+        <f t="shared" si="279"/>
         <v/>
       </c>
       <c r="P71" s="11" t="str">
@@ -8644,7 +8644,7 @@
         <v/>
       </c>
       <c r="U71" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V71" s="14" t="str">
@@ -8670,11 +8670,11 @@
         <v/>
       </c>
       <c r="E72" s="11" t="str">
-        <f t="shared" ref="E72:F72" si="279">if(not(isblank($B72)), E71, "")</f>
+        <f t="shared" ref="E72:F72" si="280">if(not(isblank($B72)), E71, "")</f>
         <v/>
       </c>
       <c r="F72" s="11" t="str">
-        <f t="shared" si="279"/>
+        <f t="shared" si="280"/>
         <v/>
       </c>
       <c r="G72" s="11" t="str">
@@ -8682,11 +8682,11 @@
         <v/>
       </c>
       <c r="H72" s="11" t="str">
-        <f t="shared" ref="H72:I72" si="280">if(not(isblank($B72)), H71, "")</f>
+        <f t="shared" ref="H72:I72" si="281">if(not(isblank($B72)), H71, "")</f>
         <v/>
       </c>
       <c r="I72" s="11" t="str">
-        <f t="shared" si="280"/>
+        <f t="shared" si="281"/>
         <v/>
       </c>
       <c r="J72" s="11" t="str">
@@ -8694,11 +8694,11 @@
         <v/>
       </c>
       <c r="K72" s="11" t="str">
-        <f t="shared" ref="K72:L72" si="281">if(not(isblank($B72)), K71, "")</f>
+        <f t="shared" ref="K72:L72" si="282">if(not(isblank($B72)), K71, "")</f>
         <v/>
       </c>
       <c r="L72" s="11" t="str">
-        <f t="shared" si="281"/>
+        <f t="shared" si="282"/>
         <v/>
       </c>
       <c r="M72" s="11" t="str">
@@ -8706,11 +8706,11 @@
         <v/>
       </c>
       <c r="N72" s="11" t="str">
-        <f t="shared" ref="N72:O72" si="282">if(not(isblank($B72)), N71, "")</f>
+        <f t="shared" ref="N72:O72" si="283">if(not(isblank($B72)), N71, "")</f>
         <v/>
       </c>
       <c r="O72" s="11" t="str">
-        <f t="shared" si="282"/>
+        <f t="shared" si="283"/>
         <v/>
       </c>
       <c r="P72" s="11" t="str">
@@ -8731,7 +8731,7 @@
         <v/>
       </c>
       <c r="U72" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V72" s="14" t="str">
@@ -8757,11 +8757,11 @@
         <v/>
       </c>
       <c r="E73" s="11" t="str">
-        <f t="shared" ref="E73:F73" si="283">if(not(isblank($B73)), E72, "")</f>
+        <f t="shared" ref="E73:F73" si="284">if(not(isblank($B73)), E72, "")</f>
         <v/>
       </c>
       <c r="F73" s="11" t="str">
-        <f t="shared" si="283"/>
+        <f t="shared" si="284"/>
         <v/>
       </c>
       <c r="G73" s="11" t="str">
@@ -8769,11 +8769,11 @@
         <v/>
       </c>
       <c r="H73" s="11" t="str">
-        <f t="shared" ref="H73:I73" si="284">if(not(isblank($B73)), H72, "")</f>
+        <f t="shared" ref="H73:I73" si="285">if(not(isblank($B73)), H72, "")</f>
         <v/>
       </c>
       <c r="I73" s="11" t="str">
-        <f t="shared" si="284"/>
+        <f t="shared" si="285"/>
         <v/>
       </c>
       <c r="J73" s="11" t="str">
@@ -8781,11 +8781,11 @@
         <v/>
       </c>
       <c r="K73" s="11" t="str">
-        <f t="shared" ref="K73:L73" si="285">if(not(isblank($B73)), K72, "")</f>
+        <f t="shared" ref="K73:L73" si="286">if(not(isblank($B73)), K72, "")</f>
         <v/>
       </c>
       <c r="L73" s="11" t="str">
-        <f t="shared" si="285"/>
+        <f t="shared" si="286"/>
         <v/>
       </c>
       <c r="M73" s="11" t="str">
@@ -8793,11 +8793,11 @@
         <v/>
       </c>
       <c r="N73" s="11" t="str">
-        <f t="shared" ref="N73:O73" si="286">if(not(isblank($B73)), N72, "")</f>
+        <f t="shared" ref="N73:O73" si="287">if(not(isblank($B73)), N72, "")</f>
         <v/>
       </c>
       <c r="O73" s="11" t="str">
-        <f t="shared" si="286"/>
+        <f t="shared" si="287"/>
         <v/>
       </c>
       <c r="P73" s="11" t="str">
@@ -8818,7 +8818,7 @@
         <v/>
       </c>
       <c r="U73" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V73" s="14" t="str">
@@ -8844,11 +8844,11 @@
         <v/>
       </c>
       <c r="E74" s="11" t="str">
-        <f t="shared" ref="E74:F74" si="287">if(not(isblank($B74)), E73, "")</f>
+        <f t="shared" ref="E74:F74" si="288">if(not(isblank($B74)), E73, "")</f>
         <v/>
       </c>
       <c r="F74" s="11" t="str">
-        <f t="shared" si="287"/>
+        <f t="shared" si="288"/>
         <v/>
       </c>
       <c r="G74" s="11" t="str">
@@ -8856,11 +8856,11 @@
         <v/>
       </c>
       <c r="H74" s="11" t="str">
-        <f t="shared" ref="H74:I74" si="288">if(not(isblank($B74)), H73, "")</f>
+        <f t="shared" ref="H74:I74" si="289">if(not(isblank($B74)), H73, "")</f>
         <v/>
       </c>
       <c r="I74" s="11" t="str">
-        <f t="shared" si="288"/>
+        <f t="shared" si="289"/>
         <v/>
       </c>
       <c r="J74" s="11" t="str">
@@ -8868,11 +8868,11 @@
         <v/>
       </c>
       <c r="K74" s="11" t="str">
-        <f t="shared" ref="K74:L74" si="289">if(not(isblank($B74)), K73, "")</f>
+        <f t="shared" ref="K74:L74" si="290">if(not(isblank($B74)), K73, "")</f>
         <v/>
       </c>
       <c r="L74" s="11" t="str">
-        <f t="shared" si="289"/>
+        <f t="shared" si="290"/>
         <v/>
       </c>
       <c r="M74" s="11" t="str">
@@ -8880,11 +8880,11 @@
         <v/>
       </c>
       <c r="N74" s="11" t="str">
-        <f t="shared" ref="N74:O74" si="290">if(not(isblank($B74)), N73, "")</f>
+        <f t="shared" ref="N74:O74" si="291">if(not(isblank($B74)), N73, "")</f>
         <v/>
       </c>
       <c r="O74" s="11" t="str">
-        <f t="shared" si="290"/>
+        <f t="shared" si="291"/>
         <v/>
       </c>
       <c r="P74" s="11" t="str">
@@ -8905,7 +8905,7 @@
         <v/>
       </c>
       <c r="U74" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V74" s="14" t="str">
@@ -8931,11 +8931,11 @@
         <v/>
       </c>
       <c r="E75" s="11" t="str">
-        <f t="shared" ref="E75:F75" si="291">if(not(isblank($B75)), E74, "")</f>
+        <f t="shared" ref="E75:F75" si="292">if(not(isblank($B75)), E74, "")</f>
         <v/>
       </c>
       <c r="F75" s="11" t="str">
-        <f t="shared" si="291"/>
+        <f t="shared" si="292"/>
         <v/>
       </c>
       <c r="G75" s="11" t="str">
@@ -8943,11 +8943,11 @@
         <v/>
       </c>
       <c r="H75" s="11" t="str">
-        <f t="shared" ref="H75:I75" si="292">if(not(isblank($B75)), H74, "")</f>
+        <f t="shared" ref="H75:I75" si="293">if(not(isblank($B75)), H74, "")</f>
         <v/>
       </c>
       <c r="I75" s="11" t="str">
-        <f t="shared" si="292"/>
+        <f t="shared" si="293"/>
         <v/>
       </c>
       <c r="J75" s="11" t="str">
@@ -8955,11 +8955,11 @@
         <v/>
       </c>
       <c r="K75" s="11" t="str">
-        <f t="shared" ref="K75:L75" si="293">if(not(isblank($B75)), K74, "")</f>
+        <f t="shared" ref="K75:L75" si="294">if(not(isblank($B75)), K74, "")</f>
         <v/>
       </c>
       <c r="L75" s="11" t="str">
-        <f t="shared" si="293"/>
+        <f t="shared" si="294"/>
         <v/>
       </c>
       <c r="M75" s="11" t="str">
@@ -8967,11 +8967,11 @@
         <v/>
       </c>
       <c r="N75" s="11" t="str">
-        <f t="shared" ref="N75:O75" si="294">if(not(isblank($B75)), N74, "")</f>
+        <f t="shared" ref="N75:O75" si="295">if(not(isblank($B75)), N74, "")</f>
         <v/>
       </c>
       <c r="O75" s="11" t="str">
-        <f t="shared" si="294"/>
+        <f t="shared" si="295"/>
         <v/>
       </c>
       <c r="P75" s="11" t="str">
@@ -8992,7 +8992,7 @@
         <v/>
       </c>
       <c r="U75" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V75" s="14" t="str">
@@ -9018,11 +9018,11 @@
         <v/>
       </c>
       <c r="E76" s="11" t="str">
-        <f t="shared" ref="E76:F76" si="295">if(not(isblank($B76)), E75, "")</f>
+        <f t="shared" ref="E76:F76" si="296">if(not(isblank($B76)), E75, "")</f>
         <v/>
       </c>
       <c r="F76" s="11" t="str">
-        <f t="shared" si="295"/>
+        <f t="shared" si="296"/>
         <v/>
       </c>
       <c r="G76" s="11" t="str">
@@ -9030,11 +9030,11 @@
         <v/>
       </c>
       <c r="H76" s="11" t="str">
-        <f t="shared" ref="H76:I76" si="296">if(not(isblank($B76)), H75, "")</f>
+        <f t="shared" ref="H76:I76" si="297">if(not(isblank($B76)), H75, "")</f>
         <v/>
       </c>
       <c r="I76" s="11" t="str">
-        <f t="shared" si="296"/>
+        <f t="shared" si="297"/>
         <v/>
       </c>
       <c r="J76" s="11" t="str">
@@ -9042,11 +9042,11 @@
         <v/>
       </c>
       <c r="K76" s="11" t="str">
-        <f t="shared" ref="K76:L76" si="297">if(not(isblank($B76)), K75, "")</f>
+        <f t="shared" ref="K76:L76" si="298">if(not(isblank($B76)), K75, "")</f>
         <v/>
       </c>
       <c r="L76" s="11" t="str">
-        <f t="shared" si="297"/>
+        <f t="shared" si="298"/>
         <v/>
       </c>
       <c r="M76" s="11" t="str">
@@ -9054,11 +9054,11 @@
         <v/>
       </c>
       <c r="N76" s="11" t="str">
-        <f t="shared" ref="N76:O76" si="298">if(not(isblank($B76)), N75, "")</f>
+        <f t="shared" ref="N76:O76" si="299">if(not(isblank($B76)), N75, "")</f>
         <v/>
       </c>
       <c r="O76" s="11" t="str">
-        <f t="shared" si="298"/>
+        <f t="shared" si="299"/>
         <v/>
       </c>
       <c r="P76" s="11" t="str">
@@ -9079,7 +9079,7 @@
         <v/>
       </c>
       <c r="U76" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V76" s="14" t="str">
@@ -9105,11 +9105,11 @@
         <v/>
       </c>
       <c r="E77" s="11" t="str">
-        <f t="shared" ref="E77:F77" si="299">if(not(isblank($B77)), E76, "")</f>
+        <f t="shared" ref="E77:F77" si="300">if(not(isblank($B77)), E76, "")</f>
         <v/>
       </c>
       <c r="F77" s="11" t="str">
-        <f t="shared" si="299"/>
+        <f t="shared" si="300"/>
         <v/>
       </c>
       <c r="G77" s="11" t="str">
@@ -9117,11 +9117,11 @@
         <v/>
       </c>
       <c r="H77" s="11" t="str">
-        <f t="shared" ref="H77:I77" si="300">if(not(isblank($B77)), H76, "")</f>
+        <f t="shared" ref="H77:I77" si="301">if(not(isblank($B77)), H76, "")</f>
         <v/>
       </c>
       <c r="I77" s="11" t="str">
-        <f t="shared" si="300"/>
+        <f t="shared" si="301"/>
         <v/>
       </c>
       <c r="J77" s="11" t="str">
@@ -9129,11 +9129,11 @@
         <v/>
       </c>
       <c r="K77" s="11" t="str">
-        <f t="shared" ref="K77:L77" si="301">if(not(isblank($B77)), K76, "")</f>
+        <f t="shared" ref="K77:L77" si="302">if(not(isblank($B77)), K76, "")</f>
         <v/>
       </c>
       <c r="L77" s="11" t="str">
-        <f t="shared" si="301"/>
+        <f t="shared" si="302"/>
         <v/>
       </c>
       <c r="M77" s="11" t="str">
@@ -9141,11 +9141,11 @@
         <v/>
       </c>
       <c r="N77" s="11" t="str">
-        <f t="shared" ref="N77:O77" si="302">if(not(isblank($B77)), N76, "")</f>
+        <f t="shared" ref="N77:O77" si="303">if(not(isblank($B77)), N76, "")</f>
         <v/>
       </c>
       <c r="O77" s="11" t="str">
-        <f t="shared" si="302"/>
+        <f t="shared" si="303"/>
         <v/>
       </c>
       <c r="P77" s="11" t="str">
@@ -9166,7 +9166,7 @@
         <v/>
       </c>
       <c r="U77" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V77" s="14" t="str">
@@ -9192,11 +9192,11 @@
         <v/>
       </c>
       <c r="E78" s="11" t="str">
-        <f t="shared" ref="E78:F78" si="303">if(not(isblank($B78)), E77, "")</f>
+        <f t="shared" ref="E78:F78" si="304">if(not(isblank($B78)), E77, "")</f>
         <v/>
       </c>
       <c r="F78" s="11" t="str">
-        <f t="shared" si="303"/>
+        <f t="shared" si="304"/>
         <v/>
       </c>
       <c r="G78" s="11" t="str">
@@ -9204,11 +9204,11 @@
         <v/>
       </c>
       <c r="H78" s="11" t="str">
-        <f t="shared" ref="H78:I78" si="304">if(not(isblank($B78)), H77, "")</f>
+        <f t="shared" ref="H78:I78" si="305">if(not(isblank($B78)), H77, "")</f>
         <v/>
       </c>
       <c r="I78" s="11" t="str">
-        <f t="shared" si="304"/>
+        <f t="shared" si="305"/>
         <v/>
       </c>
       <c r="J78" s="11" t="str">
@@ -9216,11 +9216,11 @@
         <v/>
       </c>
       <c r="K78" s="11" t="str">
-        <f t="shared" ref="K78:L78" si="305">if(not(isblank($B78)), K77, "")</f>
+        <f t="shared" ref="K78:L78" si="306">if(not(isblank($B78)), K77, "")</f>
         <v/>
       </c>
       <c r="L78" s="11" t="str">
-        <f t="shared" si="305"/>
+        <f t="shared" si="306"/>
         <v/>
       </c>
       <c r="M78" s="11" t="str">
@@ -9228,11 +9228,11 @@
         <v/>
       </c>
       <c r="N78" s="11" t="str">
-        <f t="shared" ref="N78:O78" si="306">if(not(isblank($B78)), N77, "")</f>
+        <f t="shared" ref="N78:O78" si="307">if(not(isblank($B78)), N77, "")</f>
         <v/>
       </c>
       <c r="O78" s="11" t="str">
-        <f t="shared" si="306"/>
+        <f t="shared" si="307"/>
         <v/>
       </c>
       <c r="P78" s="11" t="str">
@@ -9253,7 +9253,7 @@
         <v/>
       </c>
       <c r="U78" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V78" s="14" t="str">
@@ -9279,11 +9279,11 @@
         <v/>
       </c>
       <c r="E79" s="11" t="str">
-        <f t="shared" ref="E79:F79" si="307">if(not(isblank($B79)), E78, "")</f>
+        <f t="shared" ref="E79:F79" si="308">if(not(isblank($B79)), E78, "")</f>
         <v/>
       </c>
       <c r="F79" s="11" t="str">
-        <f t="shared" si="307"/>
+        <f t="shared" si="308"/>
         <v/>
       </c>
       <c r="G79" s="11" t="str">
@@ -9291,11 +9291,11 @@
         <v/>
       </c>
       <c r="H79" s="11" t="str">
-        <f t="shared" ref="H79:I79" si="308">if(not(isblank($B79)), H78, "")</f>
+        <f t="shared" ref="H79:I79" si="309">if(not(isblank($B79)), H78, "")</f>
         <v/>
       </c>
       <c r="I79" s="11" t="str">
-        <f t="shared" si="308"/>
+        <f t="shared" si="309"/>
         <v/>
       </c>
       <c r="J79" s="11" t="str">
@@ -9303,11 +9303,11 @@
         <v/>
       </c>
       <c r="K79" s="11" t="str">
-        <f t="shared" ref="K79:L79" si="309">if(not(isblank($B79)), K78, "")</f>
+        <f t="shared" ref="K79:L79" si="310">if(not(isblank($B79)), K78, "")</f>
         <v/>
       </c>
       <c r="L79" s="11" t="str">
-        <f t="shared" si="309"/>
+        <f t="shared" si="310"/>
         <v/>
       </c>
       <c r="M79" s="11" t="str">
@@ -9315,11 +9315,11 @@
         <v/>
       </c>
       <c r="N79" s="11" t="str">
-        <f t="shared" ref="N79:O79" si="310">if(not(isblank($B79)), N78, "")</f>
+        <f t="shared" ref="N79:O79" si="311">if(not(isblank($B79)), N78, "")</f>
         <v/>
       </c>
       <c r="O79" s="11" t="str">
-        <f t="shared" si="310"/>
+        <f t="shared" si="311"/>
         <v/>
       </c>
       <c r="P79" s="11" t="str">
@@ -9340,7 +9340,7 @@
         <v/>
       </c>
       <c r="U79" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V79" s="14" t="str">
@@ -9366,11 +9366,11 @@
         <v/>
       </c>
       <c r="E80" s="11" t="str">
-        <f t="shared" ref="E80:F80" si="311">if(not(isblank($B80)), E79, "")</f>
+        <f t="shared" ref="E80:F80" si="312">if(not(isblank($B80)), E79, "")</f>
         <v/>
       </c>
       <c r="F80" s="11" t="str">
-        <f t="shared" si="311"/>
+        <f t="shared" si="312"/>
         <v/>
       </c>
       <c r="G80" s="11" t="str">
@@ -9378,11 +9378,11 @@
         <v/>
       </c>
       <c r="H80" s="11" t="str">
-        <f t="shared" ref="H80:I80" si="312">if(not(isblank($B80)), H79, "")</f>
+        <f t="shared" ref="H80:I80" si="313">if(not(isblank($B80)), H79, "")</f>
         <v/>
       </c>
       <c r="I80" s="11" t="str">
-        <f t="shared" si="312"/>
+        <f t="shared" si="313"/>
         <v/>
       </c>
       <c r="J80" s="11" t="str">
@@ -9390,11 +9390,11 @@
         <v/>
       </c>
       <c r="K80" s="11" t="str">
-        <f t="shared" ref="K80:L80" si="313">if(not(isblank($B80)), K79, "")</f>
+        <f t="shared" ref="K80:L80" si="314">if(not(isblank($B80)), K79, "")</f>
         <v/>
       </c>
       <c r="L80" s="11" t="str">
-        <f t="shared" si="313"/>
+        <f t="shared" si="314"/>
         <v/>
       </c>
       <c r="M80" s="11" t="str">
@@ -9402,11 +9402,11 @@
         <v/>
       </c>
       <c r="N80" s="11" t="str">
-        <f t="shared" ref="N80:O80" si="314">if(not(isblank($B80)), N79, "")</f>
+        <f t="shared" ref="N80:O80" si="315">if(not(isblank($B80)), N79, "")</f>
         <v/>
       </c>
       <c r="O80" s="11" t="str">
-        <f t="shared" si="314"/>
+        <f t="shared" si="315"/>
         <v/>
       </c>
       <c r="P80" s="11" t="str">
@@ -9427,7 +9427,7 @@
         <v/>
       </c>
       <c r="U80" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V80" s="14" t="str">
@@ -9453,11 +9453,11 @@
         <v/>
       </c>
       <c r="E81" s="11" t="str">
-        <f t="shared" ref="E81:F81" si="315">if(not(isblank($B81)), E80, "")</f>
+        <f t="shared" ref="E81:F81" si="316">if(not(isblank($B81)), E80, "")</f>
         <v/>
       </c>
       <c r="F81" s="11" t="str">
-        <f t="shared" si="315"/>
+        <f t="shared" si="316"/>
         <v/>
       </c>
       <c r="G81" s="11" t="str">
@@ -9465,11 +9465,11 @@
         <v/>
       </c>
       <c r="H81" s="11" t="str">
-        <f t="shared" ref="H81:I81" si="316">if(not(isblank($B81)), H80, "")</f>
+        <f t="shared" ref="H81:I81" si="317">if(not(isblank($B81)), H80, "")</f>
         <v/>
       </c>
       <c r="I81" s="11" t="str">
-        <f t="shared" si="316"/>
+        <f t="shared" si="317"/>
         <v/>
       </c>
       <c r="J81" s="11" t="str">
@@ -9477,11 +9477,11 @@
         <v/>
       </c>
       <c r="K81" s="11" t="str">
-        <f t="shared" ref="K81:L81" si="317">if(not(isblank($B81)), K80, "")</f>
+        <f t="shared" ref="K81:L81" si="318">if(not(isblank($B81)), K80, "")</f>
         <v/>
       </c>
       <c r="L81" s="11" t="str">
-        <f t="shared" si="317"/>
+        <f t="shared" si="318"/>
         <v/>
       </c>
       <c r="M81" s="11" t="str">
@@ -9489,11 +9489,11 @@
         <v/>
       </c>
       <c r="N81" s="11" t="str">
-        <f t="shared" ref="N81:O81" si="318">if(not(isblank($B81)), N80, "")</f>
+        <f t="shared" ref="N81:O81" si="319">if(not(isblank($B81)), N80, "")</f>
         <v/>
       </c>
       <c r="O81" s="11" t="str">
-        <f t="shared" si="318"/>
+        <f t="shared" si="319"/>
         <v/>
       </c>
       <c r="P81" s="11" t="str">
@@ -9514,7 +9514,7 @@
         <v/>
       </c>
       <c r="U81" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V81" s="14" t="str">
@@ -9540,11 +9540,11 @@
         <v/>
       </c>
       <c r="E82" s="11" t="str">
-        <f t="shared" ref="E82:F82" si="319">if(not(isblank($B82)), E81, "")</f>
+        <f t="shared" ref="E82:F82" si="320">if(not(isblank($B82)), E81, "")</f>
         <v/>
       </c>
       <c r="F82" s="11" t="str">
-        <f t="shared" si="319"/>
+        <f t="shared" si="320"/>
         <v/>
       </c>
       <c r="G82" s="11" t="str">
@@ -9552,11 +9552,11 @@
         <v/>
       </c>
       <c r="H82" s="11" t="str">
-        <f t="shared" ref="H82:I82" si="320">if(not(isblank($B82)), H81, "")</f>
+        <f t="shared" ref="H82:I82" si="321">if(not(isblank($B82)), H81, "")</f>
         <v/>
       </c>
       <c r="I82" s="11" t="str">
-        <f t="shared" si="320"/>
+        <f t="shared" si="321"/>
         <v/>
       </c>
       <c r="J82" s="11" t="str">
@@ -9564,11 +9564,11 @@
         <v/>
       </c>
       <c r="K82" s="11" t="str">
-        <f t="shared" ref="K82:L82" si="321">if(not(isblank($B82)), K81, "")</f>
+        <f t="shared" ref="K82:L82" si="322">if(not(isblank($B82)), K81, "")</f>
         <v/>
       </c>
       <c r="L82" s="11" t="str">
-        <f t="shared" si="321"/>
+        <f t="shared" si="322"/>
         <v/>
       </c>
       <c r="M82" s="11" t="str">
@@ -9576,11 +9576,11 @@
         <v/>
       </c>
       <c r="N82" s="11" t="str">
-        <f t="shared" ref="N82:O82" si="322">if(not(isblank($B82)), N81, "")</f>
+        <f t="shared" ref="N82:O82" si="323">if(not(isblank($B82)), N81, "")</f>
         <v/>
       </c>
       <c r="O82" s="11" t="str">
-        <f t="shared" si="322"/>
+        <f t="shared" si="323"/>
         <v/>
       </c>
       <c r="P82" s="11" t="str">
@@ -9601,7 +9601,7 @@
         <v/>
       </c>
       <c r="U82" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V82" s="14" t="str">
@@ -9627,11 +9627,11 @@
         <v/>
       </c>
       <c r="E83" s="11" t="str">
-        <f t="shared" ref="E83:F83" si="323">if(not(isblank($B83)), E82, "")</f>
+        <f t="shared" ref="E83:F83" si="324">if(not(isblank($B83)), E82, "")</f>
         <v/>
       </c>
       <c r="F83" s="11" t="str">
-        <f t="shared" si="323"/>
+        <f t="shared" si="324"/>
         <v/>
       </c>
       <c r="G83" s="11" t="str">
@@ -9639,11 +9639,11 @@
         <v/>
       </c>
       <c r="H83" s="11" t="str">
-        <f t="shared" ref="H83:I83" si="324">if(not(isblank($B83)), H82, "")</f>
+        <f t="shared" ref="H83:I83" si="325">if(not(isblank($B83)), H82, "")</f>
         <v/>
       </c>
       <c r="I83" s="11" t="str">
-        <f t="shared" si="324"/>
+        <f t="shared" si="325"/>
         <v/>
       </c>
       <c r="J83" s="11" t="str">
@@ -9651,11 +9651,11 @@
         <v/>
       </c>
       <c r="K83" s="11" t="str">
-        <f t="shared" ref="K83:L83" si="325">if(not(isblank($B83)), K82, "")</f>
+        <f t="shared" ref="K83:L83" si="326">if(not(isblank($B83)), K82, "")</f>
         <v/>
       </c>
       <c r="L83" s="11" t="str">
-        <f t="shared" si="325"/>
+        <f t="shared" si="326"/>
         <v/>
       </c>
       <c r="M83" s="11" t="str">
@@ -9663,11 +9663,11 @@
         <v/>
       </c>
       <c r="N83" s="11" t="str">
-        <f t="shared" ref="N83:O83" si="326">if(not(isblank($B83)), N82, "")</f>
+        <f t="shared" ref="N83:O83" si="327">if(not(isblank($B83)), N82, "")</f>
         <v/>
       </c>
       <c r="O83" s="11" t="str">
-        <f t="shared" si="326"/>
+        <f t="shared" si="327"/>
         <v/>
       </c>
       <c r="P83" s="11" t="str">
@@ -9688,7 +9688,7 @@
         <v/>
       </c>
       <c r="U83" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V83" s="14" t="str">
@@ -9714,11 +9714,11 @@
         <v/>
       </c>
       <c r="E84" s="11" t="str">
-        <f t="shared" ref="E84:F84" si="327">if(not(isblank($B84)), E83, "")</f>
+        <f t="shared" ref="E84:F84" si="328">if(not(isblank($B84)), E83, "")</f>
         <v/>
       </c>
       <c r="F84" s="11" t="str">
-        <f t="shared" si="327"/>
+        <f t="shared" si="328"/>
         <v/>
       </c>
       <c r="G84" s="11" t="str">
@@ -9726,11 +9726,11 @@
         <v/>
       </c>
       <c r="H84" s="11" t="str">
-        <f t="shared" ref="H84:I84" si="328">if(not(isblank($B84)), H83, "")</f>
+        <f t="shared" ref="H84:I84" si="329">if(not(isblank($B84)), H83, "")</f>
         <v/>
       </c>
       <c r="I84" s="11" t="str">
-        <f t="shared" si="328"/>
+        <f t="shared" si="329"/>
         <v/>
       </c>
       <c r="J84" s="11" t="str">
@@ -9738,11 +9738,11 @@
         <v/>
       </c>
       <c r="K84" s="11" t="str">
-        <f t="shared" ref="K84:L84" si="329">if(not(isblank($B84)), K83, "")</f>
+        <f t="shared" ref="K84:L84" si="330">if(not(isblank($B84)), K83, "")</f>
         <v/>
       </c>
       <c r="L84" s="11" t="str">
-        <f t="shared" si="329"/>
+        <f t="shared" si="330"/>
         <v/>
       </c>
       <c r="M84" s="11" t="str">
@@ -9750,11 +9750,11 @@
         <v/>
       </c>
       <c r="N84" s="11" t="str">
-        <f t="shared" ref="N84:O84" si="330">if(not(isblank($B84)), N83, "")</f>
+        <f t="shared" ref="N84:O84" si="331">if(not(isblank($B84)), N83, "")</f>
         <v/>
       </c>
       <c r="O84" s="11" t="str">
-        <f t="shared" si="330"/>
+        <f t="shared" si="331"/>
         <v/>
       </c>
       <c r="P84" s="11" t="str">
@@ -9775,7 +9775,7 @@
         <v/>
       </c>
       <c r="U84" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V84" s="14" t="str">
@@ -9801,11 +9801,11 @@
         <v/>
       </c>
       <c r="E85" s="11" t="str">
-        <f t="shared" ref="E85:F85" si="331">if(not(isblank($B85)), E84, "")</f>
+        <f t="shared" ref="E85:F85" si="332">if(not(isblank($B85)), E84, "")</f>
         <v/>
       </c>
       <c r="F85" s="11" t="str">
-        <f t="shared" si="331"/>
+        <f t="shared" si="332"/>
         <v/>
       </c>
       <c r="G85" s="11" t="str">
@@ -9813,11 +9813,11 @@
         <v/>
       </c>
       <c r="H85" s="11" t="str">
-        <f t="shared" ref="H85:I85" si="332">if(not(isblank($B85)), H84, "")</f>
+        <f t="shared" ref="H85:I85" si="333">if(not(isblank($B85)), H84, "")</f>
         <v/>
       </c>
       <c r="I85" s="11" t="str">
-        <f t="shared" si="332"/>
+        <f t="shared" si="333"/>
         <v/>
       </c>
       <c r="J85" s="11" t="str">
@@ -9825,11 +9825,11 @@
         <v/>
       </c>
       <c r="K85" s="11" t="str">
-        <f t="shared" ref="K85:L85" si="333">if(not(isblank($B85)), K84, "")</f>
+        <f t="shared" ref="K85:L85" si="334">if(not(isblank($B85)), K84, "")</f>
         <v/>
       </c>
       <c r="L85" s="11" t="str">
-        <f t="shared" si="333"/>
+        <f t="shared" si="334"/>
         <v/>
       </c>
       <c r="M85" s="11" t="str">
@@ -9837,11 +9837,11 @@
         <v/>
       </c>
       <c r="N85" s="11" t="str">
-        <f t="shared" ref="N85:O85" si="334">if(not(isblank($B85)), N84, "")</f>
+        <f t="shared" ref="N85:O85" si="335">if(not(isblank($B85)), N84, "")</f>
         <v/>
       </c>
       <c r="O85" s="11" t="str">
-        <f t="shared" si="334"/>
+        <f t="shared" si="335"/>
         <v/>
       </c>
       <c r="P85" s="11" t="str">
@@ -9862,7 +9862,7 @@
         <v/>
       </c>
       <c r="U85" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V85" s="14" t="str">
@@ -9888,11 +9888,11 @@
         <v/>
       </c>
       <c r="E86" s="11" t="str">
-        <f t="shared" ref="E86:F86" si="335">if(not(isblank($B86)), E85, "")</f>
+        <f t="shared" ref="E86:F86" si="336">if(not(isblank($B86)), E85, "")</f>
         <v/>
       </c>
       <c r="F86" s="11" t="str">
-        <f t="shared" si="335"/>
+        <f t="shared" si="336"/>
         <v/>
       </c>
       <c r="G86" s="11" t="str">
@@ -9900,11 +9900,11 @@
         <v/>
       </c>
       <c r="H86" s="11" t="str">
-        <f t="shared" ref="H86:I86" si="336">if(not(isblank($B86)), H85, "")</f>
+        <f t="shared" ref="H86:I86" si="337">if(not(isblank($B86)), H85, "")</f>
         <v/>
       </c>
       <c r="I86" s="11" t="str">
-        <f t="shared" si="336"/>
+        <f t="shared" si="337"/>
         <v/>
       </c>
       <c r="J86" s="11" t="str">
@@ -9912,11 +9912,11 @@
         <v/>
       </c>
       <c r="K86" s="11" t="str">
-        <f t="shared" ref="K86:L86" si="337">if(not(isblank($B86)), K85, "")</f>
+        <f t="shared" ref="K86:L86" si="338">if(not(isblank($B86)), K85, "")</f>
         <v/>
       </c>
       <c r="L86" s="11" t="str">
-        <f t="shared" si="337"/>
+        <f t="shared" si="338"/>
         <v/>
       </c>
       <c r="M86" s="11" t="str">
@@ -9924,11 +9924,11 @@
         <v/>
       </c>
       <c r="N86" s="11" t="str">
-        <f t="shared" ref="N86:O86" si="338">if(not(isblank($B86)), N85, "")</f>
+        <f t="shared" ref="N86:O86" si="339">if(not(isblank($B86)), N85, "")</f>
         <v/>
       </c>
       <c r="O86" s="11" t="str">
-        <f t="shared" si="338"/>
+        <f t="shared" si="339"/>
         <v/>
       </c>
       <c r="P86" s="11" t="str">
@@ -9949,7 +9949,7 @@
         <v/>
       </c>
       <c r="U86" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V86" s="14" t="str">
@@ -9975,11 +9975,11 @@
         <v/>
       </c>
       <c r="E87" s="11" t="str">
-        <f t="shared" ref="E87:F87" si="339">if(not(isblank($B87)), E86, "")</f>
+        <f t="shared" ref="E87:F87" si="340">if(not(isblank($B87)), E86, "")</f>
         <v/>
       </c>
       <c r="F87" s="11" t="str">
-        <f t="shared" si="339"/>
+        <f t="shared" si="340"/>
         <v/>
       </c>
       <c r="G87" s="11" t="str">
@@ -9987,11 +9987,11 @@
         <v/>
       </c>
       <c r="H87" s="11" t="str">
-        <f t="shared" ref="H87:I87" si="340">if(not(isblank($B87)), H86, "")</f>
+        <f t="shared" ref="H87:I87" si="341">if(not(isblank($B87)), H86, "")</f>
         <v/>
       </c>
       <c r="I87" s="11" t="str">
-        <f t="shared" si="340"/>
+        <f t="shared" si="341"/>
         <v/>
       </c>
       <c r="J87" s="11" t="str">
@@ -9999,11 +9999,11 @@
         <v/>
       </c>
       <c r="K87" s="11" t="str">
-        <f t="shared" ref="K87:L87" si="341">if(not(isblank($B87)), K86, "")</f>
+        <f t="shared" ref="K87:L87" si="342">if(not(isblank($B87)), K86, "")</f>
         <v/>
       </c>
       <c r="L87" s="11" t="str">
-        <f t="shared" si="341"/>
+        <f t="shared" si="342"/>
         <v/>
       </c>
       <c r="M87" s="11" t="str">
@@ -10011,11 +10011,11 @@
         <v/>
       </c>
       <c r="N87" s="11" t="str">
-        <f t="shared" ref="N87:O87" si="342">if(not(isblank($B87)), N86, "")</f>
+        <f t="shared" ref="N87:O87" si="343">if(not(isblank($B87)), N86, "")</f>
         <v/>
       </c>
       <c r="O87" s="11" t="str">
-        <f t="shared" si="342"/>
+        <f t="shared" si="343"/>
         <v/>
       </c>
       <c r="P87" s="11" t="str">
@@ -10036,7 +10036,7 @@
         <v/>
       </c>
       <c r="U87" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V87" s="14" t="str">
@@ -10062,11 +10062,11 @@
         <v/>
       </c>
       <c r="E88" s="11" t="str">
-        <f t="shared" ref="E88:F88" si="343">if(not(isblank($B88)), E87, "")</f>
+        <f t="shared" ref="E88:F88" si="344">if(not(isblank($B88)), E87, "")</f>
         <v/>
       </c>
       <c r="F88" s="11" t="str">
-        <f t="shared" si="343"/>
+        <f t="shared" si="344"/>
         <v/>
       </c>
       <c r="G88" s="11" t="str">
@@ -10074,11 +10074,11 @@
         <v/>
       </c>
       <c r="H88" s="11" t="str">
-        <f t="shared" ref="H88:I88" si="344">if(not(isblank($B88)), H87, "")</f>
+        <f t="shared" ref="H88:I88" si="345">if(not(isblank($B88)), H87, "")</f>
         <v/>
       </c>
       <c r="I88" s="11" t="str">
-        <f t="shared" si="344"/>
+        <f t="shared" si="345"/>
         <v/>
       </c>
       <c r="J88" s="11" t="str">
@@ -10086,11 +10086,11 @@
         <v/>
       </c>
       <c r="K88" s="11" t="str">
-        <f t="shared" ref="K88:L88" si="345">if(not(isblank($B88)), K87, "")</f>
+        <f t="shared" ref="K88:L88" si="346">if(not(isblank($B88)), K87, "")</f>
         <v/>
       </c>
       <c r="L88" s="11" t="str">
-        <f t="shared" si="345"/>
+        <f t="shared" si="346"/>
         <v/>
       </c>
       <c r="M88" s="11" t="str">
@@ -10098,11 +10098,11 @@
         <v/>
       </c>
       <c r="N88" s="11" t="str">
-        <f t="shared" ref="N88:O88" si="346">if(not(isblank($B88)), N87, "")</f>
+        <f t="shared" ref="N88:O88" si="347">if(not(isblank($B88)), N87, "")</f>
         <v/>
       </c>
       <c r="O88" s="11" t="str">
-        <f t="shared" si="346"/>
+        <f t="shared" si="347"/>
         <v/>
       </c>
       <c r="P88" s="11" t="str">
@@ -10123,7 +10123,7 @@
         <v/>
       </c>
       <c r="U88" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V88" s="14" t="str">
@@ -10149,11 +10149,11 @@
         <v/>
       </c>
       <c r="E89" s="11" t="str">
-        <f t="shared" ref="E89:F89" si="347">if(not(isblank($B89)), E88, "")</f>
+        <f t="shared" ref="E89:F89" si="348">if(not(isblank($B89)), E88, "")</f>
         <v/>
       </c>
       <c r="F89" s="11" t="str">
-        <f t="shared" si="347"/>
+        <f t="shared" si="348"/>
         <v/>
       </c>
       <c r="G89" s="11" t="str">
@@ -10161,11 +10161,11 @@
         <v/>
       </c>
       <c r="H89" s="11" t="str">
-        <f t="shared" ref="H89:I89" si="348">if(not(isblank($B89)), H88, "")</f>
+        <f t="shared" ref="H89:I89" si="349">if(not(isblank($B89)), H88, "")</f>
         <v/>
       </c>
       <c r="I89" s="11" t="str">
-        <f t="shared" si="348"/>
+        <f t="shared" si="349"/>
         <v/>
       </c>
       <c r="J89" s="11" t="str">
@@ -10173,11 +10173,11 @@
         <v/>
       </c>
       <c r="K89" s="11" t="str">
-        <f t="shared" ref="K89:L89" si="349">if(not(isblank($B89)), K88, "")</f>
+        <f t="shared" ref="K89:L89" si="350">if(not(isblank($B89)), K88, "")</f>
         <v/>
       </c>
       <c r="L89" s="11" t="str">
-        <f t="shared" si="349"/>
+        <f t="shared" si="350"/>
         <v/>
       </c>
       <c r="M89" s="11" t="str">
@@ -10185,11 +10185,11 @@
         <v/>
       </c>
       <c r="N89" s="11" t="str">
-        <f t="shared" ref="N89:O89" si="350">if(not(isblank($B89)), N88, "")</f>
+        <f t="shared" ref="N89:O89" si="351">if(not(isblank($B89)), N88, "")</f>
         <v/>
       </c>
       <c r="O89" s="11" t="str">
-        <f t="shared" si="350"/>
+        <f t="shared" si="351"/>
         <v/>
       </c>
       <c r="P89" s="11" t="str">
@@ -10210,7 +10210,7 @@
         <v/>
       </c>
       <c r="U89" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V89" s="14" t="str">
@@ -10236,11 +10236,11 @@
         <v/>
       </c>
       <c r="E90" s="11" t="str">
-        <f t="shared" ref="E90:F90" si="351">if(not(isblank($B90)), E89, "")</f>
+        <f t="shared" ref="E90:F90" si="352">if(not(isblank($B90)), E89, "")</f>
         <v/>
       </c>
       <c r="F90" s="11" t="str">
-        <f t="shared" si="351"/>
+        <f t="shared" si="352"/>
         <v/>
       </c>
       <c r="G90" s="11" t="str">
@@ -10248,11 +10248,11 @@
         <v/>
       </c>
       <c r="H90" s="11" t="str">
-        <f t="shared" ref="H90:I90" si="352">if(not(isblank($B90)), H89, "")</f>
+        <f t="shared" ref="H90:I90" si="353">if(not(isblank($B90)), H89, "")</f>
         <v/>
       </c>
       <c r="I90" s="11" t="str">
-        <f t="shared" si="352"/>
+        <f t="shared" si="353"/>
         <v/>
       </c>
       <c r="J90" s="11" t="str">
@@ -10260,11 +10260,11 @@
         <v/>
       </c>
       <c r="K90" s="11" t="str">
-        <f t="shared" ref="K90:L90" si="353">if(not(isblank($B90)), K89, "")</f>
+        <f t="shared" ref="K90:L90" si="354">if(not(isblank($B90)), K89, "")</f>
         <v/>
       </c>
       <c r="L90" s="11" t="str">
-        <f t="shared" si="353"/>
+        <f t="shared" si="354"/>
         <v/>
       </c>
       <c r="M90" s="11" t="str">
@@ -10272,11 +10272,11 @@
         <v/>
       </c>
       <c r="N90" s="11" t="str">
-        <f t="shared" ref="N90:O90" si="354">if(not(isblank($B90)), N89, "")</f>
+        <f t="shared" ref="N90:O90" si="355">if(not(isblank($B90)), N89, "")</f>
         <v/>
       </c>
       <c r="O90" s="11" t="str">
-        <f t="shared" si="354"/>
+        <f t="shared" si="355"/>
         <v/>
       </c>
       <c r="P90" s="11" t="str">
@@ -10297,7 +10297,7 @@
         <v/>
       </c>
       <c r="U90" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V90" s="14" t="str">
@@ -10323,11 +10323,11 @@
         <v/>
       </c>
       <c r="E91" s="11" t="str">
-        <f t="shared" ref="E91:F91" si="355">if(not(isblank($B91)), E90, "")</f>
+        <f t="shared" ref="E91:F91" si="356">if(not(isblank($B91)), E90, "")</f>
         <v/>
       </c>
       <c r="F91" s="11" t="str">
-        <f t="shared" si="355"/>
+        <f t="shared" si="356"/>
         <v/>
       </c>
       <c r="G91" s="11" t="str">
@@ -10335,11 +10335,11 @@
         <v/>
       </c>
       <c r="H91" s="11" t="str">
-        <f t="shared" ref="H91:I91" si="356">if(not(isblank($B91)), H90, "")</f>
+        <f t="shared" ref="H91:I91" si="357">if(not(isblank($B91)), H90, "")</f>
         <v/>
       </c>
       <c r="I91" s="11" t="str">
-        <f t="shared" si="356"/>
+        <f t="shared" si="357"/>
         <v/>
       </c>
       <c r="J91" s="11" t="str">
@@ -10347,11 +10347,11 @@
         <v/>
       </c>
       <c r="K91" s="11" t="str">
-        <f t="shared" ref="K91:L91" si="357">if(not(isblank($B91)), K90, "")</f>
+        <f t="shared" ref="K91:L91" si="358">if(not(isblank($B91)), K90, "")</f>
         <v/>
       </c>
       <c r="L91" s="11" t="str">
-        <f t="shared" si="357"/>
+        <f t="shared" si="358"/>
         <v/>
       </c>
       <c r="M91" s="11" t="str">
@@ -10359,11 +10359,11 @@
         <v/>
       </c>
       <c r="N91" s="11" t="str">
-        <f t="shared" ref="N91:O91" si="358">if(not(isblank($B91)), N90, "")</f>
+        <f t="shared" ref="N91:O91" si="359">if(not(isblank($B91)), N90, "")</f>
         <v/>
       </c>
       <c r="O91" s="11" t="str">
-        <f t="shared" si="358"/>
+        <f t="shared" si="359"/>
         <v/>
       </c>
       <c r="P91" s="11" t="str">
@@ -10384,7 +10384,7 @@
         <v/>
       </c>
       <c r="U91" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V91" s="14" t="str">
@@ -10410,11 +10410,11 @@
         <v/>
       </c>
       <c r="E92" s="11" t="str">
-        <f t="shared" ref="E92:F92" si="359">if(not(isblank($B92)), E91, "")</f>
+        <f t="shared" ref="E92:F92" si="360">if(not(isblank($B92)), E91, "")</f>
         <v/>
       </c>
       <c r="F92" s="11" t="str">
-        <f t="shared" si="359"/>
+        <f t="shared" si="360"/>
         <v/>
       </c>
       <c r="G92" s="11" t="str">
@@ -10422,11 +10422,11 @@
         <v/>
       </c>
       <c r="H92" s="11" t="str">
-        <f t="shared" ref="H92:I92" si="360">if(not(isblank($B92)), H91, "")</f>
+        <f t="shared" ref="H92:I92" si="361">if(not(isblank($B92)), H91, "")</f>
         <v/>
       </c>
       <c r="I92" s="11" t="str">
-        <f t="shared" si="360"/>
+        <f t="shared" si="361"/>
         <v/>
       </c>
       <c r="J92" s="11" t="str">
@@ -10434,11 +10434,11 @@
         <v/>
       </c>
       <c r="K92" s="11" t="str">
-        <f t="shared" ref="K92:L92" si="361">if(not(isblank($B92)), K91, "")</f>
+        <f t="shared" ref="K92:L92" si="362">if(not(isblank($B92)), K91, "")</f>
         <v/>
       </c>
       <c r="L92" s="11" t="str">
-        <f t="shared" si="361"/>
+        <f t="shared" si="362"/>
         <v/>
       </c>
       <c r="M92" s="11" t="str">
@@ -10446,11 +10446,11 @@
         <v/>
       </c>
       <c r="N92" s="11" t="str">
-        <f t="shared" ref="N92:O92" si="362">if(not(isblank($B92)), N91, "")</f>
+        <f t="shared" ref="N92:O92" si="363">if(not(isblank($B92)), N91, "")</f>
         <v/>
       </c>
       <c r="O92" s="11" t="str">
-        <f t="shared" si="362"/>
+        <f t="shared" si="363"/>
         <v/>
       </c>
       <c r="P92" s="11" t="str">
@@ -10471,7 +10471,7 @@
         <v/>
       </c>
       <c r="U92" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V92" s="14" t="str">
@@ -10497,11 +10497,11 @@
         <v/>
       </c>
       <c r="E93" s="11" t="str">
-        <f t="shared" ref="E93:F93" si="363">if(not(isblank($B93)), E92, "")</f>
+        <f t="shared" ref="E93:F93" si="364">if(not(isblank($B93)), E92, "")</f>
         <v/>
       </c>
       <c r="F93" s="11" t="str">
-        <f t="shared" si="363"/>
+        <f t="shared" si="364"/>
         <v/>
       </c>
       <c r="G93" s="11" t="str">
@@ -10509,11 +10509,11 @@
         <v/>
       </c>
       <c r="H93" s="11" t="str">
-        <f t="shared" ref="H93:I93" si="364">if(not(isblank($B93)), H92, "")</f>
+        <f t="shared" ref="H93:I93" si="365">if(not(isblank($B93)), H92, "")</f>
         <v/>
       </c>
       <c r="I93" s="11" t="str">
-        <f t="shared" si="364"/>
+        <f t="shared" si="365"/>
         <v/>
       </c>
       <c r="J93" s="11" t="str">
@@ -10521,11 +10521,11 @@
         <v/>
       </c>
       <c r="K93" s="11" t="str">
-        <f t="shared" ref="K93:L93" si="365">if(not(isblank($B93)), K92, "")</f>
+        <f t="shared" ref="K93:L93" si="366">if(not(isblank($B93)), K92, "")</f>
         <v/>
       </c>
       <c r="L93" s="11" t="str">
-        <f t="shared" si="365"/>
+        <f t="shared" si="366"/>
         <v/>
       </c>
       <c r="M93" s="11" t="str">
@@ -10533,11 +10533,11 @@
         <v/>
       </c>
       <c r="N93" s="11" t="str">
-        <f t="shared" ref="N93:O93" si="366">if(not(isblank($B93)), N92, "")</f>
+        <f t="shared" ref="N93:O93" si="367">if(not(isblank($B93)), N92, "")</f>
         <v/>
       </c>
       <c r="O93" s="11" t="str">
-        <f t="shared" si="366"/>
+        <f t="shared" si="367"/>
         <v/>
       </c>
       <c r="P93" s="11" t="str">
@@ -10558,7 +10558,7 @@
         <v/>
       </c>
       <c r="U93" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V93" s="14" t="str">
@@ -10584,11 +10584,11 @@
         <v/>
       </c>
       <c r="E94" s="11" t="str">
-        <f t="shared" ref="E94:F94" si="367">if(not(isblank($B94)), E93, "")</f>
+        <f t="shared" ref="E94:F94" si="368">if(not(isblank($B94)), E93, "")</f>
         <v/>
       </c>
       <c r="F94" s="11" t="str">
-        <f t="shared" si="367"/>
+        <f t="shared" si="368"/>
         <v/>
       </c>
       <c r="G94" s="11" t="str">
@@ -10596,11 +10596,11 @@
         <v/>
       </c>
       <c r="H94" s="11" t="str">
-        <f t="shared" ref="H94:I94" si="368">if(not(isblank($B94)), H93, "")</f>
+        <f t="shared" ref="H94:I94" si="369">if(not(isblank($B94)), H93, "")</f>
         <v/>
       </c>
       <c r="I94" s="11" t="str">
-        <f t="shared" si="368"/>
+        <f t="shared" si="369"/>
         <v/>
       </c>
       <c r="J94" s="11" t="str">
@@ -10608,11 +10608,11 @@
         <v/>
       </c>
       <c r="K94" s="11" t="str">
-        <f t="shared" ref="K94:L94" si="369">if(not(isblank($B94)), K93, "")</f>
+        <f t="shared" ref="K94:L94" si="370">if(not(isblank($B94)), K93, "")</f>
         <v/>
       </c>
       <c r="L94" s="11" t="str">
-        <f t="shared" si="369"/>
+        <f t="shared" si="370"/>
         <v/>
       </c>
       <c r="M94" s="11" t="str">
@@ -10620,11 +10620,11 @@
         <v/>
       </c>
       <c r="N94" s="11" t="str">
-        <f t="shared" ref="N94:O94" si="370">if(not(isblank($B94)), N93, "")</f>
+        <f t="shared" ref="N94:O94" si="371">if(not(isblank($B94)), N93, "")</f>
         <v/>
       </c>
       <c r="O94" s="11" t="str">
-        <f t="shared" si="370"/>
+        <f t="shared" si="371"/>
         <v/>
       </c>
       <c r="P94" s="11" t="str">
@@ -10645,7 +10645,7 @@
         <v/>
       </c>
       <c r="U94" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V94" s="14" t="str">
@@ -10671,11 +10671,11 @@
         <v/>
       </c>
       <c r="E95" s="11" t="str">
-        <f t="shared" ref="E95:F95" si="371">if(not(isblank($B95)), E94, "")</f>
+        <f t="shared" ref="E95:F95" si="372">if(not(isblank($B95)), E94, "")</f>
         <v/>
       </c>
       <c r="F95" s="11" t="str">
-        <f t="shared" si="371"/>
+        <f t="shared" si="372"/>
         <v/>
       </c>
       <c r="G95" s="11" t="str">
@@ -10683,11 +10683,11 @@
         <v/>
       </c>
       <c r="H95" s="11" t="str">
-        <f t="shared" ref="H95:I95" si="372">if(not(isblank($B95)), H94, "")</f>
+        <f t="shared" ref="H95:I95" si="373">if(not(isblank($B95)), H94, "")</f>
         <v/>
       </c>
       <c r="I95" s="11" t="str">
-        <f t="shared" si="372"/>
+        <f t="shared" si="373"/>
         <v/>
       </c>
       <c r="J95" s="11" t="str">
@@ -10695,11 +10695,11 @@
         <v/>
       </c>
       <c r="K95" s="11" t="str">
-        <f t="shared" ref="K95:L95" si="373">if(not(isblank($B95)), K94, "")</f>
+        <f t="shared" ref="K95:L95" si="374">if(not(isblank($B95)), K94, "")</f>
         <v/>
       </c>
       <c r="L95" s="11" t="str">
-        <f t="shared" si="373"/>
+        <f t="shared" si="374"/>
         <v/>
       </c>
       <c r="M95" s="11" t="str">
@@ -10707,11 +10707,11 @@
         <v/>
       </c>
       <c r="N95" s="11" t="str">
-        <f t="shared" ref="N95:O95" si="374">if(not(isblank($B95)), N94, "")</f>
+        <f t="shared" ref="N95:O95" si="375">if(not(isblank($B95)), N94, "")</f>
         <v/>
       </c>
       <c r="O95" s="11" t="str">
-        <f t="shared" si="374"/>
+        <f t="shared" si="375"/>
         <v/>
       </c>
       <c r="P95" s="11" t="str">
@@ -10732,7 +10732,7 @@
         <v/>
       </c>
       <c r="U95" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V95" s="14" t="str">
@@ -10758,11 +10758,11 @@
         <v/>
       </c>
       <c r="E96" s="11" t="str">
-        <f t="shared" ref="E96:F96" si="375">if(not(isblank($B96)), E95, "")</f>
+        <f t="shared" ref="E96:F96" si="376">if(not(isblank($B96)), E95, "")</f>
         <v/>
       </c>
       <c r="F96" s="11" t="str">
-        <f t="shared" si="375"/>
+        <f t="shared" si="376"/>
         <v/>
       </c>
       <c r="G96" s="11" t="str">
@@ -10770,11 +10770,11 @@
         <v/>
       </c>
       <c r="H96" s="11" t="str">
-        <f t="shared" ref="H96:I96" si="376">if(not(isblank($B96)), H95, "")</f>
+        <f t="shared" ref="H96:I96" si="377">if(not(isblank($B96)), H95, "")</f>
         <v/>
       </c>
       <c r="I96" s="11" t="str">
-        <f t="shared" si="376"/>
+        <f t="shared" si="377"/>
         <v/>
       </c>
       <c r="J96" s="11" t="str">
@@ -10782,11 +10782,11 @@
         <v/>
       </c>
       <c r="K96" s="11" t="str">
-        <f t="shared" ref="K96:L96" si="377">if(not(isblank($B96)), K95, "")</f>
+        <f t="shared" ref="K96:L96" si="378">if(not(isblank($B96)), K95, "")</f>
         <v/>
       </c>
       <c r="L96" s="11" t="str">
-        <f t="shared" si="377"/>
+        <f t="shared" si="378"/>
         <v/>
       </c>
       <c r="M96" s="11" t="str">
@@ -10794,11 +10794,11 @@
         <v/>
       </c>
       <c r="N96" s="11" t="str">
-        <f t="shared" ref="N96:O96" si="378">if(not(isblank($B96)), N95, "")</f>
+        <f t="shared" ref="N96:O96" si="379">if(not(isblank($B96)), N95, "")</f>
         <v/>
       </c>
       <c r="O96" s="11" t="str">
-        <f t="shared" si="378"/>
+        <f t="shared" si="379"/>
         <v/>
       </c>
       <c r="P96" s="11" t="str">
@@ -10819,7 +10819,7 @@
         <v/>
       </c>
       <c r="U96" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V96" s="14" t="str">
@@ -10845,11 +10845,11 @@
         <v/>
       </c>
       <c r="E97" s="11" t="str">
-        <f t="shared" ref="E97:F97" si="379">if(not(isblank($B97)), E96, "")</f>
+        <f t="shared" ref="E97:F97" si="380">if(not(isblank($B97)), E96, "")</f>
         <v/>
       </c>
       <c r="F97" s="11" t="str">
-        <f t="shared" si="379"/>
+        <f t="shared" si="380"/>
         <v/>
       </c>
       <c r="G97" s="11" t="str">
@@ -10857,11 +10857,11 @@
         <v/>
       </c>
       <c r="H97" s="11" t="str">
-        <f t="shared" ref="H97:I97" si="380">if(not(isblank($B97)), H96, "")</f>
+        <f t="shared" ref="H97:I97" si="381">if(not(isblank($B97)), H96, "")</f>
         <v/>
       </c>
       <c r="I97" s="11" t="str">
-        <f t="shared" si="380"/>
+        <f t="shared" si="381"/>
         <v/>
       </c>
       <c r="J97" s="11" t="str">
@@ -10869,11 +10869,11 @@
         <v/>
       </c>
       <c r="K97" s="11" t="str">
-        <f t="shared" ref="K97:L97" si="381">if(not(isblank($B97)), K96, "")</f>
+        <f t="shared" ref="K97:L97" si="382">if(not(isblank($B97)), K96, "")</f>
         <v/>
       </c>
       <c r="L97" s="11" t="str">
-        <f t="shared" si="381"/>
+        <f t="shared" si="382"/>
         <v/>
       </c>
       <c r="M97" s="11" t="str">
@@ -10881,11 +10881,11 @@
         <v/>
       </c>
       <c r="N97" s="11" t="str">
-        <f t="shared" ref="N97:O97" si="382">if(not(isblank($B97)), N96, "")</f>
+        <f t="shared" ref="N97:O97" si="383">if(not(isblank($B97)), N96, "")</f>
         <v/>
       </c>
       <c r="O97" s="11" t="str">
-        <f t="shared" si="382"/>
+        <f t="shared" si="383"/>
         <v/>
       </c>
       <c r="P97" s="11" t="str">
@@ -10906,7 +10906,7 @@
         <v/>
       </c>
       <c r="U97" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V97" s="14" t="str">
@@ -10932,11 +10932,11 @@
         <v/>
       </c>
       <c r="E98" s="11" t="str">
-        <f t="shared" ref="E98:F98" si="383">if(not(isblank($B98)), E97, "")</f>
+        <f t="shared" ref="E98:F98" si="384">if(not(isblank($B98)), E97, "")</f>
         <v/>
       </c>
       <c r="F98" s="11" t="str">
-        <f t="shared" si="383"/>
+        <f t="shared" si="384"/>
         <v/>
       </c>
       <c r="G98" s="11" t="str">
@@ -10944,11 +10944,11 @@
         <v/>
       </c>
       <c r="H98" s="11" t="str">
-        <f t="shared" ref="H98:I98" si="384">if(not(isblank($B98)), H97, "")</f>
+        <f t="shared" ref="H98:I98" si="385">if(not(isblank($B98)), H97, "")</f>
         <v/>
       </c>
       <c r="I98" s="11" t="str">
-        <f t="shared" si="384"/>
+        <f t="shared" si="385"/>
         <v/>
       </c>
       <c r="J98" s="11" t="str">
@@ -10956,11 +10956,11 @@
         <v/>
       </c>
       <c r="K98" s="11" t="str">
-        <f t="shared" ref="K98:L98" si="385">if(not(isblank($B98)), K97, "")</f>
+        <f t="shared" ref="K98:L98" si="386">if(not(isblank($B98)), K97, "")</f>
         <v/>
       </c>
       <c r="L98" s="11" t="str">
-        <f t="shared" si="385"/>
+        <f t="shared" si="386"/>
         <v/>
       </c>
       <c r="M98" s="11" t="str">
@@ -10968,11 +10968,11 @@
         <v/>
       </c>
       <c r="N98" s="11" t="str">
-        <f t="shared" ref="N98:O98" si="386">if(not(isblank($B98)), N97, "")</f>
+        <f t="shared" ref="N98:O98" si="387">if(not(isblank($B98)), N97, "")</f>
         <v/>
       </c>
       <c r="O98" s="11" t="str">
-        <f t="shared" si="386"/>
+        <f t="shared" si="387"/>
         <v/>
       </c>
       <c r="P98" s="11" t="str">
@@ -10993,7 +10993,7 @@
         <v/>
       </c>
       <c r="U98" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V98" s="14" t="str">
@@ -11019,11 +11019,11 @@
         <v/>
       </c>
       <c r="E99" s="11" t="str">
-        <f t="shared" ref="E99:F99" si="387">if(not(isblank($B99)), E98, "")</f>
+        <f t="shared" ref="E99:F99" si="388">if(not(isblank($B99)), E98, "")</f>
         <v/>
       </c>
       <c r="F99" s="11" t="str">
-        <f t="shared" si="387"/>
+        <f t="shared" si="388"/>
         <v/>
       </c>
       <c r="G99" s="11" t="str">
@@ -11031,11 +11031,11 @@
         <v/>
       </c>
       <c r="H99" s="11" t="str">
-        <f t="shared" ref="H99:I99" si="388">if(not(isblank($B99)), H98, "")</f>
+        <f t="shared" ref="H99:I99" si="389">if(not(isblank($B99)), H98, "")</f>
         <v/>
       </c>
       <c r="I99" s="11" t="str">
-        <f t="shared" si="388"/>
+        <f t="shared" si="389"/>
         <v/>
       </c>
       <c r="J99" s="11" t="str">
@@ -11043,11 +11043,11 @@
         <v/>
       </c>
       <c r="K99" s="11" t="str">
-        <f t="shared" ref="K99:L99" si="389">if(not(isblank($B99)), K98, "")</f>
+        <f t="shared" ref="K99:L99" si="390">if(not(isblank($B99)), K98, "")</f>
         <v/>
       </c>
       <c r="L99" s="11" t="str">
-        <f t="shared" si="389"/>
+        <f t="shared" si="390"/>
         <v/>
       </c>
       <c r="M99" s="11" t="str">
@@ -11055,11 +11055,11 @@
         <v/>
       </c>
       <c r="N99" s="11" t="str">
-        <f t="shared" ref="N99:O99" si="390">if(not(isblank($B99)), N98, "")</f>
+        <f t="shared" ref="N99:O99" si="391">if(not(isblank($B99)), N98, "")</f>
         <v/>
       </c>
       <c r="O99" s="11" t="str">
-        <f t="shared" si="390"/>
+        <f t="shared" si="391"/>
         <v/>
       </c>
       <c r="P99" s="11" t="str">
@@ -11080,7 +11080,7 @@
         <v/>
       </c>
       <c r="U99" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V99" s="14" t="str">
@@ -11106,11 +11106,11 @@
         <v/>
       </c>
       <c r="E100" s="11" t="str">
-        <f t="shared" ref="E100:F100" si="391">if(not(isblank($B100)), E99, "")</f>
+        <f t="shared" ref="E100:F100" si="392">if(not(isblank($B100)), E99, "")</f>
         <v/>
       </c>
       <c r="F100" s="11" t="str">
-        <f t="shared" si="391"/>
+        <f t="shared" si="392"/>
         <v/>
       </c>
       <c r="G100" s="11" t="str">
@@ -11118,11 +11118,11 @@
         <v/>
       </c>
       <c r="H100" s="11" t="str">
-        <f t="shared" ref="H100:I100" si="392">if(not(isblank($B100)), H99, "")</f>
+        <f t="shared" ref="H100:I100" si="393">if(not(isblank($B100)), H99, "")</f>
         <v/>
       </c>
       <c r="I100" s="11" t="str">
-        <f t="shared" si="392"/>
+        <f t="shared" si="393"/>
         <v/>
       </c>
       <c r="J100" s="11" t="str">
@@ -11130,11 +11130,11 @@
         <v/>
       </c>
       <c r="K100" s="11" t="str">
-        <f t="shared" ref="K100:L100" si="393">if(not(isblank($B100)), K99, "")</f>
+        <f t="shared" ref="K100:L100" si="394">if(not(isblank($B100)), K99, "")</f>
         <v/>
       </c>
       <c r="L100" s="11" t="str">
-        <f t="shared" si="393"/>
+        <f t="shared" si="394"/>
         <v/>
       </c>
       <c r="M100" s="11" t="str">
@@ -11142,11 +11142,11 @@
         <v/>
       </c>
       <c r="N100" s="11" t="str">
-        <f t="shared" ref="N100:O100" si="394">if(not(isblank($B100)), N99, "")</f>
+        <f t="shared" ref="N100:O100" si="395">if(not(isblank($B100)), N99, "")</f>
         <v/>
       </c>
       <c r="O100" s="11" t="str">
-        <f t="shared" si="394"/>
+        <f t="shared" si="395"/>
         <v/>
       </c>
       <c r="P100" s="11" t="str">
@@ -11167,7 +11167,7 @@
         <v/>
       </c>
       <c r="U100" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V100" s="14" t="str">
@@ -11193,11 +11193,11 @@
         <v/>
       </c>
       <c r="E101" s="11" t="str">
-        <f t="shared" ref="E101:F101" si="395">if(not(isblank($B101)), E100, "")</f>
+        <f t="shared" ref="E101:F101" si="396">if(not(isblank($B101)), E100, "")</f>
         <v/>
       </c>
       <c r="F101" s="11" t="str">
-        <f t="shared" si="395"/>
+        <f t="shared" si="396"/>
         <v/>
       </c>
       <c r="G101" s="11" t="str">
@@ -11205,11 +11205,11 @@
         <v/>
       </c>
       <c r="H101" s="11" t="str">
-        <f t="shared" ref="H101:I101" si="396">if(not(isblank($B101)), H100, "")</f>
+        <f t="shared" ref="H101:I101" si="397">if(not(isblank($B101)), H100, "")</f>
         <v/>
       </c>
       <c r="I101" s="11" t="str">
-        <f t="shared" si="396"/>
+        <f t="shared" si="397"/>
         <v/>
       </c>
       <c r="J101" s="11" t="str">
@@ -11217,11 +11217,11 @@
         <v/>
       </c>
       <c r="K101" s="11" t="str">
-        <f t="shared" ref="K101:L101" si="397">if(not(isblank($B101)), K100, "")</f>
+        <f t="shared" ref="K101:L101" si="398">if(not(isblank($B101)), K100, "")</f>
         <v/>
       </c>
       <c r="L101" s="11" t="str">
-        <f t="shared" si="397"/>
+        <f t="shared" si="398"/>
         <v/>
       </c>
       <c r="M101" s="11" t="str">
@@ -11229,11 +11229,11 @@
         <v/>
       </c>
       <c r="N101" s="11" t="str">
-        <f t="shared" ref="N101:O101" si="398">if(not(isblank($B101)), N100, "")</f>
+        <f t="shared" ref="N101:O101" si="399">if(not(isblank($B101)), N100, "")</f>
         <v/>
       </c>
       <c r="O101" s="11" t="str">
-        <f t="shared" si="398"/>
+        <f t="shared" si="399"/>
         <v/>
       </c>
       <c r="P101" s="11" t="str">
@@ -11254,7 +11254,7 @@
         <v/>
       </c>
       <c r="U101" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V101" s="14" t="str">
@@ -11280,11 +11280,11 @@
         <v/>
       </c>
       <c r="E102" s="11" t="str">
-        <f t="shared" ref="E102:F102" si="399">if(not(isblank($B102)), E101, "")</f>
+        <f t="shared" ref="E102:F102" si="400">if(not(isblank($B102)), E101, "")</f>
         <v/>
       </c>
       <c r="F102" s="11" t="str">
-        <f t="shared" si="399"/>
+        <f t="shared" si="400"/>
         <v/>
       </c>
       <c r="G102" s="11" t="str">
@@ -11292,11 +11292,11 @@
         <v/>
       </c>
       <c r="H102" s="11" t="str">
-        <f t="shared" ref="H102:I102" si="400">if(not(isblank($B102)), H101, "")</f>
+        <f t="shared" ref="H102:I102" si="401">if(not(isblank($B102)), H101, "")</f>
         <v/>
       </c>
       <c r="I102" s="11" t="str">
-        <f t="shared" si="400"/>
+        <f t="shared" si="401"/>
         <v/>
       </c>
       <c r="J102" s="11" t="str">
@@ -11304,11 +11304,11 @@
         <v/>
       </c>
       <c r="K102" s="11" t="str">
-        <f t="shared" ref="K102:L102" si="401">if(not(isblank($B102)), K101, "")</f>
+        <f t="shared" ref="K102:L102" si="402">if(not(isblank($B102)), K101, "")</f>
         <v/>
       </c>
       <c r="L102" s="11" t="str">
-        <f t="shared" si="401"/>
+        <f t="shared" si="402"/>
         <v/>
       </c>
       <c r="M102" s="11" t="str">
@@ -11316,11 +11316,11 @@
         <v/>
       </c>
       <c r="N102" s="11" t="str">
-        <f t="shared" ref="N102:O102" si="402">if(not(isblank($B102)), N101, "")</f>
+        <f t="shared" ref="N102:O102" si="403">if(not(isblank($B102)), N101, "")</f>
         <v/>
       </c>
       <c r="O102" s="11" t="str">
-        <f t="shared" si="402"/>
+        <f t="shared" si="403"/>
         <v/>
       </c>
       <c r="P102" s="11" t="str">
@@ -11341,7 +11341,7 @@
         <v/>
       </c>
       <c r="U102" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V102" s="14" t="str">
@@ -11367,11 +11367,11 @@
         <v/>
       </c>
       <c r="E103" s="11" t="str">
-        <f t="shared" ref="E103:F103" si="403">if(not(isblank($B103)), E102, "")</f>
+        <f t="shared" ref="E103:F103" si="404">if(not(isblank($B103)), E102, "")</f>
         <v/>
       </c>
       <c r="F103" s="11" t="str">
-        <f t="shared" si="403"/>
+        <f t="shared" si="404"/>
         <v/>
       </c>
       <c r="G103" s="11" t="str">
@@ -11379,11 +11379,11 @@
         <v/>
       </c>
       <c r="H103" s="11" t="str">
-        <f t="shared" ref="H103:I103" si="404">if(not(isblank($B103)), H102, "")</f>
+        <f t="shared" ref="H103:I103" si="405">if(not(isblank($B103)), H102, "")</f>
         <v/>
       </c>
       <c r="I103" s="11" t="str">
-        <f t="shared" si="404"/>
+        <f t="shared" si="405"/>
         <v/>
       </c>
       <c r="J103" s="11" t="str">
@@ -11391,11 +11391,11 @@
         <v/>
       </c>
       <c r="K103" s="11" t="str">
-        <f t="shared" ref="K103:L103" si="405">if(not(isblank($B103)), K102, "")</f>
+        <f t="shared" ref="K103:L103" si="406">if(not(isblank($B103)), K102, "")</f>
         <v/>
       </c>
       <c r="L103" s="11" t="str">
-        <f t="shared" si="405"/>
+        <f t="shared" si="406"/>
         <v/>
       </c>
       <c r="M103" s="11" t="str">
@@ -11403,11 +11403,11 @@
         <v/>
       </c>
       <c r="N103" s="11" t="str">
-        <f t="shared" ref="N103:O103" si="406">if(not(isblank($B103)), N102, "")</f>
+        <f t="shared" ref="N103:O103" si="407">if(not(isblank($B103)), N102, "")</f>
         <v/>
       </c>
       <c r="O103" s="11" t="str">
-        <f t="shared" si="406"/>
+        <f t="shared" si="407"/>
         <v/>
       </c>
       <c r="P103" s="11" t="str">
@@ -11428,7 +11428,7 @@
         <v/>
       </c>
       <c r="U103" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V103" s="14" t="str">
@@ -11454,11 +11454,11 @@
         <v/>
       </c>
       <c r="E104" s="11" t="str">
-        <f t="shared" ref="E104:F104" si="407">if(not(isblank($B104)), E103, "")</f>
+        <f t="shared" ref="E104:F104" si="408">if(not(isblank($B104)), E103, "")</f>
         <v/>
       </c>
       <c r="F104" s="11" t="str">
-        <f t="shared" si="407"/>
+        <f t="shared" si="408"/>
         <v/>
       </c>
       <c r="G104" s="11" t="str">
@@ -11466,11 +11466,11 @@
         <v/>
       </c>
       <c r="H104" s="11" t="str">
-        <f t="shared" ref="H104:I104" si="408">if(not(isblank($B104)), H103, "")</f>
+        <f t="shared" ref="H104:I104" si="409">if(not(isblank($B104)), H103, "")</f>
         <v/>
       </c>
       <c r="I104" s="11" t="str">
-        <f t="shared" si="408"/>
+        <f t="shared" si="409"/>
         <v/>
       </c>
       <c r="J104" s="11" t="str">
@@ -11478,11 +11478,11 @@
         <v/>
       </c>
       <c r="K104" s="11" t="str">
-        <f t="shared" ref="K104:L104" si="409">if(not(isblank($B104)), K103, "")</f>
+        <f t="shared" ref="K104:L104" si="410">if(not(isblank($B104)), K103, "")</f>
         <v/>
       </c>
       <c r="L104" s="11" t="str">
-        <f t="shared" si="409"/>
+        <f t="shared" si="410"/>
         <v/>
       </c>
       <c r="M104" s="11" t="str">
@@ -11490,11 +11490,11 @@
         <v/>
       </c>
       <c r="N104" s="11" t="str">
-        <f t="shared" ref="N104:O104" si="410">if(not(isblank($B104)), N103, "")</f>
+        <f t="shared" ref="N104:O104" si="411">if(not(isblank($B104)), N103, "")</f>
         <v/>
       </c>
       <c r="O104" s="11" t="str">
-        <f t="shared" si="410"/>
+        <f t="shared" si="411"/>
         <v/>
       </c>
       <c r="P104" s="11" t="str">
@@ -11515,7 +11515,7 @@
         <v/>
       </c>
       <c r="U104" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V104" s="14" t="str">
@@ -11541,11 +11541,11 @@
         <v/>
       </c>
       <c r="E105" s="11" t="str">
-        <f t="shared" ref="E105:F105" si="411">if(not(isblank($B105)), E104, "")</f>
+        <f t="shared" ref="E105:F105" si="412">if(not(isblank($B105)), E104, "")</f>
         <v/>
       </c>
       <c r="F105" s="11" t="str">
-        <f t="shared" si="411"/>
+        <f t="shared" si="412"/>
         <v/>
       </c>
       <c r="G105" s="11" t="str">
@@ -11553,11 +11553,11 @@
         <v/>
       </c>
       <c r="H105" s="11" t="str">
-        <f t="shared" ref="H105:I105" si="412">if(not(isblank($B105)), H104, "")</f>
+        <f t="shared" ref="H105:I105" si="413">if(not(isblank($B105)), H104, "")</f>
         <v/>
       </c>
       <c r="I105" s="11" t="str">
-        <f t="shared" si="412"/>
+        <f t="shared" si="413"/>
         <v/>
       </c>
       <c r="J105" s="11" t="str">
@@ -11565,11 +11565,11 @@
         <v/>
       </c>
       <c r="K105" s="11" t="str">
-        <f t="shared" ref="K105:L105" si="413">if(not(isblank($B105)), K104, "")</f>
+        <f t="shared" ref="K105:L105" si="414">if(not(isblank($B105)), K104, "")</f>
         <v/>
       </c>
       <c r="L105" s="11" t="str">
-        <f t="shared" si="413"/>
+        <f t="shared" si="414"/>
         <v/>
       </c>
       <c r="M105" s="11" t="str">
@@ -11577,11 +11577,11 @@
         <v/>
       </c>
       <c r="N105" s="11" t="str">
-        <f t="shared" ref="N105:O105" si="414">if(not(isblank($B105)), N104, "")</f>
+        <f t="shared" ref="N105:O105" si="415">if(not(isblank($B105)), N104, "")</f>
         <v/>
       </c>
       <c r="O105" s="11" t="str">
-        <f t="shared" si="414"/>
+        <f t="shared" si="415"/>
         <v/>
       </c>
       <c r="P105" s="11" t="str">
@@ -11602,7 +11602,7 @@
         <v/>
       </c>
       <c r="U105" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V105" s="14" t="str">
@@ -11628,11 +11628,11 @@
         <v/>
       </c>
       <c r="E106" s="11" t="str">
-        <f t="shared" ref="E106:F106" si="415">if(not(isblank($B106)), E105, "")</f>
+        <f t="shared" ref="E106:F106" si="416">if(not(isblank($B106)), E105, "")</f>
         <v/>
       </c>
       <c r="F106" s="11" t="str">
-        <f t="shared" si="415"/>
+        <f t="shared" si="416"/>
         <v/>
       </c>
       <c r="G106" s="11" t="str">
@@ -11640,11 +11640,11 @@
         <v/>
       </c>
       <c r="H106" s="11" t="str">
-        <f t="shared" ref="H106:I106" si="416">if(not(isblank($B106)), H105, "")</f>
+        <f t="shared" ref="H106:I106" si="417">if(not(isblank($B106)), H105, "")</f>
         <v/>
       </c>
       <c r="I106" s="11" t="str">
-        <f t="shared" si="416"/>
+        <f t="shared" si="417"/>
         <v/>
       </c>
       <c r="J106" s="11" t="str">
@@ -11652,11 +11652,11 @@
         <v/>
       </c>
       <c r="K106" s="11" t="str">
-        <f t="shared" ref="K106:L106" si="417">if(not(isblank($B106)), K105, "")</f>
+        <f t="shared" ref="K106:L106" si="418">if(not(isblank($B106)), K105, "")</f>
         <v/>
       </c>
       <c r="L106" s="11" t="str">
-        <f t="shared" si="417"/>
+        <f t="shared" si="418"/>
         <v/>
       </c>
       <c r="M106" s="11" t="str">
@@ -11664,11 +11664,11 @@
         <v/>
       </c>
       <c r="N106" s="11" t="str">
-        <f t="shared" ref="N106:O106" si="418">if(not(isblank($B106)), N105, "")</f>
+        <f t="shared" ref="N106:O106" si="419">if(not(isblank($B106)), N105, "")</f>
         <v/>
       </c>
       <c r="O106" s="11" t="str">
-        <f t="shared" si="418"/>
+        <f t="shared" si="419"/>
         <v/>
       </c>
       <c r="P106" s="11" t="str">
@@ -11689,7 +11689,7 @@
         <v/>
       </c>
       <c r="U106" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V106" s="14" t="str">
@@ -11715,11 +11715,11 @@
         <v/>
       </c>
       <c r="E107" s="11" t="str">
-        <f t="shared" ref="E107:F107" si="419">if(not(isblank($B107)), E106, "")</f>
+        <f t="shared" ref="E107:F107" si="420">if(not(isblank($B107)), E106, "")</f>
         <v/>
       </c>
       <c r="F107" s="11" t="str">
-        <f t="shared" si="419"/>
+        <f t="shared" si="420"/>
         <v/>
       </c>
       <c r="G107" s="11" t="str">
@@ -11727,11 +11727,11 @@
         <v/>
       </c>
       <c r="H107" s="11" t="str">
-        <f t="shared" ref="H107:I107" si="420">if(not(isblank($B107)), H106, "")</f>
+        <f t="shared" ref="H107:I107" si="421">if(not(isblank($B107)), H106, "")</f>
         <v/>
       </c>
       <c r="I107" s="11" t="str">
-        <f t="shared" si="420"/>
+        <f t="shared" si="421"/>
         <v/>
       </c>
       <c r="J107" s="11" t="str">
@@ -11739,11 +11739,11 @@
         <v/>
       </c>
       <c r="K107" s="11" t="str">
-        <f t="shared" ref="K107:L107" si="421">if(not(isblank($B107)), K106, "")</f>
+        <f t="shared" ref="K107:L107" si="422">if(not(isblank($B107)), K106, "")</f>
         <v/>
       </c>
       <c r="L107" s="11" t="str">
-        <f t="shared" si="421"/>
+        <f t="shared" si="422"/>
         <v/>
       </c>
       <c r="M107" s="11" t="str">
@@ -11751,11 +11751,11 @@
         <v/>
       </c>
       <c r="N107" s="11" t="str">
-        <f t="shared" ref="N107:O107" si="422">if(not(isblank($B107)), N106, "")</f>
+        <f t="shared" ref="N107:O107" si="423">if(not(isblank($B107)), N106, "")</f>
         <v/>
       </c>
       <c r="O107" s="11" t="str">
-        <f t="shared" si="422"/>
+        <f t="shared" si="423"/>
         <v/>
       </c>
       <c r="P107" s="11" t="str">
@@ -11776,7 +11776,7 @@
         <v/>
       </c>
       <c r="U107" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V107" s="14" t="str">
@@ -11802,11 +11802,11 @@
         <v/>
       </c>
       <c r="E108" s="11" t="str">
-        <f t="shared" ref="E108:F108" si="423">if(not(isblank($B108)), E107, "")</f>
+        <f t="shared" ref="E108:F108" si="424">if(not(isblank($B108)), E107, "")</f>
         <v/>
       </c>
       <c r="F108" s="11" t="str">
-        <f t="shared" si="423"/>
+        <f t="shared" si="424"/>
         <v/>
       </c>
       <c r="G108" s="11" t="str">
@@ -11814,11 +11814,11 @@
         <v/>
       </c>
       <c r="H108" s="11" t="str">
-        <f t="shared" ref="H108:I108" si="424">if(not(isblank($B108)), H107, "")</f>
+        <f t="shared" ref="H108:I108" si="425">if(not(isblank($B108)), H107, "")</f>
         <v/>
       </c>
       <c r="I108" s="11" t="str">
-        <f t="shared" si="424"/>
+        <f t="shared" si="425"/>
         <v/>
       </c>
       <c r="J108" s="11" t="str">
@@ -11826,11 +11826,11 @@
         <v/>
       </c>
       <c r="K108" s="11" t="str">
-        <f t="shared" ref="K108:L108" si="425">if(not(isblank($B108)), K107, "")</f>
+        <f t="shared" ref="K108:L108" si="426">if(not(isblank($B108)), K107, "")</f>
         <v/>
       </c>
       <c r="L108" s="11" t="str">
-        <f t="shared" si="425"/>
+        <f t="shared" si="426"/>
         <v/>
       </c>
       <c r="M108" s="11" t="str">
@@ -11838,11 +11838,11 @@
         <v/>
       </c>
       <c r="N108" s="11" t="str">
-        <f t="shared" ref="N108:O108" si="426">if(not(isblank($B108)), N107, "")</f>
+        <f t="shared" ref="N108:O108" si="427">if(not(isblank($B108)), N107, "")</f>
         <v/>
       </c>
       <c r="O108" s="11" t="str">
-        <f t="shared" si="426"/>
+        <f t="shared" si="427"/>
         <v/>
       </c>
       <c r="P108" s="11" t="str">
@@ -11863,7 +11863,7 @@
         <v/>
       </c>
       <c r="U108" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V108" s="14" t="str">
@@ -11889,11 +11889,11 @@
         <v/>
       </c>
       <c r="E109" s="11" t="str">
-        <f t="shared" ref="E109:F109" si="427">if(not(isblank($B109)), E108, "")</f>
+        <f t="shared" ref="E109:F109" si="428">if(not(isblank($B109)), E108, "")</f>
         <v/>
       </c>
       <c r="F109" s="11" t="str">
-        <f t="shared" si="427"/>
+        <f t="shared" si="428"/>
         <v/>
       </c>
       <c r="G109" s="11" t="str">
@@ -11901,11 +11901,11 @@
         <v/>
       </c>
       <c r="H109" s="11" t="str">
-        <f t="shared" ref="H109:I109" si="428">if(not(isblank($B109)), H108, "")</f>
+        <f t="shared" ref="H109:I109" si="429">if(not(isblank($B109)), H108, "")</f>
         <v/>
       </c>
       <c r="I109" s="11" t="str">
-        <f t="shared" si="428"/>
+        <f t="shared" si="429"/>
         <v/>
       </c>
       <c r="J109" s="11" t="str">
@@ -11913,11 +11913,11 @@
         <v/>
       </c>
       <c r="K109" s="11" t="str">
-        <f t="shared" ref="K109:L109" si="429">if(not(isblank($B109)), K108, "")</f>
+        <f t="shared" ref="K109:L109" si="430">if(not(isblank($B109)), K108, "")</f>
         <v/>
       </c>
       <c r="L109" s="11" t="str">
-        <f t="shared" si="429"/>
+        <f t="shared" si="430"/>
         <v/>
       </c>
       <c r="M109" s="11" t="str">
@@ -11925,11 +11925,11 @@
         <v/>
       </c>
       <c r="N109" s="11" t="str">
-        <f t="shared" ref="N109:O109" si="430">if(not(isblank($B109)), N108, "")</f>
+        <f t="shared" ref="N109:O109" si="431">if(not(isblank($B109)), N108, "")</f>
         <v/>
       </c>
       <c r="O109" s="11" t="str">
-        <f t="shared" si="430"/>
+        <f t="shared" si="431"/>
         <v/>
       </c>
       <c r="P109" s="11" t="str">
@@ -11950,7 +11950,7 @@
         <v/>
       </c>
       <c r="U109" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V109" s="14" t="str">
@@ -11976,11 +11976,11 @@
         <v/>
       </c>
       <c r="E110" s="11" t="str">
-        <f t="shared" ref="E110:F110" si="431">if(not(isblank($B110)), E109, "")</f>
+        <f t="shared" ref="E110:F110" si="432">if(not(isblank($B110)), E109, "")</f>
         <v/>
       </c>
       <c r="F110" s="11" t="str">
-        <f t="shared" si="431"/>
+        <f t="shared" si="432"/>
         <v/>
       </c>
       <c r="G110" s="11" t="str">
@@ -11988,11 +11988,11 @@
         <v/>
       </c>
       <c r="H110" s="11" t="str">
-        <f t="shared" ref="H110:I110" si="432">if(not(isblank($B110)), H109, "")</f>
+        <f t="shared" ref="H110:I110" si="433">if(not(isblank($B110)), H109, "")</f>
         <v/>
       </c>
       <c r="I110" s="11" t="str">
-        <f t="shared" si="432"/>
+        <f t="shared" si="433"/>
         <v/>
       </c>
       <c r="J110" s="11" t="str">
@@ -12000,11 +12000,11 @@
         <v/>
       </c>
       <c r="K110" s="11" t="str">
-        <f t="shared" ref="K110:L110" si="433">if(not(isblank($B110)), K109, "")</f>
+        <f t="shared" ref="K110:L110" si="434">if(not(isblank($B110)), K109, "")</f>
         <v/>
       </c>
       <c r="L110" s="11" t="str">
-        <f t="shared" si="433"/>
+        <f t="shared" si="434"/>
         <v/>
       </c>
       <c r="M110" s="11" t="str">
@@ -12012,11 +12012,11 @@
         <v/>
       </c>
       <c r="N110" s="11" t="str">
-        <f t="shared" ref="N110:O110" si="434">if(not(isblank($B110)), N109, "")</f>
+        <f t="shared" ref="N110:O110" si="435">if(not(isblank($B110)), N109, "")</f>
         <v/>
       </c>
       <c r="O110" s="11" t="str">
-        <f t="shared" si="434"/>
+        <f t="shared" si="435"/>
         <v/>
       </c>
       <c r="P110" s="11" t="str">
@@ -12037,7 +12037,7 @@
         <v/>
       </c>
       <c r="U110" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V110" s="14" t="str">
@@ -12063,11 +12063,11 @@
         <v/>
       </c>
       <c r="E111" s="11" t="str">
-        <f t="shared" ref="E111:F111" si="435">if(not(isblank($B111)), E110, "")</f>
+        <f t="shared" ref="E111:F111" si="436">if(not(isblank($B111)), E110, "")</f>
         <v/>
       </c>
       <c r="F111" s="11" t="str">
-        <f t="shared" si="435"/>
+        <f t="shared" si="436"/>
         <v/>
       </c>
       <c r="G111" s="11" t="str">
@@ -12075,11 +12075,11 @@
         <v/>
       </c>
       <c r="H111" s="11" t="str">
-        <f t="shared" ref="H111:I111" si="436">if(not(isblank($B111)), H110, "")</f>
+        <f t="shared" ref="H111:I111" si="437">if(not(isblank($B111)), H110, "")</f>
         <v/>
       </c>
       <c r="I111" s="11" t="str">
-        <f t="shared" si="436"/>
+        <f t="shared" si="437"/>
         <v/>
       </c>
       <c r="J111" s="11" t="str">
@@ -12087,11 +12087,11 @@
         <v/>
       </c>
       <c r="K111" s="11" t="str">
-        <f t="shared" ref="K111:L111" si="437">if(not(isblank($B111)), K110, "")</f>
+        <f t="shared" ref="K111:L111" si="438">if(not(isblank($B111)), K110, "")</f>
         <v/>
       </c>
       <c r="L111" s="11" t="str">
-        <f t="shared" si="437"/>
+        <f t="shared" si="438"/>
         <v/>
       </c>
       <c r="M111" s="11" t="str">
@@ -12099,11 +12099,11 @@
         <v/>
       </c>
       <c r="N111" s="11" t="str">
-        <f t="shared" ref="N111:O111" si="438">if(not(isblank($B111)), N110, "")</f>
+        <f t="shared" ref="N111:O111" si="439">if(not(isblank($B111)), N110, "")</f>
         <v/>
       </c>
       <c r="O111" s="11" t="str">
-        <f t="shared" si="438"/>
+        <f t="shared" si="439"/>
         <v/>
       </c>
       <c r="P111" s="11" t="str">
@@ -12124,7 +12124,7 @@
         <v/>
       </c>
       <c r="U111" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V111" s="14" t="str">
@@ -12150,11 +12150,11 @@
         <v/>
       </c>
       <c r="E112" s="11" t="str">
-        <f t="shared" ref="E112:F112" si="439">if(not(isblank($B112)), E111, "")</f>
+        <f t="shared" ref="E112:F112" si="440">if(not(isblank($B112)), E111, "")</f>
         <v/>
       </c>
       <c r="F112" s="11" t="str">
-        <f t="shared" si="439"/>
+        <f t="shared" si="440"/>
         <v/>
       </c>
       <c r="G112" s="11" t="str">
@@ -12162,11 +12162,11 @@
         <v/>
       </c>
       <c r="H112" s="11" t="str">
-        <f t="shared" ref="H112:I112" si="440">if(not(isblank($B112)), H111, "")</f>
+        <f t="shared" ref="H112:I112" si="441">if(not(isblank($B112)), H111, "")</f>
         <v/>
       </c>
       <c r="I112" s="11" t="str">
-        <f t="shared" si="440"/>
+        <f t="shared" si="441"/>
         <v/>
       </c>
       <c r="J112" s="11" t="str">
@@ -12174,11 +12174,11 @@
         <v/>
       </c>
       <c r="K112" s="11" t="str">
-        <f t="shared" ref="K112:L112" si="441">if(not(isblank($B112)), K111, "")</f>
+        <f t="shared" ref="K112:L112" si="442">if(not(isblank($B112)), K111, "")</f>
         <v/>
       </c>
       <c r="L112" s="11" t="str">
-        <f t="shared" si="441"/>
+        <f t="shared" si="442"/>
         <v/>
       </c>
       <c r="M112" s="11" t="str">
@@ -12186,11 +12186,11 @@
         <v/>
       </c>
       <c r="N112" s="11" t="str">
-        <f t="shared" ref="N112:O112" si="442">if(not(isblank($B112)), N111, "")</f>
+        <f t="shared" ref="N112:O112" si="443">if(not(isblank($B112)), N111, "")</f>
         <v/>
       </c>
       <c r="O112" s="11" t="str">
-        <f t="shared" si="442"/>
+        <f t="shared" si="443"/>
         <v/>
       </c>
       <c r="P112" s="11" t="str">
@@ -12211,7 +12211,7 @@
         <v/>
       </c>
       <c r="U112" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V112" s="14" t="str">
@@ -12237,11 +12237,11 @@
         <v/>
       </c>
       <c r="E113" s="11" t="str">
-        <f t="shared" ref="E113:F113" si="443">if(not(isblank($B113)), E112, "")</f>
+        <f t="shared" ref="E113:F113" si="444">if(not(isblank($B113)), E112, "")</f>
         <v/>
       </c>
       <c r="F113" s="11" t="str">
-        <f t="shared" si="443"/>
+        <f t="shared" si="444"/>
         <v/>
       </c>
       <c r="G113" s="11" t="str">
@@ -12249,11 +12249,11 @@
         <v/>
       </c>
       <c r="H113" s="11" t="str">
-        <f t="shared" ref="H113:I113" si="444">if(not(isblank($B113)), H112, "")</f>
+        <f t="shared" ref="H113:I113" si="445">if(not(isblank($B113)), H112, "")</f>
         <v/>
       </c>
       <c r="I113" s="11" t="str">
-        <f t="shared" si="444"/>
+        <f t="shared" si="445"/>
         <v/>
       </c>
       <c r="J113" s="11" t="str">
@@ -12261,11 +12261,11 @@
         <v/>
       </c>
       <c r="K113" s="11" t="str">
-        <f t="shared" ref="K113:L113" si="445">if(not(isblank($B113)), K112, "")</f>
+        <f t="shared" ref="K113:L113" si="446">if(not(isblank($B113)), K112, "")</f>
         <v/>
       </c>
       <c r="L113" s="11" t="str">
-        <f t="shared" si="445"/>
+        <f t="shared" si="446"/>
         <v/>
       </c>
       <c r="M113" s="11" t="str">
@@ -12273,11 +12273,11 @@
         <v/>
       </c>
       <c r="N113" s="11" t="str">
-        <f t="shared" ref="N113:O113" si="446">if(not(isblank($B113)), N112, "")</f>
+        <f t="shared" ref="N113:O113" si="447">if(not(isblank($B113)), N112, "")</f>
         <v/>
       </c>
       <c r="O113" s="11" t="str">
-        <f t="shared" si="446"/>
+        <f t="shared" si="447"/>
         <v/>
       </c>
       <c r="P113" s="11" t="str">
@@ -12298,7 +12298,7 @@
         <v/>
       </c>
       <c r="U113" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V113" s="14" t="str">
@@ -12324,11 +12324,11 @@
         <v/>
       </c>
       <c r="E114" s="11" t="str">
-        <f t="shared" ref="E114:F114" si="447">if(not(isblank($B114)), E113, "")</f>
+        <f t="shared" ref="E114:F114" si="448">if(not(isblank($B114)), E113, "")</f>
         <v/>
       </c>
       <c r="F114" s="11" t="str">
-        <f t="shared" si="447"/>
+        <f t="shared" si="448"/>
         <v/>
       </c>
       <c r="G114" s="11" t="str">
@@ -12336,11 +12336,11 @@
         <v/>
       </c>
       <c r="H114" s="11" t="str">
-        <f t="shared" ref="H114:I114" si="448">if(not(isblank($B114)), H113, "")</f>
+        <f t="shared" ref="H114:I114" si="449">if(not(isblank($B114)), H113, "")</f>
         <v/>
       </c>
       <c r="I114" s="11" t="str">
-        <f t="shared" si="448"/>
+        <f t="shared" si="449"/>
         <v/>
       </c>
       <c r="J114" s="11" t="str">
@@ -12348,11 +12348,11 @@
         <v/>
       </c>
       <c r="K114" s="11" t="str">
-        <f t="shared" ref="K114:L114" si="449">if(not(isblank($B114)), K113, "")</f>
+        <f t="shared" ref="K114:L114" si="450">if(not(isblank($B114)), K113, "")</f>
         <v/>
       </c>
       <c r="L114" s="11" t="str">
-        <f t="shared" si="449"/>
+        <f t="shared" si="450"/>
         <v/>
       </c>
       <c r="M114" s="11" t="str">
@@ -12360,11 +12360,11 @@
         <v/>
       </c>
       <c r="N114" s="11" t="str">
-        <f t="shared" ref="N114:O114" si="450">if(not(isblank($B114)), N113, "")</f>
+        <f t="shared" ref="N114:O114" si="451">if(not(isblank($B114)), N113, "")</f>
         <v/>
       </c>
       <c r="O114" s="11" t="str">
-        <f t="shared" si="450"/>
+        <f t="shared" si="451"/>
         <v/>
       </c>
       <c r="P114" s="11" t="str">
@@ -12385,7 +12385,7 @@
         <v/>
       </c>
       <c r="U114" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V114" s="14" t="str">
@@ -12411,11 +12411,11 @@
         <v/>
       </c>
       <c r="E115" s="11" t="str">
-        <f t="shared" ref="E115:F115" si="451">if(not(isblank($B115)), E114, "")</f>
+        <f t="shared" ref="E115:F115" si="452">if(not(isblank($B115)), E114, "")</f>
         <v/>
       </c>
       <c r="F115" s="11" t="str">
-        <f t="shared" si="451"/>
+        <f t="shared" si="452"/>
         <v/>
       </c>
       <c r="G115" s="11" t="str">
@@ -12423,11 +12423,11 @@
         <v/>
       </c>
       <c r="H115" s="11" t="str">
-        <f t="shared" ref="H115:I115" si="452">if(not(isblank($B115)), H114, "")</f>
+        <f t="shared" ref="H115:I115" si="453">if(not(isblank($B115)), H114, "")</f>
         <v/>
       </c>
       <c r="I115" s="11" t="str">
-        <f t="shared" si="452"/>
+        <f t="shared" si="453"/>
         <v/>
       </c>
       <c r="J115" s="11" t="str">
@@ -12435,11 +12435,11 @@
         <v/>
       </c>
       <c r="K115" s="11" t="str">
-        <f t="shared" ref="K115:L115" si="453">if(not(isblank($B115)), K114, "")</f>
+        <f t="shared" ref="K115:L115" si="454">if(not(isblank($B115)), K114, "")</f>
         <v/>
       </c>
       <c r="L115" s="11" t="str">
-        <f t="shared" si="453"/>
+        <f t="shared" si="454"/>
         <v/>
       </c>
       <c r="M115" s="11" t="str">
@@ -12447,11 +12447,11 @@
         <v/>
       </c>
       <c r="N115" s="11" t="str">
-        <f t="shared" ref="N115:O115" si="454">if(not(isblank($B115)), N114, "")</f>
+        <f t="shared" ref="N115:O115" si="455">if(not(isblank($B115)), N114, "")</f>
         <v/>
       </c>
       <c r="O115" s="11" t="str">
-        <f t="shared" si="454"/>
+        <f t="shared" si="455"/>
         <v/>
       </c>
       <c r="P115" s="11" t="str">
@@ -12472,7 +12472,7 @@
         <v/>
       </c>
       <c r="U115" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V115" s="14" t="str">
@@ -12498,11 +12498,11 @@
         <v/>
       </c>
       <c r="E116" s="11" t="str">
-        <f t="shared" ref="E116:F116" si="455">if(not(isblank($B116)), E115, "")</f>
+        <f t="shared" ref="E116:F116" si="456">if(not(isblank($B116)), E115, "")</f>
         <v/>
       </c>
       <c r="F116" s="11" t="str">
-        <f t="shared" si="455"/>
+        <f t="shared" si="456"/>
         <v/>
       </c>
       <c r="G116" s="11" t="str">
@@ -12510,11 +12510,11 @@
         <v/>
       </c>
       <c r="H116" s="11" t="str">
-        <f t="shared" ref="H116:I116" si="456">if(not(isblank($B116)), H115, "")</f>
+        <f t="shared" ref="H116:I116" si="457">if(not(isblank($B116)), H115, "")</f>
         <v/>
       </c>
       <c r="I116" s="11" t="str">
-        <f t="shared" si="456"/>
+        <f t="shared" si="457"/>
         <v/>
       </c>
       <c r="J116" s="11" t="str">
@@ -12522,11 +12522,11 @@
         <v/>
       </c>
       <c r="K116" s="11" t="str">
-        <f t="shared" ref="K116:L116" si="457">if(not(isblank($B116)), K115, "")</f>
+        <f t="shared" ref="K116:L116" si="458">if(not(isblank($B116)), K115, "")</f>
         <v/>
       </c>
       <c r="L116" s="11" t="str">
-        <f t="shared" si="457"/>
+        <f t="shared" si="458"/>
         <v/>
       </c>
       <c r="M116" s="11" t="str">
@@ -12534,11 +12534,11 @@
         <v/>
       </c>
       <c r="N116" s="11" t="str">
-        <f t="shared" ref="N116:O116" si="458">if(not(isblank($B116)), N115, "")</f>
+        <f t="shared" ref="N116:O116" si="459">if(not(isblank($B116)), N115, "")</f>
         <v/>
       </c>
       <c r="O116" s="11" t="str">
-        <f t="shared" si="458"/>
+        <f t="shared" si="459"/>
         <v/>
       </c>
       <c r="P116" s="11" t="str">
@@ -12559,7 +12559,7 @@
         <v/>
       </c>
       <c r="U116" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V116" s="14" t="str">
@@ -12585,11 +12585,11 @@
         <v/>
       </c>
       <c r="E117" s="11" t="str">
-        <f t="shared" ref="E117:F117" si="459">if(not(isblank($B117)), E116, "")</f>
+        <f t="shared" ref="E117:F117" si="460">if(not(isblank($B117)), E116, "")</f>
         <v/>
       </c>
       <c r="F117" s="11" t="str">
-        <f t="shared" si="459"/>
+        <f t="shared" si="460"/>
         <v/>
       </c>
       <c r="G117" s="11" t="str">
@@ -12597,11 +12597,11 @@
         <v/>
       </c>
       <c r="H117" s="11" t="str">
-        <f t="shared" ref="H117:I117" si="460">if(not(isblank($B117)), H116, "")</f>
+        <f t="shared" ref="H117:I117" si="461">if(not(isblank($B117)), H116, "")</f>
         <v/>
       </c>
       <c r="I117" s="11" t="str">
-        <f t="shared" si="460"/>
+        <f t="shared" si="461"/>
         <v/>
       </c>
       <c r="J117" s="11" t="str">
@@ -12609,11 +12609,11 @@
         <v/>
       </c>
       <c r="K117" s="11" t="str">
-        <f t="shared" ref="K117:L117" si="461">if(not(isblank($B117)), K116, "")</f>
+        <f t="shared" ref="K117:L117" si="462">if(not(isblank($B117)), K116, "")</f>
         <v/>
       </c>
       <c r="L117" s="11" t="str">
-        <f t="shared" si="461"/>
+        <f t="shared" si="462"/>
         <v/>
       </c>
       <c r="M117" s="11" t="str">
@@ -12621,11 +12621,11 @@
         <v/>
       </c>
       <c r="N117" s="11" t="str">
-        <f t="shared" ref="N117:O117" si="462">if(not(isblank($B117)), N116, "")</f>
+        <f t="shared" ref="N117:O117" si="463">if(not(isblank($B117)), N116, "")</f>
         <v/>
       </c>
       <c r="O117" s="11" t="str">
-        <f t="shared" si="462"/>
+        <f t="shared" si="463"/>
         <v/>
       </c>
       <c r="P117" s="11" t="str">
@@ -12646,7 +12646,7 @@
         <v/>
       </c>
       <c r="U117" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V117" s="14" t="str">
@@ -12672,11 +12672,11 @@
         <v/>
       </c>
       <c r="E118" s="11" t="str">
-        <f t="shared" ref="E118:F118" si="463">if(not(isblank($B118)), E117, "")</f>
+        <f t="shared" ref="E118:F118" si="464">if(not(isblank($B118)), E117, "")</f>
         <v/>
       </c>
       <c r="F118" s="11" t="str">
-        <f t="shared" si="463"/>
+        <f t="shared" si="464"/>
         <v/>
       </c>
       <c r="G118" s="11" t="str">
@@ -12684,11 +12684,11 @@
         <v/>
       </c>
       <c r="H118" s="11" t="str">
-        <f t="shared" ref="H118:I118" si="464">if(not(isblank($B118)), H117, "")</f>
+        <f t="shared" ref="H118:I118" si="465">if(not(isblank($B118)), H117, "")</f>
         <v/>
       </c>
       <c r="I118" s="11" t="str">
-        <f t="shared" si="464"/>
+        <f t="shared" si="465"/>
         <v/>
       </c>
       <c r="J118" s="11" t="str">
@@ -12696,11 +12696,11 @@
         <v/>
       </c>
       <c r="K118" s="11" t="str">
-        <f t="shared" ref="K118:L118" si="465">if(not(isblank($B118)), K117, "")</f>
+        <f t="shared" ref="K118:L118" si="466">if(not(isblank($B118)), K117, "")</f>
         <v/>
       </c>
       <c r="L118" s="11" t="str">
-        <f t="shared" si="465"/>
+        <f t="shared" si="466"/>
         <v/>
       </c>
       <c r="M118" s="11" t="str">
@@ -12708,11 +12708,11 @@
         <v/>
       </c>
       <c r="N118" s="11" t="str">
-        <f t="shared" ref="N118:O118" si="466">if(not(isblank($B118)), N117, "")</f>
+        <f t="shared" ref="N118:O118" si="467">if(not(isblank($B118)), N117, "")</f>
         <v/>
       </c>
       <c r="O118" s="11" t="str">
-        <f t="shared" si="466"/>
+        <f t="shared" si="467"/>
         <v/>
       </c>
       <c r="P118" s="11" t="str">
@@ -12733,7 +12733,7 @@
         <v/>
       </c>
       <c r="U118" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V118" s="14" t="str">
@@ -12759,11 +12759,11 @@
         <v/>
       </c>
       <c r="E119" s="11" t="str">
-        <f t="shared" ref="E119:F119" si="467">if(not(isblank($B119)), E118, "")</f>
+        <f t="shared" ref="E119:F119" si="468">if(not(isblank($B119)), E118, "")</f>
         <v/>
       </c>
       <c r="F119" s="11" t="str">
-        <f t="shared" si="467"/>
+        <f t="shared" si="468"/>
         <v/>
       </c>
       <c r="G119" s="11" t="str">
@@ -12771,11 +12771,11 @@
         <v/>
       </c>
       <c r="H119" s="11" t="str">
-        <f t="shared" ref="H119:I119" si="468">if(not(isblank($B119)), H118, "")</f>
+        <f t="shared" ref="H119:I119" si="469">if(not(isblank($B119)), H118, "")</f>
         <v/>
       </c>
       <c r="I119" s="11" t="str">
-        <f t="shared" si="468"/>
+        <f t="shared" si="469"/>
         <v/>
       </c>
       <c r="J119" s="11" t="str">
@@ -12783,11 +12783,11 @@
         <v/>
       </c>
       <c r="K119" s="11" t="str">
-        <f t="shared" ref="K119:L119" si="469">if(not(isblank($B119)), K118, "")</f>
+        <f t="shared" ref="K119:L119" si="470">if(not(isblank($B119)), K118, "")</f>
         <v/>
       </c>
       <c r="L119" s="11" t="str">
-        <f t="shared" si="469"/>
+        <f t="shared" si="470"/>
         <v/>
       </c>
       <c r="M119" s="11" t="str">
@@ -12795,11 +12795,11 @@
         <v/>
       </c>
       <c r="N119" s="11" t="str">
-        <f t="shared" ref="N119:O119" si="470">if(not(isblank($B119)), N118, "")</f>
+        <f t="shared" ref="N119:O119" si="471">if(not(isblank($B119)), N118, "")</f>
         <v/>
       </c>
       <c r="O119" s="11" t="str">
-        <f t="shared" si="470"/>
+        <f t="shared" si="471"/>
         <v/>
       </c>
       <c r="P119" s="11" t="str">
@@ -12820,7 +12820,7 @@
         <v/>
       </c>
       <c r="U119" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V119" s="14" t="str">
@@ -12846,11 +12846,11 @@
         <v/>
       </c>
       <c r="E120" s="11" t="str">
-        <f t="shared" ref="E120:F120" si="471">if(not(isblank($B120)), E119, "")</f>
+        <f t="shared" ref="E120:F120" si="472">if(not(isblank($B120)), E119, "")</f>
         <v/>
       </c>
       <c r="F120" s="11" t="str">
-        <f t="shared" si="471"/>
+        <f t="shared" si="472"/>
         <v/>
       </c>
       <c r="G120" s="11" t="str">
@@ -12858,11 +12858,11 @@
         <v/>
       </c>
       <c r="H120" s="11" t="str">
-        <f t="shared" ref="H120:I120" si="472">if(not(isblank($B120)), H119, "")</f>
+        <f t="shared" ref="H120:I120" si="473">if(not(isblank($B120)), H119, "")</f>
         <v/>
       </c>
       <c r="I120" s="11" t="str">
-        <f t="shared" si="472"/>
+        <f t="shared" si="473"/>
         <v/>
       </c>
       <c r="J120" s="11" t="str">
@@ -12870,11 +12870,11 @@
         <v/>
       </c>
       <c r="K120" s="11" t="str">
-        <f t="shared" ref="K120:L120" si="473">if(not(isblank($B120)), K119, "")</f>
+        <f t="shared" ref="K120:L120" si="474">if(not(isblank($B120)), K119, "")</f>
         <v/>
       </c>
       <c r="L120" s="11" t="str">
-        <f t="shared" si="473"/>
+        <f t="shared" si="474"/>
         <v/>
       </c>
       <c r="M120" s="11" t="str">
@@ -12882,11 +12882,11 @@
         <v/>
       </c>
       <c r="N120" s="11" t="str">
-        <f t="shared" ref="N120:O120" si="474">if(not(isblank($B120)), N119, "")</f>
+        <f t="shared" ref="N120:O120" si="475">if(not(isblank($B120)), N119, "")</f>
         <v/>
       </c>
       <c r="O120" s="11" t="str">
-        <f t="shared" si="474"/>
+        <f t="shared" si="475"/>
         <v/>
       </c>
       <c r="P120" s="11" t="str">
@@ -12907,7 +12907,7 @@
         <v/>
       </c>
       <c r="U120" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V120" s="14" t="str">
@@ -12933,11 +12933,11 @@
         <v/>
       </c>
       <c r="E121" s="11" t="str">
-        <f t="shared" ref="E121:F121" si="475">if(not(isblank($B121)), E120, "")</f>
+        <f t="shared" ref="E121:F121" si="476">if(not(isblank($B121)), E120, "")</f>
         <v/>
       </c>
       <c r="F121" s="11" t="str">
-        <f t="shared" si="475"/>
+        <f t="shared" si="476"/>
         <v/>
       </c>
       <c r="G121" s="11" t="str">
@@ -12945,11 +12945,11 @@
         <v/>
       </c>
       <c r="H121" s="11" t="str">
-        <f t="shared" ref="H121:I121" si="476">if(not(isblank($B121)), H120, "")</f>
+        <f t="shared" ref="H121:I121" si="477">if(not(isblank($B121)), H120, "")</f>
         <v/>
       </c>
       <c r="I121" s="11" t="str">
-        <f t="shared" si="476"/>
+        <f t="shared" si="477"/>
         <v/>
       </c>
       <c r="J121" s="11" t="str">
@@ -12957,11 +12957,11 @@
         <v/>
       </c>
       <c r="K121" s="11" t="str">
-        <f t="shared" ref="K121:L121" si="477">if(not(isblank($B121)), K120, "")</f>
+        <f t="shared" ref="K121:L121" si="478">if(not(isblank($B121)), K120, "")</f>
         <v/>
       </c>
       <c r="L121" s="11" t="str">
-        <f t="shared" si="477"/>
+        <f t="shared" si="478"/>
         <v/>
       </c>
       <c r="M121" s="11" t="str">
@@ -12969,11 +12969,11 @@
         <v/>
       </c>
       <c r="N121" s="11" t="str">
-        <f t="shared" ref="N121:O121" si="478">if(not(isblank($B121)), N120, "")</f>
+        <f t="shared" ref="N121:O121" si="479">if(not(isblank($B121)), N120, "")</f>
         <v/>
       </c>
       <c r="O121" s="11" t="str">
-        <f t="shared" si="478"/>
+        <f t="shared" si="479"/>
         <v/>
       </c>
       <c r="P121" s="11" t="str">
@@ -12994,7 +12994,7 @@
         <v/>
       </c>
       <c r="U121" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V121" s="14" t="str">
@@ -13020,11 +13020,11 @@
         <v/>
       </c>
       <c r="E122" s="11" t="str">
-        <f t="shared" ref="E122:F122" si="479">if(not(isblank($B122)), E121, "")</f>
+        <f t="shared" ref="E122:F122" si="480">if(not(isblank($B122)), E121, "")</f>
         <v/>
       </c>
       <c r="F122" s="11" t="str">
-        <f t="shared" si="479"/>
+        <f t="shared" si="480"/>
         <v/>
       </c>
       <c r="G122" s="11" t="str">
@@ -13032,11 +13032,11 @@
         <v/>
       </c>
       <c r="H122" s="11" t="str">
-        <f t="shared" ref="H122:I122" si="480">if(not(isblank($B122)), H121, "")</f>
+        <f t="shared" ref="H122:I122" si="481">if(not(isblank($B122)), H121, "")</f>
         <v/>
       </c>
       <c r="I122" s="11" t="str">
-        <f t="shared" si="480"/>
+        <f t="shared" si="481"/>
         <v/>
       </c>
       <c r="J122" s="11" t="str">
@@ -13044,11 +13044,11 @@
         <v/>
       </c>
       <c r="K122" s="11" t="str">
-        <f t="shared" ref="K122:L122" si="481">if(not(isblank($B122)), K121, "")</f>
+        <f t="shared" ref="K122:L122" si="482">if(not(isblank($B122)), K121, "")</f>
         <v/>
       </c>
       <c r="L122" s="11" t="str">
-        <f t="shared" si="481"/>
+        <f t="shared" si="482"/>
         <v/>
       </c>
       <c r="M122" s="11" t="str">
@@ -13056,11 +13056,11 @@
         <v/>
       </c>
       <c r="N122" s="11" t="str">
-        <f t="shared" ref="N122:O122" si="482">if(not(isblank($B122)), N121, "")</f>
+        <f t="shared" ref="N122:O122" si="483">if(not(isblank($B122)), N121, "")</f>
         <v/>
       </c>
       <c r="O122" s="11" t="str">
-        <f t="shared" si="482"/>
+        <f t="shared" si="483"/>
         <v/>
       </c>
       <c r="P122" s="11" t="str">
@@ -13081,7 +13081,7 @@
         <v/>
       </c>
       <c r="U122" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V122" s="14" t="str">
@@ -13107,11 +13107,11 @@
         <v/>
       </c>
       <c r="E123" s="11" t="str">
-        <f t="shared" ref="E123:F123" si="483">if(not(isblank($B123)), E122, "")</f>
+        <f t="shared" ref="E123:F123" si="484">if(not(isblank($B123)), E122, "")</f>
         <v/>
       </c>
       <c r="F123" s="11" t="str">
-        <f t="shared" si="483"/>
+        <f t="shared" si="484"/>
         <v/>
       </c>
       <c r="G123" s="11" t="str">
@@ -13119,11 +13119,11 @@
         <v/>
       </c>
       <c r="H123" s="11" t="str">
-        <f t="shared" ref="H123:I123" si="484">if(not(isblank($B123)), H122, "")</f>
+        <f t="shared" ref="H123:I123" si="485">if(not(isblank($B123)), H122, "")</f>
         <v/>
       </c>
       <c r="I123" s="11" t="str">
-        <f t="shared" si="484"/>
+        <f t="shared" si="485"/>
         <v/>
       </c>
       <c r="J123" s="11" t="str">
@@ -13131,11 +13131,11 @@
         <v/>
       </c>
       <c r="K123" s="11" t="str">
-        <f t="shared" ref="K123:L123" si="485">if(not(isblank($B123)), K122, "")</f>
+        <f t="shared" ref="K123:L123" si="486">if(not(isblank($B123)), K122, "")</f>
         <v/>
       </c>
       <c r="L123" s="11" t="str">
-        <f t="shared" si="485"/>
+        <f t="shared" si="486"/>
         <v/>
       </c>
       <c r="M123" s="11" t="str">
@@ -13143,11 +13143,11 @@
         <v/>
       </c>
       <c r="N123" s="11" t="str">
-        <f t="shared" ref="N123:O123" si="486">if(not(isblank($B123)), N122, "")</f>
+        <f t="shared" ref="N123:O123" si="487">if(not(isblank($B123)), N122, "")</f>
         <v/>
       </c>
       <c r="O123" s="11" t="str">
-        <f t="shared" si="486"/>
+        <f t="shared" si="487"/>
         <v/>
       </c>
       <c r="P123" s="11" t="str">
@@ -13168,7 +13168,7 @@
         <v/>
       </c>
       <c r="U123" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V123" s="14" t="str">
@@ -13194,11 +13194,11 @@
         <v/>
       </c>
       <c r="E124" s="11" t="str">
-        <f t="shared" ref="E124:F124" si="487">if(not(isblank($B124)), E123, "")</f>
+        <f t="shared" ref="E124:F124" si="488">if(not(isblank($B124)), E123, "")</f>
         <v/>
       </c>
       <c r="F124" s="11" t="str">
-        <f t="shared" si="487"/>
+        <f t="shared" si="488"/>
         <v/>
       </c>
       <c r="G124" s="11" t="str">
@@ -13206,11 +13206,11 @@
         <v/>
       </c>
       <c r="H124" s="11" t="str">
-        <f t="shared" ref="H124:I124" si="488">if(not(isblank($B124)), H123, "")</f>
+        <f t="shared" ref="H124:I124" si="489">if(not(isblank($B124)), H123, "")</f>
         <v/>
       </c>
       <c r="I124" s="11" t="str">
-        <f t="shared" si="488"/>
+        <f t="shared" si="489"/>
         <v/>
       </c>
       <c r="J124" s="11" t="str">
@@ -13218,11 +13218,11 @@
         <v/>
       </c>
       <c r="K124" s="11" t="str">
-        <f t="shared" ref="K124:L124" si="489">if(not(isblank($B124)), K123, "")</f>
+        <f t="shared" ref="K124:L124" si="490">if(not(isblank($B124)), K123, "")</f>
         <v/>
       </c>
       <c r="L124" s="11" t="str">
-        <f t="shared" si="489"/>
+        <f t="shared" si="490"/>
         <v/>
       </c>
       <c r="M124" s="11" t="str">
@@ -13230,11 +13230,11 @@
         <v/>
       </c>
       <c r="N124" s="11" t="str">
-        <f t="shared" ref="N124:O124" si="490">if(not(isblank($B124)), N123, "")</f>
+        <f t="shared" ref="N124:O124" si="491">if(not(isblank($B124)), N123, "")</f>
         <v/>
       </c>
       <c r="O124" s="11" t="str">
-        <f t="shared" si="490"/>
+        <f t="shared" si="491"/>
         <v/>
       </c>
       <c r="P124" s="11" t="str">
@@ -13255,7 +13255,7 @@
         <v/>
       </c>
       <c r="U124" s="11" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="V124" s="14" t="str">

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="119">
   <si>
     <t>Data category</t>
   </si>
@@ -167,6 +167,9 @@
   </si>
   <si>
     <t>https://glodap.info/</t>
+  </si>
+  <si>
+    <t>discrete</t>
   </si>
   <si>
     <t>Water column, Open Ocean</t>
@@ -519,10 +522,10 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -882,1338 +885,1343 @@
       <c r="F3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="6"/>
+      <c r="H3" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="I3" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="7" t="s">
         <v>41</v>
       </c>
+      <c r="G4" s="6" t="s">
+        <v>42</v>
+      </c>
       <c r="H4" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K4" s="6"/>
+        <v>45</v>
+      </c>
+      <c r="K4" s="7"/>
       <c r="L4" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>41</v>
+        <v>52</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K5" s="6"/>
+        <v>54</v>
+      </c>
+      <c r="K5" s="7"/>
       <c r="L5" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6" s="6"/>
+        <v>45</v>
+      </c>
+      <c r="K6" s="7"/>
       <c r="L6" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>41</v>
+        <v>70</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" s="6"/>
+        <v>53</v>
+      </c>
+      <c r="K7" s="7"/>
       <c r="L7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="K8" s="6"/>
+      <c r="A8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="K8" s="7"/>
       <c r="L8" s="9"/>
     </row>
     <row r="9">
-      <c r="A9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="A9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="K9" s="7"/>
       <c r="L9" s="9"/>
     </row>
     <row r="10">
-      <c r="A10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="K10" s="6"/>
+      <c r="A10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="K10" s="7"/>
       <c r="L10" s="9"/>
     </row>
     <row r="11">
-      <c r="A11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="K11" s="6"/>
+      <c r="A11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="K11" s="7"/>
       <c r="L11" s="9"/>
     </row>
     <row r="12">
-      <c r="A12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="K12" s="6"/>
+      <c r="A12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="K12" s="7"/>
       <c r="L12" s="9"/>
     </row>
     <row r="13">
-      <c r="A13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="A13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="K13" s="7"/>
       <c r="L13" s="9"/>
     </row>
     <row r="14">
-      <c r="A14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="A14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="K14" s="7"/>
       <c r="L14" s="9"/>
     </row>
     <row r="15">
-      <c r="A15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="K15" s="6"/>
+      <c r="A15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="K15" s="7"/>
       <c r="L15" s="9"/>
     </row>
     <row r="16">
-      <c r="A16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="K16" s="6"/>
+      <c r="A16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="K16" s="7"/>
       <c r="L16" s="9"/>
     </row>
     <row r="17">
-      <c r="A17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="K17" s="6"/>
+      <c r="A17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="K17" s="7"/>
       <c r="L17" s="9"/>
     </row>
     <row r="18">
-      <c r="A18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="A18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="K18" s="7"/>
       <c r="L18" s="9"/>
     </row>
     <row r="19">
-      <c r="A19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="K19" s="6"/>
+      <c r="A19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="K19" s="7"/>
       <c r="L19" s="9"/>
     </row>
     <row r="20">
-      <c r="A20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="K20" s="6"/>
+      <c r="A20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="K20" s="7"/>
       <c r="L20" s="9"/>
     </row>
     <row r="21">
-      <c r="A21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="K21" s="6"/>
+      <c r="A21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="K21" s="7"/>
       <c r="L21" s="9"/>
     </row>
     <row r="22">
-      <c r="A22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="K22" s="6"/>
+      <c r="A22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="K22" s="7"/>
       <c r="L22" s="9"/>
     </row>
     <row r="23">
-      <c r="A23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="K23" s="6"/>
+      <c r="A23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="K23" s="7"/>
       <c r="L23" s="9"/>
     </row>
     <row r="24">
-      <c r="A24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="K24" s="6"/>
+      <c r="A24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="K24" s="7"/>
       <c r="L24" s="9"/>
     </row>
     <row r="25">
-      <c r="A25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="K25" s="6"/>
+      <c r="A25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="K25" s="7"/>
       <c r="L25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="K26" s="6"/>
+      <c r="A26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="K26" s="7"/>
       <c r="L26" s="9"/>
     </row>
     <row r="27">
-      <c r="A27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="K27" s="6"/>
+      <c r="A27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="K27" s="7"/>
       <c r="L27" s="9"/>
     </row>
     <row r="28">
-      <c r="A28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="K28" s="6"/>
+      <c r="A28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="K28" s="7"/>
       <c r="L28" s="9"/>
     </row>
     <row r="29">
-      <c r="A29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="K29" s="6"/>
+      <c r="A29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="K29" s="7"/>
       <c r="L29" s="9"/>
     </row>
     <row r="30">
-      <c r="A30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="K30" s="6"/>
+      <c r="A30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="K30" s="7"/>
       <c r="L30" s="9"/>
     </row>
     <row r="31">
-      <c r="A31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="K31" s="6"/>
+      <c r="A31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="K31" s="7"/>
       <c r="L31" s="9"/>
     </row>
     <row r="32">
-      <c r="A32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="K32" s="6"/>
+      <c r="A32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="K32" s="7"/>
       <c r="L32" s="9"/>
     </row>
     <row r="33">
-      <c r="A33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="K33" s="6"/>
+      <c r="A33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="K33" s="7"/>
       <c r="L33" s="9"/>
     </row>
     <row r="34">
-      <c r="A34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="K34" s="6"/>
+      <c r="A34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="K34" s="7"/>
       <c r="L34" s="9"/>
     </row>
     <row r="35">
-      <c r="A35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="K35" s="6"/>
+      <c r="A35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="K35" s="7"/>
       <c r="L35" s="9"/>
     </row>
     <row r="36">
-      <c r="A36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="K36" s="6"/>
+      <c r="A36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="K36" s="7"/>
       <c r="L36" s="9"/>
     </row>
     <row r="37">
-      <c r="A37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="K37" s="6"/>
+      <c r="A37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="K37" s="7"/>
       <c r="L37" s="9"/>
     </row>
     <row r="38">
-      <c r="A38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="K38" s="6"/>
+      <c r="A38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="K38" s="7"/>
       <c r="L38" s="9"/>
     </row>
     <row r="39">
-      <c r="A39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="K39" s="6"/>
+      <c r="A39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="K39" s="7"/>
       <c r="L39" s="9"/>
     </row>
     <row r="40">
-      <c r="A40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="K40" s="6"/>
+      <c r="A40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="K40" s="7"/>
       <c r="L40" s="9"/>
     </row>
     <row r="41">
-      <c r="A41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="K41" s="6"/>
+      <c r="A41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="K41" s="7"/>
       <c r="L41" s="9"/>
     </row>
     <row r="42">
-      <c r="A42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="K42" s="6"/>
+      <c r="A42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="K42" s="7"/>
       <c r="L42" s="9"/>
     </row>
     <row r="43">
-      <c r="A43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="K43" s="6"/>
+      <c r="A43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="K43" s="7"/>
       <c r="L43" s="9"/>
     </row>
     <row r="44">
-      <c r="A44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="K44" s="6"/>
+      <c r="A44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="K44" s="7"/>
       <c r="L44" s="9"/>
     </row>
     <row r="45">
-      <c r="A45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="K45" s="6"/>
+      <c r="A45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="K45" s="7"/>
       <c r="L45" s="9"/>
     </row>
     <row r="46">
-      <c r="A46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="K46" s="6"/>
+      <c r="A46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="K46" s="7"/>
       <c r="L46" s="9"/>
     </row>
     <row r="47">
-      <c r="A47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="K47" s="6"/>
+      <c r="A47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="K47" s="7"/>
       <c r="L47" s="9"/>
     </row>
     <row r="48">
-      <c r="A48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="K48" s="6"/>
+      <c r="A48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="K48" s="7"/>
       <c r="L48" s="9"/>
     </row>
     <row r="49">
-      <c r="A49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="K49" s="6"/>
+      <c r="A49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="K49" s="7"/>
       <c r="L49" s="9"/>
     </row>
     <row r="50">
-      <c r="A50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="K50" s="6"/>
+      <c r="A50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="K50" s="7"/>
       <c r="L50" s="9"/>
     </row>
     <row r="51">
-      <c r="A51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="K51" s="6"/>
+      <c r="A51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="K51" s="7"/>
       <c r="L51" s="9"/>
     </row>
     <row r="52">
-      <c r="A52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="K52" s="6"/>
+      <c r="A52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="7"/>
+      <c r="K52" s="7"/>
       <c r="L52" s="9"/>
     </row>
     <row r="53">
-      <c r="A53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="K53" s="6"/>
+      <c r="A53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="7"/>
+      <c r="K53" s="7"/>
       <c r="L53" s="9"/>
     </row>
     <row r="54">
-      <c r="A54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="K54" s="6"/>
+      <c r="A54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="K54" s="7"/>
       <c r="L54" s="9"/>
     </row>
     <row r="55">
-      <c r="A55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="K55" s="6"/>
+      <c r="A55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="K55" s="7"/>
       <c r="L55" s="9"/>
     </row>
     <row r="56">
-      <c r="A56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="K56" s="6"/>
+      <c r="A56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="K56" s="7"/>
       <c r="L56" s="9"/>
     </row>
     <row r="57">
-      <c r="A57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="K57" s="6"/>
+      <c r="A57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="K57" s="7"/>
       <c r="L57" s="9"/>
     </row>
     <row r="58">
-      <c r="A58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="K58" s="6"/>
+      <c r="A58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="K58" s="7"/>
       <c r="L58" s="9"/>
     </row>
     <row r="59">
-      <c r="A59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="K59" s="6"/>
+      <c r="A59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="K59" s="7"/>
       <c r="L59" s="9"/>
     </row>
     <row r="60">
-      <c r="A60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="K60" s="6"/>
+      <c r="A60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="K60" s="7"/>
       <c r="L60" s="9"/>
     </row>
     <row r="61">
-      <c r="A61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="K61" s="6"/>
+      <c r="A61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
+      <c r="K61" s="7"/>
       <c r="L61" s="9"/>
     </row>
     <row r="62">
-      <c r="A62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="K62" s="6"/>
+      <c r="A62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="K62" s="7"/>
       <c r="L62" s="9"/>
     </row>
     <row r="63">
-      <c r="A63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="K63" s="6"/>
+      <c r="A63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="K63" s="7"/>
       <c r="L63" s="9"/>
     </row>
     <row r="64">
-      <c r="A64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="K64" s="6"/>
+      <c r="A64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
+      <c r="K64" s="7"/>
       <c r="L64" s="9"/>
     </row>
     <row r="65">
-      <c r="A65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="K65" s="6"/>
+      <c r="A65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="7"/>
+      <c r="K65" s="7"/>
       <c r="L65" s="9"/>
     </row>
     <row r="66">
-      <c r="A66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="K66" s="6"/>
+      <c r="A66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
+      <c r="H66" s="7"/>
+      <c r="I66" s="7"/>
+      <c r="K66" s="7"/>
       <c r="L66" s="9"/>
     </row>
     <row r="67">
-      <c r="A67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
-      <c r="K67" s="6"/>
+      <c r="A67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="H67" s="7"/>
+      <c r="I67" s="7"/>
+      <c r="K67" s="7"/>
       <c r="L67" s="9"/>
     </row>
     <row r="68">
-      <c r="A68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="K68" s="6"/>
+      <c r="A68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+      <c r="H68" s="7"/>
+      <c r="I68" s="7"/>
+      <c r="K68" s="7"/>
       <c r="L68" s="9"/>
     </row>
     <row r="69">
-      <c r="A69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-      <c r="K69" s="6"/>
+      <c r="A69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7"/>
+      <c r="K69" s="7"/>
       <c r="L69" s="9"/>
     </row>
     <row r="70">
-      <c r="A70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-      <c r="K70" s="6"/>
+      <c r="A70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7"/>
+      <c r="K70" s="7"/>
       <c r="L70" s="9"/>
     </row>
     <row r="71">
-      <c r="A71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
-      <c r="K71" s="6"/>
+      <c r="A71" s="7"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
+      <c r="H71" s="7"/>
+      <c r="I71" s="7"/>
+      <c r="K71" s="7"/>
       <c r="L71" s="9"/>
     </row>
     <row r="72">
-      <c r="A72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="K72" s="6"/>
+      <c r="A72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="7"/>
+      <c r="K72" s="7"/>
       <c r="L72" s="9"/>
     </row>
     <row r="73">
-      <c r="A73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="6"/>
-      <c r="K73" s="6"/>
+      <c r="A73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="H73" s="7"/>
+      <c r="I73" s="7"/>
+      <c r="K73" s="7"/>
       <c r="L73" s="9"/>
     </row>
     <row r="74">
-      <c r="A74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-      <c r="K74" s="6"/>
+      <c r="A74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="K74" s="7"/>
       <c r="L74" s="9"/>
     </row>
     <row r="75">
-      <c r="A75" s="6"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="6"/>
-      <c r="K75" s="6"/>
+      <c r="A75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
+      <c r="K75" s="7"/>
       <c r="L75" s="9"/>
     </row>
     <row r="76">
-      <c r="A76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
-      <c r="K76" s="6"/>
+      <c r="A76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="7"/>
+      <c r="K76" s="7"/>
       <c r="L76" s="9"/>
     </row>
     <row r="77">
-      <c r="A77" s="6"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
-      <c r="K77" s="6"/>
+      <c r="A77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
+      <c r="H77" s="7"/>
+      <c r="I77" s="7"/>
+      <c r="K77" s="7"/>
       <c r="L77" s="9"/>
     </row>
     <row r="78">
-      <c r="A78" s="6"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="K78" s="6"/>
+      <c r="A78" s="7"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="7"/>
+      <c r="H78" s="7"/>
+      <c r="I78" s="7"/>
+      <c r="K78" s="7"/>
       <c r="L78" s="9"/>
     </row>
     <row r="79">
-      <c r="A79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-      <c r="K79" s="6"/>
+      <c r="A79" s="7"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="H79" s="7"/>
+      <c r="I79" s="7"/>
+      <c r="K79" s="7"/>
       <c r="L79" s="9"/>
     </row>
     <row r="80">
-      <c r="A80" s="6"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="K80" s="6"/>
+      <c r="A80" s="7"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7"/>
+      <c r="K80" s="7"/>
       <c r="L80" s="9"/>
     </row>
     <row r="81">
-      <c r="A81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-      <c r="K81" s="6"/>
+      <c r="A81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="7"/>
+      <c r="K81" s="7"/>
       <c r="L81" s="9"/>
     </row>
     <row r="82">
-      <c r="A82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
-      <c r="K82" s="6"/>
+      <c r="A82" s="7"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
+      <c r="H82" s="7"/>
+      <c r="I82" s="7"/>
+      <c r="K82" s="7"/>
       <c r="L82" s="9"/>
     </row>
     <row r="83">
-      <c r="A83" s="6"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="6"/>
-      <c r="F83" s="6"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="6"/>
-      <c r="K83" s="6"/>
+      <c r="A83" s="7"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="7"/>
+      <c r="H83" s="7"/>
+      <c r="I83" s="7"/>
+      <c r="K83" s="7"/>
       <c r="L83" s="9"/>
     </row>
     <row r="84">
-      <c r="A84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
-      <c r="K84" s="6"/>
+      <c r="A84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="H84" s="7"/>
+      <c r="I84" s="7"/>
+      <c r="K84" s="7"/>
       <c r="L84" s="9"/>
     </row>
     <row r="85">
-      <c r="A85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="6"/>
-      <c r="K85" s="6"/>
+      <c r="A85" s="7"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
+      <c r="H85" s="7"/>
+      <c r="I85" s="7"/>
+      <c r="K85" s="7"/>
       <c r="L85" s="9"/>
     </row>
     <row r="86">
-      <c r="A86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
-      <c r="H86" s="6"/>
-      <c r="I86" s="6"/>
-      <c r="K86" s="6"/>
+      <c r="A86" s="7"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="7"/>
+      <c r="H86" s="7"/>
+      <c r="I86" s="7"/>
+      <c r="K86" s="7"/>
       <c r="L86" s="9"/>
     </row>
     <row r="87">
-      <c r="A87" s="6"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
-      <c r="K87" s="6"/>
+      <c r="A87" s="7"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
+      <c r="H87" s="7"/>
+      <c r="I87" s="7"/>
+      <c r="K87" s="7"/>
       <c r="L87" s="9"/>
     </row>
     <row r="88">
-      <c r="A88" s="6"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="K88" s="6"/>
+      <c r="A88" s="7"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
+      <c r="H88" s="7"/>
+      <c r="I88" s="7"/>
+      <c r="K88" s="7"/>
       <c r="L88" s="9"/>
     </row>
     <row r="89">
-      <c r="A89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="6"/>
-      <c r="K89" s="6"/>
+      <c r="A89" s="7"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
+      <c r="H89" s="7"/>
+      <c r="I89" s="7"/>
+      <c r="K89" s="7"/>
       <c r="L89" s="9"/>
     </row>
     <row r="90">
-      <c r="A90" s="6"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="H90" s="6"/>
-      <c r="I90" s="6"/>
-      <c r="K90" s="6"/>
+      <c r="A90" s="7"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="7"/>
+      <c r="H90" s="7"/>
+      <c r="I90" s="7"/>
+      <c r="K90" s="7"/>
       <c r="L90" s="9"/>
     </row>
     <row r="91">
-      <c r="A91" s="6"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="6"/>
-      <c r="F91" s="6"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="6"/>
-      <c r="K91" s="6"/>
+      <c r="A91" s="7"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7"/>
+      <c r="H91" s="7"/>
+      <c r="I91" s="7"/>
+      <c r="K91" s="7"/>
       <c r="L91" s="9"/>
     </row>
     <row r="92">
-      <c r="A92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="6"/>
-      <c r="K92" s="6"/>
+      <c r="A92" s="7"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="7"/>
+      <c r="H92" s="7"/>
+      <c r="I92" s="7"/>
+      <c r="K92" s="7"/>
       <c r="L92" s="9"/>
     </row>
     <row r="93">
-      <c r="A93" s="6"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="6"/>
-      <c r="K93" s="6"/>
+      <c r="A93" s="7"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="H93" s="7"/>
+      <c r="I93" s="7"/>
+      <c r="K93" s="7"/>
       <c r="L93" s="9"/>
     </row>
     <row r="94">
-      <c r="A94" s="6"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="6"/>
-      <c r="F94" s="6"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="K94" s="6"/>
+      <c r="A94" s="7"/>
+      <c r="D94" s="7"/>
+      <c r="E94" s="7"/>
+      <c r="F94" s="7"/>
+      <c r="H94" s="7"/>
+      <c r="I94" s="7"/>
+      <c r="K94" s="7"/>
       <c r="L94" s="9"/>
     </row>
     <row r="95">
-      <c r="A95" s="6"/>
-      <c r="D95" s="6"/>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
-      <c r="K95" s="6"/>
+      <c r="A95" s="7"/>
+      <c r="D95" s="7"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
+      <c r="H95" s="7"/>
+      <c r="I95" s="7"/>
+      <c r="K95" s="7"/>
       <c r="L95" s="9"/>
     </row>
     <row r="96">
-      <c r="A96" s="6"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
-      <c r="K96" s="6"/>
+      <c r="A96" s="7"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="7"/>
+      <c r="H96" s="7"/>
+      <c r="I96" s="7"/>
+      <c r="K96" s="7"/>
       <c r="L96" s="9"/>
     </row>
     <row r="97">
-      <c r="A97" s="6"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
-      <c r="K97" s="6"/>
+      <c r="A97" s="7"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="H97" s="7"/>
+      <c r="I97" s="7"/>
+      <c r="K97" s="7"/>
       <c r="L97" s="9"/>
     </row>
     <row r="98">
-      <c r="A98" s="6"/>
-      <c r="D98" s="6"/>
-      <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="6"/>
-      <c r="K98" s="6"/>
+      <c r="A98" s="7"/>
+      <c r="D98" s="7"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="7"/>
+      <c r="H98" s="7"/>
+      <c r="I98" s="7"/>
+      <c r="K98" s="7"/>
       <c r="L98" s="9"/>
     </row>
     <row r="99">
-      <c r="A99" s="6"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
-      <c r="K99" s="6"/>
+      <c r="A99" s="7"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="7"/>
+      <c r="H99" s="7"/>
+      <c r="I99" s="7"/>
+      <c r="K99" s="7"/>
       <c r="L99" s="9"/>
     </row>
     <row r="100">
-      <c r="A100" s="6"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
-      <c r="K100" s="6"/>
+      <c r="A100" s="7"/>
+      <c r="D100" s="7"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="7"/>
+      <c r="H100" s="7"/>
+      <c r="I100" s="7"/>
+      <c r="K100" s="7"/>
       <c r="L100" s="9"/>
     </row>
     <row r="101">
-      <c r="A101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-      <c r="K101" s="6"/>
+      <c r="A101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="H101" s="7"/>
+      <c r="I101" s="7"/>
+      <c r="K101" s="7"/>
       <c r="L101" s="9"/>
     </row>
     <row r="102">
-      <c r="A102" s="6"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
-      <c r="K102" s="6"/>
+      <c r="A102" s="7"/>
+      <c r="D102" s="7"/>
+      <c r="E102" s="7"/>
+      <c r="F102" s="7"/>
+      <c r="H102" s="7"/>
+      <c r="I102" s="7"/>
+      <c r="K102" s="7"/>
       <c r="L102" s="9"/>
     </row>
     <row r="103">
-      <c r="A103" s="6"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="6"/>
-      <c r="K103" s="6"/>
+      <c r="A103" s="7"/>
+      <c r="D103" s="7"/>
+      <c r="E103" s="7"/>
+      <c r="F103" s="7"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="7"/>
+      <c r="K103" s="7"/>
       <c r="L103" s="9"/>
     </row>
     <row r="104">
-      <c r="A104" s="6"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6"/>
-      <c r="K104" s="6"/>
+      <c r="A104" s="7"/>
+      <c r="D104" s="7"/>
+      <c r="E104" s="7"/>
+      <c r="F104" s="7"/>
+      <c r="H104" s="7"/>
+      <c r="I104" s="7"/>
+      <c r="K104" s="7"/>
       <c r="L104" s="9"/>
     </row>
     <row r="105">
-      <c r="A105" s="6"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="6"/>
-      <c r="K105" s="6"/>
+      <c r="A105" s="7"/>
+      <c r="D105" s="7"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="7"/>
+      <c r="H105" s="7"/>
+      <c r="I105" s="7"/>
+      <c r="K105" s="7"/>
       <c r="L105" s="9"/>
     </row>
     <row r="106">
-      <c r="A106" s="6"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6"/>
-      <c r="K106" s="6"/>
+      <c r="A106" s="7"/>
+      <c r="D106" s="7"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="7"/>
+      <c r="H106" s="7"/>
+      <c r="I106" s="7"/>
+      <c r="K106" s="7"/>
       <c r="L106" s="9"/>
     </row>
     <row r="107">
-      <c r="A107" s="6"/>
-      <c r="D107" s="6"/>
-      <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="6"/>
-      <c r="K107" s="6"/>
+      <c r="A107" s="7"/>
+      <c r="D107" s="7"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="7"/>
+      <c r="H107" s="7"/>
+      <c r="I107" s="7"/>
+      <c r="K107" s="7"/>
       <c r="L107" s="9"/>
     </row>
     <row r="108">
-      <c r="A108" s="6"/>
-      <c r="D108" s="6"/>
-      <c r="E108" s="6"/>
-      <c r="F108" s="6"/>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6"/>
-      <c r="K108" s="6"/>
+      <c r="A108" s="7"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="7"/>
+      <c r="F108" s="7"/>
+      <c r="H108" s="7"/>
+      <c r="I108" s="7"/>
+      <c r="K108" s="7"/>
       <c r="L108" s="9"/>
     </row>
     <row r="109">
-      <c r="A109" s="6"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="6"/>
-      <c r="K109" s="6"/>
+      <c r="A109" s="7"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="7"/>
+      <c r="H109" s="7"/>
+      <c r="I109" s="7"/>
+      <c r="K109" s="7"/>
       <c r="L109" s="9"/>
     </row>
     <row r="110">
-      <c r="A110" s="6"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6"/>
-      <c r="K110" s="6"/>
+      <c r="A110" s="7"/>
+      <c r="D110" s="7"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="7"/>
+      <c r="H110" s="7"/>
+      <c r="I110" s="7"/>
+      <c r="K110" s="7"/>
       <c r="L110" s="9"/>
     </row>
     <row r="111">
-      <c r="A111" s="6"/>
-      <c r="D111" s="6"/>
-      <c r="E111" s="6"/>
-      <c r="F111" s="6"/>
-      <c r="H111" s="6"/>
-      <c r="I111" s="6"/>
-      <c r="K111" s="6"/>
+      <c r="A111" s="7"/>
+      <c r="D111" s="7"/>
+      <c r="E111" s="7"/>
+      <c r="F111" s="7"/>
+      <c r="H111" s="7"/>
+      <c r="I111" s="7"/>
+      <c r="K111" s="7"/>
       <c r="L111" s="9"/>
     </row>
     <row r="112">
-      <c r="A112" s="6"/>
-      <c r="D112" s="6"/>
-      <c r="E112" s="6"/>
-      <c r="F112" s="6"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="6"/>
-      <c r="K112" s="6"/>
+      <c r="A112" s="7"/>
+      <c r="D112" s="7"/>
+      <c r="E112" s="7"/>
+      <c r="F112" s="7"/>
+      <c r="H112" s="7"/>
+      <c r="I112" s="7"/>
+      <c r="K112" s="7"/>
       <c r="L112" s="9"/>
     </row>
     <row r="113">
-      <c r="A113" s="6"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
-      <c r="H113" s="6"/>
-      <c r="I113" s="6"/>
-      <c r="K113" s="6"/>
+      <c r="A113" s="7"/>
+      <c r="D113" s="7"/>
+      <c r="E113" s="7"/>
+      <c r="F113" s="7"/>
+      <c r="H113" s="7"/>
+      <c r="I113" s="7"/>
+      <c r="K113" s="7"/>
       <c r="L113" s="9"/>
     </row>
     <row r="114">
-      <c r="A114" s="6"/>
-      <c r="D114" s="6"/>
-      <c r="E114" s="6"/>
-      <c r="F114" s="6"/>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6"/>
-      <c r="K114" s="6"/>
+      <c r="A114" s="7"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="7"/>
+      <c r="F114" s="7"/>
+      <c r="H114" s="7"/>
+      <c r="I114" s="7"/>
+      <c r="K114" s="7"/>
       <c r="L114" s="9"/>
     </row>
     <row r="115">
-      <c r="A115" s="6"/>
-      <c r="D115" s="6"/>
-      <c r="E115" s="6"/>
-      <c r="F115" s="6"/>
-      <c r="H115" s="6"/>
-      <c r="I115" s="6"/>
-      <c r="K115" s="6"/>
+      <c r="A115" s="7"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="7"/>
+      <c r="F115" s="7"/>
+      <c r="H115" s="7"/>
+      <c r="I115" s="7"/>
+      <c r="K115" s="7"/>
       <c r="L115" s="9"/>
     </row>
     <row r="116">
-      <c r="A116" s="6"/>
-      <c r="D116" s="6"/>
-      <c r="E116" s="6"/>
-      <c r="F116" s="6"/>
-      <c r="H116" s="6"/>
-      <c r="I116" s="6"/>
-      <c r="K116" s="6"/>
+      <c r="A116" s="7"/>
+      <c r="D116" s="7"/>
+      <c r="E116" s="7"/>
+      <c r="F116" s="7"/>
+      <c r="H116" s="7"/>
+      <c r="I116" s="7"/>
+      <c r="K116" s="7"/>
       <c r="L116" s="9"/>
     </row>
     <row r="117">
-      <c r="A117" s="6"/>
-      <c r="D117" s="6"/>
-      <c r="E117" s="6"/>
-      <c r="F117" s="6"/>
-      <c r="H117" s="6"/>
-      <c r="I117" s="6"/>
-      <c r="K117" s="6"/>
+      <c r="A117" s="7"/>
+      <c r="D117" s="7"/>
+      <c r="E117" s="7"/>
+      <c r="F117" s="7"/>
+      <c r="H117" s="7"/>
+      <c r="I117" s="7"/>
+      <c r="K117" s="7"/>
       <c r="L117" s="9"/>
     </row>
     <row r="118">
-      <c r="A118" s="6"/>
-      <c r="D118" s="6"/>
-      <c r="E118" s="6"/>
-      <c r="F118" s="6"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
-      <c r="K118" s="6"/>
+      <c r="A118" s="7"/>
+      <c r="D118" s="7"/>
+      <c r="E118" s="7"/>
+      <c r="F118" s="7"/>
+      <c r="H118" s="7"/>
+      <c r="I118" s="7"/>
+      <c r="K118" s="7"/>
       <c r="L118" s="9"/>
     </row>
     <row r="119">
-      <c r="A119" s="6"/>
-      <c r="D119" s="6"/>
-      <c r="E119" s="6"/>
-      <c r="F119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
-      <c r="K119" s="6"/>
+      <c r="A119" s="7"/>
+      <c r="D119" s="7"/>
+      <c r="E119" s="7"/>
+      <c r="F119" s="7"/>
+      <c r="H119" s="7"/>
+      <c r="I119" s="7"/>
+      <c r="K119" s="7"/>
       <c r="L119" s="9"/>
     </row>
     <row r="120">
-      <c r="A120" s="6"/>
-      <c r="D120" s="6"/>
-      <c r="E120" s="6"/>
-      <c r="F120" s="6"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-      <c r="K120" s="6"/>
+      <c r="A120" s="7"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="7"/>
+      <c r="H120" s="7"/>
+      <c r="I120" s="7"/>
+      <c r="K120" s="7"/>
       <c r="L120" s="9"/>
     </row>
     <row r="121">
-      <c r="A121" s="6"/>
-      <c r="D121" s="6"/>
-      <c r="E121" s="6"/>
-      <c r="F121" s="6"/>
-      <c r="H121" s="6"/>
-      <c r="I121" s="6"/>
-      <c r="K121" s="6"/>
+      <c r="A121" s="7"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="7"/>
+      <c r="H121" s="7"/>
+      <c r="I121" s="7"/>
+      <c r="K121" s="7"/>
       <c r="L121" s="9"/>
     </row>
     <row r="122">
-      <c r="A122" s="6"/>
-      <c r="D122" s="6"/>
-      <c r="E122" s="6"/>
-      <c r="F122" s="6"/>
-      <c r="H122" s="6"/>
-      <c r="I122" s="6"/>
-      <c r="K122" s="6"/>
+      <c r="A122" s="7"/>
+      <c r="D122" s="7"/>
+      <c r="E122" s="7"/>
+      <c r="F122" s="7"/>
+      <c r="H122" s="7"/>
+      <c r="I122" s="7"/>
+      <c r="K122" s="7"/>
       <c r="L122" s="9"/>
     </row>
     <row r="123">
-      <c r="A123" s="6"/>
-      <c r="D123" s="6"/>
-      <c r="E123" s="6"/>
-      <c r="F123" s="6"/>
-      <c r="H123" s="6"/>
-      <c r="I123" s="6"/>
-      <c r="K123" s="6"/>
+      <c r="A123" s="7"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="7"/>
+      <c r="F123" s="7"/>
+      <c r="H123" s="7"/>
+      <c r="I123" s="7"/>
+      <c r="K123" s="7"/>
       <c r="L123" s="9"/>
     </row>
   </sheetData>
   <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H123">
+      <formula1>dropdown_options!$D$2:$D$14</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A123">
       <formula1>dropdown_options!$A$2:$A$8</formula1>
     </dataValidation>
@@ -2228,9 +2236,6 @@
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="E2 E3:F123">
       <formula1>IFERROR(ISURL(E2), true)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H123">
-      <formula1>dropdown_options!$D$2:$D$10</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -2270,7 +2275,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>8</v>
@@ -2287,10 +2292,10 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>19</v>
@@ -2298,72 +2303,77 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
       <c r="D8" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9">
       <c r="D9" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
       <c r="D10" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2402,138 +2412,138 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>8</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I1" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L1" s="11" t="s">
         <v>6</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U1" s="11" t="s">
         <v>12</v>
       </c>
       <c r="V1" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F2" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="H2" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="I2" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="H2" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="I2" s="12" t="s">
+      <c r="J2" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="K2" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="L2" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="K2" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="L2" s="12" t="s">
+      <c r="M2" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="N2" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="O2" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="N2" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>110</v>
-      </c>
       <c r="P2" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R2" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="T2" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U2" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="V2" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3">
@@ -2665,7 +2675,7 @@
       </c>
       <c r="J4" s="11" t="str">
         <f t="shared" si="11"/>
-        <v/>
+        <v>discrete</v>
       </c>
       <c r="K4" s="11" t="str">
         <f t="shared" ref="K4:L4" si="12">if(ISBLANK($B4), "", K$1)</f>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="122">
   <si>
     <t>Data category</t>
   </si>
@@ -324,13 +324,46 @@
     <t>https://doi.org/10.25921/295g-sn13</t>
   </si>
   <si>
-    <t>climatology, monthly</t>
+    <t>climatology, monthly, referenced</t>
   </si>
   <si>
     <t>Does not use proxy variables for extrapolation. Only produced as monthly climatology.</t>
   </si>
   <si>
     <t xml:space="preserve">Following on previous climatologies published by the late Taro Takahashi in 1997 and 2009, Fay et al. (2024) created a legacy climatology using his methodology and the updated SOCAT database of observations. This product provides 12 months of delta fCO2 values and corresponding fluxes for a base year of 2010 at 4° × 5° resolution subsequently subgridded to  1° × 1° resolution and near-global coverage. This climatology represents the mean of ocean conditions over the last four decades and is distinctive relative to many other mechanistic machine learning approaches in that it interpolates in time and space using only the available fCO2 data and a surface water advection scheme rather than using proxy variables for gap filling. It uses the median of observations to determine a reference year of 2010 and fluxes are provided using air-sea partial pressure differences and inputs from the SeaFlux product (Fay et al., 2021). </t>
+  </si>
+  <si>
+    <t>Subsurface data-derived</t>
+  </si>
+  <si>
+    <t>MOBO-DIC</t>
+  </si>
+  <si>
+    <t>MPI</t>
+  </si>
+  <si>
+    <t>Keppler et al. (2023)</t>
+  </si>
+  <si>
+    <t>https://mpimet.mpg.de/fileadmin/04_Kommunikation/01_Aktuelles/2020/201211_Paper_Keppler/Temporal_mean_MOBO-DIC_200x300_.jpg</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1029/2022GB007677</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.25921/yvzj-zx46</t>
+  </si>
+  <si>
+    <t>Open Ocean, Water column</t>
+  </si>
+  <si>
+    <t>2004 - 2019</t>
+  </si>
+  <si>
+    <t>Temporal trends and interannual variability of DIC in the interior ocean from surface to 1500 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extends the temporal resolution of MOBO-DIC to resolve monthly fields from January 2004 to December 2019, as opposed to the average climatological values in Keppler et al. (2020). This data product is on a 1° × 1° grid at 28 depth levels from the surface to 1500 m. </t>
   </si>
   <si>
     <t>Data categories</t>
@@ -352,9 +385,6 @@
   </si>
   <si>
     <t>daily</t>
-  </si>
-  <si>
-    <t>Subsurface data-derived</t>
   </si>
   <si>
     <t>Water column</t>
@@ -1082,14 +1112,46 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
+      <c r="A8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="L8" s="7"/>
-      <c r="M8" s="9"/>
+      <c r="M8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7"/>
@@ -2281,9 +2343,12 @@
     <hyperlink r:id="rId17" ref="E7"/>
     <hyperlink r:id="rId18" ref="F7"/>
     <hyperlink r:id="rId19" ref="G7"/>
+    <hyperlink r:id="rId20" ref="E8"/>
+    <hyperlink r:id="rId21" ref="F8"/>
+    <hyperlink r:id="rId22" ref="G8"/>
   </hyperlinks>
-  <drawing r:id="rId20"/>
-  <legacyDrawing r:id="rId21"/>
+  <drawing r:id="rId23"/>
+  <legacyDrawing r:id="rId24"/>
 </worksheet>
 </file>
 
@@ -2299,7 +2364,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>9</v>
@@ -2316,7 +2381,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>35</v>
@@ -2327,16 +2392,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4">
@@ -2344,18 +2409,18 @@
         <v>38</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>67</v>
@@ -2363,10 +2428,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>46</v>
@@ -2374,25 +2439,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="D8" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9">
       <c r="D9" s="1" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
       <c r="D10" s="1" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
@@ -2455,7 +2520,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G1" s="12" t="s">
         <v>9</v>
@@ -2464,7 +2529,7 @@
         <v>9</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="J1" s="12" t="s">
         <v>8</v>
@@ -2473,7 +2538,7 @@
         <v>8</v>
       </c>
       <c r="L1" s="12" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="M1" s="12" t="s">
         <v>7</v>
@@ -2482,7 +2547,7 @@
         <v>7</v>
       </c>
       <c r="O1" s="12" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>10</v>
@@ -2491,7 +2556,7 @@
         <v>10</v>
       </c>
       <c r="R1" s="12" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>2</v>
@@ -2523,79 +2588,79 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="N2" s="13" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="O2" s="13" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="P2" s="13" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="Q2" s="13" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="R2" s="13" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="S2" s="13" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="T2" s="13" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="U2" s="13" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="V2" s="13" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="W2" s="13" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="X2" s="13" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="Y2" s="13" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="Z2" s="14" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
@@ -3171,7 +3236,7 @@
       </c>
       <c r="K8" s="12" t="str">
         <f>HLOOKUP(K$1,product_listing!$1:$123,$A8,FALSE)</f>
-        <v>climatology, monthly</v>
+        <v>climatology, monthly, referenced</v>
       </c>
       <c r="L8" s="12" t="str">
         <f t="shared" ref="L8:M8" si="30">if(ISBLANK($C8), "", L$1)</f>
@@ -3241,103 +3306,103 @@
       </c>
       <c r="B9" s="12" t="str">
         <f>HLOOKUP(B$1,product_listing!$1:$123,$A9,FALSE)</f>
-        <v/>
+        <v>Subsurface data-derived</v>
       </c>
       <c r="C9" s="12" t="str">
         <f>HLOOKUP(C$1,product_listing!$1:$123,$A9,FALSE)</f>
-        <v/>
+        <v>MOBO-DIC</v>
       </c>
       <c r="D9" s="12" t="str">
         <f>HLOOKUP(D$1,product_listing!$1:$123,$A9,FALSE)</f>
-        <v/>
-      </c>
-      <c r="E9" s="12" t="str">
+        <v>Keppler et al. (2023)</v>
+      </c>
+      <c r="E9" s="15" t="str">
         <f>HLOOKUP(E$1,product_listing!$1:$123,$A9,FALSE)</f>
-        <v/>
+        <v>https://mpimet.mpg.de/fileadmin/04_Kommunikation/01_Aktuelles/2020/201211_Paper_Keppler/Temporal_mean_MOBO-DIC_200x300_.jpg</v>
       </c>
       <c r="F9" s="12" t="str">
         <f t="shared" ref="F9:G9" si="33">if(ISBLANK($C9), "", F$1)</f>
-        <v/>
+        <v>fa-solid fa-globe</v>
       </c>
       <c r="G9" s="12" t="str">
         <f t="shared" si="33"/>
-        <v/>
+        <v>Spatial domains</v>
       </c>
       <c r="H9" s="12" t="str">
         <f>HLOOKUP(H$1,product_listing!$1:$123,$A9,FALSE)</f>
-        <v/>
+        <v>Open Ocean, Water column</v>
       </c>
       <c r="I9" s="12" t="str">
         <f t="shared" ref="I9:J9" si="34">if(ISBLANK($C9), "", I$1)</f>
-        <v/>
+        <v>fa-solid fa-hourglass-start</v>
       </c>
       <c r="J9" s="12" t="str">
         <f t="shared" si="34"/>
-        <v/>
+        <v>Temporal resolution</v>
       </c>
       <c r="K9" s="12" t="str">
         <f>HLOOKUP(K$1,product_listing!$1:$123,$A9,FALSE)</f>
-        <v/>
+        <v>monthly</v>
       </c>
       <c r="L9" s="12" t="str">
         <f t="shared" ref="L9:M9" si="35">if(ISBLANK($C9), "", L$1)</f>
-        <v/>
+        <v>fa-solid fa-ruler-horizontal</v>
       </c>
       <c r="M9" s="12" t="str">
         <f t="shared" si="35"/>
-        <v/>
+        <v>Spatial resolution</v>
       </c>
       <c r="N9" s="12" t="str">
         <f>HLOOKUP(N$1,product_listing!$1:$123,$A9,FALSE)</f>
-        <v/>
+        <v>1.0°</v>
       </c>
       <c r="O9" s="12" t="str">
         <f t="shared" ref="O9:P9" si="36">if(ISBLANK($C9), "", O$1)</f>
-        <v/>
+        <v>fa-solid fa-calendar-days</v>
       </c>
       <c r="P9" s="12" t="str">
         <f t="shared" si="36"/>
-        <v/>
+        <v>Period</v>
       </c>
       <c r="Q9" s="12" t="str">
         <f>HLOOKUP(Q$1,product_listing!$1:$123,$A9,FALSE)</f>
-        <v/>
+        <v>2004 - 2019</v>
       </c>
       <c r="R9" s="12" t="str">
         <f t="shared" ref="R9:S9" si="37">if(ISBLANK($C9), "", R$1)</f>
-        <v/>
+        <v>fa-solid fa-building-columns</v>
       </c>
       <c r="S9" s="12" t="str">
         <f t="shared" si="37"/>
-        <v/>
+        <v>Institution</v>
       </c>
       <c r="T9" s="12" t="str">
         <f>HLOOKUP(T$1,product_listing!$1:$123,$A9,FALSE)</f>
-        <v/>
+        <v>MPI</v>
       </c>
       <c r="U9" s="12" t="str">
         <f>HLOOKUP(U$1,product_listing!$1:$123,$A9,FALSE)</f>
-        <v/>
+        <v>Temporal trends and interannual variability of DIC in the interior ocean from surface to 1500 m</v>
       </c>
       <c r="V9" s="12" t="str">
         <f>HLOOKUP(V$1,product_listing!$1:$123,$A9,FALSE)</f>
-        <v/>
-      </c>
-      <c r="W9" s="12" t="str">
+        <v>Keppler et al. (2023)</v>
+      </c>
+      <c r="W9" s="15" t="str">
         <f>HLOOKUP(W$1,product_listing!$1:$123,$A9,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X9" s="12" t="str">
+        <v>https://doi.org/10.1029/2022GB007677</v>
+      </c>
+      <c r="X9" s="15" t="str">
         <f>HLOOKUP(X$1,product_listing!$1:$123,$A9,FALSE)</f>
-        <v/>
+        <v>https://doi.org/10.25921/yvzj-zx46</v>
       </c>
       <c r="Y9" s="12" t="str">
         <f t="shared" si="12"/>
-        <v/>
+        <v>Description</v>
       </c>
       <c r="Z9" s="12" t="str">
         <f>HLOOKUP(Z$1,product_listing!$1:$123,$A9,FALSE)</f>
-        <v/>
+        <v>Extends the temporal resolution of MOBO-DIC to resolve monthly fields from January 2004 to December 2019, as opposed to the average climatological values in Keppler et al. (2020). This data product is on a 1° × 1° grid at 28 depth levels from the surface to 1500 m. </v>
       </c>
     </row>
     <row r="10">

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -5,7 +5,7 @@
   <sheets>
     <sheet state="visible" name="product_listing" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="dropdown_options" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="web_formatted" sheetId="3" r:id="rId6"/>
+    <sheet state="hidden" name="web_formatted" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -809,6 +809,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
+    <col customWidth="1" min="1" max="1" width="23.38"/>
     <col customWidth="1" min="2" max="2" width="17.25"/>
     <col customWidth="1" min="3" max="4" width="20.38"/>
     <col customWidth="1" min="5" max="5" width="19.75"/>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -29,44 +29,44 @@
         <t xml:space="preserve">e.g., Author et al. (2020)</t>
       </text>
     </comment>
-    <comment authorId="0" ref="E1">
+    <comment authorId="0" ref="F1">
       <text>
         <t xml:space="preserve">URL to an image
 recommended format is w300 x h200 pixels</t>
       </text>
     </comment>
-    <comment authorId="0" ref="F1">
+    <comment authorId="0" ref="G1">
       <text>
         <t xml:space="preserve">DOI to the citation</t>
       </text>
     </comment>
-    <comment authorId="0" ref="G1">
+    <comment authorId="0" ref="H1">
       <text>
         <t xml:space="preserve">Link to your data repository that is also the DOI</t>
       </text>
     </comment>
-    <comment authorId="0" ref="H1">
+    <comment authorId="0" ref="I1">
       <text>
         <t xml:space="preserve">Must be float</t>
       </text>
     </comment>
-    <comment authorId="0" ref="I1">
+    <comment authorId="0" ref="J1">
       <text>
         <t xml:space="preserve">if multiple seperate with ;</t>
       </text>
     </comment>
-    <comment authorId="0" ref="J1">
+    <comment authorId="0" ref="K1">
       <text>
         <t xml:space="preserve">e.g., coastal; open ocean; surface; water column</t>
       </text>
     </comment>
-    <comment authorId="0" ref="K1">
+    <comment authorId="0" ref="L1">
       <text>
         <t xml:space="preserve">can be YYYY-YYYY
 or climatology</t>
       </text>
     </comment>
-    <comment authorId="0" ref="L1">
+    <comment authorId="0" ref="M1">
       <text>
         <t xml:space="preserve">Only applies to observational data
 Leave blank otherwise</t>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="130">
   <si>
     <t>Data category</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>Citation</t>
+  </si>
+  <si>
+    <t>Reference</t>
   </si>
   <si>
     <t>Image</t>
@@ -141,9 +144,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Reference</t>
-  </si>
-  <si>
     <t>Data compilations</t>
   </si>
   <si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>Bakker et al. (2016)</t>
+  </si>
+  <si>
+    <t>Bakker, D. C. E., Pfeil, B., Landa, C. S., Metzl, N., O'Brien, K. M., Olsen, A., Smith, K., Cosca, C., Harasawa, S., Jones, S. D., Nakaoka, S., Nojiri, Y., Schuster, U., Steinhoff, T., Sweeney, C., Takahashi, T., Tilbrook, B., Wada, C., Wanninkhof, R., Alin, S. R., Balestrini, C. F., Barbero, L., Bates, N. R., Bianchi, A. A., Bonou, F., Boutin, J., Bozec, Y., Burger, E. F., Cai, W.-J., Castle, R. D., Chen, L., Chierici, M., Currie, K., Evans, W., Featherstone, C., Feely, R. A., Fransson, A., Goyet, C., Greenwood, N., Gregor, L., Hankin, S., Hardman-Mountford, N. J., Harlay, J., Hauck, J., Hoppema, M., Humphreys, M. P., Hunt, C. W., Huss, B., Ibánhez, J. S. P., Johannessen, T., Keeling, R., Kitidis, V., Körtzinger, A., Kozyr, A., Krasakopoulou, E., Kuwata, A., Landschützer, P., Lauvset, S. K., Lefèvre, N., Lo Monaco, C., Manke, A., Mathis, J. T., Merlivat, L., Millero, F. J., Monteiro, P. M. S., Munro, D. R., Murata, A., Newberger, T., Omar, A. M., Ono, T., Paterson, K., Pearce, D., Pierrot, D., Robbins, L. L., Saito, S., Salisbury, J., Schlitzer, R., Schneider, B., Schweitzer, R., Sieger, R., Skjelvan, I., Sullivan, K. F., Sutherland, S. C., Sutton, A. J., Tadokoro, K., Telszewski, M., Tuma, M., van Heuven, S. M. A. C., Vandemark, D., Ward, B., Watson, A. J., and Xu, S. (2016). A multi-decade record of high-quality fCO2 data in version 3 of the Surface Ocean CO2 Atlas (SOCAT), Earth Syst. Sci. Data, 8, 383–413, https://doi.org/10.5194/essd-8-383-2016.</t>
   </si>
   <si>
     <t>https://socat.info/wp-content/uploads/2017/06/cropped-socat_cat.png</t>
@@ -183,13 +186,13 @@
     <t xml:space="preserve">The Surface Ocean CO2 Atlas features surface fCO2 measurements from both the open ocean and the coastal ocean, predominantly sourced from research vessels, ships of opportunity, and autonomous platforms including fixed moorings and uncrewed surface vehicles (USVs) (Bakker et al., 2016). It represents the most extensive collection of observational ocean CO2 data for the global surface ocean. Since 2013, SOCAT has been updated annually. Dataset flags indicate the estimated uncertainty and completeness of metadata in SOCAT synthesis products. The SOCAT gridded product contains fCO2 values with an estimated uncertainty of less than 5 µatm. </t>
   </si>
   <si>
-    <t>Bakker, D. C. E., Pfeil, B., Landa, C. S., Metzl, N., O'Brien, K. M., Olsen, A., Smith, K., Cosca, C., Harasawa, S., Jones, S. D., Nakaoka, S., Nojiri, Y., Schuster, U., Steinhoff, T., Sweeney, C., Takahashi, T., Tilbrook, B., Wada, C., Wanninkhof, R., Alin, S. R., Balestrini, C. F., Barbero, L., Bates, N. R., Bianchi, A. A., Bonou, F., Boutin, J., Bozec, Y., Burger, E. F., Cai, W.-J., Castle, R. D., Chen, L., Chierici, M., Currie, K., Evans, W., Featherstone, C., Feely, R. A., Fransson, A., Goyet, C., Greenwood, N., Gregor, L., Hankin, S., Hardman-Mountford, N. J., Harlay, J., Hauck, J., Hoppema, M., Humphreys, M. P., Hunt, C. W., Huss, B., Ibánhez, J. S. P., Johannessen, T., Keeling, R., Kitidis, V., Körtzinger, A., Kozyr, A., Krasakopoulou, E., Kuwata, A., Landschützer, P., Lauvset, S. K., Lefèvre, N., Lo Monaco, C., Manke, A., Mathis, J. T., Merlivat, L., Millero, F. J., Monteiro, P. M. S., Munro, D. R., Murata, A., Newberger, T., Omar, A. M., Ono, T., Paterson, K., Pearce, D., Pierrot, D., Robbins, L. L., Saito, S., Salisbury, J., Schlitzer, R., Schneider, B., Schweitzer, R., Sieger, R., Skjelvan, I., Sullivan, K. F., Sutherland, S. C., Sutton, A. J., Tadokoro, K., Telszewski, M., Tuma, M., van Heuven, S. M. A. C., Vandemark, D., Ward, B., Watson, A. J., and Xu, S. (2016). A multi-decade record of high-quality fCO2 data in version 3 of the Surface Ocean CO2 Atlas (SOCAT), Earth Syst. Sci. Data, 8, 383–413, https://doi.org/10.5194/essd-8-383-2016.</t>
-  </si>
-  <si>
     <t>GLODAPv2</t>
   </si>
   <si>
     <t>Lauvset et al. (2024)</t>
+  </si>
+  <si>
+    <t>Lauvset, S. K., Lange, N., Tanhua, T., Bittig, H. C., Olsen, A., Kozyr, A., Álvarez, M., Azetsu-Scott, K., Brown, P. J., Carter, B. R., Cotrim da Cunha, L., Hoppema, M., Humphreys, M. P., Ishii, M., Jeansson, E., Murata, A., Müller, J. D., Pérez, F. F., Schirnick, C., Steinfeldt, R., Suzuki, T., Ulfsbo, A., Velo, A., Woosley, R. J., and Key, R. M.: The annual update GLODAPv2.2023: the global interior ocean biogeochemical data product, Earth Syst. Sci. Data, 16, 2047–2072, https://doi.org/10.5194/essd-16-2047-2024, 2024</t>
   </si>
   <si>
     <t>https://glodap.info/wp-content/uploads/2017/09/cropped-glodap_logo_trans.png</t>
@@ -219,9 +222,6 @@
     <t xml:space="preserve">The Global Ocean Data Analysis Project Version 2 (GLODAPv2) aggregates biogeochemical data collected from discrete bottle samples, offering extensive global coverage from the surface to depths (Key et al., 2015; Olsen et al., 2016; Lauvset et al., 2024). While GLODAP is primarily a product for basin-scale hydrographic data, it also includes coastal datasets and observations from a few time-series. The GLODAPv2 data product provides rigorously quality-controlled measurements for 14 essential oceanographic variables: temperature, salinity, dissolved oxygen (DO), nitrate, silicate, phosphate, DIC, TA, pH, chlorofluorocarbons (CFC-11, CFC-12, CFC-113), carbon tetrachloride (CCl4), and sulfur hexafluoride (SF6). These variables, excluding temperature, undergo both primary and secondary quality control procedures to detect outliers and adjust for significant measurement biases. GLODAPv2 was first published in 2016 and was updated annually through a living data process in Earth System Science Data from 2019 through “v2023,” which was published in 2024. For these updates, new data (including historical data not previously included in the data product) are quality controlled and adjusted to the 2016 version (Olsen et al., 2019; Olsen et al., 2020; Lauvset et al., 2021; Lauvset et al., 2022; Lauvset et al., 2024). Since the global repeat hydrography programs operate with decadal repetitions, the aim is to produce a completely new version of GLODAP, where all cruise datasets will be reevaluated, every decade. Release of the GLODAPv3 data product is planned for 2026, and is expected to evolve the secondary data quality control practices relative to those used in GLODAPv2. For more information on the secondary quality control process, refer to Tanhua et al. (2010) and Lauvset and Tanhua (2015). GLODAPv2 offers two kind of products: the collection of quality controlled data from discrete bottle samples taken at sampling location (Key et al., 2015; Olsen et al., 2016; Olsen et al., 2019; Olsen et al., 2020; Lauvset et al., 2021; Lauvset et al., 2022; Lauvset et al., 2024), and a gridded product, interpolated to a 1° × 1°  grid and the 33 standard depth levels of World Ocean Atlas (WOA) (Lauvset et al., 2016). </t>
   </si>
   <si>
-    <t>Lauvset, S. K., Lange, N., Tanhua, T., Bittig, H. C., Olsen, A., Kozyr, A., Álvarez, M., Azetsu-Scott, K., Brown, P. J., Carter, B. R., Cotrim da Cunha, L., Hoppema, M., Humphreys, M. P., Ishii, M., Jeansson, E., Murata, A., Müller, J. D., Pérez, F. F., Schirnick, C., Steinfeldt, R., Suzuki, T., Ulfsbo, A., Velo, A., Woosley, R. J., and Key, R. M.: The annual update GLODAPv2.2023: the global interior ocean biogeochemical data product, Earth Syst. Sci. Data, 16, 2047–2072, https://doi.org/10.5194/essd-16-2047-2024, 2024</t>
-  </si>
-  <si>
     <t>Gridded surface</t>
   </si>
   <si>
@@ -232,6 +232,9 @@
   </si>
   <si>
     <t>Landschützer et al. (2016)</t>
+  </si>
+  <si>
+    <t>Landschützer, P.; Gruber, N.; Bakker, D. C. Decadal Variations and Trends of the Global Ocean Carbon Sink. Global Biogeochemical Cycles 2016, 30 (10), 1396–1417. https://doi.org/10.1002/2015GB005359</t>
   </si>
   <si>
     <t>https://agupubs.onlinelibrary.wiley.com/cms/asset/547d18a7-69b5-4e93-96b2-5e8371310b43/gbc20188-fig-0001-m.jpg</t>
@@ -270,6 +273,9 @@
     <t>Gregor and Gruber (2021)</t>
   </si>
   <si>
+    <t>Gregor, L.; Gruber, N. OceanSODA-ETHZ: A Global Gridded Data Set of the Surface Ocean Carbonate System for Seasonal to Decadal Studies of Ocean Acidification. Earth System Science Data 2021, 13 (2), 777–808. https://doi.org/10.5194/essd-13-777-2021.</t>
+  </si>
+  <si>
     <t>https://essd.copernicus.org/articles/13/777/2021/essd-13-777-2021-avatar-web.png</t>
   </si>
   <si>
@@ -291,13 +297,13 @@
     <t>A monthly gridded global surface ocean data product for multiple ocean carbonate system variables, including DIC, TA, pCO2, pH (total scale), Ωarag, and Ωcalc (Gregor and Gruber, 2020; Gregor and Gruber, 2021; Gregor and Gruber, 2023; Ma et al., 2023). This dataset is structured on a 1°×1° global surface ocean grid with monthly resolution from 1982–2022, facilitating research on OA over seasonal to decadal scales. The OceanSODA-ETHZ data product was created by extrapolating in time and space the surface ocean observations of fCO2 from SOCATv2022 (Bakker et al., 2016) and TA from GLODAPv2.2022 using the newly developed Geospatial Random Cluster Ensemble Regression (GRaCER) method (Gregor, 2021). TA and pCO2 were then used to calculate the remaining variables of the marine carbonate system with the PyCO2SYS software (Humphreys et al., 2022). Phosphate and silicate from WOA 2018 product were used (Boyer et al., 2018; Garcia et al., 2018a).</t>
   </si>
   <si>
-    <t>Gregor, L.; Gruber, N. OceanSODA-ETHZ: A Global Gridded Data Set of the Surface Ocean Carbonate System for Seasonal to Decadal Studies of Ocean Acidification. Earth System Science Data 2021, 13 (2), 777–808. https://doi.org/10.5194/essd-13-777-2021.</t>
-  </si>
-  <si>
     <t>OceanSODA-ETHZv2</t>
   </si>
   <si>
     <t>Gregor et al. (2024)</t>
+  </si>
+  <si>
+    <t>Gregor, L.; Shutler, J.; Gruber, N. High-Resolution Variability of the Ocean Carbon Sink. Global Biogeochemical Cycles 2024, 38 (8), e2024GB008127. https://doi.org/10.1029/2024GB008127.</t>
   </si>
   <si>
     <t>https://agupubs.onlinelibrary.wiley.com/cms/asset/7decc330-7468-429c-bae9-ac51b085be30/gbc21584-fig-0007-m.jpg</t>
@@ -321,13 +327,13 @@
     <t>a surface fCO₂ product with a 0.25° × 0.25° spatial resolution and an 8-day temporal resolution, providing estimates starting from 1982 (Gregor et al., 2024a; Gregor et al., 2024b). The high-resolution outputs are suitable for investigating the shorter- and finer-scale dynamics of surface fCO2. Despite sharing a name with its predecessor, OceanSODA-ETHZv2 does not provide TA estimates and employs a different methodology, as described in the following steps: 1) The atmospheric trend of CO2 is removed by subtracting marine boundary layer CO2 concentrations from SOCAT fCO2 producing a new target ∆*CO2 to reduce the biases at the start and end of the time-series. 2) An 8-day seasonal climatology of ∆*CO2 is estimated using Gradient Boosted Decision Trees (GBDT), which is later used as a predictor. 3) The non-seasonal thermal component is removed from ∆*CO2, resulting in a new target, ∆*CO2nonT. 4) The new target is estimated using a feed-forward neural network, with the GBDT as one of the forcing variables. 5) Steps 4 through to 1 are inverted to arrive at fCO2. 6) Air-sea CO2 fluxes are computed using ERA5 winds.</t>
   </si>
   <si>
-    <t>Gregor, L.; Shutler, J.; Gruber, N. High-Resolution Variability of the Ocean Carbon Sink. Global Biogeochemical Cycles 2024, 38 (8), e2024GB008127. https://doi.org/10.1029/2024GB008127.</t>
-  </si>
-  <si>
     <t>fCO2 and Flux Climatology</t>
   </si>
   <si>
     <t>Fay et al. (2023)</t>
+  </si>
+  <si>
+    <t>Fay, A. R., Munro, D. R., McKinley, G. A., Pierrot, D., Sutherland, S. C., Sweeney, C., and Wanninkhof, R.: Updated climatological mean ΔfCO2 and net sea–air CO2 flux over the global open ocean regions, Earth Syst. Sci. Data, 16, 2123–2139, https://doi.org/10.5194/essd-16-2123-2024, 2024.</t>
   </si>
   <si>
     <t>https://essd.copernicus.org/articles/16/2123/2024/essd-16-2123-2024-avatar-web.png</t>
@@ -358,6 +364,9 @@
   </si>
   <si>
     <t>Keppler et al. (2023)</t>
+  </si>
+  <si>
+    <t>Keppler, L.; Landschützer, P.; Lauvset, S. K.; Gruber, N. Recent Trends and Variability in the Oceanic Storage of Dissolved Inorganic Carbon. Global Biogeochemical Cycles 2023, 37 (5), e2022GB007677. https://doi.org/10.1029/2022GB007677</t>
   </si>
   <si>
     <t>https://mpimet.mpg.de/fileadmin/04_Kommunikation/01_Aktuelles/2020/201211_Paper_Keppler/Temporal_mean_MOBO-DIC_200x300_.jpg</t>
@@ -827,17 +836,17 @@
     <col customWidth="1" min="1" max="1" width="23.38"/>
     <col customWidth="1" min="2" max="2" width="17.25"/>
     <col customWidth="1" min="3" max="4" width="20.38"/>
-    <col customWidth="1" min="5" max="5" width="19.75"/>
-    <col customWidth="1" min="6" max="6" width="21.63"/>
-    <col customWidth="1" min="7" max="7" width="24.25"/>
-    <col customWidth="1" min="8" max="8" width="13.88"/>
-    <col customWidth="1" min="9" max="9" width="23.88"/>
-    <col customWidth="1" min="10" max="10" width="29.88"/>
-    <col customWidth="1" min="11" max="11" width="12.13"/>
-    <col customWidth="1" min="12" max="12" width="18.25"/>
-    <col customWidth="1" min="13" max="13" width="34.5"/>
-    <col customWidth="1" min="14" max="14" width="31.88"/>
-    <col customWidth="1" min="15" max="15" width="59.88"/>
+    <col customWidth="1" min="5" max="5" width="36.63"/>
+    <col customWidth="1" min="6" max="6" width="19.75"/>
+    <col customWidth="1" min="7" max="7" width="21.63"/>
+    <col customWidth="1" min="8" max="8" width="24.25"/>
+    <col customWidth="1" min="9" max="9" width="13.88"/>
+    <col customWidth="1" min="10" max="10" width="23.88"/>
+    <col customWidth="1" min="11" max="11" width="29.88"/>
+    <col customWidth="1" min="12" max="12" width="12.13"/>
+    <col customWidth="1" min="13" max="13" width="18.25"/>
+    <col customWidth="1" min="14" max="14" width="34.5"/>
+    <col customWidth="1" min="15" max="15" width="31.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -900,31 +909,31 @@
       <c r="D2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="5" t="s">
         <v>27</v>
       </c>
       <c r="O2" s="1" t="s">
@@ -944,34 +953,34 @@
       <c r="D3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>34</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="4" t="s">
         <v>36</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -988,7 +997,7 @@
       <c r="D4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -997,24 +1006,27 @@
       <c r="G4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="7" t="s">
         <v>49</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="L4" s="8"/>
-      <c r="M4" s="5" t="s">
+      <c r="L4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="M4" s="8"/>
+      <c r="N4" s="5" t="s">
         <v>53</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5">
@@ -1022,44 +1034,44 @@
         <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="E5" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="F5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L5" s="8"/>
-      <c r="M5" s="5" t="s">
+      <c r="J5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="M5" s="8"/>
+      <c r="N5" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="O5" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -1067,44 +1079,44 @@
         <v>41</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="2" t="s">
         <v>67</v>
       </c>
+      <c r="E6" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="F6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H6" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="H6" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="L6" s="8"/>
-      <c r="M6" s="5" t="s">
+      <c r="I6" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>73</v>
       </c>
+      <c r="K6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" s="8"/>
+      <c r="N6" s="5" t="s">
+        <v>74</v>
+      </c>
       <c r="O6" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
@@ -1112,1273 +1124,1279 @@
         <v>41</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" s="2" t="s">
         <v>77</v>
       </c>
+      <c r="E7" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="F7" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="4" t="s">
         <v>80</v>
       </c>
+      <c r="H7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="J7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="L7" s="8"/>
-      <c r="M7" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="N7" s="1" t="s">
         <v>82</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M7" s="8"/>
+      <c r="N7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>49</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="L8" s="8"/>
-      <c r="M8" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="N8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>93</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M8" s="8"/>
+      <c r="N8" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8"/>
-      <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
-      <c r="I9" s="8"/>
+      <c r="H9" s="8"/>
       <c r="J9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="10"/>
+      <c r="K9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="10"/>
     </row>
     <row r="10">
       <c r="A10" s="8"/>
-      <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-      <c r="I10" s="8"/>
+      <c r="H10" s="8"/>
       <c r="J10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="10"/>
+      <c r="K10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="10"/>
     </row>
     <row r="11">
       <c r="A11" s="8"/>
-      <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="H11" s="8"/>
       <c r="J11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="10"/>
+      <c r="K11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="10"/>
     </row>
     <row r="12">
       <c r="A12" s="8"/>
-      <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-      <c r="I12" s="8"/>
+      <c r="H12" s="8"/>
       <c r="J12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="10"/>
+      <c r="K12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="10"/>
     </row>
     <row r="13">
       <c r="A13" s="8"/>
-      <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
-      <c r="I13" s="8"/>
+      <c r="H13" s="8"/>
       <c r="J13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="10"/>
+      <c r="K13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="10"/>
     </row>
     <row r="14">
       <c r="A14" s="8"/>
-      <c r="E14" s="8"/>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
-      <c r="I14" s="8"/>
+      <c r="H14" s="8"/>
       <c r="J14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="10"/>
+      <c r="K14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="10"/>
     </row>
     <row r="15">
       <c r="A15" s="8"/>
-      <c r="E15" s="8"/>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
-      <c r="I15" s="8"/>
+      <c r="H15" s="8"/>
       <c r="J15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="10"/>
+      <c r="K15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="10"/>
     </row>
     <row r="16">
       <c r="A16" s="8"/>
-      <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
-      <c r="I16" s="8"/>
+      <c r="H16" s="8"/>
       <c r="J16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="10"/>
+      <c r="K16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="10"/>
     </row>
     <row r="17">
       <c r="A17" s="8"/>
-      <c r="E17" s="8"/>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="I17" s="8"/>
+      <c r="H17" s="8"/>
       <c r="J17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="10"/>
+      <c r="K17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="10"/>
     </row>
     <row r="18">
       <c r="A18" s="8"/>
-      <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="I18" s="8"/>
+      <c r="H18" s="8"/>
       <c r="J18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="10"/>
+      <c r="K18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="10"/>
     </row>
     <row r="19">
       <c r="A19" s="8"/>
-      <c r="E19" s="8"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
-      <c r="I19" s="8"/>
+      <c r="H19" s="8"/>
       <c r="J19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="10"/>
+      <c r="K19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="10"/>
     </row>
     <row r="20">
       <c r="A20" s="8"/>
-      <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="I20" s="8"/>
+      <c r="H20" s="8"/>
       <c r="J20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="10"/>
+      <c r="K20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="10"/>
     </row>
     <row r="21">
       <c r="A21" s="8"/>
-      <c r="E21" s="8"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
-      <c r="I21" s="8"/>
+      <c r="H21" s="8"/>
       <c r="J21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="10"/>
+      <c r="K21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="10"/>
     </row>
     <row r="22">
       <c r="A22" s="8"/>
-      <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-      <c r="I22" s="8"/>
+      <c r="H22" s="8"/>
       <c r="J22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="10"/>
+      <c r="K22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="10"/>
     </row>
     <row r="23">
       <c r="A23" s="8"/>
-      <c r="E23" s="8"/>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
-      <c r="I23" s="8"/>
+      <c r="H23" s="8"/>
       <c r="J23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="10"/>
+      <c r="K23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="10"/>
     </row>
     <row r="24">
       <c r="A24" s="8"/>
-      <c r="E24" s="8"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
-      <c r="I24" s="8"/>
+      <c r="H24" s="8"/>
       <c r="J24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="10"/>
+      <c r="K24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="10"/>
     </row>
     <row r="25">
       <c r="A25" s="8"/>
-      <c r="E25" s="8"/>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
-      <c r="I25" s="8"/>
+      <c r="H25" s="8"/>
       <c r="J25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="10"/>
+      <c r="K25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="10"/>
     </row>
     <row r="26">
       <c r="A26" s="8"/>
-      <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
-      <c r="I26" s="8"/>
+      <c r="H26" s="8"/>
       <c r="J26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="10"/>
+      <c r="K26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="10"/>
     </row>
     <row r="27">
       <c r="A27" s="8"/>
-      <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
-      <c r="I27" s="8"/>
+      <c r="H27" s="8"/>
       <c r="J27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="10"/>
+      <c r="K27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="10"/>
     </row>
     <row r="28">
       <c r="A28" s="8"/>
-      <c r="E28" s="8"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
-      <c r="I28" s="8"/>
+      <c r="H28" s="8"/>
       <c r="J28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="10"/>
+      <c r="K28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="10"/>
     </row>
     <row r="29">
       <c r="A29" s="8"/>
-      <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
-      <c r="I29" s="8"/>
+      <c r="H29" s="8"/>
       <c r="J29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="10"/>
+      <c r="K29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="10"/>
     </row>
     <row r="30">
       <c r="A30" s="8"/>
-      <c r="E30" s="8"/>
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
-      <c r="I30" s="8"/>
+      <c r="H30" s="8"/>
       <c r="J30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="10"/>
+      <c r="K30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="10"/>
     </row>
     <row r="31">
       <c r="A31" s="8"/>
-      <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
-      <c r="I31" s="8"/>
+      <c r="H31" s="8"/>
       <c r="J31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="10"/>
+      <c r="K31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="10"/>
     </row>
     <row r="32">
       <c r="A32" s="8"/>
-      <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
-      <c r="I32" s="8"/>
+      <c r="H32" s="8"/>
       <c r="J32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="10"/>
+      <c r="K32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="10"/>
     </row>
     <row r="33">
       <c r="A33" s="8"/>
-      <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
-      <c r="I33" s="8"/>
+      <c r="H33" s="8"/>
       <c r="J33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="10"/>
+      <c r="K33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="10"/>
     </row>
     <row r="34">
       <c r="A34" s="8"/>
-      <c r="E34" s="8"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
-      <c r="I34" s="8"/>
+      <c r="H34" s="8"/>
       <c r="J34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="10"/>
+      <c r="K34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="10"/>
     </row>
     <row r="35">
       <c r="A35" s="8"/>
-      <c r="E35" s="8"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
-      <c r="I35" s="8"/>
+      <c r="H35" s="8"/>
       <c r="J35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="10"/>
+      <c r="K35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="10"/>
     </row>
     <row r="36">
       <c r="A36" s="8"/>
-      <c r="E36" s="8"/>
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
-      <c r="I36" s="8"/>
+      <c r="H36" s="8"/>
       <c r="J36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="10"/>
+      <c r="K36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="10"/>
     </row>
     <row r="37">
       <c r="A37" s="8"/>
-      <c r="E37" s="8"/>
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
-      <c r="I37" s="8"/>
+      <c r="H37" s="8"/>
       <c r="J37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="10"/>
+      <c r="K37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="10"/>
     </row>
     <row r="38">
       <c r="A38" s="8"/>
-      <c r="E38" s="8"/>
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
-      <c r="I38" s="8"/>
+      <c r="H38" s="8"/>
       <c r="J38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="10"/>
+      <c r="K38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="10"/>
     </row>
     <row r="39">
       <c r="A39" s="8"/>
-      <c r="E39" s="8"/>
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
-      <c r="I39" s="8"/>
+      <c r="H39" s="8"/>
       <c r="J39" s="8"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="10"/>
+      <c r="K39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="10"/>
     </row>
     <row r="40">
       <c r="A40" s="8"/>
-      <c r="E40" s="8"/>
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
-      <c r="I40" s="8"/>
+      <c r="H40" s="8"/>
       <c r="J40" s="8"/>
-      <c r="L40" s="8"/>
-      <c r="M40" s="10"/>
+      <c r="K40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="10"/>
     </row>
     <row r="41">
       <c r="A41" s="8"/>
-      <c r="E41" s="8"/>
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
-      <c r="I41" s="8"/>
+      <c r="H41" s="8"/>
       <c r="J41" s="8"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="10"/>
+      <c r="K41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="10"/>
     </row>
     <row r="42">
       <c r="A42" s="8"/>
-      <c r="E42" s="8"/>
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
-      <c r="I42" s="8"/>
+      <c r="H42" s="8"/>
       <c r="J42" s="8"/>
-      <c r="L42" s="8"/>
-      <c r="M42" s="10"/>
+      <c r="K42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="10"/>
     </row>
     <row r="43">
       <c r="A43" s="8"/>
-      <c r="E43" s="8"/>
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
-      <c r="I43" s="8"/>
+      <c r="H43" s="8"/>
       <c r="J43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="10"/>
+      <c r="K43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="10"/>
     </row>
     <row r="44">
       <c r="A44" s="8"/>
-      <c r="E44" s="8"/>
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
-      <c r="I44" s="8"/>
+      <c r="H44" s="8"/>
       <c r="J44" s="8"/>
-      <c r="L44" s="8"/>
-      <c r="M44" s="10"/>
+      <c r="K44" s="8"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="10"/>
     </row>
     <row r="45">
       <c r="A45" s="8"/>
-      <c r="E45" s="8"/>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
-      <c r="I45" s="8"/>
+      <c r="H45" s="8"/>
       <c r="J45" s="8"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="10"/>
+      <c r="K45" s="8"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="10"/>
     </row>
     <row r="46">
       <c r="A46" s="8"/>
-      <c r="E46" s="8"/>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
-      <c r="I46" s="8"/>
+      <c r="H46" s="8"/>
       <c r="J46" s="8"/>
-      <c r="L46" s="8"/>
-      <c r="M46" s="10"/>
+      <c r="K46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="10"/>
     </row>
     <row r="47">
       <c r="A47" s="8"/>
-      <c r="E47" s="8"/>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
-      <c r="I47" s="8"/>
+      <c r="H47" s="8"/>
       <c r="J47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="10"/>
+      <c r="K47" s="8"/>
+      <c r="M47" s="8"/>
+      <c r="N47" s="10"/>
     </row>
     <row r="48">
       <c r="A48" s="8"/>
-      <c r="E48" s="8"/>
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
-      <c r="I48" s="8"/>
+      <c r="H48" s="8"/>
       <c r="J48" s="8"/>
-      <c r="L48" s="8"/>
-      <c r="M48" s="10"/>
+      <c r="K48" s="8"/>
+      <c r="M48" s="8"/>
+      <c r="N48" s="10"/>
     </row>
     <row r="49">
       <c r="A49" s="8"/>
-      <c r="E49" s="8"/>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
-      <c r="I49" s="8"/>
+      <c r="H49" s="8"/>
       <c r="J49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="10"/>
+      <c r="K49" s="8"/>
+      <c r="M49" s="8"/>
+      <c r="N49" s="10"/>
     </row>
     <row r="50">
       <c r="A50" s="8"/>
-      <c r="E50" s="8"/>
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
-      <c r="I50" s="8"/>
+      <c r="H50" s="8"/>
       <c r="J50" s="8"/>
-      <c r="L50" s="8"/>
-      <c r="M50" s="10"/>
+      <c r="K50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="10"/>
     </row>
     <row r="51">
       <c r="A51" s="8"/>
-      <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
-      <c r="I51" s="8"/>
+      <c r="H51" s="8"/>
       <c r="J51" s="8"/>
-      <c r="L51" s="8"/>
-      <c r="M51" s="10"/>
+      <c r="K51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="10"/>
     </row>
     <row r="52">
       <c r="A52" s="8"/>
-      <c r="E52" s="8"/>
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
-      <c r="I52" s="8"/>
+      <c r="H52" s="8"/>
       <c r="J52" s="8"/>
-      <c r="L52" s="8"/>
-      <c r="M52" s="10"/>
+      <c r="K52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="10"/>
     </row>
     <row r="53">
       <c r="A53" s="8"/>
-      <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
-      <c r="I53" s="8"/>
+      <c r="H53" s="8"/>
       <c r="J53" s="8"/>
-      <c r="L53" s="8"/>
-      <c r="M53" s="10"/>
+      <c r="K53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="10"/>
     </row>
     <row r="54">
       <c r="A54" s="8"/>
-      <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
-      <c r="I54" s="8"/>
+      <c r="H54" s="8"/>
       <c r="J54" s="8"/>
-      <c r="L54" s="8"/>
-      <c r="M54" s="10"/>
+      <c r="K54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="10"/>
     </row>
     <row r="55">
       <c r="A55" s="8"/>
-      <c r="E55" s="8"/>
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
-      <c r="I55" s="8"/>
+      <c r="H55" s="8"/>
       <c r="J55" s="8"/>
-      <c r="L55" s="8"/>
-      <c r="M55" s="10"/>
+      <c r="K55" s="8"/>
+      <c r="M55" s="8"/>
+      <c r="N55" s="10"/>
     </row>
     <row r="56">
       <c r="A56" s="8"/>
-      <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
-      <c r="I56" s="8"/>
+      <c r="H56" s="8"/>
       <c r="J56" s="8"/>
-      <c r="L56" s="8"/>
-      <c r="M56" s="10"/>
+      <c r="K56" s="8"/>
+      <c r="M56" s="8"/>
+      <c r="N56" s="10"/>
     </row>
     <row r="57">
       <c r="A57" s="8"/>
-      <c r="E57" s="8"/>
       <c r="F57" s="8"/>
       <c r="G57" s="8"/>
-      <c r="I57" s="8"/>
+      <c r="H57" s="8"/>
       <c r="J57" s="8"/>
-      <c r="L57" s="8"/>
-      <c r="M57" s="10"/>
+      <c r="K57" s="8"/>
+      <c r="M57" s="8"/>
+      <c r="N57" s="10"/>
     </row>
     <row r="58">
       <c r="A58" s="8"/>
-      <c r="E58" s="8"/>
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
-      <c r="I58" s="8"/>
+      <c r="H58" s="8"/>
       <c r="J58" s="8"/>
-      <c r="L58" s="8"/>
-      <c r="M58" s="10"/>
+      <c r="K58" s="8"/>
+      <c r="M58" s="8"/>
+      <c r="N58" s="10"/>
     </row>
     <row r="59">
       <c r="A59" s="8"/>
-      <c r="E59" s="8"/>
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
-      <c r="I59" s="8"/>
+      <c r="H59" s="8"/>
       <c r="J59" s="8"/>
-      <c r="L59" s="8"/>
-      <c r="M59" s="10"/>
+      <c r="K59" s="8"/>
+      <c r="M59" s="8"/>
+      <c r="N59" s="10"/>
     </row>
     <row r="60">
       <c r="A60" s="8"/>
-      <c r="E60" s="8"/>
       <c r="F60" s="8"/>
       <c r="G60" s="8"/>
-      <c r="I60" s="8"/>
+      <c r="H60" s="8"/>
       <c r="J60" s="8"/>
-      <c r="L60" s="8"/>
-      <c r="M60" s="10"/>
+      <c r="K60" s="8"/>
+      <c r="M60" s="8"/>
+      <c r="N60" s="10"/>
     </row>
     <row r="61">
       <c r="A61" s="8"/>
-      <c r="E61" s="8"/>
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
-      <c r="I61" s="8"/>
+      <c r="H61" s="8"/>
       <c r="J61" s="8"/>
-      <c r="L61" s="8"/>
-      <c r="M61" s="10"/>
+      <c r="K61" s="8"/>
+      <c r="M61" s="8"/>
+      <c r="N61" s="10"/>
     </row>
     <row r="62">
       <c r="A62" s="8"/>
-      <c r="E62" s="8"/>
       <c r="F62" s="8"/>
       <c r="G62" s="8"/>
-      <c r="I62" s="8"/>
+      <c r="H62" s="8"/>
       <c r="J62" s="8"/>
-      <c r="L62" s="8"/>
-      <c r="M62" s="10"/>
+      <c r="K62" s="8"/>
+      <c r="M62" s="8"/>
+      <c r="N62" s="10"/>
     </row>
     <row r="63">
       <c r="A63" s="8"/>
-      <c r="E63" s="8"/>
       <c r="F63" s="8"/>
       <c r="G63" s="8"/>
-      <c r="I63" s="8"/>
+      <c r="H63" s="8"/>
       <c r="J63" s="8"/>
-      <c r="L63" s="8"/>
-      <c r="M63" s="10"/>
+      <c r="K63" s="8"/>
+      <c r="M63" s="8"/>
+      <c r="N63" s="10"/>
     </row>
     <row r="64">
       <c r="A64" s="8"/>
-      <c r="E64" s="8"/>
       <c r="F64" s="8"/>
       <c r="G64" s="8"/>
-      <c r="I64" s="8"/>
+      <c r="H64" s="8"/>
       <c r="J64" s="8"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="10"/>
+      <c r="K64" s="8"/>
+      <c r="M64" s="8"/>
+      <c r="N64" s="10"/>
     </row>
     <row r="65">
       <c r="A65" s="8"/>
-      <c r="E65" s="8"/>
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
-      <c r="I65" s="8"/>
+      <c r="H65" s="8"/>
       <c r="J65" s="8"/>
-      <c r="L65" s="8"/>
-      <c r="M65" s="10"/>
+      <c r="K65" s="8"/>
+      <c r="M65" s="8"/>
+      <c r="N65" s="10"/>
     </row>
     <row r="66">
       <c r="A66" s="8"/>
-      <c r="E66" s="8"/>
       <c r="F66" s="8"/>
       <c r="G66" s="8"/>
-      <c r="I66" s="8"/>
+      <c r="H66" s="8"/>
       <c r="J66" s="8"/>
-      <c r="L66" s="8"/>
-      <c r="M66" s="10"/>
+      <c r="K66" s="8"/>
+      <c r="M66" s="8"/>
+      <c r="N66" s="10"/>
     </row>
     <row r="67">
       <c r="A67" s="8"/>
-      <c r="E67" s="8"/>
       <c r="F67" s="8"/>
       <c r="G67" s="8"/>
-      <c r="I67" s="8"/>
+      <c r="H67" s="8"/>
       <c r="J67" s="8"/>
-      <c r="L67" s="8"/>
-      <c r="M67" s="10"/>
+      <c r="K67" s="8"/>
+      <c r="M67" s="8"/>
+      <c r="N67" s="10"/>
     </row>
     <row r="68">
       <c r="A68" s="8"/>
-      <c r="E68" s="8"/>
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
-      <c r="I68" s="8"/>
+      <c r="H68" s="8"/>
       <c r="J68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="10"/>
+      <c r="K68" s="8"/>
+      <c r="M68" s="8"/>
+      <c r="N68" s="10"/>
     </row>
     <row r="69">
       <c r="A69" s="8"/>
-      <c r="E69" s="8"/>
       <c r="F69" s="8"/>
       <c r="G69" s="8"/>
-      <c r="I69" s="8"/>
+      <c r="H69" s="8"/>
       <c r="J69" s="8"/>
-      <c r="L69" s="8"/>
-      <c r="M69" s="10"/>
+      <c r="K69" s="8"/>
+      <c r="M69" s="8"/>
+      <c r="N69" s="10"/>
     </row>
     <row r="70">
       <c r="A70" s="8"/>
-      <c r="E70" s="8"/>
       <c r="F70" s="8"/>
       <c r="G70" s="8"/>
-      <c r="I70" s="8"/>
+      <c r="H70" s="8"/>
       <c r="J70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="10"/>
+      <c r="K70" s="8"/>
+      <c r="M70" s="8"/>
+      <c r="N70" s="10"/>
     </row>
     <row r="71">
       <c r="A71" s="8"/>
-      <c r="E71" s="8"/>
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
-      <c r="I71" s="8"/>
+      <c r="H71" s="8"/>
       <c r="J71" s="8"/>
-      <c r="L71" s="8"/>
-      <c r="M71" s="10"/>
+      <c r="K71" s="8"/>
+      <c r="M71" s="8"/>
+      <c r="N71" s="10"/>
     </row>
     <row r="72">
       <c r="A72" s="8"/>
-      <c r="E72" s="8"/>
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
-      <c r="I72" s="8"/>
+      <c r="H72" s="8"/>
       <c r="J72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="10"/>
+      <c r="K72" s="8"/>
+      <c r="M72" s="8"/>
+      <c r="N72" s="10"/>
     </row>
     <row r="73">
       <c r="A73" s="8"/>
-      <c r="E73" s="8"/>
       <c r="F73" s="8"/>
       <c r="G73" s="8"/>
-      <c r="I73" s="8"/>
+      <c r="H73" s="8"/>
       <c r="J73" s="8"/>
-      <c r="L73" s="8"/>
-      <c r="M73" s="10"/>
+      <c r="K73" s="8"/>
+      <c r="M73" s="8"/>
+      <c r="N73" s="10"/>
     </row>
     <row r="74">
       <c r="A74" s="8"/>
-      <c r="E74" s="8"/>
       <c r="F74" s="8"/>
       <c r="G74" s="8"/>
-      <c r="I74" s="8"/>
+      <c r="H74" s="8"/>
       <c r="J74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="10"/>
+      <c r="K74" s="8"/>
+      <c r="M74" s="8"/>
+      <c r="N74" s="10"/>
     </row>
     <row r="75">
       <c r="A75" s="8"/>
-      <c r="E75" s="8"/>
       <c r="F75" s="8"/>
       <c r="G75" s="8"/>
-      <c r="I75" s="8"/>
+      <c r="H75" s="8"/>
       <c r="J75" s="8"/>
-      <c r="L75" s="8"/>
-      <c r="M75" s="10"/>
+      <c r="K75" s="8"/>
+      <c r="M75" s="8"/>
+      <c r="N75" s="10"/>
     </row>
     <row r="76">
       <c r="A76" s="8"/>
-      <c r="E76" s="8"/>
       <c r="F76" s="8"/>
       <c r="G76" s="8"/>
-      <c r="I76" s="8"/>
+      <c r="H76" s="8"/>
       <c r="J76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="10"/>
+      <c r="K76" s="8"/>
+      <c r="M76" s="8"/>
+      <c r="N76" s="10"/>
     </row>
     <row r="77">
       <c r="A77" s="8"/>
-      <c r="E77" s="8"/>
       <c r="F77" s="8"/>
       <c r="G77" s="8"/>
-      <c r="I77" s="8"/>
+      <c r="H77" s="8"/>
       <c r="J77" s="8"/>
-      <c r="L77" s="8"/>
-      <c r="M77" s="10"/>
+      <c r="K77" s="8"/>
+      <c r="M77" s="8"/>
+      <c r="N77" s="10"/>
     </row>
     <row r="78">
       <c r="A78" s="8"/>
-      <c r="E78" s="8"/>
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
-      <c r="I78" s="8"/>
+      <c r="H78" s="8"/>
       <c r="J78" s="8"/>
-      <c r="L78" s="8"/>
-      <c r="M78" s="10"/>
+      <c r="K78" s="8"/>
+      <c r="M78" s="8"/>
+      <c r="N78" s="10"/>
     </row>
     <row r="79">
       <c r="A79" s="8"/>
-      <c r="E79" s="8"/>
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
-      <c r="I79" s="8"/>
+      <c r="H79" s="8"/>
       <c r="J79" s="8"/>
-      <c r="L79" s="8"/>
-      <c r="M79" s="10"/>
+      <c r="K79" s="8"/>
+      <c r="M79" s="8"/>
+      <c r="N79" s="10"/>
     </row>
     <row r="80">
       <c r="A80" s="8"/>
-      <c r="E80" s="8"/>
       <c r="F80" s="8"/>
       <c r="G80" s="8"/>
-      <c r="I80" s="8"/>
+      <c r="H80" s="8"/>
       <c r="J80" s="8"/>
-      <c r="L80" s="8"/>
-      <c r="M80" s="10"/>
+      <c r="K80" s="8"/>
+      <c r="M80" s="8"/>
+      <c r="N80" s="10"/>
     </row>
     <row r="81">
       <c r="A81" s="8"/>
-      <c r="E81" s="8"/>
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
-      <c r="I81" s="8"/>
+      <c r="H81" s="8"/>
       <c r="J81" s="8"/>
-      <c r="L81" s="8"/>
-      <c r="M81" s="10"/>
+      <c r="K81" s="8"/>
+      <c r="M81" s="8"/>
+      <c r="N81" s="10"/>
     </row>
     <row r="82">
       <c r="A82" s="8"/>
-      <c r="E82" s="8"/>
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
-      <c r="I82" s="8"/>
+      <c r="H82" s="8"/>
       <c r="J82" s="8"/>
-      <c r="L82" s="8"/>
-      <c r="M82" s="10"/>
+      <c r="K82" s="8"/>
+      <c r="M82" s="8"/>
+      <c r="N82" s="10"/>
     </row>
     <row r="83">
       <c r="A83" s="8"/>
-      <c r="E83" s="8"/>
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
-      <c r="I83" s="8"/>
+      <c r="H83" s="8"/>
       <c r="J83" s="8"/>
-      <c r="L83" s="8"/>
-      <c r="M83" s="10"/>
+      <c r="K83" s="8"/>
+      <c r="M83" s="8"/>
+      <c r="N83" s="10"/>
     </row>
     <row r="84">
       <c r="A84" s="8"/>
-      <c r="E84" s="8"/>
       <c r="F84" s="8"/>
       <c r="G84" s="8"/>
-      <c r="I84" s="8"/>
+      <c r="H84" s="8"/>
       <c r="J84" s="8"/>
-      <c r="L84" s="8"/>
-      <c r="M84" s="10"/>
+      <c r="K84" s="8"/>
+      <c r="M84" s="8"/>
+      <c r="N84" s="10"/>
     </row>
     <row r="85">
       <c r="A85" s="8"/>
-      <c r="E85" s="8"/>
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
-      <c r="I85" s="8"/>
+      <c r="H85" s="8"/>
       <c r="J85" s="8"/>
-      <c r="L85" s="8"/>
-      <c r="M85" s="10"/>
+      <c r="K85" s="8"/>
+      <c r="M85" s="8"/>
+      <c r="N85" s="10"/>
     </row>
     <row r="86">
       <c r="A86" s="8"/>
-      <c r="E86" s="8"/>
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
-      <c r="I86" s="8"/>
+      <c r="H86" s="8"/>
       <c r="J86" s="8"/>
-      <c r="L86" s="8"/>
-      <c r="M86" s="10"/>
+      <c r="K86" s="8"/>
+      <c r="M86" s="8"/>
+      <c r="N86" s="10"/>
     </row>
     <row r="87">
       <c r="A87" s="8"/>
-      <c r="E87" s="8"/>
       <c r="F87" s="8"/>
       <c r="G87" s="8"/>
-      <c r="I87" s="8"/>
+      <c r="H87" s="8"/>
       <c r="J87" s="8"/>
-      <c r="L87" s="8"/>
-      <c r="M87" s="10"/>
+      <c r="K87" s="8"/>
+      <c r="M87" s="8"/>
+      <c r="N87" s="10"/>
     </row>
     <row r="88">
       <c r="A88" s="8"/>
-      <c r="E88" s="8"/>
       <c r="F88" s="8"/>
       <c r="G88" s="8"/>
-      <c r="I88" s="8"/>
+      <c r="H88" s="8"/>
       <c r="J88" s="8"/>
-      <c r="L88" s="8"/>
-      <c r="M88" s="10"/>
+      <c r="K88" s="8"/>
+      <c r="M88" s="8"/>
+      <c r="N88" s="10"/>
     </row>
     <row r="89">
       <c r="A89" s="8"/>
-      <c r="E89" s="8"/>
       <c r="F89" s="8"/>
       <c r="G89" s="8"/>
-      <c r="I89" s="8"/>
+      <c r="H89" s="8"/>
       <c r="J89" s="8"/>
-      <c r="L89" s="8"/>
-      <c r="M89" s="10"/>
+      <c r="K89" s="8"/>
+      <c r="M89" s="8"/>
+      <c r="N89" s="10"/>
     </row>
     <row r="90">
       <c r="A90" s="8"/>
-      <c r="E90" s="8"/>
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
-      <c r="I90" s="8"/>
+      <c r="H90" s="8"/>
       <c r="J90" s="8"/>
-      <c r="L90" s="8"/>
-      <c r="M90" s="10"/>
+      <c r="K90" s="8"/>
+      <c r="M90" s="8"/>
+      <c r="N90" s="10"/>
     </row>
     <row r="91">
       <c r="A91" s="8"/>
-      <c r="E91" s="8"/>
       <c r="F91" s="8"/>
       <c r="G91" s="8"/>
-      <c r="I91" s="8"/>
+      <c r="H91" s="8"/>
       <c r="J91" s="8"/>
-      <c r="L91" s="8"/>
-      <c r="M91" s="10"/>
+      <c r="K91" s="8"/>
+      <c r="M91" s="8"/>
+      <c r="N91" s="10"/>
     </row>
     <row r="92">
       <c r="A92" s="8"/>
-      <c r="E92" s="8"/>
       <c r="F92" s="8"/>
       <c r="G92" s="8"/>
-      <c r="I92" s="8"/>
+      <c r="H92" s="8"/>
       <c r="J92" s="8"/>
-      <c r="L92" s="8"/>
-      <c r="M92" s="10"/>
+      <c r="K92" s="8"/>
+      <c r="M92" s="8"/>
+      <c r="N92" s="10"/>
     </row>
     <row r="93">
       <c r="A93" s="8"/>
-      <c r="E93" s="8"/>
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
-      <c r="I93" s="8"/>
+      <c r="H93" s="8"/>
       <c r="J93" s="8"/>
-      <c r="L93" s="8"/>
-      <c r="M93" s="10"/>
+      <c r="K93" s="8"/>
+      <c r="M93" s="8"/>
+      <c r="N93" s="10"/>
     </row>
     <row r="94">
       <c r="A94" s="8"/>
-      <c r="E94" s="8"/>
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
-      <c r="I94" s="8"/>
+      <c r="H94" s="8"/>
       <c r="J94" s="8"/>
-      <c r="L94" s="8"/>
-      <c r="M94" s="10"/>
+      <c r="K94" s="8"/>
+      <c r="M94" s="8"/>
+      <c r="N94" s="10"/>
     </row>
     <row r="95">
       <c r="A95" s="8"/>
-      <c r="E95" s="8"/>
       <c r="F95" s="8"/>
       <c r="G95" s="8"/>
-      <c r="I95" s="8"/>
+      <c r="H95" s="8"/>
       <c r="J95" s="8"/>
-      <c r="L95" s="8"/>
-      <c r="M95" s="10"/>
+      <c r="K95" s="8"/>
+      <c r="M95" s="8"/>
+      <c r="N95" s="10"/>
     </row>
     <row r="96">
       <c r="A96" s="8"/>
-      <c r="E96" s="8"/>
       <c r="F96" s="8"/>
       <c r="G96" s="8"/>
-      <c r="I96" s="8"/>
+      <c r="H96" s="8"/>
       <c r="J96" s="8"/>
-      <c r="L96" s="8"/>
-      <c r="M96" s="10"/>
+      <c r="K96" s="8"/>
+      <c r="M96" s="8"/>
+      <c r="N96" s="10"/>
     </row>
     <row r="97">
       <c r="A97" s="8"/>
-      <c r="E97" s="8"/>
       <c r="F97" s="8"/>
       <c r="G97" s="8"/>
-      <c r="I97" s="8"/>
+      <c r="H97" s="8"/>
       <c r="J97" s="8"/>
-      <c r="L97" s="8"/>
-      <c r="M97" s="10"/>
+      <c r="K97" s="8"/>
+      <c r="M97" s="8"/>
+      <c r="N97" s="10"/>
     </row>
     <row r="98">
       <c r="A98" s="8"/>
-      <c r="E98" s="8"/>
       <c r="F98" s="8"/>
       <c r="G98" s="8"/>
-      <c r="I98" s="8"/>
+      <c r="H98" s="8"/>
       <c r="J98" s="8"/>
-      <c r="L98" s="8"/>
-      <c r="M98" s="10"/>
+      <c r="K98" s="8"/>
+      <c r="M98" s="8"/>
+      <c r="N98" s="10"/>
     </row>
     <row r="99">
       <c r="A99" s="8"/>
-      <c r="E99" s="8"/>
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
-      <c r="I99" s="8"/>
+      <c r="H99" s="8"/>
       <c r="J99" s="8"/>
-      <c r="L99" s="8"/>
-      <c r="M99" s="10"/>
+      <c r="K99" s="8"/>
+      <c r="M99" s="8"/>
+      <c r="N99" s="10"/>
     </row>
     <row r="100">
       <c r="A100" s="8"/>
-      <c r="E100" s="8"/>
       <c r="F100" s="8"/>
       <c r="G100" s="8"/>
-      <c r="I100" s="8"/>
+      <c r="H100" s="8"/>
       <c r="J100" s="8"/>
-      <c r="L100" s="8"/>
-      <c r="M100" s="10"/>
+      <c r="K100" s="8"/>
+      <c r="M100" s="8"/>
+      <c r="N100" s="10"/>
     </row>
     <row r="101">
       <c r="A101" s="8"/>
-      <c r="E101" s="8"/>
       <c r="F101" s="8"/>
       <c r="G101" s="8"/>
-      <c r="I101" s="8"/>
+      <c r="H101" s="8"/>
       <c r="J101" s="8"/>
-      <c r="L101" s="8"/>
-      <c r="M101" s="10"/>
+      <c r="K101" s="8"/>
+      <c r="M101" s="8"/>
+      <c r="N101" s="10"/>
     </row>
     <row r="102">
       <c r="A102" s="8"/>
-      <c r="E102" s="8"/>
       <c r="F102" s="8"/>
       <c r="G102" s="8"/>
-      <c r="I102" s="8"/>
+      <c r="H102" s="8"/>
       <c r="J102" s="8"/>
-      <c r="L102" s="8"/>
-      <c r="M102" s="10"/>
+      <c r="K102" s="8"/>
+      <c r="M102" s="8"/>
+      <c r="N102" s="10"/>
     </row>
     <row r="103">
       <c r="A103" s="8"/>
-      <c r="E103" s="8"/>
       <c r="F103" s="8"/>
       <c r="G103" s="8"/>
-      <c r="I103" s="8"/>
+      <c r="H103" s="8"/>
       <c r="J103" s="8"/>
-      <c r="L103" s="8"/>
-      <c r="M103" s="10"/>
+      <c r="K103" s="8"/>
+      <c r="M103" s="8"/>
+      <c r="N103" s="10"/>
     </row>
     <row r="104">
       <c r="A104" s="8"/>
-      <c r="E104" s="8"/>
       <c r="F104" s="8"/>
       <c r="G104" s="8"/>
-      <c r="I104" s="8"/>
+      <c r="H104" s="8"/>
       <c r="J104" s="8"/>
-      <c r="L104" s="8"/>
-      <c r="M104" s="10"/>
+      <c r="K104" s="8"/>
+      <c r="M104" s="8"/>
+      <c r="N104" s="10"/>
     </row>
     <row r="105">
       <c r="A105" s="8"/>
-      <c r="E105" s="8"/>
       <c r="F105" s="8"/>
       <c r="G105" s="8"/>
-      <c r="I105" s="8"/>
+      <c r="H105" s="8"/>
       <c r="J105" s="8"/>
-      <c r="L105" s="8"/>
-      <c r="M105" s="10"/>
+      <c r="K105" s="8"/>
+      <c r="M105" s="8"/>
+      <c r="N105" s="10"/>
     </row>
     <row r="106">
       <c r="A106" s="8"/>
-      <c r="E106" s="8"/>
       <c r="F106" s="8"/>
       <c r="G106" s="8"/>
-      <c r="I106" s="8"/>
+      <c r="H106" s="8"/>
       <c r="J106" s="8"/>
-      <c r="L106" s="8"/>
-      <c r="M106" s="10"/>
+      <c r="K106" s="8"/>
+      <c r="M106" s="8"/>
+      <c r="N106" s="10"/>
     </row>
     <row r="107">
       <c r="A107" s="8"/>
-      <c r="E107" s="8"/>
       <c r="F107" s="8"/>
       <c r="G107" s="8"/>
-      <c r="I107" s="8"/>
+      <c r="H107" s="8"/>
       <c r="J107" s="8"/>
-      <c r="L107" s="8"/>
-      <c r="M107" s="10"/>
+      <c r="K107" s="8"/>
+      <c r="M107" s="8"/>
+      <c r="N107" s="10"/>
     </row>
     <row r="108">
       <c r="A108" s="8"/>
-      <c r="E108" s="8"/>
       <c r="F108" s="8"/>
       <c r="G108" s="8"/>
-      <c r="I108" s="8"/>
+      <c r="H108" s="8"/>
       <c r="J108" s="8"/>
-      <c r="L108" s="8"/>
-      <c r="M108" s="10"/>
+      <c r="K108" s="8"/>
+      <c r="M108" s="8"/>
+      <c r="N108" s="10"/>
     </row>
     <row r="109">
       <c r="A109" s="8"/>
-      <c r="E109" s="8"/>
       <c r="F109" s="8"/>
       <c r="G109" s="8"/>
-      <c r="I109" s="8"/>
+      <c r="H109" s="8"/>
       <c r="J109" s="8"/>
-      <c r="L109" s="8"/>
-      <c r="M109" s="10"/>
+      <c r="K109" s="8"/>
+      <c r="M109" s="8"/>
+      <c r="N109" s="10"/>
     </row>
     <row r="110">
       <c r="A110" s="8"/>
-      <c r="E110" s="8"/>
       <c r="F110" s="8"/>
       <c r="G110" s="8"/>
-      <c r="I110" s="8"/>
+      <c r="H110" s="8"/>
       <c r="J110" s="8"/>
-      <c r="L110" s="8"/>
-      <c r="M110" s="10"/>
+      <c r="K110" s="8"/>
+      <c r="M110" s="8"/>
+      <c r="N110" s="10"/>
     </row>
     <row r="111">
       <c r="A111" s="8"/>
-      <c r="E111" s="8"/>
       <c r="F111" s="8"/>
       <c r="G111" s="8"/>
-      <c r="I111" s="8"/>
+      <c r="H111" s="8"/>
       <c r="J111" s="8"/>
-      <c r="L111" s="8"/>
-      <c r="M111" s="10"/>
+      <c r="K111" s="8"/>
+      <c r="M111" s="8"/>
+      <c r="N111" s="10"/>
     </row>
     <row r="112">
       <c r="A112" s="8"/>
-      <c r="E112" s="8"/>
       <c r="F112" s="8"/>
       <c r="G112" s="8"/>
-      <c r="I112" s="8"/>
+      <c r="H112" s="8"/>
       <c r="J112" s="8"/>
-      <c r="L112" s="8"/>
-      <c r="M112" s="10"/>
+      <c r="K112" s="8"/>
+      <c r="M112" s="8"/>
+      <c r="N112" s="10"/>
     </row>
     <row r="113">
       <c r="A113" s="8"/>
-      <c r="E113" s="8"/>
       <c r="F113" s="8"/>
       <c r="G113" s="8"/>
-      <c r="I113" s="8"/>
+      <c r="H113" s="8"/>
       <c r="J113" s="8"/>
-      <c r="L113" s="8"/>
-      <c r="M113" s="10"/>
+      <c r="K113" s="8"/>
+      <c r="M113" s="8"/>
+      <c r="N113" s="10"/>
     </row>
     <row r="114">
       <c r="A114" s="8"/>
-      <c r="E114" s="8"/>
       <c r="F114" s="8"/>
       <c r="G114" s="8"/>
-      <c r="I114" s="8"/>
+      <c r="H114" s="8"/>
       <c r="J114" s="8"/>
-      <c r="L114" s="8"/>
-      <c r="M114" s="10"/>
+      <c r="K114" s="8"/>
+      <c r="M114" s="8"/>
+      <c r="N114" s="10"/>
     </row>
     <row r="115">
       <c r="A115" s="8"/>
-      <c r="E115" s="8"/>
       <c r="F115" s="8"/>
       <c r="G115" s="8"/>
-      <c r="I115" s="8"/>
+      <c r="H115" s="8"/>
       <c r="J115" s="8"/>
-      <c r="L115" s="8"/>
-      <c r="M115" s="10"/>
+      <c r="K115" s="8"/>
+      <c r="M115" s="8"/>
+      <c r="N115" s="10"/>
     </row>
     <row r="116">
       <c r="A116" s="8"/>
-      <c r="E116" s="8"/>
       <c r="F116" s="8"/>
       <c r="G116" s="8"/>
-      <c r="I116" s="8"/>
+      <c r="H116" s="8"/>
       <c r="J116" s="8"/>
-      <c r="L116" s="8"/>
-      <c r="M116" s="10"/>
+      <c r="K116" s="8"/>
+      <c r="M116" s="8"/>
+      <c r="N116" s="10"/>
     </row>
     <row r="117">
       <c r="A117" s="8"/>
-      <c r="E117" s="8"/>
       <c r="F117" s="8"/>
       <c r="G117" s="8"/>
-      <c r="I117" s="8"/>
+      <c r="H117" s="8"/>
       <c r="J117" s="8"/>
-      <c r="L117" s="8"/>
-      <c r="M117" s="10"/>
+      <c r="K117" s="8"/>
+      <c r="M117" s="8"/>
+      <c r="N117" s="10"/>
     </row>
     <row r="118">
       <c r="A118" s="8"/>
-      <c r="E118" s="8"/>
       <c r="F118" s="8"/>
       <c r="G118" s="8"/>
-      <c r="I118" s="8"/>
+      <c r="H118" s="8"/>
       <c r="J118" s="8"/>
-      <c r="L118" s="8"/>
-      <c r="M118" s="10"/>
+      <c r="K118" s="8"/>
+      <c r="M118" s="8"/>
+      <c r="N118" s="10"/>
     </row>
     <row r="119">
       <c r="A119" s="8"/>
-      <c r="E119" s="8"/>
       <c r="F119" s="8"/>
       <c r="G119" s="8"/>
-      <c r="I119" s="8"/>
+      <c r="H119" s="8"/>
       <c r="J119" s="8"/>
-      <c r="L119" s="8"/>
-      <c r="M119" s="10"/>
+      <c r="K119" s="8"/>
+      <c r="M119" s="8"/>
+      <c r="N119" s="10"/>
     </row>
     <row r="120">
       <c r="A120" s="8"/>
-      <c r="E120" s="8"/>
       <c r="F120" s="8"/>
       <c r="G120" s="8"/>
-      <c r="I120" s="8"/>
+      <c r="H120" s="8"/>
       <c r="J120" s="8"/>
-      <c r="L120" s="8"/>
-      <c r="M120" s="10"/>
+      <c r="K120" s="8"/>
+      <c r="M120" s="8"/>
+      <c r="N120" s="10"/>
     </row>
     <row r="121">
       <c r="A121" s="8"/>
-      <c r="E121" s="8"/>
       <c r="F121" s="8"/>
       <c r="G121" s="8"/>
-      <c r="I121" s="8"/>
+      <c r="H121" s="8"/>
       <c r="J121" s="8"/>
-      <c r="L121" s="8"/>
-      <c r="M121" s="10"/>
+      <c r="K121" s="8"/>
+      <c r="M121" s="8"/>
+      <c r="N121" s="10"/>
     </row>
     <row r="122">
       <c r="A122" s="8"/>
-      <c r="E122" s="8"/>
       <c r="F122" s="8"/>
       <c r="G122" s="8"/>
-      <c r="I122" s="8"/>
+      <c r="H122" s="8"/>
       <c r="J122" s="8"/>
-      <c r="L122" s="8"/>
-      <c r="M122" s="10"/>
+      <c r="K122" s="8"/>
+      <c r="M122" s="8"/>
+      <c r="N122" s="10"/>
     </row>
     <row r="123">
       <c r="A123" s="8"/>
-      <c r="E123" s="8"/>
       <c r="F123" s="8"/>
       <c r="G123" s="8"/>
-      <c r="I123" s="8"/>
+      <c r="H123" s="8"/>
       <c r="J123" s="8"/>
-      <c r="L123" s="8"/>
-      <c r="M123" s="10"/>
+      <c r="K123" s="8"/>
+      <c r="M123" s="8"/>
+      <c r="N123" s="10"/>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I123">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J2:J123">
       <formula1>dropdown_options!$D$2:$D$14</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A123">
       <formula1>dropdown_options!$A$2:$A$8</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J2:J123">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K123">
       <formula1>dropdown_options!$B$2:$B$9</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" showInputMessage="1" prompt="Must be a url to an image" sqref="E2:E123">
-      <formula1>IFERROR(ISURL(E2), true)</formula1>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" showInputMessage="1" prompt="Must be a url to an image" sqref="F2:F123">
+      <formula1>IFERROR(ISURL(F2), true)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:L123">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M2:M123">
       <formula1>dropdown_options!$C$2:$C$5</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2 F3:G123">
-      <formula1>IFERROR(ISURL(F2), true)</formula1>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="G2 G3:H123">
+      <formula1>IFERROR(ISURL(G2), true)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink r:id="rId2" ref="E2"/>
-    <hyperlink r:id="rId3" ref="F2"/>
-    <hyperlink r:id="rId4" ref="G2"/>
-    <hyperlink r:id="rId5" ref="E3"/>
-    <hyperlink r:id="rId6" ref="F3"/>
-    <hyperlink r:id="rId7" ref="G3"/>
-    <hyperlink r:id="rId8" ref="E4"/>
-    <hyperlink r:id="rId9" ref="F4"/>
-    <hyperlink r:id="rId10" ref="G4"/>
-    <hyperlink r:id="rId11" ref="E5"/>
-    <hyperlink r:id="rId12" ref="F5"/>
-    <hyperlink r:id="rId13" ref="G5"/>
-    <hyperlink r:id="rId14" ref="E6"/>
-    <hyperlink r:id="rId15" ref="F6"/>
-    <hyperlink r:id="rId16" ref="G6"/>
-    <hyperlink r:id="rId17" ref="E7"/>
-    <hyperlink r:id="rId18" ref="F7"/>
-    <hyperlink r:id="rId19" ref="G7"/>
-    <hyperlink r:id="rId20" ref="E8"/>
-    <hyperlink r:id="rId21" ref="F8"/>
-    <hyperlink r:id="rId22" ref="G8"/>
+    <hyperlink r:id="rId2" ref="F2"/>
+    <hyperlink r:id="rId3" ref="G2"/>
+    <hyperlink r:id="rId4" ref="H2"/>
+    <hyperlink r:id="rId5" ref="F3"/>
+    <hyperlink r:id="rId6" ref="G3"/>
+    <hyperlink r:id="rId7" ref="H3"/>
+    <hyperlink r:id="rId8" ref="F4"/>
+    <hyperlink r:id="rId9" ref="G4"/>
+    <hyperlink r:id="rId10" ref="H4"/>
+    <hyperlink r:id="rId11" ref="F5"/>
+    <hyperlink r:id="rId12" ref="G5"/>
+    <hyperlink r:id="rId13" ref="H5"/>
+    <hyperlink r:id="rId14" ref="F6"/>
+    <hyperlink r:id="rId15" ref="G6"/>
+    <hyperlink r:id="rId16" ref="H6"/>
+    <hyperlink r:id="rId17" ref="F7"/>
+    <hyperlink r:id="rId18" ref="G7"/>
+    <hyperlink r:id="rId19" ref="H7"/>
+    <hyperlink r:id="rId20" ref="F8"/>
+    <hyperlink r:id="rId21" ref="G8"/>
+    <hyperlink r:id="rId22" ref="H8"/>
   </hyperlinks>
   <drawing r:id="rId23"/>
   <legacyDrawing r:id="rId24"/>
@@ -2397,16 +2415,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2">
@@ -2414,27 +2432,27 @@
         <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4">
@@ -2442,60 +2460,60 @@
         <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8">
       <c r="D8" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9">
       <c r="D9" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
       <c r="D10" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11">
       <c r="D11" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2550,46 +2568,46 @@
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="O1" s="6" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>2</v>
@@ -2598,28 +2616,28 @@
         <v>2</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V1" s="6" t="s">
         <v>3</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y1" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z1" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA1" s="6" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AB1" s="6" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2">
@@ -2627,85 +2645,85 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="N2" s="13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O2" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="P2" s="13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="Q2" s="13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="R2" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="S2" s="13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="T2" s="13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="U2" s="13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="V2" s="13" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="W2" s="13" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="X2" s="13" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="Y2" s="13" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Z2" s="14" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AA2" s="13" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="AB2" s="14" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3">
@@ -3047,7 +3065,7 @@
       </c>
       <c r="AB5" s="6" t="str">
         <f>HLOOKUP(AB$1,product_listing!$1:$123,$A5,FALSE)</f>
-        <v/>
+        <v>Landschützer, P.; Gruber, N.; Bakker, D. C. Decadal Variations and Trends of the Global Ocean Carbon Sink. Global Biogeochemical Cycles 2016, 30 (10), 1396–1417. https://doi.org/10.1002/2015GB005359</v>
       </c>
     </row>
     <row r="6">
@@ -3389,7 +3407,7 @@
       </c>
       <c r="AB8" s="6" t="str">
         <f>HLOOKUP(AB$1,product_listing!$1:$123,$A8,FALSE)</f>
-        <v/>
+        <v>Fay, A. R., Munro, D. R., McKinley, G. A., Pierrot, D., Sutherland, S. C., Sweeney, C., and Wanninkhof, R.: Updated climatological mean ΔfCO2 and net sea–air CO2 flux over the global open ocean regions, Earth Syst. Sci. Data, 16, 2123–2139, https://doi.org/10.5194/essd-16-2123-2024, 2024.</v>
       </c>
     </row>
     <row r="9">
@@ -3503,7 +3521,7 @@
       </c>
       <c r="AB9" s="6" t="str">
         <f>HLOOKUP(AB$1,product_listing!$1:$123,$A9,FALSE)</f>
-        <v/>
+        <v>Keppler, L.; Landschützer, P.; Lauvset, S. K.; Gruber, N. Recent Trends and Variability in the Oceanic Storage of Dissolved Inorganic Carbon. Global Biogeochemical Cycles 2023, 37 (5), e2022GB007677. https://doi.org/10.1029/2022GB007677</v>
       </c>
     </row>
     <row r="10">

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="131">
   <si>
     <t>Data category</t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>fCO2 and Flux Climatology</t>
+  </si>
+  <si>
+    <t>LDEO</t>
   </si>
   <si>
     <t>Fay et al. (2023)</t>
@@ -1126,63 +1129,65 @@
       <c r="B7" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="D7" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>49</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>62</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>49</v>
@@ -1191,17 +1196,17 @@
         <v>50</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9">
@@ -2415,7 +2420,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>10</v>
@@ -2432,7 +2437,7 @@
         <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>38</v>
@@ -2443,16 +2448,16 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4">
@@ -2460,18 +2465,18 @@
         <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>73</v>
@@ -2479,10 +2484,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>50</v>
@@ -2490,25 +2495,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8">
       <c r="D8" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9">
       <c r="D9" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
       <c r="D10" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11">
@@ -2571,7 +2576,7 @@
         <v>5</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>10</v>
@@ -2580,7 +2585,7 @@
         <v>10</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>9</v>
@@ -2589,7 +2594,7 @@
         <v>9</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M1" s="6" t="s">
         <v>8</v>
@@ -2598,7 +2603,7 @@
         <v>8</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>11</v>
@@ -2607,7 +2612,7 @@
         <v>11</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>2</v>
@@ -2645,85 +2650,85 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G2" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="I2" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="J2" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="I2" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="J2" s="13" t="s">
+      <c r="K2" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="L2" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="M2" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="L2" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="M2" s="13" t="s">
+      <c r="N2" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="O2" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="P2" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="O2" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="P2" s="13" t="s">
+      <c r="Q2" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="R2" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="Q2" s="13" t="s">
+      <c r="S2" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="R2" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="S2" s="13" t="s">
-        <v>122</v>
-      </c>
       <c r="T2" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="U2" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="V2" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="W2" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="X2" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y2" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Z2" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA2" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="AA2" s="13" t="s">
-        <v>128</v>
-      </c>
       <c r="AB2" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3">
@@ -3375,7 +3380,7 @@
       </c>
       <c r="T8" s="6" t="str">
         <f>HLOOKUP(T$1,product_listing!$1:$123,$A8,FALSE)</f>
-        <v/>
+        <v>LDEO</v>
       </c>
       <c r="U8" s="6" t="str">
         <f>HLOOKUP(U$1,product_listing!$1:$123,$A8,FALSE)</f>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -6,7 +6,7 @@
     <sheet state="visible" name="google_form" sheetId="1" r:id="rId4"/>
     <sheet state="hidden" name="product_listing" sheetId="2" r:id="rId5"/>
     <sheet state="hidden" name="dropdown_options" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="web_formatted" sheetId="4" r:id="rId7"/>
+    <sheet state="hidden" name="web_formatted" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -226,6 +226,42 @@
     <t>Gridded surface</t>
   </si>
   <si>
+    <t>CSIR-ML6</t>
+  </si>
+  <si>
+    <t>Gregor et al. (2019)</t>
+  </si>
+  <si>
+    <t>Gregor, L., Lebehot, A. D., Kok, S., and Scheel Monteiro, P. M.: A comparative assessment of the uncertainties of global surface ocean CO2 estimates using a machine-learning ensemble (CSIR-ML6 version 2019a) – have we hit the wall?, Geosci. Model Dev., 12, 5113–5136, https://doi.org/10.5194/gmd-12-5113-2019, 2019.</t>
+  </si>
+  <si>
+    <t>https://gmd.copernicus.org/articles/12/5113/2019/gmd-12-5113-2019-f09-thumb.png</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5194/gmd-12-5113-2019</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.25921/z682-mn47</t>
+  </si>
+  <si>
+    <t>1.0°</t>
+  </si>
+  <si>
+    <t>monthly</t>
+  </si>
+  <si>
+    <t>Open ocean, Surface</t>
+  </si>
+  <si>
+    <t>1982 - 2020</t>
+  </si>
+  <si>
+    <t>Various ML methods produce different results when data is sparse, but all still achieving roughly the same uncertainty</t>
+  </si>
+  <si>
+    <t>Provides monthly 1° × 1° estimates of surface pCO2 (Gregor et al., 2019a). The approach uses the conceptual two-step approach of clustering and performing regressions for each cluster as Landschützer et al. (2016). CSIR-ML6 investigates the efficacy of various machine learning (ML) methods in estimating surface pCO2, namely, feed-forward neural networks (FFNN), extremely randomized trees (ERT), gradient boosting machines (GBM), and support vector regression (SVR). It is found that the ensemble of all but the ERT method resulted in the best estimate, highlighting the fact that various ML methods do not produce the same outcome, particularly when data is sparse. Further, the variance between ensemble members can inform us about regions where uncertainty may be large due to methodological differences. Despite this, all methods achieve roughly the same uncertainty – a barrier, or wall beyond which the community has yet to overcome.</t>
+  </si>
+  <si>
     <t>OceanSODA-ETHZv1</t>
   </si>
   <si>
@@ -242,15 +278,6 @@
   </si>
   <si>
     <t>https://doi.org/10.25921/m5wx-ja34</t>
-  </si>
-  <si>
-    <t>1.0°</t>
-  </si>
-  <si>
-    <t>monthly</t>
-  </si>
-  <si>
-    <t>Open ocean, Surface</t>
   </si>
   <si>
     <t>1982 - 2022</t>
@@ -323,33 +350,6 @@
   </si>
   <si>
     <t>Harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach (Gregor and Fay, 2021). This resource provides an ensemble of six pCO2 products with air-sea CO2 fluxes computed consistently. The six included products are: CMEMS-LSCEv1, CSIR-ML6, JENA-MLS, JMA-MLR, MPI-SOMFFN, and NIES-FNN. First, missing areas of pCO2 estimates (mostly high-latitude and marginal seas) are filled using a linear-regression approach, thus addressing differences in spatial coverage between the mapping products. Further, also accounts for methodological inconsistencies in flux calculations. Fluxes are calculated using three wind products (CCMPv2, ERA5, and JRA55) along with the application of a scaled gas exchange coefficient for each of the wind products. Through these steps, SeaFlux presents a product ensemble of interpolated global surface ocean pCO2 and air–sea carbon flux estimates for the years 1990–2019</t>
-  </si>
-  <si>
-    <t>CSIR-ML6</t>
-  </si>
-  <si>
-    <t>Gregor et al. (2019)</t>
-  </si>
-  <si>
-    <t>Gregor, L., Lebehot, A. D., Kok, S., and Scheel Monteiro, P. M.: A comparative assessment of the uncertainties of global surface ocean CO2 estimates using a machine-learning ensemble (CSIR-ML6 version 2019a) – have we hit the wall?, Geosci. Model Dev., 12, 5113–5136, https://doi.org/10.5194/gmd-12-5113-2019, 2019.</t>
-  </si>
-  <si>
-    <t>https://gmd.copernicus.org/articles/12/5113/2019/gmd-12-5113-2019-f09-thumb.png</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.5194/gmd-12-5113-2019</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.25921/z682-mn47</t>
-  </si>
-  <si>
-    <t>1982 - 2020</t>
-  </si>
-  <si>
-    <t>Various ML methods produce different results when data is sparse, but all still achieving roughly the same uncertainty</t>
-  </si>
-  <si>
-    <t>Provides monthly 1° × 1° estimates of surface pCO2 (Gregor et al., 2019a). The approach uses the conceptual two-step approach of clustering and performing regressions for each cluster as Landschützer et al. (2016). CSIR-ML6 investigates the efficacy of various machine learning (ML) methods in estimating surface pCO2, namely, feed-forward neural networks (FFNN), extremely randomized trees (ERT), gradient boosting machines (GBM), and support vector regression (SVR). It is found that the ensemble of all but the ERT method resulted in the best estimate, highlighting the fact that various ML methods do not produce the same outcome, particularly when data is sparse. Further, the variance between ensemble members can inform us about regions where uncertainty may be large due to methodological differences. Despite this, all methods achieve roughly the same uncertainty – a barrier, or wall beyond which the community has yet to overcome.</t>
   </si>
   <si>
     <t>Institution</t>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>45961.909583877314</v>
+        <v>45961.95201907407</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>41</v>
@@ -1245,7 +1245,7 @@
       <c r="H4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="4" t="s">
         <v>48</v>
       </c>
       <c r="J4" s="4" t="s">
@@ -1263,11 +1263,10 @@
       <c r="O4" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="P4" s="7"/>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>45961.91270586806</v>
+        <v>45961.909583877314</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>41</v>
@@ -1290,115 +1289,116 @@
       <c r="H5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>60</v>
+      <c r="I5" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>50</v>
       </c>
       <c r="L5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="P5" s="7"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>45961.91270586806</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="P5" s="7"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="10">
+      <c r="E6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="P6" s="7"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10">
         <v>45961.90485893519</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="I6" s="8" t="s">
+      <c r="B7" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J7" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K7" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="O6" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="P6" s="14"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3">
-        <v>45961.95201907407</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="M7" s="13"/>
+      <c r="N7" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="11" t="s">
         <v>83</v>
       </c>
+      <c r="P7" s="14"/>
     </row>
     <row r="8">
       <c r="A8" s="10"/>
@@ -2685,25 +2685,25 @@
         <v>41</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>102</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="I5" s="21" t="s">
         <v>48</v>
@@ -2715,14 +2715,14 @@
         <v>103</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="M5" s="22"/>
       <c r="N5" s="19" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -2730,28 +2730,28 @@
         <v>41</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>102</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J6" s="15" t="s">
         <v>104</v>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="M6" s="22"/>
       <c r="N6" s="19" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="O6" s="15" t="s">
         <v>105</v>
@@ -4573,15 +4573,15 @@
       </c>
       <c r="C5" s="20" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$126,$A5,FALSE)</f>
-        <v>OceanSODA-ETHZv1</v>
+        <v>CSIR-ML6</v>
       </c>
       <c r="D5" s="20" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$126,$A5,FALSE)</f>
-        <v>Gregor and Gruber (2021)</v>
+        <v>Gregor et al. (2019)</v>
       </c>
       <c r="E5" s="29" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$126,$A5,FALSE)</f>
-        <v>https://essd.copernicus.org/articles/13/777/2021/essd-13-777-2021-avatar-web.png</v>
+        <v>https://gmd.copernicus.org/articles/12/5113/2019/gmd-12-5113-2019-f09-thumb.png</v>
       </c>
       <c r="F5" s="20" t="str">
         <f t="shared" ref="F5:G5" si="12">if(ISBLANK($C5), "", F$1)</f>
@@ -4629,23 +4629,23 @@
       </c>
       <c r="Q5" s="20" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$126,$A5,FALSE)</f>
-        <v>1982 - 2022</v>
+        <v>1982 - 2020</v>
       </c>
       <c r="R5" s="20" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$126,$A5,FALSE)</f>
-        <v>Temporal trends of DIC, TA, pCO2, pH, Ωarag, and Ωcalc</v>
+        <v>Various ML methods produce different results when data is sparse, but all still achieving roughly the same uncertainty</v>
       </c>
       <c r="S5" s="20" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$126,$A5,FALSE)</f>
-        <v>Gregor and Gruber (2021)</v>
+        <v>Gregor et al. (2019)</v>
       </c>
       <c r="T5" s="29" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$126,$A5,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-13-777-2021</v>
+        <v>https://doi.org/10.5194/gmd-12-5113-2019</v>
       </c>
       <c r="U5" s="29" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$126,$A5,FALSE)</f>
-        <v>https://doi.org/10.25921/m5wx-ja34</v>
+        <v>https://doi.org/10.25921/z682-mn47</v>
       </c>
       <c r="V5" s="20" t="str">
         <f t="shared" si="10"/>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="W5" s="20" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$126,$A5,FALSE)</f>
-        <v>A monthly gridded global surface ocean data product for multiple ocean carbonate system variables, including DIC, TA, pCO2, pH (total scale), Ωarag, and Ωcalc (Gregor and Gruber, 2020; Gregor and Gruber, 2021; Gregor and Gruber, 2023; Ma et al., 2023). This dataset is structured on a 1°×1° global surface ocean grid with monthly resolution from 1982–2022, facilitating research on OA over seasonal to decadal scales. The OceanSODA-ETHZ data product was created by extrapolating in time and space the surface ocean observations of fCO2 from SOCATv2022 (Bakker et al., 2016) and TA from GLODAPv2.2022 using the newly developed Geospatial Random Cluster Ensemble Regression (GRaCER) method (Gregor, 2021). TA and pCO2 were then used to calculate the remaining variables of the marine carbonate system with the PyCO2SYS software (Humphreys et al., 2022). Phosphate and silicate from WOA 2018 product were used (Boyer et al., 2018; Garcia et al., 2018a).</v>
+        <v>Provides monthly 1° × 1° estimates of surface pCO2 (Gregor et al., 2019a). The approach uses the conceptual two-step approach of clustering and performing regressions for each cluster as Landschützer et al. (2016). CSIR-ML6 investigates the efficacy of various machine learning (ML) methods in estimating surface pCO2, namely, feed-forward neural networks (FFNN), extremely randomized trees (ERT), gradient boosting machines (GBM), and support vector regression (SVR). It is found that the ensemble of all but the ERT method resulted in the best estimate, highlighting the fact that various ML methods do not produce the same outcome, particularly when data is sparse. Further, the variance between ensemble members can inform us about regions where uncertainty may be large due to methodological differences. Despite this, all methods achieve roughly the same uncertainty – a barrier, or wall beyond which the community has yet to overcome.</v>
       </c>
       <c r="X5" s="20" t="str">
         <f t="shared" si="11"/>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="Y5" s="20" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$126,$A5,FALSE)</f>
-        <v>Gregor, L.; Gruber, N. OceanSODA-ETHZ: A Global Gridded Data Set of the Surface Ocean Carbonate System for Seasonal to Decadal Studies of Ocean Acidification. Earth System Science Data 2021, 13 (2), 777–808. https://doi.org/10.5194/essd-13-777-2021.</v>
+        <v>Gregor, L., Lebehot, A. D., Kok, S., and Scheel Monteiro, P. M.: A comparative assessment of the uncertainties of global surface ocean CO2 estimates using a machine-learning ensemble (CSIR-ML6 version 2019a) – have we hit the wall?, Geosci. Model Dev., 12, 5113–5136, https://doi.org/10.5194/gmd-12-5113-2019, 2019.</v>
       </c>
     </row>
     <row r="6">
@@ -4675,15 +4675,15 @@
       </c>
       <c r="C6" s="20" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$126,$A6,FALSE)</f>
-        <v>OceanSODA-ETHZv2</v>
+        <v>OceanSODA-ETHZv1</v>
       </c>
       <c r="D6" s="20" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$126,$A6,FALSE)</f>
-        <v>Gregor et al. (2024)</v>
+        <v>Gregor and Gruber (2021)</v>
       </c>
       <c r="E6" s="29" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$126,$A6,FALSE)</f>
-        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/7decc330-7468-429c-bae9-ac51b085be30/gbc21584-fig-0007-m.jpg</v>
+        <v>https://essd.copernicus.org/articles/13/777/2021/essd-13-777-2021-avatar-web.png</v>
       </c>
       <c r="F6" s="20" t="str">
         <f t="shared" ref="F6:G6" si="16">if(ISBLANK($C6), "", F$1)</f>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="K6" s="20" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$126,$A6,FALSE)</f>
-        <v>8-day</v>
+        <v>monthly</v>
       </c>
       <c r="L6" s="20" t="str">
         <f t="shared" ref="L6:M6" si="18">if(ISBLANK($C6), "", L$1)</f>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="N6" s="30" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$126,$A6,FALSE)</f>
-        <v>0.25°</v>
+        <v>1.0°</v>
       </c>
       <c r="O6" s="20" t="str">
         <f t="shared" ref="O6:P6" si="19">if(ISBLANK($C6), "", O$1)</f>
@@ -4731,23 +4731,23 @@
       </c>
       <c r="Q6" s="20" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$126,$A6,FALSE)</f>
-        <v>1982 - 2023</v>
+        <v>1982 - 2022</v>
       </c>
       <c r="R6" s="20" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$126,$A6,FALSE)</f>
-        <v>Highlighting fine-scale and short-term variability of the ocean carbon sink</v>
+        <v>Temporal trends of DIC, TA, pCO2, pH, Ωarag, and Ωcalc</v>
       </c>
       <c r="S6" s="20" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$126,$A6,FALSE)</f>
-        <v>Gregor et al. (2024)</v>
+        <v>Gregor and Gruber (2021)</v>
       </c>
       <c r="T6" s="29" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$126,$A6,FALSE)</f>
-        <v>https://doi.org/10.1029/2024GB008127</v>
+        <v>https://doi.org/10.5194/essd-13-777-2021</v>
       </c>
       <c r="U6" s="29" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$126,$A6,FALSE)</f>
-        <v>https://zenodo.org/records/11206366</v>
+        <v>https://doi.org/10.25921/m5wx-ja34</v>
       </c>
       <c r="V6" s="20" t="str">
         <f t="shared" si="10"/>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="W6" s="20" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$126,$A6,FALSE)</f>
-        <v>A surface fCO₂ product with a 0.25° × 0.25° spatial resolution and an 8-day temporal resolution, providing estimates starting from 1982 (Gregor et al., 2024a; Gregor et al., 2024b). The high-resolution outputs are suitable for investigating the shorter- and finer-scale dynamics of surface fCO2. Despite sharing a name with its predecessor, OceanSODA-ETHZv2 does not provide TA estimates and employs a different methodology, as described in the following steps: 1) The atmospheric trend of CO2 is removed by subtracting marine boundary layer CO2 concentrations from SOCAT fCO2 producing a new target ∆*CO2 to reduce the biases at the start and end of the time-series. 2) An 8-day seasonal climatology of ∆*CO2 is estimated using Gradient Boosted Decision Trees (GBDT), which is later used as a predictor. 3) The non-seasonal thermal component is removed from ∆*CO2, resulting in a new target, ∆*CO2nonT. 4) The new target is estimated using a feed-forward neural network, with the GBDT as one of the forcing variables. 5) Steps 4 through to 1 are inverted to arrive at fCO2. 6) Air-sea CO2 fluxes are computed using ERA5 winds.</v>
+        <v>A monthly gridded global surface ocean data product for multiple ocean carbonate system variables, including DIC, TA, pCO2, pH (total scale), Ωarag, and Ωcalc (Gregor and Gruber, 2020; Gregor and Gruber, 2021; Gregor and Gruber, 2023; Ma et al., 2023). This dataset is structured on a 1°×1° global surface ocean grid with monthly resolution from 1982–2022, facilitating research on OA over seasonal to decadal scales. The OceanSODA-ETHZ data product was created by extrapolating in time and space the surface ocean observations of fCO2 from SOCATv2022 (Bakker et al., 2016) and TA from GLODAPv2.2022 using the newly developed Geospatial Random Cluster Ensemble Regression (GRaCER) method (Gregor, 2021). TA and pCO2 were then used to calculate the remaining variables of the marine carbonate system with the PyCO2SYS software (Humphreys et al., 2022). Phosphate and silicate from WOA 2018 product were used (Boyer et al., 2018; Garcia et al., 2018a).</v>
       </c>
       <c r="X6" s="20" t="str">
         <f t="shared" si="11"/>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y6" s="20" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$126,$A6,FALSE)</f>
-        <v>Gregor, L.; Shutler, J.; Gruber, N. High-Resolution Variability of the Ocean Carbon Sink. Global Biogeochemical Cycles 2024, 38 (8), e2024GB008127. https://doi.org/10.1029/2024GB008127.</v>
+        <v>Gregor, L.; Gruber, N. OceanSODA-ETHZ: A Global Gridded Data Set of the Surface Ocean Carbonate System for Seasonal to Decadal Studies of Ocean Acidification. Earth System Science Data 2021, 13 (2), 777–808. https://doi.org/10.5194/essd-13-777-2021.</v>
       </c>
     </row>
     <row r="7">
@@ -4773,19 +4773,19 @@
       </c>
       <c r="B7" s="20" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$126,$A7,FALSE)</f>
-        <v>Harmonized</v>
+        <v>Gridded surface</v>
       </c>
       <c r="C7" s="20" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$126,$A7,FALSE)</f>
-        <v>SeaFlux</v>
+        <v>OceanSODA-ETHZv2</v>
       </c>
       <c r="D7" s="20" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$126,$A7,FALSE)</f>
-        <v>Fay and Gregor et al. (2021)</v>
+        <v>Gregor et al. (2024)</v>
       </c>
       <c r="E7" s="29" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$126,$A7,FALSE)</f>
-        <v>https://seaflux.readthedocs.io/en/latest/_static/seaflux_logo.png</v>
+        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/7decc330-7468-429c-bae9-ac51b085be30/gbc21584-fig-0007-m.jpg</v>
       </c>
       <c r="F7" s="20" t="str">
         <f t="shared" ref="F7:G7" si="20">if(ISBLANK($C7), "", F$1)</f>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K7" s="20" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$126,$A7,FALSE)</f>
-        <v>monthly</v>
+        <v>8-day</v>
       </c>
       <c r="L7" s="20" t="str">
         <f t="shared" ref="L7:M7" si="22">if(ISBLANK($C7), "", L$1)</f>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="N7" s="30" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$126,$A7,FALSE)</f>
-        <v>1.0°</v>
+        <v>0.25°</v>
       </c>
       <c r="O7" s="20" t="str">
         <f t="shared" ref="O7:P7" si="23">if(ISBLANK($C7), "", O$1)</f>
@@ -4833,23 +4833,23 @@
       </c>
       <c r="Q7" s="20" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$126,$A7,FALSE)</f>
-        <v>1990 - 2022</v>
+        <v>1982 - 2023</v>
       </c>
       <c r="R7" s="20" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$126,$A7,FALSE)</f>
-        <v>Careful consideration of flux calculation provides a resource and code to the community for independent flux calculations</v>
+        <v>Highlighting fine-scale and short-term variability of the ocean carbon sink</v>
       </c>
       <c r="S7" s="20" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$126,$A7,FALSE)</f>
-        <v>Fay and Gregor et al. (2021)</v>
+        <v>Gregor et al. (2024)</v>
       </c>
       <c r="T7" s="29" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$126,$A7,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-2021-16</v>
+        <v>https://doi.org/10.1029/2024GB008127</v>
       </c>
       <c r="U7" s="29" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$126,$A7,FALSE)</f>
-        <v>https://zenodo.org/records/8280457</v>
+        <v>https://zenodo.org/records/11206366</v>
       </c>
       <c r="V7" s="20" t="str">
         <f t="shared" si="10"/>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W7" s="20" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$126,$A7,FALSE)</f>
-        <v>Harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach (Gregor and Fay, 2021). This resource provides an ensemble of six pCO2 products with air-sea CO2 fluxes computed consistently. The six included products are: CMEMS-LSCEv1, CSIR-ML6, JENA-MLS, JMA-MLR, MPI-SOMFFN, and NIES-FNN. First, missing areas of pCO2 estimates (mostly high-latitude and marginal seas) are filled using a linear-regression approach, thus addressing differences in spatial coverage between the mapping products. Further, also accounts for methodological inconsistencies in flux calculations. Fluxes are calculated using three wind products (CCMPv2, ERA5, and JRA55) along with the application of a scaled gas exchange coefficient for each of the wind products. Through these steps, SeaFlux presents a product ensemble of interpolated global surface ocean pCO2 and air–sea carbon flux estimates for the years 1990–2019</v>
+        <v>A surface fCO₂ product with a 0.25° × 0.25° spatial resolution and an 8-day temporal resolution, providing estimates starting from 1982 (Gregor et al., 2024a; Gregor et al., 2024b). The high-resolution outputs are suitable for investigating the shorter- and finer-scale dynamics of surface fCO2. Despite sharing a name with its predecessor, OceanSODA-ETHZv2 does not provide TA estimates and employs a different methodology, as described in the following steps: 1) The atmospheric trend of CO2 is removed by subtracting marine boundary layer CO2 concentrations from SOCAT fCO2 producing a new target ∆*CO2 to reduce the biases at the start and end of the time-series. 2) An 8-day seasonal climatology of ∆*CO2 is estimated using Gradient Boosted Decision Trees (GBDT), which is later used as a predictor. 3) The non-seasonal thermal component is removed from ∆*CO2, resulting in a new target, ∆*CO2nonT. 4) The new target is estimated using a feed-forward neural network, with the GBDT as one of the forcing variables. 5) Steps 4 through to 1 are inverted to arrive at fCO2. 6) Air-sea CO2 fluxes are computed using ERA5 winds.</v>
       </c>
       <c r="X7" s="20" t="str">
         <f t="shared" si="11"/>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="Y7" s="20" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$126,$A7,FALSE)</f>
-        <v>Fay, A. R., Gregor, L., Landschützer, P., McKinley, G. A., Gruber, N., Gehlen, M., Iida, Y., Laruelle, G. G., Rödenbeck, C., Roobaert, A., and Zeng, J.: SeaFlux: harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach, Earth Syst. Sci. Data, 13, 4693–4710, https://doi.org/10.5194/essd-13-4693-2021, 2021</v>
+        <v>Gregor, L.; Shutler, J.; Gruber, N. High-Resolution Variability of the Ocean Carbon Sink. Global Biogeochemical Cycles 2024, 38 (8), e2024GB008127. https://doi.org/10.1029/2024GB008127.</v>
       </c>
     </row>
     <row r="8">
@@ -4875,19 +4875,19 @@
       </c>
       <c r="B8" s="20" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$126,$A8,FALSE)</f>
-        <v>Gridded surface</v>
+        <v>Harmonized</v>
       </c>
       <c r="C8" s="20" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$126,$A8,FALSE)</f>
-        <v>CSIR-ML6</v>
+        <v>SeaFlux</v>
       </c>
       <c r="D8" s="20" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$126,$A8,FALSE)</f>
-        <v>Gregor et al. (2019)</v>
+        <v>Fay and Gregor et al. (2021)</v>
       </c>
       <c r="E8" s="29" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$126,$A8,FALSE)</f>
-        <v>https://gmd.copernicus.org/articles/12/5113/2019/gmd-12-5113-2019-f09-thumb.png</v>
+        <v>https://seaflux.readthedocs.io/en/latest/_static/seaflux_logo.png</v>
       </c>
       <c r="F8" s="20" t="str">
         <f t="shared" ref="F8:G8" si="24">if(ISBLANK($C8), "", F$1)</f>
@@ -4935,23 +4935,23 @@
       </c>
       <c r="Q8" s="20" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$126,$A8,FALSE)</f>
-        <v>1982 - 2020</v>
+        <v>1990 - 2022</v>
       </c>
       <c r="R8" s="20" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$126,$A8,FALSE)</f>
-        <v>Various ML methods produce different results when data is sparse, but all still achieving roughly the same uncertainty</v>
+        <v>Careful consideration of flux calculation provides a resource and code to the community for independent flux calculations</v>
       </c>
       <c r="S8" s="20" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$126,$A8,FALSE)</f>
-        <v>Gregor et al. (2019)</v>
+        <v>Fay and Gregor et al. (2021)</v>
       </c>
       <c r="T8" s="29" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$126,$A8,FALSE)</f>
-        <v>https://doi.org/10.5194/gmd-12-5113-2019</v>
+        <v>https://doi.org/10.5194/essd-2021-16</v>
       </c>
       <c r="U8" s="29" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$126,$A8,FALSE)</f>
-        <v>https://doi.org/10.25921/z682-mn47</v>
+        <v>https://zenodo.org/records/8280457</v>
       </c>
       <c r="V8" s="20" t="str">
         <f t="shared" si="10"/>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="W8" s="20" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$126,$A8,FALSE)</f>
-        <v>Provides monthly 1° × 1° estimates of surface pCO2 (Gregor et al., 2019a). The approach uses the conceptual two-step approach of clustering and performing regressions for each cluster as Landschützer et al. (2016). CSIR-ML6 investigates the efficacy of various machine learning (ML) methods in estimating surface pCO2, namely, feed-forward neural networks (FFNN), extremely randomized trees (ERT), gradient boosting machines (GBM), and support vector regression (SVR). It is found that the ensemble of all but the ERT method resulted in the best estimate, highlighting the fact that various ML methods do not produce the same outcome, particularly when data is sparse. Further, the variance between ensemble members can inform us about regions where uncertainty may be large due to methodological differences. Despite this, all methods achieve roughly the same uncertainty – a barrier, or wall beyond which the community has yet to overcome.</v>
+        <v>Harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach (Gregor and Fay, 2021). This resource provides an ensemble of six pCO2 products with air-sea CO2 fluxes computed consistently. The six included products are: CMEMS-LSCEv1, CSIR-ML6, JENA-MLS, JMA-MLR, MPI-SOMFFN, and NIES-FNN. First, missing areas of pCO2 estimates (mostly high-latitude and marginal seas) are filled using a linear-regression approach, thus addressing differences in spatial coverage between the mapping products. Further, also accounts for methodological inconsistencies in flux calculations. Fluxes are calculated using three wind products (CCMPv2, ERA5, and JRA55) along with the application of a scaled gas exchange coefficient for each of the wind products. Through these steps, SeaFlux presents a product ensemble of interpolated global surface ocean pCO2 and air–sea carbon flux estimates for the years 1990–2019</v>
       </c>
       <c r="X8" s="20" t="str">
         <f t="shared" si="11"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="Y8" s="20" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$126,$A8,FALSE)</f>
-        <v>Gregor, L., Lebehot, A. D., Kok, S., and Scheel Monteiro, P. M.: A comparative assessment of the uncertainties of global surface ocean CO2 estimates using a machine-learning ensemble (CSIR-ML6 version 2019a) – have we hit the wall?, Geosci. Model Dev., 12, 5113–5136, https://doi.org/10.5194/gmd-12-5113-2019, 2019.</v>
+        <v>Fay, A. R., Gregor, L., Landschützer, P., McKinley, G. A., Gruber, N., Gehlen, M., Iida, Y., Laruelle, G. G., Rödenbeck, C., Roobaert, A., and Zeng, J.: SeaFlux: harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach, Earth Syst. Sci. Data, 13, 4693–4710, https://doi.org/10.5194/essd-13-4693-2021, 2021</v>
       </c>
     </row>
     <row r="9">

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="google_form" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="web_formatted" sheetId="2" r:id="rId5"/>
+    <sheet state="hidden" name="web_formatted" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="123">
   <si>
     <t>Timestamp</t>
   </si>
@@ -178,7 +178,7 @@
     <t>https://doi.org/10.25921/z682-mn47</t>
   </si>
   <si>
-    <t>1.0°</t>
+    <t>1° x 1°</t>
   </si>
   <si>
     <t>monthly</t>
@@ -241,7 +241,7 @@
     <t>https://zenodo.org/records/11206366</t>
   </si>
   <si>
-    <t>0.25°</t>
+    <t>0.25° x 0.25°</t>
   </si>
   <si>
     <t>8-day</t>
@@ -335,9 +335,6 @@
   </si>
   <si>
     <t>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0139360.html</t>
-  </si>
-  <si>
-    <t>1° x 1°</t>
   </si>
   <si>
     <t>climatology</t>
@@ -507,9 +504,6 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -524,6 +518,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -1092,7 +1089,7 @@
       <c r="H5" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="10" t="s">
         <v>48</v>
       </c>
       <c r="J5" s="5" t="s">
@@ -1137,7 +1134,7 @@
       <c r="H6" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="11" t="s">
         <v>69</v>
       </c>
       <c r="J6" s="5" t="s">
@@ -1158,50 +1155,50 @@
       <c r="P6" s="8"/>
     </row>
     <row r="7">
-      <c r="A7" s="13">
+      <c r="A7" s="12">
         <v>45961.90485893519</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="L7" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="M7" s="16"/>
-      <c r="N7" s="14" t="s">
+      <c r="M7" s="15"/>
+      <c r="N7" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="O7" s="14" t="s">
+      <c r="O7" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="P7" s="17"/>
+      <c r="P7" s="16"/>
     </row>
     <row r="8">
       <c r="A8" s="4">
@@ -1274,1067 +1271,1067 @@
         <v>100</v>
       </c>
       <c r="I9" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>102</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>36</v>
       </c>
       <c r="L9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="N9" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="N9" s="5" t="s">
+      <c r="O9" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="O9" s="5" t="s">
-        <v>105</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="17"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="16"/>
     </row>
     <row r="11">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="17"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="16"/>
     </row>
     <row r="12">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="17"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="16"/>
     </row>
     <row r="13">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="17"/>
+      <c r="A13" s="12"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="16"/>
     </row>
     <row r="14">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="17"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="16"/>
     </row>
     <row r="15">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="17"/>
+      <c r="A15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="16"/>
     </row>
     <row r="16">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="17"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="16"/>
     </row>
     <row r="17">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="17"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="16"/>
     </row>
     <row r="18">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="17"/>
+      <c r="A18" s="12"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="16"/>
     </row>
     <row r="19">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="17"/>
+      <c r="A19" s="12"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="16"/>
     </row>
     <row r="20">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="17"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="16"/>
     </row>
     <row r="21">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="17"/>
+      <c r="A21" s="12"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="16"/>
     </row>
     <row r="22">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="17"/>
+      <c r="A22" s="12"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="16"/>
     </row>
     <row r="23">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="17"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="16"/>
     </row>
     <row r="24">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="17"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="16"/>
     </row>
     <row r="25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="17"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="16"/>
     </row>
     <row r="26">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="17"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="16"/>
     </row>
     <row r="27">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="14"/>
-      <c r="P27" s="17"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="16"/>
     </row>
     <row r="28">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="17"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="16"/>
     </row>
     <row r="29">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14"/>
-      <c r="P29" s="17"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="16"/>
     </row>
     <row r="30">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="17"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="16"/>
     </row>
     <row r="31">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14"/>
-      <c r="P31" s="17"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="16"/>
     </row>
     <row r="32">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="17"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="16"/>
     </row>
     <row r="33">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="17"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="16"/>
     </row>
     <row r="34">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14"/>
-      <c r="P34" s="17"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13"/>
+      <c r="P34" s="16"/>
     </row>
     <row r="35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14"/>
-      <c r="P35" s="17"/>
+      <c r="A35" s="12"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="16"/>
     </row>
     <row r="36">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
-      <c r="P36" s="17"/>
+      <c r="A36" s="12"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="16"/>
     </row>
     <row r="37">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="14"/>
-      <c r="P37" s="17"/>
+      <c r="A37" s="12"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13"/>
+      <c r="P37" s="16"/>
     </row>
     <row r="38">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="14"/>
-      <c r="O38" s="14"/>
-      <c r="P38" s="17"/>
+      <c r="A38" s="12"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13"/>
+      <c r="P38" s="16"/>
     </row>
     <row r="39">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="14"/>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="14"/>
-      <c r="O39" s="14"/>
-      <c r="P39" s="17"/>
+      <c r="A39" s="12"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="16"/>
     </row>
     <row r="40">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="14"/>
-      <c r="O40" s="14"/>
-      <c r="P40" s="17"/>
+      <c r="A40" s="12"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13"/>
+      <c r="P40" s="16"/>
     </row>
     <row r="41">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="14"/>
-      <c r="O41" s="14"/>
-      <c r="P41" s="17"/>
+      <c r="A41" s="12"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13"/>
+      <c r="P41" s="16"/>
     </row>
     <row r="42">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="14"/>
-      <c r="O42" s="14"/>
-      <c r="P42" s="17"/>
+      <c r="A42" s="12"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+      <c r="M42" s="15"/>
+      <c r="N42" s="13"/>
+      <c r="O42" s="13"/>
+      <c r="P42" s="16"/>
     </row>
     <row r="43">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="14"/>
-      <c r="K43" s="14"/>
-      <c r="L43" s="14"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="14"/>
-      <c r="O43" s="14"/>
-      <c r="P43" s="17"/>
+      <c r="A43" s="12"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="13"/>
+      <c r="K43" s="13"/>
+      <c r="L43" s="13"/>
+      <c r="M43" s="15"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13"/>
+      <c r="P43" s="16"/>
     </row>
     <row r="44">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="14"/>
-      <c r="K44" s="14"/>
-      <c r="L44" s="14"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="14"/>
-      <c r="O44" s="14"/>
-      <c r="P44" s="17"/>
+      <c r="A44" s="12"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="13"/>
+      <c r="M44" s="15"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13"/>
+      <c r="P44" s="16"/>
     </row>
     <row r="45">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="14"/>
-      <c r="K45" s="14"/>
-      <c r="L45" s="14"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="14"/>
-      <c r="O45" s="14"/>
-      <c r="P45" s="17"/>
+      <c r="A45" s="12"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="13"/>
+      <c r="M45" s="15"/>
+      <c r="N45" s="13"/>
+      <c r="O45" s="13"/>
+      <c r="P45" s="16"/>
     </row>
     <row r="46">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="14"/>
-      <c r="K46" s="14"/>
-      <c r="L46" s="14"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="14"/>
-      <c r="O46" s="14"/>
-      <c r="P46" s="17"/>
+      <c r="A46" s="12"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="15"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13"/>
+      <c r="P46" s="16"/>
     </row>
     <row r="47">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="14"/>
-      <c r="K47" s="14"/>
-      <c r="L47" s="14"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="14"/>
-      <c r="O47" s="14"/>
-      <c r="P47" s="17"/>
+      <c r="A47" s="12"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="13"/>
+      <c r="M47" s="15"/>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13"/>
+      <c r="P47" s="16"/>
     </row>
     <row r="48">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="14"/>
-      <c r="O48" s="14"/>
-      <c r="P48" s="17"/>
+      <c r="A48" s="12"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="13"/>
+      <c r="M48" s="15"/>
+      <c r="N48" s="13"/>
+      <c r="O48" s="13"/>
+      <c r="P48" s="16"/>
     </row>
     <row r="49">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="11"/>
-      <c r="J49" s="14"/>
-      <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="14"/>
-      <c r="O49" s="14"/>
-      <c r="P49" s="17"/>
+      <c r="A49" s="12"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="13"/>
+      <c r="K49" s="13"/>
+      <c r="L49" s="13"/>
+      <c r="M49" s="15"/>
+      <c r="N49" s="13"/>
+      <c r="O49" s="13"/>
+      <c r="P49" s="16"/>
     </row>
     <row r="50">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="14"/>
-      <c r="K50" s="14"/>
-      <c r="L50" s="14"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="14"/>
-      <c r="O50" s="14"/>
-      <c r="P50" s="17"/>
+      <c r="A50" s="12"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="15"/>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13"/>
+      <c r="P50" s="16"/>
     </row>
     <row r="51">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="14"/>
-      <c r="K51" s="14"/>
-      <c r="L51" s="14"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="14"/>
-      <c r="P51" s="17"/>
+      <c r="A51" s="12"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="13"/>
+      <c r="M51" s="15"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13"/>
+      <c r="P51" s="16"/>
     </row>
     <row r="52">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="14"/>
-      <c r="O52" s="14"/>
-      <c r="P52" s="17"/>
+      <c r="A52" s="12"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="13"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="13"/>
+      <c r="M52" s="15"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13"/>
+      <c r="P52" s="16"/>
     </row>
     <row r="53">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="11"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="14"/>
-      <c r="O53" s="14"/>
-      <c r="P53" s="17"/>
+      <c r="A53" s="12"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="15"/>
+      <c r="N53" s="13"/>
+      <c r="O53" s="13"/>
+      <c r="P53" s="16"/>
     </row>
     <row r="54">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="11"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="14"/>
-      <c r="L54" s="14"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="14"/>
-      <c r="O54" s="14"/>
-      <c r="P54" s="17"/>
+      <c r="A54" s="12"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="15"/>
+      <c r="N54" s="13"/>
+      <c r="O54" s="13"/>
+      <c r="P54" s="16"/>
     </row>
     <row r="55">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="11"/>
-      <c r="J55" s="14"/>
-      <c r="K55" s="14"/>
-      <c r="L55" s="14"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="14"/>
-      <c r="O55" s="14"/>
-      <c r="P55" s="17"/>
+      <c r="A55" s="12"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="13"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="15"/>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13"/>
+      <c r="P55" s="16"/>
     </row>
     <row r="56">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="11"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="14"/>
-      <c r="L56" s="14"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="14"/>
-      <c r="O56" s="14"/>
-      <c r="P56" s="17"/>
+      <c r="A56" s="12"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="13"/>
+      <c r="K56" s="13"/>
+      <c r="L56" s="13"/>
+      <c r="M56" s="15"/>
+      <c r="N56" s="13"/>
+      <c r="O56" s="13"/>
+      <c r="P56" s="16"/>
     </row>
     <row r="57">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="11"/>
-      <c r="J57" s="14"/>
-      <c r="K57" s="14"/>
-      <c r="L57" s="14"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="14"/>
-      <c r="O57" s="14"/>
-      <c r="P57" s="17"/>
+      <c r="A57" s="12"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="13"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="13"/>
+      <c r="M57" s="15"/>
+      <c r="N57" s="13"/>
+      <c r="O57" s="13"/>
+      <c r="P57" s="16"/>
     </row>
     <row r="58">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="11"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="14"/>
-      <c r="L58" s="14"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="14"/>
-      <c r="O58" s="14"/>
-      <c r="P58" s="17"/>
+      <c r="A58" s="12"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="13"/>
+      <c r="K58" s="13"/>
+      <c r="L58" s="13"/>
+      <c r="M58" s="15"/>
+      <c r="N58" s="13"/>
+      <c r="O58" s="13"/>
+      <c r="P58" s="16"/>
     </row>
     <row r="59">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="11"/>
-      <c r="J59" s="14"/>
-      <c r="K59" s="14"/>
-      <c r="L59" s="14"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="14"/>
-      <c r="O59" s="14"/>
-      <c r="P59" s="17"/>
+      <c r="A59" s="12"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="13"/>
+      <c r="M59" s="15"/>
+      <c r="N59" s="13"/>
+      <c r="O59" s="13"/>
+      <c r="P59" s="16"/>
     </row>
     <row r="60">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="11"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="14"/>
-      <c r="O60" s="14"/>
-      <c r="P60" s="17"/>
+      <c r="A60" s="12"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="13"/>
+      <c r="M60" s="15"/>
+      <c r="N60" s="13"/>
+      <c r="O60" s="13"/>
+      <c r="P60" s="16"/>
     </row>
     <row r="61">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="11"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="14"/>
-      <c r="O61" s="14"/>
-      <c r="P61" s="17"/>
+      <c r="A61" s="12"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+      <c r="L61" s="13"/>
+      <c r="M61" s="15"/>
+      <c r="N61" s="13"/>
+      <c r="O61" s="13"/>
+      <c r="P61" s="16"/>
     </row>
     <row r="62">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="11"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="14"/>
-      <c r="O62" s="14"/>
-      <c r="P62" s="17"/>
+      <c r="A62" s="12"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="13"/>
+      <c r="K62" s="13"/>
+      <c r="L62" s="13"/>
+      <c r="M62" s="15"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13"/>
+      <c r="P62" s="16"/>
     </row>
     <row r="63">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="11"/>
-      <c r="J63" s="14"/>
-      <c r="K63" s="14"/>
-      <c r="L63" s="14"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="14"/>
-      <c r="O63" s="14"/>
-      <c r="P63" s="17"/>
+      <c r="A63" s="12"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="13"/>
+      <c r="K63" s="13"/>
+      <c r="L63" s="13"/>
+      <c r="M63" s="15"/>
+      <c r="N63" s="13"/>
+      <c r="O63" s="13"/>
+      <c r="P63" s="16"/>
     </row>
     <row r="64">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="11"/>
-      <c r="J64" s="14"/>
-      <c r="K64" s="14"/>
-      <c r="L64" s="14"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="14"/>
-      <c r="O64" s="14"/>
-      <c r="P64" s="17"/>
+      <c r="A64" s="12"/>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="17"/>
+      <c r="J64" s="13"/>
+      <c r="K64" s="13"/>
+      <c r="L64" s="13"/>
+      <c r="M64" s="15"/>
+      <c r="N64" s="13"/>
+      <c r="O64" s="13"/>
+      <c r="P64" s="16"/>
     </row>
     <row r="65">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="11"/>
-      <c r="J65" s="14"/>
-      <c r="K65" s="14"/>
-      <c r="L65" s="14"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="14"/>
-      <c r="O65" s="14"/>
-      <c r="P65" s="17"/>
+      <c r="A65" s="12"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="13"/>
+      <c r="K65" s="13"/>
+      <c r="L65" s="13"/>
+      <c r="M65" s="15"/>
+      <c r="N65" s="13"/>
+      <c r="O65" s="13"/>
+      <c r="P65" s="16"/>
     </row>
     <row r="66">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="11"/>
-      <c r="J66" s="14"/>
-      <c r="K66" s="14"/>
-      <c r="L66" s="14"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="14"/>
-      <c r="O66" s="14"/>
-      <c r="P66" s="17"/>
+      <c r="A66" s="12"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13"/>
+      <c r="L66" s="13"/>
+      <c r="M66" s="15"/>
+      <c r="N66" s="13"/>
+      <c r="O66" s="13"/>
+      <c r="P66" s="16"/>
     </row>
     <row r="67">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="11"/>
-      <c r="J67" s="14"/>
-      <c r="K67" s="14"/>
-      <c r="L67" s="14"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="14"/>
-      <c r="O67" s="14"/>
-      <c r="P67" s="17"/>
+      <c r="A67" s="12"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="13"/>
+      <c r="K67" s="13"/>
+      <c r="L67" s="13"/>
+      <c r="M67" s="15"/>
+      <c r="N67" s="13"/>
+      <c r="O67" s="13"/>
+      <c r="P67" s="16"/>
     </row>
     <row r="68">
       <c r="I68" s="18"/>
@@ -5248,16 +5245,16 @@
         <v>5</v>
       </c>
       <c r="F1" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="20" t="s">
         <v>106</v>
-      </c>
-      <c r="G1" s="20" t="s">
-        <v>107</v>
       </c>
       <c r="H1" s="20" t="s">
         <v>10</v>
       </c>
       <c r="I1" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J1" s="20" t="s">
         <v>9</v>
@@ -5266,7 +5263,7 @@
         <v>9</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M1" s="20" t="s">
         <v>8</v>
@@ -5275,7 +5272,7 @@
         <v>8</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P1" s="21" t="s">
         <v>11</v>
@@ -5313,76 +5310,76 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="D2" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="E2" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="F2" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="G2" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="H2" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="I2" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="L2" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="M2" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="N2" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="O2" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="P2" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q2" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="R2" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="I2" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="J2" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="K2" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="L2" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="M2" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="N2" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="O2" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="P2" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q2" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="R2" s="22" t="s">
+      <c r="S2" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="S2" s="22" t="s">
+      <c r="T2" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="T2" s="22" t="s">
+      <c r="U2" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="U2" s="22" t="s">
+      <c r="V2" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="V2" s="22" t="s">
+      <c r="W2" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="W2" s="23" t="s">
-        <v>123</v>
-      </c>
       <c r="X2" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y2" s="23" t="s">
         <v>122</v>
-      </c>
-      <c r="Y2" s="23" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="3">
@@ -5644,7 +5641,7 @@
       </c>
       <c r="N5" s="25" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$128,$A5,FALSE)</f>
-        <v>1.0°</v>
+        <v>1° x 1°</v>
       </c>
       <c r="O5" s="20" t="str">
         <f t="shared" ref="O5:P5" si="15">if(ISBLANK($C5), "", O$1)</f>
@@ -5746,7 +5743,7 @@
       </c>
       <c r="N6" s="25" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$128,$A6,FALSE)</f>
-        <v>1.0°</v>
+        <v>1° x 1°</v>
       </c>
       <c r="O6" s="20" t="str">
         <f t="shared" ref="O6:P6" si="19">if(ISBLANK($C6), "", O$1)</f>
@@ -5848,7 +5845,7 @@
       </c>
       <c r="N7" s="25" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$128,$A7,FALSE)</f>
-        <v>0.25°</v>
+        <v>0.25° x 0.25°</v>
       </c>
       <c r="O7" s="20" t="str">
         <f t="shared" ref="O7:P7" si="23">if(ISBLANK($C7), "", O$1)</f>
@@ -5950,7 +5947,7 @@
       </c>
       <c r="N8" s="25" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$128,$A8,FALSE)</f>
-        <v>1.0°</v>
+        <v>1° x 1°</v>
       </c>
       <c r="O8" s="20" t="str">
         <f t="shared" ref="O8:P8" si="27">if(ISBLANK($C8), "", O$1)</f>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="206">
   <si>
     <t>Timestamp</t>
   </si>
@@ -482,6 +482,9 @@
   </si>
   <si>
     <t xml:space="preserve">Alin et al. (2024a) compiled data from 35 individual cruise data sets that sampled marine waters of the southern Salish Sea and northern Washington coast (United States) from 2008 to 2018. Ongoing seasonal sampling occurred during April, July, and September for Puget Sound cruises has occurred since 2014 and most frequently during May and October for Sound-to-Sea cruises, which sample from Puget Sound through the Strait of Juan de Fuca to the northern Washington coast. The Salish cruise data package contains observations from a total of 715 oceanographic profiles, with &gt; 7490 sensor measurements of temperature, salinity, and DO; ≥ 6070 measurements of discrete DO and nutrient (nitrate, phosphate, silicate, ammonium, nitrite) samples; and ≥ 4462 measurements of inorganic carbonate system variables (DIC and TA). A follow-on data product based on the Salish cruise data package, which only included the 3971 samples with complete information for temperature, salinity, DO, nutrients, DIC, and TA, is also available (Alin et al., 2023). This product additionally provides the most commonly used calculated carbonate system variables: pH (total scale), fCO2, pCO2, Ωarag, and Ωcalc. </t>
+  </si>
+  <si>
+    <t>Time series</t>
   </si>
   <si>
     <t>pCO2 and pH Time-series from 40 Surface Buoys</t>
@@ -1796,25 +1799,25 @@
         <v>45962.74445758102</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>23</v>
@@ -1829,10 +1832,10 @@
         <v>26</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16">
@@ -1843,40 +1846,40 @@
         <v>41</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>48</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K16" s="5" t="s">
         <v>50</v>
       </c>
       <c r="L16" s="18" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17">
@@ -1887,40 +1890,40 @@
         <v>41</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>48</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L17" s="18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18">
@@ -1931,22 +1934,22 @@
         <v>94</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>48</v>
@@ -1958,13 +1961,13 @@
         <v>36</v>
       </c>
       <c r="L18" s="18" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19">
@@ -7837,16 +7840,16 @@
         <v>5</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H1" s="23" t="s">
         <v>10</v>
       </c>
       <c r="I1" s="23" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J1" s="23" t="s">
         <v>9</v>
@@ -7855,7 +7858,7 @@
         <v>9</v>
       </c>
       <c r="L1" s="23" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M1" s="23" t="s">
         <v>8</v>
@@ -7864,7 +7867,7 @@
         <v>8</v>
       </c>
       <c r="O1" s="23" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P1" s="24" t="s">
         <v>11</v>
@@ -7902,76 +7905,76 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G2" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="I2" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="J2" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="I2" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="J2" s="25" t="s">
+      <c r="K2" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="L2" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="M2" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="L2" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="M2" s="25" t="s">
+      <c r="N2" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="O2" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="N2" s="25" t="s">
+      <c r="P2" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="O2" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="P2" s="25" t="s">
-        <v>197</v>
-      </c>
       <c r="Q2" s="25" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="S2" s="25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="T2" s="25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="U2" s="25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="V2" s="25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="W2" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="X2" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="X2" s="25" t="s">
-        <v>203</v>
-      </c>
       <c r="Y2" s="26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3">
@@ -9300,7 +9303,7 @@
       </c>
       <c r="B16" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$137,$A16,FALSE)</f>
-        <v>Data compilations</v>
+        <v>Time series</v>
       </c>
       <c r="C16" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$137,$A16,FALSE)</f>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -1687,7 +1687,7 @@
       <c r="H12" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J12" s="5" t="s">
@@ -1731,6 +1731,7 @@
       <c r="H13" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="I13" s="10"/>
       <c r="J13" s="5" t="s">
         <v>35</v>
       </c>
@@ -1775,6 +1776,7 @@
       <c r="H14" s="7" t="s">
         <v>147</v>
       </c>
+      <c r="I14" s="10"/>
       <c r="J14" s="5" t="s">
         <v>35</v>
       </c>
@@ -1819,6 +1821,7 @@
       <c r="H15" s="7" t="s">
         <v>156</v>
       </c>
+      <c r="I15" s="10"/>
       <c r="J15" s="5" t="s">
         <v>23</v>
       </c>
@@ -1863,7 +1866,7 @@
       <c r="H16" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J16" s="5" t="s">
@@ -1907,7 +1910,7 @@
       <c r="H17" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J17" s="5" t="s">
@@ -1951,7 +1954,7 @@
       <c r="H18" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="6" t="s">
         <v>48</v>
       </c>
       <c r="J18" s="5" t="s">

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -415,7 +415,7 @@
     <t>Jiang, L., Dunne, J., Carter, B. R., Tjiputra, J. F., Terhaar, J., Sharp, J. D., Olsen, A., Alin, S., Bakker, D. C., Feely, R. A., Gattuso, J., Hogan, P., Ilyina, T., Lange, N., Lauvset, S. K., Lewis, E. R., Lovato, T., Palmieri, J., Santana‐Falcón, Y., Schwinger, J., Séférian, R., Strand, G., Swart, N., Tanhua, T., Tsujino, H., Wanninkhof, R., Watanabe, M., Yamamoto, A., and Ziehn, T.: Global surface ocean acidification indicators from 1750 to 2100, Journal of Advances in Modeling Earth Systems, 15(3), https://doi.org/10.1029/2022ms003563, 2023.</t>
   </si>
   <si>
-    <t>https://agupubs.onlinelibrary.wiley.com/cms/asset/a576dee0-a9ed-43f0-a0f4-894b78276a2b/jame21817-fig-0002-m.jpg</t>
+    <t>https://agupubs.onlinelibrary.wiley.com/cms/asset/9184aab2-af20-4a63-9a8f-d0a99a4602bc/jame21817-fig-0008-m.jpg</t>
   </si>
   <si>
     <t>https://doi.org/10.1029/2022MS003563</t>
@@ -9015,7 +9015,7 @@
       </c>
       <c r="E13" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$137,$A13,FALSE)</f>
-        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/a576dee0-a9ed-43f0-a0f4-894b78276a2b/jame21817-fig-0002-m.jpg</v>
+        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/9184aab2-af20-4a63-9a8f-d0a99a4602bc/jame21817-fig-0008-m.jpg</v>
       </c>
       <c r="F13" s="23" t="str">
         <f t="shared" ref="F13:G13" si="44">if(ISBLANK($C13), "", F$1)</f>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -319,7 +319,7 @@
     <t>Gridded subsurface</t>
   </si>
   <si>
-    <t>Aragonite Saturation State Climatology</t>
+    <t>Aragonite Climatology</t>
   </si>
   <si>
     <t xml:space="preserve">Jiang et al. (2015) </t>
@@ -376,7 +376,7 @@
     <t xml:space="preserve">Jiang et al. (2024) developed a coastal OA indicators climatology on a 1°×1° grid, covering North American ocean margins from surface to 500 m at 14 standardized depth levels. This product includes 10 key oceanographic variables: fCO2, pH, [H+]total, free hydrogen ion content ([H+]free), carbonate ion content ([CO32-]), Ωarag, Ωcalc, DIC, TA, and Revelle Factor (RF), as well as temperature and salinity. The climatology was produced with the WOA gridding technologies of the NOAA National Centers for Environmental Information (NCEI), based on the recently released Coastal Ocean Data Analysis Product in North America (CODAP-NA) (Jiang et al., 2021), along with GLODAPv2.2022 (Lauvset et al., 2022). The relevant variables were adjusted to the year of 2010 before the gridding. </t>
   </si>
   <si>
-    <t>Global Surface Ocean pH and Revelle Factor</t>
+    <t>Surface Ocean pH and Revelle Factor</t>
   </si>
   <si>
     <t>Jiang et al. (2019)</t>
@@ -406,7 +406,7 @@
     <t xml:space="preserve">Jiang et al. (2019a) produced a high-resolution (1°×1°) data product delineating regionally varying view of global surface ocean pH, acidity, and Revelle Factor (RF) from 1770 to 2100 by amalgamating recent observational seawater CO2 data from the SOCAT database (Version 6, 1991–2018, ~23 million observations) (Bakker et al., 2016), and temporal trends at individual locations of the global surface ocean from an Earth System Model, i.e., GFDL-ESM2M (Dunne et al., 2013). The calculations were conducted under historical atmospheric CO2 levels (pre-2005) and four Representative Concentrations Pathways (post-2005) corresponding to the Intergovernmental Panel on Climate Change (IPCC)’s 5th Assessment Report, specifically RCP2.6, RCP4.5, RCP6.0, and RCP8.5. </t>
   </si>
   <si>
-    <t xml:space="preserve">Global Surface OA Indicators </t>
+    <t xml:space="preserve">Surface OA Indicators </t>
   </si>
   <si>
     <t>Jiang et al. (2023)</t>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="C10" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$137,$A10,FALSE)</f>
-        <v>Aragonite Saturation State Climatology</v>
+        <v>Aragonite Climatology</v>
       </c>
       <c r="D10" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$137,$A10,FALSE)</f>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C12" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$137,$A12,FALSE)</f>
-        <v>Global Surface Ocean pH and Revelle Factor</v>
+        <v>Surface Ocean pH and Revelle Factor</v>
       </c>
       <c r="D12" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$137,$A12,FALSE)</f>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="C13" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$137,$A13,FALSE)</f>
-        <v>Global Surface OA Indicators </v>
+        <v>Surface OA Indicators </v>
       </c>
       <c r="D13" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$137,$A13,FALSE)</f>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -376,7 +376,7 @@
     <t xml:space="preserve">Jiang et al. (2024) developed a coastal OA indicators climatology on a 1°×1° grid, covering North American ocean margins from surface to 500 m at 14 standardized depth levels. This product includes 10 key oceanographic variables: fCO2, pH, [H+]total, free hydrogen ion content ([H+]free), carbonate ion content ([CO32-]), Ωarag, Ωcalc, DIC, TA, and Revelle Factor (RF), as well as temperature and salinity. The climatology was produced with the WOA gridding technologies of the NOAA National Centers for Environmental Information (NCEI), based on the recently released Coastal Ocean Data Analysis Product in North America (CODAP-NA) (Jiang et al., 2021), along with GLODAPv2.2022 (Lauvset et al., 2022). The relevant variables were adjusted to the year of 2010 before the gridding. </t>
   </si>
   <si>
-    <t>Surface Ocean pH and Revelle Factor</t>
+    <t>Surface pH and Revelle Factor</t>
   </si>
   <si>
     <t>Jiang et al. (2019)</t>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C12" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$137,$A12,FALSE)</f>
-        <v>Surface Ocean pH and Revelle Factor</v>
+        <v>Surface pH and Revelle Factor</v>
       </c>
       <c r="D12" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$137,$A12,FALSE)</f>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -121,6 +121,36 @@
     <t xml:space="preserve">The Surface Ocean CO2 Atlas features surface fCO2 measurements from both the open ocean and the coastal ocean, predominantly sourced from research vessels, ships of opportunity, and autonomous platforms including fixed moorings and uncrewed surface vehicles (USVs) (Bakker et al., 2016). It represents the most extensive collection of observational ocean CO2 data for the global surface ocean. Since 2013, SOCAT has been updated annually. Dataset flags indicate the estimated uncertainty and completeness of metadata in SOCAT synthesis products. The SOCAT gridded product contains fCO2 values with an estimated uncertainty of less than 5 µatm. </t>
   </si>
   <si>
+    <t>LDEO Surface pCO2 Database</t>
+  </si>
+  <si>
+    <t>Takahashi et a. (2009)</t>
+  </si>
+  <si>
+    <t>Takahashi, T., Sutherland, S. C., Wanninkhof, R., Sweeney, C., Feely, R. A., Chipman, D. W., Hales, B., Friederich, G., Chavez, F., Sabine, C., Watson, A., Bakker, D. C. E., Schuster, U., Metzl, N., Yoshikawa-Inoue, H., Ishii, M., Midorikawa, T., Nojiri, Y., Körtzinger, A., Steinhoff, T., and de Baar, H. J. W.: Climatological mean and decadal change in Surface Ocean pCO2, and net sea–air CO2 flux over the Global Oceans, Deep Sea Research Part II: Topical Studies in Oceanography, 56(8–10), 554–577, https://doi.org/10.1016/j.dsr2.2008.12.009, 2009.</t>
+  </si>
+  <si>
+    <t>https://www.ncei.noaa.gov/access/ocean-carbon-acidification-data-system/oceans/LDEO_Underway_Database/LDEOv2019_map.jpg</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.dsr2.2008.12.009</t>
+  </si>
+  <si>
+    <t>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0160492.html</t>
+  </si>
+  <si>
+    <t>Open ocean, Surface</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>The LDEO database reports pCO2 exclusively from equilibrator-CO2 analyzer systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Taro Takahashi [LDEO, Palisades, New York] started synthesizing global surface ocean CO2 data in 1997, compiling three decades of observations (~250,000 measurements) to create  inaugural monthly global surface pCO2 maps (Takahashi et al., 1997; Takahashi et al., 2002). The most recent version (V2019) expanded this dataset to approximately 14.2 million surface water pCO2 measurements spanning from 1957–2019. Distinct from the SOCAT database, the LDEO database reports pCO2, instead of fCO2, exclusively from equilibrator-CO2 analyzer systems, with an average estimated uncertainty of ± 2.5 µatm. The database is also interpolated onto a global surface ocean 4° × 5° grid for a reference year 2000 (Takahashi et al., 2009) and 2010 (Fay et al., 2024). </t>
+  </si>
+  <si>
     <t>GLODAPv2</t>
   </si>
   <si>
@@ -182,9 +212,6 @@
   </si>
   <si>
     <t>monthly</t>
-  </si>
-  <si>
-    <t>Open ocean, Surface</t>
   </si>
   <si>
     <t>1982 - 2020</t>
@@ -451,9 +478,6 @@
     <t>https://www.ncei.noaa.gov/products/world-ocean-database</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Similar to GLODAPv2, with no adjustments</t>
   </si>
   <si>
@@ -596,30 +620,6 @@
   </si>
   <si>
     <t xml:space="preserve">Fassbender et al. (2023) generated estimates of global interior ocean changes to pH, [H+], Ωarag, pCO2, and the Revelle sensitivity factor driven by the accumulation of anthropogenic carbon (Cant) from the preindustrial period to the year 2002, and quantified the component of those changes caused by nonlinearities in the carbonate system. For each OA metric, the dataset includes year 2002 values and quasi-preindustrial values, which were estimated by subtracting Cant from the year 2002 carbonate chemistry information and recomputing each OA metric without considering any warming, circulation, or biological changes that may have occurred since the preindustrial era. </t>
-  </si>
-  <si>
-    <t>LDEO Surface pCO2 Database</t>
-  </si>
-  <si>
-    <t>Takahashi et a. (2009)</t>
-  </si>
-  <si>
-    <t>Takahashi, T., Sutherland, S. C., Wanninkhof, R., Sweeney, C., Feely, R. A., Chipman, D. W., Hales, B., Friederich, G., Chavez, F., Sabine, C., Watson, A., Bakker, D. C. E., Schuster, U., Metzl, N., Yoshikawa-Inoue, H., Ishii, M., Midorikawa, T., Nojiri, Y., Körtzinger, A., Steinhoff, T., and de Baar, H. J. W.: Climatological mean and decadal change in Surface Ocean pCO2, and net sea–air CO2 flux over the Global Oceans, Deep Sea Research Part II: Topical Studies in Oceanography, 56(8–10), 554–577, https://doi.org/10.1016/j.dsr2.2008.12.009, 2009.</t>
-  </si>
-  <si>
-    <t>https://www.ncei.noaa.gov/access/ocean-carbon-acidification-data-system/oceans/LDEO_Underway_Database/LDEOv2019_map.jpg</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.dsr2.2008.12.009</t>
-  </si>
-  <si>
-    <t>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0160492.html</t>
-  </si>
-  <si>
-    <t>The LDEO database reports pCO2 exclusively from equilibrator-CO2 analyzer systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr. Taro Takahashi [LDEO, Palisades, New York] started synthesizing global surface ocean CO2 data in 1997, compiling three decades of observations (~250,000 measurements) to create  inaugural monthly global surface pCO2 maps (Takahashi et al., 1997; Takahashi et al., 2002). The most recent version (V2019) expanded this dataset to approximately 14.2 million surface water pCO2 measurements spanning from 1957–2019. Distinct from the SOCAT database, the LDEO database reports pCO2, instead of fCO2, exclusively from equilibrator-CO2 analyzer systems, with an average estimated uncertainty of ± 2.5 µatm. The database is also interpolated onto a global surface ocean 4° × 5° grid for a reference year 2000 (Takahashi et al., 2009) and 2010 (Fay et al., 2024). </t>
   </si>
   <si>
     <t>fa-solid fa-globe</t>
@@ -771,6 +771,9 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -793,9 +796,6 @@
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -1286,15 +1286,15 @@
     </row>
     <row r="3">
       <c r="A3" s="4">
-        <v>45961.948028391205</v>
+        <v>45962.863408819445</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -1309,103 +1309,103 @@
       <c r="H3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="10"/>
       <c r="J3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="M3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4">
-        <v>45961.95201907407</v>
+        <v>45961.948028391205</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="H4" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="I4" s="11"/>
+      <c r="J4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="K4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="L4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="M4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="N4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="O4" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4">
-        <v>45961.909583877314</v>
+        <v>45961.95201907407</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="G5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="I5" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="J5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="I5" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="K5" s="5" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>60</v>
@@ -1416,14 +1416,13 @@
       <c r="O5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="P5" s="9"/>
     </row>
     <row r="6">
       <c r="A6" s="4">
-        <v>45961.91270586806</v>
+        <v>45961.909583877314</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>63</v>
@@ -1443,196 +1442,197 @@
       <c r="H6" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="N6" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" s="5" t="s">
+      <c r="O6" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="N6" s="5" t="s">
+      <c r="P6" s="9"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4">
+        <v>45961.91270586806</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="P6" s="9"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12">
+      <c r="E7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="P7" s="9"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13">
         <v>45961.90485893519</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="M7" s="16"/>
-      <c r="N7" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="O7" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="P7" s="17"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4">
-        <v>45962.03784055555</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="5" t="s">
+      <c r="I8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="K8" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="L8" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="17"/>
+      <c r="N8" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="N8" s="5" t="s">
+      <c r="O8" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="O8" s="5" t="s">
-        <v>93</v>
-      </c>
+      <c r="P8" s="18"/>
     </row>
     <row r="9">
       <c r="A9" s="4">
-        <v>45962.210738877315</v>
+        <v>45962.03784055555</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="G9" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="I9" s="11"/>
+      <c r="J9" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="L9" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="M9" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="N9" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="K9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L9" s="18" t="s">
+      <c r="O9" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4">
-        <v>45962.673469733796</v>
+        <v>45962.210738877315</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="G10" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="H10" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="I10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="I10" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>101</v>
-      </c>
       <c r="K10" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="L10" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="10" t="s">
         <v>111</v>
       </c>
       <c r="N10" s="5" t="s">
@@ -1644,12 +1644,12 @@
     </row>
     <row r="11">
       <c r="A11" s="4">
-        <v>45962.680467199076</v>
+        <v>45962.673469733796</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>114</v>
       </c>
       <c r="D11" s="6" t="s">
@@ -1668,59 +1668,59 @@
         <v>119</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="J11" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="L11" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="K11" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L11" s="18" t="s">
+      <c r="N11" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="N11" s="5" t="s">
+      <c r="O11" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4">
-        <v>45962.690968483796</v>
+        <v>45962.680467199076</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="G12" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="H12" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="I12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="K12" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L12" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="10" t="s">
         <v>130</v>
       </c>
       <c r="N12" s="5" t="s">
@@ -1732,10 +1732,10 @@
     </row>
     <row r="13">
       <c r="A13" s="4">
-        <v>45962.71938206018</v>
+        <v>45962.690968483796</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>133</v>
@@ -1755,18 +1755,17 @@
       <c r="H13" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="I13" s="10"/>
+      <c r="I13" s="6" t="s">
+        <v>58</v>
+      </c>
       <c r="J13" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="K13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L13" s="18" t="s">
+      <c r="L13" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>38</v>
       </c>
       <c r="N13" s="5" t="s">
         <v>140</v>
@@ -1777,7 +1776,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4">
-        <v>45962.72461462963</v>
+        <v>45962.71938206018</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>16</v>
@@ -1800,18 +1799,18 @@
       <c r="H14" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="I14" s="10"/>
+      <c r="I14" s="11"/>
       <c r="J14" s="5" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="L14" s="18" t="s">
-        <v>139</v>
+        <v>46</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>36</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="N14" s="5" t="s">
         <v>148</v>
@@ -1822,55 +1821,55 @@
     </row>
     <row r="15">
       <c r="A15" s="4">
-        <v>45962.74445758102</v>
+        <v>45962.72461462963</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="G15" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="H15" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="I15" s="11"/>
+      <c r="J15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N15" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="M15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N15" s="5" t="s">
+      <c r="O15" s="5" t="s">
         <v>157</v>
-      </c>
-      <c r="O15" s="5" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4">
-        <v>45962.75772594908</v>
+        <v>45962.74445758102</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>41</v>
+        <v>158</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>159</v>
@@ -1890,149 +1889,150 @@
       <c r="H16" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>48</v>
-      </c>
+      <c r="I16" s="11"/>
       <c r="J16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="K16" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L16" s="18" t="s">
+      <c r="O16" s="5" t="s">
         <v>166</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="O16" s="5" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4">
-        <v>45962.76769828703</v>
+        <v>45962.75772594908</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="F17" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="G17" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="H17" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="I17" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="K17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L17" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="K17" s="5" t="s">
+      <c r="N17" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="L17" s="18" t="s">
+      <c r="O17" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4">
-        <v>45962.780607939814</v>
+        <v>45962.76769828703</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="F18" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="G18" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="H18" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="I18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="K18" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="L18" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L18" s="18" t="s">
+      <c r="N18" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="N18" s="5" t="s">
+      <c r="O18" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4">
-        <v>45962.863408819445</v>
+        <v>45962.780607939814</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="G19" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="H19" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="I19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L19" s="10" t="s">
         <v>193</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L19" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="N19" s="5" t="s">
         <v>194</v>
@@ -2042,1048 +2042,1048 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
       <c r="I20" s="19"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
       <c r="L20" s="20"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="18"/>
     </row>
     <row r="21">
-      <c r="A21" s="12"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
       <c r="I21" s="19"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
       <c r="L21" s="20"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="18"/>
     </row>
     <row r="22">
-      <c r="A22" s="12"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
       <c r="I22" s="19"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
       <c r="L22" s="20"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="13"/>
-      <c r="P22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="18"/>
     </row>
     <row r="23">
-      <c r="A23" s="12"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
       <c r="I23" s="19"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
       <c r="L23" s="20"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
+      <c r="P23" s="18"/>
     </row>
     <row r="24">
-      <c r="A24" s="12"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="14"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="15"/>
       <c r="D24" s="21"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
       <c r="I24" s="19"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
       <c r="L24" s="20"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="18"/>
     </row>
     <row r="25">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="14"/>
+      <c r="A25" s="13"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="15"/>
       <c r="D25" s="21"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
       <c r="I25" s="19"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
       <c r="L25" s="20"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14"/>
+      <c r="P25" s="18"/>
     </row>
     <row r="26">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="14"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="15"/>
       <c r="D26" s="21"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
       <c r="I26" s="19"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
       <c r="L26" s="20"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
+      <c r="P26" s="18"/>
     </row>
     <row r="27">
-      <c r="A27" s="12"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
       <c r="I27" s="19"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
       <c r="L27" s="20"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="17"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="18"/>
     </row>
     <row r="28">
-      <c r="A28" s="12"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
       <c r="L28" s="20"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="18"/>
     </row>
     <row r="29">
-      <c r="A29" s="12"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
       <c r="I29" s="19"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
       <c r="L29" s="20"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="18"/>
     </row>
     <row r="30">
-      <c r="A30" s="12"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
       <c r="I30" s="19"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
       <c r="L30" s="20"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="13"/>
-      <c r="P30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="18"/>
     </row>
     <row r="31">
-      <c r="A31" s="12"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
       <c r="I31" s="19"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
       <c r="L31" s="20"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="13"/>
-      <c r="P31" s="17"/>
+      <c r="M31" s="17"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="18"/>
     </row>
     <row r="32">
-      <c r="A32" s="12"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
+      <c r="A32" s="13"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
       <c r="I32" s="19"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
       <c r="L32" s="20"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="13"/>
-      <c r="P32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="18"/>
     </row>
     <row r="33">
-      <c r="A33" s="12"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
       <c r="I33" s="19"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
       <c r="L33" s="20"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="13"/>
-      <c r="P33" s="17"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="18"/>
     </row>
     <row r="34">
-      <c r="A34" s="12"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
+      <c r="A34" s="13"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
       <c r="I34" s="19"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
       <c r="L34" s="20"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13"/>
-      <c r="P34" s="17"/>
+      <c r="M34" s="17"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="14"/>
+      <c r="P34" s="18"/>
     </row>
     <row r="35">
-      <c r="A35" s="12"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
+      <c r="A35" s="13"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
       <c r="I35" s="19"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
       <c r="L35" s="20"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="13"/>
-      <c r="P35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
+      <c r="P35" s="18"/>
     </row>
     <row r="36">
-      <c r="A36" s="12"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
+      <c r="A36" s="13"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
       <c r="I36" s="19"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
       <c r="L36" s="20"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="17"/>
+      <c r="M36" s="17"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
+      <c r="P36" s="18"/>
     </row>
     <row r="37">
-      <c r="A37" s="12"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
+      <c r="A37" s="13"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
       <c r="I37" s="19"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
       <c r="L37" s="20"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="13"/>
-      <c r="P37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
+      <c r="P37" s="18"/>
     </row>
     <row r="38">
-      <c r="A38" s="12"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
+      <c r="A38" s="13"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
       <c r="I38" s="19"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
       <c r="L38" s="20"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="13"/>
-      <c r="O38" s="13"/>
-      <c r="P38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="14"/>
+      <c r="O38" s="14"/>
+      <c r="P38" s="18"/>
     </row>
     <row r="39">
-      <c r="A39" s="12"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
+      <c r="A39" s="13"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
       <c r="I39" s="19"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="14"/>
       <c r="L39" s="20"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="13"/>
-      <c r="O39" s="13"/>
-      <c r="P39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="14"/>
+      <c r="O39" s="14"/>
+      <c r="P39" s="18"/>
     </row>
     <row r="40">
-      <c r="A40" s="12"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
+      <c r="A40" s="13"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
       <c r="I40" s="19"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="13"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="14"/>
       <c r="L40" s="20"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="13"/>
-      <c r="O40" s="13"/>
-      <c r="P40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="14"/>
+      <c r="O40" s="14"/>
+      <c r="P40" s="18"/>
     </row>
     <row r="41">
-      <c r="A41" s="12"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
+      <c r="A41" s="13"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
       <c r="I41" s="19"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
       <c r="L41" s="20"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="13"/>
-      <c r="O41" s="13"/>
-      <c r="P41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="14"/>
+      <c r="O41" s="14"/>
+      <c r="P41" s="18"/>
     </row>
     <row r="42">
-      <c r="A42" s="12"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
+      <c r="A42" s="13"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
       <c r="I42" s="19"/>
-      <c r="J42" s="13"/>
-      <c r="K42" s="13"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
       <c r="L42" s="20"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="13"/>
-      <c r="O42" s="13"/>
-      <c r="P42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" s="14"/>
+      <c r="O42" s="14"/>
+      <c r="P42" s="18"/>
     </row>
     <row r="43">
-      <c r="A43" s="12"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
+      <c r="A43" s="13"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
       <c r="I43" s="19"/>
-      <c r="J43" s="13"/>
-      <c r="K43" s="13"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="14"/>
       <c r="L43" s="20"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="13"/>
-      <c r="O43" s="13"/>
-      <c r="P43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="14"/>
+      <c r="O43" s="14"/>
+      <c r="P43" s="18"/>
     </row>
     <row r="44">
-      <c r="A44" s="12"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
+      <c r="A44" s="13"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
       <c r="I44" s="19"/>
-      <c r="J44" s="13"/>
-      <c r="K44" s="13"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="14"/>
       <c r="L44" s="20"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="13"/>
-      <c r="O44" s="13"/>
-      <c r="P44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="14"/>
+      <c r="O44" s="14"/>
+      <c r="P44" s="18"/>
     </row>
     <row r="45">
-      <c r="A45" s="12"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
+      <c r="A45" s="13"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
       <c r="I45" s="19"/>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
+      <c r="J45" s="14"/>
+      <c r="K45" s="14"/>
       <c r="L45" s="20"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="13"/>
-      <c r="O45" s="13"/>
-      <c r="P45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="14"/>
+      <c r="O45" s="14"/>
+      <c r="P45" s="18"/>
     </row>
     <row r="46">
-      <c r="A46" s="12"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
+      <c r="A46" s="13"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
       <c r="I46" s="19"/>
-      <c r="J46" s="13"/>
-      <c r="K46" s="13"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="14"/>
       <c r="L46" s="20"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="13"/>
-      <c r="O46" s="13"/>
-      <c r="P46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="14"/>
+      <c r="O46" s="14"/>
+      <c r="P46" s="18"/>
     </row>
     <row r="47">
-      <c r="A47" s="12"/>
-      <c r="B47" s="13"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
+      <c r="A47" s="13"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
       <c r="I47" s="19"/>
-      <c r="J47" s="13"/>
-      <c r="K47" s="13"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
       <c r="L47" s="20"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="13"/>
-      <c r="O47" s="13"/>
-      <c r="P47" s="17"/>
+      <c r="M47" s="17"/>
+      <c r="N47" s="14"/>
+      <c r="O47" s="14"/>
+      <c r="P47" s="18"/>
     </row>
     <row r="48">
-      <c r="A48" s="12"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
+      <c r="A48" s="13"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
       <c r="I48" s="19"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="14"/>
       <c r="L48" s="20"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="13"/>
-      <c r="O48" s="13"/>
-      <c r="P48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="14"/>
+      <c r="O48" s="14"/>
+      <c r="P48" s="18"/>
     </row>
     <row r="49">
-      <c r="A49" s="12"/>
-      <c r="B49" s="13"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
+      <c r="A49" s="13"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
       <c r="I49" s="19"/>
-      <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
       <c r="L49" s="20"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="13"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="17"/>
+      <c r="M49" s="17"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="14"/>
+      <c r="P49" s="18"/>
     </row>
     <row r="50">
-      <c r="A50" s="12"/>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
+      <c r="A50" s="13"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14"/>
       <c r="I50" s="19"/>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="14"/>
       <c r="L50" s="20"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="13"/>
-      <c r="O50" s="13"/>
-      <c r="P50" s="17"/>
+      <c r="M50" s="17"/>
+      <c r="N50" s="14"/>
+      <c r="O50" s="14"/>
+      <c r="P50" s="18"/>
     </row>
     <row r="51">
-      <c r="A51" s="12"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
+      <c r="A51" s="13"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
       <c r="I51" s="19"/>
-      <c r="J51" s="13"/>
-      <c r="K51" s="13"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
       <c r="L51" s="20"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="13"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="17"/>
+      <c r="M51" s="17"/>
+      <c r="N51" s="14"/>
+      <c r="O51" s="14"/>
+      <c r="P51" s="18"/>
     </row>
     <row r="52">
-      <c r="A52" s="12"/>
-      <c r="B52" s="13"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
+      <c r="A52" s="13"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
       <c r="I52" s="19"/>
-      <c r="J52" s="13"/>
-      <c r="K52" s="13"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
       <c r="L52" s="20"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="13"/>
-      <c r="O52" s="13"/>
-      <c r="P52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="14"/>
+      <c r="O52" s="14"/>
+      <c r="P52" s="18"/>
     </row>
     <row r="53">
-      <c r="A53" s="12"/>
-      <c r="B53" s="13"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
+      <c r="A53" s="13"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
       <c r="I53" s="19"/>
-      <c r="J53" s="13"/>
-      <c r="K53" s="13"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="14"/>
       <c r="L53" s="20"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="13"/>
-      <c r="O53" s="13"/>
-      <c r="P53" s="17"/>
+      <c r="M53" s="17"/>
+      <c r="N53" s="14"/>
+      <c r="O53" s="14"/>
+      <c r="P53" s="18"/>
     </row>
     <row r="54">
-      <c r="A54" s="12"/>
-      <c r="B54" s="13"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
+      <c r="A54" s="13"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
       <c r="I54" s="19"/>
-      <c r="J54" s="13"/>
-      <c r="K54" s="13"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="14"/>
       <c r="L54" s="20"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="13"/>
-      <c r="O54" s="13"/>
-      <c r="P54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="14"/>
+      <c r="O54" s="14"/>
+      <c r="P54" s="18"/>
     </row>
     <row r="55">
-      <c r="A55" s="12"/>
-      <c r="B55" s="13"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
+      <c r="A55" s="13"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
       <c r="I55" s="19"/>
-      <c r="J55" s="13"/>
-      <c r="K55" s="13"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
       <c r="L55" s="20"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="13"/>
-      <c r="O55" s="13"/>
-      <c r="P55" s="17"/>
+      <c r="M55" s="17"/>
+      <c r="N55" s="14"/>
+      <c r="O55" s="14"/>
+      <c r="P55" s="18"/>
     </row>
     <row r="56">
-      <c r="A56" s="12"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
+      <c r="A56" s="13"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
       <c r="I56" s="19"/>
-      <c r="J56" s="13"/>
-      <c r="K56" s="13"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
       <c r="L56" s="20"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="13"/>
-      <c r="O56" s="13"/>
-      <c r="P56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="14"/>
+      <c r="O56" s="14"/>
+      <c r="P56" s="18"/>
     </row>
     <row r="57">
-      <c r="A57" s="12"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
+      <c r="A57" s="13"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
       <c r="I57" s="19"/>
-      <c r="J57" s="13"/>
-      <c r="K57" s="13"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="14"/>
       <c r="L57" s="20"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="13"/>
-      <c r="O57" s="13"/>
-      <c r="P57" s="17"/>
+      <c r="M57" s="17"/>
+      <c r="N57" s="14"/>
+      <c r="O57" s="14"/>
+      <c r="P57" s="18"/>
     </row>
     <row r="58">
-      <c r="A58" s="12"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
+      <c r="A58" s="13"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
       <c r="I58" s="19"/>
-      <c r="J58" s="13"/>
-      <c r="K58" s="13"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="14"/>
       <c r="L58" s="20"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="13"/>
-      <c r="O58" s="13"/>
-      <c r="P58" s="17"/>
+      <c r="M58" s="17"/>
+      <c r="N58" s="14"/>
+      <c r="O58" s="14"/>
+      <c r="P58" s="18"/>
     </row>
     <row r="59">
-      <c r="A59" s="12"/>
-      <c r="B59" s="13"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
+      <c r="A59" s="13"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
       <c r="I59" s="19"/>
-      <c r="J59" s="13"/>
-      <c r="K59" s="13"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
       <c r="L59" s="20"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="13"/>
-      <c r="O59" s="13"/>
-      <c r="P59" s="17"/>
+      <c r="M59" s="17"/>
+      <c r="N59" s="14"/>
+      <c r="O59" s="14"/>
+      <c r="P59" s="18"/>
     </row>
     <row r="60">
-      <c r="A60" s="12"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
+      <c r="A60" s="13"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
       <c r="I60" s="19"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
       <c r="L60" s="20"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="13"/>
-      <c r="O60" s="13"/>
-      <c r="P60" s="17"/>
+      <c r="M60" s="17"/>
+      <c r="N60" s="14"/>
+      <c r="O60" s="14"/>
+      <c r="P60" s="18"/>
     </row>
     <row r="61">
-      <c r="A61" s="12"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
+      <c r="A61" s="13"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14"/>
       <c r="I61" s="19"/>
-      <c r="J61" s="13"/>
-      <c r="K61" s="13"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="14"/>
       <c r="L61" s="20"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="13"/>
-      <c r="O61" s="13"/>
-      <c r="P61" s="17"/>
+      <c r="M61" s="17"/>
+      <c r="N61" s="14"/>
+      <c r="O61" s="14"/>
+      <c r="P61" s="18"/>
     </row>
     <row r="62">
-      <c r="A62" s="12"/>
-      <c r="B62" s="13"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
+      <c r="A62" s="13"/>
+      <c r="B62" s="14"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="15"/>
+      <c r="E62" s="14"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14"/>
       <c r="I62" s="19"/>
-      <c r="J62" s="13"/>
-      <c r="K62" s="13"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="14"/>
       <c r="L62" s="20"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="13"/>
-      <c r="O62" s="13"/>
-      <c r="P62" s="17"/>
+      <c r="M62" s="17"/>
+      <c r="N62" s="14"/>
+      <c r="O62" s="14"/>
+      <c r="P62" s="18"/>
     </row>
     <row r="63">
-      <c r="A63" s="12"/>
-      <c r="B63" s="13"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
+      <c r="A63" s="13"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="15"/>
+      <c r="D63" s="15"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14"/>
       <c r="I63" s="19"/>
-      <c r="J63" s="13"/>
-      <c r="K63" s="13"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="14"/>
       <c r="L63" s="20"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="13"/>
-      <c r="O63" s="13"/>
-      <c r="P63" s="17"/>
+      <c r="M63" s="17"/>
+      <c r="N63" s="14"/>
+      <c r="O63" s="14"/>
+      <c r="P63" s="18"/>
     </row>
     <row r="64">
-      <c r="A64" s="12"/>
-      <c r="B64" s="13"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
+      <c r="A64" s="13"/>
+      <c r="B64" s="14"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="15"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14"/>
       <c r="I64" s="19"/>
-      <c r="J64" s="13"/>
-      <c r="K64" s="13"/>
+      <c r="J64" s="14"/>
+      <c r="K64" s="14"/>
       <c r="L64" s="20"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="13"/>
-      <c r="O64" s="13"/>
-      <c r="P64" s="17"/>
+      <c r="M64" s="17"/>
+      <c r="N64" s="14"/>
+      <c r="O64" s="14"/>
+      <c r="P64" s="18"/>
     </row>
     <row r="65">
-      <c r="A65" s="12"/>
-      <c r="B65" s="13"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
+      <c r="A65" s="13"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="14"/>
       <c r="I65" s="19"/>
-      <c r="J65" s="13"/>
-      <c r="K65" s="13"/>
+      <c r="J65" s="14"/>
+      <c r="K65" s="14"/>
       <c r="L65" s="20"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="13"/>
-      <c r="O65" s="13"/>
-      <c r="P65" s="17"/>
+      <c r="M65" s="17"/>
+      <c r="N65" s="14"/>
+      <c r="O65" s="14"/>
+      <c r="P65" s="18"/>
     </row>
     <row r="66">
-      <c r="A66" s="12"/>
-      <c r="B66" s="13"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
+      <c r="A66" s="13"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14"/>
       <c r="I66" s="19"/>
-      <c r="J66" s="13"/>
-      <c r="K66" s="13"/>
+      <c r="J66" s="14"/>
+      <c r="K66" s="14"/>
       <c r="L66" s="20"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="13"/>
-      <c r="O66" s="13"/>
-      <c r="P66" s="17"/>
+      <c r="M66" s="17"/>
+      <c r="N66" s="14"/>
+      <c r="O66" s="14"/>
+      <c r="P66" s="18"/>
     </row>
     <row r="67">
-      <c r="A67" s="12"/>
-      <c r="B67" s="13"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
+      <c r="A67" s="13"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="14"/>
       <c r="I67" s="19"/>
-      <c r="J67" s="13"/>
-      <c r="K67" s="13"/>
+      <c r="J67" s="14"/>
+      <c r="K67" s="14"/>
       <c r="L67" s="20"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="13"/>
-      <c r="O67" s="13"/>
-      <c r="P67" s="17"/>
+      <c r="M67" s="17"/>
+      <c r="N67" s="14"/>
+      <c r="O67" s="14"/>
+      <c r="P67" s="18"/>
     </row>
     <row r="68">
-      <c r="A68" s="12"/>
-      <c r="B68" s="13"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
+      <c r="A68" s="13"/>
+      <c r="B68" s="14"/>
+      <c r="C68" s="15"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
       <c r="I68" s="19"/>
-      <c r="J68" s="13"/>
-      <c r="K68" s="13"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="14"/>
       <c r="L68" s="20"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="13"/>
-      <c r="O68" s="13"/>
-      <c r="P68" s="17"/>
+      <c r="M68" s="17"/>
+      <c r="N68" s="14"/>
+      <c r="O68" s="14"/>
+      <c r="P68" s="18"/>
     </row>
     <row r="69">
-      <c r="A69" s="12"/>
-      <c r="B69" s="13"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
+      <c r="A69" s="13"/>
+      <c r="B69" s="14"/>
+      <c r="C69" s="15"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14"/>
       <c r="I69" s="19"/>
-      <c r="J69" s="13"/>
-      <c r="K69" s="13"/>
+      <c r="J69" s="14"/>
+      <c r="K69" s="14"/>
       <c r="L69" s="20"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="13"/>
-      <c r="O69" s="13"/>
-      <c r="P69" s="17"/>
+      <c r="M69" s="17"/>
+      <c r="N69" s="14"/>
+      <c r="O69" s="14"/>
+      <c r="P69" s="18"/>
     </row>
     <row r="70">
-      <c r="A70" s="12"/>
-      <c r="B70" s="13"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
+      <c r="A70" s="13"/>
+      <c r="B70" s="14"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="14"/>
       <c r="I70" s="19"/>
-      <c r="J70" s="13"/>
-      <c r="K70" s="13"/>
+      <c r="J70" s="14"/>
+      <c r="K70" s="14"/>
       <c r="L70" s="20"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="13"/>
-      <c r="O70" s="13"/>
-      <c r="P70" s="17"/>
+      <c r="M70" s="17"/>
+      <c r="N70" s="14"/>
+      <c r="O70" s="14"/>
+      <c r="P70" s="18"/>
     </row>
     <row r="71">
-      <c r="A71" s="12"/>
-      <c r="B71" s="13"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
+      <c r="A71" s="13"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
       <c r="I71" s="19"/>
-      <c r="J71" s="13"/>
-      <c r="K71" s="13"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="14"/>
       <c r="L71" s="20"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="13"/>
-      <c r="O71" s="13"/>
-      <c r="P71" s="17"/>
+      <c r="M71" s="17"/>
+      <c r="N71" s="14"/>
+      <c r="O71" s="14"/>
+      <c r="P71" s="18"/>
     </row>
     <row r="72">
-      <c r="A72" s="12"/>
-      <c r="B72" s="13"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
+      <c r="A72" s="13"/>
+      <c r="B72" s="14"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
       <c r="I72" s="19"/>
-      <c r="J72" s="13"/>
-      <c r="K72" s="13"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="14"/>
       <c r="L72" s="20"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="13"/>
-      <c r="O72" s="13"/>
-      <c r="P72" s="17"/>
+      <c r="M72" s="17"/>
+      <c r="N72" s="14"/>
+      <c r="O72" s="14"/>
+      <c r="P72" s="18"/>
     </row>
     <row r="73">
-      <c r="A73" s="12"/>
-      <c r="B73" s="13"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
+      <c r="A73" s="13"/>
+      <c r="B73" s="14"/>
+      <c r="C73" s="15"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
       <c r="I73" s="19"/>
-      <c r="J73" s="13"/>
-      <c r="K73" s="13"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="14"/>
       <c r="L73" s="20"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="13"/>
-      <c r="O73" s="13"/>
-      <c r="P73" s="17"/>
+      <c r="M73" s="17"/>
+      <c r="N73" s="14"/>
+      <c r="O73" s="14"/>
+      <c r="P73" s="18"/>
     </row>
     <row r="74">
-      <c r="A74" s="12"/>
-      <c r="B74" s="13"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
+      <c r="A74" s="13"/>
+      <c r="B74" s="14"/>
+      <c r="C74" s="15"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14"/>
       <c r="I74" s="19"/>
-      <c r="J74" s="13"/>
-      <c r="K74" s="13"/>
+      <c r="J74" s="14"/>
+      <c r="K74" s="14"/>
       <c r="L74" s="20"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="13"/>
-      <c r="O74" s="13"/>
-      <c r="P74" s="17"/>
+      <c r="M74" s="17"/>
+      <c r="N74" s="14"/>
+      <c r="O74" s="14"/>
+      <c r="P74" s="18"/>
     </row>
     <row r="75">
-      <c r="A75" s="12"/>
-      <c r="B75" s="13"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
+      <c r="A75" s="13"/>
+      <c r="B75" s="14"/>
+      <c r="C75" s="15"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="14"/>
       <c r="I75" s="19"/>
-      <c r="J75" s="13"/>
-      <c r="K75" s="13"/>
+      <c r="J75" s="14"/>
+      <c r="K75" s="14"/>
       <c r="L75" s="20"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="13"/>
-      <c r="O75" s="13"/>
-      <c r="P75" s="17"/>
+      <c r="M75" s="17"/>
+      <c r="N75" s="14"/>
+      <c r="O75" s="14"/>
+      <c r="P75" s="18"/>
     </row>
     <row r="76">
-      <c r="A76" s="12"/>
-      <c r="B76" s="13"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
+      <c r="A76" s="13"/>
+      <c r="B76" s="14"/>
+      <c r="C76" s="15"/>
+      <c r="D76" s="15"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="14"/>
+      <c r="H76" s="14"/>
       <c r="I76" s="19"/>
-      <c r="J76" s="13"/>
-      <c r="K76" s="13"/>
+      <c r="J76" s="14"/>
+      <c r="K76" s="14"/>
       <c r="L76" s="20"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="13"/>
-      <c r="O76" s="13"/>
-      <c r="P76" s="17"/>
+      <c r="M76" s="17"/>
+      <c r="N76" s="14"/>
+      <c r="O76" s="14"/>
+      <c r="P76" s="18"/>
     </row>
     <row r="77">
-      <c r="A77" s="12"/>
-      <c r="B77" s="13"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
+      <c r="A77" s="13"/>
+      <c r="B77" s="14"/>
+      <c r="C77" s="15"/>
+      <c r="D77" s="15"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="14"/>
+      <c r="H77" s="14"/>
       <c r="I77" s="19"/>
-      <c r="J77" s="13"/>
-      <c r="K77" s="13"/>
+      <c r="J77" s="14"/>
+      <c r="K77" s="14"/>
       <c r="L77" s="20"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="13"/>
-      <c r="O77" s="13"/>
-      <c r="P77" s="17"/>
+      <c r="M77" s="17"/>
+      <c r="N77" s="14"/>
+      <c r="O77" s="14"/>
+      <c r="P77" s="18"/>
     </row>
     <row r="78">
       <c r="C78" s="3"/>
@@ -8164,15 +8164,15 @@
       </c>
       <c r="C4" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A4,FALSE)</f>
-        <v>GLODAPv2</v>
+        <v>LDEO Surface pCO2 Database</v>
       </c>
       <c r="D4" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A4,FALSE)</f>
-        <v>Lauvset et al. (2024)</v>
+        <v>Takahashi et a. (2009)</v>
       </c>
       <c r="E4" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A4,FALSE)</f>
-        <v>https://glodap.info/wp-content/uploads/2017/09/cropped-glodap_logo_trans.png</v>
+        <v>https://www.ncei.noaa.gov/access/ocean-carbon-acidification-data-system/oceans/LDEO_Underway_Database/LDEOv2019_map.jpg</v>
       </c>
       <c r="F4" s="23" t="str">
         <f t="shared" ref="F4:G4" si="6">if(ISBLANK($C4), "", F$1)</f>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="H4" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A4,FALSE)</f>
-        <v>Open ocean, Water column</v>
+        <v>Open ocean, Surface</v>
       </c>
       <c r="I4" s="23" t="str">
         <f t="shared" ref="I4:J4" si="7">if(ISBLANK($C4), "", I$1)</f>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="K4" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A4,FALSE)</f>
-        <v>discrete</v>
+        <v>continuous</v>
       </c>
       <c r="L4" s="23" t="str">
         <f t="shared" ref="L4:M4" si="8">if(ISBLANK($C4), "", L$1)</f>
@@ -8220,23 +8220,23 @@
       </c>
       <c r="Q4" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A4,FALSE)</f>
-        <v>1960 - 2024</v>
+        <v/>
       </c>
       <c r="R4" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A4,FALSE)</f>
-        <v>Adjustments are applied by comparing data in the deep ocean (&gt;2000 m) using a crossover and inversion method as described by Johnson et al. (2001).</v>
+        <v>The LDEO database reports pCO2 exclusively from equilibrator-CO2 analyzer systems</v>
       </c>
       <c r="S4" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A4,FALSE)</f>
-        <v>Lauvset et al. (2024)</v>
+        <v>Takahashi et a. (2009)</v>
       </c>
       <c r="T4" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A4,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-16-2047-2024</v>
+        <v>https://doi.org/10.1016/j.dsr2.2008.12.009</v>
       </c>
       <c r="U4" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A4,FALSE)</f>
-        <v>https://glodap.info/</v>
+        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0160492.html</v>
       </c>
       <c r="V4" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="W4" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A4,FALSE)</f>
-        <v>The Global Ocean Data Analysis Project Version 2 (GLODAPv2) aggregates biogeochemical data collected from discrete bottle samples, offering extensive global coverage from the surface to depths (Key et al., 2015; Olsen et al., 2016; Lauvset et al., 2024). While GLODAP is primarily a product for basin-scale hydrographic data, it also includes coastal datasets and observations from a few time-series. The GLODAPv2 data product provides rigorously quality-controlled measurements for 14 essential oceanographic variables: temperature, salinity, dissolved oxygen (DO), nitrate, silicate, phosphate, DIC, TA, pH, chlorofluorocarbons (CFC-11, CFC-12, CFC-113), carbon tetrachloride (CCl4), and sulfur hexafluoride (SF6). These variables, excluding temperature, undergo both primary and secondary quality control procedures to detect outliers and adjust for significant measurement biases. GLODAPv2 was first published in 2016 and was updated annually through a living data process in Earth System Science Data from 2019 through “v2023,” which was published in 2024. For these updates, new data (including historical data not previously included in the data product) are quality controlled and adjusted to the 2016 version (Olsen et al., 2019; Olsen et al., 2020; Lauvset et al., 2021; Lauvset et al., 2022; Lauvset et al., 2024). Since the global repeat hydrography programs operate with decadal repetitions, the aim is to produce a completely new version of GLODAP, where all cruise datasets will be reevaluated, every decade. Release of the GLODAPv3 data product is planned for 2026, and is expected to evolve the secondary data quality control practices relative to those used in GLODAPv2. For more information on the secondary quality control process, refer to Tanhua et al. (2010) and Lauvset and Tanhua (2015). GLODAPv2 offers two kind of products: the collection of quality controlled data from discrete bottle samples taken at sampling location (Key et al., 2015; Olsen et al., 2016; Olsen et al., 2019; Olsen et al., 2020; Lauvset et al., 2021; Lauvset et al., 2022; Lauvset et al., 2024), and a gridded product, interpolated to a 1° × 1°  grid and the 33 standard depth levels of World Ocean Atlas (WOA) (Lauvset et al., 2016). </v>
+        <v>Dr. Taro Takahashi [LDEO, Palisades, New York] started synthesizing global surface ocean CO2 data in 1997, compiling three decades of observations (~250,000 measurements) to create  inaugural monthly global surface pCO2 maps (Takahashi et al., 1997; Takahashi et al., 2002). The most recent version (V2019) expanded this dataset to approximately 14.2 million surface water pCO2 measurements spanning from 1957–2019. Distinct from the SOCAT database, the LDEO database reports pCO2, instead of fCO2, exclusively from equilibrator-CO2 analyzer systems, with an average estimated uncertainty of ± 2.5 µatm. The database is also interpolated onto a global surface ocean 4° × 5° grid for a reference year 2000 (Takahashi et al., 2009) and 2010 (Fay et al., 2024). </v>
       </c>
       <c r="X4" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8252,7 +8252,7 @@
       </c>
       <c r="Y4" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A4,FALSE)</f>
-        <v>Lauvset, S. K., Lange, N., Tanhua, T., Bittig, H. C., Olsen, A., Kozyr, A., Álvarez, M., Azetsu-Scott, K., Brown, P. J., Carter, B. R., Cotrim da Cunha, L., Hoppema, M., Humphreys, M. P., Ishii, M., Jeansson, E., Murata, A., Müller, J. D., Pérez, F. F., Schirnick, C., Steinfeldt, R., Suzuki, T., Ulfsbo, A., Velo, A., Woosley, R. J., and Key, R. M.: The annual update GLODAPv2.2023: the global interior ocean biogeochemical data product, Earth Syst. Sci. Data, 16, 2047–2072, https://doi.org/10.5194/essd-16-2047-2024, 2024</v>
+        <v>Takahashi, T., Sutherland, S. C., Wanninkhof, R., Sweeney, C., Feely, R. A., Chipman, D. W., Hales, B., Friederich, G., Chavez, F., Sabine, C., Watson, A., Bakker, D. C. E., Schuster, U., Metzl, N., Yoshikawa-Inoue, H., Ishii, M., Midorikawa, T., Nojiri, Y., Körtzinger, A., Steinhoff, T., and de Baar, H. J. W.: Climatological mean and decadal change in Surface Ocean pCO2, and net sea–air CO2 flux over the Global Oceans, Deep Sea Research Part II: Topical Studies in Oceanography, 56(8–10), 554–577, https://doi.org/10.1016/j.dsr2.2008.12.009, 2009.</v>
       </c>
     </row>
     <row r="5">
@@ -8262,19 +8262,19 @@
       </c>
       <c r="B5" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A5,FALSE)</f>
-        <v>Gridded surface</v>
+        <v>Data compilations</v>
       </c>
       <c r="C5" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A5,FALSE)</f>
-        <v>CSIR-ML6</v>
+        <v>GLODAPv2</v>
       </c>
       <c r="D5" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A5,FALSE)</f>
-        <v>Gregor et al. (2019)</v>
+        <v>Lauvset et al. (2024)</v>
       </c>
       <c r="E5" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A5,FALSE)</f>
-        <v>https://gmd.copernicus.org/articles/12/5113/2019/gmd-12-5113-2019-f09-thumb.png</v>
+        <v>https://glodap.info/wp-content/uploads/2017/09/cropped-glodap_logo_trans.png</v>
       </c>
       <c r="F5" s="23" t="str">
         <f t="shared" ref="F5:G5" si="12">if(ISBLANK($C5), "", F$1)</f>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="H5" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A5,FALSE)</f>
-        <v>Open ocean, Surface</v>
+        <v>Open ocean, Water column</v>
       </c>
       <c r="I5" s="23" t="str">
         <f t="shared" ref="I5:J5" si="13">if(ISBLANK($C5), "", I$1)</f>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="K5" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A5,FALSE)</f>
-        <v>monthly</v>
+        <v>discrete</v>
       </c>
       <c r="L5" s="23" t="str">
         <f t="shared" ref="L5:M5" si="14">if(ISBLANK($C5), "", L$1)</f>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="N5" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A5,FALSE)</f>
-        <v>1° x 1°</v>
+        <v/>
       </c>
       <c r="O5" s="23" t="str">
         <f t="shared" ref="O5:P5" si="15">if(ISBLANK($C5), "", O$1)</f>
@@ -8322,23 +8322,23 @@
       </c>
       <c r="Q5" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A5,FALSE)</f>
-        <v>1982 - 2020</v>
+        <v>1960 - 2024</v>
       </c>
       <c r="R5" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A5,FALSE)</f>
-        <v>Various ML methods produce different results when data is sparse, but all still achieving roughly the same uncertainty</v>
+        <v>Adjustments are applied by comparing data in the deep ocean (&gt;2000 m) using a crossover and inversion method as described by Johnson et al. (2001).</v>
       </c>
       <c r="S5" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A5,FALSE)</f>
-        <v>Gregor et al. (2019)</v>
+        <v>Lauvset et al. (2024)</v>
       </c>
       <c r="T5" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A5,FALSE)</f>
-        <v>https://doi.org/10.5194/gmd-12-5113-2019</v>
+        <v>https://doi.org/10.5194/essd-16-2047-2024</v>
       </c>
       <c r="U5" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A5,FALSE)</f>
-        <v>https://doi.org/10.25921/z682-mn47</v>
+        <v>https://glodap.info/</v>
       </c>
       <c r="V5" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="W5" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A5,FALSE)</f>
-        <v>Provides monthly 1° × 1° estimates of surface pCO2 (Gregor et al., 2019a). The approach uses the conceptual two-step approach of clustering and performing regressions for each cluster as Landschützer et al. (2016). CSIR-ML6 investigates the efficacy of various machine learning (ML) methods in estimating surface pCO2, namely, feed-forward neural networks (FFNN), extremely randomized trees (ERT), gradient boosting machines (GBM), and support vector regression (SVR). It is found that the ensemble of all but the ERT method resulted in the best estimate, highlighting the fact that various ML methods do not produce the same outcome, particularly when data is sparse. Further, the variance between ensemble members can inform us about regions where uncertainty may be large due to methodological differences. Despite this, all methods achieve roughly the same uncertainty – a barrier, or wall beyond which the community has yet to overcome.</v>
+        <v>The Global Ocean Data Analysis Project Version 2 (GLODAPv2) aggregates biogeochemical data collected from discrete bottle samples, offering extensive global coverage from the surface to depths (Key et al., 2015; Olsen et al., 2016; Lauvset et al., 2024). While GLODAP is primarily a product for basin-scale hydrographic data, it also includes coastal datasets and observations from a few time-series. The GLODAPv2 data product provides rigorously quality-controlled measurements for 14 essential oceanographic variables: temperature, salinity, dissolved oxygen (DO), nitrate, silicate, phosphate, DIC, TA, pH, chlorofluorocarbons (CFC-11, CFC-12, CFC-113), carbon tetrachloride (CCl4), and sulfur hexafluoride (SF6). These variables, excluding temperature, undergo both primary and secondary quality control procedures to detect outliers and adjust for significant measurement biases. GLODAPv2 was first published in 2016 and was updated annually through a living data process in Earth System Science Data from 2019 through “v2023,” which was published in 2024. For these updates, new data (including historical data not previously included in the data product) are quality controlled and adjusted to the 2016 version (Olsen et al., 2019; Olsen et al., 2020; Lauvset et al., 2021; Lauvset et al., 2022; Lauvset et al., 2024). Since the global repeat hydrography programs operate with decadal repetitions, the aim is to produce a completely new version of GLODAP, where all cruise datasets will be reevaluated, every decade. Release of the GLODAPv3 data product is planned for 2026, and is expected to evolve the secondary data quality control practices relative to those used in GLODAPv2. For more information on the secondary quality control process, refer to Tanhua et al. (2010) and Lauvset and Tanhua (2015). GLODAPv2 offers two kind of products: the collection of quality controlled data from discrete bottle samples taken at sampling location (Key et al., 2015; Olsen et al., 2016; Olsen et al., 2019; Olsen et al., 2020; Lauvset et al., 2021; Lauvset et al., 2022; Lauvset et al., 2024), and a gridded product, interpolated to a 1° × 1°  grid and the 33 standard depth levels of World Ocean Atlas (WOA) (Lauvset et al., 2016). </v>
       </c>
       <c r="X5" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="Y5" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A5,FALSE)</f>
-        <v>Gregor, L., Lebehot, A. D., Kok, S., and Scheel Monteiro, P. M.: A comparative assessment of the uncertainties of global surface ocean CO2 estimates using a machine-learning ensemble (CSIR-ML6 version 2019a) – have we hit the wall?, Geosci. Model Dev., 12, 5113–5136, https://doi.org/10.5194/gmd-12-5113-2019, 2019.</v>
+        <v>Lauvset, S. K., Lange, N., Tanhua, T., Bittig, H. C., Olsen, A., Kozyr, A., Álvarez, M., Azetsu-Scott, K., Brown, P. J., Carter, B. R., Cotrim da Cunha, L., Hoppema, M., Humphreys, M. P., Ishii, M., Jeansson, E., Murata, A., Müller, J. D., Pérez, F. F., Schirnick, C., Steinfeldt, R., Suzuki, T., Ulfsbo, A., Velo, A., Woosley, R. J., and Key, R. M.: The annual update GLODAPv2.2023: the global interior ocean biogeochemical data product, Earth Syst. Sci. Data, 16, 2047–2072, https://doi.org/10.5194/essd-16-2047-2024, 2024</v>
       </c>
     </row>
     <row r="6">
@@ -8368,15 +8368,15 @@
       </c>
       <c r="C6" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>OceanSODA-ETHZv1</v>
+        <v>CSIR-ML6</v>
       </c>
       <c r="D6" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>Gregor and Gruber (2021)</v>
+        <v>Gregor et al. (2019)</v>
       </c>
       <c r="E6" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>https://essd.copernicus.org/articles/13/777/2021/essd-13-777-2021-avatar-web.png</v>
+        <v>https://gmd.copernicus.org/articles/12/5113/2019/gmd-12-5113-2019-f09-thumb.png</v>
       </c>
       <c r="F6" s="23" t="str">
         <f t="shared" ref="F6:G6" si="16">if(ISBLANK($C6), "", F$1)</f>
@@ -8424,23 +8424,23 @@
       </c>
       <c r="Q6" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>1982 - 2022</v>
+        <v>1982 - 2020</v>
       </c>
       <c r="R6" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>Temporal trends of DIC, TA, pCO2, pH, Ωarag, and Ωcalc</v>
+        <v>Various ML methods produce different results when data is sparse, but all still achieving roughly the same uncertainty</v>
       </c>
       <c r="S6" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>Gregor and Gruber (2021)</v>
+        <v>Gregor et al. (2019)</v>
       </c>
       <c r="T6" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-13-777-2021</v>
+        <v>https://doi.org/10.5194/gmd-12-5113-2019</v>
       </c>
       <c r="U6" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>https://doi.org/10.25921/m5wx-ja34</v>
+        <v>https://doi.org/10.25921/z682-mn47</v>
       </c>
       <c r="V6" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="W6" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>A monthly gridded global surface ocean data product for multiple ocean carbonate system variables, including DIC, TA, pCO2, pH (total scale), Ωarag, and Ωcalc (Gregor and Gruber, 2020; Gregor and Gruber, 2021; Gregor and Gruber, 2023; Ma et al., 2023). This dataset is structured on a 1°×1° global surface ocean grid with monthly resolution from 1982–2022, facilitating research on OA over seasonal to decadal scales. The OceanSODA-ETHZ data product was created by extrapolating in time and space the surface ocean observations of fCO2 from SOCATv2022 (Bakker et al., 2016) and TA from GLODAPv2.2022 using the newly developed Geospatial Random Cluster Ensemble Regression (GRaCER) method (Gregor, 2021). TA and pCO2 were then used to calculate the remaining variables of the marine carbonate system with the PyCO2SYS software (Humphreys et al., 2022). Phosphate and silicate from WOA 2018 product were used (Boyer et al., 2018; Garcia et al., 2018a).</v>
+        <v>Provides monthly 1° × 1° estimates of surface pCO2 (Gregor et al., 2019a). The approach uses the conceptual two-step approach of clustering and performing regressions for each cluster as Landschützer et al. (2016). CSIR-ML6 investigates the efficacy of various machine learning (ML) methods in estimating surface pCO2, namely, feed-forward neural networks (FFNN), extremely randomized trees (ERT), gradient boosting machines (GBM), and support vector regression (SVR). It is found that the ensemble of all but the ERT method resulted in the best estimate, highlighting the fact that various ML methods do not produce the same outcome, particularly when data is sparse. Further, the variance between ensemble members can inform us about regions where uncertainty may be large due to methodological differences. Despite this, all methods achieve roughly the same uncertainty – a barrier, or wall beyond which the community has yet to overcome.</v>
       </c>
       <c r="X6" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="Y6" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>Gregor, L.; Gruber, N. OceanSODA-ETHZ: A Global Gridded Data Set of the Surface Ocean Carbonate System for Seasonal to Decadal Studies of Ocean Acidification. Earth System Science Data 2021, 13 (2), 777–808. https://doi.org/10.5194/essd-13-777-2021.</v>
+        <v>Gregor, L., Lebehot, A. D., Kok, S., and Scheel Monteiro, P. M.: A comparative assessment of the uncertainties of global surface ocean CO2 estimates using a machine-learning ensemble (CSIR-ML6 version 2019a) – have we hit the wall?, Geosci. Model Dev., 12, 5113–5136, https://doi.org/10.5194/gmd-12-5113-2019, 2019.</v>
       </c>
     </row>
     <row r="7">
@@ -8470,15 +8470,15 @@
       </c>
       <c r="C7" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>OceanSODA-ETHZv2</v>
+        <v>OceanSODA-ETHZv1</v>
       </c>
       <c r="D7" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>Gregor et al. (2024)</v>
+        <v>Gregor and Gruber (2021)</v>
       </c>
       <c r="E7" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/7decc330-7468-429c-bae9-ac51b085be30/gbc21584-fig-0007-m.jpg</v>
+        <v>https://essd.copernicus.org/articles/13/777/2021/essd-13-777-2021-avatar-web.png</v>
       </c>
       <c r="F7" s="23" t="str">
         <f t="shared" ref="F7:G7" si="20">if(ISBLANK($C7), "", F$1)</f>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="K7" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>8-day</v>
+        <v>monthly</v>
       </c>
       <c r="L7" s="23" t="str">
         <f t="shared" ref="L7:M7" si="22">if(ISBLANK($C7), "", L$1)</f>
@@ -8514,7 +8514,7 @@
       </c>
       <c r="N7" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>0.25° x 0.25°</v>
+        <v>1° x 1°</v>
       </c>
       <c r="O7" s="23" t="str">
         <f t="shared" ref="O7:P7" si="23">if(ISBLANK($C7), "", O$1)</f>
@@ -8526,23 +8526,23 @@
       </c>
       <c r="Q7" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>1982 - 2023</v>
+        <v>1982 - 2022</v>
       </c>
       <c r="R7" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>Highlighting fine-scale and short-term variability of the ocean carbon sink</v>
+        <v>Temporal trends of DIC, TA, pCO2, pH, Ωarag, and Ωcalc</v>
       </c>
       <c r="S7" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>Gregor et al. (2024)</v>
+        <v>Gregor and Gruber (2021)</v>
       </c>
       <c r="T7" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>https://doi.org/10.1029/2024GB008127</v>
+        <v>https://doi.org/10.5194/essd-13-777-2021</v>
       </c>
       <c r="U7" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>https://zenodo.org/records/11206366</v>
+        <v>https://doi.org/10.25921/m5wx-ja34</v>
       </c>
       <c r="V7" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="W7" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>A surface fCO₂ product with a 0.25° × 0.25° spatial resolution and an 8-day temporal resolution, providing estimates starting from 1982 (Gregor et al., 2024a; Gregor et al., 2024b). The high-resolution outputs are suitable for investigating the shorter- and finer-scale dynamics of surface fCO2. Despite sharing a name with its predecessor, OceanSODA-ETHZv2 does not provide TA estimates and employs a different methodology, as described in the following steps: 1) The atmospheric trend of CO2 is removed by subtracting marine boundary layer CO2 concentrations from SOCAT fCO2 producing a new target ∆*CO2 to reduce the biases at the start and end of the time-series. 2) An 8-day seasonal climatology of ∆*CO2 is estimated using Gradient Boosted Decision Trees (GBDT), which is later used as a predictor. 3) The non-seasonal thermal component is removed from ∆*CO2, resulting in a new target, ∆*CO2nonT. 4) The new target is estimated using a feed-forward neural network, with the GBDT as one of the forcing variables. 5) Steps 4 through to 1 are inverted to arrive at fCO2. 6) Air-sea CO2 fluxes are computed using ERA5 winds.</v>
+        <v>A monthly gridded global surface ocean data product for multiple ocean carbonate system variables, including DIC, TA, pCO2, pH (total scale), Ωarag, and Ωcalc (Gregor and Gruber, 2020; Gregor and Gruber, 2021; Gregor and Gruber, 2023; Ma et al., 2023). This dataset is structured on a 1°×1° global surface ocean grid with monthly resolution from 1982–2022, facilitating research on OA over seasonal to decadal scales. The OceanSODA-ETHZ data product was created by extrapolating in time and space the surface ocean observations of fCO2 from SOCATv2022 (Bakker et al., 2016) and TA from GLODAPv2.2022 using the newly developed Geospatial Random Cluster Ensemble Regression (GRaCER) method (Gregor, 2021). TA and pCO2 were then used to calculate the remaining variables of the marine carbonate system with the PyCO2SYS software (Humphreys et al., 2022). Phosphate and silicate from WOA 2018 product were used (Boyer et al., 2018; Garcia et al., 2018a).</v>
       </c>
       <c r="X7" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="Y7" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>Gregor, L.; Shutler, J.; Gruber, N. High-Resolution Variability of the Ocean Carbon Sink. Global Biogeochemical Cycles 2024, 38 (8), e2024GB008127. https://doi.org/10.1029/2024GB008127.</v>
+        <v>Gregor, L.; Gruber, N. OceanSODA-ETHZ: A Global Gridded Data Set of the Surface Ocean Carbonate System for Seasonal to Decadal Studies of Ocean Acidification. Earth System Science Data 2021, 13 (2), 777–808. https://doi.org/10.5194/essd-13-777-2021.</v>
       </c>
     </row>
     <row r="8">
@@ -8568,19 +8568,19 @@
       </c>
       <c r="B8" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>Harmonized</v>
+        <v>Gridded surface</v>
       </c>
       <c r="C8" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>SeaFlux</v>
+        <v>OceanSODA-ETHZv2</v>
       </c>
       <c r="D8" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>Fay and Gregor et al. (2021)</v>
+        <v>Gregor et al. (2024)</v>
       </c>
       <c r="E8" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>https://seaflux.readthedocs.io/en/latest/_static/seaflux_logo.png</v>
+        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/7decc330-7468-429c-bae9-ac51b085be30/gbc21584-fig-0007-m.jpg</v>
       </c>
       <c r="F8" s="23" t="str">
         <f t="shared" ref="F8:G8" si="24">if(ISBLANK($C8), "", F$1)</f>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="K8" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>monthly</v>
+        <v>8-day</v>
       </c>
       <c r="L8" s="23" t="str">
         <f t="shared" ref="L8:M8" si="26">if(ISBLANK($C8), "", L$1)</f>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="N8" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>1° x 1°</v>
+        <v>0.25° x 0.25°</v>
       </c>
       <c r="O8" s="23" t="str">
         <f t="shared" ref="O8:P8" si="27">if(ISBLANK($C8), "", O$1)</f>
@@ -8628,23 +8628,23 @@
       </c>
       <c r="Q8" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>1990 - 2022</v>
+        <v>1982 - 2023</v>
       </c>
       <c r="R8" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>Careful consideration of flux calculation provides a resource and code to the community for independent flux calculations</v>
+        <v>Highlighting fine-scale and short-term variability of the ocean carbon sink</v>
       </c>
       <c r="S8" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>Fay and Gregor et al. (2021)</v>
+        <v>Gregor et al. (2024)</v>
       </c>
       <c r="T8" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-2021-16</v>
+        <v>https://doi.org/10.1029/2024GB008127</v>
       </c>
       <c r="U8" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>https://zenodo.org/records/8280457</v>
+        <v>https://zenodo.org/records/11206366</v>
       </c>
       <c r="V8" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="W8" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>Harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach (Gregor and Fay, 2021). This resource provides an ensemble of six pCO2 products with air-sea CO2 fluxes computed consistently. The six included products are: CMEMS-LSCEv1, CSIR-ML6, JENA-MLS, JMA-MLR, MPI-SOMFFN, and NIES-FNN. First, missing areas of pCO2 estimates (mostly high-latitude and marginal seas) are filled using a linear-regression approach, thus addressing differences in spatial coverage between the mapping products. Further, also accounts for methodological inconsistencies in flux calculations. Fluxes are calculated using three wind products (CCMPv2, ERA5, and JRA55) along with the application of a scaled gas exchange coefficient for each of the wind products. Through these steps, SeaFlux presents a product ensemble of interpolated global surface ocean pCO2 and air–sea carbon flux estimates for the years 1990–2019</v>
+        <v>A surface fCO₂ product with a 0.25° × 0.25° spatial resolution and an 8-day temporal resolution, providing estimates starting from 1982 (Gregor et al., 2024a; Gregor et al., 2024b). The high-resolution outputs are suitable for investigating the shorter- and finer-scale dynamics of surface fCO2. Despite sharing a name with its predecessor, OceanSODA-ETHZv2 does not provide TA estimates and employs a different methodology, as described in the following steps: 1) The atmospheric trend of CO2 is removed by subtracting marine boundary layer CO2 concentrations from SOCAT fCO2 producing a new target ∆*CO2 to reduce the biases at the start and end of the time-series. 2) An 8-day seasonal climatology of ∆*CO2 is estimated using Gradient Boosted Decision Trees (GBDT), which is later used as a predictor. 3) The non-seasonal thermal component is removed from ∆*CO2, resulting in a new target, ∆*CO2nonT. 4) The new target is estimated using a feed-forward neural network, with the GBDT as one of the forcing variables. 5) Steps 4 through to 1 are inverted to arrive at fCO2. 6) Air-sea CO2 fluxes are computed using ERA5 winds.</v>
       </c>
       <c r="X8" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="Y8" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>Fay, A. R., Gregor, L., Landschützer, P., McKinley, G. A., Gruber, N., Gehlen, M., Iida, Y., Laruelle, G. G., Rödenbeck, C., Roobaert, A., and Zeng, J.: SeaFlux: harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach, Earth Syst. Sci. Data, 13, 4693–4710, https://doi.org/10.5194/essd-13-4693-2021, 2021</v>
+        <v>Gregor, L.; Shutler, J.; Gruber, N. High-Resolution Variability of the Ocean Carbon Sink. Global Biogeochemical Cycles 2024, 38 (8), e2024GB008127. https://doi.org/10.1029/2024GB008127.</v>
       </c>
     </row>
     <row r="9">
@@ -8670,19 +8670,19 @@
       </c>
       <c r="B9" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Data compilations</v>
+        <v>Harmonized</v>
       </c>
       <c r="C9" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>CODAP-NA</v>
+        <v>SeaFlux</v>
       </c>
       <c r="D9" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Jiang et al. (2021)</v>
+        <v>Fay and Gregor et al. (2021)</v>
       </c>
       <c r="E9" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>https://essd.copernicus.org/articles/13/2777/2021/essd-13-2777-2021-f01-web.png</v>
+        <v>https://seaflux.readthedocs.io/en/latest/_static/seaflux_logo.png</v>
       </c>
       <c r="F9" s="23" t="str">
         <f t="shared" ref="F9:G9" si="28">if(ISBLANK($C9), "", F$1)</f>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="H9" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Coastal, Water column</v>
+        <v>Open ocean, Surface</v>
       </c>
       <c r="I9" s="23" t="str">
         <f t="shared" ref="I9:J9" si="29">if(ISBLANK($C9), "", I$1)</f>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="K9" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>discrete</v>
+        <v>monthly</v>
       </c>
       <c r="L9" s="23" t="str">
         <f t="shared" ref="L9:M9" si="30">if(ISBLANK($C9), "", L$1)</f>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="N9" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v/>
+        <v>1° x 1°</v>
       </c>
       <c r="O9" s="23" t="str">
         <f t="shared" ref="O9:P9" si="31">if(ISBLANK($C9), "", O$1)</f>
@@ -8730,23 +8730,23 @@
       </c>
       <c r="Q9" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>2003 - 2018</v>
+        <v>1990 - 2022</v>
       </c>
       <c r="R9" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Like GLODAPv2, but for the North American coastal ocean</v>
+        <v>Careful consideration of flux calculation provides a resource and code to the community for independent flux calculations</v>
       </c>
       <c r="S9" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Jiang et al. (2021)</v>
+        <v>Fay and Gregor et al. (2021)</v>
       </c>
       <c r="T9" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-13-2777-2021</v>
+        <v>https://doi.org/10.5194/essd-2021-16</v>
       </c>
       <c r="U9" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0219960.html</v>
+        <v>https://zenodo.org/records/8280457</v>
       </c>
       <c r="V9" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="W9" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Jiang et al. (2021) synthesized two decades of discrete measurements of carbonate system variables, DO, and nutrient data from the North American continental shelves to generate the first version of Coastal Ocean Data Analysis Data Product in North America (CODAP-NA). The 2021 release encompasses 3,391 oceanographic profiles from 61 research cruises spanning the North American continental shelves from Alaska to Mexico in the west and from Canada to the Caribbean in the east. It includes 14 key variables, including temperature, salinity, DO, DIC, TA, pH, carbonate ion, fCO2, silicate, phosphate, nitrate. </v>
+        <v>Harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach (Gregor and Fay, 2021). This resource provides an ensemble of six pCO2 products with air-sea CO2 fluxes computed consistently. The six included products are: CMEMS-LSCEv1, CSIR-ML6, JENA-MLS, JMA-MLR, MPI-SOMFFN, and NIES-FNN. First, missing areas of pCO2 estimates (mostly high-latitude and marginal seas) are filled using a linear-regression approach, thus addressing differences in spatial coverage between the mapping products. Further, also accounts for methodological inconsistencies in flux calculations. Fluxes are calculated using three wind products (CCMPv2, ERA5, and JRA55) along with the application of a scaled gas exchange coefficient for each of the wind products. Through these steps, SeaFlux presents a product ensemble of interpolated global surface ocean pCO2 and air–sea carbon flux estimates for the years 1990–2019</v>
       </c>
       <c r="X9" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="Y9" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Jiang, L.-Q., Feely, R. A., Wanninkhof, R., Greeley, D., Barbero, L., Alin, S., Carter, B. R., Pierrot, D., Featherstone, C., Hooper, J., Melrose, C., Monacci, N., Sharp, J. D., Shellito, S., Xu, Y.-Y., Kozyr, A., Byrne, R. H., Cai, W.-J., Cross, J., Johnson, G. C., Hales, B., Langdon, C., Mathis, J., Salisbury, J., and Townsend, D. W.: Coastal Ocean Data Analysis Product in North America (CODAP-NA) – an internally consistent data product for discrete inorganic carbon, oxygen, and nutrients on the North American ocean margins, Earth Syst. Sci. Data, 13, 2777–2799, https://doi.org/10.5194/essd-13-2777-2021, 2021.</v>
+        <v>Fay, A. R., Gregor, L., Landschützer, P., McKinley, G. A., Gruber, N., Gehlen, M., Iida, Y., Laruelle, G. G., Rödenbeck, C., Roobaert, A., and Zeng, J.: SeaFlux: harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach, Earth Syst. Sci. Data, 13, 4693–4710, https://doi.org/10.5194/essd-13-4693-2021, 2021</v>
       </c>
     </row>
     <row r="10">
@@ -8771,19 +8771,19 @@
       </c>
       <c r="B10" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Gridded subsurface</v>
+        <v>Data compilations</v>
       </c>
       <c r="C10" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Aragonite Climatology</v>
+        <v>CODAP-NA</v>
       </c>
       <c r="D10" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Jiang et al. (2015) </v>
+        <v>Jiang et al. (2021)</v>
       </c>
       <c r="E10" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/1787fd59-795c-4979-9565-6e7270b0fdbf/gbc20348-fig-0002-m.jpg</v>
+        <v>https://essd.copernicus.org/articles/13/2777/2021/essd-13-2777-2021-f01-web.png</v>
       </c>
       <c r="F10" s="23" t="str">
         <f t="shared" ref="F10:G10" si="32">if(ISBLANK($C10), "", F$1)</f>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="H10" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Open ocean, Water column</v>
+        <v>Coastal, Water column</v>
       </c>
       <c r="I10" s="23" t="str">
         <f t="shared" ref="I10:J10" si="33">if(ISBLANK($C10), "", I$1)</f>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="K10" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>climatology</v>
+        <v>discrete</v>
       </c>
       <c r="L10" s="23" t="str">
         <f t="shared" ref="L10:M10" si="34">if(ISBLANK($C10), "", L$1)</f>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="N10" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>1° x 1°</v>
+        <v/>
       </c>
       <c r="O10" s="23" t="str">
         <f t="shared" ref="O10:P10" si="35">if(ISBLANK($C10), "", O$1)</f>
@@ -8829,25 +8829,25 @@
         <f t="shared" si="35"/>
         <v>Period</v>
       </c>
-      <c r="Q10" s="29" t="str">
+      <c r="Q10" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>2000</v>
+        <v>2003 - 2018</v>
       </c>
       <c r="R10" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Ocean interior climatology for (Ωarag) from surface to 4000 m (referenced to year 2000)</v>
+        <v>Like GLODAPv2, but for the North American coastal ocean</v>
       </c>
       <c r="S10" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Jiang et al. (2015) </v>
+        <v>Jiang et al. (2021)</v>
       </c>
       <c r="T10" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>https://doi.org/10.1002/2015GB005198</v>
+        <v>https://doi.org/10.5194/essd-13-2777-2021</v>
       </c>
       <c r="U10" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0139360.html</v>
+        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0219960.html</v>
       </c>
       <c r="V10" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8855,7 +8855,7 @@
       </c>
       <c r="W10" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Jiang et al. (2015a) developed an interior ocean Ωarag climatology (referenced to 2000), on a 1° × 1° grid at 9 standardized depth levels from the surface down to 4000m. This was accomplished by integrating data from the first version of GLODAP (Key et al., 2004), CARINA (Key et al., 2010), and PACIFICA (Suzuki et al., 2013), along with additional recent cruise datasets up to 2012. </v>
+        <v>Jiang et al. (2021) synthesized two decades of discrete measurements of carbonate system variables, DO, and nutrient data from the North American continental shelves to generate the first version of Coastal Ocean Data Analysis Data Product in North America (CODAP-NA). The 2021 release encompasses 3,391 oceanographic profiles from 61 research cruises spanning the North American continental shelves from Alaska to Mexico in the west and from Canada to the Caribbean in the east. It includes 14 key variables, including temperature, salinity, DO, DIC, TA, pH, carbonate ion, fCO2, silicate, phosphate, nitrate. </v>
       </c>
       <c r="X10" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="Y10" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Jiang, L.-Q., Feely, R. A., Carter, B. R., Greeley, D. J., Gledhill, D. K., and Arzayus, K. M.: Climatological distribution of aragonite saturation state in the global oceans,  Global Biogeochemical Cycles, 29(10), 1656–1673, https://doi.org/10.1002/2015GB005198, 2015. </v>
+        <v>Jiang, L.-Q., Feely, R. A., Wanninkhof, R., Greeley, D., Barbero, L., Alin, S., Carter, B. R., Pierrot, D., Featherstone, C., Hooper, J., Melrose, C., Monacci, N., Sharp, J. D., Shellito, S., Xu, Y.-Y., Kozyr, A., Byrne, R. H., Cai, W.-J., Cross, J., Johnson, G. C., Hales, B., Langdon, C., Mathis, J., Salisbury, J., and Townsend, D. W.: Coastal Ocean Data Analysis Product in North America (CODAP-NA) – an internally consistent data product for discrete inorganic carbon, oxygen, and nutrients on the North American ocean margins, Earth Syst. Sci. Data, 13, 2777–2799, https://doi.org/10.5194/essd-13-2777-2021, 2021.</v>
       </c>
     </row>
     <row r="11">
@@ -8876,15 +8876,15 @@
       </c>
       <c r="C11" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>CODAP-NA Climatology</v>
+        <v>Aragonite Climatology</v>
       </c>
       <c r="D11" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Jiang et al. (2024)</v>
+        <v>Jiang et al. (2015) </v>
       </c>
       <c r="E11" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>https://essd.copernicus.org/articles/16/3383/2024/essd-16-3383-2024-avatar-web.png</v>
+        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/1787fd59-795c-4979-9565-6e7270b0fdbf/gbc20348-fig-0002-m.jpg</v>
       </c>
       <c r="F11" s="23" t="str">
         <f t="shared" ref="F11:G11" si="36">if(ISBLANK($C11), "", F$1)</f>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="H11" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Coastal, Water column</v>
+        <v>Open ocean, Water column</v>
       </c>
       <c r="I11" s="23" t="str">
         <f t="shared" ref="I11:J11" si="37">if(ISBLANK($C11), "", I$1)</f>
@@ -8930,25 +8930,25 @@
         <f t="shared" si="39"/>
         <v>Period</v>
       </c>
-      <c r="Q11" s="23" t="str">
+      <c r="Q11" s="29" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="R11" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>The first discrete bottle based climatology in the North American ocean margins</v>
+        <v>Ocean interior climatology for (Ωarag) from surface to 4000 m (referenced to year 2000)</v>
       </c>
       <c r="S11" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Jiang et al. (2024)</v>
+        <v>Jiang et al. (2015) </v>
       </c>
       <c r="T11" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-16-3383-2024</v>
+        <v>https://doi.org/10.1002/2015GB005198</v>
       </c>
       <c r="U11" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0270962.html</v>
+        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0139360.html</v>
       </c>
       <c r="V11" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="W11" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Jiang et al. (2024) developed a coastal OA indicators climatology on a 1°×1° grid, covering North American ocean margins from surface to 500 m at 14 standardized depth levels. This product includes 10 key oceanographic variables: fCO2, pH, [H+]total, free hydrogen ion content ([H+]free), carbonate ion content ([CO32-]), Ωarag, Ωcalc, DIC, TA, and Revelle Factor (RF), as well as temperature and salinity. The climatology was produced with the WOA gridding technologies of the NOAA National Centers for Environmental Information (NCEI), based on the recently released Coastal Ocean Data Analysis Product in North America (CODAP-NA) (Jiang et al., 2021), along with GLODAPv2.2022 (Lauvset et al., 2022). The relevant variables were adjusted to the year of 2010 before the gridding. </v>
+        <v>Jiang et al. (2015a) developed an interior ocean Ωarag climatology (referenced to 2000), on a 1° × 1° grid at 9 standardized depth levels from the surface down to 4000m. This was accomplished by integrating data from the first version of GLODAP (Key et al., 2004), CARINA (Key et al., 2010), and PACIFICA (Suzuki et al., 2013), along with additional recent cruise datasets up to 2012. </v>
       </c>
       <c r="X11" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="Y11" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Jiang, L.-Q., Boyer, T. P., Paver, C. R., Yoo, H., Reagan, J. R., Alin, S. R., Barbero, L., Carter, B. R., Feely, R. A., and Wanninkhof, R.: Climatological distribution of ocean acidification variables along the North American ocean margins, Earth System Science Data, 16(7), 3383–3390, https://doi.org/10.5194/essd-16-3383-2024, 2024. </v>
+        <v>Jiang, L.-Q., Feely, R. A., Carter, B. R., Greeley, D. J., Gledhill, D. K., and Arzayus, K. M.: Climatological distribution of aragonite saturation state in the global oceans,  Global Biogeochemical Cycles, 29(10), 1656–1673, https://doi.org/10.1002/2015GB005198, 2015. </v>
       </c>
     </row>
     <row r="12">
@@ -8973,19 +8973,19 @@
       </c>
       <c r="B12" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>Gridded surface</v>
+        <v>Gridded subsurface</v>
       </c>
       <c r="C12" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>Surface pH and Revelle Factor</v>
+        <v>CODAP-NA Climatology</v>
       </c>
       <c r="D12" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>Jiang et al. (2019)</v>
+        <v>Jiang et al. (2024)</v>
       </c>
       <c r="E12" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>https://media.springernature.com/lw685/springer-static/image/art%3A10.1038%2Fs41598-019-55039-4/MediaObjects/41598_2019_55039_Fig6_HTML.png?as=webp</v>
+        <v>https://essd.copernicus.org/articles/16/3383/2024/essd-16-3383-2024-avatar-web.png</v>
       </c>
       <c r="F12" s="23" t="str">
         <f t="shared" ref="F12:G12" si="40">if(ISBLANK($C12), "", F$1)</f>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="H12" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>Open ocean, Surface</v>
+        <v>Coastal, Water column</v>
       </c>
       <c r="I12" s="23" t="str">
         <f t="shared" ref="I12:J12" si="41">if(ISBLANK($C12), "", I$1)</f>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="K12" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>decadal, climatology</v>
+        <v>climatology</v>
       </c>
       <c r="L12" s="23" t="str">
         <f t="shared" ref="L12:M12" si="42">if(ISBLANK($C12), "", L$1)</f>
@@ -9033,23 +9033,23 @@
       </c>
       <c r="Q12" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>1770 - 2100</v>
+        <v>2010</v>
       </c>
       <c r="R12" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>A model-observation fusion product for pH, acidity and Revelle Factor, leveraging GFDL-ESM2M and SOCATv6</v>
+        <v>The first discrete bottle based climatology in the North American ocean margins</v>
       </c>
       <c r="S12" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>Jiang et al. (2019)</v>
+        <v>Jiang et al. (2024)</v>
       </c>
       <c r="T12" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>https://doi.org/10.1038/s41598-019-55039-4</v>
+        <v>https://doi.org/10.5194/essd-16-3383-2024</v>
       </c>
       <c r="U12" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0206289.html </v>
+        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0270962.html</v>
       </c>
       <c r="V12" s="23" t="str">
         <f t="shared" si="10"/>
@@ -9057,7 +9057,7 @@
       </c>
       <c r="W12" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>Jiang et al. (2019a) produced a high-resolution (1°×1°) data product delineating regionally varying view of global surface ocean pH, acidity, and Revelle Factor (RF) from 1770 to 2100 by amalgamating recent observational seawater CO2 data from the SOCAT database (Version 6, 1991–2018, ~23 million observations) (Bakker et al., 2016), and temporal trends at individual locations of the global surface ocean from an Earth System Model, i.e., GFDL-ESM2M (Dunne et al., 2013). The calculations were conducted under historical atmospheric CO2 levels (pre-2005) and four Representative Concentrations Pathways (post-2005) corresponding to the Intergovernmental Panel on Climate Change (IPCC)’s 5th Assessment Report, specifically RCP2.6, RCP4.5, RCP6.0, and RCP8.5. </v>
+        <v>Jiang et al. (2024) developed a coastal OA indicators climatology on a 1°×1° grid, covering North American ocean margins from surface to 500 m at 14 standardized depth levels. This product includes 10 key oceanographic variables: fCO2, pH, [H+]total, free hydrogen ion content ([H+]free), carbonate ion content ([CO32-]), Ωarag, Ωcalc, DIC, TA, and Revelle Factor (RF), as well as temperature and salinity. The climatology was produced with the WOA gridding technologies of the NOAA National Centers for Environmental Information (NCEI), based on the recently released Coastal Ocean Data Analysis Product in North America (CODAP-NA) (Jiang et al., 2021), along with GLODAPv2.2022 (Lauvset et al., 2022). The relevant variables were adjusted to the year of 2010 before the gridding. </v>
       </c>
       <c r="X12" s="23" t="str">
         <f t="shared" si="11"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="Y12" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>Jiang, L.-Q., Carter, B. R., Feely, R. A., Lauvset, S., and Olsen, A.: Surface ocean pH and buffer capacity: Past, present and future, Scientific Reports, 9(1), 18624, https://doi.org/10.1038/s41598-019-55039-4, 2019. </v>
+        <v>Jiang, L.-Q., Boyer, T. P., Paver, C. R., Yoo, H., Reagan, J. R., Alin, S. R., Barbero, L., Carter, B. R., Feely, R. A., and Wanninkhof, R.: Climatological distribution of ocean acidification variables along the North American ocean margins, Earth System Science Data, 16(7), 3383–3390, https://doi.org/10.5194/essd-16-3383-2024, 2024. </v>
       </c>
     </row>
     <row r="13">
@@ -9078,15 +9078,15 @@
       </c>
       <c r="C13" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>Surface OA Indicators </v>
+        <v>Surface pH and Revelle Factor</v>
       </c>
       <c r="D13" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>Jiang et al. (2023)</v>
+        <v>Jiang et al. (2019)</v>
       </c>
       <c r="E13" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/9184aab2-af20-4a63-9a8f-d0a99a4602bc/jame21817-fig-0008-m.jpg</v>
+        <v>https://media.springernature.com/lw685/springer-static/image/art%3A10.1038%2Fs41598-019-55039-4/MediaObjects/41598_2019_55039_Fig6_HTML.png?as=webp</v>
       </c>
       <c r="F13" s="23" t="str">
         <f t="shared" ref="F13:G13" si="44">if(ISBLANK($C13), "", F$1)</f>
@@ -9134,23 +9134,23 @@
       </c>
       <c r="Q13" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>1750 - 2100</v>
+        <v>1770 - 2100</v>
       </c>
       <c r="R13" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>A model-observation fusion product for all major OA indicators, leveraging a consortium of 14 Earth System Models and 3 observational data products</v>
+        <v>A model-observation fusion product for pH, acidity and Revelle Factor, leveraging GFDL-ESM2M and SOCATv6</v>
       </c>
       <c r="S13" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>Jiang et al. (2023)</v>
+        <v>Jiang et al. (2019)</v>
       </c>
       <c r="T13" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>https://doi.org/10.1029/2022MS003563</v>
+        <v>https://doi.org/10.1038/s41598-019-55039-4</v>
       </c>
       <c r="U13" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0259391.html</v>
+        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0206289.html </v>
       </c>
       <c r="V13" s="23" t="str">
         <f t="shared" si="10"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="W13" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>Jiang et al. (2023) developed a comprehensive model-data fusion product that delineates the trajectory of 10 OA indicators: fCO2, pH, [H+]total, [H+]free [CO32-], Ωarag, Ωcalc, DIC, TA, and RF, as well as temperature and salinity at all locations of the global surface ocean from 1750 to 2100. This product marks a significant breakthrough in OA forecasting by refining temporal trends with data from 14 Earth System Models (ESMs) within CMIP6, and by applying bias and drift corrections from three updated observational ocean carbonate system data products: SOCAT (Version 2022) (Bakker et al., 2016), GLODAPv2.2022 (Lauvset et al., 2022), and CODAP-NA (Jiang et al., 2021). This dataset offers 10-year averages on a 1° × 1° global surface ocean grid, capturing trends from preindustrial times (1750), through historical conditions (1850–2010), and projects future conditions to 2100 across five Shared Socioeconomic Pathways: SSP1-1.9, SSP1-2.6, SSP2-4.5, SSP3-7.0, and SSP5-8.5. </v>
+        <v>Jiang et al. (2019a) produced a high-resolution (1°×1°) data product delineating regionally varying view of global surface ocean pH, acidity, and Revelle Factor (RF) from 1770 to 2100 by amalgamating recent observational seawater CO2 data from the SOCAT database (Version 6, 1991–2018, ~23 million observations) (Bakker et al., 2016), and temporal trends at individual locations of the global surface ocean from an Earth System Model, i.e., GFDL-ESM2M (Dunne et al., 2013). The calculations were conducted under historical atmospheric CO2 levels (pre-2005) and four Representative Concentrations Pathways (post-2005) corresponding to the Intergovernmental Panel on Climate Change (IPCC)’s 5th Assessment Report, specifically RCP2.6, RCP4.5, RCP6.0, and RCP8.5. </v>
       </c>
       <c r="X13" s="23" t="str">
         <f t="shared" si="11"/>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="Y13" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>Jiang, L., Dunne, J., Carter, B. R., Tjiputra, J. F., Terhaar, J., Sharp, J. D., Olsen, A., Alin, S., Bakker, D. C., Feely, R. A., Gattuso, J., Hogan, P., Ilyina, T., Lange, N., Lauvset, S. K., Lewis, E. R., Lovato, T., Palmieri, J., Santana‐Falcón, Y., Schwinger, J., Séférian, R., Strand, G., Swart, N., Tanhua, T., Tsujino, H., Wanninkhof, R., Watanabe, M., Yamamoto, A., and Ziehn, T.: Global surface ocean acidification indicators from 1750 to 2100, Journal of Advances in Modeling Earth Systems, 15(3), https://doi.org/10.1029/2022ms003563, 2023.</v>
+        <v>Jiang, L.-Q., Carter, B. R., Feely, R. A., Lauvset, S., and Olsen, A.: Surface ocean pH and buffer capacity: Past, present and future, Scientific Reports, 9(1), 18624, https://doi.org/10.1038/s41598-019-55039-4, 2019. </v>
       </c>
     </row>
     <row r="14">
@@ -9175,19 +9175,19 @@
       </c>
       <c r="B14" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>Data compilations</v>
+        <v>Gridded surface</v>
       </c>
       <c r="C14" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>World Ocean Database</v>
+        <v>Surface OA Indicators </v>
       </c>
       <c r="D14" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>Mishonov et al. (2024)</v>
+        <v>Jiang et al. (2023)</v>
       </c>
       <c r="E14" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/sites/g/files/anmtlf171/files/inline-images/World%20Ocean%20Atlas%202023%20Climatology%2C%20Decade%202015-2022.png</v>
+        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/9184aab2-af20-4a63-9a8f-d0a99a4602bc/jame21817-fig-0008-m.jpg</v>
       </c>
       <c r="F14" s="23" t="str">
         <f t="shared" ref="F14:G14" si="48">if(ISBLANK($C14), "", F$1)</f>
@@ -9199,7 +9199,7 @@
       </c>
       <c r="H14" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>Open ocean, Water column</v>
+        <v>Open ocean, Surface</v>
       </c>
       <c r="I14" s="23" t="str">
         <f t="shared" ref="I14:J14" si="49">if(ISBLANK($C14), "", I$1)</f>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="K14" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>discrete</v>
+        <v>decadal, climatology</v>
       </c>
       <c r="L14" s="23" t="str">
         <f t="shared" ref="L14:M14" si="50">if(ISBLANK($C14), "", L$1)</f>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="N14" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v/>
+        <v>1° x 1°</v>
       </c>
       <c r="O14" s="23" t="str">
         <f t="shared" ref="O14:P14" si="51">if(ISBLANK($C14), "", O$1)</f>
@@ -9235,23 +9235,23 @@
       </c>
       <c r="Q14" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v/>
+        <v>1750 - 2100</v>
       </c>
       <c r="R14" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>Similar to GLODAPv2, with no adjustments</v>
+        <v>A model-observation fusion product for all major OA indicators, leveraging a consortium of 14 Earth System Models and 3 observational data products</v>
       </c>
       <c r="S14" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>Mishonov et al. (2024)</v>
+        <v>Jiang et al. (2023)</v>
       </c>
       <c r="T14" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>https://doi.org/10.25923/z885-h264</v>
+        <v>https://doi.org/10.1029/2022MS003563</v>
       </c>
       <c r="U14" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/products/world-ocean-database</v>
+        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0259391.html</v>
       </c>
       <c r="V14" s="23" t="str">
         <f t="shared" si="10"/>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="W14" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>In addition to the GLODAPv2 and JOA Suite, users can also access historical and recent original biogeochemical data collected from discrete bottle samples in a uniform format and units, along with their originator quality control (QC) flags, through the World Ocean Database (WOD) (Mishonov et al., 2024). Like the JOA Suite, these measured data remain unaltered. The WOD allows users to filter and subset data with specific variables, platforms, institutions, projects, regions, or time periods (Garcia et al., 2024). Users can visualize sampling locations on a “distribution plot” and access a cruise list for all selected data and variables. Users also have the option of exporting data in NetCDF or Comma-Separated Values (CSV) formats. Additionally, all data in the WOD are reproducible and traceable to their original data sources archived at NOAA’s National Centers for Environmental Information (NCEI). </v>
+        <v>Jiang et al. (2023) developed a comprehensive model-data fusion product that delineates the trajectory of 10 OA indicators: fCO2, pH, [H+]total, [H+]free [CO32-], Ωarag, Ωcalc, DIC, TA, and RF, as well as temperature and salinity at all locations of the global surface ocean from 1750 to 2100. This product marks a significant breakthrough in OA forecasting by refining temporal trends with data from 14 Earth System Models (ESMs) within CMIP6, and by applying bias and drift corrections from three updated observational ocean carbonate system data products: SOCAT (Version 2022) (Bakker et al., 2016), GLODAPv2.2022 (Lauvset et al., 2022), and CODAP-NA (Jiang et al., 2021). This dataset offers 10-year averages on a 1° × 1° global surface ocean grid, capturing trends from preindustrial times (1750), through historical conditions (1850–2010), and projects future conditions to 2100 across five Shared Socioeconomic Pathways: SSP1-1.9, SSP1-2.6, SSP2-4.5, SSP3-7.0, and SSP5-8.5. </v>
       </c>
       <c r="X14" s="23" t="str">
         <f t="shared" si="11"/>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="Y14" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>Mishonov, A. V., Boyer, T. P., Baranova, O. K., Bouchard, C. N., Cross, S. L., Garcia H. E., Locarnini, R. A., Paver, C. R., Wang, Z., Seidov, D., Grodsky, A. I., Beauchamp, J. G.: World Ocean Database 2023, C. Bouchard, Technical Ed., NOAA Atlas NESDIS 97, 206 pp., https://doi.org/10.25923/z885-h264, 2024. </v>
+        <v>Jiang, L., Dunne, J., Carter, B. R., Tjiputra, J. F., Terhaar, J., Sharp, J. D., Olsen, A., Alin, S., Bakker, D. C., Feely, R. A., Gattuso, J., Hogan, P., Ilyina, T., Lange, N., Lauvset, S. K., Lewis, E. R., Lovato, T., Palmieri, J., Santana‐Falcón, Y., Schwinger, J., Séférian, R., Strand, G., Swart, N., Tanhua, T., Tsujino, H., Wanninkhof, R., Watanabe, M., Yamamoto, A., and Ziehn, T.: Global surface ocean acidification indicators from 1750 to 2100, Journal of Advances in Modeling Earth Systems, 15(3), https://doi.org/10.1029/2022ms003563, 2023.</v>
       </c>
     </row>
     <row r="15">
@@ -9280,15 +9280,15 @@
       </c>
       <c r="C15" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>Salish Sea Multi-stressor Data Product</v>
+        <v>World Ocean Database</v>
       </c>
       <c r="D15" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>Alin et al. (2024)</v>
+        <v>Mishonov et al. (2024)</v>
       </c>
       <c r="E15" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>https://essd.copernicus.org/articles/16/837/2024/essd-16-837-2024-avatar-web.png</v>
+        <v>https://www.ncei.noaa.gov/sites/g/files/anmtlf171/files/inline-images/World%20Ocean%20Atlas%202023%20Climatology%2C%20Decade%202015-2022.png</v>
       </c>
       <c r="F15" s="23" t="str">
         <f t="shared" ref="F15:G15" si="52">if(ISBLANK($C15), "", F$1)</f>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="H15" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>Coastal, Water column</v>
+        <v>Open ocean, Water column</v>
       </c>
       <c r="I15" s="23" t="str">
         <f t="shared" ref="I15:J15" si="53">if(ISBLANK($C15), "", I$1)</f>
@@ -9340,19 +9340,19 @@
       </c>
       <c r="R15" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>A data compilation and multi-stressor (OA, hypoxia, temperature) data product based on cruises from 2002 to 2018 in the southern Salish Sea and Washington coast. </v>
+        <v>Similar to GLODAPv2, with no adjustments</v>
       </c>
       <c r="S15" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>Alin et al. (2024)</v>
+        <v>Mishonov et al. (2024)</v>
       </c>
       <c r="T15" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-16-837-2024</v>
+        <v>https://doi.org/10.25923/z885-h264</v>
       </c>
       <c r="U15" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/access/ocean-at-acidification-data-system/oceans/SalishCruise_DataPackage.html. </v>
+        <v>https://www.ncei.noaa.gov/products/world-ocean-database</v>
       </c>
       <c r="V15" s="23" t="str">
         <f t="shared" si="10"/>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="W15" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>Alin et al. (2024a) compiled data from 35 individual cruise data sets that sampled marine waters of the southern Salish Sea and northern Washington coast (United States) from 2008 to 2018. Ongoing seasonal sampling occurred during April, July, and September for Puget Sound cruises has occurred since 2014 and most frequently during May and October for Sound-to-Sea cruises, which sample from Puget Sound through the Strait of Juan de Fuca to the northern Washington coast. The Salish cruise data package contains observations from a total of 715 oceanographic profiles, with &gt; 7490 sensor measurements of temperature, salinity, and DO; ≥ 6070 measurements of discrete DO and nutrient (nitrate, phosphate, silicate, ammonium, nitrite) samples; and ≥ 4462 measurements of inorganic carbonate system variables (DIC and TA). A follow-on data product based on the Salish cruise data package, which only included the 3971 samples with complete information for temperature, salinity, DO, nutrients, DIC, and TA, is also available (Alin et al., 2023). This product additionally provides the most commonly used calculated carbonate system variables: pH (total scale), fCO2, pCO2, Ωarag, and Ωcalc. </v>
+        <v>In addition to the GLODAPv2 and JOA Suite, users can also access historical and recent original biogeochemical data collected from discrete bottle samples in a uniform format and units, along with their originator quality control (QC) flags, through the World Ocean Database (WOD) (Mishonov et al., 2024). Like the JOA Suite, these measured data remain unaltered. The WOD allows users to filter and subset data with specific variables, platforms, institutions, projects, regions, or time periods (Garcia et al., 2024). Users can visualize sampling locations on a “distribution plot” and access a cruise list for all selected data and variables. Users also have the option of exporting data in NetCDF or Comma-Separated Values (CSV) formats. Additionally, all data in the WOD are reproducible and traceable to their original data sources archived at NOAA’s National Centers for Environmental Information (NCEI). </v>
       </c>
       <c r="X15" s="23" t="str">
         <f t="shared" si="11"/>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="Y15" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>Alin, S. R., Newton, J. A., Feely, R. A., Greeley, D., Curry, B., Herndon, J., and Warner, M.: A decade-long cruise time series (2008–2018) of physical and biogeochemical conditions in the southern Salish Sea, North America, Earth Syst. Sci. Data, 16, 837–865, https://doi.org/10.5194/essd-16-837-2024, 2024. </v>
+        <v>Mishonov, A. V., Boyer, T. P., Baranova, O. K., Bouchard, C. N., Cross, S. L., Garcia H. E., Locarnini, R. A., Paver, C. R., Wang, Z., Seidov, D., Grodsky, A. I., Beauchamp, J. G.: World Ocean Database 2023, C. Bouchard, Technical Ed., NOAA Atlas NESDIS 97, 206 pp., https://doi.org/10.25923/z885-h264, 2024. </v>
       </c>
     </row>
     <row r="16">
@@ -9377,19 +9377,19 @@
       </c>
       <c r="B16" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A16,FALSE)</f>
-        <v>Time series</v>
+        <v>Data compilations</v>
       </c>
       <c r="C16" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A16,FALSE)</f>
-        <v>pCO2 and pH Time-series from 40 Surface Buoys</v>
+        <v>Salish Sea Multi-stressor Data Product</v>
       </c>
       <c r="D16" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A16,FALSE)</f>
-        <v>Sutton et al. (2019)</v>
+        <v>Alin et al. (2024)</v>
       </c>
       <c r="E16" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A16,FALSE)</f>
-        <v>https://essd.copernicus.org/articles/11/421/2019/essd-11-421-2019-avatar-web.png</v>
+        <v>https://essd.copernicus.org/articles/16/837/2024/essd-16-837-2024-avatar-web.png</v>
       </c>
       <c r="F16" s="23" t="str">
         <f t="shared" ref="F16:G16" si="56">if(ISBLANK($C16), "", F$1)</f>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="H16" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A16,FALSE)</f>
-        <v>Open ocean, Coastal, Surface</v>
+        <v>Coastal, Water column</v>
       </c>
       <c r="I16" s="23" t="str">
         <f t="shared" ref="I16:J16" si="57">if(ISBLANK($C16), "", I$1)</f>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="K16" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A16,FALSE)</f>
-        <v>continuous</v>
+        <v>discrete</v>
       </c>
       <c r="L16" s="23" t="str">
         <f t="shared" ref="L16:M16" si="58">if(ISBLANK($C16), "", L$1)</f>
@@ -9441,19 +9441,19 @@
       </c>
       <c r="R16" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A16,FALSE)</f>
-        <v>Based on 40 moored surface pCO2 time-series, with 17 of them containing pH</v>
+        <v>A data compilation and multi-stressor (OA, hypoxia, temperature) data product based on cruises from 2002 to 2018 in the southern Salish Sea and Washington coast. </v>
       </c>
       <c r="S16" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A16,FALSE)</f>
-        <v>Sutton et al. (2019)</v>
+        <v>Alin et al. (2024)</v>
       </c>
       <c r="T16" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A16,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-11-421-2019</v>
+        <v>https://doi.org/10.5194/essd-16-837-2024</v>
       </c>
       <c r="U16" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A16,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0173932.html</v>
+        <v>https://www.ncei.noaa.gov/access/ocean-at-acidification-data-system/oceans/SalishCruise_DataPackage.html. </v>
       </c>
       <c r="V16" s="23" t="str">
         <f t="shared" si="10"/>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="W16" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A16,FALSE)</f>
-        <v>Sutton et al. (2019) established a living dataset comprising 40 individual autonomous moored surface ocean pCO2 time-series established between 2004 and 2013, 17 of them also include autonomous pH measurements. These time-series characterize a wide range of surface ocean carbonate system conditions, across a variety of environments, including 17 oceanic and 13 coastal locations, as well as 10 coral reefs. </v>
+        <v>Alin et al. (2024a) compiled data from 35 individual cruise data sets that sampled marine waters of the southern Salish Sea and northern Washington coast (United States) from 2008 to 2018. Ongoing seasonal sampling occurred during April, July, and September for Puget Sound cruises has occurred since 2014 and most frequently during May and October for Sound-to-Sea cruises, which sample from Puget Sound through the Strait of Juan de Fuca to the northern Washington coast. The Salish cruise data package contains observations from a total of 715 oceanographic profiles, with &gt; 7490 sensor measurements of temperature, salinity, and DO; ≥ 6070 measurements of discrete DO and nutrient (nitrate, phosphate, silicate, ammonium, nitrite) samples; and ≥ 4462 measurements of inorganic carbonate system variables (DIC and TA). A follow-on data product based on the Salish cruise data package, which only included the 3971 samples with complete information for temperature, salinity, DO, nutrients, DIC, and TA, is also available (Alin et al., 2023). This product additionally provides the most commonly used calculated carbonate system variables: pH (total scale), fCO2, pCO2, Ωarag, and Ωcalc. </v>
       </c>
       <c r="X16" s="23" t="str">
         <f t="shared" si="11"/>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="Y16" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A16,FALSE)</f>
-        <v>Sutton, A. J., Feely, R. A., Maenner-Jones, S., Musielwicz, S., Osborne, J., Dietrich, C., Monacci, N., Cross, J., Bott, R., Kozyr, A., Andersson, A. J., Bates, N. R., Cai, W.-J., Cronin, M. F., De Carlo, E. H., Hales, B., Howden, S. D., Lee, C. M., Manzello, D. P., McPhaden, M. J., Meléndez, M., Mickett, J. B., Newton, J. A., Noakes, S. E., Noh, J. H., Olafsdottir, S. R., Salisbury, J. E., Send, U., Trull, T. W., Vandemark, D. C., and Weller, R. A.: Autonomous seawater pCO2 and pH time series from 40 surface buoys and the emergence of anthropogenic trends, Earth Syst. Sci. Data, 11, 421–439, https://doi.org/10.5194/essd-11-421-2019, 2019.</v>
+        <v>Alin, S. R., Newton, J. A., Feely, R. A., Greeley, D., Curry, B., Herndon, J., and Warner, M.: A decade-long cruise time series (2008–2018) of physical and biogeochemical conditions in the southern Salish Sea, North America, Earth Syst. Sci. Data, 16, 837–865, https://doi.org/10.5194/essd-16-837-2024, 2024. </v>
       </c>
     </row>
     <row r="17">
@@ -9478,19 +9478,19 @@
       </c>
       <c r="B17" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A17,FALSE)</f>
-        <v>Gridded surface</v>
+        <v>Time series</v>
       </c>
       <c r="C17" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A17,FALSE)</f>
-        <v>AOML-ET</v>
+        <v>pCO2 and pH Time-series from 40 Surface Buoys</v>
       </c>
       <c r="D17" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A17,FALSE)</f>
-        <v>Wanninkhof et al. (2015)</v>
+        <v>Sutton et al. (2019)</v>
       </c>
       <c r="E17" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A17,FALSE)</f>
-        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/449791f9-d01c-4710-bb96-bb6bf991906f/gbc21621-fig-0010-m.jpg</v>
+        <v>https://essd.copernicus.org/articles/11/421/2019/essd-11-421-2019-avatar-web.png</v>
       </c>
       <c r="F17" s="23" t="str">
         <f t="shared" ref="F17:G17" si="60">if(ISBLANK($C17), "", F$1)</f>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="H17" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A17,FALSE)</f>
-        <v>Open ocean, Surface</v>
+        <v>Open ocean, Coastal, Surface</v>
       </c>
       <c r="I17" s="23" t="str">
         <f t="shared" ref="I17:J17" si="61">if(ISBLANK($C17), "", I$1)</f>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="K17" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A17,FALSE)</f>
-        <v>monthly, climatology</v>
+        <v>continuous</v>
       </c>
       <c r="L17" s="23" t="str">
         <f t="shared" ref="L17:M17" si="62">if(ISBLANK($C17), "", L$1)</f>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="N17" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A17,FALSE)</f>
-        <v>1° x 1°</v>
+        <v/>
       </c>
       <c r="O17" s="23" t="str">
         <f t="shared" ref="O17:P17" si="63">if(ISBLANK($C17), "", O$1)</f>
@@ -9538,23 +9538,23 @@
       </c>
       <c r="Q17" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A17,FALSE)</f>
-        <v>1998 - 2023</v>
+        <v/>
       </c>
       <c r="R17" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A17,FALSE)</f>
-        <v>Monthly global sea-air CO2 flux maps in modern era</v>
+        <v>Based on 40 moored surface pCO2 time-series, with 17 of them containing pH</v>
       </c>
       <c r="S17" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A17,FALSE)</f>
-        <v>Wanninkhof et al. (2015)</v>
+        <v>Sutton et al. (2019)</v>
       </c>
       <c r="T17" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A17,FALSE)</f>
-        <v>https://doi.org/10.1029/2024GB008315</v>
+        <v>https://doi.org/10.5194/essd-11-421-2019</v>
       </c>
       <c r="U17" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A17,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0298989.html</v>
+        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0173932.html</v>
       </c>
       <c r="V17" s="23" t="str">
         <f t="shared" si="10"/>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="W17" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A17,FALSE)</f>
-        <v>Wanninkhof et al. (2025) developed a monthly global ocean data product of seawater pCO2 and sea-air CO2 fluxes, referred to as AOML-ET, using an extremely randomized trees (ET) machine learning technique. These maps are created on 1° × 1° spatial grids, providing global surface ocean coverages from 1998 to 2023. AOML-ET incorporates several predictor variables, including time, location, SST, SSS, MLD, and chlorophyll-a. The model was trained using the v2020 and v2023 releases of the SOCAT data product (No. 1). Sea-air CO2 fluxes were calculated using the air-sea CO2 partial pressure difference (∆pCO2) and a bulk gas transfer formulation incorporating windspeed. </v>
+        <v>Sutton et al. (2019) established a living dataset comprising 40 individual autonomous moored surface ocean pCO2 time-series established between 2004 and 2013, 17 of them also include autonomous pH measurements. These time-series characterize a wide range of surface ocean carbonate system conditions, across a variety of environments, including 17 oceanic and 13 coastal locations, as well as 10 coral reefs. </v>
       </c>
       <c r="X17" s="23" t="str">
         <f t="shared" si="11"/>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="Y17" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A17,FALSE)</f>
-        <v>Wanninkhof, R., Triñanes, J., Pierrot, D., Munro, D. R., Sweeney, C., and Fay, A. R.: Trends in sea-air CO2 fluxes and sensitivities to atmospheric forcing using an extremely randomized trees machine learning approach, Global Biogeochemical Cycles, 39, https://doi.org/10.1029/2024GB008315, 2025.</v>
+        <v>Sutton, A. J., Feely, R. A., Maenner-Jones, S., Musielwicz, S., Osborne, J., Dietrich, C., Monacci, N., Cross, J., Bott, R., Kozyr, A., Andersson, A. J., Bates, N. R., Cai, W.-J., Cronin, M. F., De Carlo, E. H., Hales, B., Howden, S. D., Lee, C. M., Manzello, D. P., McPhaden, M. J., Meléndez, M., Mickett, J. B., Newton, J. A., Noakes, S. E., Noh, J. H., Olafsdottir, S. R., Salisbury, J. E., Send, U., Trull, T. W., Vandemark, D. C., and Weller, R. A.: Autonomous seawater pCO2 and pH time series from 40 surface buoys and the emergence of anthropogenic trends, Earth Syst. Sci. Data, 11, 421–439, https://doi.org/10.5194/essd-11-421-2019, 2019.</v>
       </c>
     </row>
     <row r="18">
@@ -9583,15 +9583,15 @@
       </c>
       <c r="C18" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A18,FALSE)</f>
-        <v>Gridded Surface OA Indicators in the Northern Caribbean Sea</v>
+        <v>AOML-ET</v>
       </c>
       <c r="D18" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A18,FALSE)</f>
-        <v>Wanninkhof et al. (2020)</v>
+        <v>Wanninkhof et al. (2015)</v>
       </c>
       <c r="E18" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A18,FALSE)</f>
-        <v>https://essd.copernicus.org/articles/12/1489/2020/essd-12-1489-2020-avatar-web.png</v>
+        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/449791f9-d01c-4710-bb96-bb6bf991906f/gbc21621-fig-0010-m.jpg</v>
       </c>
       <c r="F18" s="23" t="str">
         <f t="shared" ref="F18:G18" si="64">if(ISBLANK($C18), "", F$1)</f>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="H18" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A18,FALSE)</f>
-        <v>Coastal</v>
+        <v>Open ocean, Surface</v>
       </c>
       <c r="I18" s="23" t="str">
         <f t="shared" ref="I18:J18" si="65">if(ISBLANK($C18), "", I$1)</f>
@@ -9639,23 +9639,23 @@
       </c>
       <c r="Q18" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A18,FALSE)</f>
-        <v>2002 - 2019</v>
+        <v>1998 - 2023</v>
       </c>
       <c r="R18" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A18,FALSE)</f>
-        <v>A 17-year record of  fCO2, TA, pH, Ωarag, and air-sea CO2 flux in the Caribbean Sea </v>
+        <v>Monthly global sea-air CO2 flux maps in modern era</v>
       </c>
       <c r="S18" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A18,FALSE)</f>
-        <v>Wanninkhof et al. (2020)</v>
+        <v>Wanninkhof et al. (2015)</v>
       </c>
       <c r="T18" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A18,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-12-1489-2020</v>
+        <v>https://doi.org/10.1029/2024GB008315</v>
       </c>
       <c r="U18" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A18,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0207749.html </v>
+        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0298989.html</v>
       </c>
       <c r="V18" s="23" t="str">
         <f t="shared" si="10"/>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="W18" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A18,FALSE)</f>
-        <v>This dataset contains a high-quality dataset of derived products from over a million observations of surface water partial pressure/fugacity of carbon dioxide (pCO2w/fCO2w), for the Caribbean Sea, Gulf of Mexico/Gulf of America and North-West Atlantic Ocean covering the timespan from 2002-01-01 to 2019-12-30. The derived quantities include TA, acidity (pH), Ωarag and air-sea CO2 flux (Wanninkhof et al., 2020). </v>
+        <v>Wanninkhof et al. (2025) developed a monthly global ocean data product of seawater pCO2 and sea-air CO2 fluxes, referred to as AOML-ET, using an extremely randomized trees (ET) machine learning technique. These maps are created on 1° × 1° spatial grids, providing global surface ocean coverages from 1998 to 2023. AOML-ET incorporates several predictor variables, including time, location, SST, SSS, MLD, and chlorophyll-a. The model was trained using the v2020 and v2023 releases of the SOCAT data product (No. 1). Sea-air CO2 fluxes were calculated using the air-sea CO2 partial pressure difference (∆pCO2) and a bulk gas transfer formulation incorporating windspeed. </v>
       </c>
       <c r="X18" s="23" t="str">
         <f t="shared" si="11"/>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="Y18" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A18,FALSE)</f>
-        <v>Wanninkhof, R., Pierrot, D., Sullivan, K., Barbero, L., and Triñanes, J.: A 17-year dataset of surface water fugacity of CO2 along with calculated pH, aragonite saturation state and air–sea CO2 fluxes in the northern Caribbean Sea, Earth Syst. Sci. Data, 12, 1489–1509, https://doi.org/10.5194/essd-12-1489-2020, 2020.</v>
+        <v>Wanninkhof, R., Triñanes, J., Pierrot, D., Munro, D. R., Sweeney, C., and Fay, A. R.: Trends in sea-air CO2 fluxes and sensitivities to atmospheric forcing using an extremely randomized trees machine learning approach, Global Biogeochemical Cycles, 39, https://doi.org/10.1029/2024GB008315, 2025.</v>
       </c>
     </row>
     <row r="19">
@@ -9680,19 +9680,19 @@
       </c>
       <c r="B19" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A19,FALSE)</f>
-        <v>Gridded subsurface</v>
+        <v>Gridded surface</v>
       </c>
       <c r="C19" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A19,FALSE)</f>
-        <v>Acidification Metrics in the Ocean Interior</v>
+        <v>Gridded Surface OA Indicators in the Northern Caribbean Sea</v>
       </c>
       <c r="D19" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A19,FALSE)</f>
-        <v>Fassbender et al. (2023) </v>
+        <v>Wanninkhof et al. (2020)</v>
       </c>
       <c r="E19" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A19,FALSE)</f>
-        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/c15194d4-6cd1-4bed-a018-d654d574a917/gbc21500-fig-0001-m.jpg</v>
+        <v>https://essd.copernicus.org/articles/12/1489/2020/essd-12-1489-2020-avatar-web.png</v>
       </c>
       <c r="F19" s="23" t="str">
         <f t="shared" ref="F19:G19" si="68">if(ISBLANK($C19), "", F$1)</f>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="H19" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A19,FALSE)</f>
-        <v>Open ocean, Water column</v>
+        <v>Coastal</v>
       </c>
       <c r="I19" s="23" t="str">
         <f t="shared" ref="I19:J19" si="69">if(ISBLANK($C19), "", I$1)</f>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="K19" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A19,FALSE)</f>
-        <v>climatology</v>
+        <v>monthly, climatology</v>
       </c>
       <c r="L19" s="23" t="str">
         <f t="shared" ref="L19:M19" si="70">if(ISBLANK($C19), "", L$1)</f>
@@ -9740,23 +9740,23 @@
       </c>
       <c r="Q19" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A19,FALSE)</f>
-        <v>1850 - 2002</v>
+        <v>2002 - 2019</v>
       </c>
       <c r="R19" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A19,FALSE)</f>
-        <v>Metrics of acidification in the ocean interior (to 2000 m) and the component of those changes caused by carbonate system nonlinearities</v>
+        <v>A 17-year record of  fCO2, TA, pH, Ωarag, and air-sea CO2 flux in the Caribbean Sea </v>
       </c>
       <c r="S19" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A19,FALSE)</f>
-        <v>Fassbender et al. (2023) </v>
+        <v>Wanninkhof et al. (2020)</v>
       </c>
       <c r="T19" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A19,FALSE)</f>
-        <v>https://doi.org/10.1029/2023GB007843</v>
+        <v>https://doi.org/10.5194/essd-12-1489-2020</v>
       </c>
       <c r="U19" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A19,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0290073.html</v>
+        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0207749.html </v>
       </c>
       <c r="V19" s="23" t="str">
         <f t="shared" si="10"/>
@@ -9764,7 +9764,7 @@
       </c>
       <c r="W19" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A19,FALSE)</f>
-        <v>Fassbender et al. (2023) generated estimates of global interior ocean changes to pH, [H+], Ωarag, pCO2, and the Revelle sensitivity factor driven by the accumulation of anthropogenic carbon (Cant) from the preindustrial period to the year 2002, and quantified the component of those changes caused by nonlinearities in the carbonate system. For each OA metric, the dataset includes year 2002 values and quasi-preindustrial values, which were estimated by subtracting Cant from the year 2002 carbonate chemistry information and recomputing each OA metric without considering any warming, circulation, or biological changes that may have occurred since the preindustrial era. </v>
+        <v>This dataset contains a high-quality dataset of derived products from over a million observations of surface water partial pressure/fugacity of carbon dioxide (pCO2w/fCO2w), for the Caribbean Sea, Gulf of Mexico/Gulf of America and North-West Atlantic Ocean covering the timespan from 2002-01-01 to 2019-12-30. The derived quantities include TA, acidity (pH), Ωarag and air-sea CO2 flux (Wanninkhof et al., 2020). </v>
       </c>
       <c r="X19" s="23" t="str">
         <f t="shared" si="11"/>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="Y19" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A19,FALSE)</f>
-        <v>Fassbender, A. J., Carter, B. R., Sharp, J. D., Huang, Y., Arroyo, M. C., and Frenzel, H.: Amplified subsurface signals of ocean acidification, Global Biogeochemical Cycles, 37, e2023GB007843, https://doi.org/10.1029/2023GB007843, 2023. </v>
+        <v>Wanninkhof, R., Pierrot, D., Sullivan, K., Barbero, L., and Triñanes, J.: A 17-year dataset of surface water fugacity of CO2 along with calculated pH, aragonite saturation state and air–sea CO2 fluxes in the northern Caribbean Sea, Earth Syst. Sci. Data, 12, 1489–1509, https://doi.org/10.5194/essd-12-1489-2020, 2020.</v>
       </c>
     </row>
     <row r="20">
@@ -9781,19 +9781,19 @@
       </c>
       <c r="B20" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A20,FALSE)</f>
-        <v>Data compilations</v>
+        <v>Gridded subsurface</v>
       </c>
       <c r="C20" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A20,FALSE)</f>
-        <v>LDEO Surface pCO2 Database</v>
+        <v>Acidification Metrics in the Ocean Interior</v>
       </c>
       <c r="D20" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A20,FALSE)</f>
-        <v>Takahashi et a. (2009)</v>
+        <v>Fassbender et al. (2023) </v>
       </c>
       <c r="E20" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A20,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/access/ocean-carbon-acidification-data-system/oceans/LDEO_Underway_Database/LDEOv2019_map.jpg</v>
+        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/c15194d4-6cd1-4bed-a018-d654d574a917/gbc21500-fig-0001-m.jpg</v>
       </c>
       <c r="F20" s="23" t="str">
         <f t="shared" ref="F20:G20" si="72">if(ISBLANK($C20), "", F$1)</f>
@@ -9805,7 +9805,7 @@
       </c>
       <c r="H20" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A20,FALSE)</f>
-        <v>Open ocean, Surface</v>
+        <v>Open ocean, Water column</v>
       </c>
       <c r="I20" s="23" t="str">
         <f t="shared" ref="I20:J20" si="73">if(ISBLANK($C20), "", I$1)</f>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="K20" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A20,FALSE)</f>
-        <v>continuous</v>
+        <v>climatology</v>
       </c>
       <c r="L20" s="23" t="str">
         <f t="shared" ref="L20:M20" si="74">if(ISBLANK($C20), "", L$1)</f>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="N20" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A20,FALSE)</f>
-        <v/>
+        <v>1° x 1°</v>
       </c>
       <c r="O20" s="23" t="str">
         <f t="shared" ref="O20:P20" si="75">if(ISBLANK($C20), "", O$1)</f>
@@ -9841,23 +9841,23 @@
       </c>
       <c r="Q20" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A20,FALSE)</f>
-        <v/>
+        <v>1850 - 2002</v>
       </c>
       <c r="R20" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A20,FALSE)</f>
-        <v>The LDEO database reports pCO2 exclusively from equilibrator-CO2 analyzer systems</v>
+        <v>Metrics of acidification in the ocean interior (to 2000 m) and the component of those changes caused by carbonate system nonlinearities</v>
       </c>
       <c r="S20" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A20,FALSE)</f>
-        <v>Takahashi et a. (2009)</v>
+        <v>Fassbender et al. (2023) </v>
       </c>
       <c r="T20" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A20,FALSE)</f>
-        <v>https://doi.org/10.1016/j.dsr2.2008.12.009</v>
+        <v>https://doi.org/10.1029/2023GB007843</v>
       </c>
       <c r="U20" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A20,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0160492.html</v>
+        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0290073.html</v>
       </c>
       <c r="V20" s="23" t="str">
         <f t="shared" si="10"/>
@@ -9865,7 +9865,7 @@
       </c>
       <c r="W20" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A20,FALSE)</f>
-        <v>Dr. Taro Takahashi [LDEO, Palisades, New York] started synthesizing global surface ocean CO2 data in 1997, compiling three decades of observations (~250,000 measurements) to create  inaugural monthly global surface pCO2 maps (Takahashi et al., 1997; Takahashi et al., 2002). The most recent version (V2019) expanded this dataset to approximately 14.2 million surface water pCO2 measurements spanning from 1957–2019. Distinct from the SOCAT database, the LDEO database reports pCO2, instead of fCO2, exclusively from equilibrator-CO2 analyzer systems, with an average estimated uncertainty of ± 2.5 µatm. The database is also interpolated onto a global surface ocean 4° × 5° grid for a reference year 2000 (Takahashi et al., 2009) and 2010 (Fay et al., 2024). </v>
+        <v>Fassbender et al. (2023) generated estimates of global interior ocean changes to pH, [H+], Ωarag, pCO2, and the Revelle sensitivity factor driven by the accumulation of anthropogenic carbon (Cant) from the preindustrial period to the year 2002, and quantified the component of those changes caused by nonlinearities in the carbonate system. For each OA metric, the dataset includes year 2002 values and quasi-preindustrial values, which were estimated by subtracting Cant from the year 2002 carbonate chemistry information and recomputing each OA metric without considering any warming, circulation, or biological changes that may have occurred since the preindustrial era. </v>
       </c>
       <c r="X20" s="23" t="str">
         <f t="shared" si="11"/>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="Y20" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A20,FALSE)</f>
-        <v>Takahashi, T., Sutherland, S. C., Wanninkhof, R., Sweeney, C., Feely, R. A., Chipman, D. W., Hales, B., Friederich, G., Chavez, F., Sabine, C., Watson, A., Bakker, D. C. E., Schuster, U., Metzl, N., Yoshikawa-Inoue, H., Ishii, M., Midorikawa, T., Nojiri, Y., Körtzinger, A., Steinhoff, T., and de Baar, H. J. W.: Climatological mean and decadal change in Surface Ocean pCO2, and net sea–air CO2 flux over the Global Oceans, Deep Sea Research Part II: Topical Studies in Oceanography, 56(8–10), 554–577, https://doi.org/10.1016/j.dsr2.2008.12.009, 2009.</v>
+        <v>Fassbender, A. J., Carter, B. R., Sharp, J. D., Huang, Y., Arroyo, M. C., and Frenzel, H.: Amplified subsurface signals of ocean acidification, Global Biogeochemical Cycles, 37, e2023GB007843, https://doi.org/10.1029/2023GB007843, 2023. </v>
       </c>
     </row>
     <row r="21">

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -185,6 +185,30 @@
   </si>
   <si>
     <t xml:space="preserve">The Global Ocean Data Analysis Project Version 2 (GLODAPv2) aggregates biogeochemical data collected from discrete bottle samples, offering extensive global coverage from the surface to depths (Key et al., 2015; Olsen et al., 2016; Lauvset et al., 2024). While GLODAP is primarily a product for basin-scale hydrographic data, it also includes coastal datasets and observations from a few time-series. The GLODAPv2 data product provides rigorously quality-controlled measurements for 14 essential oceanographic variables: temperature, salinity, dissolved oxygen (DO), nitrate, silicate, phosphate, DIC, TA, pH, chlorofluorocarbons (CFC-11, CFC-12, CFC-113), carbon tetrachloride (CCl4), and sulfur hexafluoride (SF6). These variables, excluding temperature, undergo both primary and secondary quality control procedures to detect outliers and adjust for significant measurement biases. GLODAPv2 was first published in 2016 and was updated annually through a living data process in Earth System Science Data from 2019 through “v2023,” which was published in 2024. For these updates, new data (including historical data not previously included in the data product) are quality controlled and adjusted to the 2016 version (Olsen et al., 2019; Olsen et al., 2020; Lauvset et al., 2021; Lauvset et al., 2022; Lauvset et al., 2024). Since the global repeat hydrography programs operate with decadal repetitions, the aim is to produce a completely new version of GLODAP, where all cruise datasets will be reevaluated, every decade. Release of the GLODAPv3 data product is planned for 2026, and is expected to evolve the secondary data quality control practices relative to those used in GLODAPv2. For more information on the secondary quality control process, refer to Tanhua et al. (2010) and Lauvset and Tanhua (2015). GLODAPv2 offers two kind of products: the collection of quality controlled data from discrete bottle samples taken at sampling location (Key et al., 2015; Olsen et al., 2016; Olsen et al., 2019; Olsen et al., 2020; Lauvset et al., 2021; Lauvset et al., 2022; Lauvset et al., 2024), and a gridded product, interpolated to a 1° × 1°  grid and the 33 standard depth levels of World Ocean Atlas (WOA) (Lauvset et al., 2016). </t>
+  </si>
+  <si>
+    <t>World Ocean Database</t>
+  </si>
+  <si>
+    <t>Mishonov et al. (2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mishonov, A. V., Boyer, T. P., Baranova, O. K., Bouchard, C. N., Cross, S. L., Garcia H. E., Locarnini, R. A., Paver, C. R., Wang, Z., Seidov, D., Grodsky, A. I., Beauchamp, J. G.: World Ocean Database 2023, C. Bouchard, Technical Ed., NOAA Atlas NESDIS 97, 206 pp., https://doi.org/10.25923/z885-h264, 2024. </t>
+  </si>
+  <si>
+    <t>https://www.ncei.noaa.gov/sites/g/files/anmtlf171/files/inline-images/World%20Ocean%20Atlas%202023%20Climatology%2C%20Decade%202015-2022.png</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.25923/z885-h264</t>
+  </si>
+  <si>
+    <t>https://www.ncei.noaa.gov/products/world-ocean-database</t>
+  </si>
+  <si>
+    <t>Similar to GLODAPv2, with no adjustments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In addition to the GLODAPv2 and JOA Suite, users can also access historical and recent original biogeochemical data collected from discrete bottle samples in a uniform format and units, along with their originator quality control (QC) flags, through the World Ocean Database (WOD) (Mishonov et al., 2024). Like the JOA Suite, these measured data remain unaltered. The WOD allows users to filter and subset data with specific variables, platforms, institutions, projects, regions, or time periods (Garcia et al., 2024). Users can visualize sampling locations on a “distribution plot” and access a cruise list for all selected data and variables. Users also have the option of exporting data in NetCDF or Comma-Separated Values (CSV) formats. Additionally, all data in the WOD are reproducible and traceable to their original data sources archived at NOAA’s National Centers for Environmental Information (NCEI). </t>
   </si>
   <si>
     <t>Gridded surface</t>
@@ -458,30 +482,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jiang et al. (2023) developed a comprehensive model-data fusion product that delineates the trajectory of 10 OA indicators: fCO2, pH, [H+]total, [H+]free [CO32-], Ωarag, Ωcalc, DIC, TA, and RF, as well as temperature and salinity at all locations of the global surface ocean from 1750 to 2100. This product marks a significant breakthrough in OA forecasting by refining temporal trends with data from 14 Earth System Models (ESMs) within CMIP6, and by applying bias and drift corrections from three updated observational ocean carbonate system data products: SOCAT (Version 2022) (Bakker et al., 2016), GLODAPv2.2022 (Lauvset et al., 2022), and CODAP-NA (Jiang et al., 2021). This dataset offers 10-year averages on a 1° × 1° global surface ocean grid, capturing trends from preindustrial times (1750), through historical conditions (1850–2010), and projects future conditions to 2100 across five Shared Socioeconomic Pathways: SSP1-1.9, SSP1-2.6, SSP2-4.5, SSP3-7.0, and SSP5-8.5. </t>
-  </si>
-  <si>
-    <t>World Ocean Database</t>
-  </si>
-  <si>
-    <t>Mishonov et al. (2024)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mishonov, A. V., Boyer, T. P., Baranova, O. K., Bouchard, C. N., Cross, S. L., Garcia H. E., Locarnini, R. A., Paver, C. R., Wang, Z., Seidov, D., Grodsky, A. I., Beauchamp, J. G.: World Ocean Database 2023, C. Bouchard, Technical Ed., NOAA Atlas NESDIS 97, 206 pp., https://doi.org/10.25923/z885-h264, 2024. </t>
-  </si>
-  <si>
-    <t>https://www.ncei.noaa.gov/sites/g/files/anmtlf171/files/inline-images/World%20Ocean%20Atlas%202023%20Climatology%2C%20Decade%202015-2022.png</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.25923/z885-h264</t>
-  </si>
-  <si>
-    <t>https://www.ncei.noaa.gov/products/world-ocean-database</t>
-  </si>
-  <si>
-    <t>Similar to GLODAPv2, with no adjustments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In addition to the GLODAPv2 and JOA Suite, users can also access historical and recent original biogeochemical data collected from discrete bottle samples in a uniform format and units, along with their originator quality control (QC) flags, through the World Ocean Database (WOD) (Mishonov et al., 2024). Like the JOA Suite, these measured data remain unaltered. The WOD allows users to filter and subset data with specific variables, platforms, institutions, projects, regions, or time periods (Garcia et al., 2024). Users can visualize sampling locations on a “distribution plot” and access a cruise list for all selected data and variables. Users also have the option of exporting data in NetCDF or Comma-Separated Values (CSV) formats. Additionally, all data in the WOD are reproducible and traceable to their original data sources archived at NOAA’s National Centers for Environmental Information (NCEI). </t>
   </si>
   <si>
     <t>Salish Sea Multi-stressor Data Product</t>
@@ -1375,442 +1375,442 @@
     </row>
     <row r="5">
       <c r="A5" s="4">
-        <v>45961.95201907407</v>
+        <v>45962.71938206018</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="11"/>
+      <c r="J5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="O5" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4">
-        <v>45961.909583877314</v>
+        <v>45961.95201907407</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="G6" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="H6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="I6" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="J6" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>59</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>35</v>
       </c>
       <c r="L6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="N6" s="5" t="s">
+      <c r="O6" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="O6" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="P6" s="9"/>
     </row>
     <row r="7">
       <c r="A7" s="4">
-        <v>45961.91270586806</v>
+        <v>45961.909583877314</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>78</v>
+      <c r="I7" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>35</v>
       </c>
       <c r="L7" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="P7" s="9"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4">
+        <v>45961.91270586806</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="N7" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="P7" s="9"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13">
+      <c r="F8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="P8" s="9"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13">
         <v>45961.90485893519</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="K8" s="14" t="s">
+      <c r="B9" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L8" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="M8" s="17"/>
-      <c r="N8" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="O8" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="P8" s="18"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4">
-        <v>45962.03784055555</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="H9" s="7" t="s">
+      <c r="L9" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="K9" s="5" t="s">
+      <c r="M9" s="17"/>
+      <c r="N9" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="L9" s="5" t="s">
+      <c r="O9" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="M9" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>102</v>
-      </c>
+      <c r="P9" s="18"/>
     </row>
     <row r="10">
       <c r="A10" s="4">
-        <v>45962.210738877315</v>
+        <v>45962.03784055555</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="F10" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="G10" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="H10" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="I10" s="11"/>
+      <c r="J10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="L10" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="M10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N10" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="I10" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J10" s="5" t="s">
+      <c r="O10" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4">
-        <v>45962.673469733796</v>
+        <v>45962.210738877315</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="F11" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="G11" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="I11" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="K11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L11" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="L11" s="10" t="s">
+      <c r="N11" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="N11" s="5" t="s">
+      <c r="O11" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4">
-        <v>45962.680467199076</v>
+        <v>45962.673469733796</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="G12" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="H12" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="I12" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="L12" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J12" s="5" t="s">
+      <c r="N12" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="K12" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" s="10" t="s">
+      <c r="O12" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4">
-        <v>45962.690968483796</v>
+        <v>45962.680467199076</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="F13" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="G13" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="H13" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="I13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>35</v>
       </c>
       <c r="L13" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="N13" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="N13" s="5" t="s">
+      <c r="O13" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4">
-        <v>45962.71938206018</v>
+        <v>45962.690968483796</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="G14" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="H14" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="I14" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="M14" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="N14" s="5" t="s">
         <v>148</v>
@@ -1849,7 +1849,7 @@
         <v>45</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>36</v>
@@ -1914,7 +1914,7 @@
         <v>45962.75772594908</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>167</v>
@@ -1935,7 +1935,7 @@
         <v>172</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>173</v>
@@ -1958,7 +1958,7 @@
         <v>45962.76769828703</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>177</v>
@@ -1979,7 +1979,7 @@
         <v>182</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>173</v>
@@ -2002,7 +2002,7 @@
         <v>45962.780607939814</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>187</v>
@@ -2023,10 +2023,10 @@
         <v>192</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>46</v>
@@ -8364,19 +8364,19 @@
       </c>
       <c r="B6" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>Gridded surface</v>
+        <v>Data compilations</v>
       </c>
       <c r="C6" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>CSIR-ML6</v>
+        <v>World Ocean Database</v>
       </c>
       <c r="D6" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>Gregor et al. (2019)</v>
+        <v>Mishonov et al. (2024)</v>
       </c>
       <c r="E6" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>https://gmd.copernicus.org/articles/12/5113/2019/gmd-12-5113-2019-f09-thumb.png</v>
+        <v>https://www.ncei.noaa.gov/sites/g/files/anmtlf171/files/inline-images/World%20Ocean%20Atlas%202023%20Climatology%2C%20Decade%202015-2022.png</v>
       </c>
       <c r="F6" s="23" t="str">
         <f t="shared" ref="F6:G6" si="16">if(ISBLANK($C6), "", F$1)</f>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="H6" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>Open ocean, Surface</v>
+        <v>Open ocean, Water column</v>
       </c>
       <c r="I6" s="23" t="str">
         <f t="shared" ref="I6:J6" si="17">if(ISBLANK($C6), "", I$1)</f>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="K6" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>monthly</v>
+        <v>discrete</v>
       </c>
       <c r="L6" s="23" t="str">
         <f t="shared" ref="L6:M6" si="18">if(ISBLANK($C6), "", L$1)</f>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="N6" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>1° x 1°</v>
+        <v/>
       </c>
       <c r="O6" s="23" t="str">
         <f t="shared" ref="O6:P6" si="19">if(ISBLANK($C6), "", O$1)</f>
@@ -8424,23 +8424,23 @@
       </c>
       <c r="Q6" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>1982 - 2020</v>
+        <v/>
       </c>
       <c r="R6" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>Various ML methods produce different results when data is sparse, but all still achieving roughly the same uncertainty</v>
+        <v>Similar to GLODAPv2, with no adjustments</v>
       </c>
       <c r="S6" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>Gregor et al. (2019)</v>
+        <v>Mishonov et al. (2024)</v>
       </c>
       <c r="T6" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>https://doi.org/10.5194/gmd-12-5113-2019</v>
+        <v>https://doi.org/10.25923/z885-h264</v>
       </c>
       <c r="U6" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>https://doi.org/10.25921/z682-mn47</v>
+        <v>https://www.ncei.noaa.gov/products/world-ocean-database</v>
       </c>
       <c r="V6" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="W6" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>Provides monthly 1° × 1° estimates of surface pCO2 (Gregor et al., 2019a). The approach uses the conceptual two-step approach of clustering and performing regressions for each cluster as Landschützer et al. (2016). CSIR-ML6 investigates the efficacy of various machine learning (ML) methods in estimating surface pCO2, namely, feed-forward neural networks (FFNN), extremely randomized trees (ERT), gradient boosting machines (GBM), and support vector regression (SVR). It is found that the ensemble of all but the ERT method resulted in the best estimate, highlighting the fact that various ML methods do not produce the same outcome, particularly when data is sparse. Further, the variance between ensemble members can inform us about regions where uncertainty may be large due to methodological differences. Despite this, all methods achieve roughly the same uncertainty – a barrier, or wall beyond which the community has yet to overcome.</v>
+        <v>In addition to the GLODAPv2 and JOA Suite, users can also access historical and recent original biogeochemical data collected from discrete bottle samples in a uniform format and units, along with their originator quality control (QC) flags, through the World Ocean Database (WOD) (Mishonov et al., 2024). Like the JOA Suite, these measured data remain unaltered. The WOD allows users to filter and subset data with specific variables, platforms, institutions, projects, regions, or time periods (Garcia et al., 2024). Users can visualize sampling locations on a “distribution plot” and access a cruise list for all selected data and variables. Users also have the option of exporting data in NetCDF or Comma-Separated Values (CSV) formats. Additionally, all data in the WOD are reproducible and traceable to their original data sources archived at NOAA’s National Centers for Environmental Information (NCEI). </v>
       </c>
       <c r="X6" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="Y6" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A6,FALSE)</f>
-        <v>Gregor, L., Lebehot, A. D., Kok, S., and Scheel Monteiro, P. M.: A comparative assessment of the uncertainties of global surface ocean CO2 estimates using a machine-learning ensemble (CSIR-ML6 version 2019a) – have we hit the wall?, Geosci. Model Dev., 12, 5113–5136, https://doi.org/10.5194/gmd-12-5113-2019, 2019.</v>
+        <v>Mishonov, A. V., Boyer, T. P., Baranova, O. K., Bouchard, C. N., Cross, S. L., Garcia H. E., Locarnini, R. A., Paver, C. R., Wang, Z., Seidov, D., Grodsky, A. I., Beauchamp, J. G.: World Ocean Database 2023, C. Bouchard, Technical Ed., NOAA Atlas NESDIS 97, 206 pp., https://doi.org/10.25923/z885-h264, 2024. </v>
       </c>
     </row>
     <row r="7">
@@ -8470,15 +8470,15 @@
       </c>
       <c r="C7" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>OceanSODA-ETHZv1</v>
+        <v>CSIR-ML6</v>
       </c>
       <c r="D7" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>Gregor and Gruber (2021)</v>
+        <v>Gregor et al. (2019)</v>
       </c>
       <c r="E7" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>https://essd.copernicus.org/articles/13/777/2021/essd-13-777-2021-avatar-web.png</v>
+        <v>https://gmd.copernicus.org/articles/12/5113/2019/gmd-12-5113-2019-f09-thumb.png</v>
       </c>
       <c r="F7" s="23" t="str">
         <f t="shared" ref="F7:G7" si="20">if(ISBLANK($C7), "", F$1)</f>
@@ -8526,23 +8526,23 @@
       </c>
       <c r="Q7" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>1982 - 2022</v>
+        <v>1982 - 2020</v>
       </c>
       <c r="R7" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>Temporal trends of DIC, TA, pCO2, pH, Ωarag, and Ωcalc</v>
+        <v>Various ML methods produce different results when data is sparse, but all still achieving roughly the same uncertainty</v>
       </c>
       <c r="S7" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>Gregor and Gruber (2021)</v>
+        <v>Gregor et al. (2019)</v>
       </c>
       <c r="T7" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-13-777-2021</v>
+        <v>https://doi.org/10.5194/gmd-12-5113-2019</v>
       </c>
       <c r="U7" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>https://doi.org/10.25921/m5wx-ja34</v>
+        <v>https://doi.org/10.25921/z682-mn47</v>
       </c>
       <c r="V7" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="W7" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>A monthly gridded global surface ocean data product for multiple ocean carbonate system variables, including DIC, TA, pCO2, pH (total scale), Ωarag, and Ωcalc (Gregor and Gruber, 2020; Gregor and Gruber, 2021; Gregor and Gruber, 2023; Ma et al., 2023). This dataset is structured on a 1°×1° global surface ocean grid with monthly resolution from 1982–2022, facilitating research on OA over seasonal to decadal scales. The OceanSODA-ETHZ data product was created by extrapolating in time and space the surface ocean observations of fCO2 from SOCATv2022 (Bakker et al., 2016) and TA from GLODAPv2.2022 using the newly developed Geospatial Random Cluster Ensemble Regression (GRaCER) method (Gregor, 2021). TA and pCO2 were then used to calculate the remaining variables of the marine carbonate system with the PyCO2SYS software (Humphreys et al., 2022). Phosphate and silicate from WOA 2018 product were used (Boyer et al., 2018; Garcia et al., 2018a).</v>
+        <v>Provides monthly 1° × 1° estimates of surface pCO2 (Gregor et al., 2019a). The approach uses the conceptual two-step approach of clustering and performing regressions for each cluster as Landschützer et al. (2016). CSIR-ML6 investigates the efficacy of various machine learning (ML) methods in estimating surface pCO2, namely, feed-forward neural networks (FFNN), extremely randomized trees (ERT), gradient boosting machines (GBM), and support vector regression (SVR). It is found that the ensemble of all but the ERT method resulted in the best estimate, highlighting the fact that various ML methods do not produce the same outcome, particularly when data is sparse. Further, the variance between ensemble members can inform us about regions where uncertainty may be large due to methodological differences. Despite this, all methods achieve roughly the same uncertainty – a barrier, or wall beyond which the community has yet to overcome.</v>
       </c>
       <c r="X7" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="Y7" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>Gregor, L.; Gruber, N. OceanSODA-ETHZ: A Global Gridded Data Set of the Surface Ocean Carbonate System for Seasonal to Decadal Studies of Ocean Acidification. Earth System Science Data 2021, 13 (2), 777–808. https://doi.org/10.5194/essd-13-777-2021.</v>
+        <v>Gregor, L., Lebehot, A. D., Kok, S., and Scheel Monteiro, P. M.: A comparative assessment of the uncertainties of global surface ocean CO2 estimates using a machine-learning ensemble (CSIR-ML6 version 2019a) – have we hit the wall?, Geosci. Model Dev., 12, 5113–5136, https://doi.org/10.5194/gmd-12-5113-2019, 2019.</v>
       </c>
     </row>
     <row r="8">
@@ -8572,15 +8572,15 @@
       </c>
       <c r="C8" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>OceanSODA-ETHZv2</v>
+        <v>OceanSODA-ETHZv1</v>
       </c>
       <c r="D8" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>Gregor et al. (2024)</v>
+        <v>Gregor and Gruber (2021)</v>
       </c>
       <c r="E8" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/7decc330-7468-429c-bae9-ac51b085be30/gbc21584-fig-0007-m.jpg</v>
+        <v>https://essd.copernicus.org/articles/13/777/2021/essd-13-777-2021-avatar-web.png</v>
       </c>
       <c r="F8" s="23" t="str">
         <f t="shared" ref="F8:G8" si="24">if(ISBLANK($C8), "", F$1)</f>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="K8" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>8-day</v>
+        <v>monthly</v>
       </c>
       <c r="L8" s="23" t="str">
         <f t="shared" ref="L8:M8" si="26">if(ISBLANK($C8), "", L$1)</f>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="N8" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>0.25° x 0.25°</v>
+        <v>1° x 1°</v>
       </c>
       <c r="O8" s="23" t="str">
         <f t="shared" ref="O8:P8" si="27">if(ISBLANK($C8), "", O$1)</f>
@@ -8628,23 +8628,23 @@
       </c>
       <c r="Q8" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>1982 - 2023</v>
+        <v>1982 - 2022</v>
       </c>
       <c r="R8" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>Highlighting fine-scale and short-term variability of the ocean carbon sink</v>
+        <v>Temporal trends of DIC, TA, pCO2, pH, Ωarag, and Ωcalc</v>
       </c>
       <c r="S8" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>Gregor et al. (2024)</v>
+        <v>Gregor and Gruber (2021)</v>
       </c>
       <c r="T8" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>https://doi.org/10.1029/2024GB008127</v>
+        <v>https://doi.org/10.5194/essd-13-777-2021</v>
       </c>
       <c r="U8" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>https://zenodo.org/records/11206366</v>
+        <v>https://doi.org/10.25921/m5wx-ja34</v>
       </c>
       <c r="V8" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="W8" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>A surface fCO₂ product with a 0.25° × 0.25° spatial resolution and an 8-day temporal resolution, providing estimates starting from 1982 (Gregor et al., 2024a; Gregor et al., 2024b). The high-resolution outputs are suitable for investigating the shorter- and finer-scale dynamics of surface fCO2. Despite sharing a name with its predecessor, OceanSODA-ETHZv2 does not provide TA estimates and employs a different methodology, as described in the following steps: 1) The atmospheric trend of CO2 is removed by subtracting marine boundary layer CO2 concentrations from SOCAT fCO2 producing a new target ∆*CO2 to reduce the biases at the start and end of the time-series. 2) An 8-day seasonal climatology of ∆*CO2 is estimated using Gradient Boosted Decision Trees (GBDT), which is later used as a predictor. 3) The non-seasonal thermal component is removed from ∆*CO2, resulting in a new target, ∆*CO2nonT. 4) The new target is estimated using a feed-forward neural network, with the GBDT as one of the forcing variables. 5) Steps 4 through to 1 are inverted to arrive at fCO2. 6) Air-sea CO2 fluxes are computed using ERA5 winds.</v>
+        <v>A monthly gridded global surface ocean data product for multiple ocean carbonate system variables, including DIC, TA, pCO2, pH (total scale), Ωarag, and Ωcalc (Gregor and Gruber, 2020; Gregor and Gruber, 2021; Gregor and Gruber, 2023; Ma et al., 2023). This dataset is structured on a 1°×1° global surface ocean grid with monthly resolution from 1982–2022, facilitating research on OA over seasonal to decadal scales. The OceanSODA-ETHZ data product was created by extrapolating in time and space the surface ocean observations of fCO2 from SOCATv2022 (Bakker et al., 2016) and TA from GLODAPv2.2022 using the newly developed Geospatial Random Cluster Ensemble Regression (GRaCER) method (Gregor, 2021). TA and pCO2 were then used to calculate the remaining variables of the marine carbonate system with the PyCO2SYS software (Humphreys et al., 2022). Phosphate and silicate from WOA 2018 product were used (Boyer et al., 2018; Garcia et al., 2018a).</v>
       </c>
       <c r="X8" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="Y8" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>Gregor, L.; Shutler, J.; Gruber, N. High-Resolution Variability of the Ocean Carbon Sink. Global Biogeochemical Cycles 2024, 38 (8), e2024GB008127. https://doi.org/10.1029/2024GB008127.</v>
+        <v>Gregor, L.; Gruber, N. OceanSODA-ETHZ: A Global Gridded Data Set of the Surface Ocean Carbonate System for Seasonal to Decadal Studies of Ocean Acidification. Earth System Science Data 2021, 13 (2), 777–808. https://doi.org/10.5194/essd-13-777-2021.</v>
       </c>
     </row>
     <row r="9">
@@ -8670,19 +8670,19 @@
       </c>
       <c r="B9" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Harmonized</v>
+        <v>Gridded surface</v>
       </c>
       <c r="C9" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>SeaFlux</v>
+        <v>OceanSODA-ETHZv2</v>
       </c>
       <c r="D9" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Fay and Gregor et al. (2021)</v>
+        <v>Gregor et al. (2024)</v>
       </c>
       <c r="E9" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>https://seaflux.readthedocs.io/en/latest/_static/seaflux_logo.png</v>
+        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/7decc330-7468-429c-bae9-ac51b085be30/gbc21584-fig-0007-m.jpg</v>
       </c>
       <c r="F9" s="23" t="str">
         <f t="shared" ref="F9:G9" si="28">if(ISBLANK($C9), "", F$1)</f>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="K9" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>monthly</v>
+        <v>8-day</v>
       </c>
       <c r="L9" s="23" t="str">
         <f t="shared" ref="L9:M9" si="30">if(ISBLANK($C9), "", L$1)</f>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="N9" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>1° x 1°</v>
+        <v>0.25° x 0.25°</v>
       </c>
       <c r="O9" s="23" t="str">
         <f t="shared" ref="O9:P9" si="31">if(ISBLANK($C9), "", O$1)</f>
@@ -8730,23 +8730,23 @@
       </c>
       <c r="Q9" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>1990 - 2022</v>
+        <v>1982 - 2023</v>
       </c>
       <c r="R9" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Careful consideration of flux calculation provides a resource and code to the community for independent flux calculations</v>
+        <v>Highlighting fine-scale and short-term variability of the ocean carbon sink</v>
       </c>
       <c r="S9" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Fay and Gregor et al. (2021)</v>
+        <v>Gregor et al. (2024)</v>
       </c>
       <c r="T9" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-2021-16</v>
+        <v>https://doi.org/10.1029/2024GB008127</v>
       </c>
       <c r="U9" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>https://zenodo.org/records/8280457</v>
+        <v>https://zenodo.org/records/11206366</v>
       </c>
       <c r="V9" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="W9" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach (Gregor and Fay, 2021). This resource provides an ensemble of six pCO2 products with air-sea CO2 fluxes computed consistently. The six included products are: CMEMS-LSCEv1, CSIR-ML6, JENA-MLS, JMA-MLR, MPI-SOMFFN, and NIES-FNN. First, missing areas of pCO2 estimates (mostly high-latitude and marginal seas) are filled using a linear-regression approach, thus addressing differences in spatial coverage between the mapping products. Further, also accounts for methodological inconsistencies in flux calculations. Fluxes are calculated using three wind products (CCMPv2, ERA5, and JRA55) along with the application of a scaled gas exchange coefficient for each of the wind products. Through these steps, SeaFlux presents a product ensemble of interpolated global surface ocean pCO2 and air–sea carbon flux estimates for the years 1990–2019</v>
+        <v>A surface fCO₂ product with a 0.25° × 0.25° spatial resolution and an 8-day temporal resolution, providing estimates starting from 1982 (Gregor et al., 2024a; Gregor et al., 2024b). The high-resolution outputs are suitable for investigating the shorter- and finer-scale dynamics of surface fCO2. Despite sharing a name with its predecessor, OceanSODA-ETHZv2 does not provide TA estimates and employs a different methodology, as described in the following steps: 1) The atmospheric trend of CO2 is removed by subtracting marine boundary layer CO2 concentrations from SOCAT fCO2 producing a new target ∆*CO2 to reduce the biases at the start and end of the time-series. 2) An 8-day seasonal climatology of ∆*CO2 is estimated using Gradient Boosted Decision Trees (GBDT), which is later used as a predictor. 3) The non-seasonal thermal component is removed from ∆*CO2, resulting in a new target, ∆*CO2nonT. 4) The new target is estimated using a feed-forward neural network, with the GBDT as one of the forcing variables. 5) Steps 4 through to 1 are inverted to arrive at fCO2. 6) Air-sea CO2 fluxes are computed using ERA5 winds.</v>
       </c>
       <c r="X9" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="Y9" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Fay, A. R., Gregor, L., Landschützer, P., McKinley, G. A., Gruber, N., Gehlen, M., Iida, Y., Laruelle, G. G., Rödenbeck, C., Roobaert, A., and Zeng, J.: SeaFlux: harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach, Earth Syst. Sci. Data, 13, 4693–4710, https://doi.org/10.5194/essd-13-4693-2021, 2021</v>
+        <v>Gregor, L.; Shutler, J.; Gruber, N. High-Resolution Variability of the Ocean Carbon Sink. Global Biogeochemical Cycles 2024, 38 (8), e2024GB008127. https://doi.org/10.1029/2024GB008127.</v>
       </c>
     </row>
     <row r="10">
@@ -8771,19 +8771,19 @@
       </c>
       <c r="B10" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Data compilations</v>
+        <v>Harmonized</v>
       </c>
       <c r="C10" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>CODAP-NA</v>
+        <v>SeaFlux</v>
       </c>
       <c r="D10" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Jiang et al. (2021)</v>
+        <v>Fay and Gregor et al. (2021)</v>
       </c>
       <c r="E10" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>https://essd.copernicus.org/articles/13/2777/2021/essd-13-2777-2021-f01-web.png</v>
+        <v>https://seaflux.readthedocs.io/en/latest/_static/seaflux_logo.png</v>
       </c>
       <c r="F10" s="23" t="str">
         <f t="shared" ref="F10:G10" si="32">if(ISBLANK($C10), "", F$1)</f>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="H10" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Coastal, Water column</v>
+        <v>Open ocean, Surface</v>
       </c>
       <c r="I10" s="23" t="str">
         <f t="shared" ref="I10:J10" si="33">if(ISBLANK($C10), "", I$1)</f>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="K10" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>discrete</v>
+        <v>monthly</v>
       </c>
       <c r="L10" s="23" t="str">
         <f t="shared" ref="L10:M10" si="34">if(ISBLANK($C10), "", L$1)</f>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="N10" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v/>
+        <v>1° x 1°</v>
       </c>
       <c r="O10" s="23" t="str">
         <f t="shared" ref="O10:P10" si="35">if(ISBLANK($C10), "", O$1)</f>
@@ -8831,23 +8831,23 @@
       </c>
       <c r="Q10" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>2003 - 2018</v>
+        <v>1990 - 2022</v>
       </c>
       <c r="R10" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Like GLODAPv2, but for the North American coastal ocean</v>
+        <v>Careful consideration of flux calculation provides a resource and code to the community for independent flux calculations</v>
       </c>
       <c r="S10" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Jiang et al. (2021)</v>
+        <v>Fay and Gregor et al. (2021)</v>
       </c>
       <c r="T10" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-13-2777-2021</v>
+        <v>https://doi.org/10.5194/essd-2021-16</v>
       </c>
       <c r="U10" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0219960.html</v>
+        <v>https://zenodo.org/records/8280457</v>
       </c>
       <c r="V10" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8855,7 +8855,7 @@
       </c>
       <c r="W10" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Jiang et al. (2021) synthesized two decades of discrete measurements of carbonate system variables, DO, and nutrient data from the North American continental shelves to generate the first version of Coastal Ocean Data Analysis Data Product in North America (CODAP-NA). The 2021 release encompasses 3,391 oceanographic profiles from 61 research cruises spanning the North American continental shelves from Alaska to Mexico in the west and from Canada to the Caribbean in the east. It includes 14 key variables, including temperature, salinity, DO, DIC, TA, pH, carbonate ion, fCO2, silicate, phosphate, nitrate. </v>
+        <v>Harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach (Gregor and Fay, 2021). This resource provides an ensemble of six pCO2 products with air-sea CO2 fluxes computed consistently. The six included products are: CMEMS-LSCEv1, CSIR-ML6, JENA-MLS, JMA-MLR, MPI-SOMFFN, and NIES-FNN. First, missing areas of pCO2 estimates (mostly high-latitude and marginal seas) are filled using a linear-regression approach, thus addressing differences in spatial coverage between the mapping products. Further, also accounts for methodological inconsistencies in flux calculations. Fluxes are calculated using three wind products (CCMPv2, ERA5, and JRA55) along with the application of a scaled gas exchange coefficient for each of the wind products. Through these steps, SeaFlux presents a product ensemble of interpolated global surface ocean pCO2 and air–sea carbon flux estimates for the years 1990–2019</v>
       </c>
       <c r="X10" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="Y10" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Jiang, L.-Q., Feely, R. A., Wanninkhof, R., Greeley, D., Barbero, L., Alin, S., Carter, B. R., Pierrot, D., Featherstone, C., Hooper, J., Melrose, C., Monacci, N., Sharp, J. D., Shellito, S., Xu, Y.-Y., Kozyr, A., Byrne, R. H., Cai, W.-J., Cross, J., Johnson, G. C., Hales, B., Langdon, C., Mathis, J., Salisbury, J., and Townsend, D. W.: Coastal Ocean Data Analysis Product in North America (CODAP-NA) – an internally consistent data product for discrete inorganic carbon, oxygen, and nutrients on the North American ocean margins, Earth Syst. Sci. Data, 13, 2777–2799, https://doi.org/10.5194/essd-13-2777-2021, 2021.</v>
+        <v>Fay, A. R., Gregor, L., Landschützer, P., McKinley, G. A., Gruber, N., Gehlen, M., Iida, Y., Laruelle, G. G., Rödenbeck, C., Roobaert, A., and Zeng, J.: SeaFlux: harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach, Earth Syst. Sci. Data, 13, 4693–4710, https://doi.org/10.5194/essd-13-4693-2021, 2021</v>
       </c>
     </row>
     <row r="11">
@@ -8872,19 +8872,19 @@
       </c>
       <c r="B11" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Gridded subsurface</v>
+        <v>Data compilations</v>
       </c>
       <c r="C11" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Aragonite Climatology</v>
+        <v>CODAP-NA</v>
       </c>
       <c r="D11" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Jiang et al. (2015) </v>
+        <v>Jiang et al. (2021)</v>
       </c>
       <c r="E11" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/1787fd59-795c-4979-9565-6e7270b0fdbf/gbc20348-fig-0002-m.jpg</v>
+        <v>https://essd.copernicus.org/articles/13/2777/2021/essd-13-2777-2021-f01-web.png</v>
       </c>
       <c r="F11" s="23" t="str">
         <f t="shared" ref="F11:G11" si="36">if(ISBLANK($C11), "", F$1)</f>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="H11" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Open ocean, Water column</v>
+        <v>Coastal, Water column</v>
       </c>
       <c r="I11" s="23" t="str">
         <f t="shared" ref="I11:J11" si="37">if(ISBLANK($C11), "", I$1)</f>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="K11" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>climatology</v>
+        <v>discrete</v>
       </c>
       <c r="L11" s="23" t="str">
         <f t="shared" ref="L11:M11" si="38">if(ISBLANK($C11), "", L$1)</f>
@@ -8920,7 +8920,7 @@
       </c>
       <c r="N11" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>1° x 1°</v>
+        <v/>
       </c>
       <c r="O11" s="23" t="str">
         <f t="shared" ref="O11:P11" si="39">if(ISBLANK($C11), "", O$1)</f>
@@ -8930,25 +8930,25 @@
         <f t="shared" si="39"/>
         <v>Period</v>
       </c>
-      <c r="Q11" s="29" t="str">
+      <c r="Q11" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>2000</v>
+        <v>2003 - 2018</v>
       </c>
       <c r="R11" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Ocean interior climatology for (Ωarag) from surface to 4000 m (referenced to year 2000)</v>
+        <v>Like GLODAPv2, but for the North American coastal ocean</v>
       </c>
       <c r="S11" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Jiang et al. (2015) </v>
+        <v>Jiang et al. (2021)</v>
       </c>
       <c r="T11" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>https://doi.org/10.1002/2015GB005198</v>
+        <v>https://doi.org/10.5194/essd-13-2777-2021</v>
       </c>
       <c r="U11" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0139360.html</v>
+        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0219960.html</v>
       </c>
       <c r="V11" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="W11" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Jiang et al. (2015a) developed an interior ocean Ωarag climatology (referenced to 2000), on a 1° × 1° grid at 9 standardized depth levels from the surface down to 4000m. This was accomplished by integrating data from the first version of GLODAP (Key et al., 2004), CARINA (Key et al., 2010), and PACIFICA (Suzuki et al., 2013), along with additional recent cruise datasets up to 2012. </v>
+        <v>Jiang et al. (2021) synthesized two decades of discrete measurements of carbonate system variables, DO, and nutrient data from the North American continental shelves to generate the first version of Coastal Ocean Data Analysis Data Product in North America (CODAP-NA). The 2021 release encompasses 3,391 oceanographic profiles from 61 research cruises spanning the North American continental shelves from Alaska to Mexico in the west and from Canada to the Caribbean in the east. It includes 14 key variables, including temperature, salinity, DO, DIC, TA, pH, carbonate ion, fCO2, silicate, phosphate, nitrate. </v>
       </c>
       <c r="X11" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="Y11" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Jiang, L.-Q., Feely, R. A., Carter, B. R., Greeley, D. J., Gledhill, D. K., and Arzayus, K. M.: Climatological distribution of aragonite saturation state in the global oceans,  Global Biogeochemical Cycles, 29(10), 1656–1673, https://doi.org/10.1002/2015GB005198, 2015. </v>
+        <v>Jiang, L.-Q., Feely, R. A., Wanninkhof, R., Greeley, D., Barbero, L., Alin, S., Carter, B. R., Pierrot, D., Featherstone, C., Hooper, J., Melrose, C., Monacci, N., Sharp, J. D., Shellito, S., Xu, Y.-Y., Kozyr, A., Byrne, R. H., Cai, W.-J., Cross, J., Johnson, G. C., Hales, B., Langdon, C., Mathis, J., Salisbury, J., and Townsend, D. W.: Coastal Ocean Data Analysis Product in North America (CODAP-NA) – an internally consistent data product for discrete inorganic carbon, oxygen, and nutrients on the North American ocean margins, Earth Syst. Sci. Data, 13, 2777–2799, https://doi.org/10.5194/essd-13-2777-2021, 2021.</v>
       </c>
     </row>
     <row r="12">
@@ -8977,15 +8977,15 @@
       </c>
       <c r="C12" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>CODAP-NA Climatology</v>
+        <v>Aragonite Climatology</v>
       </c>
       <c r="D12" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>Jiang et al. (2024)</v>
+        <v>Jiang et al. (2015) </v>
       </c>
       <c r="E12" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>https://essd.copernicus.org/articles/16/3383/2024/essd-16-3383-2024-avatar-web.png</v>
+        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/1787fd59-795c-4979-9565-6e7270b0fdbf/gbc20348-fig-0002-m.jpg</v>
       </c>
       <c r="F12" s="23" t="str">
         <f t="shared" ref="F12:G12" si="40">if(ISBLANK($C12), "", F$1)</f>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="H12" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>Coastal, Water column</v>
+        <v>Open ocean, Water column</v>
       </c>
       <c r="I12" s="23" t="str">
         <f t="shared" ref="I12:J12" si="41">if(ISBLANK($C12), "", I$1)</f>
@@ -9031,25 +9031,25 @@
         <f t="shared" si="43"/>
         <v>Period</v>
       </c>
-      <c r="Q12" s="23" t="str">
+      <c r="Q12" s="29" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="R12" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>The first discrete bottle based climatology in the North American ocean margins</v>
+        <v>Ocean interior climatology for (Ωarag) from surface to 4000 m (referenced to year 2000)</v>
       </c>
       <c r="S12" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>Jiang et al. (2024)</v>
+        <v>Jiang et al. (2015) </v>
       </c>
       <c r="T12" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-16-3383-2024</v>
+        <v>https://doi.org/10.1002/2015GB005198</v>
       </c>
       <c r="U12" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0270962.html</v>
+        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0139360.html</v>
       </c>
       <c r="V12" s="23" t="str">
         <f t="shared" si="10"/>
@@ -9057,7 +9057,7 @@
       </c>
       <c r="W12" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>Jiang et al. (2024) developed a coastal OA indicators climatology on a 1°×1° grid, covering North American ocean margins from surface to 500 m at 14 standardized depth levels. This product includes 10 key oceanographic variables: fCO2, pH, [H+]total, free hydrogen ion content ([H+]free), carbonate ion content ([CO32-]), Ωarag, Ωcalc, DIC, TA, and Revelle Factor (RF), as well as temperature and salinity. The climatology was produced with the WOA gridding technologies of the NOAA National Centers for Environmental Information (NCEI), based on the recently released Coastal Ocean Data Analysis Product in North America (CODAP-NA) (Jiang et al., 2021), along with GLODAPv2.2022 (Lauvset et al., 2022). The relevant variables were adjusted to the year of 2010 before the gridding. </v>
+        <v>Jiang et al. (2015a) developed an interior ocean Ωarag climatology (referenced to 2000), on a 1° × 1° grid at 9 standardized depth levels from the surface down to 4000m. This was accomplished by integrating data from the first version of GLODAP (Key et al., 2004), CARINA (Key et al., 2010), and PACIFICA (Suzuki et al., 2013), along with additional recent cruise datasets up to 2012. </v>
       </c>
       <c r="X12" s="23" t="str">
         <f t="shared" si="11"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="Y12" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A12,FALSE)</f>
-        <v>Jiang, L.-Q., Boyer, T. P., Paver, C. R., Yoo, H., Reagan, J. R., Alin, S. R., Barbero, L., Carter, B. R., Feely, R. A., and Wanninkhof, R.: Climatological distribution of ocean acidification variables along the North American ocean margins, Earth System Science Data, 16(7), 3383–3390, https://doi.org/10.5194/essd-16-3383-2024, 2024. </v>
+        <v>Jiang, L.-Q., Feely, R. A., Carter, B. R., Greeley, D. J., Gledhill, D. K., and Arzayus, K. M.: Climatological distribution of aragonite saturation state in the global oceans,  Global Biogeochemical Cycles, 29(10), 1656–1673, https://doi.org/10.1002/2015GB005198, 2015. </v>
       </c>
     </row>
     <row r="13">
@@ -9074,19 +9074,19 @@
       </c>
       <c r="B13" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>Gridded surface</v>
+        <v>Gridded subsurface</v>
       </c>
       <c r="C13" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>Surface pH and Revelle Factor</v>
+        <v>CODAP-NA Climatology</v>
       </c>
       <c r="D13" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>Jiang et al. (2019)</v>
+        <v>Jiang et al. (2024)</v>
       </c>
       <c r="E13" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>https://media.springernature.com/lw685/springer-static/image/art%3A10.1038%2Fs41598-019-55039-4/MediaObjects/41598_2019_55039_Fig6_HTML.png?as=webp</v>
+        <v>https://essd.copernicus.org/articles/16/3383/2024/essd-16-3383-2024-avatar-web.png</v>
       </c>
       <c r="F13" s="23" t="str">
         <f t="shared" ref="F13:G13" si="44">if(ISBLANK($C13), "", F$1)</f>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="H13" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>Open ocean, Surface</v>
+        <v>Coastal, Water column</v>
       </c>
       <c r="I13" s="23" t="str">
         <f t="shared" ref="I13:J13" si="45">if(ISBLANK($C13), "", I$1)</f>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="K13" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>decadal, climatology</v>
+        <v>climatology</v>
       </c>
       <c r="L13" s="23" t="str">
         <f t="shared" ref="L13:M13" si="46">if(ISBLANK($C13), "", L$1)</f>
@@ -9134,23 +9134,23 @@
       </c>
       <c r="Q13" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>1770 - 2100</v>
+        <v>2010</v>
       </c>
       <c r="R13" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>A model-observation fusion product for pH, acidity and Revelle Factor, leveraging GFDL-ESM2M and SOCATv6</v>
+        <v>The first discrete bottle based climatology in the North American ocean margins</v>
       </c>
       <c r="S13" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>Jiang et al. (2019)</v>
+        <v>Jiang et al. (2024)</v>
       </c>
       <c r="T13" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>https://doi.org/10.1038/s41598-019-55039-4</v>
+        <v>https://doi.org/10.5194/essd-16-3383-2024</v>
       </c>
       <c r="U13" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0206289.html </v>
+        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0270962.html</v>
       </c>
       <c r="V13" s="23" t="str">
         <f t="shared" si="10"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="W13" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>Jiang et al. (2019a) produced a high-resolution (1°×1°) data product delineating regionally varying view of global surface ocean pH, acidity, and Revelle Factor (RF) from 1770 to 2100 by amalgamating recent observational seawater CO2 data from the SOCAT database (Version 6, 1991–2018, ~23 million observations) (Bakker et al., 2016), and temporal trends at individual locations of the global surface ocean from an Earth System Model, i.e., GFDL-ESM2M (Dunne et al., 2013). The calculations were conducted under historical atmospheric CO2 levels (pre-2005) and four Representative Concentrations Pathways (post-2005) corresponding to the Intergovernmental Panel on Climate Change (IPCC)’s 5th Assessment Report, specifically RCP2.6, RCP4.5, RCP6.0, and RCP8.5. </v>
+        <v>Jiang et al. (2024) developed a coastal OA indicators climatology on a 1°×1° grid, covering North American ocean margins from surface to 500 m at 14 standardized depth levels. This product includes 10 key oceanographic variables: fCO2, pH, [H+]total, free hydrogen ion content ([H+]free), carbonate ion content ([CO32-]), Ωarag, Ωcalc, DIC, TA, and Revelle Factor (RF), as well as temperature and salinity. The climatology was produced with the WOA gridding technologies of the NOAA National Centers for Environmental Information (NCEI), based on the recently released Coastal Ocean Data Analysis Product in North America (CODAP-NA) (Jiang et al., 2021), along with GLODAPv2.2022 (Lauvset et al., 2022). The relevant variables were adjusted to the year of 2010 before the gridding. </v>
       </c>
       <c r="X13" s="23" t="str">
         <f t="shared" si="11"/>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="Y13" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A13,FALSE)</f>
-        <v>Jiang, L.-Q., Carter, B. R., Feely, R. A., Lauvset, S., and Olsen, A.: Surface ocean pH and buffer capacity: Past, present and future, Scientific Reports, 9(1), 18624, https://doi.org/10.1038/s41598-019-55039-4, 2019. </v>
+        <v>Jiang, L.-Q., Boyer, T. P., Paver, C. R., Yoo, H., Reagan, J. R., Alin, S. R., Barbero, L., Carter, B. R., Feely, R. A., and Wanninkhof, R.: Climatological distribution of ocean acidification variables along the North American ocean margins, Earth System Science Data, 16(7), 3383–3390, https://doi.org/10.5194/essd-16-3383-2024, 2024. </v>
       </c>
     </row>
     <row r="14">
@@ -9179,15 +9179,15 @@
       </c>
       <c r="C14" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>Surface OA Indicators </v>
+        <v>Surface pH and Revelle Factor</v>
       </c>
       <c r="D14" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>Jiang et al. (2023)</v>
+        <v>Jiang et al. (2019)</v>
       </c>
       <c r="E14" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/9184aab2-af20-4a63-9a8f-d0a99a4602bc/jame21817-fig-0008-m.jpg</v>
+        <v>https://media.springernature.com/lw685/springer-static/image/art%3A10.1038%2Fs41598-019-55039-4/MediaObjects/41598_2019_55039_Fig6_HTML.png?as=webp</v>
       </c>
       <c r="F14" s="23" t="str">
         <f t="shared" ref="F14:G14" si="48">if(ISBLANK($C14), "", F$1)</f>
@@ -9235,23 +9235,23 @@
       </c>
       <c r="Q14" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>1750 - 2100</v>
+        <v>1770 - 2100</v>
       </c>
       <c r="R14" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>A model-observation fusion product for all major OA indicators, leveraging a consortium of 14 Earth System Models and 3 observational data products</v>
+        <v>A model-observation fusion product for pH, acidity and Revelle Factor, leveraging GFDL-ESM2M and SOCATv6</v>
       </c>
       <c r="S14" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>Jiang et al. (2023)</v>
+        <v>Jiang et al. (2019)</v>
       </c>
       <c r="T14" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>https://doi.org/10.1029/2022MS003563</v>
+        <v>https://doi.org/10.1038/s41598-019-55039-4</v>
       </c>
       <c r="U14" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0259391.html</v>
+        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0206289.html </v>
       </c>
       <c r="V14" s="23" t="str">
         <f t="shared" si="10"/>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="W14" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>Jiang et al. (2023) developed a comprehensive model-data fusion product that delineates the trajectory of 10 OA indicators: fCO2, pH, [H+]total, [H+]free [CO32-], Ωarag, Ωcalc, DIC, TA, and RF, as well as temperature and salinity at all locations of the global surface ocean from 1750 to 2100. This product marks a significant breakthrough in OA forecasting by refining temporal trends with data from 14 Earth System Models (ESMs) within CMIP6, and by applying bias and drift corrections from three updated observational ocean carbonate system data products: SOCAT (Version 2022) (Bakker et al., 2016), GLODAPv2.2022 (Lauvset et al., 2022), and CODAP-NA (Jiang et al., 2021). This dataset offers 10-year averages on a 1° × 1° global surface ocean grid, capturing trends from preindustrial times (1750), through historical conditions (1850–2010), and projects future conditions to 2100 across five Shared Socioeconomic Pathways: SSP1-1.9, SSP1-2.6, SSP2-4.5, SSP3-7.0, and SSP5-8.5. </v>
+        <v>Jiang et al. (2019a) produced a high-resolution (1°×1°) data product delineating regionally varying view of global surface ocean pH, acidity, and Revelle Factor (RF) from 1770 to 2100 by amalgamating recent observational seawater CO2 data from the SOCAT database (Version 6, 1991–2018, ~23 million observations) (Bakker et al., 2016), and temporal trends at individual locations of the global surface ocean from an Earth System Model, i.e., GFDL-ESM2M (Dunne et al., 2013). The calculations were conducted under historical atmospheric CO2 levels (pre-2005) and four Representative Concentrations Pathways (post-2005) corresponding to the Intergovernmental Panel on Climate Change (IPCC)’s 5th Assessment Report, specifically RCP2.6, RCP4.5, RCP6.0, and RCP8.5. </v>
       </c>
       <c r="X14" s="23" t="str">
         <f t="shared" si="11"/>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="Y14" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A14,FALSE)</f>
-        <v>Jiang, L., Dunne, J., Carter, B. R., Tjiputra, J. F., Terhaar, J., Sharp, J. D., Olsen, A., Alin, S., Bakker, D. C., Feely, R. A., Gattuso, J., Hogan, P., Ilyina, T., Lange, N., Lauvset, S. K., Lewis, E. R., Lovato, T., Palmieri, J., Santana‐Falcón, Y., Schwinger, J., Séférian, R., Strand, G., Swart, N., Tanhua, T., Tsujino, H., Wanninkhof, R., Watanabe, M., Yamamoto, A., and Ziehn, T.: Global surface ocean acidification indicators from 1750 to 2100, Journal of Advances in Modeling Earth Systems, 15(3), https://doi.org/10.1029/2022ms003563, 2023.</v>
+        <v>Jiang, L.-Q., Carter, B. R., Feely, R. A., Lauvset, S., and Olsen, A.: Surface ocean pH and buffer capacity: Past, present and future, Scientific Reports, 9(1), 18624, https://doi.org/10.1038/s41598-019-55039-4, 2019. </v>
       </c>
     </row>
     <row r="15">
@@ -9276,19 +9276,19 @@
       </c>
       <c r="B15" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>Data compilations</v>
+        <v>Gridded surface</v>
       </c>
       <c r="C15" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>World Ocean Database</v>
+        <v>Surface OA Indicators </v>
       </c>
       <c r="D15" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>Mishonov et al. (2024)</v>
+        <v>Jiang et al. (2023)</v>
       </c>
       <c r="E15" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/sites/g/files/anmtlf171/files/inline-images/World%20Ocean%20Atlas%202023%20Climatology%2C%20Decade%202015-2022.png</v>
+        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/9184aab2-af20-4a63-9a8f-d0a99a4602bc/jame21817-fig-0008-m.jpg</v>
       </c>
       <c r="F15" s="23" t="str">
         <f t="shared" ref="F15:G15" si="52">if(ISBLANK($C15), "", F$1)</f>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="H15" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>Open ocean, Water column</v>
+        <v>Open ocean, Surface</v>
       </c>
       <c r="I15" s="23" t="str">
         <f t="shared" ref="I15:J15" si="53">if(ISBLANK($C15), "", I$1)</f>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="K15" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>discrete</v>
+        <v>decadal, climatology</v>
       </c>
       <c r="L15" s="23" t="str">
         <f t="shared" ref="L15:M15" si="54">if(ISBLANK($C15), "", L$1)</f>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="N15" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v/>
+        <v>1° x 1°</v>
       </c>
       <c r="O15" s="23" t="str">
         <f t="shared" ref="O15:P15" si="55">if(ISBLANK($C15), "", O$1)</f>
@@ -9336,23 +9336,23 @@
       </c>
       <c r="Q15" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v/>
+        <v>1750 - 2100</v>
       </c>
       <c r="R15" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>Similar to GLODAPv2, with no adjustments</v>
+        <v>A model-observation fusion product for all major OA indicators, leveraging a consortium of 14 Earth System Models and 3 observational data products</v>
       </c>
       <c r="S15" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>Mishonov et al. (2024)</v>
+        <v>Jiang et al. (2023)</v>
       </c>
       <c r="T15" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>https://doi.org/10.25923/z885-h264</v>
+        <v>https://doi.org/10.1029/2022MS003563</v>
       </c>
       <c r="U15" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/products/world-ocean-database</v>
+        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0259391.html</v>
       </c>
       <c r="V15" s="23" t="str">
         <f t="shared" si="10"/>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="W15" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>In addition to the GLODAPv2 and JOA Suite, users can also access historical and recent original biogeochemical data collected from discrete bottle samples in a uniform format and units, along with their originator quality control (QC) flags, through the World Ocean Database (WOD) (Mishonov et al., 2024). Like the JOA Suite, these measured data remain unaltered. The WOD allows users to filter and subset data with specific variables, platforms, institutions, projects, regions, or time periods (Garcia et al., 2024). Users can visualize sampling locations on a “distribution plot” and access a cruise list for all selected data and variables. Users also have the option of exporting data in NetCDF or Comma-Separated Values (CSV) formats. Additionally, all data in the WOD are reproducible and traceable to their original data sources archived at NOAA’s National Centers for Environmental Information (NCEI). </v>
+        <v>Jiang et al. (2023) developed a comprehensive model-data fusion product that delineates the trajectory of 10 OA indicators: fCO2, pH, [H+]total, [H+]free [CO32-], Ωarag, Ωcalc, DIC, TA, and RF, as well as temperature and salinity at all locations of the global surface ocean from 1750 to 2100. This product marks a significant breakthrough in OA forecasting by refining temporal trends with data from 14 Earth System Models (ESMs) within CMIP6, and by applying bias and drift corrections from three updated observational ocean carbonate system data products: SOCAT (Version 2022) (Bakker et al., 2016), GLODAPv2.2022 (Lauvset et al., 2022), and CODAP-NA (Jiang et al., 2021). This dataset offers 10-year averages on a 1° × 1° global surface ocean grid, capturing trends from preindustrial times (1750), through historical conditions (1850–2010), and projects future conditions to 2100 across five Shared Socioeconomic Pathways: SSP1-1.9, SSP1-2.6, SSP2-4.5, SSP3-7.0, and SSP5-8.5. </v>
       </c>
       <c r="X15" s="23" t="str">
         <f t="shared" si="11"/>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="Y15" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A15,FALSE)</f>
-        <v>Mishonov, A. V., Boyer, T. P., Baranova, O. K., Bouchard, C. N., Cross, S. L., Garcia H. E., Locarnini, R. A., Paver, C. R., Wang, Z., Seidov, D., Grodsky, A. I., Beauchamp, J. G.: World Ocean Database 2023, C. Bouchard, Technical Ed., NOAA Atlas NESDIS 97, 206 pp., https://doi.org/10.25923/z885-h264, 2024. </v>
+        <v>Jiang, L., Dunne, J., Carter, B. R., Tjiputra, J. F., Terhaar, J., Sharp, J. D., Olsen, A., Alin, S., Bakker, D. C., Feely, R. A., Gattuso, J., Hogan, P., Ilyina, T., Lange, N., Lauvset, S. K., Lewis, E. R., Lovato, T., Palmieri, J., Santana‐Falcón, Y., Schwinger, J., Séférian, R., Strand, G., Swart, N., Tanhua, T., Tsujino, H., Wanninkhof, R., Watanabe, M., Yamamoto, A., and Ziehn, T.: Global surface ocean acidification indicators from 1750 to 2100, Journal of Advances in Modeling Earth Systems, 15(3), https://doi.org/10.1029/2022ms003563, 2023.</v>
       </c>
     </row>
     <row r="16">

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -211,6 +211,36 @@
     <t xml:space="preserve">In addition to the GLODAPv2 and JOA Suite, users can also access historical and recent original biogeochemical data collected from discrete bottle samples in a uniform format and units, along with their originator quality control (QC) flags, through the World Ocean Database (WOD) (Mishonov et al., 2024). Like the JOA Suite, these measured data remain unaltered. The WOD allows users to filter and subset data with specific variables, platforms, institutions, projects, regions, or time periods (Garcia et al., 2024). Users can visualize sampling locations on a “distribution plot” and access a cruise list for all selected data and variables. Users also have the option of exporting data in NetCDF or Comma-Separated Values (CSV) formats. Additionally, all data in the WOD are reproducible and traceable to their original data sources archived at NOAA’s National Centers for Environmental Information (NCEI). </t>
   </si>
   <si>
+    <t>CODAP-NA</t>
+  </si>
+  <si>
+    <t>Jiang et al. (2021)</t>
+  </si>
+  <si>
+    <t>Jiang, L.-Q., Feely, R. A., Wanninkhof, R., Greeley, D., Barbero, L., Alin, S., Carter, B. R., Pierrot, D., Featherstone, C., Hooper, J., Melrose, C., Monacci, N., Sharp, J. D., Shellito, S., Xu, Y.-Y., Kozyr, A., Byrne, R. H., Cai, W.-J., Cross, J., Johnson, G. C., Hales, B., Langdon, C., Mathis, J., Salisbury, J., and Townsend, D. W.: Coastal Ocean Data Analysis Product in North America (CODAP-NA) – an internally consistent data product for discrete inorganic carbon, oxygen, and nutrients on the North American ocean margins, Earth Syst. Sci. Data, 13, 2777–2799, https://doi.org/10.5194/essd-13-2777-2021, 2021.</t>
+  </si>
+  <si>
+    <t>https://essd.copernicus.org/articles/13/2777/2021/essd-13-2777-2021-f01-web.png</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5194/essd-13-2777-2021</t>
+  </si>
+  <si>
+    <t>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0219960.html</t>
+  </si>
+  <si>
+    <t>Coastal, Water column</t>
+  </si>
+  <si>
+    <t>2003 - 2018</t>
+  </si>
+  <si>
+    <t>Like GLODAPv2, but for the North American coastal ocean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jiang et al. (2021) synthesized two decades of discrete measurements of carbonate system variables, DO, and nutrient data from the North American continental shelves to generate the first version of Coastal Ocean Data Analysis Data Product in North America (CODAP-NA). The 2021 release encompasses 3,391 oceanographic profiles from 61 research cruises spanning the North American continental shelves from Alaska to Mexico in the west and from Canada to the Caribbean in the east. It includes 14 key variables, including temperature, salinity, DO, DIC, TA, pH, carbonate ion, fCO2, silicate, phosphate, nitrate. </t>
+  </si>
+  <si>
     <t>Gridded surface</t>
   </si>
   <si>
@@ -335,36 +365,6 @@
   </si>
   <si>
     <t>Harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach (Gregor and Fay, 2021). This resource provides an ensemble of six pCO2 products with air-sea CO2 fluxes computed consistently. The six included products are: CMEMS-LSCEv1, CSIR-ML6, JENA-MLS, JMA-MLR, MPI-SOMFFN, and NIES-FNN. First, missing areas of pCO2 estimates (mostly high-latitude and marginal seas) are filled using a linear-regression approach, thus addressing differences in spatial coverage between the mapping products. Further, also accounts for methodological inconsistencies in flux calculations. Fluxes are calculated using three wind products (CCMPv2, ERA5, and JRA55) along with the application of a scaled gas exchange coefficient for each of the wind products. Through these steps, SeaFlux presents a product ensemble of interpolated global surface ocean pCO2 and air–sea carbon flux estimates for the years 1990–2019</t>
-  </si>
-  <si>
-    <t>CODAP-NA</t>
-  </si>
-  <si>
-    <t>Jiang et al. (2021)</t>
-  </si>
-  <si>
-    <t>Jiang, L.-Q., Feely, R. A., Wanninkhof, R., Greeley, D., Barbero, L., Alin, S., Carter, B. R., Pierrot, D., Featherstone, C., Hooper, J., Melrose, C., Monacci, N., Sharp, J. D., Shellito, S., Xu, Y.-Y., Kozyr, A., Byrne, R. H., Cai, W.-J., Cross, J., Johnson, G. C., Hales, B., Langdon, C., Mathis, J., Salisbury, J., and Townsend, D. W.: Coastal Ocean Data Analysis Product in North America (CODAP-NA) – an internally consistent data product for discrete inorganic carbon, oxygen, and nutrients on the North American ocean margins, Earth Syst. Sci. Data, 13, 2777–2799, https://doi.org/10.5194/essd-13-2777-2021, 2021.</t>
-  </si>
-  <si>
-    <t>https://essd.copernicus.org/articles/13/2777/2021/essd-13-2777-2021-f01-web.png</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.5194/essd-13-2777-2021</t>
-  </si>
-  <si>
-    <t>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0219960.html</t>
-  </si>
-  <si>
-    <t>Coastal, Water column</t>
-  </si>
-  <si>
-    <t>2003 - 2018</t>
-  </si>
-  <si>
-    <t>Like GLODAPv2, but for the North American coastal ocean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jiang et al. (2021) synthesized two decades of discrete measurements of carbonate system variables, DO, and nutrient data from the North American continental shelves to generate the first version of Coastal Ocean Data Analysis Data Product in North America (CODAP-NA). The 2021 release encompasses 3,391 oceanographic profiles from 61 research cruises spanning the North American continental shelves from Alaska to Mexico in the west and from Canada to the Caribbean in the east. It includes 14 key variables, including temperature, salinity, DO, DIC, TA, pH, carbonate ion, fCO2, silicate, phosphate, nitrate. </t>
   </si>
   <si>
     <t>Gridded subsurface</t>
@@ -1420,228 +1420,228 @@
     </row>
     <row r="6">
       <c r="A6" s="4">
-        <v>45961.95201907407</v>
+        <v>45962.03784055555</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="I6" s="11"/>
+      <c r="J6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="L6" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="M6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="5" t="s">
+      <c r="O6" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4">
-        <v>45961.909583877314</v>
+        <v>45961.95201907407</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="I7" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>66</v>
-      </c>
       <c r="J7" s="5" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>35</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="P7" s="9"/>
+        <v>80</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4">
-        <v>45961.91270586806</v>
+        <v>45961.909583877314</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="I8" s="12" t="s">
         <v>86</v>
       </c>
+      <c r="I8" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="J8" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>35</v>
       </c>
       <c r="L8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="N8" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N8" s="5" t="s">
+      <c r="O8" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="P8" s="9"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4">
+        <v>45961.91270586806</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="P8" s="9"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13">
+      <c r="D9" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="P9" s="9"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13">
         <v>45961.90485893519</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="K9" s="14" t="s">
+      <c r="B10" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="K10" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="M9" s="17"/>
-      <c r="N9" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="O9" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="P9" s="18"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4">
-        <v>45962.03784055555</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="L10" s="5" t="s">
+      <c r="L10" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="M10" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="N10" s="5" t="s">
+      <c r="M10" s="17"/>
+      <c r="N10" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="O10" s="5" t="s">
+      <c r="O10" s="14" t="s">
         <v>110</v>
       </c>
+      <c r="P10" s="18"/>
     </row>
     <row r="11">
       <c r="A11" s="4">
@@ -1669,7 +1669,7 @@
         <v>117</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>118</v>
@@ -1713,13 +1713,13 @@
         <v>127</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>118</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>128</v>
@@ -1736,7 +1736,7 @@
         <v>45962.680467199076</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>131</v>
@@ -1757,7 +1757,7 @@
         <v>136</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>137</v>
@@ -1780,7 +1780,7 @@
         <v>45962.690968483796</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>141</v>
@@ -1801,7 +1801,7 @@
         <v>146</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>137</v>
@@ -1849,7 +1849,7 @@
         <v>45</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>36</v>
@@ -1914,7 +1914,7 @@
         <v>45962.75772594908</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>167</v>
@@ -1935,7 +1935,7 @@
         <v>172</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>173</v>
@@ -1958,7 +1958,7 @@
         <v>45962.76769828703</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>177</v>
@@ -1979,7 +1979,7 @@
         <v>182</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>173</v>
@@ -2023,7 +2023,7 @@
         <v>192</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>118</v>
@@ -8466,19 +8466,19 @@
       </c>
       <c r="B7" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>Gridded surface</v>
+        <v>Data compilations</v>
       </c>
       <c r="C7" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>CSIR-ML6</v>
+        <v>CODAP-NA</v>
       </c>
       <c r="D7" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>Gregor et al. (2019)</v>
+        <v>Jiang et al. (2021)</v>
       </c>
       <c r="E7" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>https://gmd.copernicus.org/articles/12/5113/2019/gmd-12-5113-2019-f09-thumb.png</v>
+        <v>https://essd.copernicus.org/articles/13/2777/2021/essd-13-2777-2021-f01-web.png</v>
       </c>
       <c r="F7" s="23" t="str">
         <f t="shared" ref="F7:G7" si="20">if(ISBLANK($C7), "", F$1)</f>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="H7" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>Open ocean, Surface</v>
+        <v>Coastal, Water column</v>
       </c>
       <c r="I7" s="23" t="str">
         <f t="shared" ref="I7:J7" si="21">if(ISBLANK($C7), "", I$1)</f>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="K7" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>monthly</v>
+        <v>discrete</v>
       </c>
       <c r="L7" s="23" t="str">
         <f t="shared" ref="L7:M7" si="22">if(ISBLANK($C7), "", L$1)</f>
@@ -8514,7 +8514,7 @@
       </c>
       <c r="N7" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>1° x 1°</v>
+        <v/>
       </c>
       <c r="O7" s="23" t="str">
         <f t="shared" ref="O7:P7" si="23">if(ISBLANK($C7), "", O$1)</f>
@@ -8526,23 +8526,23 @@
       </c>
       <c r="Q7" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>1982 - 2020</v>
+        <v>2003 - 2018</v>
       </c>
       <c r="R7" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>Various ML methods produce different results when data is sparse, but all still achieving roughly the same uncertainty</v>
+        <v>Like GLODAPv2, but for the North American coastal ocean</v>
       </c>
       <c r="S7" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>Gregor et al. (2019)</v>
+        <v>Jiang et al. (2021)</v>
       </c>
       <c r="T7" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>https://doi.org/10.5194/gmd-12-5113-2019</v>
+        <v>https://doi.org/10.5194/essd-13-2777-2021</v>
       </c>
       <c r="U7" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>https://doi.org/10.25921/z682-mn47</v>
+        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0219960.html</v>
       </c>
       <c r="V7" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="W7" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>Provides monthly 1° × 1° estimates of surface pCO2 (Gregor et al., 2019a). The approach uses the conceptual two-step approach of clustering and performing regressions for each cluster as Landschützer et al. (2016). CSIR-ML6 investigates the efficacy of various machine learning (ML) methods in estimating surface pCO2, namely, feed-forward neural networks (FFNN), extremely randomized trees (ERT), gradient boosting machines (GBM), and support vector regression (SVR). It is found that the ensemble of all but the ERT method resulted in the best estimate, highlighting the fact that various ML methods do not produce the same outcome, particularly when data is sparse. Further, the variance between ensemble members can inform us about regions where uncertainty may be large due to methodological differences. Despite this, all methods achieve roughly the same uncertainty – a barrier, or wall beyond which the community has yet to overcome.</v>
+        <v>Jiang et al. (2021) synthesized two decades of discrete measurements of carbonate system variables, DO, and nutrient data from the North American continental shelves to generate the first version of Coastal Ocean Data Analysis Data Product in North America (CODAP-NA). The 2021 release encompasses 3,391 oceanographic profiles from 61 research cruises spanning the North American continental shelves from Alaska to Mexico in the west and from Canada to the Caribbean in the east. It includes 14 key variables, including temperature, salinity, DO, DIC, TA, pH, carbonate ion, fCO2, silicate, phosphate, nitrate. </v>
       </c>
       <c r="X7" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="Y7" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A7,FALSE)</f>
-        <v>Gregor, L., Lebehot, A. D., Kok, S., and Scheel Monteiro, P. M.: A comparative assessment of the uncertainties of global surface ocean CO2 estimates using a machine-learning ensemble (CSIR-ML6 version 2019a) – have we hit the wall?, Geosci. Model Dev., 12, 5113–5136, https://doi.org/10.5194/gmd-12-5113-2019, 2019.</v>
+        <v>Jiang, L.-Q., Feely, R. A., Wanninkhof, R., Greeley, D., Barbero, L., Alin, S., Carter, B. R., Pierrot, D., Featherstone, C., Hooper, J., Melrose, C., Monacci, N., Sharp, J. D., Shellito, S., Xu, Y.-Y., Kozyr, A., Byrne, R. H., Cai, W.-J., Cross, J., Johnson, G. C., Hales, B., Langdon, C., Mathis, J., Salisbury, J., and Townsend, D. W.: Coastal Ocean Data Analysis Product in North America (CODAP-NA) – an internally consistent data product for discrete inorganic carbon, oxygen, and nutrients on the North American ocean margins, Earth Syst. Sci. Data, 13, 2777–2799, https://doi.org/10.5194/essd-13-2777-2021, 2021.</v>
       </c>
     </row>
     <row r="8">
@@ -8572,15 +8572,15 @@
       </c>
       <c r="C8" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>OceanSODA-ETHZv1</v>
+        <v>CSIR-ML6</v>
       </c>
       <c r="D8" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>Gregor and Gruber (2021)</v>
+        <v>Gregor et al. (2019)</v>
       </c>
       <c r="E8" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>https://essd.copernicus.org/articles/13/777/2021/essd-13-777-2021-avatar-web.png</v>
+        <v>https://gmd.copernicus.org/articles/12/5113/2019/gmd-12-5113-2019-f09-thumb.png</v>
       </c>
       <c r="F8" s="23" t="str">
         <f t="shared" ref="F8:G8" si="24">if(ISBLANK($C8), "", F$1)</f>
@@ -8628,23 +8628,23 @@
       </c>
       <c r="Q8" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>1982 - 2022</v>
+        <v>1982 - 2020</v>
       </c>
       <c r="R8" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>Temporal trends of DIC, TA, pCO2, pH, Ωarag, and Ωcalc</v>
+        <v>Various ML methods produce different results when data is sparse, but all still achieving roughly the same uncertainty</v>
       </c>
       <c r="S8" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>Gregor and Gruber (2021)</v>
+        <v>Gregor et al. (2019)</v>
       </c>
       <c r="T8" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-13-777-2021</v>
+        <v>https://doi.org/10.5194/gmd-12-5113-2019</v>
       </c>
       <c r="U8" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>https://doi.org/10.25921/m5wx-ja34</v>
+        <v>https://doi.org/10.25921/z682-mn47</v>
       </c>
       <c r="V8" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="W8" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>A monthly gridded global surface ocean data product for multiple ocean carbonate system variables, including DIC, TA, pCO2, pH (total scale), Ωarag, and Ωcalc (Gregor and Gruber, 2020; Gregor and Gruber, 2021; Gregor and Gruber, 2023; Ma et al., 2023). This dataset is structured on a 1°×1° global surface ocean grid with monthly resolution from 1982–2022, facilitating research on OA over seasonal to decadal scales. The OceanSODA-ETHZ data product was created by extrapolating in time and space the surface ocean observations of fCO2 from SOCATv2022 (Bakker et al., 2016) and TA from GLODAPv2.2022 using the newly developed Geospatial Random Cluster Ensemble Regression (GRaCER) method (Gregor, 2021). TA and pCO2 were then used to calculate the remaining variables of the marine carbonate system with the PyCO2SYS software (Humphreys et al., 2022). Phosphate and silicate from WOA 2018 product were used (Boyer et al., 2018; Garcia et al., 2018a).</v>
+        <v>Provides monthly 1° × 1° estimates of surface pCO2 (Gregor et al., 2019a). The approach uses the conceptual two-step approach of clustering and performing regressions for each cluster as Landschützer et al. (2016). CSIR-ML6 investigates the efficacy of various machine learning (ML) methods in estimating surface pCO2, namely, feed-forward neural networks (FFNN), extremely randomized trees (ERT), gradient boosting machines (GBM), and support vector regression (SVR). It is found that the ensemble of all but the ERT method resulted in the best estimate, highlighting the fact that various ML methods do not produce the same outcome, particularly when data is sparse. Further, the variance between ensemble members can inform us about regions where uncertainty may be large due to methodological differences. Despite this, all methods achieve roughly the same uncertainty – a barrier, or wall beyond which the community has yet to overcome.</v>
       </c>
       <c r="X8" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="Y8" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A8,FALSE)</f>
-        <v>Gregor, L.; Gruber, N. OceanSODA-ETHZ: A Global Gridded Data Set of the Surface Ocean Carbonate System for Seasonal to Decadal Studies of Ocean Acidification. Earth System Science Data 2021, 13 (2), 777–808. https://doi.org/10.5194/essd-13-777-2021.</v>
+        <v>Gregor, L., Lebehot, A. D., Kok, S., and Scheel Monteiro, P. M.: A comparative assessment of the uncertainties of global surface ocean CO2 estimates using a machine-learning ensemble (CSIR-ML6 version 2019a) – have we hit the wall?, Geosci. Model Dev., 12, 5113–5136, https://doi.org/10.5194/gmd-12-5113-2019, 2019.</v>
       </c>
     </row>
     <row r="9">
@@ -8674,15 +8674,15 @@
       </c>
       <c r="C9" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>OceanSODA-ETHZv2</v>
+        <v>OceanSODA-ETHZv1</v>
       </c>
       <c r="D9" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Gregor et al. (2024)</v>
+        <v>Gregor and Gruber (2021)</v>
       </c>
       <c r="E9" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/7decc330-7468-429c-bae9-ac51b085be30/gbc21584-fig-0007-m.jpg</v>
+        <v>https://essd.copernicus.org/articles/13/777/2021/essd-13-777-2021-avatar-web.png</v>
       </c>
       <c r="F9" s="23" t="str">
         <f t="shared" ref="F9:G9" si="28">if(ISBLANK($C9), "", F$1)</f>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="K9" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>8-day</v>
+        <v>monthly</v>
       </c>
       <c r="L9" s="23" t="str">
         <f t="shared" ref="L9:M9" si="30">if(ISBLANK($C9), "", L$1)</f>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="N9" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>0.25° x 0.25°</v>
+        <v>1° x 1°</v>
       </c>
       <c r="O9" s="23" t="str">
         <f t="shared" ref="O9:P9" si="31">if(ISBLANK($C9), "", O$1)</f>
@@ -8730,23 +8730,23 @@
       </c>
       <c r="Q9" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>1982 - 2023</v>
+        <v>1982 - 2022</v>
       </c>
       <c r="R9" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Highlighting fine-scale and short-term variability of the ocean carbon sink</v>
+        <v>Temporal trends of DIC, TA, pCO2, pH, Ωarag, and Ωcalc</v>
       </c>
       <c r="S9" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Gregor et al. (2024)</v>
+        <v>Gregor and Gruber (2021)</v>
       </c>
       <c r="T9" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>https://doi.org/10.1029/2024GB008127</v>
+        <v>https://doi.org/10.5194/essd-13-777-2021</v>
       </c>
       <c r="U9" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>https://zenodo.org/records/11206366</v>
+        <v>https://doi.org/10.25921/m5wx-ja34</v>
       </c>
       <c r="V9" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="W9" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>A surface fCO₂ product with a 0.25° × 0.25° spatial resolution and an 8-day temporal resolution, providing estimates starting from 1982 (Gregor et al., 2024a; Gregor et al., 2024b). The high-resolution outputs are suitable for investigating the shorter- and finer-scale dynamics of surface fCO2. Despite sharing a name with its predecessor, OceanSODA-ETHZv2 does not provide TA estimates and employs a different methodology, as described in the following steps: 1) The atmospheric trend of CO2 is removed by subtracting marine boundary layer CO2 concentrations from SOCAT fCO2 producing a new target ∆*CO2 to reduce the biases at the start and end of the time-series. 2) An 8-day seasonal climatology of ∆*CO2 is estimated using Gradient Boosted Decision Trees (GBDT), which is later used as a predictor. 3) The non-seasonal thermal component is removed from ∆*CO2, resulting in a new target, ∆*CO2nonT. 4) The new target is estimated using a feed-forward neural network, with the GBDT as one of the forcing variables. 5) Steps 4 through to 1 are inverted to arrive at fCO2. 6) Air-sea CO2 fluxes are computed using ERA5 winds.</v>
+        <v>A monthly gridded global surface ocean data product for multiple ocean carbonate system variables, including DIC, TA, pCO2, pH (total scale), Ωarag, and Ωcalc (Gregor and Gruber, 2020; Gregor and Gruber, 2021; Gregor and Gruber, 2023; Ma et al., 2023). This dataset is structured on a 1°×1° global surface ocean grid with monthly resolution from 1982–2022, facilitating research on OA over seasonal to decadal scales. The OceanSODA-ETHZ data product was created by extrapolating in time and space the surface ocean observations of fCO2 from SOCATv2022 (Bakker et al., 2016) and TA from GLODAPv2.2022 using the newly developed Geospatial Random Cluster Ensemble Regression (GRaCER) method (Gregor, 2021). TA and pCO2 were then used to calculate the remaining variables of the marine carbonate system with the PyCO2SYS software (Humphreys et al., 2022). Phosphate and silicate from WOA 2018 product were used (Boyer et al., 2018; Garcia et al., 2018a).</v>
       </c>
       <c r="X9" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="Y9" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A9,FALSE)</f>
-        <v>Gregor, L.; Shutler, J.; Gruber, N. High-Resolution Variability of the Ocean Carbon Sink. Global Biogeochemical Cycles 2024, 38 (8), e2024GB008127. https://doi.org/10.1029/2024GB008127.</v>
+        <v>Gregor, L.; Gruber, N. OceanSODA-ETHZ: A Global Gridded Data Set of the Surface Ocean Carbonate System for Seasonal to Decadal Studies of Ocean Acidification. Earth System Science Data 2021, 13 (2), 777–808. https://doi.org/10.5194/essd-13-777-2021.</v>
       </c>
     </row>
     <row r="10">
@@ -8771,19 +8771,19 @@
       </c>
       <c r="B10" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Harmonized</v>
+        <v>Gridded surface</v>
       </c>
       <c r="C10" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>SeaFlux</v>
+        <v>OceanSODA-ETHZv2</v>
       </c>
       <c r="D10" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Fay and Gregor et al. (2021)</v>
+        <v>Gregor et al. (2024)</v>
       </c>
       <c r="E10" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>https://seaflux.readthedocs.io/en/latest/_static/seaflux_logo.png</v>
+        <v>https://agupubs.onlinelibrary.wiley.com/cms/asset/7decc330-7468-429c-bae9-ac51b085be30/gbc21584-fig-0007-m.jpg</v>
       </c>
       <c r="F10" s="23" t="str">
         <f t="shared" ref="F10:G10" si="32">if(ISBLANK($C10), "", F$1)</f>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="K10" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>monthly</v>
+        <v>8-day</v>
       </c>
       <c r="L10" s="23" t="str">
         <f t="shared" ref="L10:M10" si="34">if(ISBLANK($C10), "", L$1)</f>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="N10" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>1° x 1°</v>
+        <v>0.25° x 0.25°</v>
       </c>
       <c r="O10" s="23" t="str">
         <f t="shared" ref="O10:P10" si="35">if(ISBLANK($C10), "", O$1)</f>
@@ -8831,23 +8831,23 @@
       </c>
       <c r="Q10" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>1990 - 2022</v>
+        <v>1982 - 2023</v>
       </c>
       <c r="R10" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Careful consideration of flux calculation provides a resource and code to the community for independent flux calculations</v>
+        <v>Highlighting fine-scale and short-term variability of the ocean carbon sink</v>
       </c>
       <c r="S10" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Fay and Gregor et al. (2021)</v>
+        <v>Gregor et al. (2024)</v>
       </c>
       <c r="T10" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-2021-16</v>
+        <v>https://doi.org/10.1029/2024GB008127</v>
       </c>
       <c r="U10" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>https://zenodo.org/records/8280457</v>
+        <v>https://zenodo.org/records/11206366</v>
       </c>
       <c r="V10" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8855,7 +8855,7 @@
       </c>
       <c r="W10" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach (Gregor and Fay, 2021). This resource provides an ensemble of six pCO2 products with air-sea CO2 fluxes computed consistently. The six included products are: CMEMS-LSCEv1, CSIR-ML6, JENA-MLS, JMA-MLR, MPI-SOMFFN, and NIES-FNN. First, missing areas of pCO2 estimates (mostly high-latitude and marginal seas) are filled using a linear-regression approach, thus addressing differences in spatial coverage between the mapping products. Further, also accounts for methodological inconsistencies in flux calculations. Fluxes are calculated using three wind products (CCMPv2, ERA5, and JRA55) along with the application of a scaled gas exchange coefficient for each of the wind products. Through these steps, SeaFlux presents a product ensemble of interpolated global surface ocean pCO2 and air–sea carbon flux estimates for the years 1990–2019</v>
+        <v>A surface fCO₂ product with a 0.25° × 0.25° spatial resolution and an 8-day temporal resolution, providing estimates starting from 1982 (Gregor et al., 2024a; Gregor et al., 2024b). The high-resolution outputs are suitable for investigating the shorter- and finer-scale dynamics of surface fCO2. Despite sharing a name with its predecessor, OceanSODA-ETHZv2 does not provide TA estimates and employs a different methodology, as described in the following steps: 1) The atmospheric trend of CO2 is removed by subtracting marine boundary layer CO2 concentrations from SOCAT fCO2 producing a new target ∆*CO2 to reduce the biases at the start and end of the time-series. 2) An 8-day seasonal climatology of ∆*CO2 is estimated using Gradient Boosted Decision Trees (GBDT), which is later used as a predictor. 3) The non-seasonal thermal component is removed from ∆*CO2, resulting in a new target, ∆*CO2nonT. 4) The new target is estimated using a feed-forward neural network, with the GBDT as one of the forcing variables. 5) Steps 4 through to 1 are inverted to arrive at fCO2. 6) Air-sea CO2 fluxes are computed using ERA5 winds.</v>
       </c>
       <c r="X10" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="Y10" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A10,FALSE)</f>
-        <v>Fay, A. R., Gregor, L., Landschützer, P., McKinley, G. A., Gruber, N., Gehlen, M., Iida, Y., Laruelle, G. G., Rödenbeck, C., Roobaert, A., and Zeng, J.: SeaFlux: harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach, Earth Syst. Sci. Data, 13, 4693–4710, https://doi.org/10.5194/essd-13-4693-2021, 2021</v>
+        <v>Gregor, L.; Shutler, J.; Gruber, N. High-Resolution Variability of the Ocean Carbon Sink. Global Biogeochemical Cycles 2024, 38 (8), e2024GB008127. https://doi.org/10.1029/2024GB008127.</v>
       </c>
     </row>
     <row r="11">
@@ -8872,19 +8872,19 @@
       </c>
       <c r="B11" s="23" t="str">
         <f>HLOOKUP(B$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Data compilations</v>
+        <v>Harmonized</v>
       </c>
       <c r="C11" s="23" t="str">
         <f>HLOOKUP(C$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>CODAP-NA</v>
+        <v>SeaFlux</v>
       </c>
       <c r="D11" s="23" t="str">
         <f>HLOOKUP(D$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Jiang et al. (2021)</v>
+        <v>Fay and Gregor et al. (2021)</v>
       </c>
       <c r="E11" s="27" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>https://essd.copernicus.org/articles/13/2777/2021/essd-13-2777-2021-f01-web.png</v>
+        <v>https://seaflux.readthedocs.io/en/latest/_static/seaflux_logo.png</v>
       </c>
       <c r="F11" s="23" t="str">
         <f t="shared" ref="F11:G11" si="36">if(ISBLANK($C11), "", F$1)</f>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="H11" s="23" t="str">
         <f>HLOOKUP(H$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Coastal, Water column</v>
+        <v>Open ocean, Surface</v>
       </c>
       <c r="I11" s="23" t="str">
         <f t="shared" ref="I11:J11" si="37">if(ISBLANK($C11), "", I$1)</f>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="K11" s="23" t="str">
         <f>HLOOKUP(K$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>discrete</v>
+        <v>monthly</v>
       </c>
       <c r="L11" s="23" t="str">
         <f t="shared" ref="L11:M11" si="38">if(ISBLANK($C11), "", L$1)</f>
@@ -8920,7 +8920,7 @@
       </c>
       <c r="N11" s="28" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v/>
+        <v>1° x 1°</v>
       </c>
       <c r="O11" s="23" t="str">
         <f t="shared" ref="O11:P11" si="39">if(ISBLANK($C11), "", O$1)</f>
@@ -8932,23 +8932,23 @@
       </c>
       <c r="Q11" s="23" t="str">
         <f>HLOOKUP(Q$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>2003 - 2018</v>
+        <v>1990 - 2022</v>
       </c>
       <c r="R11" s="23" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Like GLODAPv2, but for the North American coastal ocean</v>
+        <v>Careful consideration of flux calculation provides a resource and code to the community for independent flux calculations</v>
       </c>
       <c r="S11" s="23" t="str">
         <f>HLOOKUP(S$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Jiang et al. (2021)</v>
+        <v>Fay and Gregor et al. (2021)</v>
       </c>
       <c r="T11" s="27" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>https://doi.org/10.5194/essd-13-2777-2021</v>
+        <v>https://doi.org/10.5194/essd-2021-16</v>
       </c>
       <c r="U11" s="27" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0219960.html</v>
+        <v>https://zenodo.org/records/8280457</v>
       </c>
       <c r="V11" s="23" t="str">
         <f t="shared" si="10"/>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="W11" s="23" t="str">
         <f>HLOOKUP(W$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Jiang et al. (2021) synthesized two decades of discrete measurements of carbonate system variables, DO, and nutrient data from the North American continental shelves to generate the first version of Coastal Ocean Data Analysis Data Product in North America (CODAP-NA). The 2021 release encompasses 3,391 oceanographic profiles from 61 research cruises spanning the North American continental shelves from Alaska to Mexico in the west and from Canada to the Caribbean in the east. It includes 14 key variables, including temperature, salinity, DO, DIC, TA, pH, carbonate ion, fCO2, silicate, phosphate, nitrate. </v>
+        <v>Harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach (Gregor and Fay, 2021). This resource provides an ensemble of six pCO2 products with air-sea CO2 fluxes computed consistently. The six included products are: CMEMS-LSCEv1, CSIR-ML6, JENA-MLS, JMA-MLR, MPI-SOMFFN, and NIES-FNN. First, missing areas of pCO2 estimates (mostly high-latitude and marginal seas) are filled using a linear-regression approach, thus addressing differences in spatial coverage between the mapping products. Further, also accounts for methodological inconsistencies in flux calculations. Fluxes are calculated using three wind products (CCMPv2, ERA5, and JRA55) along with the application of a scaled gas exchange coefficient for each of the wind products. Through these steps, SeaFlux presents a product ensemble of interpolated global surface ocean pCO2 and air–sea carbon flux estimates for the years 1990–2019</v>
       </c>
       <c r="X11" s="23" t="str">
         <f t="shared" si="11"/>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="Y11" s="23" t="str">
         <f>HLOOKUP(Y$1,google_form!$1:$138,$A11,FALSE)</f>
-        <v>Jiang, L.-Q., Feely, R. A., Wanninkhof, R., Greeley, D., Barbero, L., Alin, S., Carter, B. R., Pierrot, D., Featherstone, C., Hooper, J., Melrose, C., Monacci, N., Sharp, J. D., Shellito, S., Xu, Y.-Y., Kozyr, A., Byrne, R. H., Cai, W.-J., Cross, J., Johnson, G. C., Hales, B., Langdon, C., Mathis, J., Salisbury, J., and Townsend, D. W.: Coastal Ocean Data Analysis Product in North America (CODAP-NA) – an internally consistent data product for discrete inorganic carbon, oxygen, and nutrients on the North American ocean margins, Earth Syst. Sci. Data, 13, 2777–2799, https://doi.org/10.5194/essd-13-2777-2021, 2021.</v>
+        <v>Fay, A. R., Gregor, L., Landschützer, P., McKinley, G. A., Gruber, N., Gehlen, M., Iida, Y., Laruelle, G. G., Rödenbeck, C., Roobaert, A., and Zeng, J.: SeaFlux: harmonization of air–sea CO2 fluxes from surface pCO2 data products using a standardized approach, Earth Syst. Sci. Data, 13, 4693–4710, https://doi.org/10.5194/essd-13-4693-2021, 2021</v>
       </c>
     </row>
     <row r="12">

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -3891,7 +3891,7 @@
       </c>
       <c r="Q17" s="11">
         <f t="shared" si="1"/>
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="R17" s="11">
         <f t="shared" si="2"/>
@@ -4603,9 +4603,9 @@
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="R30" s="11">
+      <c r="R30" s="11" t="str">
         <f t="shared" si="2"/>
-        <v>200</v>
+        <v>#ERROR!</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="Q50" s="11">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="R50" s="11">
         <f t="shared" si="2"/>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="Q57" s="11">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="R57" s="11">
         <f t="shared" si="2"/>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="Q66" s="11">
         <f t="shared" si="1"/>
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="R66" s="11">
         <f t="shared" si="2"/>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -3124,7 +3124,7 @@
       </c>
       <c r="Q3" s="11">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="R3" s="11">
         <f t="shared" si="2"/>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="Q17" s="11">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="R17" s="11">
         <f t="shared" si="2"/>
@@ -4603,9 +4603,9 @@
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="R30" s="11" t="str">
+      <c r="R30" s="11">
         <f t="shared" si="2"/>
-        <v>#ERROR!</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="Q31" s="11">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="R31" s="11">
         <f t="shared" si="2"/>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="Q66" s="11">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="R66" s="11">
         <f t="shared" si="2"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="Q76" s="11">
         <f t="shared" si="1"/>
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="R76" s="11">
         <f t="shared" si="2"/>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -4656,7 +4656,7 @@
       </c>
       <c r="Q31" s="11">
         <f t="shared" si="1"/>
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="R31" s="11">
         <f t="shared" si="2"/>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="Q32" s="11">
         <f t="shared" si="1"/>
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="R32" s="11">
         <f t="shared" si="2"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="Q76" s="11">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="R76" s="11">
         <f t="shared" si="2"/>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -3836,7 +3836,7 @@
       </c>
       <c r="Q16" s="11">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="R16" s="11">
         <f t="shared" si="2"/>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="Q31" s="11">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="R31" s="11">
         <f t="shared" si="2"/>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="Q52" s="11">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="R52" s="11">
         <f t="shared" si="2"/>

--- a/docs/data.xlsx
+++ b/docs/data.xlsx
@@ -2578,11 +2578,11 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -2605,11 +2605,11 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -3071,7 +3071,7 @@
       <c r="P1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="8" t="s">
         <v>34</v>
       </c>
       <c r="R1" s="9" t="s">
@@ -3104,7 +3104,7 @@
       <c r="I2" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="16"/>
+      <c r="J2" s="17"/>
       <c r="K2" s="12" t="s">
         <v>43</v>
       </c>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Q18" s="18">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="R18" s="18">
         <f t="shared" si="2"/>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="Q19" s="18">
         <f t="shared" si="1"/>
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="R19" s="18">
         <f t="shared" si="2"/>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Q33" s="18">
         <f t="shared" si="1"/>
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="R33" s="18">
         <f t="shared" si="2"/>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="Q35" s="18">
         <f t="shared" si="1"/>
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="R35" s="18">
         <f t="shared" si="2"/>
@@ -5373,9 +5373,9 @@
         <f t="shared" si="1"/>
         <v>#ERROR!</v>
       </c>
-      <c r="R43" s="18">
+      <c r="R43" s="18" t="str">
         <f t="shared" si="2"/>
-        <v>200</v>
+        <v>#ERROR!</v>
       </c>
     </row>
     <row r="44" ht="22.5" customHeight="1">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="Q52" s="18">
         <f t="shared" si="1"/>
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="R52" s="18">
         <f t="shared" si="2"/>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="Q55" s="18">
         <f t="shared" si="1"/>
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="R55" s="18">
         <f t="shared" si="2"/>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="Q56" s="18">
         <f t="shared" si="1"/>
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="R56" s="18">
         <f t="shared" si="2"/>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="Q59" s="18">
         <f t="shared" si="1"/>
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="R59" s="18">
         <f t="shared" si="2"/>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="Q73" s="18">
         <f t="shared" si="1"/>
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="R73" s="18">
         <f t="shared" si="2"/>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="Q78" s="18">
         <f t="shared" si="1"/>
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="R78" s="18">
         <f t="shared" si="2"/>
@@ -7802,7 +7802,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A3,FALSE)</f>
         <v>Bakker et al. (2016)</v>
       </c>
-      <c r="E3" s="8" t="str">
+      <c r="E3" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A3,FALSE)</f>
         <v>https://socat.info/wp-content/uploads/2017/06/cropped-socat_cat.png</v>
       </c>
@@ -7838,7 +7838,7 @@
         <f t="shared" si="3"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N3" s="17" t="str">
+      <c r="N3" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A3,FALSE)</f>
         <v/>
       </c>
@@ -7862,11 +7862,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A3,FALSE)</f>
         <v>Bakker et al. (2016)</v>
       </c>
-      <c r="T3" s="8" t="str">
+      <c r="T3" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A3,FALSE)</f>
         <v>https://doi.org/10.5194/essd-8-383-2016</v>
       </c>
-      <c r="U3" s="8" t="str">
+      <c r="U3" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A3,FALSE)</f>
         <v>https://socat.info/</v>
       </c>
@@ -7904,7 +7904,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A4,FALSE)</f>
         <v>Takahashi et a. (2009)</v>
       </c>
-      <c r="E4" s="8" t="str">
+      <c r="E4" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A4,FALSE)</f>
         <v>https://www.ncei.noaa.gov/access/ocean-carbon-acidification-data-system/oceans/LDEO_Underway_Database/LDEOv2019_map.jpg</v>
       </c>
@@ -7940,7 +7940,7 @@
         <f t="shared" si="8"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N4" s="17" t="str">
+      <c r="N4" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A4,FALSE)</f>
         <v/>
       </c>
@@ -7964,11 +7964,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A4,FALSE)</f>
         <v>Takahashi et a. (2009)</v>
       </c>
-      <c r="T4" s="8" t="str">
+      <c r="T4" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A4,FALSE)</f>
         <v>https://doi.org/10.1016/j.dsr2.2008.12.009</v>
       </c>
-      <c r="U4" s="8" t="str">
+      <c r="U4" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A4,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0160492.html</v>
       </c>
@@ -8006,7 +8006,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A5,FALSE)</f>
         <v>Lauvset et al. (2024)</v>
       </c>
-      <c r="E5" s="8" t="str">
+      <c r="E5" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A5,FALSE)</f>
         <v>https://glodap.info/wp-content/uploads/2017/09/cropped-glodap_logo_trans.png</v>
       </c>
@@ -8042,7 +8042,7 @@
         <f t="shared" si="14"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N5" s="17" t="str">
+      <c r="N5" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A5,FALSE)</f>
         <v/>
       </c>
@@ -8066,11 +8066,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A5,FALSE)</f>
         <v>Lauvset et al. (2024)</v>
       </c>
-      <c r="T5" s="8" t="str">
+      <c r="T5" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A5,FALSE)</f>
         <v>https://doi.org/10.5194/essd-16-2047-2024</v>
       </c>
-      <c r="U5" s="8" t="str">
+      <c r="U5" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A5,FALSE)</f>
         <v>https://glodap.info/</v>
       </c>
@@ -8108,7 +8108,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A6,FALSE)</f>
         <v>Swift et al. (2026)</v>
       </c>
-      <c r="E6" s="8" t="str">
+      <c r="E6" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A6,FALSE)</f>
         <v>https://i.ibb.co/Q7YZfHK2/Swift-Vertical-Section-Map.png</v>
       </c>
@@ -8144,7 +8144,7 @@
         <f t="shared" si="18"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N6" s="17" t="str">
+      <c r="N6" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A6,FALSE)</f>
         <v/>
       </c>
@@ -8172,7 +8172,7 @@
         <f>HLOOKUP(T$1,google_form!$1:$198,$A6,FALSE)</f>
         <v>n/a</v>
       </c>
-      <c r="U6" s="8" t="str">
+      <c r="U6" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A6,FALSE)</f>
         <v>https://joa.ucsd.edu/Data_homepage</v>
       </c>
@@ -8210,7 +8210,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A7,FALSE)</f>
         <v>Mishonov et al. (2024)</v>
       </c>
-      <c r="E7" s="8" t="str">
+      <c r="E7" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A7,FALSE)</f>
         <v>https://www.ncei.noaa.gov/sites/g/files/anmtlf171/files/inline-images/World%20Ocean%20Atlas%202023%20Climatology%2C%20Decade%202015-2022.png</v>
       </c>
@@ -8246,7 +8246,7 @@
         <f t="shared" si="22"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N7" s="17" t="str">
+      <c r="N7" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A7,FALSE)</f>
         <v/>
       </c>
@@ -8270,11 +8270,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A7,FALSE)</f>
         <v>Mishonov et al. (2024)</v>
       </c>
-      <c r="T7" s="8" t="str">
+      <c r="T7" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A7,FALSE)</f>
         <v>https://doi.org/10.25923/z885-h264</v>
       </c>
-      <c r="U7" s="8" t="str">
+      <c r="U7" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A7,FALSE)</f>
         <v>https://www.ncei.noaa.gov/products/world-ocean-database</v>
       </c>
@@ -8312,7 +8312,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A8,FALSE)</f>
         <v>Mamnun et al. (2026)</v>
       </c>
-      <c r="E8" s="8" t="str">
+      <c r="E8" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A8,FALSE)</f>
         <v>https://upload.wikimedia.org/wikipedia/commons/1/14/No_Image_Available.jpg</v>
       </c>
@@ -8348,7 +8348,7 @@
         <f t="shared" si="26"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N8" s="17" t="str">
+      <c r="N8" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A8,FALSE)</f>
         <v/>
       </c>
@@ -8372,11 +8372,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A8,FALSE)</f>
         <v>Mamnun et al. (2026)</v>
       </c>
-      <c r="T8" s="8" t="str">
+      <c r="T8" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A8,FALSE)</f>
         <v>https://doi.org/10.5194/essd-2026-691</v>
       </c>
-      <c r="U8" s="8" t="str">
+      <c r="U8" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A8,FALSE)</f>
         <v>https://doi.org/10.5281/zenodo.18674659</v>
       </c>
@@ -8414,7 +8414,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A9,FALSE)</f>
         <v>Metzl et al (2024)</v>
       </c>
-      <c r="E9" s="8" t="str">
+      <c r="E9" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A9,FALSE)</f>
         <v>https://www.seanoe.org/data/00911/102337/illustration.gif</v>
       </c>
@@ -8450,7 +8450,7 @@
         <f t="shared" si="30"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N9" s="17" t="str">
+      <c r="N9" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A9,FALSE)</f>
         <v/>
       </c>
@@ -8474,11 +8474,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A9,FALSE)</f>
         <v>Metzl et al (2024)</v>
       </c>
-      <c r="T9" s="8" t="str">
+      <c r="T9" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A9,FALSE)</f>
         <v>https://doi.org/10.5194/essd-16-89-2024</v>
       </c>
-      <c r="U9" s="8" t="str">
+      <c r="U9" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A9,FALSE)</f>
         <v>https://doi.org/10.17882/102337</v>
       </c>
@@ -8515,7 +8515,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A10,FALSE)</f>
         <v>Jiang et al. (2021)</v>
       </c>
-      <c r="E10" s="8" t="str">
+      <c r="E10" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A10,FALSE)</f>
         <v>https://essd.copernicus.org/articles/13/2777/2021/essd-13-2777-2021-f01-web.png</v>
       </c>
@@ -8551,7 +8551,7 @@
         <f t="shared" si="34"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N10" s="17" t="str">
+      <c r="N10" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A10,FALSE)</f>
         <v/>
       </c>
@@ -8575,11 +8575,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A10,FALSE)</f>
         <v>Jiang et al. (2021)</v>
       </c>
-      <c r="T10" s="8" t="str">
+      <c r="T10" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A10,FALSE)</f>
         <v>https://doi.org/10.5194/essd-13-2777-2021</v>
       </c>
-      <c r="U10" s="8" t="str">
+      <c r="U10" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A10,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0219960.html</v>
       </c>
@@ -8616,7 +8616,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A11,FALSE)</f>
         <v>Álvarez et al. (2026)</v>
       </c>
-      <c r="E11" s="8" t="str">
+      <c r="E11" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A11,FALSE)</f>
         <v>https://essd.copernicus.org/articles/18/4915/2026/essd-18-4915-2026-f01-web.png</v>
       </c>
@@ -8652,7 +8652,7 @@
         <f t="shared" si="38"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N11" s="17" t="str">
+      <c r="N11" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A11,FALSE)</f>
         <v/>
       </c>
@@ -8676,11 +8676,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A11,FALSE)</f>
         <v>Álvarez et al. (2026)</v>
       </c>
-      <c r="T11" s="8" t="str">
+      <c r="T11" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A11,FALSE)</f>
         <v>https://doi.org/10.5194/essd-18-4915-2026</v>
       </c>
-      <c r="U11" s="8" t="str">
+      <c r="U11" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A11,FALSE)</f>
         <v>https://www.ncei.noaa.gov/access/ocean-carbon-acidification-data-system/oceans/CARIMED/</v>
       </c>
@@ -8718,7 +8718,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A12,FALSE)</f>
         <v>Gibb et al. (2023)</v>
       </c>
-      <c r="E12" s="8" t="str">
+      <c r="E12" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A12,FALSE)</f>
         <v>https://essd.copernicus.org/articles/15/4127/2023/essd-15-4127-2023-avatar-web.png</v>
       </c>
@@ -8754,7 +8754,7 @@
         <f t="shared" si="42"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N12" s="17" t="str">
+      <c r="N12" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A12,FALSE)</f>
         <v/>
       </c>
@@ -8778,11 +8778,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A12,FALSE)</f>
         <v>Gibb et al. (2023)</v>
       </c>
-      <c r="T12" s="8" t="str">
+      <c r="T12" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A12,FALSE)</f>
         <v>https://doi.org/10.5194/essd-15-4127-2023</v>
       </c>
-      <c r="U12" s="8" t="str">
+      <c r="U12" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A12,FALSE)</f>
         <v>https://doi.org/10.20383/102.0673</v>
       </c>
@@ -8819,7 +8819,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A13,FALSE)</f>
         <v>Kennedy et al., 2023</v>
       </c>
-      <c r="E13" s="8" t="str">
+      <c r="E13" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A13,FALSE)</f>
         <v>https://i.ibb.co/XrpxsXPX/data-locs-composite-bs.png</v>
       </c>
@@ -8855,7 +8855,7 @@
         <f t="shared" si="46"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N13" s="17" t="str">
+      <c r="N13" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A13,FALSE)</f>
         <v/>
       </c>
@@ -8879,11 +8879,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A13,FALSE)</f>
         <v>Kennedy et al., 2023</v>
       </c>
-      <c r="T13" s="8" t="str">
+      <c r="T13" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A13,FALSE)</f>
         <v>https://doi.org/10.25921/2vve-fh39</v>
       </c>
-      <c r="U13" s="8" t="str">
+      <c r="U13" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A13,FALSE)</f>
         <v>https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:0277984</v>
       </c>
@@ -8920,7 +8920,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A14,FALSE)</f>
         <v>Padin et al. (2020)</v>
       </c>
-      <c r="E14" s="8" t="str">
+      <c r="E14" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A14,FALSE)</f>
         <v>https://essd.copernicus.org/articles/12/2647/2020/essd-12-2647-2020-f01-web.png</v>
       </c>
@@ -8956,7 +8956,7 @@
         <f t="shared" si="50"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N14" s="17" t="str">
+      <c r="N14" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A14,FALSE)</f>
         <v/>
       </c>
@@ -8980,11 +8980,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A14,FALSE)</f>
         <v>Padin et al. (2020)</v>
       </c>
-      <c r="T14" s="8" t="str">
+      <c r="T14" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A14,FALSE)</f>
         <v>https://doi.org/10.5194/essd-12-2647-2020</v>
       </c>
-      <c r="U14" s="8" t="str">
+      <c r="U14" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A14,FALSE)</f>
         <v>https://doi.org/10.20350/digitalCSIC/12498</v>
       </c>
@@ -9021,7 +9021,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A15,FALSE)</f>
         <v>Monacci et al. (2024)</v>
       </c>
-      <c r="E15" s="8" t="str">
+      <c r="E15" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A15,FALSE)</f>
         <v>https://essd.copernicus.org/articles/16/647/2024/essd-16-647-2024-avatar-web.png</v>
       </c>
@@ -9057,7 +9057,7 @@
         <f t="shared" si="54"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N15" s="17" t="str">
+      <c r="N15" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A15,FALSE)</f>
         <v/>
       </c>
@@ -9081,11 +9081,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A15,FALSE)</f>
         <v>Monacci et al. (2024)</v>
       </c>
-      <c r="T15" s="8" t="str">
+      <c r="T15" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A15,FALSE)</f>
         <v>https://doi.org/10.5194/essd-16-647-2024</v>
       </c>
-      <c r="U15" s="8" t="str">
+      <c r="U15" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A15,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0277034.html</v>
       </c>
@@ -9122,7 +9122,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A16,FALSE)</f>
         <v>Palacio-Castro et al. (2023)</v>
       </c>
-      <c r="E16" s="8" t="str">
+      <c r="E16" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A16,FALSE)</f>
         <v>https://i.ibb.co/yc5J25Q6/gbc21508-fig-0001-m.jpg</v>
       </c>
@@ -9158,7 +9158,7 @@
         <f t="shared" si="58"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N16" s="17" t="str">
+      <c r="N16" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A16,FALSE)</f>
         <v/>
       </c>
@@ -9182,11 +9182,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A16,FALSE)</f>
         <v>Palacio-Castro et al. (2023)</v>
       </c>
-      <c r="T16" s="8" t="str">
+      <c r="T16" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A16,FALSE)</f>
         <v>https://doi.org/10.1029/2023GB007789</v>
       </c>
-      <c r="U16" s="8" t="str">
+      <c r="U16" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A16,FALSE)</f>
         <v>https://www.ncei.noaa.gov/access/metadata/landing-page/bin/iso?id=gov.noaa.nodc:NCRMP-CO3-Atlantic</v>
       </c>
@@ -9223,7 +9223,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A17,FALSE)</f>
         <v>Alin et al. (2025a)</v>
       </c>
-      <c r="E17" s="8" t="str">
+      <c r="E17" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A17,FALSE)</f>
         <v>https://essd.copernicus.org/articles/16/837/2024/essd-16-837-2024-avatar-web.png</v>
       </c>
@@ -9259,7 +9259,7 @@
         <f t="shared" si="62"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N17" s="17" t="str">
+      <c r="N17" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A17,FALSE)</f>
         <v/>
       </c>
@@ -9283,11 +9283,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A17,FALSE)</f>
         <v>Alin et al. (2025a)</v>
       </c>
-      <c r="T17" s="8" t="str">
+      <c r="T17" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A17,FALSE)</f>
         <v>https://doi.org/10.5194/essd-16-837-2024</v>
       </c>
-      <c r="U17" s="8" t="str">
+      <c r="U17" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A17,FALSE)</f>
         <v>https://www.ncei.noaa.gov/access/ocean-carbon-acidification-data-system/oceans/SalishCruise_DataPackage.html</v>
       </c>
@@ -9324,7 +9324,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A18,FALSE)</f>
         <v>Alin et al. (2025b)</v>
       </c>
-      <c r="E18" s="8" t="str">
+      <c r="E18" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A18,FALSE)</f>
         <v>https://bg.copernicus.org/articles/21/1639/2024/bg-21-1639-2024-avatar-web.png</v>
       </c>
@@ -9360,7 +9360,7 @@
         <f t="shared" si="66"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N18" s="17" t="str">
+      <c r="N18" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A18,FALSE)</f>
         <v/>
       </c>
@@ -9384,11 +9384,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A18,FALSE)</f>
         <v>Alin et al. (2025b)</v>
       </c>
-      <c r="T18" s="8" t="str">
+      <c r="T18" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A18,FALSE)</f>
         <v>https://doi.org/10.5194/bg-21-1639-2024</v>
       </c>
-      <c r="U18" s="8" t="str">
+      <c r="U18" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A18,FALSE)</f>
         <v>https://www.ncei.noaa.gov/access/ocean-carbon-acidification-data-system/oceans/SalishCruises_DataProduct.html</v>
       </c>
@@ -9425,7 +9425,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A19,FALSE)</f>
         <v>Franco et al., (2021)</v>
       </c>
-      <c r="E19" s="8" t="str">
+      <c r="E19" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A19,FALSE)</f>
         <v>https://i.ibb.co/4wb5JLp1/fig1-map-francoetal2021.png</v>
       </c>
@@ -9461,7 +9461,7 @@
         <f t="shared" si="70"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N19" s="17" t="str">
+      <c r="N19" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A19,FALSE)</f>
         <v/>
       </c>
@@ -9485,11 +9485,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A19,FALSE)</f>
         <v>Franco et al., (2021)</v>
       </c>
-      <c r="T19" s="8" t="str">
+      <c r="T19" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A19,FALSE)</f>
         <v>https://doi.org/10.1029/2020GB006829</v>
       </c>
-      <c r="U19" s="8" t="str">
+      <c r="U19" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A19,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0234342.html</v>
       </c>
@@ -9526,7 +9526,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A20,FALSE)</f>
         <v>Terhaar et al. (2020)</v>
       </c>
-      <c r="E20" s="8" t="str">
+      <c r="E20" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A20,FALSE)</f>
         <v>https://www.seanoe.org/data/00927/103920/illustration.gif</v>
       </c>
@@ -9562,7 +9562,7 @@
         <f t="shared" si="74"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N20" s="17" t="str">
+      <c r="N20" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A20,FALSE)</f>
         <v/>
       </c>
@@ -9586,11 +9586,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A20,FALSE)</f>
         <v>Terhaar et al. (2020)</v>
       </c>
-      <c r="T20" s="8" t="str">
+      <c r="T20" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A20,FALSE)</f>
         <v>https://doi.org/10.1029/2020jc016124</v>
       </c>
-      <c r="U20" s="8" t="str">
+      <c r="U20" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A20,FALSE)</f>
         <v>https://www.seanoe.org/data/00927/103920/</v>
       </c>
@@ -9627,7 +9627,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A21,FALSE)</f>
         <v>Bates and Johnson (2023)</v>
       </c>
-      <c r="E21" s="8" t="str">
+      <c r="E21" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A21,FALSE)</f>
         <v>https://www.frontiersin.org/files/Articles/1289931/fmars-10-1289931-HTML-r1/image_m/fmars-10-1289931-g001.jpg</v>
       </c>
@@ -9663,7 +9663,7 @@
         <f t="shared" si="78"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N21" s="17" t="str">
+      <c r="N21" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A21,FALSE)</f>
         <v/>
       </c>
@@ -9687,11 +9687,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A21,FALSE)</f>
         <v>Bates and Johnson (2023)</v>
       </c>
-      <c r="T21" s="8" t="str">
+      <c r="T21" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A21,FALSE)</f>
         <v>https://doi.org/10.3389/fmars.2023.1289931</v>
       </c>
-      <c r="U21" s="8" t="str">
+      <c r="U21" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A21,FALSE)</f>
         <v>https://www.bco-dmo.org/project/2124</v>
       </c>
@@ -9728,7 +9728,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A22,FALSE)</f>
         <v>Dore et al. (2009)</v>
       </c>
-      <c r="E22" s="8" t="str">
+      <c r="E22" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A22,FALSE)</f>
         <v>https://i.ibb.co/B2vPqjyw/HOTlogo.jpg</v>
       </c>
@@ -9764,7 +9764,7 @@
         <f t="shared" si="82"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N22" s="17" t="str">
+      <c r="N22" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A22,FALSE)</f>
         <v/>
       </c>
@@ -9788,11 +9788,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A22,FALSE)</f>
         <v>Dore et al. (2009)</v>
       </c>
-      <c r="T22" s="8" t="str">
+      <c r="T22" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A22,FALSE)</f>
         <v>https://doi.org/10.1073/pnas.0906044106</v>
       </c>
-      <c r="U22" s="8" t="str">
+      <c r="U22" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A22,FALSE)</f>
         <v>https://doi.org/10.1575/1912/bco-dmo.3773.1</v>
       </c>
@@ -9829,7 +9829,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A23,FALSE)</f>
         <v>González-Dávila and Santana-Casiano (2023)</v>
       </c>
-      <c r="E23" s="8" t="str">
+      <c r="E23" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A23,FALSE)</f>
         <v>https://www.frontiersin.org/files/Articles/1236214/fmars-10-1236214-HTML-r1/image_m/fmars-10-1236214-g001.jpg</v>
       </c>
@@ -9865,7 +9865,7 @@
         <f t="shared" si="86"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N23" s="17" t="str">
+      <c r="N23" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A23,FALSE)</f>
         <v/>
       </c>
@@ -9889,11 +9889,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A23,FALSE)</f>
         <v>González-Dávila and Santana-Casiano (2023)</v>
       </c>
-      <c r="T23" s="8" t="str">
+      <c r="T23" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A23,FALSE)</f>
         <v>https://doi.org/10.3389/fmars.2023.1236214</v>
       </c>
-      <c r="U23" s="8" t="str">
+      <c r="U23" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A23,FALSE)</f>
         <v>https://doi.org/10.1594/PANGAEA.959856</v>
       </c>
@@ -9930,7 +9930,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A24,FALSE)</f>
         <v>Kapsenberg et al. (2017)</v>
       </c>
-      <c r="E24" s="8" t="str">
+      <c r="E24" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A24,FALSE)</f>
         <v>https://i.ibb.co/8gK4B2BP/Point-B.png</v>
       </c>
@@ -9966,7 +9966,7 @@
         <f t="shared" si="90"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N24" s="17" t="str">
+      <c r="N24" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A24,FALSE)</f>
         <v/>
       </c>
@@ -9990,11 +9990,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A24,FALSE)</f>
         <v>Kapsenberg et al. (2017)</v>
       </c>
-      <c r="T24" s="8" t="str">
+      <c r="T24" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A24,FALSE)</f>
         <v>https://doi.org/10.5194/os-13-411-2017</v>
       </c>
-      <c r="U24" s="8" t="str">
+      <c r="U24" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A24,FALSE)</f>
         <v>https://doi.org/10.1594/PANGAEA.727120 </v>
       </c>
@@ -10031,7 +10031,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A25,FALSE)</f>
         <v>Gattuso et al. (2023)</v>
       </c>
-      <c r="E25" s="8" t="str">
+      <c r="E25" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A25,FALSE)</f>
         <v>https://essd.copernicus.org/articles/15/2809/2023/essd-15-2809-2023-avatar-web.png</v>
       </c>
@@ -10067,7 +10067,7 @@
         <f t="shared" si="94"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N25" s="17" t="str">
+      <c r="N25" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A25,FALSE)</f>
         <v/>
       </c>
@@ -10091,11 +10091,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A25,FALSE)</f>
         <v>Gattuso et al. (2023)</v>
       </c>
-      <c r="T25" s="8" t="str">
+      <c r="T25" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A25,FALSE)</f>
         <v>https://doi.org/10.5194/essd-15-2809-2023</v>
       </c>
-      <c r="U25" s="8" t="str">
+      <c r="U25" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A25,FALSE)</f>
         <v>https://doi.org//10.1594/PANGAEA.957028</v>
       </c>
@@ -10132,7 +10132,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A26,FALSE)</f>
         <v>Lange et al., (2024)</v>
       </c>
-      <c r="E26" s="8" t="str">
+      <c r="E26" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A26,FALSE)</f>
         <v>https://i.ibb.co/qYM6NNbv/Logo.png</v>
       </c>
@@ -10168,7 +10168,7 @@
         <f t="shared" si="98"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N26" s="17" t="str">
+      <c r="N26" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A26,FALSE)</f>
         <v/>
       </c>
@@ -10192,11 +10192,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A26,FALSE)</f>
         <v>Lange et al., (2024)</v>
       </c>
-      <c r="T26" s="8" t="str">
+      <c r="T26" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A26,FALSE)</f>
         <v>https://doi.org/10.5194/essd-16-1901-2024</v>
       </c>
-      <c r="U26" s="8" t="str">
+      <c r="U26" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A26,FALSE)</f>
         <v>https://www.bco-dmo.org/dataset/896862</v>
       </c>
@@ -10233,7 +10233,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A27,FALSE)</f>
         <v>Sutton et al. (2019)</v>
       </c>
-      <c r="E27" s="8" t="str">
+      <c r="E27" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A27,FALSE)</f>
         <v>https://essd.copernicus.org/articles/11/421/2019/essd-11-421-2019-avatar-web.png</v>
       </c>
@@ -10269,7 +10269,7 @@
         <f t="shared" si="102"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N27" s="17" t="str">
+      <c r="N27" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A27,FALSE)</f>
         <v/>
       </c>
@@ -10293,11 +10293,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A27,FALSE)</f>
         <v>Sutton et al. (2019)</v>
       </c>
-      <c r="T27" s="8" t="str">
+      <c r="T27" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A27,FALSE)</f>
         <v>https://doi.org/10.5194/essd-11-421-2019</v>
       </c>
-      <c r="U27" s="8" t="str">
+      <c r="U27" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A27,FALSE)</f>
         <v>https://www.ncei.noaa.gov/access/ocean-carbon-acidification-data-system/oceans/Moorings/ndp097.html</v>
       </c>
@@ -10334,7 +10334,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A28,FALSE)</f>
         <v>Petton et al. (2022)</v>
       </c>
-      <c r="E28" s="8" t="str">
+      <c r="E28" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A28,FALSE)</f>
         <v>https://i.ibb.co/67Qd9xr3/Fig6-Suivi-Cocori-CO2-p-H.png</v>
       </c>
@@ -10370,7 +10370,7 @@
         <f t="shared" si="106"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N28" s="17" t="str">
+      <c r="N28" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A28,FALSE)</f>
         <v/>
       </c>
@@ -10394,11 +10394,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A28,FALSE)</f>
         <v>Petton et al. (2022)</v>
       </c>
-      <c r="T28" s="8" t="str">
+      <c r="T28" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A28,FALSE)</f>
         <v>https://doi.org/10.5194/essd-16-1667-2024</v>
       </c>
-      <c r="U28" s="8" t="str">
+      <c r="U28" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A28,FALSE)</f>
         <v>https://doi.org/10.17882/96982</v>
       </c>
@@ -10435,7 +10435,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A29,FALSE)</f>
         <v>Fay et al. (2024)</v>
       </c>
-      <c r="E29" s="8" t="str">
+      <c r="E29" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A29,FALSE)</f>
         <v>https://essd.copernicus.org/articles/16/2123/2024/essd-16-2123-2024-avatar-web.png</v>
       </c>
@@ -10471,7 +10471,7 @@
         <f t="shared" si="110"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N29" s="17" t="str">
+      <c r="N29" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A29,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -10495,11 +10495,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A29,FALSE)</f>
         <v>Fay et al. (2024)</v>
       </c>
-      <c r="T29" s="8" t="str">
+      <c r="T29" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A29,FALSE)</f>
         <v>https://doi.org/10.5194/essd-16-2123-2024</v>
       </c>
-      <c r="U29" s="8" t="str">
+      <c r="U29" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A29,FALSE)</f>
         <v>https://doi.org/10.25921/295g-sn13</v>
       </c>
@@ -10537,7 +10537,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A30,FALSE)</f>
         <v>Landschützer et al. (2020) </v>
       </c>
-      <c r="E30" s="8" t="str">
+      <c r="E30" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A30,FALSE)</f>
         <v>https://essd.copernicus.org/articles/12/2537/2020/essd-12-2537-2020-avatar-web.png</v>
       </c>
@@ -10573,7 +10573,7 @@
         <f t="shared" si="114"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N30" s="17" t="str">
+      <c r="N30" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A30,FALSE)</f>
         <v>0.25° x 0.25°</v>
       </c>
@@ -10597,11 +10597,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A30,FALSE)</f>
         <v>Landschützer et al. (2020) </v>
       </c>
-      <c r="T30" s="8" t="str">
+      <c r="T30" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A30,FALSE)</f>
         <v>https://doi.org/10.5194/essd-12-2537-2020</v>
       </c>
-      <c r="U30" s="8" t="str">
+      <c r="U30" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A30,FALSE)</f>
         <v>https://www.ncei.noaa.gov/access/ocean-carbon-acidification-data-system/oceans/MPI-ULB-SOM_FFN_clim.html</v>
       </c>
@@ -10638,7 +10638,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A31,FALSE)</f>
         <v>Landschützer et al. (2016) </v>
       </c>
-      <c r="E31" s="8" t="str">
+      <c r="E31" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A31,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/archive/arc0105/0160558/8.8/about/0160558_preview.png</v>
       </c>
@@ -10674,7 +10674,7 @@
         <f t="shared" si="118"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N31" s="17" t="str">
+      <c r="N31" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A31,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -10698,11 +10698,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A31,FALSE)</f>
         <v>Landschützer et al. (2016) </v>
       </c>
-      <c r="T31" s="8" t="str">
+      <c r="T31" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A31,FALSE)</f>
         <v>https://doi.org/10.1002/2015gb005359</v>
       </c>
-      <c r="U31" s="8" t="str">
+      <c r="U31" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A31,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0160558.html</v>
       </c>
@@ -10739,7 +10739,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A32,FALSE)</f>
         <v>Iida et al. (2021)</v>
       </c>
-      <c r="E32" s="8" t="str">
+      <c r="E32" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A32,FALSE)</f>
         <v>https://www.data.jma.go.jp/kaiyou/data/db/mar_env/results/co2_flux/animation/fluxmap_fig/flux_2023MN.png</v>
       </c>
@@ -10775,7 +10775,7 @@
         <f t="shared" si="122"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N32" s="17" t="str">
+      <c r="N32" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A32,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -10799,11 +10799,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A32,FALSE)</f>
         <v>Iida et al. (2021)</v>
       </c>
-      <c r="T32" s="8" t="str">
+      <c r="T32" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A32,FALSE)</f>
         <v>https://doi.org/10.1007/s10872-020-00571-5</v>
       </c>
-      <c r="U32" s="8" t="str">
+      <c r="U32" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A32,FALSE)</f>
         <v>https://doi.org/10.1007/s10872-020-00571-5</v>
       </c>
@@ -10840,7 +10840,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A33,FALSE)</f>
         <v>Gregor and Gruber (2021)</v>
       </c>
-      <c r="E33" s="8" t="str">
+      <c r="E33" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A33,FALSE)</f>
         <v>https://essd.copernicus.org/articles/13/777/2021/essd-13-777-2021-avatar-web.png</v>
       </c>
@@ -10876,7 +10876,7 @@
         <f t="shared" si="126"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N33" s="17" t="str">
+      <c r="N33" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A33,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -10900,11 +10900,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A33,FALSE)</f>
         <v>Gregor and Gruber (2021)</v>
       </c>
-      <c r="T33" s="8" t="str">
+      <c r="T33" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A33,FALSE)</f>
         <v>https://doi.org/10.5194/essd-13-777-2021</v>
       </c>
-      <c r="U33" s="8" t="str">
+      <c r="U33" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A33,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0220059.html</v>
       </c>
@@ -10941,7 +10941,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A34,FALSE)</f>
         <v>Gregor et al. (2024)</v>
       </c>
-      <c r="E34" s="8" t="str">
+      <c r="E34" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A34,FALSE)</f>
         <v>https://i.ibb.co/9mHfTX1H/gbc21584-fig-0007-m.jpg</v>
       </c>
@@ -10977,7 +10977,7 @@
         <f t="shared" si="130"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N34" s="17" t="str">
+      <c r="N34" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A34,FALSE)</f>
         <v>0.25° x 0.25°</v>
       </c>
@@ -11001,11 +11001,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A34,FALSE)</f>
         <v>Gregor et al. (2024)</v>
       </c>
-      <c r="T34" s="8" t="str">
+      <c r="T34" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A34,FALSE)</f>
         <v>https://doi.org/10.1029/2024GB008127</v>
       </c>
-      <c r="U34" s="8" t="str">
+      <c r="U34" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A34,FALSE)</f>
         <v>https://zenodo.org/records/11206366</v>
       </c>
@@ -11042,7 +11042,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A35,FALSE)</f>
         <v>Gloege et al. (2022)</v>
       </c>
-      <c r="E35" s="8" t="str">
+      <c r="E35" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A35,FALSE)</f>
         <v>https://i.ibb.co/pBXT90wP/jame21511-fig-0001-m.jpg</v>
       </c>
@@ -11078,7 +11078,7 @@
         <f t="shared" si="134"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N35" s="17" t="str">
+      <c r="N35" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A35,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -11102,11 +11102,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A35,FALSE)</f>
         <v>Gloege et al. (2022)</v>
       </c>
-      <c r="T35" s="8" t="str">
+      <c r="T35" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A35,FALSE)</f>
         <v>https://doi.org/10.1029/2021ms002620</v>
       </c>
-      <c r="U35" s="8" t="str">
+      <c r="U35" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A35,FALSE)</f>
         <v>https://zenodo.org/records/4760205</v>
       </c>
@@ -11143,7 +11143,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A36,FALSE)</f>
         <v>Gloege et al. (2022), Bennington et al. (2022)</v>
       </c>
-      <c r="E36" s="8" t="str">
+      <c r="E36" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A36,FALSE)</f>
         <v>https://i.ibb.co/pBXT90wP/jame21511-fig-0001-m.jpg</v>
       </c>
@@ -11179,7 +11179,7 @@
         <f t="shared" si="138"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N36" s="17" t="str">
+      <c r="N36" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A36,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -11203,11 +11203,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A36,FALSE)</f>
         <v>Gloege et al. (2022), Bennington et al. (2022)</v>
       </c>
-      <c r="T36" s="8" t="str">
+      <c r="T36" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A36,FALSE)</f>
         <v>https://doi.org/10.1029/2022GL098632</v>
       </c>
-      <c r="U36" s="8" t="str">
+      <c r="U36" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A36,FALSE)</f>
         <v>https://zenodo.org/records/13891722</v>
       </c>
@@ -11244,7 +11244,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A37,FALSE)</f>
         <v>Bennington et al. (2022)</v>
       </c>
-      <c r="E37" s="8" t="str">
+      <c r="E37" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A37,FALSE)</f>
         <v>https://i.ibb.co/xSw1HkMf/jame21703-fig-0001-m.jpg</v>
       </c>
@@ -11280,7 +11280,7 @@
         <f t="shared" si="142"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N37" s="17" t="str">
+      <c r="N37" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A37,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -11304,11 +11304,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A37,FALSE)</f>
         <v>Bennington et al. (2022)</v>
       </c>
-      <c r="T37" s="8" t="str">
+      <c r="T37" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A37,FALSE)</f>
         <v>https://doi.org/10.1029/2021MS002960</v>
       </c>
-      <c r="U37" s="8" t="str">
+      <c r="U37" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A37,FALSE)</f>
         <v>https://zenodo.org/records/13941548</v>
       </c>
@@ -11345,7 +11345,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A38,FALSE)</f>
         <v>Chau et al. (2022)</v>
       </c>
-      <c r="E38" s="8" t="str">
+      <c r="E38" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A38,FALSE)</f>
         <v>https://bg.copernicus.org/articles/19/1087/2022/bg-19-1087-2022-avatar-web.png</v>
       </c>
@@ -11381,7 +11381,7 @@
         <f t="shared" si="146"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N38" s="17" t="str">
+      <c r="N38" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A38,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -11405,11 +11405,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A38,FALSE)</f>
         <v>Chau et al. (2022)</v>
       </c>
-      <c r="T38" s="8" t="str">
+      <c r="T38" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A38,FALSE)</f>
         <v>https://doi.org/10.5194/bg-19-1087-2022</v>
       </c>
-      <c r="U38" s="8" t="str">
+      <c r="U38" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A38,FALSE)</f>
         <v>https://data.ipsl.fr/catalog/srv/eng/catalog.search#/metadata/a2f0891b-763a-49e9-af1b-78ed78b16982</v>
       </c>
@@ -11446,7 +11446,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A39,FALSE)</f>
         <v>Chau et al. (2024)</v>
       </c>
-      <c r="E39" s="8" t="str">
+      <c r="E39" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A39,FALSE)</f>
         <v>https://essd.copernicus.org/articles/16/121/2024/essd-16-121-2024-avatar-web.png</v>
       </c>
@@ -11482,7 +11482,7 @@
         <f t="shared" si="150"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N39" s="17" t="str">
+      <c r="N39" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A39,FALSE)</f>
         <v>0.25° x 0.25°</v>
       </c>
@@ -11506,11 +11506,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A39,FALSE)</f>
         <v>Chau et al. (2024)</v>
       </c>
-      <c r="T39" s="8" t="str">
+      <c r="T39" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A39,FALSE)</f>
         <v>https://doi.org/10.5194/essd-16-121-2024</v>
       </c>
-      <c r="U39" s="8" t="str">
+      <c r="U39" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A39,FALSE)</f>
         <v>https://doi.org/10.48670/moi-00047</v>
       </c>
@@ -11547,7 +11547,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A40,FALSE)</f>
         <v>Rödenbeck et al. (2022)</v>
       </c>
-      <c r="E40" s="8" t="str">
+      <c r="E40" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A40,FALSE)</f>
         <v>https://bg.copernicus.org/articles/19/2627/2022/bg-19-2627-2022-avatar-web.png</v>
       </c>
@@ -11583,7 +11583,7 @@
         <f t="shared" si="154"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N40" s="17" t="str">
+      <c r="N40" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A40,FALSE)</f>
         <v>2.5° x 2°</v>
       </c>
@@ -11607,11 +11607,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A40,FALSE)</f>
         <v>Rödenbeck et al. (2022)</v>
       </c>
-      <c r="T40" s="8" t="str">
+      <c r="T40" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A40,FALSE)</f>
         <v>https://doi.org/10.5194/bg-19-2627-2022</v>
       </c>
-      <c r="U40" s="8" t="str">
+      <c r="U40" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A40,FALSE)</f>
         <v>https://www.bgc-jena.mpg.de/CarboScope/</v>
       </c>
@@ -11648,7 +11648,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A41,FALSE)</f>
         <v>Watson et al (2020)</v>
       </c>
-      <c r="E41" s="8" t="str">
+      <c r="E41" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A41,FALSE)</f>
         <v>https://i.ibb.co/tpmH1dzt/Watson.png</v>
       </c>
@@ -11684,7 +11684,7 @@
         <f t="shared" si="158"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N41" s="17" t="str">
+      <c r="N41" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A41,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -11708,11 +11708,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A41,FALSE)</f>
         <v>Watson et al (2020)</v>
       </c>
-      <c r="T41" s="8" t="str">
+      <c r="T41" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A41,FALSE)</f>
         <v>https://doi.org/10.1038/s41467-020-18203-3</v>
       </c>
-      <c r="U41" s="8" t="str">
+      <c r="U41" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A41,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/data/0301544/</v>
       </c>
@@ -11749,7 +11749,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A42,FALSE)</f>
         <v>Zeng et al. (2022)</v>
       </c>
-      <c r="E42" s="8" t="str">
+      <c r="E42" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A42,FALSE)</f>
         <v>https://i.ibb.co/zW1nfm1f/Picture3b.png</v>
       </c>
@@ -11785,7 +11785,7 @@
         <f t="shared" si="162"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N42" s="17" t="str">
+      <c r="N42" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A42,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -11809,11 +11809,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A42,FALSE)</f>
         <v>Zeng et al. (2022)</v>
       </c>
-      <c r="T42" s="8" t="str">
+      <c r="T42" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A42,FALSE)</f>
         <v>https://doi.org/10.3389/fmars.2022.989233</v>
       </c>
-      <c r="U42" s="8" t="str">
+      <c r="U42" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A42,FALSE)</f>
         <v>https://www.nies.go.jp/doi/10.17595/20220311.001-e.html</v>
       </c>
@@ -11850,7 +11850,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A43,FALSE)</f>
         <v>Gregor et al. (2019)</v>
       </c>
-      <c r="E43" s="8" t="str">
+      <c r="E43" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A43,FALSE)</f>
         <v>https://gmd.copernicus.org/articles/12/5113/2019/gmd-12-5113-2019-f09-web.png</v>
       </c>
@@ -11886,7 +11886,7 @@
         <f t="shared" si="166"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N43" s="17" t="str">
+      <c r="N43" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A43,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -11910,11 +11910,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A43,FALSE)</f>
         <v>Gregor et al. (2019)</v>
       </c>
-      <c r="T43" s="8" t="str">
+      <c r="T43" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A43,FALSE)</f>
         <v>https://doi.org/10.5194/gmd-12-5113-2019</v>
       </c>
-      <c r="U43" s="8" t="str">
+      <c r="U43" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A43,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0206205.html</v>
       </c>
@@ -11951,7 +11951,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A44,FALSE)</f>
         <v>Zhong et al. (2022)</v>
       </c>
-      <c r="E44" s="8" t="str">
+      <c r="E44" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A44,FALSE)</f>
         <v>https://appletmsdc.qdio.ac.cn//files/metadata/images/2025-08-14_1955061943601487874/DATA20251000212_11415094_1.jpg</v>
       </c>
@@ -11987,7 +11987,7 @@
         <f t="shared" si="170"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N44" s="17" t="str">
+      <c r="N44" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A44,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -12011,11 +12011,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A44,FALSE)</f>
         <v>Zhong et al. (2022)</v>
       </c>
-      <c r="T44" s="8" t="str">
+      <c r="T44" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A44,FALSE)</f>
         <v> http://doi.org/10.12157/IOCAS.20250814.001</v>
       </c>
-      <c r="U44" s="8" t="str">
+      <c r="U44" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A44,FALSE)</f>
         <v> http://doi.org/10.12157/IOCAS.20250814.001</v>
       </c>
@@ -12052,7 +12052,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A45,FALSE)</f>
         <v>Wanninkhof et al. (2015)</v>
       </c>
-      <c r="E45" s="8" t="str">
+      <c r="E45" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A45,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/archive/arc0235/0298989/2.2/about/0298989_preview.jpg</v>
       </c>
@@ -12088,7 +12088,7 @@
         <f t="shared" si="174"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N45" s="17" t="str">
+      <c r="N45" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A45,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -12112,11 +12112,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A45,FALSE)</f>
         <v>Wanninkhof et al. (2015)</v>
       </c>
-      <c r="T45" s="8" t="str">
+      <c r="T45" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A45,FALSE)</f>
         <v>https://doi.org/10.1029/2024GB008315</v>
       </c>
-      <c r="U45" s="8" t="str">
+      <c r="U45" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A45,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0298989.html</v>
       </c>
@@ -12153,7 +12153,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A46,FALSE)</f>
         <v>Roobaert et al. (2024)</v>
       </c>
-      <c r="E46" s="8" t="str">
+      <c r="E46" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A46,FALSE)</f>
         <v>https://essd.copernicus.org/articles/16/421/2024/essd-16-421-2024-f01-web.png</v>
       </c>
@@ -12189,7 +12189,7 @@
         <f t="shared" si="178"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N46" s="17" t="str">
+      <c r="N46" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A46,FALSE)</f>
         <v>0.25° x 0.25°</v>
       </c>
@@ -12213,11 +12213,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A46,FALSE)</f>
         <v>Roobaert et al. (2024)</v>
       </c>
-      <c r="T46" s="8" t="str">
+      <c r="T46" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A46,FALSE)</f>
         <v>https://doi.org/10.5194/essd-16-421-2024</v>
       </c>
-      <c r="U46" s="8" t="str">
+      <c r="U46" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A46,FALSE)</f>
         <v>https://doi.org/10.25921/4sde-p068</v>
       </c>
@@ -12254,7 +12254,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A47,FALSE)</f>
         <v>Sharp et al. (2024)</v>
       </c>
-      <c r="E47" s="8" t="str">
+      <c r="E47" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A47,FALSE)</f>
         <v>https://i.ibb.co/ynxb1Hry/Screenshot-2025-11-07-at-09-32-32.png</v>
       </c>
@@ -12290,7 +12290,7 @@
         <f t="shared" si="182"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N47" s="17" t="str">
+      <c r="N47" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A47,FALSE)</f>
         <v>0.25° x 0.25°</v>
       </c>
@@ -12314,11 +12314,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A47,FALSE)</f>
         <v>Sharp et al. (2024)</v>
       </c>
-      <c r="T47" s="8" t="str">
+      <c r="T47" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A47,FALSE)</f>
         <v>https://doi.org/10.1038/s41597-024-03530-7</v>
       </c>
-      <c r="U47" s="8" t="str">
+      <c r="U47" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A47,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0287551.html</v>
       </c>
@@ -12355,7 +12355,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A48,FALSE)</f>
         <v>Wu et al. (2025)</v>
       </c>
-      <c r="E48" s="8" t="str">
+      <c r="E48" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A48,FALSE)</f>
         <v>https://essd.copernicus.org/articles/17/43/2025/essd-17-43-2025-avatar-web.png</v>
       </c>
@@ -12391,7 +12391,7 @@
         <f t="shared" si="186"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N48" s="17" t="str">
+      <c r="N48" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A48,FALSE)</f>
         <v>0.25° x 0.25°</v>
       </c>
@@ -12416,11 +12416,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A48,FALSE)</f>
         <v>Wu et al. (2025)</v>
       </c>
-      <c r="T48" s="8" t="str">
+      <c r="T48" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A48,FALSE)</f>
         <v>https://doi.org/10.5194/essd-17-43-2025</v>
       </c>
-      <c r="U48" s="8" t="str">
+      <c r="U48" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A48,FALSE)</f>
         <v>https://doi.org/10.5281/zenodo.11500974</v>
       </c>
@@ -12457,7 +12457,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A49,FALSE)</f>
         <v>Wanninkhof et al. (2020)</v>
       </c>
-      <c r="E49" s="8" t="str">
+      <c r="E49" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A49,FALSE)</f>
         <v>https://essd.copernicus.org/articles/12/1489/2020/essd-12-1489-2020-avatar-web.png</v>
       </c>
@@ -12493,7 +12493,7 @@
         <f t="shared" si="190"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N49" s="17" t="str">
+      <c r="N49" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A49,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -12517,11 +12517,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A49,FALSE)</f>
         <v>Wanninkhof et al. (2020)</v>
       </c>
-      <c r="T49" s="8" t="str">
+      <c r="T49" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A49,FALSE)</f>
         <v>https://doi.org/10.5194/essd-12-1489-2020</v>
       </c>
-      <c r="U49" s="8" t="str">
+      <c r="U49" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A49,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0207749.html </v>
       </c>
@@ -12558,7 +12558,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A50,FALSE)</f>
         <v>van Hooidonk (2022)</v>
       </c>
-      <c r="E50" s="8" t="str">
+      <c r="E50" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A50,FALSE)</f>
         <v>https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Aomlogo.svg/330px-Aomlogo.svg.png</v>
       </c>
@@ -12594,7 +12594,7 @@
         <f t="shared" si="194"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N50" s="17" t="str">
+      <c r="N50" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A50,FALSE)</f>
         <v>0.088° x 0.088°</v>
       </c>
@@ -12610,7 +12610,7 @@
         <f>HLOOKUP(Q$1,google_form!$1:$198,$A50,FALSE)</f>
         <v>2014-2020</v>
       </c>
-      <c r="R50" s="8" t="str">
+      <c r="R50" s="7" t="str">
         <f>HLOOKUP(R$1,google_form!$1:$198,$A50,FALSE)</f>
         <v>https://upload.wikimedia.org/wikipedia/commons/thumb/5/59/Aomlogo.svg/330px-Aomlogo.svg.png</v>
       </c>
@@ -12618,11 +12618,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A50,FALSE)</f>
         <v>van Hooidonk (2022)</v>
       </c>
-      <c r="T50" s="8" t="str">
+      <c r="T50" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A50,FALSE)</f>
         <v>https://doi.org/10.25921/tt1c-dx53</v>
       </c>
-      <c r="U50" s="8" t="str">
+      <c r="U50" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A50,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0245950.html</v>
       </c>
@@ -12659,7 +12659,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A51,FALSE)</f>
         <v>Bittig et al. (2024)</v>
       </c>
-      <c r="E51" s="8" t="str">
+      <c r="E51" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A51,FALSE)</f>
         <v>https://essd.copernicus.org/articles/16/753/2024/essd-16-753-2024-avatar-web.png</v>
       </c>
@@ -12695,7 +12695,7 @@
         <f t="shared" si="198"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N51" s="17" t="str">
+      <c r="N51" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A51,FALSE)</f>
         <v>0.10° x 0.05°</v>
       </c>
@@ -12719,11 +12719,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A51,FALSE)</f>
         <v>Bittig et al. (2024)</v>
       </c>
-      <c r="T51" s="8" t="str">
+      <c r="T51" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A51,FALSE)</f>
         <v>https://doi.org/10.5194/essd-16-753-2024</v>
       </c>
-      <c r="U51" s="8" t="str">
+      <c r="U51" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A51,FALSE)</f>
         <v>https://doi.org/10.1594/PANGAEA.961119 </v>
       </c>
@@ -12760,7 +12760,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A52,FALSE)</f>
         <v>Joshi et al. (2024)</v>
       </c>
-      <c r="E52" s="8" t="str">
+      <c r="E52" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A52,FALSE)</f>
         <v>https://i.ibb.co/cShr87g7/pCO2-BoB.png</v>
       </c>
@@ -12796,7 +12796,7 @@
         <f t="shared" si="202"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N52" s="17" t="str">
+      <c r="N52" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A52,FALSE)</f>
         <v>0.083° x 0.083°</v>
       </c>
@@ -12820,11 +12820,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A52,FALSE)</f>
         <v>Joshi et al. (2024)</v>
       </c>
-      <c r="T52" s="8" t="str">
+      <c r="T52" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A52,FALSE)</f>
         <v>https://doi.org/10.1038/s41597-024-03236-w</v>
       </c>
-      <c r="U52" s="8" t="str">
+      <c r="U52" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A52,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0307627.html</v>
       </c>
@@ -12861,7 +12861,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A53,FALSE)</f>
         <v>Joshi et al. (2025)</v>
       </c>
-      <c r="E53" s="8" t="str">
+      <c r="E53" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A53,FALSE)</f>
         <v>https://i.ibb.co/BYn8GyH/Climatology-TA.png</v>
       </c>
@@ -12897,7 +12897,7 @@
         <f t="shared" si="206"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N53" s="17" t="str">
+      <c r="N53" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A53,FALSE)</f>
         <v>0.083° x 0.083°</v>
       </c>
@@ -12921,11 +12921,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A53,FALSE)</f>
         <v>Joshi et al. (2025)</v>
       </c>
-      <c r="T53" s="8" t="str">
+      <c r="T53" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A53,FALSE)</f>
         <v>https://doi.org/10.1029/2024GB008344</v>
       </c>
-      <c r="U53" s="8" t="str">
+      <c r="U53" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A53,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0307789.html</v>
       </c>
@@ -12962,7 +12962,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A54,FALSE)</f>
         <v>Lauvset et al. (2016)</v>
       </c>
-      <c r="E54" s="8" t="str">
+      <c r="E54" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A54,FALSE)</f>
         <v>https://i.ibb.co/dwFT2QJx/GLODAPv2-Climatology.png</v>
       </c>
@@ -12998,7 +12998,7 @@
         <f t="shared" si="210"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N54" s="17" t="str">
+      <c r="N54" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A54,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -13022,11 +13022,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A54,FALSE)</f>
         <v>Lauvset et al. (2016)</v>
       </c>
-      <c r="T54" s="8" t="str">
+      <c r="T54" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A54,FALSE)</f>
         <v>https://doi.org/10.5194/essd-8-325-2016</v>
       </c>
-      <c r="U54" s="8" t="str">
+      <c r="U54" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A54,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0286118.html </v>
       </c>
@@ -13063,7 +13063,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A55,FALSE)</f>
         <v>Jiang et al. (2015) </v>
       </c>
-      <c r="E55" s="8" t="str">
+      <c r="E55" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A55,FALSE)</f>
         <v>https://i.ibb.co/KpxH4y77/gbc20348-fig-0002-m.jpg</v>
       </c>
@@ -13099,7 +13099,7 @@
         <f t="shared" si="214"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N55" s="17" t="str">
+      <c r="N55" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A55,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -13123,11 +13123,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A55,FALSE)</f>
         <v>Jiang et al. (2015) </v>
       </c>
-      <c r="T55" s="8" t="str">
+      <c r="T55" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A55,FALSE)</f>
         <v>https://doi.org/10.1002/2015GB005198</v>
       </c>
-      <c r="U55" s="8" t="str">
+      <c r="U55" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A55,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0139360.html</v>
       </c>
@@ -13164,7 +13164,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A56,FALSE)</f>
         <v>Keppler et al., 2020</v>
       </c>
-      <c r="E56" s="8" t="str">
+      <c r="E56" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A56,FALSE)</f>
         <v>https://www.ncei.noaa.gov/access/ocean-carbon-acidification-data-system/oceans/ndp_104/Moby.jpg</v>
       </c>
@@ -13200,7 +13200,7 @@
         <f t="shared" si="218"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N56" s="17" t="str">
+      <c r="N56" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A56,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -13224,11 +13224,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A56,FALSE)</f>
         <v>Keppler et al., 2020</v>
       </c>
-      <c r="T56" s="8" t="str">
+      <c r="T56" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A56,FALSE)</f>
         <v>https://doi.org/10.1029/2020GB006571</v>
       </c>
-      <c r="U56" s="8" t="str">
+      <c r="U56" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A56,FALSE)</f>
         <v>https://www.ncei.noaa.gov/access/ocean-carbon-acidification-data-system/oceans/ndp_104/ndp104.html</v>
       </c>
@@ -13265,7 +13265,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A57,FALSE)</f>
         <v>Keppler et al. (2023)</v>
       </c>
-      <c r="E57" s="8" t="str">
+      <c r="E57" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A57,FALSE)</f>
         <v>https://www.ncei.noaa.gov/access/ocean-carbon-acidification-data-system/oceans/ndp_104/Moby.jpg</v>
       </c>
@@ -13301,7 +13301,7 @@
         <f t="shared" si="222"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N57" s="17" t="str">
+      <c r="N57" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A57,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -13325,11 +13325,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A57,FALSE)</f>
         <v>Keppler et al. (2023)</v>
       </c>
-      <c r="T57" s="8" t="str">
+      <c r="T57" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A57,FALSE)</f>
         <v>https://doi.org/10.1029/2022gb007677</v>
       </c>
-      <c r="U57" s="8" t="str">
+      <c r="U57" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A57,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0277099.html</v>
       </c>
@@ -13366,7 +13366,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A58,FALSE)</f>
         <v>Broullon et al., (2019)</v>
       </c>
-      <c r="E58" s="8" t="str">
+      <c r="E58" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A58,FALSE)</f>
         <v>https://essd.copernicus.org/articles/11/1109/2019/essd-11-1109-2019-f09-web.png</v>
       </c>
@@ -13402,7 +13402,7 @@
         <f t="shared" si="226"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N58" s="17" t="str">
+      <c r="N58" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A58,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -13426,11 +13426,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A58,FALSE)</f>
         <v>Broullon et al., (2019)</v>
       </c>
-      <c r="T58" s="8" t="str">
+      <c r="T58" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A58,FALSE)</f>
         <v>https://doi.org/10.5194/essd-11-1109-2019</v>
       </c>
-      <c r="U58" s="8" t="str">
+      <c r="U58" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A58,FALSE)</f>
         <v>https://doi.org/10.25921/5p69-y471</v>
       </c>
@@ -13467,7 +13467,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A59,FALSE)</f>
         <v>Broullón et al., (2020)</v>
       </c>
-      <c r="E59" s="8" t="str">
+      <c r="E59" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A59,FALSE)</f>
         <v>https://essd.copernicus.org/articles/12/1725/2020/essd-12-1725-2020-f07-web.png</v>
       </c>
@@ -13503,7 +13503,7 @@
         <f t="shared" si="230"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N59" s="17" t="str">
+      <c r="N59" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A59,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -13527,11 +13527,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A59,FALSE)</f>
         <v>Broullón et al., (2020)</v>
       </c>
-      <c r="T59" s="8" t="str">
+      <c r="T59" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A59,FALSE)</f>
         <v>https://doi.org/10.5194/essd-12-1725-2020</v>
       </c>
-      <c r="U59" s="8" t="str">
+      <c r="U59" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A59,FALSE)</f>
         <v>https://doi.org/10.25921/ndgj-jp24</v>
       </c>
@@ -13568,7 +13568,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A60,FALSE)</f>
         <v>Fassbender et al. (2023) </v>
       </c>
-      <c r="E60" s="8" t="str">
+      <c r="E60" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A60,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/archive/arc0227/0290073/1.1/about/0290073_preview.jpg</v>
       </c>
@@ -13604,7 +13604,7 @@
         <f t="shared" si="234"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N60" s="17" t="str">
+      <c r="N60" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A60,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -13628,11 +13628,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A60,FALSE)</f>
         <v>Fassbender et al. (2023) </v>
       </c>
-      <c r="T60" s="8" t="str">
+      <c r="T60" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A60,FALSE)</f>
         <v>https://doi.org/10.1029/2023GB007843</v>
       </c>
-      <c r="U60" s="8" t="str">
+      <c r="U60" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A60,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0290073.html</v>
       </c>
@@ -13669,7 +13669,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A61,FALSE)</f>
         <v>Müller et al. (2024)</v>
       </c>
-      <c r="E61" s="8" t="str">
+      <c r="E61" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A61,FALSE)</f>
         <v>https://i.ibb.co/YT3rjvDc/sciadv-ado3103-f1.jpg</v>
       </c>
@@ -13705,7 +13705,7 @@
         <f t="shared" si="238"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N61" s="17" t="str">
+      <c r="N61" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A61,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -13729,11 +13729,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A61,FALSE)</f>
         <v>Müller et al. (2024)</v>
       </c>
-      <c r="T61" s="8" t="str">
+      <c r="T61" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A61,FALSE)</f>
         <v>https://doi.org/10.1126/sciadv.ado3103</v>
       </c>
-      <c r="U61" s="8" t="str">
+      <c r="U61" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A61,FALSE)</f>
         <v>https://doi.org/10.25921/tefm-x802</v>
       </c>
@@ -13770,7 +13770,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A62,FALSE)</f>
         <v>Gruber et al. (2019) </v>
       </c>
-      <c r="E62" s="8" t="str">
+      <c r="E62" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A62,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/archive/arc0132/0186034/1.1/about/0186034_preview.jpg</v>
       </c>
@@ -13806,7 +13806,7 @@
         <f t="shared" si="242"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N62" s="17" t="str">
+      <c r="N62" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A62,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -13830,11 +13830,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A62,FALSE)</f>
         <v>Gruber et al. (2019) </v>
       </c>
-      <c r="T62" s="8" t="str">
+      <c r="T62" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A62,FALSE)</f>
         <v>https://doi.org/10.1126/science.aau5153</v>
       </c>
-      <c r="U62" s="8" t="str">
+      <c r="U62" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A62,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0186034.html</v>
       </c>
@@ -13871,7 +13871,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A63,FALSE)</f>
         <v>Müller et al. (2023)</v>
       </c>
-      <c r="E63" s="8" t="str">
+      <c r="E63" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A63,FALSE)</f>
         <v>https://eos.org/wp-content/uploads/2023/08/Fig2_highlight.jpg</v>
       </c>
@@ -13907,7 +13907,7 @@
         <f t="shared" si="246"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N63" s="17" t="str">
+      <c r="N63" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A63,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -13931,11 +13931,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A63,FALSE)</f>
         <v>Müller et al. (2023)</v>
       </c>
-      <c r="T63" s="8" t="str">
+      <c r="T63" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A63,FALSE)</f>
         <v>https://doi.org/10.1029/2023AV000875</v>
       </c>
-      <c r="U63" s="8" t="str">
+      <c r="U63" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A63,FALSE)</f>
         <v>https://doi.org/10.25921/ppcf-w020</v>
       </c>
@@ -13972,7 +13972,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A64,FALSE)</f>
         <v>Carter et al. (2025)</v>
       </c>
-      <c r="E64" s="8" t="str">
+      <c r="E64" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A64,FALSE)</f>
         <v>https://essd.copernicus.org/articles/17/3073/2025/essd-17-3073-2025-avatar-web.png</v>
       </c>
@@ -14008,7 +14008,7 @@
         <f t="shared" si="250"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N64" s="17" t="str">
+      <c r="N64" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A64,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -14032,11 +14032,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A64,FALSE)</f>
         <v>Carter et al. (2025)</v>
       </c>
-      <c r="T64" s="8" t="str">
+      <c r="T64" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A64,FALSE)</f>
         <v>https://doi.org/10.5194/essd-17-3073-2025</v>
       </c>
-      <c r="U64" s="8" t="str">
+      <c r="U64" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A64,FALSE)</f>
         <v>https://zenodo.org/records/15692788</v>
       </c>
@@ -14073,7 +14073,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A65,FALSE)</f>
         <v>Carter et al. (2021)</v>
       </c>
-      <c r="E65" s="8" t="str">
+      <c r="E65" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A65,FALSE)</f>
         <v>https://i.ibb.co/S488KKjG/gbc21075-fig-0003-m.jpg</v>
       </c>
@@ -14109,7 +14109,7 @@
         <f t="shared" si="254"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N65" s="17" t="str">
+      <c r="N65" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A65,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -14133,11 +14133,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A65,FALSE)</f>
         <v>Carter et al. (2021)</v>
       </c>
-      <c r="T65" s="8" t="str">
+      <c r="T65" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A65,FALSE)</f>
         <v>https://zenodo.org/records/3745002</v>
       </c>
-      <c r="U65" s="8" t="str">
+      <c r="U65" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A65,FALSE)</f>
         <v>https://github.com/BRCScienceProducts/PreformedPropertyEstimates</v>
       </c>
@@ -14174,7 +14174,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A66,FALSE)</f>
         <v>Zhong et al. (2025)</v>
       </c>
-      <c r="E66" s="8" t="str">
+      <c r="E66" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A66,FALSE)</f>
         <v>https://appletmsdc.qdio.ac.cn//files/metadata/images/2025-11-07_1681888486837194754/DATA2023000009_zhongguorong_1.jpg</v>
       </c>
@@ -14210,7 +14210,7 @@
         <f t="shared" si="258"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N66" s="17" t="str">
+      <c r="N66" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A66,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -14234,11 +14234,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A66,FALSE)</f>
         <v>Zhong et al. (2025)</v>
       </c>
-      <c r="T66" s="8" t="str">
+      <c r="T66" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A66,FALSE)</f>
         <v> http://doi.org/10.12157/IOCAS.20230720.001</v>
       </c>
-      <c r="U66" s="8" t="str">
+      <c r="U66" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A66,FALSE)</f>
         <v> http://doi.org/10.12157/IOCAS.20230720.001</v>
       </c>
@@ -14275,7 +14275,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A67,FALSE)</f>
         <v>Jiang et al. (2024)</v>
       </c>
-      <c r="E67" s="8" t="str">
+      <c r="E67" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A67,FALSE)</f>
         <v>https://essd.copernicus.org/articles/16/3383/2024/essd-16-3383-2024-avatar-web.png</v>
       </c>
@@ -14311,7 +14311,7 @@
         <f t="shared" si="262"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N67" s="17" t="str">
+      <c r="N67" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A67,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -14335,11 +14335,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A67,FALSE)</f>
         <v>Jiang et al. (2024)</v>
       </c>
-      <c r="T67" s="8" t="str">
+      <c r="T67" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A67,FALSE)</f>
         <v>https://doi.org/10.5194/essd-16-3383-2024</v>
       </c>
-      <c r="U67" s="8" t="str">
+      <c r="U67" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A67,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0270962.html</v>
       </c>
@@ -14376,7 +14376,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A68,FALSE)</f>
         <v>Fay and Gregor et al. (2021)</v>
       </c>
-      <c r="E68" s="8" t="str">
+      <c r="E68" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A68,FALSE)</f>
         <v>https://seaflux.readthedocs.io/en/latest/_static/seaflux_logo.png</v>
       </c>
@@ -14412,7 +14412,7 @@
         <f t="shared" si="266"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N68" s="17" t="str">
+      <c r="N68" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A68,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -14436,11 +14436,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A68,FALSE)</f>
         <v>Fay and Gregor et al. (2021)</v>
       </c>
-      <c r="T68" s="8" t="str">
+      <c r="T68" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A68,FALSE)</f>
         <v>https://doi.org/10.5194/essd-2021-16</v>
       </c>
-      <c r="U68" s="8" t="str">
+      <c r="U68" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A68,FALSE)</f>
         <v>https://zenodo.org/records/8280457</v>
       </c>
@@ -14477,7 +14477,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A69,FALSE)</f>
         <v>DeVries et al. (2023)</v>
       </c>
-      <c r="E69" s="8" t="str">
+      <c r="E69" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A69,FALSE)</f>
         <v>https://i.ibb.co/NgXDHSQh/gbc21476-fig-0001-m.jpg</v>
       </c>
@@ -14513,7 +14513,7 @@
         <f t="shared" si="270"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N69" s="17" t="str">
+      <c r="N69" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A69,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -14537,11 +14537,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A69,FALSE)</f>
         <v>DeVries et al. (2023)</v>
       </c>
-      <c r="T69" s="8" t="str">
+      <c r="T69" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A69,FALSE)</f>
         <v>https://doi.org/10.1029/2023gb007780</v>
       </c>
-      <c r="U69" s="8" t="str">
+      <c r="U69" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A69,FALSE)</f>
         <v>https://zenodo.org/records/7990823</v>
       </c>
@@ -14578,7 +14578,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A70,FALSE)</f>
         <v>Friedlingstein et al. (2025)</v>
       </c>
-      <c r="E70" s="8" t="str">
+      <c r="E70" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A70,FALSE)</f>
         <v>https://i.ibb.co/TxwRM1tp/GCP.jpg</v>
       </c>
@@ -14614,7 +14614,7 @@
         <f t="shared" si="274"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N70" s="17" t="str">
+      <c r="N70" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A70,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -14638,11 +14638,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A70,FALSE)</f>
         <v>Friedlingstein et al. (2025)</v>
       </c>
-      <c r="T70" s="8" t="str">
+      <c r="T70" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A70,FALSE)</f>
         <v>https://doi.org/10.5194/essd-17-965-2025</v>
       </c>
-      <c r="U70" s="8" t="str">
+      <c r="U70" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A70,FALSE)</f>
         <v>https://doi.org/10.5281/zenodo.17579108</v>
       </c>
@@ -14679,7 +14679,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A71,FALSE)</f>
         <v>DeVries et al. (2019)</v>
       </c>
-      <c r="E71" s="8" t="str">
+      <c r="E71" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A71,FALSE)</f>
         <v>https://i.ibb.co/RTWv9Yp9/pnas-1900371116fig01.jpg</v>
       </c>
@@ -14715,7 +14715,7 @@
         <f t="shared" si="278"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N71" s="17" t="str">
+      <c r="N71" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A71,FALSE)</f>
         <v/>
       </c>
@@ -14739,11 +14739,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A71,FALSE)</f>
         <v>DeVries et al. (2019)</v>
       </c>
-      <c r="T71" s="8" t="str">
+      <c r="T71" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A71,FALSE)</f>
         <v>https://doi.org/10.1073/pnas.1900371116</v>
       </c>
-      <c r="U71" s="8" t="str">
+      <c r="U71" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A71,FALSE)</f>
         <v>https://doi.org/10.6084/m9.figshare.8091161.v1</v>
       </c>
@@ -14780,7 +14780,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A72,FALSE)</f>
         <v>Carroll et al. (2020)</v>
       </c>
-      <c r="E72" s="8" t="str">
+      <c r="E72" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A72,FALSE)</f>
         <v>https://ecco-group.org/images/ecco_rotator01.jpg</v>
       </c>
@@ -14816,7 +14816,7 @@
         <f t="shared" si="282"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N72" s="17" t="str">
+      <c r="N72" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A72,FALSE)</f>
         <v>0.33° x 0.33°</v>
       </c>
@@ -14840,11 +14840,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A72,FALSE)</f>
         <v>Carroll et al. (2020)</v>
       </c>
-      <c r="T72" s="8" t="str">
+      <c r="T72" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A72,FALSE)</f>
         <v>https://doi.org/10.5281/zenodo.10627664</v>
       </c>
-      <c r="U72" s="8" t="str">
+      <c r="U72" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A72,FALSE)</f>
         <v>https://data.nas.nasa.gov/ecco/</v>
       </c>
@@ -14881,7 +14881,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A73,FALSE)</f>
         <v>Jiang et al. (2019)</v>
       </c>
-      <c r="E73" s="8" t="str">
+      <c r="E73" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A73,FALSE)</f>
         <v>https://media.springernature.com/lw685/springer-static/image/art%3A10.1038%2Fs41598-019-55039-4/MediaObjects/41598_2019_55039_Fig6_HTML.png</v>
       </c>
@@ -14917,7 +14917,7 @@
         <f t="shared" si="286"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N73" s="17" t="str">
+      <c r="N73" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A73,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -14941,11 +14941,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A73,FALSE)</f>
         <v>Jiang et al. (2019)</v>
       </c>
-      <c r="T73" s="8" t="str">
+      <c r="T73" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A73,FALSE)</f>
         <v>https://doi.org/10.1038/s41598-019-55039-4</v>
       </c>
-      <c r="U73" s="8" t="str">
+      <c r="U73" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A73,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0206289.html </v>
       </c>
@@ -14982,7 +14982,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A74,FALSE)</f>
         <v>Jiang et al. (2023)</v>
       </c>
-      <c r="E74" s="8" t="str">
+      <c r="E74" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A74,FALSE)</f>
         <v>https://i.ibb.co/27sB2HLw/jame21817-fig-0008-m.jpg</v>
       </c>
@@ -15018,7 +15018,7 @@
         <f t="shared" si="290"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N74" s="17" t="str">
+      <c r="N74" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A74,FALSE)</f>
         <v>1° x 1°</v>
       </c>
@@ -15042,11 +15042,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A74,FALSE)</f>
         <v>Jiang et al. (2023)</v>
       </c>
-      <c r="T74" s="8" t="str">
+      <c r="T74" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A74,FALSE)</f>
         <v>https://doi.org/10.1029/2022MS003563</v>
       </c>
-      <c r="U74" s="8" t="str">
+      <c r="U74" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A74,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0259391.html</v>
       </c>
@@ -15083,7 +15083,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A75,FALSE)</f>
         <v>Terhaar et al. (2021)</v>
       </c>
-      <c r="E75" s="8" t="str">
+      <c r="E75" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A75,FALSE)</f>
         <v>https://www.seanoe.org/data/00927/103934/illustration.gif</v>
       </c>
@@ -15119,7 +15119,7 @@
         <f t="shared" si="294"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N75" s="17" t="str">
+      <c r="N75" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A75,FALSE)</f>
         <v/>
       </c>
@@ -15143,11 +15143,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A75,FALSE)</f>
         <v>Terhaar et al. (2021)</v>
       </c>
-      <c r="T75" s="8" t="str">
+      <c r="T75" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A75,FALSE)</f>
         <v>https://doi.org/10.1126/sciadv.abd5964</v>
       </c>
-      <c r="U75" s="8" t="str">
+      <c r="U75" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A75,FALSE)</f>
         <v>https://www.seanoe.org/data/00927/103938/</v>
       </c>
@@ -15184,7 +15184,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A76,FALSE)</f>
         <v>Terhaar et al., (2022)</v>
       </c>
-      <c r="E76" s="8" t="str">
+      <c r="E76" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A76,FALSE)</f>
         <v>https://www.seanoe.org/data/00927/103934/illustration.gif</v>
       </c>
@@ -15220,7 +15220,7 @@
         <f t="shared" si="298"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N76" s="17" t="str">
+      <c r="N76" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A76,FALSE)</f>
         <v/>
       </c>
@@ -15244,11 +15244,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A76,FALSE)</f>
         <v>Terhaar et al., (2022)</v>
       </c>
-      <c r="T76" s="8" t="str">
+      <c r="T76" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A76,FALSE)</f>
         <v>https://doi.org/10.5194/bg-19-4431-2022</v>
       </c>
-      <c r="U76" s="8" t="str">
+      <c r="U76" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A76,FALSE)</f>
         <v>https://www.seanoe.org/data/00927/103934</v>
       </c>
@@ -15285,7 +15285,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A77,FALSE)</f>
         <v>Terhaar (2025)</v>
       </c>
-      <c r="E77" s="8" t="str">
+      <c r="E77" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A77,FALSE)</f>
         <v>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9c/Ocean_water.jpg/960px-Ocean_water.jpg</v>
       </c>
@@ -15321,7 +15321,7 @@
         <f t="shared" si="302"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N77" s="17" t="str">
+      <c r="N77" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A77,FALSE)</f>
         <v/>
       </c>
@@ -15345,11 +15345,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A77,FALSE)</f>
         <v>Terhaar (2025)</v>
       </c>
-      <c r="T77" s="8" t="str">
+      <c r="T77" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A77,FALSE)</f>
         <v>https://doi.org/10.5194/bg-22-1631-2025</v>
       </c>
-      <c r="U77" s="8" t="str">
+      <c r="U77" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A77,FALSE)</f>
         <v>https://doi.org/10.5194/bg-22-1631-2025</v>
       </c>
@@ -15386,7 +15386,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A78,FALSE)</f>
         <v>Ghoshal et al. (2025)</v>
       </c>
-      <c r="E78" s="8" t="str">
+      <c r="E78" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A78,FALSE)</f>
         <v>https://i.ibb.co/8DtF8Zz4/p-CIBR-p-CO2-DECADAL.png</v>
       </c>
@@ -15422,7 +15422,7 @@
         <f t="shared" si="306"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N78" s="17" t="str">
+      <c r="N78" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A78,FALSE)</f>
         <v>0.083° x 0.083°</v>
       </c>
@@ -15446,11 +15446,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A78,FALSE)</f>
         <v>Ghoshal et al. (2025)</v>
       </c>
-      <c r="T78" s="8" t="str">
+      <c r="T78" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A78,FALSE)</f>
         <v>https://doi.org/10.1038/s41597-025-04914-z</v>
       </c>
-      <c r="U78" s="8" t="str">
+      <c r="U78" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A78,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0307788.html</v>
       </c>
@@ -15487,7 +15487,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A79,FALSE)</f>
         <v>Chakraborty et al. (2024)</v>
       </c>
-      <c r="E79" s="8" t="str">
+      <c r="E79" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A79,FALSE)</f>
         <v>https://i.ibb.co/wFc3f1bY/p-H-DECADAL.png</v>
       </c>
@@ -15523,7 +15523,7 @@
         <f t="shared" si="310"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N79" s="17" t="str">
+      <c r="N79" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A79,FALSE)</f>
         <v>0.083° x 0.083°</v>
       </c>
@@ -15547,11 +15547,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A79,FALSE)</f>
         <v>Chakraborty et al. (2024)</v>
       </c>
-      <c r="T79" s="8" t="str">
+      <c r="T79" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A79,FALSE)</f>
         <v>https://doi.org/10.1029/2024GB008139</v>
       </c>
-      <c r="U79" s="8" t="str">
+      <c r="U79" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A79,FALSE)</f>
         <v>https://www.ncei.noaa.gov/data/oceans/ncei/ocads/metadata/0307663.html</v>
       </c>
@@ -15588,7 +15588,7 @@
         <f>HLOOKUP(D$1,google_form!$1:$218,$A80,FALSE)</f>
         <v>DeVries (2022b)</v>
       </c>
-      <c r="E80" s="8" t="str">
+      <c r="E80" s="7" t="str">
         <f>HLOOKUP(E$1,google_form!$1:$218,$A80,FALSE)</f>
         <v>https://i.ibb.co/Xxbcrf2b/Screenshot-2025-11-14-at-08-56-35.png</v>
       </c>
@@ -15624,7 +15624,7 @@
         <f t="shared" si="314"/>
         <v>Spatial resolution</v>
       </c>
-      <c r="N80" s="17" t="str">
+      <c r="N80" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A80,FALSE)</f>
         <v>2° x 2°</v>
       </c>
@@ -15648,11 +15648,11 @@
         <f>HLOOKUP(S$1,google_form!$1:$198,$A80,FALSE)</f>
         <v>DeVries (2022b)</v>
       </c>
-      <c r="T80" s="8" t="str">
+      <c r="T80" s="7" t="str">
         <f>HLOOKUP(T$1,google_form!$1:$198,$A80,FALSE)</f>
         <v>https://doi.org/10.1029/2021GL096018</v>
       </c>
-      <c r="U80" s="8" t="str">
+      <c r="U80" s="7" t="str">
         <f>HLOOKUP(U$1,google_form!$1:$198,$A80,FALSE)</f>
         <v>https://figshare.com/articles/dataset/OCIM2-48L_abiotic_ocean_carbon_cycle_model_output/19341974</v>
       </c>
@@ -15725,7 +15725,7 @@
         <f t="shared" si="318"/>
         <v/>
       </c>
-      <c r="N81" s="17" t="str">
+      <c r="N81" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A81,FALSE)</f>
         <v/>
       </c>
@@ -15826,7 +15826,7 @@
         <f t="shared" si="322"/>
         <v/>
       </c>
-      <c r="N82" s="17" t="str">
+      <c r="N82" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A82,FALSE)</f>
         <v/>
       </c>
@@ -15927,7 +15927,7 @@
         <f t="shared" si="326"/>
         <v/>
       </c>
-      <c r="N83" s="17" t="str">
+      <c r="N83" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A83,FALSE)</f>
         <v/>
       </c>
@@ -16028,7 +16028,7 @@
         <f t="shared" si="330"/>
         <v/>
       </c>
-      <c r="N84" s="17" t="str">
+      <c r="N84" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A84,FALSE)</f>
         <v/>
       </c>
@@ -16129,7 +16129,7 @@
         <f t="shared" si="334"/>
         <v/>
       </c>
-      <c r="N85" s="17" t="str">
+      <c r="N85" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A85,FALSE)</f>
         <v/>
       </c>
@@ -16230,7 +16230,7 @@
         <f t="shared" si="338"/>
         <v/>
       </c>
-      <c r="N86" s="17" t="str">
+      <c r="N86" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A86,FALSE)</f>
         <v/>
       </c>
@@ -16331,7 +16331,7 @@
         <f t="shared" si="342"/>
         <v/>
       </c>
-      <c r="N87" s="17" t="str">
+      <c r="N87" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A87,FALSE)</f>
         <v/>
       </c>
@@ -16432,7 +16432,7 @@
         <f t="shared" si="346"/>
         <v/>
       </c>
-      <c r="N88" s="17" t="str">
+      <c r="N88" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A88,FALSE)</f>
         <v/>
       </c>
@@ -16533,7 +16533,7 @@
         <f t="shared" si="350"/>
         <v/>
       </c>
-      <c r="N89" s="17" t="str">
+      <c r="N89" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A89,FALSE)</f>
         <v/>
       </c>
@@ -16634,7 +16634,7 @@
         <f t="shared" si="354"/>
         <v/>
       </c>
-      <c r="N90" s="17" t="str">
+      <c r="N90" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A90,FALSE)</f>
         <v/>
       </c>
@@ -16735,7 +16735,7 @@
         <f t="shared" si="358"/>
         <v/>
       </c>
-      <c r="N91" s="17" t="str">
+      <c r="N91" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A91,FALSE)</f>
         <v/>
       </c>
@@ -16836,7 +16836,7 @@
         <f t="shared" si="362"/>
         <v/>
       </c>
-      <c r="N92" s="17" t="str">
+      <c r="N92" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A92,FALSE)</f>
         <v/>
       </c>
@@ -16937,7 +16937,7 @@
         <f t="shared" si="366"/>
         <v/>
       </c>
-      <c r="N93" s="17" t="str">
+      <c r="N93" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A93,FALSE)</f>
         <v/>
       </c>
@@ -17038,7 +17038,7 @@
         <f t="shared" si="370"/>
         <v/>
       </c>
-      <c r="N94" s="17" t="str">
+      <c r="N94" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A94,FALSE)</f>
         <v/>
       </c>
@@ -17139,7 +17139,7 @@
         <f t="shared" si="374"/>
         <v/>
       </c>
-      <c r="N95" s="17" t="str">
+      <c r="N95" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A95,FALSE)</f>
         <v/>
       </c>
@@ -17240,7 +17240,7 @@
         <f t="shared" si="378"/>
         <v/>
       </c>
-      <c r="N96" s="17" t="str">
+      <c r="N96" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A96,FALSE)</f>
         <v/>
       </c>
@@ -17341,7 +17341,7 @@
         <f t="shared" si="382"/>
         <v/>
       </c>
-      <c r="N97" s="17" t="str">
+      <c r="N97" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A97,FALSE)</f>
         <v/>
       </c>
@@ -17442,7 +17442,7 @@
         <f t="shared" si="386"/>
         <v/>
       </c>
-      <c r="N98" s="17" t="str">
+      <c r="N98" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A98,FALSE)</f>
         <v/>
       </c>
@@ -17543,7 +17543,7 @@
         <f t="shared" si="390"/>
         <v/>
       </c>
-      <c r="N99" s="17" t="str">
+      <c r="N99" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A99,FALSE)</f>
         <v/>
       </c>
@@ -17644,7 +17644,7 @@
         <f t="shared" si="394"/>
         <v/>
       </c>
-      <c r="N100" s="17" t="str">
+      <c r="N100" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A100,FALSE)</f>
         <v/>
       </c>
@@ -17745,7 +17745,7 @@
         <f t="shared" si="398"/>
         <v/>
       </c>
-      <c r="N101" s="17" t="str">
+      <c r="N101" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A101,FALSE)</f>
         <v/>
       </c>
@@ -17846,7 +17846,7 @@
         <f t="shared" si="402"/>
         <v/>
       </c>
-      <c r="N102" s="17" t="str">
+      <c r="N102" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A102,FALSE)</f>
         <v/>
       </c>
@@ -17947,7 +17947,7 @@
         <f t="shared" si="406"/>
         <v/>
       </c>
-      <c r="N103" s="17" t="str">
+      <c r="N103" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A103,FALSE)</f>
         <v/>
       </c>
@@ -18048,7 +18048,7 @@
         <f t="shared" si="410"/>
         <v/>
       </c>
-      <c r="N104" s="17" t="str">
+      <c r="N104" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A104,FALSE)</f>
         <v/>
       </c>
@@ -18149,7 +18149,7 @@
         <f t="shared" si="414"/>
         <v/>
       </c>
-      <c r="N105" s="17" t="str">
+      <c r="N105" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A105,FALSE)</f>
         <v/>
       </c>
@@ -18250,7 +18250,7 @@
         <f t="shared" si="418"/>
         <v/>
       </c>
-      <c r="N106" s="17" t="str">
+      <c r="N106" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A106,FALSE)</f>
         <v/>
       </c>
@@ -18351,7 +18351,7 @@
         <f t="shared" si="422"/>
         <v/>
       </c>
-      <c r="N107" s="17" t="str">
+      <c r="N107" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A107,FALSE)</f>
         <v/>
       </c>
@@ -18452,7 +18452,7 @@
         <f t="shared" si="426"/>
         <v/>
       </c>
-      <c r="N108" s="17" t="str">
+      <c r="N108" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A108,FALSE)</f>
         <v/>
       </c>
@@ -18553,7 +18553,7 @@
         <f t="shared" si="430"/>
         <v/>
       </c>
-      <c r="N109" s="17" t="str">
+      <c r="N109" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A109,FALSE)</f>
         <v/>
       </c>
@@ -18654,7 +18654,7 @@
         <f t="shared" si="434"/>
         <v/>
       </c>
-      <c r="N110" s="17" t="str">
+      <c r="N110" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A110,FALSE)</f>
         <v/>
       </c>
@@ -18755,7 +18755,7 @@
         <f t="shared" si="438"/>
         <v/>
       </c>
-      <c r="N111" s="17" t="str">
+      <c r="N111" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A111,FALSE)</f>
         <v/>
       </c>
@@ -18856,7 +18856,7 @@
         <f t="shared" si="442"/>
         <v/>
       </c>
-      <c r="N112" s="17" t="str">
+      <c r="N112" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A112,FALSE)</f>
         <v/>
       </c>
@@ -18957,7 +18957,7 @@
         <f t="shared" si="446"/>
         <v/>
       </c>
-      <c r="N113" s="17" t="str">
+      <c r="N113" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A113,FALSE)</f>
         <v/>
       </c>
@@ -19058,7 +19058,7 @@
         <f t="shared" si="450"/>
         <v/>
       </c>
-      <c r="N114" s="17" t="str">
+      <c r="N114" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A114,FALSE)</f>
         <v/>
       </c>
@@ -19159,7 +19159,7 @@
         <f t="shared" si="454"/>
         <v/>
       </c>
-      <c r="N115" s="17" t="str">
+      <c r="N115" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A115,FALSE)</f>
         <v/>
       </c>
@@ -19260,7 +19260,7 @@
         <f t="shared" si="458"/>
         <v/>
       </c>
-      <c r="N116" s="17" t="str">
+      <c r="N116" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A116,FALSE)</f>
         <v/>
       </c>
@@ -19361,7 +19361,7 @@
         <f t="shared" si="462"/>
         <v/>
       </c>
-      <c r="N117" s="17" t="str">
+      <c r="N117" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A117,FALSE)</f>
         <v/>
       </c>
@@ -19462,7 +19462,7 @@
         <f t="shared" si="466"/>
         <v/>
       </c>
-      <c r="N118" s="17" t="str">
+      <c r="N118" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A118,FALSE)</f>
         <v/>
       </c>
@@ -19563,7 +19563,7 @@
         <f t="shared" si="470"/>
         <v/>
       </c>
-      <c r="N119" s="17" t="str">
+      <c r="N119" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A119,FALSE)</f>
         <v/>
       </c>
@@ -19664,7 +19664,7 @@
         <f t="shared" si="474"/>
         <v/>
       </c>
-      <c r="N120" s="17" t="str">
+      <c r="N120" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A120,FALSE)</f>
         <v/>
       </c>
@@ -19765,7 +19765,7 @@
         <f t="shared" si="478"/>
         <v/>
       </c>
-      <c r="N121" s="17" t="str">
+      <c r="N121" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A121,FALSE)</f>
         <v/>
       </c>
@@ -19866,7 +19866,7 @@
         <f t="shared" si="482"/>
         <v/>
       </c>
-      <c r="N122" s="17" t="str">
+      <c r="N122" s="16" t="str">
         <f>HLOOKUP(N$1,google_form!$1:$198,$A122,FALSE)</f>
         <v/>
       </c>
